--- a/Budget-Report.xlsx
+++ b/Budget-Report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orathai\Desktop\Claude Cowork\Budget Report\25690423\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9508966A-75B0-482C-8BFC-9AEC681FD998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E28E645A-F750-4972-964C-A36067B8CB42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="จำแนกตามแผนงาน" sheetId="1" r:id="rId1"/>
@@ -1823,26 +1823,26 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2172,17 +2172,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+    </row>
+    <row r="4" spans="1:18" ht="32.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
         <v>1</v>
       </c>
@@ -8375,10 +8375,10 @@
       </c>
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A115" s="24" t="s">
+      <c r="A115" s="22" t="s">
         <v>227</v>
       </c>
-      <c r="B115" s="24"/>
+      <c r="B115" s="22"/>
       <c r="C115" s="10">
         <v>220142200</v>
       </c>
@@ -16269,10 +16269,10 @@
       </c>
     </row>
     <row r="256" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A256" s="24" t="s">
+      <c r="A256" s="22" t="s">
         <v>502</v>
       </c>
-      <c r="B256" s="24"/>
+      <c r="B256" s="22"/>
       <c r="C256" s="10">
         <v>76013828.769999996</v>
       </c>
@@ -16323,10 +16323,10 @@
       </c>
     </row>
     <row r="257" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A257" s="25" t="s">
+      <c r="A257" s="23" t="s">
         <v>503</v>
       </c>
-      <c r="B257" s="25"/>
+      <c r="B257" s="23"/>
       <c r="C257" s="12">
         <v>296156028.76999998</v>
       </c>
@@ -16545,10 +16545,10 @@
       </c>
     </row>
     <row r="261" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A261" s="24" t="s">
+      <c r="A261" s="22" t="s">
         <v>510</v>
       </c>
-      <c r="B261" s="24"/>
+      <c r="B261" s="22"/>
       <c r="C261" s="10">
         <v>16725580.18</v>
       </c>
@@ -16599,10 +16599,10 @@
       </c>
     </row>
     <row r="262" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A262" s="25" t="s">
+      <c r="A262" s="23" t="s">
         <v>511</v>
       </c>
-      <c r="B262" s="25"/>
+      <c r="B262" s="23"/>
       <c r="C262" s="12">
         <v>312881608.94999999</v>
       </c>
@@ -16821,10 +16821,10 @@
       </c>
     </row>
     <row r="266" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A266" s="24" t="s">
+      <c r="A266" s="22" t="s">
         <v>518</v>
       </c>
-      <c r="B266" s="24"/>
+      <c r="B266" s="22"/>
       <c r="C266" s="10">
         <v>4037940.24</v>
       </c>
@@ -16875,10 +16875,10 @@
       </c>
     </row>
     <row r="267" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A267" s="25" t="s">
+      <c r="A267" s="23" t="s">
         <v>519</v>
       </c>
-      <c r="B267" s="25"/>
+      <c r="B267" s="23"/>
       <c r="C267" s="12">
         <v>316919549.19</v>
       </c>
@@ -17321,10 +17321,10 @@
       </c>
     </row>
     <row r="275" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A275" s="22" t="s">
+      <c r="A275" s="24" t="s">
         <v>520</v>
       </c>
-      <c r="B275" s="22"/>
+      <c r="B275" s="24"/>
       <c r="C275" s="15">
         <v>316919549.19</v>
       </c>
@@ -17375,15 +17375,28 @@
       </c>
     </row>
     <row r="276" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="O276" s="23" t="s">
+      <c r="O276" s="25" t="s">
         <v>521</v>
       </c>
-      <c r="P276" s="23"/>
-      <c r="Q276" s="23"/>
-      <c r="R276" s="23"/>
+      <c r="P276" s="25"/>
+      <c r="Q276" s="25"/>
+      <c r="R276" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="Q4:R4"/>
     <mergeCell ref="A266:B266"/>
     <mergeCell ref="A267:B267"/>
     <mergeCell ref="A275:B275"/>
@@ -17393,19 +17406,6 @@
     <mergeCell ref="A257:B257"/>
     <mergeCell ref="A261:B261"/>
     <mergeCell ref="A262:B262"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="O4:P4"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:H4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17437,17 +17437,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+    </row>
+    <row r="4" spans="1:18" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
         <v>522</v>
       </c>
@@ -19028,10 +19028,10 @@
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A33" s="24" t="s">
+      <c r="A33" s="22" t="s">
         <v>227</v>
       </c>
-      <c r="B33" s="24"/>
+      <c r="B33" s="22"/>
       <c r="C33" s="10">
         <v>220142200</v>
       </c>
@@ -20414,10 +20414,10 @@
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A58" s="24" t="s">
+      <c r="A58" s="22" t="s">
         <v>502</v>
       </c>
-      <c r="B58" s="24"/>
+      <c r="B58" s="22"/>
       <c r="C58" s="10">
         <v>76013828.769999996</v>
       </c>
@@ -20468,10 +20468,10 @@
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A59" s="25" t="s">
+      <c r="A59" s="23" t="s">
         <v>503</v>
       </c>
-      <c r="B59" s="25"/>
+      <c r="B59" s="23"/>
       <c r="C59" s="12">
         <v>296156028.76999998</v>
       </c>
@@ -20632,10 +20632,10 @@
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A62" s="24" t="s">
+      <c r="A62" s="22" t="s">
         <v>510</v>
       </c>
-      <c r="B62" s="24"/>
+      <c r="B62" s="22"/>
       <c r="C62" s="10">
         <v>16725580.18</v>
       </c>
@@ -20686,10 +20686,10 @@
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A63" s="25" t="s">
+      <c r="A63" s="23" t="s">
         <v>511</v>
       </c>
-      <c r="B63" s="25"/>
+      <c r="B63" s="23"/>
       <c r="C63" s="12">
         <v>312881608.94999999</v>
       </c>
@@ -20850,10 +20850,10 @@
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A66" s="24" t="s">
+      <c r="A66" s="22" t="s">
         <v>518</v>
       </c>
-      <c r="B66" s="24"/>
+      <c r="B66" s="22"/>
       <c r="C66" s="10">
         <v>4037940.24</v>
       </c>
@@ -20904,10 +20904,10 @@
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A67" s="25" t="s">
+      <c r="A67" s="23" t="s">
         <v>519</v>
       </c>
-      <c r="B67" s="25"/>
+      <c r="B67" s="23"/>
       <c r="C67" s="12">
         <v>316919549.19</v>
       </c>
@@ -21498,10 +21498,10 @@
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A78" s="22" t="s">
+      <c r="A78" s="24" t="s">
         <v>520</v>
       </c>
-      <c r="B78" s="22"/>
+      <c r="B78" s="24"/>
       <c r="C78" s="15">
         <v>316919549.19</v>
       </c>
@@ -21552,15 +21552,28 @@
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="O79" s="23" t="s">
+      <c r="O79" s="25" t="s">
         <v>534</v>
       </c>
-      <c r="P79" s="23"/>
-      <c r="Q79" s="23"/>
-      <c r="R79" s="23"/>
+      <c r="P79" s="25"/>
+      <c r="Q79" s="25"/>
+      <c r="R79" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="O79:R79"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="Q4:R4"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A4:A5"/>
@@ -21570,19 +21583,6 @@
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="O4:P4"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="O79:R79"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A67:B67"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Budget-Report.xlsx
+++ b/Budget-Report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orathai\Desktop\Claude Cowork\Budget Report\00 BK\25690626\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orathai\Desktop\Claude Cowork\Budget Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9D92BB7-3E0B-46FE-8BCC-DD7A2202A0F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D945D426-F09B-4CC9-AA46-E23DFA7BAB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="จำแนกตามแผนงาน" sheetId="1" r:id="rId1"/>
@@ -1730,7 +1730,7 @@
     <t>รวมทั้งสิ้น</t>
   </si>
   <si>
-    <t>( ข้อมูลระบบ ณ วันที่ 26 มิถุนายน 2569 เวลา 22:30:47 น.)</t>
+    <t>( ข้อมูลระบบ ณ วันที่ 3 กรกฎาคม 2569 เวลา 23:35:06 น.)</t>
   </si>
   <si>
     <t>สำนัก/โครงการ</t>
@@ -1769,7 +1769,7 @@
     <t>สย.</t>
   </si>
   <si>
-    <t>( ข้อมูลระบบ ณ วันที่ 26 มิถุนายน 2569 เวลา 22:33:14 น.)</t>
+    <t>( ข้อมูลระบบ ณ วันที่ 3 กรกฎาคม 2569 เวลา 23:37:40 น.)</t>
   </si>
 </sst>
 </file>
@@ -1894,7 +1894,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1976,6 +1976,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2284,23 +2287,24 @@
   <dimension ref="A1:R301"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.69921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.8984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.19921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.8984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.8984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.3984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.8984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.09765625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.3984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.8984375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.09765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24" style="28" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.69921875" style="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.8984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.19921875" style="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.3984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.8984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.3984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.796875" style="28" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.3984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.8984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.3984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.8984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.09765625" style="28" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.796875" style="28" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.3984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.8984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.09765625" style="28" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.796875" style="28"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -2314,7 +2318,7 @@
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
     </row>
-    <row r="4" spans="1:18" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
         <v>1</v>
       </c>
@@ -2422,40 +2426,40 @@
         <v>46540814</v>
       </c>
       <c r="G6" s="4">
-        <v>21663295.120000001</v>
+        <v>21481675.600000001</v>
       </c>
       <c r="H6" s="5">
-        <v>46.55</v>
+        <v>46.16</v>
       </c>
       <c r="I6" s="4">
-        <v>15514682.15</v>
+        <v>16350843.189999999</v>
       </c>
       <c r="J6" s="5">
-        <v>33.340000000000003</v>
+        <v>35.130000000000003</v>
       </c>
       <c r="K6" s="4">
-        <v>37177977.270000003</v>
+        <v>37832518.789999999</v>
       </c>
       <c r="L6" s="5">
-        <v>79.88</v>
+        <v>81.290000000000006</v>
       </c>
       <c r="M6" s="4">
-        <v>9362836.7300000004</v>
+        <v>8708295.2100000009</v>
       </c>
       <c r="N6" s="5">
-        <v>20.12</v>
+        <v>18.71</v>
       </c>
       <c r="O6" s="4">
-        <v>1966721.6</v>
+        <v>1938721.6</v>
       </c>
       <c r="P6" s="5">
-        <v>4.2300000000000004</v>
+        <v>4.17</v>
       </c>
       <c r="Q6" s="4">
-        <v>7396115.1299999999</v>
+        <v>6769573.6100000003</v>
       </c>
       <c r="R6" s="5">
-        <v>15.89</v>
+        <v>14.55</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -2478,28 +2482,28 @@
         <v>37235000</v>
       </c>
       <c r="G7" s="8">
-        <v>16834530.120000001</v>
+        <v>16601351.6</v>
       </c>
       <c r="H7" s="9">
-        <v>45.21</v>
+        <v>44.59</v>
       </c>
       <c r="I7" s="8">
-        <v>14215282.48</v>
+        <v>14809523.52</v>
       </c>
       <c r="J7" s="9">
-        <v>38.18</v>
+        <v>39.770000000000003</v>
       </c>
       <c r="K7" s="8">
-        <v>31049812.600000001</v>
+        <v>31410875.120000001</v>
       </c>
       <c r="L7" s="9">
-        <v>83.39</v>
+        <v>84.36</v>
       </c>
       <c r="M7" s="8">
-        <v>6185187.4000000004</v>
+        <v>5824124.8799999999</v>
       </c>
       <c r="N7" s="9">
-        <v>16.61</v>
+        <v>15.64</v>
       </c>
       <c r="O7" s="8">
         <v>1680000</v>
@@ -2508,10 +2512,10 @@
         <v>4.51</v>
       </c>
       <c r="Q7" s="8">
-        <v>4505187.4000000004</v>
+        <v>4144124.88</v>
       </c>
       <c r="R7" s="9">
-        <v>12.1</v>
+        <v>11.13</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -2534,10 +2538,10 @@
         <v>3500000</v>
       </c>
       <c r="G8" s="12">
-        <v>2051976.41</v>
+        <v>2052906.41</v>
       </c>
       <c r="H8" s="13">
-        <v>58.63</v>
+        <v>58.65</v>
       </c>
       <c r="I8" s="12">
         <v>38300</v>
@@ -2546,16 +2550,16 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="K8" s="12">
-        <v>2090276.41</v>
+        <v>2091206.41</v>
       </c>
       <c r="L8" s="13">
-        <v>59.72</v>
+        <v>59.75</v>
       </c>
       <c r="M8" s="12">
-        <v>1409723.59</v>
+        <v>1408793.59</v>
       </c>
       <c r="N8" s="13">
-        <v>40.28</v>
+        <v>40.25</v>
       </c>
       <c r="O8" s="12">
         <v>0</v>
@@ -2564,10 +2568,10 @@
         <v>0</v>
       </c>
       <c r="Q8" s="12">
-        <v>1409723.59</v>
+        <v>1408793.59</v>
       </c>
       <c r="R8" s="13">
-        <v>40.28</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
@@ -2590,28 +2594,28 @@
         <v>698900</v>
       </c>
       <c r="G9" s="12">
-        <v>425466</v>
+        <v>431671</v>
       </c>
       <c r="H9" s="13">
-        <v>60.88</v>
+        <v>61.76</v>
       </c>
       <c r="I9" s="12">
-        <v>18900</v>
+        <v>7900</v>
       </c>
       <c r="J9" s="13">
-        <v>2.7</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="K9" s="12">
-        <v>444366</v>
+        <v>439571</v>
       </c>
       <c r="L9" s="13">
-        <v>63.58</v>
+        <v>62.89</v>
       </c>
       <c r="M9" s="12">
-        <v>254534</v>
+        <v>259329</v>
       </c>
       <c r="N9" s="13">
-        <v>36.42</v>
+        <v>37.11</v>
       </c>
       <c r="O9" s="12">
         <v>0</v>
@@ -2620,10 +2624,10 @@
         <v>0</v>
       </c>
       <c r="Q9" s="12">
-        <v>254534</v>
+        <v>259329</v>
       </c>
       <c r="R9" s="13">
-        <v>36.42</v>
+        <v>37.11</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -2652,22 +2656,22 @@
         <v>52</v>
       </c>
       <c r="I10" s="12">
-        <v>300</v>
+        <v>478640</v>
       </c>
       <c r="J10" s="13">
-        <v>0.04</v>
+        <v>68.38</v>
       </c>
       <c r="K10" s="12">
-        <v>364276</v>
+        <v>842616</v>
       </c>
       <c r="L10" s="13">
-        <v>52.04</v>
+        <v>120.37</v>
       </c>
       <c r="M10" s="12">
-        <v>335724</v>
+        <v>-142616</v>
       </c>
       <c r="N10" s="13">
-        <v>47.96</v>
+        <v>-20.37</v>
       </c>
       <c r="O10" s="12">
         <v>95000</v>
@@ -2676,10 +2680,10 @@
         <v>13.57</v>
       </c>
       <c r="Q10" s="12">
-        <v>240724</v>
+        <v>-237616</v>
       </c>
       <c r="R10" s="13">
-        <v>34.39</v>
+        <v>-33.950000000000003</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
@@ -2814,28 +2818,28 @@
         <v>800000</v>
       </c>
       <c r="G13" s="12">
-        <v>608649.5</v>
+        <v>622419.5</v>
       </c>
       <c r="H13" s="13">
-        <v>76.08</v>
+        <v>77.8</v>
       </c>
       <c r="I13" s="12">
-        <v>130498</v>
+        <v>118878</v>
       </c>
       <c r="J13" s="13">
-        <v>16.309999999999999</v>
+        <v>14.86</v>
       </c>
       <c r="K13" s="12">
-        <v>739147.5</v>
+        <v>741297.5</v>
       </c>
       <c r="L13" s="13">
-        <v>92.39</v>
+        <v>92.66</v>
       </c>
       <c r="M13" s="12">
-        <v>60852.5</v>
+        <v>58702.5</v>
       </c>
       <c r="N13" s="13">
-        <v>7.61</v>
+        <v>7.34</v>
       </c>
       <c r="O13" s="12">
         <v>0</v>
@@ -2844,10 +2848,10 @@
         <v>0</v>
       </c>
       <c r="Q13" s="12">
-        <v>60852.5</v>
+        <v>58702.5</v>
       </c>
       <c r="R13" s="13">
-        <v>7.61</v>
+        <v>7.34</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -2870,16 +2874,16 @@
         <v>88850</v>
       </c>
       <c r="G14" s="12">
-        <v>16680</v>
+        <v>53730</v>
       </c>
       <c r="H14" s="13">
-        <v>18.77</v>
+        <v>60.47</v>
       </c>
       <c r="I14" s="12">
-        <v>53170</v>
+        <v>16120</v>
       </c>
       <c r="J14" s="13">
-        <v>59.84</v>
+        <v>18.14</v>
       </c>
       <c r="K14" s="12">
         <v>69850</v>
@@ -2926,28 +2930,28 @@
         <v>2706831.37</v>
       </c>
       <c r="G15" s="12">
-        <v>1891496.56</v>
+        <v>1563736.04</v>
       </c>
       <c r="H15" s="13">
-        <v>69.88</v>
+        <v>57.77</v>
       </c>
       <c r="I15" s="12">
-        <v>345139.48</v>
+        <v>566560.52</v>
       </c>
       <c r="J15" s="13">
-        <v>12.75</v>
+        <v>20.93</v>
       </c>
       <c r="K15" s="12">
-        <v>2236636.04</v>
+        <v>2130296.56</v>
       </c>
       <c r="L15" s="13">
-        <v>82.63</v>
+        <v>78.7</v>
       </c>
       <c r="M15" s="12">
-        <v>470195.33</v>
+        <v>576534.81000000006</v>
       </c>
       <c r="N15" s="13">
-        <v>17.37</v>
+        <v>21.3</v>
       </c>
       <c r="O15" s="12">
         <v>5000</v>
@@ -2956,10 +2960,10 @@
         <v>0.18</v>
       </c>
       <c r="Q15" s="12">
-        <v>465195.33</v>
+        <v>571534.81000000006</v>
       </c>
       <c r="R15" s="13">
-        <v>17.190000000000001</v>
+        <v>21.11</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -3100,22 +3104,22 @@
         <v>20.65</v>
       </c>
       <c r="I18" s="12">
-        <v>33240</v>
+        <v>32640</v>
       </c>
       <c r="J18" s="13">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="K18" s="12">
-        <v>270381</v>
+        <v>269781</v>
       </c>
       <c r="L18" s="13">
-        <v>23.54</v>
+        <v>23.49</v>
       </c>
       <c r="M18" s="12">
-        <v>878194.97</v>
+        <v>878794.97</v>
       </c>
       <c r="N18" s="13">
-        <v>76.459999999999994</v>
+        <v>76.510000000000005</v>
       </c>
       <c r="O18" s="12">
         <v>0</v>
@@ -3124,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="Q18" s="12">
-        <v>878194.97</v>
+        <v>878794.97</v>
       </c>
       <c r="R18" s="13">
-        <v>76.459999999999994</v>
+        <v>76.510000000000005</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
@@ -3206,28 +3210,28 @@
         <v>179733</v>
       </c>
       <c r="G20" s="12">
-        <v>127129</v>
+        <v>153906</v>
       </c>
       <c r="H20" s="13">
-        <v>70.73</v>
+        <v>85.63</v>
       </c>
       <c r="I20" s="12">
-        <v>32500</v>
+        <v>0</v>
       </c>
       <c r="J20" s="13">
-        <v>18.079999999999998</v>
+        <v>0</v>
       </c>
       <c r="K20" s="12">
-        <v>159629</v>
+        <v>153906</v>
       </c>
       <c r="L20" s="13">
-        <v>88.81</v>
+        <v>85.63</v>
       </c>
       <c r="M20" s="12">
-        <v>20104</v>
+        <v>25827</v>
       </c>
       <c r="N20" s="13">
-        <v>11.19</v>
+        <v>14.37</v>
       </c>
       <c r="O20" s="12">
         <v>0</v>
@@ -3236,10 +3240,10 @@
         <v>0</v>
       </c>
       <c r="Q20" s="12">
-        <v>20104</v>
+        <v>25827</v>
       </c>
       <c r="R20" s="13">
-        <v>11.19</v>
+        <v>14.37</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -3598,28 +3602,28 @@
         <v>330355</v>
       </c>
       <c r="G27" s="12">
-        <v>96814.6</v>
+        <v>106664.6</v>
       </c>
       <c r="H27" s="13">
-        <v>29.31</v>
+        <v>32.29</v>
       </c>
       <c r="I27" s="12">
-        <v>14585</v>
+        <v>1835</v>
       </c>
       <c r="J27" s="13">
-        <v>4.41</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="K27" s="12">
-        <v>111399.6</v>
+        <v>108499.6</v>
       </c>
       <c r="L27" s="13">
-        <v>33.72</v>
+        <v>32.840000000000003</v>
       </c>
       <c r="M27" s="12">
-        <v>218955.4</v>
+        <v>221855.4</v>
       </c>
       <c r="N27" s="13">
-        <v>66.28</v>
+        <v>67.16</v>
       </c>
       <c r="O27" s="12">
         <v>0</v>
@@ -3628,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="Q27" s="12">
-        <v>218955.4</v>
+        <v>221855.4</v>
       </c>
       <c r="R27" s="13">
-        <v>66.28</v>
+        <v>67.16</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -3654,34 +3658,34 @@
         <v>4260000</v>
       </c>
       <c r="G28" s="8">
-        <v>1698170.43</v>
+        <v>1700370.43</v>
       </c>
       <c r="H28" s="9">
-        <v>39.86</v>
+        <v>39.909999999999997</v>
       </c>
       <c r="I28" s="8">
-        <v>554621.67000000004</v>
+        <v>580421.67000000004</v>
       </c>
       <c r="J28" s="9">
-        <v>13.02</v>
+        <v>13.62</v>
       </c>
       <c r="K28" s="8">
-        <v>2252792.1</v>
+        <v>2280792.1</v>
       </c>
       <c r="L28" s="9">
-        <v>52.88</v>
+        <v>53.54</v>
       </c>
       <c r="M28" s="8">
-        <v>2007207.9</v>
+        <v>1979207.9</v>
       </c>
       <c r="N28" s="9">
-        <v>47.12</v>
+        <v>46.46</v>
       </c>
       <c r="O28" s="8">
-        <v>282000</v>
+        <v>254000</v>
       </c>
       <c r="P28" s="9">
-        <v>6.62</v>
+        <v>5.96</v>
       </c>
       <c r="Q28" s="8">
         <v>1725207.9</v>
@@ -3766,16 +3770,16 @@
         <v>1000000</v>
       </c>
       <c r="G30" s="12">
-        <v>117165.8</v>
+        <v>119365.8</v>
       </c>
       <c r="H30" s="13">
-        <v>11.72</v>
+        <v>11.94</v>
       </c>
       <c r="I30" s="12">
-        <v>32200</v>
+        <v>30000</v>
       </c>
       <c r="J30" s="13">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="K30" s="12">
         <v>149365.79999999999</v>
@@ -3884,28 +3888,28 @@
         <v>194.3</v>
       </c>
       <c r="I32" s="12">
-        <v>426896.67</v>
+        <v>454896.67</v>
       </c>
       <c r="J32" s="13">
-        <v>106.72</v>
+        <v>113.72</v>
       </c>
       <c r="K32" s="12">
-        <v>1204091.43</v>
+        <v>1232091.43</v>
       </c>
       <c r="L32" s="13">
-        <v>301.02</v>
+        <v>308.02</v>
       </c>
       <c r="M32" s="12">
-        <v>-804091.43</v>
+        <v>-832091.43</v>
       </c>
       <c r="N32" s="13">
-        <v>-201.02</v>
+        <v>-208.02</v>
       </c>
       <c r="O32" s="12">
-        <v>30000</v>
+        <v>2000</v>
       </c>
       <c r="P32" s="13">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="Q32" s="12">
         <v>-834091.43</v>
@@ -3996,22 +4000,22 @@
         <v>81.48</v>
       </c>
       <c r="I34" s="8">
-        <v>156070</v>
+        <v>150000</v>
       </c>
       <c r="J34" s="9">
-        <v>20.73</v>
+        <v>19.920000000000002</v>
       </c>
       <c r="K34" s="8">
-        <v>769520</v>
+        <v>763450</v>
       </c>
       <c r="L34" s="9">
-        <v>102.21</v>
+        <v>101.4</v>
       </c>
       <c r="M34" s="8">
-        <v>-16620</v>
+        <v>-10550</v>
       </c>
       <c r="N34" s="9">
-        <v>-2.21</v>
+        <v>-1.4</v>
       </c>
       <c r="O34" s="8">
         <v>0</v>
@@ -4020,10 +4024,10 @@
         <v>0</v>
       </c>
       <c r="Q34" s="8">
-        <v>-16620</v>
+        <v>-10550</v>
       </c>
       <c r="R34" s="9">
-        <v>-2.21</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -4052,22 +4056,22 @@
         <v>81.48</v>
       </c>
       <c r="I35" s="12">
-        <v>156070</v>
+        <v>150000</v>
       </c>
       <c r="J35" s="13">
-        <v>20.73</v>
+        <v>19.920000000000002</v>
       </c>
       <c r="K35" s="12">
-        <v>769520</v>
+        <v>763450</v>
       </c>
       <c r="L35" s="13">
-        <v>102.21</v>
+        <v>101.4</v>
       </c>
       <c r="M35" s="12">
-        <v>-16620</v>
+        <v>-10550</v>
       </c>
       <c r="N35" s="13">
-        <v>-2.21</v>
+        <v>-1.4</v>
       </c>
       <c r="O35" s="12">
         <v>0</v>
@@ -4076,10 +4080,10 @@
         <v>0</v>
       </c>
       <c r="Q35" s="12">
-        <v>-16620</v>
+        <v>-10550</v>
       </c>
       <c r="R35" s="13">
-        <v>-2.21</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="36" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -4102,28 +4106,28 @@
         <v>500000</v>
       </c>
       <c r="G36" s="8">
-        <v>343308.9</v>
+        <v>357667.9</v>
       </c>
       <c r="H36" s="9">
-        <v>68.66</v>
+        <v>71.53</v>
       </c>
       <c r="I36" s="8">
-        <v>137550</v>
+        <v>118800</v>
       </c>
       <c r="J36" s="9">
-        <v>27.51</v>
+        <v>23.76</v>
       </c>
       <c r="K36" s="8">
-        <v>480858.9</v>
+        <v>476467.9</v>
       </c>
       <c r="L36" s="9">
-        <v>96.17</v>
+        <v>95.29</v>
       </c>
       <c r="M36" s="8">
-        <v>19141.099999999999</v>
+        <v>23532.1</v>
       </c>
       <c r="N36" s="9">
-        <v>3.83</v>
+        <v>4.71</v>
       </c>
       <c r="O36" s="8">
         <v>4721.6000000000004</v>
@@ -4132,10 +4136,10 @@
         <v>0.94</v>
       </c>
       <c r="Q36" s="8">
-        <v>14419.5</v>
+        <v>18810.5</v>
       </c>
       <c r="R36" s="9">
-        <v>2.88</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="37" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -4158,28 +4162,28 @@
         <v>400000</v>
       </c>
       <c r="G37" s="12">
-        <v>281520.90000000002</v>
+        <v>295879.90000000002</v>
       </c>
       <c r="H37" s="13">
-        <v>70.38</v>
+        <v>73.97</v>
       </c>
       <c r="I37" s="12">
-        <v>99550</v>
+        <v>80800</v>
       </c>
       <c r="J37" s="13">
-        <v>24.89</v>
+        <v>20.2</v>
       </c>
       <c r="K37" s="12">
-        <v>381070.9</v>
+        <v>376679.9</v>
       </c>
       <c r="L37" s="13">
-        <v>95.27</v>
+        <v>94.17</v>
       </c>
       <c r="M37" s="12">
-        <v>18929.099999999999</v>
+        <v>23320.1</v>
       </c>
       <c r="N37" s="13">
-        <v>4.7300000000000004</v>
+        <v>5.83</v>
       </c>
       <c r="O37" s="12">
         <v>4721.6000000000004</v>
@@ -4188,10 +4192,10 @@
         <v>1.18</v>
       </c>
       <c r="Q37" s="12">
-        <v>14207.5</v>
+        <v>18598.5</v>
       </c>
       <c r="R37" s="13">
-        <v>3.55</v>
+        <v>4.6500000000000004</v>
       </c>
     </row>
     <row r="38" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -4270,28 +4274,28 @@
         <v>1180000</v>
       </c>
       <c r="G39" s="8">
-        <v>603349</v>
+        <v>638349</v>
       </c>
       <c r="H39" s="9">
-        <v>51.13</v>
+        <v>54.1</v>
       </c>
       <c r="I39" s="8">
-        <v>35800</v>
+        <v>277000</v>
       </c>
       <c r="J39" s="9">
-        <v>3.03</v>
+        <v>23.47</v>
       </c>
       <c r="K39" s="8">
-        <v>639149</v>
+        <v>915349</v>
       </c>
       <c r="L39" s="9">
-        <v>54.17</v>
+        <v>77.569999999999993</v>
       </c>
       <c r="M39" s="8">
-        <v>540851</v>
+        <v>264651</v>
       </c>
       <c r="N39" s="9">
-        <v>45.83</v>
+        <v>22.43</v>
       </c>
       <c r="O39" s="8">
         <v>0</v>
@@ -4300,10 +4304,10 @@
         <v>0</v>
       </c>
       <c r="Q39" s="8">
-        <v>540851</v>
+        <v>264651</v>
       </c>
       <c r="R39" s="9">
-        <v>45.83</v>
+        <v>22.43</v>
       </c>
     </row>
     <row r="40" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -4332,22 +4336,22 @@
         <v>72.2</v>
       </c>
       <c r="I40" s="12">
-        <v>0</v>
+        <v>277000</v>
       </c>
       <c r="J40" s="13">
-        <v>0</v>
+        <v>69.25</v>
       </c>
       <c r="K40" s="12">
-        <v>288811</v>
+        <v>565811</v>
       </c>
       <c r="L40" s="13">
-        <v>72.2</v>
+        <v>141.44999999999999</v>
       </c>
       <c r="M40" s="12">
-        <v>111189</v>
+        <v>-165811</v>
       </c>
       <c r="N40" s="13">
-        <v>27.8</v>
+        <v>-41.45</v>
       </c>
       <c r="O40" s="12">
         <v>0</v>
@@ -4356,10 +4360,10 @@
         <v>0</v>
       </c>
       <c r="Q40" s="12">
-        <v>111189</v>
+        <v>-165811</v>
       </c>
       <c r="R40" s="13">
-        <v>27.8</v>
+        <v>-41.45</v>
       </c>
     </row>
     <row r="41" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -4382,28 +4386,28 @@
         <v>780000</v>
       </c>
       <c r="G41" s="12">
-        <v>314538</v>
+        <v>349538</v>
       </c>
       <c r="H41" s="13">
-        <v>40.33</v>
+        <v>44.81</v>
       </c>
       <c r="I41" s="12">
-        <v>35800</v>
+        <v>0</v>
       </c>
       <c r="J41" s="13">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="K41" s="12">
-        <v>350338</v>
+        <v>349538</v>
       </c>
       <c r="L41" s="13">
-        <v>44.92</v>
+        <v>44.81</v>
       </c>
       <c r="M41" s="12">
-        <v>429662</v>
+        <v>430462</v>
       </c>
       <c r="N41" s="13">
-        <v>55.08</v>
+        <v>55.19</v>
       </c>
       <c r="O41" s="12">
         <v>0</v>
@@ -4412,10 +4416,10 @@
         <v>0</v>
       </c>
       <c r="Q41" s="12">
-        <v>429662</v>
+        <v>430462</v>
       </c>
       <c r="R41" s="13">
-        <v>55.08</v>
+        <v>55.19</v>
       </c>
     </row>
     <row r="42" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -4444,22 +4448,22 @@
         <v>60.1</v>
       </c>
       <c r="I42" s="8">
-        <v>415358</v>
+        <v>415098</v>
       </c>
       <c r="J42" s="9">
-        <v>15.9</v>
+        <v>15.89</v>
       </c>
       <c r="K42" s="8">
-        <v>1985844.67</v>
+        <v>1985584.67</v>
       </c>
       <c r="L42" s="9">
-        <v>76</v>
+        <v>75.989999999999995</v>
       </c>
       <c r="M42" s="8">
-        <v>627069.32999999996</v>
+        <v>627329.32999999996</v>
       </c>
       <c r="N42" s="9">
-        <v>24</v>
+        <v>24.01</v>
       </c>
       <c r="O42" s="8">
         <v>0</v>
@@ -4468,10 +4472,10 @@
         <v>0</v>
       </c>
       <c r="Q42" s="8">
-        <v>627069.32999999996</v>
+        <v>627329.32999999996</v>
       </c>
       <c r="R42" s="9">
-        <v>24</v>
+        <v>24.01</v>
       </c>
     </row>
     <row r="43" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -4668,22 +4672,22 @@
         <v>57.33</v>
       </c>
       <c r="I46" s="12">
-        <v>4700</v>
+        <v>4440</v>
       </c>
       <c r="J46" s="13">
-        <v>2.2599999999999998</v>
+        <v>2.13</v>
       </c>
       <c r="K46" s="12">
-        <v>124170</v>
+        <v>123910</v>
       </c>
       <c r="L46" s="13">
-        <v>59.58</v>
+        <v>59.46</v>
       </c>
       <c r="M46" s="12">
-        <v>84230</v>
+        <v>84490</v>
       </c>
       <c r="N46" s="13">
-        <v>40.42</v>
+        <v>40.54</v>
       </c>
       <c r="O46" s="12">
         <v>0</v>
@@ -4692,10 +4696,10 @@
         <v>0</v>
       </c>
       <c r="Q46" s="12">
-        <v>84230</v>
+        <v>84490</v>
       </c>
       <c r="R46" s="13">
-        <v>40.42</v>
+        <v>40.54</v>
       </c>
     </row>
     <row r="47" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -4718,40 +4722,40 @@
         <v>54940200</v>
       </c>
       <c r="G47" s="4">
-        <v>37757627.240000002</v>
+        <v>38494573.619999997</v>
       </c>
       <c r="H47" s="5">
-        <v>68.72</v>
+        <v>70.069999999999993</v>
       </c>
       <c r="I47" s="4">
-        <v>6722008.2599999998</v>
+        <v>5999195.7599999998</v>
       </c>
       <c r="J47" s="5">
-        <v>12.24</v>
+        <v>10.92</v>
       </c>
       <c r="K47" s="4">
-        <v>44479635.5</v>
+        <v>44493769.380000003</v>
       </c>
       <c r="L47" s="5">
-        <v>80.959999999999994</v>
+        <v>80.989999999999995</v>
       </c>
       <c r="M47" s="4">
-        <v>10460564.5</v>
+        <v>10446430.619999999</v>
       </c>
       <c r="N47" s="5">
-        <v>19.04</v>
+        <v>19.010000000000002</v>
       </c>
       <c r="O47" s="4">
-        <v>390422.5</v>
+        <v>1046422.5</v>
       </c>
       <c r="P47" s="5">
-        <v>0.71</v>
+        <v>1.9</v>
       </c>
       <c r="Q47" s="4">
-        <v>10070142</v>
+        <v>9400008.1199999992</v>
       </c>
       <c r="R47" s="5">
-        <v>18.329999999999998</v>
+        <v>17.11</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -4774,40 +4778,40 @@
         <v>11340200</v>
       </c>
       <c r="G48" s="8">
-        <v>7633387.6399999997</v>
+        <v>8405804.9600000009</v>
       </c>
       <c r="H48" s="9">
-        <v>67.31</v>
+        <v>74.12</v>
       </c>
       <c r="I48" s="8">
-        <v>1983542.67</v>
+        <v>1337047.3500000001</v>
       </c>
       <c r="J48" s="9">
-        <v>17.489999999999998</v>
+        <v>11.79</v>
       </c>
       <c r="K48" s="8">
-        <v>9616930.3100000005</v>
+        <v>9742852.3100000005</v>
       </c>
       <c r="L48" s="9">
-        <v>84.8</v>
+        <v>85.91</v>
       </c>
       <c r="M48" s="8">
-        <v>1723269.69</v>
+        <v>1597347.69</v>
       </c>
       <c r="N48" s="9">
-        <v>15.2</v>
+        <v>14.09</v>
       </c>
       <c r="O48" s="8">
-        <v>114079.5</v>
+        <v>140079.5</v>
       </c>
       <c r="P48" s="9">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="Q48" s="8">
-        <v>1609190.19</v>
+        <v>1457268.19</v>
       </c>
       <c r="R48" s="9">
-        <v>14.19</v>
+        <v>12.85</v>
       </c>
     </row>
     <row r="49" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -4830,40 +4834,40 @@
         <v>1300000</v>
       </c>
       <c r="G49" s="12">
-        <v>737219.5</v>
+        <v>848130.5</v>
       </c>
       <c r="H49" s="13">
-        <v>56.71</v>
+        <v>65.239999999999995</v>
       </c>
       <c r="I49" s="12">
-        <v>178000</v>
+        <v>127000</v>
       </c>
       <c r="J49" s="13">
-        <v>13.69</v>
+        <v>9.77</v>
       </c>
       <c r="K49" s="12">
-        <v>915219.5</v>
+        <v>975130.5</v>
       </c>
       <c r="L49" s="13">
-        <v>70.400000000000006</v>
+        <v>75.010000000000005</v>
       </c>
       <c r="M49" s="12">
-        <v>384780.5</v>
+        <v>324869.5</v>
       </c>
       <c r="N49" s="13">
-        <v>29.6</v>
+        <v>24.99</v>
       </c>
       <c r="O49" s="12">
-        <v>64000</v>
+        <v>90000</v>
       </c>
       <c r="P49" s="13">
-        <v>4.92</v>
+        <v>6.92</v>
       </c>
       <c r="Q49" s="12">
-        <v>320780.5</v>
+        <v>234869.5</v>
       </c>
       <c r="R49" s="13">
-        <v>24.68</v>
+        <v>18.07</v>
       </c>
     </row>
     <row r="50" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -4886,16 +4890,16 @@
         <v>3200000</v>
       </c>
       <c r="G50" s="12">
-        <v>2419790</v>
+        <v>2859790</v>
       </c>
       <c r="H50" s="13">
-        <v>75.62</v>
+        <v>89.37</v>
       </c>
       <c r="I50" s="12">
-        <v>756800</v>
+        <v>316800</v>
       </c>
       <c r="J50" s="13">
-        <v>23.65</v>
+        <v>9.9</v>
       </c>
       <c r="K50" s="12">
         <v>3176590</v>
@@ -4942,28 +4946,28 @@
         <v>4320000</v>
       </c>
       <c r="G51" s="12">
-        <v>2449753.38</v>
+        <v>2602484.7000000002</v>
       </c>
       <c r="H51" s="13">
-        <v>56.71</v>
+        <v>60.24</v>
       </c>
       <c r="I51" s="12">
-        <v>798352.67</v>
+        <v>703267.35</v>
       </c>
       <c r="J51" s="13">
-        <v>18.48</v>
+        <v>16.28</v>
       </c>
       <c r="K51" s="12">
-        <v>3248106.05</v>
+        <v>3305752.05</v>
       </c>
       <c r="L51" s="13">
-        <v>75.19</v>
+        <v>76.52</v>
       </c>
       <c r="M51" s="12">
-        <v>1071893.95</v>
+        <v>1014247.95</v>
       </c>
       <c r="N51" s="13">
-        <v>24.81</v>
+        <v>23.48</v>
       </c>
       <c r="O51" s="12">
         <v>0</v>
@@ -4972,10 +4976,10 @@
         <v>0</v>
       </c>
       <c r="Q51" s="12">
-        <v>1071893.95</v>
+        <v>1014247.95</v>
       </c>
       <c r="R51" s="13">
-        <v>24.81</v>
+        <v>23.48</v>
       </c>
     </row>
     <row r="52" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -4998,28 +5002,28 @@
         <v>2020200</v>
       </c>
       <c r="G52" s="12">
-        <v>1691181</v>
+        <v>1729956</v>
       </c>
       <c r="H52" s="13">
-        <v>83.71</v>
+        <v>85.63</v>
       </c>
       <c r="I52" s="12">
-        <v>220390</v>
+        <v>189980</v>
       </c>
       <c r="J52" s="13">
-        <v>10.91</v>
+        <v>9.4</v>
       </c>
       <c r="K52" s="12">
-        <v>1911571</v>
+        <v>1919936</v>
       </c>
       <c r="L52" s="13">
-        <v>94.62</v>
+        <v>95.04</v>
       </c>
       <c r="M52" s="12">
-        <v>108629</v>
+        <v>100264</v>
       </c>
       <c r="N52" s="13">
-        <v>5.38</v>
+        <v>4.96</v>
       </c>
       <c r="O52" s="12">
         <v>20079.5</v>
@@ -5028,10 +5032,10 @@
         <v>0.99</v>
       </c>
       <c r="Q52" s="12">
-        <v>88549.5</v>
+        <v>80184.5</v>
       </c>
       <c r="R52" s="13">
-        <v>4.38</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="53" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -5054,16 +5058,16 @@
         <v>500000</v>
       </c>
       <c r="G53" s="12">
-        <v>335443.76</v>
+        <v>365443.76</v>
       </c>
       <c r="H53" s="13">
-        <v>67.09</v>
+        <v>73.09</v>
       </c>
       <c r="I53" s="12">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="J53" s="13">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K53" s="12">
         <v>365443.76</v>
@@ -5110,28 +5114,28 @@
         <v>13420000</v>
       </c>
       <c r="G54" s="8">
-        <v>9719269.5700000003</v>
+        <v>9438778.7699999996</v>
       </c>
       <c r="H54" s="9">
-        <v>72.42</v>
+        <v>70.33</v>
       </c>
       <c r="I54" s="8">
-        <v>1232465.5900000001</v>
+        <v>1649419.41</v>
       </c>
       <c r="J54" s="9">
-        <v>9.18</v>
+        <v>12.29</v>
       </c>
       <c r="K54" s="8">
-        <v>10951735.16</v>
+        <v>11088198.18</v>
       </c>
       <c r="L54" s="9">
-        <v>81.61</v>
+        <v>82.62</v>
       </c>
       <c r="M54" s="8">
-        <v>2468264.84</v>
+        <v>2331801.8199999998</v>
       </c>
       <c r="N54" s="9">
-        <v>18.39</v>
+        <v>17.38</v>
       </c>
       <c r="O54" s="8">
         <v>275743</v>
@@ -5140,10 +5144,10 @@
         <v>2.0499999999999998</v>
       </c>
       <c r="Q54" s="8">
-        <v>2192521.84</v>
+        <v>2056058.82</v>
       </c>
       <c r="R54" s="9">
-        <v>16.34</v>
+        <v>15.32</v>
       </c>
     </row>
     <row r="55" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -5222,28 +5226,28 @@
         <v>2700000</v>
       </c>
       <c r="G56" s="12">
-        <v>1637006.55</v>
+        <v>1717164.55</v>
       </c>
       <c r="H56" s="13">
-        <v>60.63</v>
+        <v>63.6</v>
       </c>
       <c r="I56" s="12">
-        <v>419954</v>
+        <v>419454</v>
       </c>
       <c r="J56" s="13">
-        <v>15.55</v>
+        <v>15.54</v>
       </c>
       <c r="K56" s="12">
-        <v>2056960.55</v>
+        <v>2136618.5499999998</v>
       </c>
       <c r="L56" s="13">
-        <v>76.180000000000007</v>
+        <v>79.13</v>
       </c>
       <c r="M56" s="12">
-        <v>643039.44999999995</v>
+        <v>563381.44999999995</v>
       </c>
       <c r="N56" s="13">
-        <v>23.82</v>
+        <v>20.87</v>
       </c>
       <c r="O56" s="12">
         <v>160000</v>
@@ -5252,10 +5256,10 @@
         <v>5.93</v>
       </c>
       <c r="Q56" s="12">
-        <v>483039.45</v>
+        <v>403381.45</v>
       </c>
       <c r="R56" s="13">
-        <v>17.89</v>
+        <v>14.94</v>
       </c>
     </row>
     <row r="57" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -5278,28 +5282,28 @@
         <v>3400000</v>
       </c>
       <c r="G57" s="12">
-        <v>2396458.75</v>
+        <v>2440838.36</v>
       </c>
       <c r="H57" s="13">
-        <v>70.48</v>
+        <v>71.790000000000006</v>
       </c>
       <c r="I57" s="12">
-        <v>348840</v>
+        <v>373400</v>
       </c>
       <c r="J57" s="13">
-        <v>10.26</v>
+        <v>10.98</v>
       </c>
       <c r="K57" s="12">
-        <v>2745298.75</v>
+        <v>2814238.36</v>
       </c>
       <c r="L57" s="13">
-        <v>80.739999999999995</v>
+        <v>82.77</v>
       </c>
       <c r="M57" s="12">
-        <v>654701.25</v>
+        <v>585761.64</v>
       </c>
       <c r="N57" s="13">
-        <v>19.260000000000002</v>
+        <v>17.23</v>
       </c>
       <c r="O57" s="12">
         <v>0</v>
@@ -5308,10 +5312,10 @@
         <v>0</v>
       </c>
       <c r="Q57" s="12">
-        <v>654701.25</v>
+        <v>585761.64</v>
       </c>
       <c r="R57" s="13">
-        <v>19.260000000000002</v>
+        <v>17.23</v>
       </c>
     </row>
     <row r="58" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -5502,28 +5506,28 @@
         <v>2600000</v>
       </c>
       <c r="G61" s="12">
-        <v>1593977.22</v>
+        <v>1188948.81</v>
       </c>
       <c r="H61" s="13">
-        <v>61.31</v>
+        <v>45.73</v>
       </c>
       <c r="I61" s="12">
-        <v>63671.59</v>
+        <v>456565.41</v>
       </c>
       <c r="J61" s="13">
-        <v>2.4500000000000002</v>
+        <v>17.559999999999999</v>
       </c>
       <c r="K61" s="12">
-        <v>1657648.81</v>
+        <v>1645514.22</v>
       </c>
       <c r="L61" s="13">
-        <v>63.76</v>
+        <v>63.29</v>
       </c>
       <c r="M61" s="12">
-        <v>942351.19</v>
+        <v>954485.78</v>
       </c>
       <c r="N61" s="13">
-        <v>36.24</v>
+        <v>36.71</v>
       </c>
       <c r="O61" s="12">
         <v>115743</v>
@@ -5532,10 +5536,10 @@
         <v>4.45</v>
       </c>
       <c r="Q61" s="12">
-        <v>826608.19</v>
+        <v>838742.78</v>
       </c>
       <c r="R61" s="13">
-        <v>31.79</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="62" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -5726,28 +5730,28 @@
         <v>11720000</v>
       </c>
       <c r="G65" s="8">
-        <v>7555576</v>
+        <v>7481436</v>
       </c>
       <c r="H65" s="9">
-        <v>64.47</v>
+        <v>63.83</v>
       </c>
       <c r="I65" s="8">
-        <v>1610493</v>
+        <v>1458873</v>
       </c>
       <c r="J65" s="9">
-        <v>13.74</v>
+        <v>12.45</v>
       </c>
       <c r="K65" s="8">
-        <v>9166069</v>
+        <v>8940309</v>
       </c>
       <c r="L65" s="9">
-        <v>78.209999999999994</v>
+        <v>76.28</v>
       </c>
       <c r="M65" s="8">
-        <v>2553931</v>
+        <v>2779691</v>
       </c>
       <c r="N65" s="9">
-        <v>21.79</v>
+        <v>23.72</v>
       </c>
       <c r="O65" s="8">
         <v>600</v>
@@ -5756,10 +5760,10 @@
         <v>0.01</v>
       </c>
       <c r="Q65" s="8">
-        <v>2553331</v>
+        <v>2779091</v>
       </c>
       <c r="R65" s="9">
-        <v>21.79</v>
+        <v>23.71</v>
       </c>
     </row>
     <row r="66" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -5838,28 +5842,28 @@
         <v>1775000</v>
       </c>
       <c r="G67" s="12">
-        <v>495887</v>
+        <v>533437</v>
       </c>
       <c r="H67" s="13">
-        <v>27.94</v>
+        <v>30.05</v>
       </c>
       <c r="I67" s="12">
-        <v>192900</v>
+        <v>139200</v>
       </c>
       <c r="J67" s="13">
-        <v>10.87</v>
+        <v>7.84</v>
       </c>
       <c r="K67" s="12">
-        <v>688787</v>
+        <v>672637</v>
       </c>
       <c r="L67" s="13">
-        <v>38.799999999999997</v>
+        <v>37.9</v>
       </c>
       <c r="M67" s="12">
-        <v>1086213</v>
+        <v>1102363</v>
       </c>
       <c r="N67" s="13">
-        <v>61.2</v>
+        <v>62.1</v>
       </c>
       <c r="O67" s="12">
         <v>0</v>
@@ -5868,10 +5872,10 @@
         <v>0</v>
       </c>
       <c r="Q67" s="12">
-        <v>1086213</v>
+        <v>1102363</v>
       </c>
       <c r="R67" s="13">
-        <v>61.2</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="68" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -5894,28 +5898,28 @@
         <v>2820000</v>
       </c>
       <c r="G68" s="12">
-        <v>1959989</v>
+        <v>1848299</v>
       </c>
       <c r="H68" s="13">
-        <v>69.5</v>
+        <v>65.540000000000006</v>
       </c>
       <c r="I68" s="12">
-        <v>573064</v>
+        <v>475144</v>
       </c>
       <c r="J68" s="13">
-        <v>20.32</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="K68" s="12">
-        <v>2533053</v>
+        <v>2323443</v>
       </c>
       <c r="L68" s="13">
-        <v>89.82</v>
+        <v>82.39</v>
       </c>
       <c r="M68" s="12">
-        <v>286947</v>
+        <v>496557</v>
       </c>
       <c r="N68" s="13">
-        <v>10.18</v>
+        <v>17.61</v>
       </c>
       <c r="O68" s="12">
         <v>600</v>
@@ -5924,10 +5928,10 @@
         <v>0.02</v>
       </c>
       <c r="Q68" s="12">
-        <v>286347</v>
+        <v>495957</v>
       </c>
       <c r="R68" s="13">
-        <v>10.15</v>
+        <v>17.59</v>
       </c>
     </row>
     <row r="69" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -6062,40 +6066,40 @@
         <v>10640000</v>
       </c>
       <c r="G71" s="8">
-        <v>7531415.4299999997</v>
+        <v>7810024.29</v>
       </c>
       <c r="H71" s="9">
-        <v>70.78</v>
+        <v>73.400000000000006</v>
       </c>
       <c r="I71" s="8">
-        <v>1245497</v>
+        <v>950197</v>
       </c>
       <c r="J71" s="9">
-        <v>11.71</v>
+        <v>8.93</v>
       </c>
       <c r="K71" s="8">
-        <v>8776912.4299999997</v>
+        <v>8760221.2899999991</v>
       </c>
       <c r="L71" s="9">
-        <v>82.49</v>
+        <v>82.33</v>
       </c>
       <c r="M71" s="8">
-        <v>1863087.57</v>
+        <v>1879778.71</v>
       </c>
       <c r="N71" s="9">
-        <v>17.510000000000002</v>
+        <v>17.670000000000002</v>
       </c>
       <c r="O71" s="8">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="P71" s="9">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="Q71" s="8">
-        <v>1863087.57</v>
+        <v>1799778.71</v>
       </c>
       <c r="R71" s="9">
-        <v>17.510000000000002</v>
+        <v>16.920000000000002</v>
       </c>
     </row>
     <row r="72" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -6124,22 +6128,22 @@
         <v>53.58</v>
       </c>
       <c r="I72" s="12">
-        <v>209510</v>
+        <v>207510</v>
       </c>
       <c r="J72" s="13">
-        <v>18.38</v>
+        <v>18.2</v>
       </c>
       <c r="K72" s="12">
-        <v>820364.22</v>
+        <v>818364.22</v>
       </c>
       <c r="L72" s="13">
-        <v>71.959999999999994</v>
+        <v>71.790000000000006</v>
       </c>
       <c r="M72" s="12">
-        <v>319635.78000000003</v>
+        <v>321635.78000000003</v>
       </c>
       <c r="N72" s="13">
-        <v>28.04</v>
+        <v>28.21</v>
       </c>
       <c r="O72" s="12">
         <v>0</v>
@@ -6148,10 +6152,10 @@
         <v>0</v>
       </c>
       <c r="Q72" s="12">
-        <v>319635.78000000003</v>
+        <v>321635.78000000003</v>
       </c>
       <c r="R72" s="13">
-        <v>28.04</v>
+        <v>28.21</v>
       </c>
     </row>
     <row r="73" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -6174,28 +6178,28 @@
         <v>2200000</v>
       </c>
       <c r="G73" s="12">
-        <v>1832390.51</v>
+        <v>1962809.37</v>
       </c>
       <c r="H73" s="13">
-        <v>83.29</v>
+        <v>89.22</v>
       </c>
       <c r="I73" s="12">
-        <v>133730</v>
+        <v>2630</v>
       </c>
       <c r="J73" s="13">
-        <v>6.08</v>
+        <v>0.12</v>
       </c>
       <c r="K73" s="12">
-        <v>1966120.51</v>
+        <v>1965439.37</v>
       </c>
       <c r="L73" s="13">
-        <v>89.37</v>
+        <v>89.34</v>
       </c>
       <c r="M73" s="12">
-        <v>233879.49</v>
+        <v>234560.63</v>
       </c>
       <c r="N73" s="13">
-        <v>10.63</v>
+        <v>10.66</v>
       </c>
       <c r="O73" s="12">
         <v>0</v>
@@ -6204,10 +6208,10 @@
         <v>0</v>
       </c>
       <c r="Q73" s="12">
-        <v>233879.49</v>
+        <v>234560.63</v>
       </c>
       <c r="R73" s="13">
-        <v>10.63</v>
+        <v>10.66</v>
       </c>
     </row>
     <row r="74" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -6230,40 +6234,40 @@
         <v>700000</v>
       </c>
       <c r="G74" s="12">
-        <v>394251</v>
+        <v>434411</v>
       </c>
       <c r="H74" s="13">
-        <v>56.32</v>
+        <v>62.06</v>
       </c>
       <c r="I74" s="12">
-        <v>42400</v>
+        <v>0</v>
       </c>
       <c r="J74" s="13">
-        <v>6.06</v>
+        <v>0</v>
       </c>
       <c r="K74" s="12">
-        <v>436651</v>
+        <v>434411</v>
       </c>
       <c r="L74" s="13">
-        <v>62.38</v>
+        <v>62.06</v>
       </c>
       <c r="M74" s="12">
-        <v>263349</v>
+        <v>265589</v>
       </c>
       <c r="N74" s="13">
-        <v>37.619999999999997</v>
+        <v>37.94</v>
       </c>
       <c r="O74" s="12">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="P74" s="13">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="Q74" s="12">
-        <v>263349</v>
+        <v>235589</v>
       </c>
       <c r="R74" s="13">
-        <v>37.619999999999997</v>
+        <v>33.659999999999997</v>
       </c>
     </row>
     <row r="75" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -6342,28 +6346,28 @@
         <v>3300000</v>
       </c>
       <c r="G76" s="12">
-        <v>2199943.6</v>
+        <v>2307973.6</v>
       </c>
       <c r="H76" s="13">
-        <v>66.66</v>
+        <v>69.94</v>
       </c>
       <c r="I76" s="12">
-        <v>506097</v>
+        <v>386297</v>
       </c>
       <c r="J76" s="13">
-        <v>15.34</v>
+        <v>11.71</v>
       </c>
       <c r="K76" s="12">
-        <v>2706040.6</v>
+        <v>2694270.6</v>
       </c>
       <c r="L76" s="13">
-        <v>82</v>
+        <v>81.64</v>
       </c>
       <c r="M76" s="12">
-        <v>593959.4</v>
+        <v>605729.4</v>
       </c>
       <c r="N76" s="13">
-        <v>18</v>
+        <v>18.36</v>
       </c>
       <c r="O76" s="12">
         <v>0</v>
@@ -6372,10 +6376,10 @@
         <v>0</v>
       </c>
       <c r="Q76" s="12">
-        <v>593959.4</v>
+        <v>605729.4</v>
       </c>
       <c r="R76" s="13">
-        <v>18</v>
+        <v>18.36</v>
       </c>
     </row>
     <row r="77" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -6478,16 +6482,16 @@
         <v>24.94</v>
       </c>
       <c r="O78" s="12">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="P78" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q78" s="12">
-        <v>124700</v>
+        <v>74700</v>
       </c>
       <c r="R78" s="13">
-        <v>24.94</v>
+        <v>14.94</v>
       </c>
     </row>
     <row r="79" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -6566,40 +6570,40 @@
         <v>7820000</v>
       </c>
       <c r="G80" s="8">
-        <v>5317978.5999999996</v>
+        <v>5358529.5999999996</v>
       </c>
       <c r="H80" s="9">
-        <v>68</v>
+        <v>68.52</v>
       </c>
       <c r="I80" s="8">
-        <v>650010</v>
+        <v>603659</v>
       </c>
       <c r="J80" s="9">
-        <v>8.31</v>
+        <v>7.72</v>
       </c>
       <c r="K80" s="8">
-        <v>5967988.5999999996</v>
+        <v>5962188.5999999996</v>
       </c>
       <c r="L80" s="9">
-        <v>76.319999999999993</v>
+        <v>76.239999999999995</v>
       </c>
       <c r="M80" s="8">
-        <v>1852011.4</v>
+        <v>1857811.4</v>
       </c>
       <c r="N80" s="9">
-        <v>23.68</v>
+        <v>23.76</v>
       </c>
       <c r="O80" s="8">
-        <v>0</v>
+        <v>550000</v>
       </c>
       <c r="P80" s="9">
-        <v>0</v>
+        <v>7.03</v>
       </c>
       <c r="Q80" s="8">
-        <v>1852011.4</v>
+        <v>1307811.3999999999</v>
       </c>
       <c r="R80" s="9">
-        <v>23.68</v>
+        <v>16.72</v>
       </c>
     </row>
     <row r="81" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -6678,28 +6682,28 @@
         <v>1200000</v>
       </c>
       <c r="G82" s="12">
-        <v>1540177</v>
+        <v>1553877</v>
       </c>
       <c r="H82" s="13">
-        <v>128.35</v>
+        <v>129.49</v>
       </c>
       <c r="I82" s="12">
-        <v>35750</v>
+        <v>15350</v>
       </c>
       <c r="J82" s="13">
-        <v>2.98</v>
+        <v>1.28</v>
       </c>
       <c r="K82" s="12">
-        <v>1575927</v>
+        <v>1569227</v>
       </c>
       <c r="L82" s="13">
-        <v>131.33000000000001</v>
+        <v>130.77000000000001</v>
       </c>
       <c r="M82" s="12">
-        <v>-375927</v>
+        <v>-369227</v>
       </c>
       <c r="N82" s="13">
-        <v>-31.33</v>
+        <v>-30.77</v>
       </c>
       <c r="O82" s="12">
         <v>0</v>
@@ -6708,10 +6712,10 @@
         <v>0</v>
       </c>
       <c r="Q82" s="12">
-        <v>-375927</v>
+        <v>-369227</v>
       </c>
       <c r="R82" s="13">
-        <v>-31.33</v>
+        <v>-30.77</v>
       </c>
     </row>
     <row r="83" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -6790,28 +6794,28 @@
         <v>3000000</v>
       </c>
       <c r="G84" s="12">
-        <v>2640460.2999999998</v>
+        <v>2645961.2999999998</v>
       </c>
       <c r="H84" s="13">
-        <v>88.02</v>
+        <v>88.2</v>
       </c>
       <c r="I84" s="12">
-        <v>303340</v>
+        <v>298739</v>
       </c>
       <c r="J84" s="13">
-        <v>10.11</v>
+        <v>9.9600000000000009</v>
       </c>
       <c r="K84" s="12">
-        <v>2943800.3</v>
+        <v>2944700.3</v>
       </c>
       <c r="L84" s="13">
-        <v>98.13</v>
+        <v>98.16</v>
       </c>
       <c r="M84" s="12">
-        <v>56199.7</v>
+        <v>55299.7</v>
       </c>
       <c r="N84" s="13">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="O84" s="12">
         <v>0</v>
@@ -6820,10 +6824,10 @@
         <v>0</v>
       </c>
       <c r="Q84" s="12">
-        <v>56199.7</v>
+        <v>55299.7</v>
       </c>
       <c r="R84" s="13">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="85" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -7014,16 +7018,16 @@
         <v>220000</v>
       </c>
       <c r="G88" s="12">
-        <v>25755</v>
+        <v>47105</v>
       </c>
       <c r="H88" s="13">
-        <v>11.71</v>
+        <v>21.41</v>
       </c>
       <c r="I88" s="12">
-        <v>21350</v>
+        <v>0</v>
       </c>
       <c r="J88" s="13">
-        <v>9.6999999999999993</v>
+        <v>0</v>
       </c>
       <c r="K88" s="12">
         <v>47105</v>
@@ -7094,16 +7098,16 @@
         <v>92.42</v>
       </c>
       <c r="O89" s="12">
-        <v>0</v>
+        <v>550000</v>
       </c>
       <c r="P89" s="13">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="Q89" s="12">
-        <v>924250</v>
+        <v>374250</v>
       </c>
       <c r="R89" s="13">
-        <v>92.42</v>
+        <v>37.43</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
@@ -7126,28 +7130,28 @@
         <v>9800000</v>
       </c>
       <c r="G90" s="4">
-        <v>4926297.9800000004</v>
+        <v>4952297.9800000004</v>
       </c>
       <c r="H90" s="5">
-        <v>50.27</v>
+        <v>50.53</v>
       </c>
       <c r="I90" s="4">
-        <v>1046394.97</v>
+        <v>1012522.97</v>
       </c>
       <c r="J90" s="5">
-        <v>10.68</v>
+        <v>10.33</v>
       </c>
       <c r="K90" s="4">
-        <v>5972692.9500000002</v>
+        <v>5964820.9500000002</v>
       </c>
       <c r="L90" s="5">
-        <v>60.95</v>
+        <v>60.87</v>
       </c>
       <c r="M90" s="4">
-        <v>3827307.05</v>
+        <v>3835179.05</v>
       </c>
       <c r="N90" s="5">
-        <v>39.049999999999997</v>
+        <v>39.130000000000003</v>
       </c>
       <c r="O90" s="4">
         <v>2233789.54</v>
@@ -7156,10 +7160,10 @@
         <v>22.79</v>
       </c>
       <c r="Q90" s="4">
-        <v>1593517.51</v>
+        <v>1601389.51</v>
       </c>
       <c r="R90" s="5">
-        <v>16.260000000000002</v>
+        <v>16.34</v>
       </c>
     </row>
     <row r="91" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -7182,28 +7186,28 @@
         <v>9800000</v>
       </c>
       <c r="G91" s="8">
-        <v>4926297.9800000004</v>
+        <v>4952297.9800000004</v>
       </c>
       <c r="H91" s="9">
-        <v>50.27</v>
+        <v>50.53</v>
       </c>
       <c r="I91" s="8">
-        <v>1046394.97</v>
+        <v>1012522.97</v>
       </c>
       <c r="J91" s="9">
-        <v>10.68</v>
+        <v>10.33</v>
       </c>
       <c r="K91" s="8">
-        <v>5972692.9500000002</v>
+        <v>5964820.9500000002</v>
       </c>
       <c r="L91" s="9">
-        <v>60.95</v>
+        <v>60.87</v>
       </c>
       <c r="M91" s="8">
-        <v>3827307.05</v>
+        <v>3835179.05</v>
       </c>
       <c r="N91" s="9">
-        <v>39.049999999999997</v>
+        <v>39.130000000000003</v>
       </c>
       <c r="O91" s="8">
         <v>2233789.54</v>
@@ -7212,10 +7216,10 @@
         <v>22.79</v>
       </c>
       <c r="Q91" s="8">
-        <v>1593517.51</v>
+        <v>1601389.51</v>
       </c>
       <c r="R91" s="9">
-        <v>16.260000000000002</v>
+        <v>16.34</v>
       </c>
     </row>
     <row r="92" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
@@ -7238,28 +7242,28 @@
         <v>4305000</v>
       </c>
       <c r="G92" s="12">
-        <v>2316239.4900000002</v>
+        <v>2317739.4900000002</v>
       </c>
       <c r="H92" s="13">
-        <v>53.8</v>
+        <v>53.84</v>
       </c>
       <c r="I92" s="12">
-        <v>761144.97</v>
+        <v>744572.97</v>
       </c>
       <c r="J92" s="13">
-        <v>17.68</v>
+        <v>17.3</v>
       </c>
       <c r="K92" s="12">
-        <v>3077384.46</v>
+        <v>3062312.46</v>
       </c>
       <c r="L92" s="13">
-        <v>71.48</v>
+        <v>71.13</v>
       </c>
       <c r="M92" s="12">
-        <v>1227615.54</v>
+        <v>1242687.54</v>
       </c>
       <c r="N92" s="13">
-        <v>28.52</v>
+        <v>28.87</v>
       </c>
       <c r="O92" s="12">
         <v>801289.54</v>
@@ -7268,10 +7272,10 @@
         <v>18.61</v>
       </c>
       <c r="Q92" s="12">
-        <v>426326</v>
+        <v>441398</v>
       </c>
       <c r="R92" s="13">
-        <v>9.9</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="93" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -7294,16 +7298,16 @@
         <v>3140000</v>
       </c>
       <c r="G93" s="12">
-        <v>1636027.49</v>
+        <v>1660527.49</v>
       </c>
       <c r="H93" s="13">
-        <v>52.1</v>
+        <v>52.88</v>
       </c>
       <c r="I93" s="12">
-        <v>285250</v>
+        <v>260750</v>
       </c>
       <c r="J93" s="13">
-        <v>9.08</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="K93" s="12">
         <v>1921277.49</v>
@@ -7356,22 +7360,22 @@
         <v>41.36</v>
       </c>
       <c r="I94" s="12">
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="J94" s="13">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="K94" s="12">
-        <v>974031</v>
+        <v>981231</v>
       </c>
       <c r="L94" s="13">
-        <v>41.36</v>
+        <v>41.67</v>
       </c>
       <c r="M94" s="12">
-        <v>1380969</v>
+        <v>1373769</v>
       </c>
       <c r="N94" s="13">
-        <v>58.64</v>
+        <v>58.33</v>
       </c>
       <c r="O94" s="12">
         <v>750000</v>
@@ -7380,10 +7384,10 @@
         <v>31.85</v>
       </c>
       <c r="Q94" s="12">
-        <v>630969</v>
+        <v>623769</v>
       </c>
       <c r="R94" s="13">
-        <v>26.79</v>
+        <v>26.49</v>
       </c>
     </row>
     <row r="95" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -7406,40 +7410,40 @@
         <v>119421186</v>
       </c>
       <c r="G95" s="4">
-        <v>78180004.799999997</v>
+        <v>78356303.409999996</v>
       </c>
       <c r="H95" s="5">
-        <v>65.47</v>
+        <v>65.61</v>
       </c>
       <c r="I95" s="4">
-        <v>13911303.93</v>
+        <v>13687572.32</v>
       </c>
       <c r="J95" s="5">
-        <v>11.65</v>
+        <v>11.46</v>
       </c>
       <c r="K95" s="4">
-        <v>92091308.730000004</v>
+        <v>92043875.730000004</v>
       </c>
       <c r="L95" s="5">
-        <v>77.11</v>
+        <v>77.069999999999993</v>
       </c>
       <c r="M95" s="4">
-        <v>27329877.27</v>
+        <v>27377310.27</v>
       </c>
       <c r="N95" s="5">
-        <v>22.89</v>
+        <v>22.93</v>
       </c>
       <c r="O95" s="4">
-        <v>3528765.77</v>
+        <v>2612317.27</v>
       </c>
       <c r="P95" s="5">
-        <v>2.95</v>
+        <v>2.19</v>
       </c>
       <c r="Q95" s="4">
-        <v>23801111.5</v>
+        <v>24764993</v>
       </c>
       <c r="R95" s="5">
-        <v>19.93</v>
+        <v>20.74</v>
       </c>
     </row>
     <row r="96" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -7462,40 +7466,40 @@
         <v>29200000</v>
       </c>
       <c r="G96" s="8">
-        <v>16096171.26</v>
+        <v>16148502.869999999</v>
       </c>
       <c r="H96" s="9">
-        <v>55.12</v>
+        <v>55.3</v>
       </c>
       <c r="I96" s="8">
-        <v>7442003.5999999996</v>
+        <v>7352779.9900000002</v>
       </c>
       <c r="J96" s="9">
-        <v>25.49</v>
+        <v>25.18</v>
       </c>
       <c r="K96" s="8">
-        <v>23538174.859999999</v>
+        <v>23501282.859999999</v>
       </c>
       <c r="L96" s="9">
-        <v>80.61</v>
+        <v>80.48</v>
       </c>
       <c r="M96" s="8">
-        <v>5661825.1399999997</v>
+        <v>5698717.1399999997</v>
       </c>
       <c r="N96" s="9">
-        <v>19.39</v>
+        <v>19.52</v>
       </c>
       <c r="O96" s="8">
-        <v>2610833.37</v>
+        <v>1639333.37</v>
       </c>
       <c r="P96" s="9">
-        <v>8.94</v>
+        <v>5.61</v>
       </c>
       <c r="Q96" s="8">
-        <v>3050991.77</v>
+        <v>4059383.77</v>
       </c>
       <c r="R96" s="9">
-        <v>10.45</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="97" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -7518,40 +7522,40 @@
         <v>3261268.89</v>
       </c>
       <c r="G97" s="12">
-        <v>2041857.37</v>
+        <v>2051442.37</v>
       </c>
       <c r="H97" s="13">
-        <v>62.61</v>
+        <v>62.9</v>
       </c>
       <c r="I97" s="12">
-        <v>1117940</v>
+        <v>1131840</v>
       </c>
       <c r="J97" s="13">
-        <v>34.28</v>
+        <v>34.71</v>
       </c>
       <c r="K97" s="12">
-        <v>3159797.37</v>
+        <v>3183282.37</v>
       </c>
       <c r="L97" s="13">
-        <v>96.89</v>
+        <v>97.61</v>
       </c>
       <c r="M97" s="12">
-        <v>101471.52</v>
+        <v>77986.52</v>
       </c>
       <c r="N97" s="13">
-        <v>3.11</v>
+        <v>2.39</v>
       </c>
       <c r="O97" s="12">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="P97" s="13">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="Q97" s="12">
-        <v>91471.52</v>
+        <v>77986.52</v>
       </c>
       <c r="R97" s="13">
-        <v>2.8</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="98" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -7574,16 +7578,16 @@
         <v>4780425.63</v>
       </c>
       <c r="G98" s="12">
-        <v>2319859.5299999998</v>
+        <v>2332545.39</v>
       </c>
       <c r="H98" s="13">
-        <v>48.53</v>
+        <v>48.79</v>
       </c>
       <c r="I98" s="12">
-        <v>2460566.1</v>
+        <v>2447880.2400000002</v>
       </c>
       <c r="J98" s="13">
-        <v>51.47</v>
+        <v>51.21</v>
       </c>
       <c r="K98" s="12">
         <v>4780425.63</v>
@@ -7598,16 +7602,16 @@
         <v>0</v>
       </c>
       <c r="O98" s="12">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="P98" s="13">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q98" s="12">
-        <v>-80000</v>
+        <v>0</v>
       </c>
       <c r="R98" s="13">
-        <v>-1.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -7630,40 +7634,40 @@
         <v>8310076.75</v>
       </c>
       <c r="G99" s="12">
-        <v>2814257.63</v>
+        <v>2844318.38</v>
       </c>
       <c r="H99" s="13">
-        <v>33.869999999999997</v>
+        <v>34.229999999999997</v>
       </c>
       <c r="I99" s="12">
-        <v>3785465.5</v>
+        <v>3773059.75</v>
       </c>
       <c r="J99" s="13">
-        <v>45.55</v>
+        <v>45.4</v>
       </c>
       <c r="K99" s="12">
-        <v>6599723.1299999999</v>
+        <v>6617378.1299999999</v>
       </c>
       <c r="L99" s="13">
-        <v>79.42</v>
+        <v>79.63</v>
       </c>
       <c r="M99" s="12">
-        <v>1710353.62</v>
+        <v>1692698.62</v>
       </c>
       <c r="N99" s="13">
-        <v>20.58</v>
+        <v>20.37</v>
       </c>
       <c r="O99" s="12">
-        <v>2140833.37</v>
+        <v>1259333.3700000001</v>
       </c>
       <c r="P99" s="13">
-        <v>25.76</v>
+        <v>15.15</v>
       </c>
       <c r="Q99" s="12">
-        <v>-430479.75</v>
+        <v>433365.25</v>
       </c>
       <c r="R99" s="13">
-        <v>-5.18</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="100" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -7748,22 +7752,22 @@
         <v>69.430000000000007</v>
       </c>
       <c r="I101" s="12">
-        <v>78032</v>
+        <v>0</v>
       </c>
       <c r="J101" s="13">
-        <v>0.61</v>
+        <v>0</v>
       </c>
       <c r="K101" s="12">
-        <v>8998228.7300000004</v>
+        <v>8920196.7300000004</v>
       </c>
       <c r="L101" s="13">
-        <v>70.03</v>
+        <v>69.430000000000007</v>
       </c>
       <c r="M101" s="12">
-        <v>3850000</v>
+        <v>3928032</v>
       </c>
       <c r="N101" s="13">
-        <v>29.97</v>
+        <v>30.57</v>
       </c>
       <c r="O101" s="12">
         <v>380000</v>
@@ -7772,10 +7776,10 @@
         <v>2.96</v>
       </c>
       <c r="Q101" s="12">
-        <v>3470000</v>
+        <v>3548032</v>
       </c>
       <c r="R101" s="13">
-        <v>27.01</v>
+        <v>27.61</v>
       </c>
     </row>
     <row r="102" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -7798,28 +7802,28 @@
         <v>1000000</v>
       </c>
       <c r="G102" s="8">
-        <v>466919</v>
+        <v>498719</v>
       </c>
       <c r="H102" s="9">
-        <v>46.69</v>
+        <v>49.87</v>
       </c>
       <c r="I102" s="8">
-        <v>68570</v>
+        <v>30120</v>
       </c>
       <c r="J102" s="9">
-        <v>6.86</v>
+        <v>3.01</v>
       </c>
       <c r="K102" s="8">
-        <v>535489</v>
+        <v>528839</v>
       </c>
       <c r="L102" s="9">
-        <v>53.55</v>
+        <v>52.88</v>
       </c>
       <c r="M102" s="8">
-        <v>464511</v>
+        <v>471161</v>
       </c>
       <c r="N102" s="9">
-        <v>46.45</v>
+        <v>47.12</v>
       </c>
       <c r="O102" s="8">
         <v>0</v>
@@ -7828,10 +7832,10 @@
         <v>0</v>
       </c>
       <c r="Q102" s="8">
-        <v>464511</v>
+        <v>471161</v>
       </c>
       <c r="R102" s="9">
-        <v>46.45</v>
+        <v>47.12</v>
       </c>
     </row>
     <row r="103" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -7854,28 +7858,28 @@
         <v>886600</v>
       </c>
       <c r="G103" s="12">
-        <v>396529</v>
+        <v>428329</v>
       </c>
       <c r="H103" s="13">
-        <v>44.72</v>
+        <v>48.31</v>
       </c>
       <c r="I103" s="12">
-        <v>68570</v>
+        <v>17870</v>
       </c>
       <c r="J103" s="13">
-        <v>7.73</v>
+        <v>2.02</v>
       </c>
       <c r="K103" s="12">
-        <v>465099</v>
+        <v>446199</v>
       </c>
       <c r="L103" s="13">
-        <v>52.46</v>
+        <v>50.33</v>
       </c>
       <c r="M103" s="12">
-        <v>421501</v>
+        <v>440401</v>
       </c>
       <c r="N103" s="13">
-        <v>47.54</v>
+        <v>49.67</v>
       </c>
       <c r="O103" s="12">
         <v>0</v>
@@ -7884,10 +7888,10 @@
         <v>0</v>
       </c>
       <c r="Q103" s="12">
-        <v>421501</v>
+        <v>440401</v>
       </c>
       <c r="R103" s="13">
-        <v>47.54</v>
+        <v>49.67</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
@@ -7916,22 +7920,22 @@
         <v>62.07</v>
       </c>
       <c r="I104" s="12">
-        <v>0</v>
+        <v>12250</v>
       </c>
       <c r="J104" s="13">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="K104" s="12">
-        <v>70390</v>
+        <v>82640</v>
       </c>
       <c r="L104" s="13">
-        <v>62.07</v>
+        <v>72.87</v>
       </c>
       <c r="M104" s="12">
-        <v>43010</v>
+        <v>30760</v>
       </c>
       <c r="N104" s="13">
-        <v>37.93</v>
+        <v>27.13</v>
       </c>
       <c r="O104" s="12">
         <v>0</v>
@@ -7940,10 +7944,10 @@
         <v>0</v>
       </c>
       <c r="Q104" s="12">
-        <v>43010</v>
+        <v>30760</v>
       </c>
       <c r="R104" s="13">
-        <v>37.93</v>
+        <v>27.13</v>
       </c>
     </row>
     <row r="105" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -8140,34 +8144,34 @@
         <v>30.4</v>
       </c>
       <c r="I108" s="8">
-        <v>5906250.5999999996</v>
+        <v>5906356.5999999996</v>
       </c>
       <c r="J108" s="9">
         <v>57.94</v>
       </c>
       <c r="K108" s="8">
-        <v>9005093.5999999996</v>
+        <v>9005199.5999999996</v>
       </c>
       <c r="L108" s="9">
         <v>88.34</v>
       </c>
       <c r="M108" s="8">
-        <v>1189092.3999999999</v>
+        <v>1188986.3999999999</v>
       </c>
       <c r="N108" s="9">
         <v>11.66</v>
       </c>
       <c r="O108" s="8">
-        <v>897932.4</v>
+        <v>971441.4</v>
       </c>
       <c r="P108" s="9">
-        <v>8.81</v>
+        <v>9.5299999999999994</v>
       </c>
       <c r="Q108" s="8">
-        <v>291160</v>
+        <v>217545</v>
       </c>
       <c r="R108" s="9">
-        <v>2.86</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="109" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -8196,34 +8200,34 @@
         <v>26.2</v>
       </c>
       <c r="I109" s="12">
-        <v>3206299.6</v>
+        <v>3205549.6</v>
       </c>
       <c r="J109" s="13">
-        <v>57.13</v>
+        <v>57.12</v>
       </c>
       <c r="K109" s="12">
-        <v>4676778.5999999996</v>
+        <v>4676028.5999999996</v>
       </c>
       <c r="L109" s="13">
-        <v>83.33</v>
+        <v>83.32</v>
       </c>
       <c r="M109" s="12">
-        <v>935321.4</v>
+        <v>936071.4</v>
       </c>
       <c r="N109" s="13">
-        <v>16.670000000000002</v>
+        <v>16.68</v>
       </c>
       <c r="O109" s="12">
-        <v>708323.4</v>
+        <v>702688.4</v>
       </c>
       <c r="P109" s="13">
-        <v>12.62</v>
+        <v>12.52</v>
       </c>
       <c r="Q109" s="12">
-        <v>226998</v>
+        <v>233383</v>
       </c>
       <c r="R109" s="13">
-        <v>4.04</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="110" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -8252,34 +8256,34 @@
         <v>35.54</v>
       </c>
       <c r="I110" s="12">
-        <v>2699951</v>
+        <v>2700807</v>
       </c>
       <c r="J110" s="13">
-        <v>58.92</v>
+        <v>58.94</v>
       </c>
       <c r="K110" s="12">
-        <v>4328315</v>
+        <v>4329171</v>
       </c>
       <c r="L110" s="13">
-        <v>94.46</v>
+        <v>94.48</v>
       </c>
       <c r="M110" s="12">
-        <v>253771</v>
+        <v>252915</v>
       </c>
       <c r="N110" s="13">
-        <v>5.54</v>
+        <v>5.52</v>
       </c>
       <c r="O110" s="12">
-        <v>189609</v>
+        <v>268753</v>
       </c>
       <c r="P110" s="13">
-        <v>4.1399999999999997</v>
+        <v>5.87</v>
       </c>
       <c r="Q110" s="12">
-        <v>64162</v>
+        <v>-15838</v>
       </c>
       <c r="R110" s="13">
-        <v>1.4</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="111" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -8302,40 +8306,40 @@
         <v>78027000</v>
       </c>
       <c r="G111" s="8">
-        <v>57787595.799999997</v>
+        <v>57879762.799999997</v>
       </c>
       <c r="H111" s="9">
-        <v>74.06</v>
+        <v>74.180000000000007</v>
       </c>
       <c r="I111" s="8">
-        <v>299811.73</v>
+        <v>203647.73</v>
       </c>
       <c r="J111" s="9">
-        <v>0.38</v>
+        <v>0.26</v>
       </c>
       <c r="K111" s="8">
-        <v>58087407.530000001</v>
+        <v>58083410.530000001</v>
       </c>
       <c r="L111" s="9">
-        <v>74.45</v>
+        <v>74.44</v>
       </c>
       <c r="M111" s="8">
-        <v>19939592.469999999</v>
+        <v>19943589.469999999</v>
       </c>
       <c r="N111" s="9">
-        <v>25.55</v>
+        <v>25.56</v>
       </c>
       <c r="O111" s="8">
-        <v>20000</v>
+        <v>1542.5</v>
       </c>
       <c r="P111" s="9">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="Q111" s="8">
-        <v>19919592.469999999</v>
+        <v>19942046.969999999</v>
       </c>
       <c r="R111" s="9">
-        <v>25.53</v>
+        <v>25.56</v>
       </c>
     </row>
     <row r="112" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -8358,40 +8362,40 @@
         <v>640000</v>
       </c>
       <c r="G112" s="12">
-        <v>228555</v>
+        <v>231355</v>
       </c>
       <c r="H112" s="13">
-        <v>35.71</v>
+        <v>36.15</v>
       </c>
       <c r="I112" s="12">
-        <v>5490</v>
+        <v>31647.5</v>
       </c>
       <c r="J112" s="13">
-        <v>0.86</v>
+        <v>4.9400000000000004</v>
       </c>
       <c r="K112" s="12">
-        <v>234045</v>
+        <v>263002.5</v>
       </c>
       <c r="L112" s="13">
-        <v>36.57</v>
+        <v>41.09</v>
       </c>
       <c r="M112" s="12">
-        <v>405955</v>
+        <v>376997.5</v>
       </c>
       <c r="N112" s="13">
-        <v>63.43</v>
+        <v>58.91</v>
       </c>
       <c r="O112" s="12">
-        <v>20000</v>
+        <v>1542.5</v>
       </c>
       <c r="P112" s="13">
-        <v>3.12</v>
+        <v>0.24</v>
       </c>
       <c r="Q112" s="12">
-        <v>385955</v>
+        <v>375455</v>
       </c>
       <c r="R112" s="13">
-        <v>60.31</v>
+        <v>58.66</v>
       </c>
     </row>
     <row r="113" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -8414,28 +8418,28 @@
         <v>2387000</v>
       </c>
       <c r="G113" s="12">
-        <v>2476249.0699999998</v>
+        <v>2557754.0699999998</v>
       </c>
       <c r="H113" s="13">
-        <v>103.74</v>
+        <v>107.15</v>
       </c>
       <c r="I113" s="12">
-        <v>294321.73</v>
+        <v>172000.23</v>
       </c>
       <c r="J113" s="13">
-        <v>12.33</v>
+        <v>7.21</v>
       </c>
       <c r="K113" s="12">
-        <v>2770570.8</v>
+        <v>2729754.3</v>
       </c>
       <c r="L113" s="13">
-        <v>116.07</v>
+        <v>114.36</v>
       </c>
       <c r="M113" s="12">
-        <v>-383570.8</v>
+        <v>-342754.3</v>
       </c>
       <c r="N113" s="13">
-        <v>-16.07</v>
+        <v>-14.36</v>
       </c>
       <c r="O113" s="12">
         <v>0</v>
@@ -8444,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Q113" s="12">
-        <v>-383570.8</v>
+        <v>-342754.3</v>
       </c>
       <c r="R113" s="13">
-        <v>-16.07</v>
+        <v>-14.36</v>
       </c>
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.25">
@@ -8470,10 +8474,10 @@
         <v>75000000</v>
       </c>
       <c r="G114" s="12">
-        <v>55082791.729999997</v>
+        <v>55090653.729999997</v>
       </c>
       <c r="H114" s="13">
-        <v>73.44</v>
+        <v>73.45</v>
       </c>
       <c r="I114" s="12">
         <v>0</v>
@@ -8482,16 +8486,16 @@
         <v>0</v>
       </c>
       <c r="K114" s="12">
-        <v>55082791.729999997</v>
+        <v>55090653.729999997</v>
       </c>
       <c r="L114" s="13">
-        <v>73.44</v>
+        <v>73.45</v>
       </c>
       <c r="M114" s="12">
-        <v>19917208.27</v>
+        <v>19909346.27</v>
       </c>
       <c r="N114" s="13">
-        <v>26.56</v>
+        <v>26.55</v>
       </c>
       <c r="O114" s="12">
         <v>0</v>
@@ -8500,10 +8504,10 @@
         <v>0</v>
       </c>
       <c r="Q114" s="12">
-        <v>19917208.27</v>
+        <v>19909346.27</v>
       </c>
       <c r="R114" s="13">
-        <v>26.56</v>
+        <v>26.55</v>
       </c>
     </row>
     <row r="115" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -8692,40 +8696,40 @@
         <v>230702200</v>
       </c>
       <c r="G118" s="14">
-        <v>142527225.13999999</v>
+        <v>143284850.61000001</v>
       </c>
       <c r="H118" s="15">
-        <v>61.78</v>
+        <v>62.11</v>
       </c>
       <c r="I118" s="14">
-        <v>37194389.310000002</v>
+        <v>37050134.240000002</v>
       </c>
       <c r="J118" s="15">
-        <v>16.12</v>
+        <v>16.059999999999999</v>
       </c>
       <c r="K118" s="14">
-        <v>179721614.44999999</v>
+        <v>180334984.84999999</v>
       </c>
       <c r="L118" s="15">
-        <v>77.900000000000006</v>
+        <v>78.17</v>
       </c>
       <c r="M118" s="14">
-        <v>50980585.549999997</v>
+        <v>50367215.149999999</v>
       </c>
       <c r="N118" s="15">
-        <v>22.1</v>
+        <v>21.83</v>
       </c>
       <c r="O118" s="14">
-        <v>8119699.4100000001</v>
+        <v>7831250.9100000001</v>
       </c>
       <c r="P118" s="15">
-        <v>3.52</v>
+        <v>3.39</v>
       </c>
       <c r="Q118" s="14">
-        <v>42860886.140000001</v>
+        <v>42535964.240000002</v>
       </c>
       <c r="R118" s="15">
-        <v>18.579999999999998</v>
+        <v>18.440000000000001</v>
       </c>
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
@@ -8748,40 +8752,40 @@
         <v>100622228.15000001</v>
       </c>
       <c r="G119" s="4">
-        <v>21751803.469999999</v>
+        <v>22946611.77</v>
       </c>
       <c r="H119" s="5">
-        <v>21.62</v>
+        <v>22.8</v>
       </c>
       <c r="I119" s="4">
-        <v>11592441.65</v>
+        <v>19851637.949999999</v>
       </c>
       <c r="J119" s="5">
-        <v>11.52</v>
+        <v>19.73</v>
       </c>
       <c r="K119" s="4">
-        <v>33344245.120000001</v>
+        <v>42798249.719999999</v>
       </c>
       <c r="L119" s="5">
-        <v>33.14</v>
+        <v>42.53</v>
       </c>
       <c r="M119" s="4">
-        <v>67277983.030000001</v>
+        <v>57823978.43</v>
       </c>
       <c r="N119" s="5">
-        <v>66.86</v>
+        <v>57.47</v>
       </c>
       <c r="O119" s="4">
-        <v>11951093</v>
+        <v>6671343</v>
       </c>
       <c r="P119" s="5">
-        <v>11.88</v>
+        <v>6.63</v>
       </c>
       <c r="Q119" s="4">
-        <v>55326890.030000001</v>
+        <v>51152635.43</v>
       </c>
       <c r="R119" s="5">
-        <v>54.98</v>
+        <v>50.84</v>
       </c>
     </row>
     <row r="120" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -9756,28 +9760,28 @@
         <v>7768581.8099999996</v>
       </c>
       <c r="G137" s="8">
-        <v>3968742.94</v>
+        <v>4902612.9400000004</v>
       </c>
       <c r="H137" s="9">
-        <v>51.09</v>
+        <v>63.11</v>
       </c>
       <c r="I137" s="8">
-        <v>1905517.16</v>
+        <v>962602.16</v>
       </c>
       <c r="J137" s="9">
-        <v>24.53</v>
+        <v>12.39</v>
       </c>
       <c r="K137" s="8">
-        <v>5874260.0999999996</v>
+        <v>5865215.0999999996</v>
       </c>
       <c r="L137" s="9">
-        <v>75.62</v>
+        <v>75.5</v>
       </c>
       <c r="M137" s="8">
-        <v>1894321.71</v>
+        <v>1903366.71</v>
       </c>
       <c r="N137" s="9">
-        <v>24.38</v>
+        <v>24.5</v>
       </c>
       <c r="O137" s="8">
         <v>613445</v>
@@ -9786,10 +9790,10 @@
         <v>7.9</v>
       </c>
       <c r="Q137" s="8">
-        <v>1280876.71</v>
+        <v>1289921.71</v>
       </c>
       <c r="R137" s="9">
-        <v>16.489999999999998</v>
+        <v>16.600000000000001</v>
       </c>
     </row>
     <row r="138" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -9812,28 +9816,28 @@
         <v>2672753.2999999998</v>
       </c>
       <c r="G138" s="12">
-        <v>1263025.1000000001</v>
+        <v>2164940.1</v>
       </c>
       <c r="H138" s="13">
-        <v>47.26</v>
+        <v>81</v>
       </c>
       <c r="I138" s="12">
-        <v>902115</v>
+        <v>0</v>
       </c>
       <c r="J138" s="13">
-        <v>33.75</v>
+        <v>0</v>
       </c>
       <c r="K138" s="12">
-        <v>2165140.1</v>
+        <v>2164940.1</v>
       </c>
       <c r="L138" s="13">
-        <v>81.010000000000005</v>
+        <v>81</v>
       </c>
       <c r="M138" s="12">
-        <v>507613.2</v>
+        <v>507813.2</v>
       </c>
       <c r="N138" s="13">
-        <v>18.989999999999998</v>
+        <v>19</v>
       </c>
       <c r="O138" s="12">
         <v>554945</v>
@@ -9842,10 +9846,10 @@
         <v>20.76</v>
       </c>
       <c r="Q138" s="12">
-        <v>-47331.8</v>
+        <v>-47131.8</v>
       </c>
       <c r="R138" s="13">
-        <v>-1.77</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="139" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -9980,28 +9984,28 @@
         <v>586550</v>
       </c>
       <c r="G141" s="12">
-        <v>391570</v>
+        <v>423525</v>
       </c>
       <c r="H141" s="13">
-        <v>66.760000000000005</v>
+        <v>72.209999999999994</v>
       </c>
       <c r="I141" s="12">
-        <v>321500</v>
+        <v>280700</v>
       </c>
       <c r="J141" s="13">
-        <v>54.81</v>
+        <v>47.86</v>
       </c>
       <c r="K141" s="12">
-        <v>713070</v>
+        <v>704225</v>
       </c>
       <c r="L141" s="13">
-        <v>121.57</v>
+        <v>120.06</v>
       </c>
       <c r="M141" s="12">
-        <v>-126520</v>
+        <v>-117675</v>
       </c>
       <c r="N141" s="13">
-        <v>-21.57</v>
+        <v>-20.059999999999999</v>
       </c>
       <c r="O141" s="12">
         <v>50000</v>
@@ -10010,10 +10014,10 @@
         <v>8.52</v>
       </c>
       <c r="Q141" s="12">
-        <v>-176520</v>
+        <v>-167675</v>
       </c>
       <c r="R141" s="13">
-        <v>-30.09</v>
+        <v>-28.59</v>
       </c>
     </row>
     <row r="142" spans="1:18" x14ac:dyDescent="0.25">
@@ -11604,28 +11608,28 @@
         <v>8926239.0199999996</v>
       </c>
       <c r="G170" s="8">
-        <v>1038332.08</v>
+        <v>1080387.78</v>
       </c>
       <c r="H170" s="9">
-        <v>11.63</v>
+        <v>12.1</v>
       </c>
       <c r="I170" s="8">
-        <v>3380146.7</v>
+        <v>5243008</v>
       </c>
       <c r="J170" s="9">
-        <v>37.869999999999997</v>
+        <v>58.74</v>
       </c>
       <c r="K170" s="8">
-        <v>4418478.78</v>
+        <v>6323395.7800000003</v>
       </c>
       <c r="L170" s="9">
-        <v>49.5</v>
+        <v>70.84</v>
       </c>
       <c r="M170" s="8">
-        <v>4507760.24</v>
+        <v>2602843.2400000002</v>
       </c>
       <c r="N170" s="9">
-        <v>50.5</v>
+        <v>29.16</v>
       </c>
       <c r="O170" s="8">
         <v>500000</v>
@@ -11634,10 +11638,10 @@
         <v>5.6</v>
       </c>
       <c r="Q170" s="8">
-        <v>4007760.24</v>
+        <v>2102843.2400000002</v>
       </c>
       <c r="R170" s="9">
-        <v>44.9</v>
+        <v>23.56</v>
       </c>
     </row>
     <row r="171" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -11666,22 +11670,22 @@
         <v>16.64</v>
       </c>
       <c r="I171" s="12">
-        <v>0</v>
+        <v>1902000</v>
       </c>
       <c r="J171" s="13">
-        <v>0</v>
+        <v>82.63</v>
       </c>
       <c r="K171" s="12">
-        <v>383035.81</v>
+        <v>2285035.81</v>
       </c>
       <c r="L171" s="13">
-        <v>16.64</v>
+        <v>99.27</v>
       </c>
       <c r="M171" s="12">
-        <v>1918714.19</v>
+        <v>16714.189999999999</v>
       </c>
       <c r="N171" s="13">
-        <v>83.36</v>
+        <v>0.73</v>
       </c>
       <c r="O171" s="12">
         <v>0</v>
@@ -11690,10 +11694,10 @@
         <v>0</v>
       </c>
       <c r="Q171" s="12">
-        <v>1918714.19</v>
+        <v>16714.189999999999</v>
       </c>
       <c r="R171" s="13">
-        <v>83.36</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="172" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -12276,28 +12280,28 @@
         <v>1410000</v>
       </c>
       <c r="G182" s="12">
-        <v>30532</v>
+        <v>72587.7</v>
       </c>
       <c r="H182" s="13">
-        <v>2.17</v>
+        <v>5.15</v>
       </c>
       <c r="I182" s="12">
-        <v>89366.7</v>
+        <v>50228</v>
       </c>
       <c r="J182" s="13">
-        <v>6.34</v>
+        <v>3.56</v>
       </c>
       <c r="K182" s="12">
-        <v>119898.7</v>
+        <v>122815.7</v>
       </c>
       <c r="L182" s="13">
-        <v>8.5</v>
+        <v>8.7100000000000009</v>
       </c>
       <c r="M182" s="12">
-        <v>1290101.3</v>
+        <v>1287184.3</v>
       </c>
       <c r="N182" s="13">
-        <v>91.5</v>
+        <v>91.29</v>
       </c>
       <c r="O182" s="12">
         <v>0</v>
@@ -12306,10 +12310,10 @@
         <v>0</v>
       </c>
       <c r="Q182" s="12">
-        <v>1290101.3</v>
+        <v>1287184.3</v>
       </c>
       <c r="R182" s="13">
-        <v>91.5</v>
+        <v>91.29</v>
       </c>
     </row>
     <row r="183" spans="1:18" x14ac:dyDescent="0.25">
@@ -14148,16 +14152,16 @@
         <v>70.760000000000005</v>
       </c>
       <c r="O215" s="8">
-        <v>3495000</v>
+        <v>3295000</v>
       </c>
       <c r="P215" s="9">
-        <v>18.78</v>
+        <v>17.71</v>
       </c>
       <c r="Q215" s="8">
-        <v>9671419.3900000006</v>
+        <v>9871419.3900000006</v>
       </c>
       <c r="R215" s="9">
-        <v>51.98</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="216" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -14372,16 +14376,16 @@
         <v>100</v>
       </c>
       <c r="O219" s="12">
-        <v>1000000</v>
+        <v>800000</v>
       </c>
       <c r="P219" s="13">
-        <v>83.33</v>
+        <v>66.67</v>
       </c>
       <c r="Q219" s="12">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="R219" s="13">
-        <v>16.670000000000002</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="220" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -16084,28 +16088,28 @@
         <v>2528000</v>
       </c>
       <c r="G250" s="8">
-        <v>506847.24</v>
+        <v>615729.84</v>
       </c>
       <c r="H250" s="9">
-        <v>20.05</v>
+        <v>24.36</v>
       </c>
       <c r="I250" s="8">
-        <v>711810</v>
+        <v>665560</v>
       </c>
       <c r="J250" s="9">
-        <v>28.16</v>
+        <v>26.33</v>
       </c>
       <c r="K250" s="8">
-        <v>1218657.24</v>
+        <v>1281289.8400000001</v>
       </c>
       <c r="L250" s="9">
-        <v>48.21</v>
+        <v>50.68</v>
       </c>
       <c r="M250" s="8">
-        <v>1309342.76</v>
+        <v>1246710.1599999999</v>
       </c>
       <c r="N250" s="9">
-        <v>51.79</v>
+        <v>49.32</v>
       </c>
       <c r="O250" s="8">
         <v>20000</v>
@@ -16114,10 +16118,10 @@
         <v>0.79</v>
       </c>
       <c r="Q250" s="8">
-        <v>1289342.76</v>
+        <v>1226710.1599999999</v>
       </c>
       <c r="R250" s="9">
-        <v>51</v>
+        <v>48.52</v>
       </c>
     </row>
     <row r="251" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -16140,28 +16144,28 @@
         <v>792000</v>
       </c>
       <c r="G251" s="12">
-        <v>129000</v>
+        <v>147000</v>
       </c>
       <c r="H251" s="13">
-        <v>16.29</v>
+        <v>18.559999999999999</v>
       </c>
       <c r="I251" s="12">
-        <v>296000</v>
+        <v>335600</v>
       </c>
       <c r="J251" s="13">
-        <v>37.369999999999997</v>
+        <v>42.37</v>
       </c>
       <c r="K251" s="12">
-        <v>425000</v>
+        <v>482600</v>
       </c>
       <c r="L251" s="13">
-        <v>53.66</v>
+        <v>60.93</v>
       </c>
       <c r="M251" s="12">
-        <v>367000</v>
+        <v>309400</v>
       </c>
       <c r="N251" s="13">
-        <v>46.34</v>
+        <v>39.07</v>
       </c>
       <c r="O251" s="12">
         <v>20000</v>
@@ -16170,10 +16174,10 @@
         <v>2.5299999999999998</v>
       </c>
       <c r="Q251" s="12">
-        <v>347000</v>
+        <v>289400</v>
       </c>
       <c r="R251" s="13">
-        <v>43.81</v>
+        <v>36.54</v>
       </c>
     </row>
     <row r="252" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -16196,16 +16200,16 @@
         <v>944000</v>
       </c>
       <c r="G252" s="12">
-        <v>248027.24</v>
+        <v>273027.24</v>
       </c>
       <c r="H252" s="13">
-        <v>26.27</v>
+        <v>28.92</v>
       </c>
       <c r="I252" s="12">
-        <v>245000</v>
+        <v>220000</v>
       </c>
       <c r="J252" s="13">
-        <v>25.95</v>
+        <v>23.31</v>
       </c>
       <c r="K252" s="12">
         <v>493027.24</v>
@@ -16252,28 +16256,28 @@
         <v>792000</v>
       </c>
       <c r="G253" s="12">
-        <v>129820</v>
+        <v>195702.6</v>
       </c>
       <c r="H253" s="13">
-        <v>16.39</v>
+        <v>24.71</v>
       </c>
       <c r="I253" s="12">
-        <v>170810</v>
+        <v>109960</v>
       </c>
       <c r="J253" s="13">
-        <v>21.57</v>
+        <v>13.88</v>
       </c>
       <c r="K253" s="12">
-        <v>300630</v>
+        <v>305662.59999999998</v>
       </c>
       <c r="L253" s="13">
-        <v>37.96</v>
+        <v>38.590000000000003</v>
       </c>
       <c r="M253" s="12">
-        <v>491370</v>
+        <v>486337.4</v>
       </c>
       <c r="N253" s="13">
-        <v>62.04</v>
+        <v>61.41</v>
       </c>
       <c r="O253" s="12">
         <v>0</v>
@@ -16282,10 +16286,10 @@
         <v>0</v>
       </c>
       <c r="Q253" s="12">
-        <v>491370</v>
+        <v>486337.4</v>
       </c>
       <c r="R253" s="13">
-        <v>62.04</v>
+        <v>61.41</v>
       </c>
     </row>
     <row r="254" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -16308,16 +16312,16 @@
         <v>12554100</v>
       </c>
       <c r="G254" s="8">
-        <v>2756335.44</v>
+        <v>2866335.44</v>
       </c>
       <c r="H254" s="9">
-        <v>21.96</v>
+        <v>22.83</v>
       </c>
       <c r="I254" s="8">
-        <v>1302358.56</v>
+        <v>1192358.56</v>
       </c>
       <c r="J254" s="9">
-        <v>10.37</v>
+        <v>9.5</v>
       </c>
       <c r="K254" s="8">
         <v>4058694</v>
@@ -16420,16 +16424,16 @@
         <v>4556000</v>
       </c>
       <c r="G256" s="12">
-        <v>1374743</v>
+        <v>1484743</v>
       </c>
       <c r="H256" s="13">
-        <v>30.17</v>
+        <v>32.590000000000003</v>
       </c>
       <c r="I256" s="12">
-        <v>736100</v>
+        <v>626100</v>
       </c>
       <c r="J256" s="13">
-        <v>16.16</v>
+        <v>13.74</v>
       </c>
       <c r="K256" s="12">
         <v>2110843</v>
@@ -17042,34 +17046,34 @@
         <v>0.06</v>
       </c>
       <c r="I267" s="8">
-        <v>8370</v>
+        <v>7348620</v>
       </c>
       <c r="J267" s="9">
-        <v>0.04</v>
+        <v>37.090000000000003</v>
       </c>
       <c r="K267" s="8">
-        <v>20920</v>
+        <v>7361170</v>
       </c>
       <c r="L267" s="9">
-        <v>0.11</v>
+        <v>37.159999999999997</v>
       </c>
       <c r="M267" s="8">
-        <v>19790180</v>
+        <v>12449930</v>
       </c>
       <c r="N267" s="9">
-        <v>99.89</v>
+        <v>62.84</v>
       </c>
       <c r="O267" s="8">
-        <v>6000000</v>
+        <v>200250</v>
       </c>
       <c r="P267" s="9">
-        <v>30.29</v>
+        <v>1.01</v>
       </c>
       <c r="Q267" s="8">
-        <v>13790180</v>
+        <v>12249680</v>
       </c>
       <c r="R267" s="9">
-        <v>69.61</v>
+        <v>61.83</v>
       </c>
     </row>
     <row r="268" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -17154,34 +17158,34 @@
         <v>0</v>
       </c>
       <c r="I269" s="12">
-        <v>0</v>
+        <v>7200000</v>
       </c>
       <c r="J269" s="13">
-        <v>0</v>
+        <v>69.23</v>
       </c>
       <c r="K269" s="12">
-        <v>0</v>
+        <v>7200000</v>
       </c>
       <c r="L269" s="13">
-        <v>0</v>
+        <v>69.23</v>
       </c>
       <c r="M269" s="12">
-        <v>10400000</v>
+        <v>3200000</v>
       </c>
       <c r="N269" s="13">
-        <v>100</v>
+        <v>30.77</v>
       </c>
       <c r="O269" s="12">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="P269" s="13">
-        <v>57.69</v>
+        <v>0</v>
       </c>
       <c r="Q269" s="12">
-        <v>4400000</v>
+        <v>3200000</v>
       </c>
       <c r="R269" s="13">
-        <v>42.31</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="270" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -17378,34 +17382,34 @@
         <v>0</v>
       </c>
       <c r="I273" s="12">
-        <v>0</v>
+        <v>140250</v>
       </c>
       <c r="J273" s="13">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="K273" s="12">
-        <v>0</v>
+        <v>140250</v>
       </c>
       <c r="L273" s="13">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="M273" s="12">
-        <v>3697200</v>
+        <v>3556950</v>
       </c>
       <c r="N273" s="13">
-        <v>100</v>
+        <v>96.21</v>
       </c>
       <c r="O273" s="12">
-        <v>0</v>
+        <v>200250</v>
       </c>
       <c r="P273" s="13">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="Q273" s="12">
-        <v>3697200</v>
+        <v>3356700</v>
       </c>
       <c r="R273" s="13">
-        <v>100</v>
+        <v>90.79</v>
       </c>
     </row>
     <row r="274" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -17546,34 +17550,34 @@
         <v>0</v>
       </c>
       <c r="I276" s="8">
-        <v>0</v>
+        <v>155250</v>
       </c>
       <c r="J276" s="9">
-        <v>0</v>
+        <v>7.04</v>
       </c>
       <c r="K276" s="8">
-        <v>0</v>
+        <v>155250</v>
       </c>
       <c r="L276" s="9">
-        <v>0</v>
+        <v>7.04</v>
       </c>
       <c r="M276" s="8">
-        <v>2205500</v>
+        <v>2050250</v>
       </c>
       <c r="N276" s="9">
-        <v>100</v>
+        <v>92.96</v>
       </c>
       <c r="O276" s="8">
-        <v>0</v>
+        <v>720000</v>
       </c>
       <c r="P276" s="9">
-        <v>0</v>
+        <v>32.65</v>
       </c>
       <c r="Q276" s="8">
-        <v>2205500</v>
+        <v>1330250</v>
       </c>
       <c r="R276" s="9">
-        <v>100</v>
+        <v>60.32</v>
       </c>
     </row>
     <row r="277" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -17620,16 +17624,16 @@
         <v>100</v>
       </c>
       <c r="O277" s="12">
-        <v>0</v>
+        <v>720000</v>
       </c>
       <c r="P277" s="13">
-        <v>0</v>
+        <v>40.82</v>
       </c>
       <c r="Q277" s="12">
-        <v>1763750</v>
+        <v>1043750</v>
       </c>
       <c r="R277" s="13">
-        <v>100</v>
+        <v>59.18</v>
       </c>
     </row>
     <row r="278" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -17714,22 +17718,22 @@
         <v>0</v>
       </c>
       <c r="I279" s="12">
-        <v>0</v>
+        <v>155250</v>
       </c>
       <c r="J279" s="13">
-        <v>0</v>
+        <v>87.34</v>
       </c>
       <c r="K279" s="12">
-        <v>0</v>
+        <v>155250</v>
       </c>
       <c r="L279" s="13">
-        <v>0</v>
+        <v>87.34</v>
       </c>
       <c r="M279" s="12">
-        <v>177750</v>
+        <v>22500</v>
       </c>
       <c r="N279" s="13">
-        <v>100</v>
+        <v>12.66</v>
       </c>
       <c r="O279" s="12">
         <v>0</v>
@@ -17738,10 +17742,10 @@
         <v>0</v>
       </c>
       <c r="Q279" s="12">
-        <v>177750</v>
+        <v>22500</v>
       </c>
       <c r="R279" s="13">
-        <v>100</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="280" spans="1:18" x14ac:dyDescent="0.25">
@@ -17762,40 +17766,40 @@
         <v>100622228.15000001</v>
       </c>
       <c r="G280" s="14">
-        <v>21751803.469999999</v>
+        <v>22946611.77</v>
       </c>
       <c r="H280" s="15">
-        <v>21.62</v>
+        <v>22.8</v>
       </c>
       <c r="I280" s="14">
-        <v>11592441.65</v>
+        <v>19851637.949999999</v>
       </c>
       <c r="J280" s="15">
-        <v>11.52</v>
+        <v>19.73</v>
       </c>
       <c r="K280" s="14">
-        <v>33344245.120000001</v>
+        <v>42798249.719999999</v>
       </c>
       <c r="L280" s="15">
-        <v>33.14</v>
+        <v>42.53</v>
       </c>
       <c r="M280" s="14">
-        <v>67277983.030000001</v>
+        <v>57823978.43</v>
       </c>
       <c r="N280" s="15">
-        <v>66.86</v>
+        <v>57.47</v>
       </c>
       <c r="O280" s="14">
-        <v>11951093</v>
+        <v>6671343</v>
       </c>
       <c r="P280" s="15">
-        <v>11.88</v>
+        <v>6.63</v>
       </c>
       <c r="Q280" s="14">
-        <v>55326890.030000001</v>
+        <v>51152635.43</v>
       </c>
       <c r="R280" s="15">
-        <v>54.98</v>
+        <v>50.84</v>
       </c>
     </row>
     <row r="281" spans="1:18" x14ac:dyDescent="0.25">
@@ -17816,40 +17820,40 @@
         <v>331324428.14999998</v>
       </c>
       <c r="G281" s="16">
-        <v>164279028.61000001</v>
+        <v>166231462.38</v>
       </c>
       <c r="H281" s="17">
-        <v>49.58</v>
+        <v>50.17</v>
       </c>
       <c r="I281" s="16">
-        <v>48786830.960000001</v>
+        <v>56901772.189999998</v>
       </c>
       <c r="J281" s="17">
-        <v>14.72</v>
+        <v>17.170000000000002</v>
       </c>
       <c r="K281" s="16">
-        <v>213065859.56999999</v>
+        <v>223133234.56999999</v>
       </c>
       <c r="L281" s="17">
-        <v>64.31</v>
+        <v>67.349999999999994</v>
       </c>
       <c r="M281" s="16">
-        <v>118258568.58</v>
+        <v>108191193.58</v>
       </c>
       <c r="N281" s="17">
-        <v>35.69</v>
+        <v>32.65</v>
       </c>
       <c r="O281" s="16">
-        <v>20070792.41</v>
+        <v>14502593.91</v>
       </c>
       <c r="P281" s="17">
-        <v>6.06</v>
+        <v>4.38</v>
       </c>
       <c r="Q281" s="16">
-        <v>98187776.170000002</v>
+        <v>93688599.670000002</v>
       </c>
       <c r="R281" s="17">
-        <v>29.63</v>
+        <v>28.28</v>
       </c>
     </row>
     <row r="282" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -18092,40 +18096,40 @@
         <v>337490008.32999998</v>
       </c>
       <c r="G286" s="16">
-        <v>164279028.61000001</v>
+        <v>166231462.38</v>
       </c>
       <c r="H286" s="17">
-        <v>48.68</v>
+        <v>49.26</v>
       </c>
       <c r="I286" s="16">
-        <v>48786830.960000001</v>
+        <v>56901772.189999998</v>
       </c>
       <c r="J286" s="17">
-        <v>14.46</v>
+        <v>16.86</v>
       </c>
       <c r="K286" s="16">
-        <v>213065859.56999999</v>
+        <v>223133234.56999999</v>
       </c>
       <c r="L286" s="17">
-        <v>63.13</v>
+        <v>66.12</v>
       </c>
       <c r="M286" s="16">
-        <v>124424148.76000001</v>
+        <v>114356773.76000001</v>
       </c>
       <c r="N286" s="17">
-        <v>36.869999999999997</v>
+        <v>33.880000000000003</v>
       </c>
       <c r="O286" s="16">
-        <v>20070792.41</v>
+        <v>14502593.91</v>
       </c>
       <c r="P286" s="17">
-        <v>5.95</v>
+        <v>4.3</v>
       </c>
       <c r="Q286" s="16">
-        <v>104353356.34999999</v>
+        <v>99854179.849999994</v>
       </c>
       <c r="R286" s="17">
-        <v>30.92</v>
+        <v>29.59</v>
       </c>
     </row>
     <row r="287" spans="1:18" x14ac:dyDescent="0.25">
@@ -18148,28 +18152,28 @@
         <v>4037940.24</v>
       </c>
       <c r="G287" s="4">
-        <v>505725.98</v>
+        <v>555190.98</v>
       </c>
       <c r="H287" s="5">
-        <v>12.52</v>
+        <v>13.75</v>
       </c>
       <c r="I287" s="4">
-        <v>202893.9</v>
+        <v>158448.9</v>
       </c>
       <c r="J287" s="5">
-        <v>5.0199999999999996</v>
+        <v>3.92</v>
       </c>
       <c r="K287" s="4">
-        <v>708619.88</v>
+        <v>713639.88</v>
       </c>
       <c r="L287" s="5">
-        <v>17.55</v>
+        <v>17.670000000000002</v>
       </c>
       <c r="M287" s="4">
-        <v>3329320.36</v>
+        <v>3324300.36</v>
       </c>
       <c r="N287" s="5">
-        <v>82.45</v>
+        <v>82.33</v>
       </c>
       <c r="O287" s="4">
         <v>6129.12</v>
@@ -18178,10 +18182,10 @@
         <v>0.15</v>
       </c>
       <c r="Q287" s="4">
-        <v>3323191.24</v>
+        <v>3318171.24</v>
       </c>
       <c r="R287" s="5">
-        <v>82.3</v>
+        <v>82.17</v>
       </c>
     </row>
     <row r="288" spans="1:18" x14ac:dyDescent="0.25">
@@ -18204,28 +18208,28 @@
         <v>4037940.24</v>
       </c>
       <c r="G288" s="8">
-        <v>505725.98</v>
+        <v>555190.98</v>
       </c>
       <c r="H288" s="9">
-        <v>12.52</v>
+        <v>13.75</v>
       </c>
       <c r="I288" s="8">
-        <v>202893.9</v>
+        <v>158448.9</v>
       </c>
       <c r="J288" s="9">
-        <v>5.0199999999999996</v>
+        <v>3.92</v>
       </c>
       <c r="K288" s="8">
-        <v>708619.88</v>
+        <v>713639.88</v>
       </c>
       <c r="L288" s="9">
-        <v>17.55</v>
+        <v>17.670000000000002</v>
       </c>
       <c r="M288" s="8">
-        <v>3329320.36</v>
+        <v>3324300.36</v>
       </c>
       <c r="N288" s="9">
-        <v>82.45</v>
+        <v>82.33</v>
       </c>
       <c r="O288" s="8">
         <v>6129.12</v>
@@ -18234,10 +18238,10 @@
         <v>0.15</v>
       </c>
       <c r="Q288" s="8">
-        <v>3323191.24</v>
+        <v>3318171.24</v>
       </c>
       <c r="R288" s="9">
-        <v>82.3</v>
+        <v>82.17</v>
       </c>
     </row>
     <row r="289" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -18260,28 +18264,28 @@
         <v>4037940.24</v>
       </c>
       <c r="G289" s="12">
-        <v>505725.98</v>
+        <v>555190.98</v>
       </c>
       <c r="H289" s="13">
-        <v>12.52</v>
+        <v>13.75</v>
       </c>
       <c r="I289" s="12">
-        <v>202893.9</v>
+        <v>158448.9</v>
       </c>
       <c r="J289" s="13">
-        <v>5.0199999999999996</v>
+        <v>3.92</v>
       </c>
       <c r="K289" s="12">
-        <v>708619.88</v>
+        <v>713639.88</v>
       </c>
       <c r="L289" s="13">
-        <v>17.55</v>
+        <v>17.670000000000002</v>
       </c>
       <c r="M289" s="12">
-        <v>3329320.36</v>
+        <v>3324300.36</v>
       </c>
       <c r="N289" s="13">
-        <v>82.45</v>
+        <v>82.33</v>
       </c>
       <c r="O289" s="12">
         <v>6129.12</v>
@@ -18290,10 +18294,10 @@
         <v>0.15</v>
       </c>
       <c r="Q289" s="12">
-        <v>3323191.24</v>
+        <v>3318171.24</v>
       </c>
       <c r="R289" s="13">
-        <v>82.3</v>
+        <v>82.17</v>
       </c>
     </row>
     <row r="290" spans="1:18" x14ac:dyDescent="0.25">
@@ -18314,28 +18318,28 @@
         <v>4037940.24</v>
       </c>
       <c r="G290" s="14">
-        <v>505725.98</v>
+        <v>555190.98</v>
       </c>
       <c r="H290" s="15">
-        <v>12.52</v>
+        <v>13.75</v>
       </c>
       <c r="I290" s="14">
-        <v>202893.9</v>
+        <v>158448.9</v>
       </c>
       <c r="J290" s="15">
-        <v>5.0199999999999996</v>
+        <v>3.92</v>
       </c>
       <c r="K290" s="14">
-        <v>708619.88</v>
+        <v>713639.88</v>
       </c>
       <c r="L290" s="15">
-        <v>17.55</v>
+        <v>17.670000000000002</v>
       </c>
       <c r="M290" s="14">
-        <v>3329320.36</v>
+        <v>3324300.36</v>
       </c>
       <c r="N290" s="15">
-        <v>82.45</v>
+        <v>82.33</v>
       </c>
       <c r="O290" s="14">
         <v>6129.12</v>
@@ -18344,10 +18348,10 @@
         <v>0.15</v>
       </c>
       <c r="Q290" s="14">
-        <v>3323191.24</v>
+        <v>3318171.24</v>
       </c>
       <c r="R290" s="15">
-        <v>82.3</v>
+        <v>82.17</v>
       </c>
     </row>
     <row r="291" spans="1:18" x14ac:dyDescent="0.25">
@@ -18368,40 +18372,40 @@
         <v>341527948.56999999</v>
       </c>
       <c r="G291" s="16">
-        <v>164784754.59</v>
+        <v>166786653.36000001</v>
       </c>
       <c r="H291" s="17">
-        <v>48.25</v>
+        <v>48.84</v>
       </c>
       <c r="I291" s="16">
-        <v>48989724.859999999</v>
+        <v>57060221.090000004</v>
       </c>
       <c r="J291" s="17">
-        <v>14.34</v>
+        <v>16.71</v>
       </c>
       <c r="K291" s="16">
-        <v>213774479.44999999</v>
+        <v>223846874.44999999</v>
       </c>
       <c r="L291" s="17">
-        <v>62.59</v>
+        <v>65.540000000000006</v>
       </c>
       <c r="M291" s="16">
-        <v>127753469.12</v>
+        <v>117681074.12</v>
       </c>
       <c r="N291" s="17">
-        <v>37.409999999999997</v>
+        <v>34.46</v>
       </c>
       <c r="O291" s="16">
-        <v>20076921.530000001</v>
+        <v>14508723.029999999</v>
       </c>
       <c r="P291" s="17">
-        <v>5.88</v>
+        <v>4.25</v>
       </c>
       <c r="Q291" s="16">
-        <v>107676547.59</v>
+        <v>103172351.09</v>
       </c>
       <c r="R291" s="17">
-        <v>31.53</v>
+        <v>30.21</v>
       </c>
     </row>
     <row r="292" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -18424,40 +18428,40 @@
         <v>46540814</v>
       </c>
       <c r="G292" s="19">
-        <v>21663295.120000001</v>
+        <v>21481675.600000001</v>
       </c>
       <c r="H292" s="20">
-        <v>46.55</v>
+        <v>46.16</v>
       </c>
       <c r="I292" s="19">
-        <v>15514682.15</v>
+        <v>16350843.189999999</v>
       </c>
       <c r="J292" s="20">
-        <v>33.340000000000003</v>
+        <v>35.130000000000003</v>
       </c>
       <c r="K292" s="19">
-        <v>37177977.270000003</v>
+        <v>37832518.789999999</v>
       </c>
       <c r="L292" s="20">
-        <v>79.88</v>
+        <v>81.290000000000006</v>
       </c>
       <c r="M292" s="19">
-        <v>9362836.7300000004</v>
+        <v>8708295.2100000009</v>
       </c>
       <c r="N292" s="20">
-        <v>20.12</v>
+        <v>18.71</v>
       </c>
       <c r="O292" s="19">
-        <v>1966721.6</v>
+        <v>1938721.6</v>
       </c>
       <c r="P292" s="20">
-        <v>4.2300000000000004</v>
+        <v>4.17</v>
       </c>
       <c r="Q292" s="19">
-        <v>7396115.1299999999</v>
+        <v>6769573.6100000003</v>
       </c>
       <c r="R292" s="20">
-        <v>15.89</v>
+        <v>14.55</v>
       </c>
     </row>
     <row r="293" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -18480,40 +18484,40 @@
         <v>54940200</v>
       </c>
       <c r="G293" s="19">
-        <v>37757627.240000002</v>
+        <v>38494573.619999997</v>
       </c>
       <c r="H293" s="20">
-        <v>68.72</v>
+        <v>70.069999999999993</v>
       </c>
       <c r="I293" s="19">
-        <v>6722008.2599999998</v>
+        <v>5999195.7599999998</v>
       </c>
       <c r="J293" s="20">
-        <v>12.24</v>
+        <v>10.92</v>
       </c>
       <c r="K293" s="19">
-        <v>44479635.5</v>
+        <v>44493769.380000003</v>
       </c>
       <c r="L293" s="20">
-        <v>80.959999999999994</v>
+        <v>80.989999999999995</v>
       </c>
       <c r="M293" s="19">
-        <v>10460564.5</v>
+        <v>10446430.619999999</v>
       </c>
       <c r="N293" s="20">
-        <v>19.04</v>
+        <v>19.010000000000002</v>
       </c>
       <c r="O293" s="19">
-        <v>390422.5</v>
+        <v>1046422.5</v>
       </c>
       <c r="P293" s="20">
-        <v>0.71</v>
+        <v>1.9</v>
       </c>
       <c r="Q293" s="19">
-        <v>10070142</v>
+        <v>9400008.1199999992</v>
       </c>
       <c r="R293" s="20">
-        <v>18.329999999999998</v>
+        <v>17.11</v>
       </c>
     </row>
     <row r="294" spans="1:18" x14ac:dyDescent="0.25">
@@ -18536,28 +18540,28 @@
         <v>9800000</v>
       </c>
       <c r="G294" s="19">
-        <v>4926297.9800000004</v>
+        <v>4952297.9800000004</v>
       </c>
       <c r="H294" s="20">
-        <v>50.27</v>
+        <v>50.53</v>
       </c>
       <c r="I294" s="19">
-        <v>1046394.97</v>
+        <v>1012522.97</v>
       </c>
       <c r="J294" s="20">
-        <v>10.68</v>
+        <v>10.33</v>
       </c>
       <c r="K294" s="19">
-        <v>5972692.9500000002</v>
+        <v>5964820.9500000002</v>
       </c>
       <c r="L294" s="20">
-        <v>60.95</v>
+        <v>60.87</v>
       </c>
       <c r="M294" s="19">
-        <v>3827307.05</v>
+        <v>3835179.05</v>
       </c>
       <c r="N294" s="20">
-        <v>39.049999999999997</v>
+        <v>39.130000000000003</v>
       </c>
       <c r="O294" s="19">
         <v>2233789.54</v>
@@ -18566,10 +18570,10 @@
         <v>22.79</v>
       </c>
       <c r="Q294" s="19">
-        <v>1593517.51</v>
+        <v>1601389.51</v>
       </c>
       <c r="R294" s="20">
-        <v>16.260000000000002</v>
+        <v>16.34</v>
       </c>
     </row>
     <row r="295" spans="1:18" x14ac:dyDescent="0.25">
@@ -18592,40 +18596,40 @@
         <v>100622228.15000001</v>
       </c>
       <c r="G295" s="19">
-        <v>21751803.469999999</v>
+        <v>22946611.77</v>
       </c>
       <c r="H295" s="20">
-        <v>21.62</v>
+        <v>22.8</v>
       </c>
       <c r="I295" s="19">
-        <v>11592441.65</v>
+        <v>19851637.949999999</v>
       </c>
       <c r="J295" s="20">
-        <v>11.52</v>
+        <v>19.73</v>
       </c>
       <c r="K295" s="19">
-        <v>33344245.120000001</v>
+        <v>42798249.719999999</v>
       </c>
       <c r="L295" s="20">
-        <v>33.14</v>
+        <v>42.53</v>
       </c>
       <c r="M295" s="19">
-        <v>67277983.030000001</v>
+        <v>57823978.43</v>
       </c>
       <c r="N295" s="20">
-        <v>66.86</v>
+        <v>57.47</v>
       </c>
       <c r="O295" s="19">
-        <v>11951093</v>
+        <v>6671343</v>
       </c>
       <c r="P295" s="20">
-        <v>11.88</v>
+        <v>6.63</v>
       </c>
       <c r="Q295" s="19">
-        <v>55326890.030000001</v>
+        <v>51152635.43</v>
       </c>
       <c r="R295" s="20">
-        <v>54.98</v>
+        <v>50.84</v>
       </c>
     </row>
     <row r="296" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -18704,28 +18708,28 @@
         <v>4037940.24</v>
       </c>
       <c r="G297" s="19">
-        <v>505725.98</v>
+        <v>555190.98</v>
       </c>
       <c r="H297" s="20">
-        <v>12.52</v>
+        <v>13.75</v>
       </c>
       <c r="I297" s="19">
-        <v>202893.9</v>
+        <v>158448.9</v>
       </c>
       <c r="J297" s="20">
-        <v>5.0199999999999996</v>
+        <v>3.92</v>
       </c>
       <c r="K297" s="19">
-        <v>708619.88</v>
+        <v>713639.88</v>
       </c>
       <c r="L297" s="20">
-        <v>17.55</v>
+        <v>17.670000000000002</v>
       </c>
       <c r="M297" s="19">
-        <v>3329320.36</v>
+        <v>3324300.36</v>
       </c>
       <c r="N297" s="20">
-        <v>82.45</v>
+        <v>82.33</v>
       </c>
       <c r="O297" s="19">
         <v>6129.12</v>
@@ -18734,10 +18738,10 @@
         <v>0.15</v>
       </c>
       <c r="Q297" s="19">
-        <v>3323191.24</v>
+        <v>3318171.24</v>
       </c>
       <c r="R297" s="20">
-        <v>82.3</v>
+        <v>82.17</v>
       </c>
     </row>
     <row r="298" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -18760,40 +18764,40 @@
         <v>119421186</v>
       </c>
       <c r="G298" s="19">
-        <v>78180004.799999997</v>
+        <v>78356303.409999996</v>
       </c>
       <c r="H298" s="20">
-        <v>65.47</v>
+        <v>65.61</v>
       </c>
       <c r="I298" s="19">
-        <v>13911303.93</v>
+        <v>13687572.32</v>
       </c>
       <c r="J298" s="20">
-        <v>11.65</v>
+        <v>11.46</v>
       </c>
       <c r="K298" s="19">
-        <v>92091308.730000004</v>
+        <v>92043875.730000004</v>
       </c>
       <c r="L298" s="20">
-        <v>77.11</v>
+        <v>77.069999999999993</v>
       </c>
       <c r="M298" s="19">
-        <v>27329877.27</v>
+        <v>27377310.27</v>
       </c>
       <c r="N298" s="20">
-        <v>22.89</v>
+        <v>22.93</v>
       </c>
       <c r="O298" s="19">
-        <v>3528765.77</v>
+        <v>2612317.27</v>
       </c>
       <c r="P298" s="20">
-        <v>2.95</v>
+        <v>2.19</v>
       </c>
       <c r="Q298" s="19">
-        <v>23801111.5</v>
+        <v>24764993</v>
       </c>
       <c r="R298" s="20">
-        <v>19.93</v>
+        <v>20.74</v>
       </c>
     </row>
     <row r="299" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -18870,40 +18874,40 @@
         <v>341527948.56999999</v>
       </c>
       <c r="G300" s="19">
-        <v>164784754.59</v>
+        <v>166786653.36000001</v>
       </c>
       <c r="H300" s="20">
-        <v>48.25</v>
+        <v>48.84</v>
       </c>
       <c r="I300" s="19">
-        <v>48989724.859999999</v>
+        <v>57060221.090000004</v>
       </c>
       <c r="J300" s="20">
-        <v>14.34</v>
+        <v>16.71</v>
       </c>
       <c r="K300" s="19">
-        <v>213774479.44999999</v>
+        <v>223846874.44999999</v>
       </c>
       <c r="L300" s="20">
-        <v>62.59</v>
+        <v>65.540000000000006</v>
       </c>
       <c r="M300" s="19">
-        <v>127753469.12</v>
+        <v>117681074.12</v>
       </c>
       <c r="N300" s="20">
-        <v>37.409999999999997</v>
+        <v>34.46</v>
       </c>
       <c r="O300" s="19">
-        <v>20076921.530000001</v>
+        <v>14508723.029999999</v>
       </c>
       <c r="P300" s="20">
-        <v>5.88</v>
+        <v>4.25</v>
       </c>
       <c r="Q300" s="19">
-        <v>107676547.59</v>
+        <v>103172351.09</v>
       </c>
       <c r="R300" s="20">
-        <v>31.53</v>
+        <v>30.21</v>
       </c>
     </row>
     <row r="301" spans="1:18" x14ac:dyDescent="0.25">
@@ -18944,27 +18948,28 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A10E46C6-4964-4979-A00D-674177DC038E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AD63382-A003-4D81-892C-760F98FB6BA0}">
   <dimension ref="A1:R83"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.296875" customWidth="1"/>
-    <col min="2" max="2" width="12.796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.8984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.19921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.8984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.8984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.8984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.8984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.3984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.8984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.8984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.8984375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21" style="28" customWidth="1"/>
+    <col min="2" max="2" width="12.796875" style="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.8984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.19921875" style="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.3984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.8984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.8984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.796875" style="28" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.8984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.8984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.3984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.8984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7" style="28" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.796875" style="28" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.3984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.8984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7" style="28" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.796875" style="28"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -18978,7 +18983,7 @@
       <c r="F1" s="27"/>
       <c r="G1" s="27"/>
     </row>
-    <row r="4" spans="1:18" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
         <v>568</v>
       </c>
@@ -19194,28 +19199,28 @@
         <v>1000000</v>
       </c>
       <c r="G8" s="4">
-        <v>466919</v>
+        <v>498719</v>
       </c>
       <c r="H8" s="5">
-        <v>46.69</v>
+        <v>49.87</v>
       </c>
       <c r="I8" s="4">
-        <v>68570</v>
+        <v>30120</v>
       </c>
       <c r="J8" s="5">
-        <v>6.86</v>
+        <v>3.01</v>
       </c>
       <c r="K8" s="4">
-        <v>535489</v>
+        <v>528839</v>
       </c>
       <c r="L8" s="5">
-        <v>53.55</v>
+        <v>52.88</v>
       </c>
       <c r="M8" s="4">
-        <v>464511</v>
+        <v>471161</v>
       </c>
       <c r="N8" s="5">
-        <v>46.45</v>
+        <v>47.12</v>
       </c>
       <c r="O8" s="4">
         <v>0</v>
@@ -19224,13 +19229,13 @@
         <v>0</v>
       </c>
       <c r="Q8" s="4">
-        <v>464511</v>
+        <v>471161</v>
       </c>
       <c r="R8" s="5">
-        <v>46.45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+        <v>47.12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>201</v>
       </c>
@@ -19250,28 +19255,28 @@
         <v>1000000</v>
       </c>
       <c r="G9" s="8">
-        <v>466919</v>
+        <v>498719</v>
       </c>
       <c r="H9" s="9">
-        <v>46.69</v>
+        <v>49.87</v>
       </c>
       <c r="I9" s="8">
-        <v>68570</v>
+        <v>30120</v>
       </c>
       <c r="J9" s="9">
-        <v>6.86</v>
+        <v>3.01</v>
       </c>
       <c r="K9" s="8">
-        <v>535489</v>
+        <v>528839</v>
       </c>
       <c r="L9" s="9">
-        <v>53.55</v>
+        <v>52.88</v>
       </c>
       <c r="M9" s="8">
-        <v>464511</v>
+        <v>471161</v>
       </c>
       <c r="N9" s="9">
-        <v>46.45</v>
+        <v>47.12</v>
       </c>
       <c r="O9" s="8">
         <v>0</v>
@@ -19280,10 +19285,10 @@
         <v>0</v>
       </c>
       <c r="Q9" s="8">
-        <v>464511</v>
+        <v>471161</v>
       </c>
       <c r="R9" s="9">
-        <v>46.45</v>
+        <v>47.12</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -19304,28 +19309,28 @@
         <v>11720000</v>
       </c>
       <c r="G10" s="4">
-        <v>7555576</v>
+        <v>7481436</v>
       </c>
       <c r="H10" s="5">
-        <v>64.47</v>
+        <v>63.83</v>
       </c>
       <c r="I10" s="4">
-        <v>1610493</v>
+        <v>1458873</v>
       </c>
       <c r="J10" s="5">
-        <v>13.74</v>
+        <v>12.45</v>
       </c>
       <c r="K10" s="4">
-        <v>9166069</v>
+        <v>8940309</v>
       </c>
       <c r="L10" s="5">
-        <v>78.209999999999994</v>
+        <v>76.28</v>
       </c>
       <c r="M10" s="4">
-        <v>2553931</v>
+        <v>2779691</v>
       </c>
       <c r="N10" s="5">
-        <v>21.79</v>
+        <v>23.72</v>
       </c>
       <c r="O10" s="4">
         <v>600</v>
@@ -19334,10 +19339,10 @@
         <v>0.01</v>
       </c>
       <c r="Q10" s="4">
-        <v>2553331</v>
+        <v>2779091</v>
       </c>
       <c r="R10" s="5">
-        <v>21.79</v>
+        <v>23.71</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -19360,28 +19365,28 @@
         <v>11720000</v>
       </c>
       <c r="G11" s="8">
-        <v>7555576</v>
+        <v>7481436</v>
       </c>
       <c r="H11" s="9">
-        <v>64.47</v>
+        <v>63.83</v>
       </c>
       <c r="I11" s="8">
-        <v>1610493</v>
+        <v>1458873</v>
       </c>
       <c r="J11" s="9">
-        <v>13.74</v>
+        <v>12.45</v>
       </c>
       <c r="K11" s="8">
-        <v>9166069</v>
+        <v>8940309</v>
       </c>
       <c r="L11" s="9">
-        <v>78.209999999999994</v>
+        <v>76.28</v>
       </c>
       <c r="M11" s="8">
-        <v>2553931</v>
+        <v>2779691</v>
       </c>
       <c r="N11" s="9">
-        <v>21.79</v>
+        <v>23.72</v>
       </c>
       <c r="O11" s="8">
         <v>600</v>
@@ -19390,10 +19395,10 @@
         <v>0.01</v>
       </c>
       <c r="Q11" s="8">
-        <v>2553331</v>
+        <v>2779091</v>
       </c>
       <c r="R11" s="9">
-        <v>21.79</v>
+        <v>23.71</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -19414,43 +19419,43 @@
         <v>11820000</v>
       </c>
       <c r="G12" s="4">
-        <v>8134764.4299999997</v>
+        <v>8448373.2899999991</v>
       </c>
       <c r="H12" s="5">
-        <v>68.819999999999993</v>
+        <v>71.48</v>
       </c>
       <c r="I12" s="4">
-        <v>1281297</v>
+        <v>1227197</v>
       </c>
       <c r="J12" s="5">
-        <v>10.84</v>
+        <v>10.38</v>
       </c>
       <c r="K12" s="4">
-        <v>9416061.4299999997</v>
+        <v>9675570.2899999991</v>
       </c>
       <c r="L12" s="5">
-        <v>79.66</v>
+        <v>81.86</v>
       </c>
       <c r="M12" s="4">
-        <v>2403938.5699999998</v>
+        <v>2144429.71</v>
       </c>
       <c r="N12" s="5">
-        <v>20.34</v>
+        <v>18.14</v>
       </c>
       <c r="O12" s="4">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="P12" s="5">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="Q12" s="4">
-        <v>2403938.5699999998</v>
+        <v>2064429.71</v>
       </c>
       <c r="R12" s="5">
-        <v>20.34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+        <v>17.47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>81</v>
       </c>
@@ -19470,28 +19475,28 @@
         <v>1180000</v>
       </c>
       <c r="G13" s="8">
-        <v>603349</v>
+        <v>638349</v>
       </c>
       <c r="H13" s="9">
-        <v>51.13</v>
+        <v>54.1</v>
       </c>
       <c r="I13" s="8">
-        <v>35800</v>
+        <v>277000</v>
       </c>
       <c r="J13" s="9">
-        <v>3.03</v>
+        <v>23.47</v>
       </c>
       <c r="K13" s="8">
-        <v>639149</v>
+        <v>915349</v>
       </c>
       <c r="L13" s="9">
-        <v>54.17</v>
+        <v>77.569999999999993</v>
       </c>
       <c r="M13" s="8">
-        <v>540851</v>
+        <v>264651</v>
       </c>
       <c r="N13" s="9">
-        <v>45.83</v>
+        <v>22.43</v>
       </c>
       <c r="O13" s="8">
         <v>0</v>
@@ -19500,10 +19505,10 @@
         <v>0</v>
       </c>
       <c r="Q13" s="8">
-        <v>540851</v>
+        <v>264651</v>
       </c>
       <c r="R13" s="9">
-        <v>45.83</v>
+        <v>22.43</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -19526,40 +19531,40 @@
         <v>10640000</v>
       </c>
       <c r="G14" s="8">
-        <v>7531415.4299999997</v>
+        <v>7810024.29</v>
       </c>
       <c r="H14" s="9">
-        <v>70.78</v>
+        <v>73.400000000000006</v>
       </c>
       <c r="I14" s="8">
-        <v>1245497</v>
+        <v>950197</v>
       </c>
       <c r="J14" s="9">
-        <v>11.71</v>
+        <v>8.93</v>
       </c>
       <c r="K14" s="8">
-        <v>8776912.4299999997</v>
+        <v>8760221.2899999991</v>
       </c>
       <c r="L14" s="9">
-        <v>82.49</v>
+        <v>82.33</v>
       </c>
       <c r="M14" s="8">
-        <v>1863087.57</v>
+        <v>1879778.71</v>
       </c>
       <c r="N14" s="9">
-        <v>17.510000000000002</v>
+        <v>17.670000000000002</v>
       </c>
       <c r="O14" s="8">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="P14" s="9">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="Q14" s="8">
-        <v>1863087.57</v>
+        <v>1799778.71</v>
       </c>
       <c r="R14" s="9">
-        <v>17.510000000000002</v>
+        <v>16.920000000000002</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -19580,43 +19585,43 @@
         <v>11840200</v>
       </c>
       <c r="G15" s="4">
-        <v>7976696.54</v>
+        <v>8763472.8599999994</v>
       </c>
       <c r="H15" s="5">
-        <v>67.37</v>
+        <v>74.010000000000005</v>
       </c>
       <c r="I15" s="4">
-        <v>2121092.67</v>
+        <v>1455847.35</v>
       </c>
       <c r="J15" s="5">
-        <v>17.91</v>
+        <v>12.3</v>
       </c>
       <c r="K15" s="4">
-        <v>10097789.210000001</v>
+        <v>10219320.210000001</v>
       </c>
       <c r="L15" s="5">
-        <v>85.28</v>
+        <v>86.31</v>
       </c>
       <c r="M15" s="4">
-        <v>1742410.79</v>
+        <v>1620879.79</v>
       </c>
       <c r="N15" s="5">
-        <v>14.72</v>
+        <v>13.69</v>
       </c>
       <c r="O15" s="4">
-        <v>118801.1</v>
+        <v>144801.1</v>
       </c>
       <c r="P15" s="5">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="Q15" s="4">
-        <v>1623609.69</v>
+        <v>1476078.69</v>
       </c>
       <c r="R15" s="5">
-        <v>13.71</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
+        <v>12.47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>75</v>
       </c>
@@ -19636,28 +19641,28 @@
         <v>500000</v>
       </c>
       <c r="G16" s="8">
-        <v>343308.9</v>
+        <v>357667.9</v>
       </c>
       <c r="H16" s="9">
-        <v>68.66</v>
+        <v>71.53</v>
       </c>
       <c r="I16" s="8">
-        <v>137550</v>
+        <v>118800</v>
       </c>
       <c r="J16" s="9">
-        <v>27.51</v>
+        <v>23.76</v>
       </c>
       <c r="K16" s="8">
-        <v>480858.9</v>
+        <v>476467.9</v>
       </c>
       <c r="L16" s="9">
-        <v>96.17</v>
+        <v>95.29</v>
       </c>
       <c r="M16" s="8">
-        <v>19141.099999999999</v>
+        <v>23532.1</v>
       </c>
       <c r="N16" s="9">
-        <v>3.83</v>
+        <v>4.71</v>
       </c>
       <c r="O16" s="8">
         <v>4721.6000000000004</v>
@@ -19666,10 +19671,10 @@
         <v>0.94</v>
       </c>
       <c r="Q16" s="8">
-        <v>14419.5</v>
+        <v>18810.5</v>
       </c>
       <c r="R16" s="9">
-        <v>2.88</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -19692,40 +19697,40 @@
         <v>11340200</v>
       </c>
       <c r="G17" s="8">
-        <v>7633387.6399999997</v>
+        <v>8405804.9600000009</v>
       </c>
       <c r="H17" s="9">
-        <v>67.31</v>
+        <v>74.12</v>
       </c>
       <c r="I17" s="8">
-        <v>1983542.67</v>
+        <v>1337047.3500000001</v>
       </c>
       <c r="J17" s="9">
-        <v>17.489999999999998</v>
+        <v>11.79</v>
       </c>
       <c r="K17" s="8">
-        <v>9616930.3100000005</v>
+        <v>9742852.3100000005</v>
       </c>
       <c r="L17" s="9">
-        <v>84.8</v>
+        <v>85.91</v>
       </c>
       <c r="M17" s="8">
-        <v>1723269.69</v>
+        <v>1597347.69</v>
       </c>
       <c r="N17" s="9">
-        <v>15.2</v>
+        <v>14.09</v>
       </c>
       <c r="O17" s="8">
-        <v>114079.5</v>
+        <v>140079.5</v>
       </c>
       <c r="P17" s="9">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="Q17" s="8">
-        <v>1609190.19</v>
+        <v>1457268.19</v>
       </c>
       <c r="R17" s="9">
-        <v>14.19</v>
+        <v>12.85</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -19746,43 +19751,43 @@
         <v>7820000</v>
       </c>
       <c r="G18" s="4">
-        <v>5317978.5999999996</v>
+        <v>5358529.5999999996</v>
       </c>
       <c r="H18" s="5">
-        <v>68</v>
+        <v>68.52</v>
       </c>
       <c r="I18" s="4">
-        <v>650010</v>
+        <v>603659</v>
       </c>
       <c r="J18" s="5">
-        <v>8.31</v>
+        <v>7.72</v>
       </c>
       <c r="K18" s="4">
-        <v>5967988.5999999996</v>
+        <v>5962188.5999999996</v>
       </c>
       <c r="L18" s="5">
-        <v>76.319999999999993</v>
+        <v>76.239999999999995</v>
       </c>
       <c r="M18" s="4">
-        <v>1852011.4</v>
+        <v>1857811.4</v>
       </c>
       <c r="N18" s="5">
-        <v>23.68</v>
+        <v>23.76</v>
       </c>
       <c r="O18" s="4">
-        <v>0</v>
+        <v>550000</v>
       </c>
       <c r="P18" s="5">
-        <v>0</v>
+        <v>7.03</v>
       </c>
       <c r="Q18" s="4">
-        <v>1852011.4</v>
+        <v>1307811.3999999999</v>
       </c>
       <c r="R18" s="5">
-        <v>23.68</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+        <v>16.72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>161</v>
       </c>
@@ -19802,40 +19807,40 @@
         <v>7820000</v>
       </c>
       <c r="G19" s="8">
-        <v>5317978.5999999996</v>
+        <v>5358529.5999999996</v>
       </c>
       <c r="H19" s="9">
-        <v>68</v>
+        <v>68.52</v>
       </c>
       <c r="I19" s="8">
-        <v>650010</v>
+        <v>603659</v>
       </c>
       <c r="J19" s="9">
-        <v>8.31</v>
+        <v>7.72</v>
       </c>
       <c r="K19" s="8">
-        <v>5967988.5999999996</v>
+        <v>5962188.5999999996</v>
       </c>
       <c r="L19" s="9">
-        <v>76.319999999999993</v>
+        <v>76.239999999999995</v>
       </c>
       <c r="M19" s="8">
-        <v>1852011.4</v>
+        <v>1857811.4</v>
       </c>
       <c r="N19" s="9">
-        <v>23.68</v>
+        <v>23.76</v>
       </c>
       <c r="O19" s="8">
-        <v>0</v>
+        <v>550000</v>
       </c>
       <c r="P19" s="9">
-        <v>0</v>
+        <v>7.03</v>
       </c>
       <c r="Q19" s="8">
-        <v>1852011.4</v>
+        <v>1307811.3999999999</v>
       </c>
       <c r="R19" s="9">
-        <v>23.68</v>
+        <v>16.72</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -19856,28 +19861,28 @@
         <v>13420000</v>
       </c>
       <c r="G20" s="4">
-        <v>9719269.5700000003</v>
+        <v>9438778.7699999996</v>
       </c>
       <c r="H20" s="5">
-        <v>72.42</v>
+        <v>70.33</v>
       </c>
       <c r="I20" s="4">
-        <v>1232465.5900000001</v>
+        <v>1649419.41</v>
       </c>
       <c r="J20" s="5">
-        <v>9.18</v>
+        <v>12.29</v>
       </c>
       <c r="K20" s="4">
-        <v>10951735.16</v>
+        <v>11088198.18</v>
       </c>
       <c r="L20" s="5">
-        <v>81.61</v>
+        <v>82.62</v>
       </c>
       <c r="M20" s="4">
-        <v>2468264.84</v>
+        <v>2331801.8199999998</v>
       </c>
       <c r="N20" s="5">
-        <v>18.39</v>
+        <v>17.38</v>
       </c>
       <c r="O20" s="4">
         <v>275743</v>
@@ -19886,13 +19891,13 @@
         <v>2.0499999999999998</v>
       </c>
       <c r="Q20" s="4">
-        <v>2192521.84</v>
+        <v>2056058.82</v>
       </c>
       <c r="R20" s="5">
-        <v>16.34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+        <v>15.32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>111</v>
       </c>
@@ -19912,28 +19917,28 @@
         <v>13420000</v>
       </c>
       <c r="G21" s="8">
-        <v>9719269.5700000003</v>
+        <v>9438778.7699999996</v>
       </c>
       <c r="H21" s="9">
-        <v>72.42</v>
+        <v>70.33</v>
       </c>
       <c r="I21" s="8">
-        <v>1232465.5900000001</v>
+        <v>1649419.41</v>
       </c>
       <c r="J21" s="9">
-        <v>9.18</v>
+        <v>12.29</v>
       </c>
       <c r="K21" s="8">
-        <v>10951735.16</v>
+        <v>11088198.18</v>
       </c>
       <c r="L21" s="9">
-        <v>81.61</v>
+        <v>82.62</v>
       </c>
       <c r="M21" s="8">
-        <v>2468264.84</v>
+        <v>2331801.8199999998</v>
       </c>
       <c r="N21" s="9">
-        <v>18.39</v>
+        <v>17.38</v>
       </c>
       <c r="O21" s="8">
         <v>275743</v>
@@ -19942,10 +19947,10 @@
         <v>2.0499999999999998</v>
       </c>
       <c r="Q21" s="8">
-        <v>2192521.84</v>
+        <v>2056058.82</v>
       </c>
       <c r="R21" s="9">
-        <v>16.34</v>
+        <v>15.32</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -19966,40 +19971,40 @@
         <v>107227000</v>
       </c>
       <c r="G22" s="4">
-        <v>73883767.060000002</v>
+        <v>74028265.670000002</v>
       </c>
       <c r="H22" s="5">
-        <v>68.900000000000006</v>
+        <v>69.040000000000006</v>
       </c>
       <c r="I22" s="4">
-        <v>7741815.3300000001</v>
+        <v>7556427.7199999997</v>
       </c>
       <c r="J22" s="5">
-        <v>7.22</v>
+        <v>7.05</v>
       </c>
       <c r="K22" s="4">
-        <v>81625582.390000001</v>
+        <v>81584693.390000001</v>
       </c>
       <c r="L22" s="5">
-        <v>76.12</v>
+        <v>76.09</v>
       </c>
       <c r="M22" s="4">
-        <v>25601417.609999999</v>
+        <v>25642306.609999999</v>
       </c>
       <c r="N22" s="5">
-        <v>23.88</v>
+        <v>23.91</v>
       </c>
       <c r="O22" s="4">
-        <v>2630833.37</v>
+        <v>1640875.87</v>
       </c>
       <c r="P22" s="5">
-        <v>2.4500000000000002</v>
+        <v>1.53</v>
       </c>
       <c r="Q22" s="4">
-        <v>22970584.239999998</v>
+        <v>24001430.739999998</v>
       </c>
       <c r="R22" s="5">
-        <v>21.42</v>
+        <v>22.38</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -20022,40 +20027,40 @@
         <v>29200000</v>
       </c>
       <c r="G23" s="8">
-        <v>16096171.26</v>
+        <v>16148502.869999999</v>
       </c>
       <c r="H23" s="9">
-        <v>55.12</v>
+        <v>55.3</v>
       </c>
       <c r="I23" s="8">
-        <v>7442003.5999999996</v>
+        <v>7352779.9900000002</v>
       </c>
       <c r="J23" s="9">
-        <v>25.49</v>
+        <v>25.18</v>
       </c>
       <c r="K23" s="8">
-        <v>23538174.859999999</v>
+        <v>23501282.859999999</v>
       </c>
       <c r="L23" s="9">
-        <v>80.61</v>
+        <v>80.48</v>
       </c>
       <c r="M23" s="8">
-        <v>5661825.1399999997</v>
+        <v>5698717.1399999997</v>
       </c>
       <c r="N23" s="9">
-        <v>19.39</v>
+        <v>19.52</v>
       </c>
       <c r="O23" s="8">
-        <v>2610833.37</v>
+        <v>1639333.37</v>
       </c>
       <c r="P23" s="9">
-        <v>8.94</v>
+        <v>5.61</v>
       </c>
       <c r="Q23" s="8">
-        <v>3050991.77</v>
+        <v>4059383.77</v>
       </c>
       <c r="R23" s="9">
-        <v>10.45</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="24" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -20078,43 +20083,43 @@
         <v>78027000</v>
       </c>
       <c r="G24" s="8">
-        <v>57787595.799999997</v>
+        <v>57879762.799999997</v>
       </c>
       <c r="H24" s="9">
-        <v>74.06</v>
+        <v>74.180000000000007</v>
       </c>
       <c r="I24" s="8">
-        <v>299811.73</v>
+        <v>203647.73</v>
       </c>
       <c r="J24" s="9">
-        <v>0.38</v>
+        <v>0.26</v>
       </c>
       <c r="K24" s="8">
-        <v>58087407.530000001</v>
+        <v>58083410.530000001</v>
       </c>
       <c r="L24" s="9">
-        <v>74.45</v>
+        <v>74.44</v>
       </c>
       <c r="M24" s="8">
-        <v>19939592.469999999</v>
+        <v>19943589.469999999</v>
       </c>
       <c r="N24" s="9">
-        <v>25.55</v>
+        <v>25.56</v>
       </c>
       <c r="O24" s="8">
-        <v>20000</v>
+        <v>1542.5</v>
       </c>
       <c r="P24" s="9">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="8">
-        <v>19919592.469999999</v>
+        <v>19942046.969999999</v>
       </c>
       <c r="R24" s="9">
-        <v>25.53</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+        <v>25.56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>229</v>
       </c>
@@ -20188,34 +20193,34 @@
         <v>4260000</v>
       </c>
       <c r="G26" s="4">
-        <v>1698170.43</v>
+        <v>1700370.43</v>
       </c>
       <c r="H26" s="5">
-        <v>39.86</v>
+        <v>39.909999999999997</v>
       </c>
       <c r="I26" s="4">
-        <v>554621.67000000004</v>
+        <v>580421.67000000004</v>
       </c>
       <c r="J26" s="5">
-        <v>13.02</v>
+        <v>13.62</v>
       </c>
       <c r="K26" s="4">
-        <v>2252792.1</v>
+        <v>2280792.1</v>
       </c>
       <c r="L26" s="5">
-        <v>52.88</v>
+        <v>53.54</v>
       </c>
       <c r="M26" s="4">
-        <v>2007207.9</v>
+        <v>1979207.9</v>
       </c>
       <c r="N26" s="5">
-        <v>47.12</v>
+        <v>46.46</v>
       </c>
       <c r="O26" s="4">
-        <v>282000</v>
+        <v>254000</v>
       </c>
       <c r="P26" s="5">
-        <v>6.62</v>
+        <v>5.96</v>
       </c>
       <c r="Q26" s="4">
         <v>1725207.9</v>
@@ -20224,7 +20229,7 @@
         <v>40.5</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>59</v>
       </c>
@@ -20244,34 +20249,34 @@
         <v>4260000</v>
       </c>
       <c r="G27" s="8">
-        <v>1698170.43</v>
+        <v>1700370.43</v>
       </c>
       <c r="H27" s="9">
-        <v>39.86</v>
+        <v>39.909999999999997</v>
       </c>
       <c r="I27" s="8">
-        <v>554621.67000000004</v>
+        <v>580421.67000000004</v>
       </c>
       <c r="J27" s="9">
-        <v>13.02</v>
+        <v>13.62</v>
       </c>
       <c r="K27" s="8">
-        <v>2252792.1</v>
+        <v>2280792.1</v>
       </c>
       <c r="L27" s="9">
-        <v>52.88</v>
+        <v>53.54</v>
       </c>
       <c r="M27" s="8">
-        <v>2007207.9</v>
+        <v>1979207.9</v>
       </c>
       <c r="N27" s="9">
-        <v>47.12</v>
+        <v>46.46</v>
       </c>
       <c r="O27" s="8">
-        <v>282000</v>
+        <v>254000</v>
       </c>
       <c r="P27" s="9">
-        <v>6.62</v>
+        <v>5.96</v>
       </c>
       <c r="Q27" s="8">
         <v>1725207.9</v>
@@ -20298,43 +20303,43 @@
         <v>60595000</v>
       </c>
       <c r="G28" s="4">
-        <v>27043607.77</v>
+        <v>26836429.25</v>
       </c>
       <c r="H28" s="5">
-        <v>44.63</v>
+        <v>44.29</v>
       </c>
       <c r="I28" s="4">
-        <v>21739356.050000001</v>
+        <v>22293501.09</v>
       </c>
       <c r="J28" s="5">
-        <v>35.880000000000003</v>
+        <v>36.79</v>
       </c>
       <c r="K28" s="4">
-        <v>48782963.82</v>
+        <v>49129930.340000004</v>
       </c>
       <c r="L28" s="5">
-        <v>80.510000000000005</v>
+        <v>81.08</v>
       </c>
       <c r="M28" s="4">
-        <v>11812036.18</v>
+        <v>11465069.66</v>
       </c>
       <c r="N28" s="5">
-        <v>19.489999999999998</v>
+        <v>18.920000000000002</v>
       </c>
       <c r="O28" s="4">
-        <v>4811721.9400000004</v>
+        <v>4885230.9400000004</v>
       </c>
       <c r="P28" s="5">
-        <v>7.94</v>
+        <v>8.06</v>
       </c>
       <c r="Q28" s="4">
-        <v>7000314.2400000002</v>
+        <v>6579838.7199999997</v>
       </c>
       <c r="R28" s="5">
-        <v>11.55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+        <v>10.86</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>17</v>
       </c>
@@ -20354,28 +20359,28 @@
         <v>37235000</v>
       </c>
       <c r="G29" s="8">
-        <v>16834530.120000001</v>
+        <v>16601351.6</v>
       </c>
       <c r="H29" s="9">
-        <v>45.21</v>
+        <v>44.59</v>
       </c>
       <c r="I29" s="8">
-        <v>14215282.48</v>
+        <v>14809523.52</v>
       </c>
       <c r="J29" s="9">
-        <v>38.18</v>
+        <v>39.770000000000003</v>
       </c>
       <c r="K29" s="8">
-        <v>31049812.600000001</v>
+        <v>31410875.120000001</v>
       </c>
       <c r="L29" s="9">
-        <v>83.39</v>
+        <v>84.36</v>
       </c>
       <c r="M29" s="8">
-        <v>6185187.4000000004</v>
+        <v>5824124.8799999999</v>
       </c>
       <c r="N29" s="9">
-        <v>16.61</v>
+        <v>15.64</v>
       </c>
       <c r="O29" s="8">
         <v>1680000</v>
@@ -20384,10 +20389,10 @@
         <v>4.51</v>
       </c>
       <c r="Q29" s="8">
-        <v>4505187.4000000004</v>
+        <v>4144124.88</v>
       </c>
       <c r="R29" s="9">
-        <v>12.1</v>
+        <v>11.13</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -20416,22 +20421,22 @@
         <v>81.48</v>
       </c>
       <c r="I30" s="8">
-        <v>156070</v>
+        <v>150000</v>
       </c>
       <c r="J30" s="9">
-        <v>20.73</v>
+        <v>19.920000000000002</v>
       </c>
       <c r="K30" s="8">
-        <v>769520</v>
+        <v>763450</v>
       </c>
       <c r="L30" s="9">
-        <v>102.21</v>
+        <v>101.4</v>
       </c>
       <c r="M30" s="8">
-        <v>-16620</v>
+        <v>-10550</v>
       </c>
       <c r="N30" s="9">
-        <v>-2.21</v>
+        <v>-1.4</v>
       </c>
       <c r="O30" s="8">
         <v>0</v>
@@ -20440,13 +20445,13 @@
         <v>0</v>
       </c>
       <c r="Q30" s="8">
-        <v>-16620</v>
+        <v>-10550</v>
       </c>
       <c r="R30" s="9">
-        <v>-2.21</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>87</v>
       </c>
@@ -20472,22 +20477,22 @@
         <v>60.1</v>
       </c>
       <c r="I31" s="8">
-        <v>415358</v>
+        <v>415098</v>
       </c>
       <c r="J31" s="9">
-        <v>15.9</v>
+        <v>15.89</v>
       </c>
       <c r="K31" s="8">
-        <v>1985844.67</v>
+        <v>1985584.67</v>
       </c>
       <c r="L31" s="9">
-        <v>76</v>
+        <v>75.989999999999995</v>
       </c>
       <c r="M31" s="8">
-        <v>627069.32999999996</v>
+        <v>627329.32999999996</v>
       </c>
       <c r="N31" s="9">
-        <v>24</v>
+        <v>24.01</v>
       </c>
       <c r="O31" s="8">
         <v>0</v>
@@ -20496,13 +20501,13 @@
         <v>0</v>
       </c>
       <c r="Q31" s="8">
-        <v>627069.32999999996</v>
+        <v>627329.32999999996</v>
       </c>
       <c r="R31" s="9">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
+        <v>24.01</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>180</v>
       </c>
@@ -20522,28 +20527,28 @@
         <v>9800000</v>
       </c>
       <c r="G32" s="8">
-        <v>4926297.9800000004</v>
+        <v>4952297.9800000004</v>
       </c>
       <c r="H32" s="9">
-        <v>50.27</v>
+        <v>50.53</v>
       </c>
       <c r="I32" s="8">
-        <v>1046394.97</v>
+        <v>1012522.97</v>
       </c>
       <c r="J32" s="9">
-        <v>10.68</v>
+        <v>10.33</v>
       </c>
       <c r="K32" s="8">
-        <v>5972692.9500000002</v>
+        <v>5964820.9500000002</v>
       </c>
       <c r="L32" s="9">
-        <v>60.95</v>
+        <v>60.87</v>
       </c>
       <c r="M32" s="8">
-        <v>3827307.05</v>
+        <v>3835179.05</v>
       </c>
       <c r="N32" s="9">
-        <v>39.049999999999997</v>
+        <v>39.130000000000003</v>
       </c>
       <c r="O32" s="8">
         <v>2233789.54</v>
@@ -20552,13 +20557,13 @@
         <v>22.79</v>
       </c>
       <c r="Q32" s="8">
-        <v>1593517.51</v>
+        <v>1601389.51</v>
       </c>
       <c r="R32" s="9">
-        <v>16.260000000000002</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+        <v>16.34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>213</v>
       </c>
@@ -20584,34 +20589,34 @@
         <v>30.4</v>
       </c>
       <c r="I33" s="8">
-        <v>5906250.5999999996</v>
+        <v>5906356.5999999996</v>
       </c>
       <c r="J33" s="9">
         <v>57.94</v>
       </c>
       <c r="K33" s="8">
-        <v>9005093.5999999996</v>
+        <v>9005199.5999999996</v>
       </c>
       <c r="L33" s="9">
         <v>88.34</v>
       </c>
       <c r="M33" s="8">
-        <v>1189092.3999999999</v>
+        <v>1188986.3999999999</v>
       </c>
       <c r="N33" s="9">
         <v>11.66</v>
       </c>
       <c r="O33" s="8">
-        <v>897932.4</v>
+        <v>971441.4</v>
       </c>
       <c r="P33" s="9">
-        <v>8.81</v>
+        <v>9.5299999999999994</v>
       </c>
       <c r="Q33" s="8">
-        <v>291160</v>
+        <v>217545</v>
       </c>
       <c r="R33" s="9">
-        <v>2.86</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
@@ -20632,40 +20637,40 @@
         <v>230702200</v>
       </c>
       <c r="G34" s="14">
-        <v>142527225.13999999</v>
+        <v>143284850.61000001</v>
       </c>
       <c r="H34" s="15">
-        <v>61.78</v>
+        <v>62.11</v>
       </c>
       <c r="I34" s="14">
-        <v>37194389.310000002</v>
+        <v>37050134.240000002</v>
       </c>
       <c r="J34" s="15">
-        <v>16.12</v>
+        <v>16.059999999999999</v>
       </c>
       <c r="K34" s="14">
-        <v>179721614.44999999</v>
+        <v>180334984.84999999</v>
       </c>
       <c r="L34" s="15">
-        <v>77.900000000000006</v>
+        <v>78.17</v>
       </c>
       <c r="M34" s="14">
-        <v>50980585.549999997</v>
+        <v>50367215.149999999</v>
       </c>
       <c r="N34" s="15">
-        <v>22.1</v>
+        <v>21.83</v>
       </c>
       <c r="O34" s="14">
-        <v>8119699.4100000001</v>
+        <v>7831250.9100000001</v>
       </c>
       <c r="P34" s="15">
-        <v>3.52</v>
+        <v>3.39</v>
       </c>
       <c r="Q34" s="14">
-        <v>42860886.140000001</v>
+        <v>42535964.240000002</v>
       </c>
       <c r="R34" s="15">
-        <v>18.579999999999998</v>
+        <v>18.440000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
@@ -20722,7 +20727,7 @@
         <v>54.44</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="66" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>279</v>
       </c>
@@ -20832,7 +20837,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>236</v>
       </c>
@@ -20942,7 +20947,7 @@
         <v>39.450000000000003</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
         <v>307</v>
       </c>
@@ -21016,43 +21021,43 @@
         <v>22528181.809999999</v>
       </c>
       <c r="G41" s="4">
-        <v>6725078.3799999999</v>
+        <v>7768948.3799999999</v>
       </c>
       <c r="H41" s="5">
-        <v>29.85</v>
+        <v>34.49</v>
       </c>
       <c r="I41" s="4">
-        <v>3207875.72</v>
+        <v>2310210.7200000002</v>
       </c>
       <c r="J41" s="5">
-        <v>14.24</v>
+        <v>10.25</v>
       </c>
       <c r="K41" s="4">
-        <v>9932954.0999999996</v>
+        <v>10079159.1</v>
       </c>
       <c r="L41" s="5">
-        <v>44.09</v>
+        <v>44.74</v>
       </c>
       <c r="M41" s="4">
-        <v>12595227.710000001</v>
+        <v>12449022.710000001</v>
       </c>
       <c r="N41" s="5">
-        <v>55.91</v>
+        <v>55.26</v>
       </c>
       <c r="O41" s="4">
-        <v>1477593</v>
+        <v>2197593</v>
       </c>
       <c r="P41" s="5">
-        <v>6.56</v>
+        <v>9.75</v>
       </c>
       <c r="Q41" s="4">
-        <v>11117634.710000001</v>
+        <v>10251429.710000001</v>
       </c>
       <c r="R41" s="5">
-        <v>49.35</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
         <v>267</v>
       </c>
@@ -21072,28 +21077,28 @@
         <v>7768581.8099999996</v>
       </c>
       <c r="G42" s="8">
-        <v>3968742.94</v>
+        <v>4902612.9400000004</v>
       </c>
       <c r="H42" s="9">
-        <v>51.09</v>
+        <v>63.11</v>
       </c>
       <c r="I42" s="8">
-        <v>1905517.16</v>
+        <v>962602.16</v>
       </c>
       <c r="J42" s="9">
-        <v>24.53</v>
+        <v>12.39</v>
       </c>
       <c r="K42" s="8">
-        <v>5874260.0999999996</v>
+        <v>5865215.0999999996</v>
       </c>
       <c r="L42" s="9">
-        <v>75.62</v>
+        <v>75.5</v>
       </c>
       <c r="M42" s="8">
-        <v>1894321.71</v>
+        <v>1903366.71</v>
       </c>
       <c r="N42" s="9">
-        <v>24.38</v>
+        <v>24.5</v>
       </c>
       <c r="O42" s="8">
         <v>613445</v>
@@ -21102,13 +21107,13 @@
         <v>7.9</v>
       </c>
       <c r="Q42" s="8">
-        <v>1280876.71</v>
+        <v>1289921.71</v>
       </c>
       <c r="R42" s="9">
-        <v>16.489999999999998</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" ht="66" x14ac:dyDescent="0.25">
+        <v>16.600000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
         <v>500</v>
       </c>
@@ -21128,16 +21133,16 @@
         <v>12554100</v>
       </c>
       <c r="G43" s="8">
-        <v>2756335.44</v>
+        <v>2866335.44</v>
       </c>
       <c r="H43" s="9">
-        <v>21.96</v>
+        <v>22.83</v>
       </c>
       <c r="I43" s="8">
-        <v>1302358.56</v>
+        <v>1192358.56</v>
       </c>
       <c r="J43" s="9">
-        <v>10.37</v>
+        <v>9.5</v>
       </c>
       <c r="K43" s="8">
         <v>4058694</v>
@@ -21164,7 +21169,7 @@
         <v>60.79</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>541</v>
       </c>
@@ -21190,34 +21195,34 @@
         <v>0</v>
       </c>
       <c r="I44" s="8">
-        <v>0</v>
+        <v>155250</v>
       </c>
       <c r="J44" s="9">
-        <v>0</v>
+        <v>7.04</v>
       </c>
       <c r="K44" s="8">
-        <v>0</v>
+        <v>155250</v>
       </c>
       <c r="L44" s="9">
-        <v>0</v>
+        <v>7.04</v>
       </c>
       <c r="M44" s="8">
-        <v>2205500</v>
+        <v>2050250</v>
       </c>
       <c r="N44" s="9">
-        <v>100</v>
+        <v>92.96</v>
       </c>
       <c r="O44" s="8">
-        <v>0</v>
+        <v>720000</v>
       </c>
       <c r="P44" s="9">
-        <v>0</v>
+        <v>32.65</v>
       </c>
       <c r="Q44" s="8">
-        <v>2205500</v>
+        <v>1330250</v>
       </c>
       <c r="R44" s="9">
-        <v>100</v>
+        <v>60.32</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
@@ -21274,7 +21279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>488</v>
       </c>
@@ -21348,43 +21353,43 @@
         <v>72788490.920000002</v>
       </c>
       <c r="G47" s="4">
-        <v>12957730.859999999</v>
+        <v>13108669.16</v>
       </c>
       <c r="H47" s="5">
-        <v>17.8</v>
+        <v>18.010000000000002</v>
       </c>
       <c r="I47" s="4">
-        <v>8303670.9299999997</v>
+        <v>17460532.23</v>
       </c>
       <c r="J47" s="5">
-        <v>11.41</v>
+        <v>23.99</v>
       </c>
       <c r="K47" s="4">
-        <v>21261401.789999999</v>
+        <v>30569201.390000001</v>
       </c>
       <c r="L47" s="5">
-        <v>29.21</v>
+        <v>42</v>
       </c>
       <c r="M47" s="4">
-        <v>51527089.130000003</v>
+        <v>42219289.530000001</v>
       </c>
       <c r="N47" s="5">
-        <v>70.790000000000006</v>
+        <v>58</v>
       </c>
       <c r="O47" s="4">
-        <v>10473500</v>
+        <v>4473750</v>
       </c>
       <c r="P47" s="5">
-        <v>14.39</v>
+        <v>6.15</v>
       </c>
       <c r="Q47" s="4">
-        <v>41053589.130000003</v>
+        <v>37745539.530000001</v>
       </c>
       <c r="R47" s="5">
-        <v>56.4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
+        <v>51.86</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="118.8" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>248</v>
       </c>
@@ -21440,7 +21445,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>260</v>
       </c>
@@ -21496,7 +21501,7 @@
         <v>99.98</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>299</v>
       </c>
@@ -21552,7 +21557,7 @@
         <v>90.15</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="66" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
         <v>317</v>
       </c>
@@ -21608,7 +21613,7 @@
         <v>22.96</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" ht="132" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>333</v>
       </c>
@@ -21628,28 +21633,28 @@
         <v>8926239.0199999996</v>
       </c>
       <c r="G52" s="8">
-        <v>1038332.08</v>
+        <v>1080387.78</v>
       </c>
       <c r="H52" s="9">
-        <v>11.63</v>
+        <v>12.1</v>
       </c>
       <c r="I52" s="8">
-        <v>3380146.7</v>
+        <v>5243008</v>
       </c>
       <c r="J52" s="9">
-        <v>37.869999999999997</v>
+        <v>58.74</v>
       </c>
       <c r="K52" s="8">
-        <v>4418478.78</v>
+        <v>6323395.7800000003</v>
       </c>
       <c r="L52" s="9">
-        <v>49.5</v>
+        <v>70.84</v>
       </c>
       <c r="M52" s="8">
-        <v>4507760.24</v>
+        <v>2602843.2400000002</v>
       </c>
       <c r="N52" s="9">
-        <v>50.5</v>
+        <v>29.16</v>
       </c>
       <c r="O52" s="8">
         <v>500000</v>
@@ -21658,13 +21663,13 @@
         <v>5.6</v>
       </c>
       <c r="Q52" s="8">
-        <v>4007760.24</v>
+        <v>2102843.2400000002</v>
       </c>
       <c r="R52" s="9">
-        <v>44.9</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+        <v>23.56</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
         <v>362</v>
       </c>
@@ -21720,7 +21725,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
         <v>390</v>
       </c>
@@ -21776,7 +21781,7 @@
         <v>-17.489999999999998</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>398</v>
       </c>
@@ -21832,7 +21837,7 @@
         <v>70.61</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" ht="118.8" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
         <v>422</v>
       </c>
@@ -21876,16 +21881,16 @@
         <v>70.760000000000005</v>
       </c>
       <c r="O56" s="8">
-        <v>3495000</v>
+        <v>3295000</v>
       </c>
       <c r="P56" s="9">
-        <v>18.78</v>
+        <v>17.71</v>
       </c>
       <c r="Q56" s="8">
-        <v>9671419.3900000006</v>
+        <v>9871419.3900000006</v>
       </c>
       <c r="R56" s="9">
-        <v>51.98</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="57" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -21944,7 +21949,7 @@
         <v>30.38</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
         <v>472</v>
       </c>
@@ -22000,7 +22005,7 @@
         <v>-8.08</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
         <v>492</v>
       </c>
@@ -22020,28 +22025,28 @@
         <v>2528000</v>
       </c>
       <c r="G59" s="8">
-        <v>506847.24</v>
+        <v>615729.84</v>
       </c>
       <c r="H59" s="9">
-        <v>20.05</v>
+        <v>24.36</v>
       </c>
       <c r="I59" s="8">
-        <v>711810</v>
+        <v>665560</v>
       </c>
       <c r="J59" s="9">
-        <v>28.16</v>
+        <v>26.33</v>
       </c>
       <c r="K59" s="8">
-        <v>1218657.24</v>
+        <v>1281289.8400000001</v>
       </c>
       <c r="L59" s="9">
-        <v>48.21</v>
+        <v>50.68</v>
       </c>
       <c r="M59" s="8">
-        <v>1309342.76</v>
+        <v>1246710.1599999999</v>
       </c>
       <c r="N59" s="9">
-        <v>51.79</v>
+        <v>49.32</v>
       </c>
       <c r="O59" s="8">
         <v>20000</v>
@@ -22050,13 +22055,13 @@
         <v>0.79</v>
       </c>
       <c r="Q59" s="8">
-        <v>1289342.76</v>
+        <v>1226710.1599999999</v>
       </c>
       <c r="R59" s="9">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="60" spans="1:18" ht="66" x14ac:dyDescent="0.25">
+        <v>48.52</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
         <v>508</v>
       </c>
@@ -22112,7 +22117,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="66" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
         <v>523</v>
       </c>
@@ -22138,34 +22143,34 @@
         <v>0.06</v>
       </c>
       <c r="I61" s="8">
-        <v>8370</v>
+        <v>7348620</v>
       </c>
       <c r="J61" s="9">
-        <v>0.04</v>
+        <v>37.090000000000003</v>
       </c>
       <c r="K61" s="8">
-        <v>20920</v>
+        <v>7361170</v>
       </c>
       <c r="L61" s="9">
-        <v>0.11</v>
+        <v>37.159999999999997</v>
       </c>
       <c r="M61" s="8">
-        <v>19790180</v>
+        <v>12449930</v>
       </c>
       <c r="N61" s="9">
-        <v>99.89</v>
+        <v>62.84</v>
       </c>
       <c r="O61" s="8">
-        <v>6000000</v>
+        <v>200250</v>
       </c>
       <c r="P61" s="9">
-        <v>30.29</v>
+        <v>1.01</v>
       </c>
       <c r="Q61" s="8">
-        <v>13790180</v>
+        <v>12249680</v>
       </c>
       <c r="R61" s="9">
-        <v>69.61</v>
+        <v>61.83</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
@@ -22186,40 +22191,40 @@
         <v>100622228.15000001</v>
       </c>
       <c r="G62" s="14">
-        <v>21751803.469999999</v>
+        <v>22946611.77</v>
       </c>
       <c r="H62" s="15">
-        <v>21.62</v>
+        <v>22.8</v>
       </c>
       <c r="I62" s="14">
-        <v>11592441.65</v>
+        <v>19851637.949999999</v>
       </c>
       <c r="J62" s="15">
-        <v>11.52</v>
+        <v>19.73</v>
       </c>
       <c r="K62" s="14">
-        <v>33344245.120000001</v>
+        <v>42798249.719999999</v>
       </c>
       <c r="L62" s="15">
-        <v>33.14</v>
+        <v>42.53</v>
       </c>
       <c r="M62" s="14">
-        <v>67277983.030000001</v>
+        <v>57823978.43</v>
       </c>
       <c r="N62" s="15">
-        <v>66.86</v>
+        <v>57.47</v>
       </c>
       <c r="O62" s="14">
-        <v>11951093</v>
+        <v>6671343</v>
       </c>
       <c r="P62" s="15">
-        <v>11.88</v>
+        <v>6.63</v>
       </c>
       <c r="Q62" s="14">
-        <v>55326890.030000001</v>
+        <v>51152635.43</v>
       </c>
       <c r="R62" s="15">
-        <v>54.98</v>
+        <v>50.84</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
@@ -22240,40 +22245,40 @@
         <v>331324428.14999998</v>
       </c>
       <c r="G63" s="16">
-        <v>164279028.61000001</v>
+        <v>166231462.38</v>
       </c>
       <c r="H63" s="17">
-        <v>49.58</v>
+        <v>50.17</v>
       </c>
       <c r="I63" s="16">
-        <v>48786830.960000001</v>
+        <v>56901772.189999998</v>
       </c>
       <c r="J63" s="17">
-        <v>14.72</v>
+        <v>17.170000000000002</v>
       </c>
       <c r="K63" s="16">
-        <v>213065859.56999999</v>
+        <v>223133234.56999999</v>
       </c>
       <c r="L63" s="17">
-        <v>64.31</v>
+        <v>67.349999999999994</v>
       </c>
       <c r="M63" s="16">
-        <v>118258568.58</v>
+        <v>108191193.58</v>
       </c>
       <c r="N63" s="17">
-        <v>35.69</v>
+        <v>32.65</v>
       </c>
       <c r="O63" s="16">
-        <v>20070792.41</v>
+        <v>14502593.91</v>
       </c>
       <c r="P63" s="17">
-        <v>6.06</v>
+        <v>4.38</v>
       </c>
       <c r="Q63" s="16">
-        <v>98187776.170000002</v>
+        <v>93688599.670000002</v>
       </c>
       <c r="R63" s="17">
-        <v>29.63</v>
+        <v>28.28</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
@@ -22330,7 +22335,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="65" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
         <v>552</v>
       </c>
@@ -22458,40 +22463,40 @@
         <v>337490008.32999998</v>
       </c>
       <c r="G67" s="16">
-        <v>164279028.61000001</v>
+        <v>166231462.38</v>
       </c>
       <c r="H67" s="17">
-        <v>48.68</v>
+        <v>49.26</v>
       </c>
       <c r="I67" s="16">
-        <v>48786830.960000001</v>
+        <v>56901772.189999998</v>
       </c>
       <c r="J67" s="17">
-        <v>14.46</v>
+        <v>16.86</v>
       </c>
       <c r="K67" s="16">
-        <v>213065859.56999999</v>
+        <v>223133234.56999999</v>
       </c>
       <c r="L67" s="17">
-        <v>63.13</v>
+        <v>66.12</v>
       </c>
       <c r="M67" s="16">
-        <v>124424148.76000001</v>
+        <v>114356773.76000001</v>
       </c>
       <c r="N67" s="17">
-        <v>36.869999999999997</v>
+        <v>33.880000000000003</v>
       </c>
       <c r="O67" s="16">
-        <v>20070792.41</v>
+        <v>14502593.91</v>
       </c>
       <c r="P67" s="17">
-        <v>5.95</v>
+        <v>4.3</v>
       </c>
       <c r="Q67" s="16">
-        <v>104353356.34999999</v>
+        <v>99854179.849999994</v>
       </c>
       <c r="R67" s="17">
-        <v>30.92</v>
+        <v>29.59</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
@@ -22512,28 +22517,28 @@
         <v>4037940.24</v>
       </c>
       <c r="G68" s="4">
-        <v>505725.98</v>
+        <v>555190.98</v>
       </c>
       <c r="H68" s="5">
-        <v>12.52</v>
+        <v>13.75</v>
       </c>
       <c r="I68" s="4">
-        <v>202893.9</v>
+        <v>158448.9</v>
       </c>
       <c r="J68" s="5">
-        <v>5.0199999999999996</v>
+        <v>3.92</v>
       </c>
       <c r="K68" s="4">
-        <v>708619.88</v>
+        <v>713639.88</v>
       </c>
       <c r="L68" s="5">
-        <v>17.55</v>
+        <v>17.670000000000002</v>
       </c>
       <c r="M68" s="4">
-        <v>3329320.36</v>
+        <v>3324300.36</v>
       </c>
       <c r="N68" s="5">
-        <v>82.45</v>
+        <v>82.33</v>
       </c>
       <c r="O68" s="4">
         <v>6129.12</v>
@@ -22542,10 +22547,10 @@
         <v>0.15</v>
       </c>
       <c r="Q68" s="4">
-        <v>3323191.24</v>
+        <v>3318171.24</v>
       </c>
       <c r="R68" s="5">
-        <v>82.3</v>
+        <v>82.17</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
@@ -22568,28 +22573,28 @@
         <v>4037940.24</v>
       </c>
       <c r="G69" s="8">
-        <v>505725.98</v>
+        <v>555190.98</v>
       </c>
       <c r="H69" s="9">
-        <v>12.52</v>
+        <v>13.75</v>
       </c>
       <c r="I69" s="8">
-        <v>202893.9</v>
+        <v>158448.9</v>
       </c>
       <c r="J69" s="9">
-        <v>5.0199999999999996</v>
+        <v>3.92</v>
       </c>
       <c r="K69" s="8">
-        <v>708619.88</v>
+        <v>713639.88</v>
       </c>
       <c r="L69" s="9">
-        <v>17.55</v>
+        <v>17.670000000000002</v>
       </c>
       <c r="M69" s="8">
-        <v>3329320.36</v>
+        <v>3324300.36</v>
       </c>
       <c r="N69" s="9">
-        <v>82.45</v>
+        <v>82.33</v>
       </c>
       <c r="O69" s="8">
         <v>6129.12</v>
@@ -22598,10 +22603,10 @@
         <v>0.15</v>
       </c>
       <c r="Q69" s="8">
-        <v>3323191.24</v>
+        <v>3318171.24</v>
       </c>
       <c r="R69" s="9">
-        <v>82.3</v>
+        <v>82.17</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
@@ -22622,28 +22627,28 @@
         <v>4037940.24</v>
       </c>
       <c r="G70" s="14">
-        <v>505725.98</v>
+        <v>555190.98</v>
       </c>
       <c r="H70" s="15">
-        <v>12.52</v>
+        <v>13.75</v>
       </c>
       <c r="I70" s="14">
-        <v>202893.9</v>
+        <v>158448.9</v>
       </c>
       <c r="J70" s="15">
-        <v>5.0199999999999996</v>
+        <v>3.92</v>
       </c>
       <c r="K70" s="14">
-        <v>708619.88</v>
+        <v>713639.88</v>
       </c>
       <c r="L70" s="15">
-        <v>17.55</v>
+        <v>17.670000000000002</v>
       </c>
       <c r="M70" s="14">
-        <v>3329320.36</v>
+        <v>3324300.36</v>
       </c>
       <c r="N70" s="15">
-        <v>82.45</v>
+        <v>82.33</v>
       </c>
       <c r="O70" s="14">
         <v>6129.12</v>
@@ -22652,10 +22657,10 @@
         <v>0.15</v>
       </c>
       <c r="Q70" s="14">
-        <v>3323191.24</v>
+        <v>3318171.24</v>
       </c>
       <c r="R70" s="15">
-        <v>82.3</v>
+        <v>82.17</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
@@ -22676,40 +22681,40 @@
         <v>341527948.56999999</v>
       </c>
       <c r="G71" s="16">
-        <v>164784754.59</v>
+        <v>166786653.36000001</v>
       </c>
       <c r="H71" s="17">
-        <v>48.25</v>
+        <v>48.84</v>
       </c>
       <c r="I71" s="16">
-        <v>48989724.859999999</v>
+        <v>57060221.090000004</v>
       </c>
       <c r="J71" s="17">
-        <v>14.34</v>
+        <v>16.71</v>
       </c>
       <c r="K71" s="16">
-        <v>213774479.44999999</v>
+        <v>223846874.44999999</v>
       </c>
       <c r="L71" s="17">
-        <v>62.59</v>
+        <v>65.540000000000006</v>
       </c>
       <c r="M71" s="16">
-        <v>127753469.12</v>
+        <v>117681074.12</v>
       </c>
       <c r="N71" s="17">
-        <v>37.409999999999997</v>
+        <v>34.46</v>
       </c>
       <c r="O71" s="16">
-        <v>20076921.530000001</v>
+        <v>14508723.029999999</v>
       </c>
       <c r="P71" s="17">
-        <v>5.88</v>
+        <v>4.25</v>
       </c>
       <c r="Q71" s="16">
-        <v>107676547.59</v>
+        <v>103172351.09</v>
       </c>
       <c r="R71" s="17">
-        <v>31.53</v>
+        <v>30.21</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
@@ -22784,28 +22789,28 @@
         <v>1000000</v>
       </c>
       <c r="G73" s="19">
-        <v>466919</v>
+        <v>498719</v>
       </c>
       <c r="H73" s="20">
-        <v>46.69</v>
+        <v>49.87</v>
       </c>
       <c r="I73" s="19">
-        <v>68570</v>
+        <v>30120</v>
       </c>
       <c r="J73" s="20">
-        <v>6.86</v>
+        <v>3.01</v>
       </c>
       <c r="K73" s="19">
-        <v>535489</v>
+        <v>528839</v>
       </c>
       <c r="L73" s="20">
-        <v>53.55</v>
+        <v>52.88</v>
       </c>
       <c r="M73" s="19">
-        <v>464511</v>
+        <v>471161</v>
       </c>
       <c r="N73" s="20">
-        <v>46.45</v>
+        <v>47.12</v>
       </c>
       <c r="O73" s="19">
         <v>0</v>
@@ -22814,10 +22819,10 @@
         <v>0</v>
       </c>
       <c r="Q73" s="19">
-        <v>464511</v>
+        <v>471161</v>
       </c>
       <c r="R73" s="20">
-        <v>46.45</v>
+        <v>47.12</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
@@ -22838,28 +22843,28 @@
         <v>12535870.93</v>
       </c>
       <c r="G74" s="19">
-        <v>7927301.0499999998</v>
+        <v>7853161.0499999998</v>
       </c>
       <c r="H74" s="20">
-        <v>63.24</v>
+        <v>62.65</v>
       </c>
       <c r="I74" s="19">
-        <v>1610503</v>
+        <v>1458883</v>
       </c>
       <c r="J74" s="20">
-        <v>12.85</v>
+        <v>11.64</v>
       </c>
       <c r="K74" s="19">
-        <v>9537804.0500000007</v>
+        <v>9312044.0500000007</v>
       </c>
       <c r="L74" s="20">
-        <v>76.08</v>
+        <v>74.28</v>
       </c>
       <c r="M74" s="19">
-        <v>2998066.88</v>
+        <v>3223826.88</v>
       </c>
       <c r="N74" s="20">
-        <v>23.92</v>
+        <v>25.72</v>
       </c>
       <c r="O74" s="19">
         <v>600</v>
@@ -22868,10 +22873,10 @@
         <v>0</v>
       </c>
       <c r="Q74" s="19">
-        <v>2997466.88</v>
+        <v>3223226.88</v>
       </c>
       <c r="R74" s="20">
-        <v>23.91</v>
+        <v>25.71</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
@@ -22892,40 +22897,40 @@
         <v>13373180.710000001</v>
       </c>
       <c r="G75" s="19">
-        <v>8134769.4299999997</v>
+        <v>8448378.2899999991</v>
       </c>
       <c r="H75" s="20">
-        <v>60.83</v>
+        <v>63.17</v>
       </c>
       <c r="I75" s="19">
-        <v>1281297</v>
+        <v>1227197</v>
       </c>
       <c r="J75" s="20">
-        <v>9.58</v>
+        <v>9.18</v>
       </c>
       <c r="K75" s="19">
-        <v>9416066.4299999997</v>
+        <v>9675575.2899999991</v>
       </c>
       <c r="L75" s="20">
-        <v>70.41</v>
+        <v>72.349999999999994</v>
       </c>
       <c r="M75" s="19">
-        <v>3957114.28</v>
+        <v>3697605.42</v>
       </c>
       <c r="N75" s="20">
-        <v>29.59</v>
+        <v>27.65</v>
       </c>
       <c r="O75" s="19">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="P75" s="20">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="Q75" s="19">
-        <v>3957114.28</v>
+        <v>3617605.42</v>
       </c>
       <c r="R75" s="20">
-        <v>29.59</v>
+        <v>27.05</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
@@ -22946,40 +22951,40 @@
         <v>14776703.779999999</v>
       </c>
       <c r="G76" s="19">
-        <v>9673960.7200000007</v>
+        <v>10460737.039999999</v>
       </c>
       <c r="H76" s="20">
-        <v>65.47</v>
+        <v>70.790000000000006</v>
       </c>
       <c r="I76" s="19">
-        <v>2201977.67</v>
+        <v>1536732.35</v>
       </c>
       <c r="J76" s="20">
-        <v>14.9</v>
+        <v>10.4</v>
       </c>
       <c r="K76" s="19">
-        <v>11875938.390000001</v>
+        <v>11997469.390000001</v>
       </c>
       <c r="L76" s="20">
-        <v>80.37</v>
+        <v>81.19</v>
       </c>
       <c r="M76" s="19">
-        <v>2900765.39</v>
+        <v>2779234.39</v>
       </c>
       <c r="N76" s="20">
-        <v>19.63</v>
+        <v>18.809999999999999</v>
       </c>
       <c r="O76" s="19">
-        <v>118801.1</v>
+        <v>144801.1</v>
       </c>
       <c r="P76" s="20">
-        <v>0.8</v>
+        <v>0.98</v>
       </c>
       <c r="Q76" s="19">
-        <v>2781964.29</v>
+        <v>2634433.29</v>
       </c>
       <c r="R76" s="20">
-        <v>18.829999999999998</v>
+        <v>17.829999999999998</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
@@ -23000,40 +23005,40 @@
         <v>30348181.809999999</v>
       </c>
       <c r="G77" s="19">
-        <v>12043056.98</v>
+        <v>13127477.98</v>
       </c>
       <c r="H77" s="20">
-        <v>39.68</v>
+        <v>43.26</v>
       </c>
       <c r="I77" s="19">
-        <v>3857885.72</v>
+        <v>2913869.72</v>
       </c>
       <c r="J77" s="20">
-        <v>12.71</v>
+        <v>9.6</v>
       </c>
       <c r="K77" s="19">
-        <v>15900942.699999999</v>
+        <v>16041347.699999999</v>
       </c>
       <c r="L77" s="20">
-        <v>52.4</v>
+        <v>52.86</v>
       </c>
       <c r="M77" s="19">
-        <v>14447239.109999999</v>
+        <v>14306834.109999999</v>
       </c>
       <c r="N77" s="20">
-        <v>47.6</v>
+        <v>47.14</v>
       </c>
       <c r="O77" s="19">
-        <v>1477593</v>
+        <v>2747593</v>
       </c>
       <c r="P77" s="20">
-        <v>4.87</v>
+        <v>9.0500000000000007</v>
       </c>
       <c r="Q77" s="19">
-        <v>12969646.109999999</v>
+        <v>11559241.109999999</v>
       </c>
       <c r="R77" s="20">
-        <v>42.74</v>
+        <v>38.090000000000003</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
@@ -23054,28 +23059,28 @@
         <v>13420000</v>
       </c>
       <c r="G78" s="19">
-        <v>9719269.5700000003</v>
+        <v>9438778.7699999996</v>
       </c>
       <c r="H78" s="20">
-        <v>72.42</v>
+        <v>70.33</v>
       </c>
       <c r="I78" s="19">
-        <v>1232465.5900000001</v>
+        <v>1649419.41</v>
       </c>
       <c r="J78" s="20">
-        <v>9.18</v>
+        <v>12.29</v>
       </c>
       <c r="K78" s="19">
-        <v>10951735.16</v>
+        <v>11088198.18</v>
       </c>
       <c r="L78" s="20">
-        <v>81.61</v>
+        <v>82.62</v>
       </c>
       <c r="M78" s="19">
-        <v>2468264.84</v>
+        <v>2331801.8199999998</v>
       </c>
       <c r="N78" s="20">
-        <v>18.39</v>
+        <v>17.38</v>
       </c>
       <c r="O78" s="19">
         <v>275743</v>
@@ -23084,10 +23089,10 @@
         <v>2.0499999999999998</v>
       </c>
       <c r="Q78" s="19">
-        <v>2192521.84</v>
+        <v>2056058.82</v>
       </c>
       <c r="R78" s="20">
-        <v>16.34</v>
+        <v>15.32</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
@@ -23108,40 +23113,40 @@
         <v>111264940.23999999</v>
       </c>
       <c r="G79" s="19">
-        <v>74389493.040000007</v>
+        <v>74583456.650000006</v>
       </c>
       <c r="H79" s="20">
-        <v>66.86</v>
+        <v>67.03</v>
       </c>
       <c r="I79" s="19">
-        <v>7944709.2300000004</v>
+        <v>7714876.6200000001</v>
       </c>
       <c r="J79" s="20">
-        <v>7.14</v>
+        <v>6.93</v>
       </c>
       <c r="K79" s="19">
-        <v>82334202.269999996</v>
+        <v>82298333.269999996</v>
       </c>
       <c r="L79" s="20">
-        <v>74</v>
+        <v>73.97</v>
       </c>
       <c r="M79" s="19">
-        <v>28930737.969999999</v>
+        <v>28966606.969999999</v>
       </c>
       <c r="N79" s="20">
-        <v>26</v>
+        <v>26.03</v>
       </c>
       <c r="O79" s="19">
-        <v>2636962.4900000002</v>
+        <v>1647004.99</v>
       </c>
       <c r="P79" s="20">
-        <v>2.37</v>
+        <v>1.48</v>
       </c>
       <c r="Q79" s="19">
-        <v>26293775.48</v>
+        <v>27319601.98</v>
       </c>
       <c r="R79" s="20">
-        <v>23.63</v>
+        <v>24.55</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
@@ -23162,34 +23167,34 @@
         <v>4260000</v>
       </c>
       <c r="G80" s="19">
-        <v>1698170.43</v>
+        <v>1700370.43</v>
       </c>
       <c r="H80" s="20">
-        <v>39.86</v>
+        <v>39.909999999999997</v>
       </c>
       <c r="I80" s="19">
-        <v>554621.67000000004</v>
+        <v>580421.67000000004</v>
       </c>
       <c r="J80" s="20">
-        <v>13.02</v>
+        <v>13.62</v>
       </c>
       <c r="K80" s="19">
-        <v>2252792.1</v>
+        <v>2280792.1</v>
       </c>
       <c r="L80" s="20">
-        <v>52.88</v>
+        <v>53.54</v>
       </c>
       <c r="M80" s="19">
-        <v>2007207.9</v>
+        <v>1979207.9</v>
       </c>
       <c r="N80" s="20">
-        <v>47.12</v>
+        <v>46.46</v>
       </c>
       <c r="O80" s="19">
-        <v>282000</v>
+        <v>254000</v>
       </c>
       <c r="P80" s="20">
-        <v>6.62</v>
+        <v>5.96</v>
       </c>
       <c r="Q80" s="19">
         <v>1725207.9</v>
@@ -23216,40 +23221,40 @@
         <v>139549071.09999999</v>
       </c>
       <c r="G81" s="19">
-        <v>40001338.630000003</v>
+        <v>39945098.409999996</v>
       </c>
       <c r="H81" s="20">
-        <v>28.66</v>
+        <v>28.62</v>
       </c>
       <c r="I81" s="19">
-        <v>30043026.98</v>
+        <v>39754033.32</v>
       </c>
       <c r="J81" s="20">
-        <v>21.53</v>
+        <v>28.49</v>
       </c>
       <c r="K81" s="19">
-        <v>70044365.609999999</v>
+        <v>79699131.730000004</v>
       </c>
       <c r="L81" s="20">
-        <v>50.19</v>
+        <v>57.11</v>
       </c>
       <c r="M81" s="19">
-        <v>69504705.489999995</v>
+        <v>59849939.369999997</v>
       </c>
       <c r="N81" s="20">
-        <v>49.81</v>
+        <v>42.89</v>
       </c>
       <c r="O81" s="19">
-        <v>15285221.939999999</v>
+        <v>9358980.9399999995</v>
       </c>
       <c r="P81" s="20">
-        <v>10.95</v>
+        <v>6.71</v>
       </c>
       <c r="Q81" s="19">
-        <v>54219483.549999997</v>
+        <v>50490958.43</v>
       </c>
       <c r="R81" s="20">
-        <v>38.85</v>
+        <v>36.18</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
@@ -23270,40 +23275,40 @@
         <v>341527948.56999999</v>
       </c>
       <c r="G82" s="19">
-        <v>164784754.59</v>
+        <v>166786653.36000001</v>
       </c>
       <c r="H82" s="20">
-        <v>48.25</v>
+        <v>48.84</v>
       </c>
       <c r="I82" s="19">
-        <v>48989724.859999999</v>
+        <v>57060221.090000004</v>
       </c>
       <c r="J82" s="20">
-        <v>14.34</v>
+        <v>16.71</v>
       </c>
       <c r="K82" s="19">
-        <v>213774479.44999999</v>
+        <v>223846874.44999999</v>
       </c>
       <c r="L82" s="20">
-        <v>62.59</v>
+        <v>65.540000000000006</v>
       </c>
       <c r="M82" s="19">
-        <v>127753469.12</v>
+        <v>117681074.12</v>
       </c>
       <c r="N82" s="20">
-        <v>37.409999999999997</v>
+        <v>34.46</v>
       </c>
       <c r="O82" s="19">
-        <v>20076921.530000001</v>
+        <v>14508723.029999999</v>
       </c>
       <c r="P82" s="20">
-        <v>5.88</v>
+        <v>4.25</v>
       </c>
       <c r="Q82" s="19">
-        <v>107676547.59</v>
+        <v>103172351.09</v>
       </c>
       <c r="R82" s="20">
-        <v>31.53</v>
+        <v>30.21</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">

--- a/Budget-Report.xlsx
+++ b/Budget-Report.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orathai\Desktop\Claude Cowork\Budget Report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orathai\Desktop\Claude Cowork\Budget Report\00 BK\25690710\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D945D426-F09B-4CC9-AA46-E23DFA7BAB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F22DA70-C280-4B22-9588-A2BB6546AFD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1730,7 +1730,7 @@
     <t>รวมทั้งสิ้น</t>
   </si>
   <si>
-    <t>( ข้อมูลระบบ ณ วันที่ 3 กรกฎาคม 2569 เวลา 23:35:06 น.)</t>
+    <t>( ข้อมูลระบบ ณ วันที่ 10 กรกฎาคม 2569 เวลา 22:39:31 น.)</t>
   </si>
   <si>
     <t>สำนัก/โครงการ</t>
@@ -1769,7 +1769,7 @@
     <t>สย.</t>
   </si>
   <si>
-    <t>( ข้อมูลระบบ ณ วันที่ 3 กรกฎาคม 2569 เวลา 23:37:40 น.)</t>
+    <t>( ข้อมูลระบบ ณ วันที่ 10 กรกฎาคม 2569 เวลา 22:40:55 น.)</t>
   </si>
 </sst>
 </file>
@@ -2302,7 +2302,7 @@
     <col min="14" max="14" width="7.09765625" style="28" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.796875" style="28" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="6.3984375" style="28" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.8984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.796875" style="28" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="7.09765625" style="28" bestFit="1" customWidth="1"/>
     <col min="19" max="16384" width="8.796875" style="28"/>
   </cols>
@@ -2426,40 +2426,40 @@
         <v>46540814</v>
       </c>
       <c r="G6" s="4">
-        <v>21481675.600000001</v>
+        <v>21925150.120000001</v>
       </c>
       <c r="H6" s="5">
-        <v>46.16</v>
+        <v>47.11</v>
       </c>
       <c r="I6" s="4">
-        <v>16350843.189999999</v>
+        <v>16086468.67</v>
       </c>
       <c r="J6" s="5">
-        <v>35.130000000000003</v>
+        <v>34.56</v>
       </c>
       <c r="K6" s="4">
-        <v>37832518.789999999</v>
+        <v>38011618.789999999</v>
       </c>
       <c r="L6" s="5">
-        <v>81.290000000000006</v>
+        <v>81.67</v>
       </c>
       <c r="M6" s="4">
-        <v>8708295.2100000009</v>
+        <v>8529195.2100000009</v>
       </c>
       <c r="N6" s="5">
-        <v>18.71</v>
+        <v>18.329999999999998</v>
       </c>
       <c r="O6" s="4">
-        <v>1938721.6</v>
+        <v>1493446.6</v>
       </c>
       <c r="P6" s="5">
-        <v>4.17</v>
+        <v>3.21</v>
       </c>
       <c r="Q6" s="4">
-        <v>6769573.6100000003</v>
+        <v>7035748.6100000003</v>
       </c>
       <c r="R6" s="5">
-        <v>14.55</v>
+        <v>15.12</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -2482,40 +2482,40 @@
         <v>37235000</v>
       </c>
       <c r="G7" s="8">
-        <v>16601351.6</v>
+        <v>16966626.120000001</v>
       </c>
       <c r="H7" s="9">
-        <v>44.59</v>
+        <v>45.57</v>
       </c>
       <c r="I7" s="8">
-        <v>14809523.52</v>
+        <v>14425034</v>
       </c>
       <c r="J7" s="9">
-        <v>39.770000000000003</v>
+        <v>38.74</v>
       </c>
       <c r="K7" s="8">
-        <v>31410875.120000001</v>
+        <v>31391660.120000001</v>
       </c>
       <c r="L7" s="9">
-        <v>84.36</v>
+        <v>84.31</v>
       </c>
       <c r="M7" s="8">
-        <v>5824124.8799999999</v>
+        <v>5843339.8799999999</v>
       </c>
       <c r="N7" s="9">
-        <v>15.64</v>
+        <v>15.69</v>
       </c>
       <c r="O7" s="8">
-        <v>1680000</v>
+        <v>1387200</v>
       </c>
       <c r="P7" s="9">
-        <v>4.51</v>
+        <v>3.73</v>
       </c>
       <c r="Q7" s="8">
-        <v>4144124.88</v>
+        <v>4456139.88</v>
       </c>
       <c r="R7" s="9">
-        <v>11.13</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -2600,22 +2600,22 @@
         <v>61.76</v>
       </c>
       <c r="I9" s="12">
-        <v>7900</v>
+        <v>8900</v>
       </c>
       <c r="J9" s="13">
-        <v>1.1299999999999999</v>
+        <v>1.27</v>
       </c>
       <c r="K9" s="12">
-        <v>439571</v>
+        <v>440571</v>
       </c>
       <c r="L9" s="13">
-        <v>62.89</v>
+        <v>63.04</v>
       </c>
       <c r="M9" s="12">
-        <v>259329</v>
+        <v>258329</v>
       </c>
       <c r="N9" s="13">
-        <v>37.11</v>
+        <v>36.96</v>
       </c>
       <c r="O9" s="12">
         <v>0</v>
@@ -2624,10 +2624,10 @@
         <v>0</v>
       </c>
       <c r="Q9" s="12">
-        <v>259329</v>
+        <v>258329</v>
       </c>
       <c r="R9" s="13">
-        <v>37.11</v>
+        <v>36.96</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -2650,40 +2650,40 @@
         <v>700000</v>
       </c>
       <c r="G10" s="12">
-        <v>363976</v>
+        <v>372481</v>
       </c>
       <c r="H10" s="13">
-        <v>52</v>
+        <v>53.21</v>
       </c>
       <c r="I10" s="12">
-        <v>478640</v>
+        <v>567940</v>
       </c>
       <c r="J10" s="13">
-        <v>68.38</v>
+        <v>81.13</v>
       </c>
       <c r="K10" s="12">
-        <v>842616</v>
+        <v>940421</v>
       </c>
       <c r="L10" s="13">
-        <v>120.37</v>
+        <v>134.35</v>
       </c>
       <c r="M10" s="12">
-        <v>-142616</v>
+        <v>-240421</v>
       </c>
       <c r="N10" s="13">
-        <v>-20.37</v>
+        <v>-34.35</v>
       </c>
       <c r="O10" s="12">
-        <v>95000</v>
+        <v>2200</v>
       </c>
       <c r="P10" s="13">
-        <v>13.57</v>
+        <v>0.31</v>
       </c>
       <c r="Q10" s="12">
-        <v>-237616</v>
+        <v>-242621</v>
       </c>
       <c r="R10" s="13">
-        <v>-33.950000000000003</v>
+        <v>-34.659999999999997</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
@@ -2706,28 +2706,28 @@
         <v>3030982</v>
       </c>
       <c r="G11" s="12">
-        <v>877782</v>
+        <v>885582</v>
       </c>
       <c r="H11" s="13">
-        <v>28.96</v>
+        <v>29.22</v>
       </c>
       <c r="I11" s="12">
-        <v>2107550</v>
+        <v>2100050</v>
       </c>
       <c r="J11" s="13">
-        <v>69.53</v>
+        <v>69.290000000000006</v>
       </c>
       <c r="K11" s="12">
-        <v>2985332</v>
+        <v>2985632</v>
       </c>
       <c r="L11" s="13">
-        <v>98.49</v>
+        <v>98.5</v>
       </c>
       <c r="M11" s="12">
-        <v>45650</v>
+        <v>45350</v>
       </c>
       <c r="N11" s="13">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="O11" s="12">
         <v>10000</v>
@@ -2736,10 +2736,10 @@
         <v>0.33</v>
       </c>
       <c r="Q11" s="12">
-        <v>35650</v>
+        <v>35350</v>
       </c>
       <c r="R11" s="13">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -2762,25 +2762,25 @@
         <v>20000000</v>
       </c>
       <c r="G12" s="12">
-        <v>8067286</v>
+        <v>8081805</v>
       </c>
       <c r="H12" s="13">
-        <v>40.340000000000003</v>
+        <v>40.409999999999997</v>
       </c>
       <c r="I12" s="12">
-        <v>9978250</v>
+        <v>9964481</v>
       </c>
       <c r="J12" s="13">
-        <v>49.89</v>
+        <v>49.82</v>
       </c>
       <c r="K12" s="12">
-        <v>18045536</v>
+        <v>18046286</v>
       </c>
       <c r="L12" s="13">
         <v>90.23</v>
       </c>
       <c r="M12" s="12">
-        <v>1954464</v>
+        <v>1953714</v>
       </c>
       <c r="N12" s="13">
         <v>9.77</v>
@@ -2792,7 +2792,7 @@
         <v>5</v>
       </c>
       <c r="Q12" s="12">
-        <v>954464</v>
+        <v>953714</v>
       </c>
       <c r="R12" s="13">
         <v>4.7699999999999996</v>
@@ -2818,28 +2818,28 @@
         <v>800000</v>
       </c>
       <c r="G13" s="12">
-        <v>622419.5</v>
+        <v>624979.5</v>
       </c>
       <c r="H13" s="13">
-        <v>77.8</v>
+        <v>78.12</v>
       </c>
       <c r="I13" s="12">
-        <v>118878</v>
+        <v>119518</v>
       </c>
       <c r="J13" s="13">
-        <v>14.86</v>
+        <v>14.94</v>
       </c>
       <c r="K13" s="12">
-        <v>741297.5</v>
+        <v>744497.5</v>
       </c>
       <c r="L13" s="13">
-        <v>92.66</v>
+        <v>93.06</v>
       </c>
       <c r="M13" s="12">
-        <v>58702.5</v>
+        <v>55502.5</v>
       </c>
       <c r="N13" s="13">
-        <v>7.34</v>
+        <v>6.94</v>
       </c>
       <c r="O13" s="12">
         <v>0</v>
@@ -2848,10 +2848,10 @@
         <v>0</v>
       </c>
       <c r="Q13" s="12">
-        <v>58702.5</v>
+        <v>55502.5</v>
       </c>
       <c r="R13" s="13">
-        <v>7.34</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -2930,28 +2930,28 @@
         <v>2706831.37</v>
       </c>
       <c r="G15" s="12">
-        <v>1563736.04</v>
+        <v>1889126.56</v>
       </c>
       <c r="H15" s="13">
-        <v>57.77</v>
+        <v>69.790000000000006</v>
       </c>
       <c r="I15" s="12">
-        <v>566560.52</v>
+        <v>238800</v>
       </c>
       <c r="J15" s="13">
-        <v>20.93</v>
+        <v>8.82</v>
       </c>
       <c r="K15" s="12">
-        <v>2130296.56</v>
+        <v>2127926.56</v>
       </c>
       <c r="L15" s="13">
-        <v>78.7</v>
+        <v>78.61</v>
       </c>
       <c r="M15" s="12">
-        <v>576534.81000000006</v>
+        <v>578904.81000000006</v>
       </c>
       <c r="N15" s="13">
-        <v>21.3</v>
+        <v>21.39</v>
       </c>
       <c r="O15" s="12">
         <v>5000</v>
@@ -2960,10 +2960,10 @@
         <v>0.18</v>
       </c>
       <c r="Q15" s="12">
-        <v>571534.81000000006</v>
+        <v>573904.81000000006</v>
       </c>
       <c r="R15" s="13">
-        <v>21.11</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -2992,22 +2992,22 @@
         <v>8.5500000000000007</v>
       </c>
       <c r="I16" s="12">
-        <v>352000</v>
+        <v>0</v>
       </c>
       <c r="J16" s="13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K16" s="12">
-        <v>382100</v>
+        <v>30100</v>
       </c>
       <c r="L16" s="13">
-        <v>108.55</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="M16" s="12">
-        <v>-30100</v>
+        <v>321900</v>
       </c>
       <c r="N16" s="13">
-        <v>-8.5500000000000007</v>
+        <v>91.45</v>
       </c>
       <c r="O16" s="12">
         <v>0</v>
@@ -3016,10 +3016,10 @@
         <v>0</v>
       </c>
       <c r="Q16" s="12">
-        <v>-30100</v>
+        <v>321900</v>
       </c>
       <c r="R16" s="13">
-        <v>-8.5500000000000007</v>
+        <v>91.45</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -3104,22 +3104,22 @@
         <v>20.65</v>
       </c>
       <c r="I18" s="12">
-        <v>32640</v>
+        <v>63740</v>
       </c>
       <c r="J18" s="13">
-        <v>2.84</v>
+        <v>5.55</v>
       </c>
       <c r="K18" s="12">
-        <v>269781</v>
+        <v>300881</v>
       </c>
       <c r="L18" s="13">
-        <v>23.49</v>
+        <v>26.2</v>
       </c>
       <c r="M18" s="12">
-        <v>878794.97</v>
+        <v>847694.97</v>
       </c>
       <c r="N18" s="13">
-        <v>76.510000000000005</v>
+        <v>73.8</v>
       </c>
       <c r="O18" s="12">
         <v>0</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="Q18" s="12">
-        <v>878794.97</v>
+        <v>847694.97</v>
       </c>
       <c r="R18" s="13">
-        <v>76.510000000000005</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
@@ -3546,40 +3546,40 @@
         <v>330000</v>
       </c>
       <c r="G26" s="12">
-        <v>235135.39</v>
+        <v>241635.39</v>
       </c>
       <c r="H26" s="13">
-        <v>71.25</v>
+        <v>73.22</v>
       </c>
       <c r="I26" s="12">
-        <v>6350</v>
+        <v>200850</v>
       </c>
       <c r="J26" s="13">
-        <v>1.92</v>
+        <v>60.86</v>
       </c>
       <c r="K26" s="12">
-        <v>241485.39</v>
+        <v>442485.39</v>
       </c>
       <c r="L26" s="13">
-        <v>73.180000000000007</v>
+        <v>134.09</v>
       </c>
       <c r="M26" s="12">
-        <v>88514.61</v>
+        <v>-112485.39</v>
       </c>
       <c r="N26" s="13">
-        <v>26.82</v>
+        <v>-34.090000000000003</v>
       </c>
       <c r="O26" s="12">
-        <v>210000</v>
+        <v>10000</v>
       </c>
       <c r="P26" s="13">
-        <v>63.64</v>
+        <v>3.03</v>
       </c>
       <c r="Q26" s="12">
-        <v>-121485.39</v>
+        <v>-122485.39</v>
       </c>
       <c r="R26" s="13">
-        <v>-36.81</v>
+        <v>-37.119999999999997</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -3664,28 +3664,28 @@
         <v>39.909999999999997</v>
       </c>
       <c r="I28" s="8">
-        <v>580421.67000000004</v>
+        <v>732896.67</v>
       </c>
       <c r="J28" s="9">
-        <v>13.62</v>
+        <v>17.2</v>
       </c>
       <c r="K28" s="8">
-        <v>2280792.1</v>
+        <v>2433267.1</v>
       </c>
       <c r="L28" s="9">
-        <v>53.54</v>
+        <v>57.12</v>
       </c>
       <c r="M28" s="8">
-        <v>1979207.9</v>
+        <v>1826732.9</v>
       </c>
       <c r="N28" s="9">
-        <v>46.46</v>
+        <v>42.88</v>
       </c>
       <c r="O28" s="8">
-        <v>254000</v>
+        <v>101525</v>
       </c>
       <c r="P28" s="9">
-        <v>5.96</v>
+        <v>2.38</v>
       </c>
       <c r="Q28" s="8">
         <v>1725207.9</v>
@@ -3720,28 +3720,28 @@
         <v>40.5</v>
       </c>
       <c r="I29" s="12">
-        <v>92655</v>
+        <v>245130</v>
       </c>
       <c r="J29" s="13">
-        <v>5.09</v>
+        <v>13.47</v>
       </c>
       <c r="K29" s="12">
-        <v>829744.87</v>
+        <v>982219.87</v>
       </c>
       <c r="L29" s="13">
-        <v>45.59</v>
+        <v>53.97</v>
       </c>
       <c r="M29" s="12">
-        <v>990255.13</v>
+        <v>837780.13</v>
       </c>
       <c r="N29" s="13">
-        <v>54.41</v>
+        <v>46.03</v>
       </c>
       <c r="O29" s="12">
-        <v>250000</v>
+        <v>97525</v>
       </c>
       <c r="P29" s="13">
-        <v>13.74</v>
+        <v>5.36</v>
       </c>
       <c r="Q29" s="12">
         <v>740255.13</v>
@@ -4000,22 +4000,22 @@
         <v>81.48</v>
       </c>
       <c r="I34" s="8">
-        <v>150000</v>
+        <v>151840</v>
       </c>
       <c r="J34" s="9">
-        <v>19.920000000000002</v>
+        <v>20.170000000000002</v>
       </c>
       <c r="K34" s="8">
-        <v>763450</v>
+        <v>765290</v>
       </c>
       <c r="L34" s="9">
-        <v>101.4</v>
+        <v>101.65</v>
       </c>
       <c r="M34" s="8">
-        <v>-10550</v>
+        <v>-12390</v>
       </c>
       <c r="N34" s="9">
-        <v>-1.4</v>
+        <v>-1.65</v>
       </c>
       <c r="O34" s="8">
         <v>0</v>
@@ -4024,10 +4024,10 @@
         <v>0</v>
       </c>
       <c r="Q34" s="8">
-        <v>-10550</v>
+        <v>-12390</v>
       </c>
       <c r="R34" s="9">
-        <v>-1.4</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -4056,22 +4056,22 @@
         <v>81.48</v>
       </c>
       <c r="I35" s="12">
-        <v>150000</v>
+        <v>151840</v>
       </c>
       <c r="J35" s="13">
-        <v>19.920000000000002</v>
+        <v>20.170000000000002</v>
       </c>
       <c r="K35" s="12">
-        <v>763450</v>
+        <v>765290</v>
       </c>
       <c r="L35" s="13">
-        <v>101.4</v>
+        <v>101.65</v>
       </c>
       <c r="M35" s="12">
-        <v>-10550</v>
+        <v>-12390</v>
       </c>
       <c r="N35" s="13">
-        <v>-1.4</v>
+        <v>-1.65</v>
       </c>
       <c r="O35" s="12">
         <v>0</v>
@@ -4080,10 +4080,10 @@
         <v>0</v>
       </c>
       <c r="Q35" s="12">
-        <v>-10550</v>
+        <v>-12390</v>
       </c>
       <c r="R35" s="13">
-        <v>-1.4</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="36" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -4106,16 +4106,16 @@
         <v>500000</v>
       </c>
       <c r="G36" s="8">
-        <v>357667.9</v>
+        <v>435867.9</v>
       </c>
       <c r="H36" s="9">
-        <v>71.53</v>
+        <v>87.17</v>
       </c>
       <c r="I36" s="8">
-        <v>118800</v>
+        <v>40600</v>
       </c>
       <c r="J36" s="9">
-        <v>23.76</v>
+        <v>8.1199999999999992</v>
       </c>
       <c r="K36" s="8">
         <v>476467.9</v>
@@ -4162,16 +4162,16 @@
         <v>400000</v>
       </c>
       <c r="G37" s="12">
-        <v>295879.90000000002</v>
+        <v>374079.9</v>
       </c>
       <c r="H37" s="13">
-        <v>73.97</v>
+        <v>93.52</v>
       </c>
       <c r="I37" s="12">
-        <v>80800</v>
+        <v>2600</v>
       </c>
       <c r="J37" s="13">
-        <v>20.2</v>
+        <v>0.65</v>
       </c>
       <c r="K37" s="12">
         <v>376679.9</v>
@@ -4448,22 +4448,22 @@
         <v>60.1</v>
       </c>
       <c r="I42" s="8">
-        <v>415098</v>
+        <v>459098</v>
       </c>
       <c r="J42" s="9">
-        <v>15.89</v>
+        <v>17.57</v>
       </c>
       <c r="K42" s="8">
-        <v>1985584.67</v>
+        <v>2029584.67</v>
       </c>
       <c r="L42" s="9">
-        <v>75.989999999999995</v>
+        <v>77.680000000000007</v>
       </c>
       <c r="M42" s="8">
-        <v>627329.32999999996</v>
+        <v>583329.32999999996</v>
       </c>
       <c r="N42" s="9">
-        <v>24.01</v>
+        <v>22.32</v>
       </c>
       <c r="O42" s="8">
         <v>0</v>
@@ -4472,10 +4472,10 @@
         <v>0</v>
       </c>
       <c r="Q42" s="8">
-        <v>627329.32999999996</v>
+        <v>583329.32999999996</v>
       </c>
       <c r="R42" s="9">
-        <v>24.01</v>
+        <v>22.32</v>
       </c>
     </row>
     <row r="43" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -4672,22 +4672,22 @@
         <v>57.33</v>
       </c>
       <c r="I46" s="12">
-        <v>4440</v>
+        <v>48440</v>
       </c>
       <c r="J46" s="13">
-        <v>2.13</v>
+        <v>23.24</v>
       </c>
       <c r="K46" s="12">
-        <v>123910</v>
+        <v>167910</v>
       </c>
       <c r="L46" s="13">
-        <v>59.46</v>
+        <v>80.569999999999993</v>
       </c>
       <c r="M46" s="12">
-        <v>84490</v>
+        <v>40490</v>
       </c>
       <c r="N46" s="13">
-        <v>40.54</v>
+        <v>19.43</v>
       </c>
       <c r="O46" s="12">
         <v>0</v>
@@ -4696,10 +4696,10 @@
         <v>0</v>
       </c>
       <c r="Q46" s="12">
-        <v>84490</v>
+        <v>40490</v>
       </c>
       <c r="R46" s="13">
-        <v>40.54</v>
+        <v>19.43</v>
       </c>
     </row>
     <row r="47" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -4722,40 +4722,40 @@
         <v>54940200</v>
       </c>
       <c r="G47" s="4">
-        <v>38494573.619999997</v>
+        <v>39760418.880000003</v>
       </c>
       <c r="H47" s="5">
-        <v>70.069999999999993</v>
+        <v>72.37</v>
       </c>
       <c r="I47" s="4">
-        <v>5999195.7599999998</v>
+        <v>6458190.6699999999</v>
       </c>
       <c r="J47" s="5">
-        <v>10.92</v>
+        <v>11.75</v>
       </c>
       <c r="K47" s="4">
-        <v>44493769.380000003</v>
+        <v>46218609.549999997</v>
       </c>
       <c r="L47" s="5">
-        <v>80.989999999999995</v>
+        <v>84.13</v>
       </c>
       <c r="M47" s="4">
-        <v>10446430.619999999</v>
+        <v>8721590.4499999993</v>
       </c>
       <c r="N47" s="5">
-        <v>19.010000000000002</v>
+        <v>15.87</v>
       </c>
       <c r="O47" s="4">
-        <v>1046422.5</v>
+        <v>1019422.5</v>
       </c>
       <c r="P47" s="5">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="Q47" s="4">
-        <v>9400008.1199999992</v>
+        <v>7702167.9500000002</v>
       </c>
       <c r="R47" s="5">
-        <v>17.11</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -4778,28 +4778,28 @@
         <v>11340200</v>
       </c>
       <c r="G48" s="8">
-        <v>8405804.9600000009</v>
+        <v>8562529.9600000009</v>
       </c>
       <c r="H48" s="9">
-        <v>74.12</v>
+        <v>75.510000000000005</v>
       </c>
       <c r="I48" s="8">
-        <v>1337047.3500000001</v>
+        <v>1573722.67</v>
       </c>
       <c r="J48" s="9">
-        <v>11.79</v>
+        <v>13.88</v>
       </c>
       <c r="K48" s="8">
-        <v>9742852.3100000005</v>
+        <v>10136252.630000001</v>
       </c>
       <c r="L48" s="9">
-        <v>85.91</v>
+        <v>89.38</v>
       </c>
       <c r="M48" s="8">
-        <v>1597347.69</v>
+        <v>1203947.3700000001</v>
       </c>
       <c r="N48" s="9">
-        <v>14.09</v>
+        <v>10.62</v>
       </c>
       <c r="O48" s="8">
         <v>140079.5</v>
@@ -4808,10 +4808,10 @@
         <v>1.24</v>
       </c>
       <c r="Q48" s="8">
-        <v>1457268.19</v>
+        <v>1063867.8700000001</v>
       </c>
       <c r="R48" s="9">
-        <v>12.85</v>
+        <v>9.3800000000000008</v>
       </c>
     </row>
     <row r="49" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -4834,28 +4834,28 @@
         <v>1300000</v>
       </c>
       <c r="G49" s="12">
-        <v>848130.5</v>
+        <v>916630.5</v>
       </c>
       <c r="H49" s="13">
-        <v>65.239999999999995</v>
+        <v>70.510000000000005</v>
       </c>
       <c r="I49" s="12">
-        <v>127000</v>
+        <v>418740</v>
       </c>
       <c r="J49" s="13">
-        <v>9.77</v>
+        <v>32.21</v>
       </c>
       <c r="K49" s="12">
-        <v>975130.5</v>
+        <v>1335370.5</v>
       </c>
       <c r="L49" s="13">
-        <v>75.010000000000005</v>
+        <v>102.72</v>
       </c>
       <c r="M49" s="12">
-        <v>324869.5</v>
+        <v>-35370.5</v>
       </c>
       <c r="N49" s="13">
-        <v>24.99</v>
+        <v>-2.72</v>
       </c>
       <c r="O49" s="12">
         <v>90000</v>
@@ -4864,10 +4864,10 @@
         <v>6.92</v>
       </c>
       <c r="Q49" s="12">
-        <v>234869.5</v>
+        <v>-125370.5</v>
       </c>
       <c r="R49" s="13">
-        <v>18.07</v>
+        <v>-9.64</v>
       </c>
     </row>
     <row r="50" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -4946,28 +4946,28 @@
         <v>4320000</v>
       </c>
       <c r="G51" s="12">
-        <v>2602484.7000000002</v>
+        <v>2682709.7000000002</v>
       </c>
       <c r="H51" s="13">
-        <v>60.24</v>
+        <v>62.1</v>
       </c>
       <c r="I51" s="12">
-        <v>703267.35</v>
+        <v>654202.67000000004</v>
       </c>
       <c r="J51" s="13">
-        <v>16.28</v>
+        <v>15.14</v>
       </c>
       <c r="K51" s="12">
-        <v>3305752.05</v>
+        <v>3336912.37</v>
       </c>
       <c r="L51" s="13">
-        <v>76.52</v>
+        <v>77.239999999999995</v>
       </c>
       <c r="M51" s="12">
-        <v>1014247.95</v>
+        <v>983087.63</v>
       </c>
       <c r="N51" s="13">
-        <v>23.48</v>
+        <v>22.76</v>
       </c>
       <c r="O51" s="12">
         <v>0</v>
@@ -4976,10 +4976,10 @@
         <v>0</v>
       </c>
       <c r="Q51" s="12">
-        <v>1014247.95</v>
+        <v>983087.63</v>
       </c>
       <c r="R51" s="13">
-        <v>23.48</v>
+        <v>22.76</v>
       </c>
     </row>
     <row r="52" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -5002,28 +5002,28 @@
         <v>2020200</v>
       </c>
       <c r="G52" s="12">
-        <v>1729956</v>
+        <v>1737956</v>
       </c>
       <c r="H52" s="13">
-        <v>85.63</v>
+        <v>86.03</v>
       </c>
       <c r="I52" s="12">
-        <v>189980</v>
+        <v>183980</v>
       </c>
       <c r="J52" s="13">
-        <v>9.4</v>
+        <v>9.11</v>
       </c>
       <c r="K52" s="12">
-        <v>1919936</v>
+        <v>1921936</v>
       </c>
       <c r="L52" s="13">
-        <v>95.04</v>
+        <v>95.14</v>
       </c>
       <c r="M52" s="12">
-        <v>100264</v>
+        <v>98264</v>
       </c>
       <c r="N52" s="13">
-        <v>4.96</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="O52" s="12">
         <v>20079.5</v>
@@ -5032,10 +5032,10 @@
         <v>0.99</v>
       </c>
       <c r="Q52" s="12">
-        <v>80184.5</v>
+        <v>78184.5</v>
       </c>
       <c r="R52" s="13">
-        <v>3.97</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="53" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -5114,40 +5114,40 @@
         <v>13420000</v>
       </c>
       <c r="G54" s="8">
-        <v>9438778.7699999996</v>
+        <v>10131340.029999999</v>
       </c>
       <c r="H54" s="9">
-        <v>70.33</v>
+        <v>75.489999999999995</v>
       </c>
       <c r="I54" s="8">
-        <v>1649419.41</v>
+        <v>1802304</v>
       </c>
       <c r="J54" s="9">
-        <v>12.29</v>
+        <v>13.43</v>
       </c>
       <c r="K54" s="8">
-        <v>11088198.18</v>
+        <v>11933644.029999999</v>
       </c>
       <c r="L54" s="9">
-        <v>82.62</v>
+        <v>88.92</v>
       </c>
       <c r="M54" s="8">
-        <v>2331801.8199999998</v>
+        <v>1486355.97</v>
       </c>
       <c r="N54" s="9">
-        <v>17.38</v>
+        <v>11.08</v>
       </c>
       <c r="O54" s="8">
-        <v>275743</v>
+        <v>248743</v>
       </c>
       <c r="P54" s="9">
-        <v>2.0499999999999998</v>
+        <v>1.85</v>
       </c>
       <c r="Q54" s="8">
-        <v>2056058.82</v>
+        <v>1237612.97</v>
       </c>
       <c r="R54" s="9">
-        <v>15.32</v>
+        <v>9.2200000000000006</v>
       </c>
     </row>
     <row r="55" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -5226,40 +5226,40 @@
         <v>2700000</v>
       </c>
       <c r="G56" s="12">
-        <v>1717164.55</v>
+        <v>1902110.35</v>
       </c>
       <c r="H56" s="13">
-        <v>63.6</v>
+        <v>70.45</v>
       </c>
       <c r="I56" s="12">
-        <v>419454</v>
+        <v>241954</v>
       </c>
       <c r="J56" s="13">
-        <v>15.54</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="K56" s="12">
-        <v>2136618.5499999998</v>
+        <v>2144064.35</v>
       </c>
       <c r="L56" s="13">
-        <v>79.13</v>
+        <v>79.41</v>
       </c>
       <c r="M56" s="12">
-        <v>563381.44999999995</v>
+        <v>555935.65</v>
       </c>
       <c r="N56" s="13">
-        <v>20.87</v>
+        <v>20.59</v>
       </c>
       <c r="O56" s="12">
-        <v>160000</v>
+        <v>133000</v>
       </c>
       <c r="P56" s="13">
-        <v>5.93</v>
+        <v>4.93</v>
       </c>
       <c r="Q56" s="12">
-        <v>403381.45</v>
+        <v>422935.65</v>
       </c>
       <c r="R56" s="13">
-        <v>14.94</v>
+        <v>15.66</v>
       </c>
     </row>
     <row r="57" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -5282,28 +5282,28 @@
         <v>3400000</v>
       </c>
       <c r="G57" s="12">
-        <v>2440838.36</v>
+        <v>2496168.41</v>
       </c>
       <c r="H57" s="13">
-        <v>71.790000000000006</v>
+        <v>73.42</v>
       </c>
       <c r="I57" s="12">
-        <v>373400</v>
+        <v>375650</v>
       </c>
       <c r="J57" s="13">
-        <v>10.98</v>
+        <v>11.05</v>
       </c>
       <c r="K57" s="12">
-        <v>2814238.36</v>
+        <v>2871818.41</v>
       </c>
       <c r="L57" s="13">
-        <v>82.77</v>
+        <v>84.47</v>
       </c>
       <c r="M57" s="12">
-        <v>585761.64</v>
+        <v>528181.59</v>
       </c>
       <c r="N57" s="13">
-        <v>17.23</v>
+        <v>15.53</v>
       </c>
       <c r="O57" s="12">
         <v>0</v>
@@ -5312,10 +5312,10 @@
         <v>0</v>
       </c>
       <c r="Q57" s="12">
-        <v>585761.64</v>
+        <v>528181.59</v>
       </c>
       <c r="R57" s="13">
-        <v>17.23</v>
+        <v>15.53</v>
       </c>
     </row>
     <row r="58" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -5400,22 +5400,22 @@
         <v>77.17</v>
       </c>
       <c r="I59" s="12">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="J59" s="13">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K59" s="12">
-        <v>154338</v>
+        <v>254338</v>
       </c>
       <c r="L59" s="13">
-        <v>77.17</v>
+        <v>127.17</v>
       </c>
       <c r="M59" s="12">
-        <v>45662</v>
+        <v>-54338</v>
       </c>
       <c r="N59" s="13">
-        <v>22.83</v>
+        <v>-27.17</v>
       </c>
       <c r="O59" s="12">
         <v>0</v>
@@ -5424,10 +5424,10 @@
         <v>0</v>
       </c>
       <c r="Q59" s="12">
-        <v>45662</v>
+        <v>-54338</v>
       </c>
       <c r="R59" s="13">
-        <v>22.83</v>
+        <v>-27.17</v>
       </c>
     </row>
     <row r="60" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -5506,28 +5506,28 @@
         <v>2600000</v>
       </c>
       <c r="G61" s="12">
-        <v>1188948.81</v>
+        <v>1641234.22</v>
       </c>
       <c r="H61" s="13">
-        <v>45.73</v>
+        <v>63.12</v>
       </c>
       <c r="I61" s="12">
-        <v>456565.41</v>
+        <v>684700</v>
       </c>
       <c r="J61" s="13">
-        <v>17.559999999999999</v>
+        <v>26.33</v>
       </c>
       <c r="K61" s="12">
-        <v>1645514.22</v>
+        <v>2325934.2200000002</v>
       </c>
       <c r="L61" s="13">
-        <v>63.29</v>
+        <v>89.46</v>
       </c>
       <c r="M61" s="12">
-        <v>954485.78</v>
+        <v>274065.78000000003</v>
       </c>
       <c r="N61" s="13">
-        <v>36.71</v>
+        <v>10.54</v>
       </c>
       <c r="O61" s="12">
         <v>115743</v>
@@ -5536,10 +5536,10 @@
         <v>4.45</v>
       </c>
       <c r="Q61" s="12">
-        <v>838742.78</v>
+        <v>158322.78</v>
       </c>
       <c r="R61" s="13">
-        <v>32.26</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="62" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -5730,28 +5730,28 @@
         <v>11720000</v>
       </c>
       <c r="G65" s="8">
-        <v>7481436</v>
+        <v>7582346</v>
       </c>
       <c r="H65" s="9">
-        <v>63.83</v>
+        <v>64.7</v>
       </c>
       <c r="I65" s="8">
-        <v>1458873</v>
+        <v>1490828</v>
       </c>
       <c r="J65" s="9">
-        <v>12.45</v>
+        <v>12.72</v>
       </c>
       <c r="K65" s="8">
-        <v>8940309</v>
+        <v>9073174</v>
       </c>
       <c r="L65" s="9">
-        <v>76.28</v>
+        <v>77.42</v>
       </c>
       <c r="M65" s="8">
-        <v>2779691</v>
+        <v>2646826</v>
       </c>
       <c r="N65" s="9">
-        <v>23.72</v>
+        <v>22.58</v>
       </c>
       <c r="O65" s="8">
         <v>600</v>
@@ -5760,10 +5760,10 @@
         <v>0.01</v>
       </c>
       <c r="Q65" s="8">
-        <v>2779091</v>
+        <v>2646226</v>
       </c>
       <c r="R65" s="9">
-        <v>23.71</v>
+        <v>22.58</v>
       </c>
     </row>
     <row r="66" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -5842,28 +5842,28 @@
         <v>1775000</v>
       </c>
       <c r="G67" s="12">
-        <v>533437</v>
+        <v>608047</v>
       </c>
       <c r="H67" s="13">
-        <v>30.05</v>
+        <v>34.26</v>
       </c>
       <c r="I67" s="12">
-        <v>139200</v>
+        <v>40705</v>
       </c>
       <c r="J67" s="13">
-        <v>7.84</v>
+        <v>2.29</v>
       </c>
       <c r="K67" s="12">
-        <v>672637</v>
+        <v>648752</v>
       </c>
       <c r="L67" s="13">
-        <v>37.9</v>
+        <v>36.549999999999997</v>
       </c>
       <c r="M67" s="12">
-        <v>1102363</v>
+        <v>1126248</v>
       </c>
       <c r="N67" s="13">
-        <v>62.1</v>
+        <v>63.45</v>
       </c>
       <c r="O67" s="12">
         <v>0</v>
@@ -5872,10 +5872,10 @@
         <v>0</v>
       </c>
       <c r="Q67" s="12">
-        <v>1102363</v>
+        <v>1126248</v>
       </c>
       <c r="R67" s="13">
-        <v>62.1</v>
+        <v>63.45</v>
       </c>
     </row>
     <row r="68" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -5898,28 +5898,28 @@
         <v>2820000</v>
       </c>
       <c r="G68" s="12">
-        <v>1848299</v>
+        <v>1874599</v>
       </c>
       <c r="H68" s="13">
-        <v>65.540000000000006</v>
+        <v>66.48</v>
       </c>
       <c r="I68" s="12">
-        <v>475144</v>
+        <v>605594</v>
       </c>
       <c r="J68" s="13">
-        <v>16.850000000000001</v>
+        <v>21.47</v>
       </c>
       <c r="K68" s="12">
-        <v>2323443</v>
+        <v>2480193</v>
       </c>
       <c r="L68" s="13">
-        <v>82.39</v>
+        <v>87.95</v>
       </c>
       <c r="M68" s="12">
-        <v>496557</v>
+        <v>339807</v>
       </c>
       <c r="N68" s="13">
-        <v>17.61</v>
+        <v>12.05</v>
       </c>
       <c r="O68" s="12">
         <v>600</v>
@@ -5928,10 +5928,10 @@
         <v>0.02</v>
       </c>
       <c r="Q68" s="12">
-        <v>495957</v>
+        <v>339207</v>
       </c>
       <c r="R68" s="13">
-        <v>17.59</v>
+        <v>12.03</v>
       </c>
     </row>
     <row r="69" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -6066,28 +6066,28 @@
         <v>10640000</v>
       </c>
       <c r="G71" s="8">
-        <v>7810024.29</v>
+        <v>8006844.29</v>
       </c>
       <c r="H71" s="9">
-        <v>73.400000000000006</v>
+        <v>75.25</v>
       </c>
       <c r="I71" s="8">
-        <v>950197</v>
+        <v>1042847</v>
       </c>
       <c r="J71" s="9">
-        <v>8.93</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="K71" s="8">
-        <v>8760221.2899999991</v>
+        <v>9049691.2899999991</v>
       </c>
       <c r="L71" s="9">
-        <v>82.33</v>
+        <v>85.05</v>
       </c>
       <c r="M71" s="8">
-        <v>1879778.71</v>
+        <v>1590308.71</v>
       </c>
       <c r="N71" s="9">
-        <v>17.670000000000002</v>
+        <v>14.95</v>
       </c>
       <c r="O71" s="8">
         <v>80000</v>
@@ -6096,10 +6096,10 @@
         <v>0.75</v>
       </c>
       <c r="Q71" s="8">
-        <v>1799778.71</v>
+        <v>1510308.71</v>
       </c>
       <c r="R71" s="9">
-        <v>16.920000000000002</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="72" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -6122,28 +6122,28 @@
         <v>1140000</v>
       </c>
       <c r="G72" s="12">
-        <v>610854.22</v>
+        <v>757574.22</v>
       </c>
       <c r="H72" s="13">
-        <v>53.58</v>
+        <v>66.45</v>
       </c>
       <c r="I72" s="12">
-        <v>207510</v>
+        <v>45410</v>
       </c>
       <c r="J72" s="13">
-        <v>18.2</v>
+        <v>3.98</v>
       </c>
       <c r="K72" s="12">
-        <v>818364.22</v>
+        <v>802984.22</v>
       </c>
       <c r="L72" s="13">
-        <v>71.790000000000006</v>
+        <v>70.44</v>
       </c>
       <c r="M72" s="12">
-        <v>321635.78000000003</v>
+        <v>337015.78</v>
       </c>
       <c r="N72" s="13">
-        <v>28.21</v>
+        <v>29.56</v>
       </c>
       <c r="O72" s="12">
         <v>0</v>
@@ -6152,10 +6152,10 @@
         <v>0</v>
       </c>
       <c r="Q72" s="12">
-        <v>321635.78000000003</v>
+        <v>337015.78</v>
       </c>
       <c r="R72" s="13">
-        <v>28.21</v>
+        <v>29.56</v>
       </c>
     </row>
     <row r="73" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -6184,22 +6184,22 @@
         <v>89.22</v>
       </c>
       <c r="I73" s="12">
-        <v>2630</v>
+        <v>7630</v>
       </c>
       <c r="J73" s="13">
-        <v>0.12</v>
+        <v>0.35</v>
       </c>
       <c r="K73" s="12">
-        <v>1965439.37</v>
+        <v>1970439.37</v>
       </c>
       <c r="L73" s="13">
-        <v>89.34</v>
+        <v>89.57</v>
       </c>
       <c r="M73" s="12">
-        <v>234560.63</v>
+        <v>229560.63</v>
       </c>
       <c r="N73" s="13">
-        <v>10.66</v>
+        <v>10.43</v>
       </c>
       <c r="O73" s="12">
         <v>0</v>
@@ -6208,10 +6208,10 @@
         <v>0</v>
       </c>
       <c r="Q73" s="12">
-        <v>234560.63</v>
+        <v>229560.63</v>
       </c>
       <c r="R73" s="13">
-        <v>10.66</v>
+        <v>10.43</v>
       </c>
     </row>
     <row r="74" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -6240,22 +6240,22 @@
         <v>62.06</v>
       </c>
       <c r="I74" s="12">
-        <v>0</v>
+        <v>228100</v>
       </c>
       <c r="J74" s="13">
-        <v>0</v>
+        <v>32.590000000000003</v>
       </c>
       <c r="K74" s="12">
-        <v>434411</v>
+        <v>662511</v>
       </c>
       <c r="L74" s="13">
-        <v>62.06</v>
+        <v>94.64</v>
       </c>
       <c r="M74" s="12">
-        <v>265589</v>
+        <v>37489</v>
       </c>
       <c r="N74" s="13">
-        <v>37.94</v>
+        <v>5.36</v>
       </c>
       <c r="O74" s="12">
         <v>30000</v>
@@ -6264,10 +6264,10 @@
         <v>4.29</v>
       </c>
       <c r="Q74" s="12">
-        <v>235589</v>
+        <v>7489</v>
       </c>
       <c r="R74" s="13">
-        <v>33.659999999999997</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="75" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -6458,28 +6458,28 @@
         <v>500000</v>
       </c>
       <c r="G78" s="12">
-        <v>224050</v>
+        <v>274150</v>
       </c>
       <c r="H78" s="13">
-        <v>44.81</v>
+        <v>54.83</v>
       </c>
       <c r="I78" s="12">
-        <v>151250</v>
+        <v>172900</v>
       </c>
       <c r="J78" s="13">
-        <v>30.25</v>
+        <v>34.58</v>
       </c>
       <c r="K78" s="12">
-        <v>375300</v>
+        <v>447050</v>
       </c>
       <c r="L78" s="13">
-        <v>75.06</v>
+        <v>89.41</v>
       </c>
       <c r="M78" s="12">
-        <v>124700</v>
+        <v>52950</v>
       </c>
       <c r="N78" s="13">
-        <v>24.94</v>
+        <v>10.59</v>
       </c>
       <c r="O78" s="12">
         <v>50000</v>
@@ -6488,10 +6488,10 @@
         <v>10</v>
       </c>
       <c r="Q78" s="12">
-        <v>74700</v>
+        <v>2950</v>
       </c>
       <c r="R78" s="13">
-        <v>14.94</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="79" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -6570,28 +6570,28 @@
         <v>7820000</v>
       </c>
       <c r="G80" s="8">
-        <v>5358529.5999999996</v>
+        <v>5477358.5999999996</v>
       </c>
       <c r="H80" s="9">
-        <v>68.52</v>
+        <v>70.040000000000006</v>
       </c>
       <c r="I80" s="8">
-        <v>603659</v>
+        <v>548489</v>
       </c>
       <c r="J80" s="9">
-        <v>7.72</v>
+        <v>7.01</v>
       </c>
       <c r="K80" s="8">
-        <v>5962188.5999999996</v>
+        <v>6025847.5999999996</v>
       </c>
       <c r="L80" s="9">
-        <v>76.239999999999995</v>
+        <v>77.06</v>
       </c>
       <c r="M80" s="8">
-        <v>1857811.4</v>
+        <v>1794152.4</v>
       </c>
       <c r="N80" s="9">
-        <v>23.76</v>
+        <v>22.94</v>
       </c>
       <c r="O80" s="8">
         <v>550000</v>
@@ -6600,10 +6600,10 @@
         <v>7.03</v>
       </c>
       <c r="Q80" s="8">
-        <v>1307811.3999999999</v>
+        <v>1244152.3999999999</v>
       </c>
       <c r="R80" s="9">
-        <v>16.72</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="81" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -6626,28 +6626,28 @@
         <v>1000000</v>
       </c>
       <c r="G81" s="12">
-        <v>333594</v>
+        <v>556263</v>
       </c>
       <c r="H81" s="13">
-        <v>33.36</v>
+        <v>55.63</v>
       </c>
       <c r="I81" s="12">
-        <v>225870</v>
+        <v>0</v>
       </c>
       <c r="J81" s="13">
-        <v>22.59</v>
+        <v>0</v>
       </c>
       <c r="K81" s="12">
-        <v>559464</v>
+        <v>556263</v>
       </c>
       <c r="L81" s="13">
-        <v>55.95</v>
+        <v>55.63</v>
       </c>
       <c r="M81" s="12">
-        <v>440536</v>
+        <v>443737</v>
       </c>
       <c r="N81" s="13">
-        <v>44.05</v>
+        <v>44.37</v>
       </c>
       <c r="O81" s="12">
         <v>0</v>
@@ -6656,10 +6656,10 @@
         <v>0</v>
       </c>
       <c r="Q81" s="12">
-        <v>440536</v>
+        <v>443737</v>
       </c>
       <c r="R81" s="13">
-        <v>44.05</v>
+        <v>44.37</v>
       </c>
     </row>
     <row r="82" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -6688,22 +6688,22 @@
         <v>129.49</v>
       </c>
       <c r="I82" s="12">
-        <v>15350</v>
+        <v>281350</v>
       </c>
       <c r="J82" s="13">
-        <v>1.28</v>
+        <v>23.45</v>
       </c>
       <c r="K82" s="12">
-        <v>1569227</v>
+        <v>1835227</v>
       </c>
       <c r="L82" s="13">
-        <v>130.77000000000001</v>
+        <v>152.94</v>
       </c>
       <c r="M82" s="12">
-        <v>-369227</v>
+        <v>-635227</v>
       </c>
       <c r="N82" s="13">
-        <v>-30.77</v>
+        <v>-52.94</v>
       </c>
       <c r="O82" s="12">
         <v>0</v>
@@ -6712,10 +6712,10 @@
         <v>0</v>
       </c>
       <c r="Q82" s="12">
-        <v>-369227</v>
+        <v>-635227</v>
       </c>
       <c r="R82" s="13">
-        <v>-30.77</v>
+        <v>-52.94</v>
       </c>
     </row>
     <row r="83" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -6794,28 +6794,28 @@
         <v>3000000</v>
       </c>
       <c r="G84" s="12">
-        <v>2645961.2999999998</v>
+        <v>2485961.2999999998</v>
       </c>
       <c r="H84" s="13">
-        <v>88.2</v>
+        <v>82.87</v>
       </c>
       <c r="I84" s="12">
-        <v>298739</v>
+        <v>267139</v>
       </c>
       <c r="J84" s="13">
-        <v>9.9600000000000009</v>
+        <v>8.9</v>
       </c>
       <c r="K84" s="12">
-        <v>2944700.3</v>
+        <v>2753100.3</v>
       </c>
       <c r="L84" s="13">
-        <v>98.16</v>
+        <v>91.77</v>
       </c>
       <c r="M84" s="12">
-        <v>55299.7</v>
+        <v>246899.7</v>
       </c>
       <c r="N84" s="13">
-        <v>1.84</v>
+        <v>8.23</v>
       </c>
       <c r="O84" s="12">
         <v>0</v>
@@ -6824,10 +6824,10 @@
         <v>0</v>
       </c>
       <c r="Q84" s="12">
-        <v>55299.7</v>
+        <v>246899.7</v>
       </c>
       <c r="R84" s="13">
-        <v>1.84</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="85" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -7074,28 +7074,28 @@
         <v>1000000</v>
       </c>
       <c r="G89" s="12">
-        <v>12050</v>
+        <v>68210</v>
       </c>
       <c r="H89" s="13">
-        <v>1.21</v>
+        <v>6.82</v>
       </c>
       <c r="I89" s="12">
-        <v>63700</v>
+        <v>0</v>
       </c>
       <c r="J89" s="13">
-        <v>6.37</v>
+        <v>0</v>
       </c>
       <c r="K89" s="12">
-        <v>75750</v>
+        <v>68210</v>
       </c>
       <c r="L89" s="13">
-        <v>7.58</v>
+        <v>6.82</v>
       </c>
       <c r="M89" s="12">
-        <v>924250</v>
+        <v>931790</v>
       </c>
       <c r="N89" s="13">
-        <v>92.42</v>
+        <v>93.18</v>
       </c>
       <c r="O89" s="12">
         <v>550000</v>
@@ -7104,10 +7104,10 @@
         <v>55</v>
       </c>
       <c r="Q89" s="12">
-        <v>374250</v>
+        <v>381790</v>
       </c>
       <c r="R89" s="13">
-        <v>37.43</v>
+        <v>38.18</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
@@ -7130,40 +7130,40 @@
         <v>9800000</v>
       </c>
       <c r="G90" s="4">
-        <v>4952297.9800000004</v>
+        <v>5245581.9800000004</v>
       </c>
       <c r="H90" s="5">
-        <v>50.53</v>
+        <v>53.53</v>
       </c>
       <c r="I90" s="4">
-        <v>1012522.97</v>
+        <v>1204232.97</v>
       </c>
       <c r="J90" s="5">
-        <v>10.33</v>
+        <v>12.29</v>
       </c>
       <c r="K90" s="4">
-        <v>5964820.9500000002</v>
+        <v>6449814.9500000002</v>
       </c>
       <c r="L90" s="5">
-        <v>60.87</v>
+        <v>65.81</v>
       </c>
       <c r="M90" s="4">
-        <v>3835179.05</v>
+        <v>3350185.05</v>
       </c>
       <c r="N90" s="5">
-        <v>39.130000000000003</v>
+        <v>34.19</v>
       </c>
       <c r="O90" s="4">
-        <v>2233789.54</v>
+        <v>1737551.54</v>
       </c>
       <c r="P90" s="5">
-        <v>22.79</v>
+        <v>17.73</v>
       </c>
       <c r="Q90" s="4">
-        <v>1601389.51</v>
+        <v>1612633.51</v>
       </c>
       <c r="R90" s="5">
-        <v>16.34</v>
+        <v>16.46</v>
       </c>
     </row>
     <row r="91" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -7186,40 +7186,40 @@
         <v>9800000</v>
       </c>
       <c r="G91" s="8">
-        <v>4952297.9800000004</v>
+        <v>5245581.9800000004</v>
       </c>
       <c r="H91" s="9">
-        <v>50.53</v>
+        <v>53.53</v>
       </c>
       <c r="I91" s="8">
-        <v>1012522.97</v>
+        <v>1204232.97</v>
       </c>
       <c r="J91" s="9">
-        <v>10.33</v>
+        <v>12.29</v>
       </c>
       <c r="K91" s="8">
-        <v>5964820.9500000002</v>
+        <v>6449814.9500000002</v>
       </c>
       <c r="L91" s="9">
-        <v>60.87</v>
+        <v>65.81</v>
       </c>
       <c r="M91" s="8">
-        <v>3835179.05</v>
+        <v>3350185.05</v>
       </c>
       <c r="N91" s="9">
-        <v>39.130000000000003</v>
+        <v>34.19</v>
       </c>
       <c r="O91" s="8">
-        <v>2233789.54</v>
+        <v>1737551.54</v>
       </c>
       <c r="P91" s="9">
-        <v>22.79</v>
+        <v>17.73</v>
       </c>
       <c r="Q91" s="8">
-        <v>1601389.51</v>
+        <v>1612633.51</v>
       </c>
       <c r="R91" s="9">
-        <v>16.34</v>
+        <v>16.46</v>
       </c>
     </row>
     <row r="92" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
@@ -7242,28 +7242,28 @@
         <v>4305000</v>
       </c>
       <c r="G92" s="12">
-        <v>2317739.4900000002</v>
+        <v>2611023.4900000002</v>
       </c>
       <c r="H92" s="13">
-        <v>53.84</v>
+        <v>60.65</v>
       </c>
       <c r="I92" s="12">
-        <v>744572.97</v>
+        <v>440544.97</v>
       </c>
       <c r="J92" s="13">
-        <v>17.3</v>
+        <v>10.23</v>
       </c>
       <c r="K92" s="12">
-        <v>3062312.46</v>
+        <v>3051568.46</v>
       </c>
       <c r="L92" s="13">
-        <v>71.13</v>
+        <v>70.88</v>
       </c>
       <c r="M92" s="12">
-        <v>1242687.54</v>
+        <v>1253431.54</v>
       </c>
       <c r="N92" s="13">
-        <v>28.87</v>
+        <v>29.12</v>
       </c>
       <c r="O92" s="12">
         <v>801289.54</v>
@@ -7272,10 +7272,10 @@
         <v>18.61</v>
       </c>
       <c r="Q92" s="12">
-        <v>441398</v>
+        <v>452142</v>
       </c>
       <c r="R92" s="13">
-        <v>10.25</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="93" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -7304,28 +7304,28 @@
         <v>52.88</v>
       </c>
       <c r="I93" s="12">
-        <v>260750</v>
+        <v>560750</v>
       </c>
       <c r="J93" s="13">
-        <v>8.3000000000000007</v>
+        <v>17.86</v>
       </c>
       <c r="K93" s="12">
-        <v>1921277.49</v>
+        <v>2221277.4900000002</v>
       </c>
       <c r="L93" s="13">
-        <v>61.19</v>
+        <v>70.739999999999995</v>
       </c>
       <c r="M93" s="12">
-        <v>1218722.51</v>
+        <v>918722.51</v>
       </c>
       <c r="N93" s="13">
-        <v>38.81</v>
+        <v>29.26</v>
       </c>
       <c r="O93" s="12">
-        <v>682500</v>
+        <v>382500</v>
       </c>
       <c r="P93" s="13">
-        <v>21.74</v>
+        <v>12.18</v>
       </c>
       <c r="Q93" s="12">
         <v>536222.51</v>
@@ -7360,34 +7360,34 @@
         <v>41.36</v>
       </c>
       <c r="I94" s="12">
-        <v>7200</v>
+        <v>202938</v>
       </c>
       <c r="J94" s="13">
-        <v>0.31</v>
+        <v>8.6199999999999992</v>
       </c>
       <c r="K94" s="12">
-        <v>981231</v>
+        <v>1176969</v>
       </c>
       <c r="L94" s="13">
-        <v>41.67</v>
+        <v>49.98</v>
       </c>
       <c r="M94" s="12">
-        <v>1373769</v>
+        <v>1178031</v>
       </c>
       <c r="N94" s="13">
-        <v>58.33</v>
+        <v>50.02</v>
       </c>
       <c r="O94" s="12">
-        <v>750000</v>
+        <v>553762</v>
       </c>
       <c r="P94" s="13">
-        <v>31.85</v>
+        <v>23.51</v>
       </c>
       <c r="Q94" s="12">
-        <v>623769</v>
+        <v>624269</v>
       </c>
       <c r="R94" s="13">
-        <v>26.49</v>
+        <v>26.51</v>
       </c>
     </row>
     <row r="95" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -7410,40 +7410,40 @@
         <v>119421186</v>
       </c>
       <c r="G95" s="4">
-        <v>78356303.409999996</v>
+        <v>78812424.010000005</v>
       </c>
       <c r="H95" s="5">
-        <v>65.61</v>
+        <v>66</v>
       </c>
       <c r="I95" s="4">
-        <v>13687572.32</v>
+        <v>13638961.060000001</v>
       </c>
       <c r="J95" s="5">
-        <v>11.46</v>
+        <v>11.42</v>
       </c>
       <c r="K95" s="4">
-        <v>92043875.730000004</v>
+        <v>92451385.069999993</v>
       </c>
       <c r="L95" s="5">
-        <v>77.069999999999993</v>
+        <v>77.42</v>
       </c>
       <c r="M95" s="4">
-        <v>27377310.27</v>
+        <v>26969800.93</v>
       </c>
       <c r="N95" s="5">
-        <v>22.93</v>
+        <v>22.58</v>
       </c>
       <c r="O95" s="4">
-        <v>2612317.27</v>
+        <v>2245573.4300000002</v>
       </c>
       <c r="P95" s="5">
-        <v>2.19</v>
+        <v>1.88</v>
       </c>
       <c r="Q95" s="4">
-        <v>24764993</v>
+        <v>24724227.5</v>
       </c>
       <c r="R95" s="5">
-        <v>20.74</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="96" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -7466,40 +7466,40 @@
         <v>29200000</v>
       </c>
       <c r="G96" s="8">
-        <v>16148502.869999999</v>
+        <v>16179251.970000001</v>
       </c>
       <c r="H96" s="9">
-        <v>55.3</v>
+        <v>55.41</v>
       </c>
       <c r="I96" s="8">
-        <v>7352779.9900000002</v>
+        <v>7693680.8899999997</v>
       </c>
       <c r="J96" s="9">
-        <v>25.18</v>
+        <v>26.35</v>
       </c>
       <c r="K96" s="8">
-        <v>23501282.859999999</v>
+        <v>23872932.859999999</v>
       </c>
       <c r="L96" s="9">
-        <v>80.48</v>
+        <v>81.760000000000005</v>
       </c>
       <c r="M96" s="8">
-        <v>5698717.1399999997</v>
+        <v>5327067.1399999997</v>
       </c>
       <c r="N96" s="9">
-        <v>19.52</v>
+        <v>18.239999999999998</v>
       </c>
       <c r="O96" s="8">
-        <v>1639333.37</v>
+        <v>1274333.3700000001</v>
       </c>
       <c r="P96" s="9">
-        <v>5.61</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="Q96" s="8">
-        <v>4059383.77</v>
+        <v>4052733.77</v>
       </c>
       <c r="R96" s="9">
-        <v>13.9</v>
+        <v>13.88</v>
       </c>
     </row>
     <row r="97" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -7522,28 +7522,28 @@
         <v>3261268.89</v>
       </c>
       <c r="G97" s="12">
-        <v>2051442.37</v>
+        <v>2054292.37</v>
       </c>
       <c r="H97" s="13">
-        <v>62.9</v>
+        <v>62.99</v>
       </c>
       <c r="I97" s="12">
-        <v>1131840</v>
+        <v>1135640</v>
       </c>
       <c r="J97" s="13">
-        <v>34.71</v>
+        <v>34.82</v>
       </c>
       <c r="K97" s="12">
-        <v>3183282.37</v>
+        <v>3189932.37</v>
       </c>
       <c r="L97" s="13">
-        <v>97.61</v>
+        <v>97.81</v>
       </c>
       <c r="M97" s="12">
-        <v>77986.52</v>
+        <v>71336.52</v>
       </c>
       <c r="N97" s="13">
-        <v>2.39</v>
+        <v>2.19</v>
       </c>
       <c r="O97" s="12">
         <v>0</v>
@@ -7552,10 +7552,10 @@
         <v>0</v>
       </c>
       <c r="Q97" s="12">
-        <v>77986.52</v>
+        <v>71336.52</v>
       </c>
       <c r="R97" s="13">
-        <v>2.39</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="98" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -7578,16 +7578,16 @@
         <v>4780425.63</v>
       </c>
       <c r="G98" s="12">
-        <v>2332545.39</v>
+        <v>2335695.39</v>
       </c>
       <c r="H98" s="13">
-        <v>48.79</v>
+        <v>48.86</v>
       </c>
       <c r="I98" s="12">
-        <v>2447880.2400000002</v>
+        <v>2444730.2400000002</v>
       </c>
       <c r="J98" s="13">
-        <v>51.21</v>
+        <v>51.14</v>
       </c>
       <c r="K98" s="12">
         <v>4780425.63</v>
@@ -7634,16 +7634,16 @@
         <v>8310076.75</v>
       </c>
       <c r="G99" s="12">
-        <v>2844318.38</v>
+        <v>2869067.48</v>
       </c>
       <c r="H99" s="13">
-        <v>34.229999999999997</v>
+        <v>34.53</v>
       </c>
       <c r="I99" s="12">
-        <v>3773059.75</v>
+        <v>3748310.65</v>
       </c>
       <c r="J99" s="13">
-        <v>45.4</v>
+        <v>45.11</v>
       </c>
       <c r="K99" s="12">
         <v>6617378.1299999999</v>
@@ -7752,28 +7752,28 @@
         <v>69.430000000000007</v>
       </c>
       <c r="I101" s="12">
-        <v>0</v>
+        <v>365000</v>
       </c>
       <c r="J101" s="13">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="K101" s="12">
-        <v>8920196.7300000004</v>
+        <v>9285196.7300000004</v>
       </c>
       <c r="L101" s="13">
-        <v>69.430000000000007</v>
+        <v>72.27</v>
       </c>
       <c r="M101" s="12">
-        <v>3928032</v>
+        <v>3563032</v>
       </c>
       <c r="N101" s="13">
-        <v>30.57</v>
+        <v>27.73</v>
       </c>
       <c r="O101" s="12">
-        <v>380000</v>
+        <v>15000</v>
       </c>
       <c r="P101" s="13">
-        <v>2.96</v>
+        <v>0.12</v>
       </c>
       <c r="Q101" s="12">
         <v>3548032</v>
@@ -7808,22 +7808,22 @@
         <v>49.87</v>
       </c>
       <c r="I102" s="8">
-        <v>30120</v>
+        <v>67120</v>
       </c>
       <c r="J102" s="9">
-        <v>3.01</v>
+        <v>6.71</v>
       </c>
       <c r="K102" s="8">
-        <v>528839</v>
+        <v>565839</v>
       </c>
       <c r="L102" s="9">
-        <v>52.88</v>
+        <v>56.58</v>
       </c>
       <c r="M102" s="8">
-        <v>471161</v>
+        <v>434161</v>
       </c>
       <c r="N102" s="9">
-        <v>47.12</v>
+        <v>43.42</v>
       </c>
       <c r="O102" s="8">
         <v>0</v>
@@ -7832,10 +7832,10 @@
         <v>0</v>
       </c>
       <c r="Q102" s="8">
-        <v>471161</v>
+        <v>434161</v>
       </c>
       <c r="R102" s="9">
-        <v>47.12</v>
+        <v>43.42</v>
       </c>
     </row>
     <row r="103" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -7864,22 +7864,22 @@
         <v>48.31</v>
       </c>
       <c r="I103" s="12">
-        <v>17870</v>
+        <v>54870</v>
       </c>
       <c r="J103" s="13">
-        <v>2.02</v>
+        <v>6.19</v>
       </c>
       <c r="K103" s="12">
-        <v>446199</v>
+        <v>483199</v>
       </c>
       <c r="L103" s="13">
-        <v>50.33</v>
+        <v>54.5</v>
       </c>
       <c r="M103" s="12">
-        <v>440401</v>
+        <v>403401</v>
       </c>
       <c r="N103" s="13">
-        <v>49.67</v>
+        <v>45.5</v>
       </c>
       <c r="O103" s="12">
         <v>0</v>
@@ -7888,10 +7888,10 @@
         <v>0</v>
       </c>
       <c r="Q103" s="12">
-        <v>440401</v>
+        <v>403401</v>
       </c>
       <c r="R103" s="13">
-        <v>49.67</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
@@ -7970,28 +7970,28 @@
         <v>1000000</v>
       </c>
       <c r="G105" s="8">
-        <v>730475.74</v>
+        <v>747825.74</v>
       </c>
       <c r="H105" s="9">
-        <v>73.05</v>
+        <v>74.78</v>
       </c>
       <c r="I105" s="8">
-        <v>194668</v>
+        <v>173268</v>
       </c>
       <c r="J105" s="9">
-        <v>19.47</v>
+        <v>17.329999999999998</v>
       </c>
       <c r="K105" s="8">
-        <v>925143.74</v>
+        <v>921093.74</v>
       </c>
       <c r="L105" s="9">
-        <v>92.51</v>
+        <v>92.11</v>
       </c>
       <c r="M105" s="8">
-        <v>74856.259999999995</v>
+        <v>78906.259999999995</v>
       </c>
       <c r="N105" s="9">
-        <v>7.49</v>
+        <v>7.89</v>
       </c>
       <c r="O105" s="8">
         <v>0</v>
@@ -8000,10 +8000,10 @@
         <v>0</v>
       </c>
       <c r="Q105" s="8">
-        <v>74856.259999999995</v>
+        <v>78906.259999999995</v>
       </c>
       <c r="R105" s="9">
-        <v>7.49</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="106" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -8026,28 +8026,28 @@
         <v>213000</v>
       </c>
       <c r="G106" s="12">
-        <v>150988</v>
+        <v>168338</v>
       </c>
       <c r="H106" s="13">
-        <v>70.89</v>
+        <v>79.03</v>
       </c>
       <c r="I106" s="12">
-        <v>21400</v>
+        <v>0</v>
       </c>
       <c r="J106" s="13">
-        <v>10.050000000000001</v>
+        <v>0</v>
       </c>
       <c r="K106" s="12">
-        <v>172388</v>
+        <v>168338</v>
       </c>
       <c r="L106" s="13">
-        <v>80.930000000000007</v>
+        <v>79.03</v>
       </c>
       <c r="M106" s="12">
-        <v>40612</v>
+        <v>44662</v>
       </c>
       <c r="N106" s="13">
-        <v>19.07</v>
+        <v>20.97</v>
       </c>
       <c r="O106" s="12">
         <v>0</v>
@@ -8056,10 +8056,10 @@
         <v>0</v>
       </c>
       <c r="Q106" s="12">
-        <v>40612</v>
+        <v>44662</v>
       </c>
       <c r="R106" s="13">
-        <v>19.07</v>
+        <v>20.97</v>
       </c>
     </row>
     <row r="107" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -8138,34 +8138,34 @@
         <v>10194186</v>
       </c>
       <c r="G108" s="8">
-        <v>3098843</v>
+        <v>3495199</v>
       </c>
       <c r="H108" s="9">
-        <v>30.4</v>
+        <v>34.29</v>
       </c>
       <c r="I108" s="8">
-        <v>5906356.5999999996</v>
+        <v>5511744.4400000004</v>
       </c>
       <c r="J108" s="9">
-        <v>57.94</v>
+        <v>54.07</v>
       </c>
       <c r="K108" s="8">
-        <v>9005199.5999999996</v>
+        <v>9006943.4399999995</v>
       </c>
       <c r="L108" s="9">
-        <v>88.34</v>
+        <v>88.35</v>
       </c>
       <c r="M108" s="8">
-        <v>1188986.3999999999</v>
+        <v>1187242.56</v>
       </c>
       <c r="N108" s="9">
-        <v>11.66</v>
+        <v>11.65</v>
       </c>
       <c r="O108" s="8">
-        <v>971441.4</v>
+        <v>969697.56</v>
       </c>
       <c r="P108" s="9">
-        <v>9.5299999999999994</v>
+        <v>9.51</v>
       </c>
       <c r="Q108" s="8">
         <v>217545</v>
@@ -8194,34 +8194,34 @@
         <v>5612100</v>
       </c>
       <c r="G109" s="12">
-        <v>1470479</v>
+        <v>1525479</v>
       </c>
       <c r="H109" s="13">
-        <v>26.2</v>
+        <v>27.18</v>
       </c>
       <c r="I109" s="12">
-        <v>3205549.6</v>
+        <v>3152293.44</v>
       </c>
       <c r="J109" s="13">
-        <v>57.12</v>
+        <v>56.17</v>
       </c>
       <c r="K109" s="12">
-        <v>4676028.5999999996</v>
+        <v>4677772.4400000004</v>
       </c>
       <c r="L109" s="13">
-        <v>83.32</v>
+        <v>83.35</v>
       </c>
       <c r="M109" s="12">
-        <v>936071.4</v>
+        <v>934327.56</v>
       </c>
       <c r="N109" s="13">
-        <v>16.68</v>
+        <v>16.649999999999999</v>
       </c>
       <c r="O109" s="12">
-        <v>702688.4</v>
+        <v>700944.56</v>
       </c>
       <c r="P109" s="13">
-        <v>12.52</v>
+        <v>12.49</v>
       </c>
       <c r="Q109" s="12">
         <v>233383</v>
@@ -8250,16 +8250,16 @@
         <v>4582086</v>
       </c>
       <c r="G110" s="12">
-        <v>1628364</v>
+        <v>1969720</v>
       </c>
       <c r="H110" s="13">
-        <v>35.54</v>
+        <v>42.99</v>
       </c>
       <c r="I110" s="12">
-        <v>2700807</v>
+        <v>2359451</v>
       </c>
       <c r="J110" s="13">
-        <v>58.94</v>
+        <v>51.49</v>
       </c>
       <c r="K110" s="12">
         <v>4329171</v>
@@ -8306,25 +8306,25 @@
         <v>78027000</v>
       </c>
       <c r="G111" s="8">
-        <v>57879762.799999997</v>
+        <v>57891428.299999997</v>
       </c>
       <c r="H111" s="9">
-        <v>74.180000000000007</v>
+        <v>74.19</v>
       </c>
       <c r="I111" s="8">
-        <v>203647.73</v>
+        <v>193147.73</v>
       </c>
       <c r="J111" s="9">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="K111" s="8">
-        <v>58083410.530000001</v>
+        <v>58084576.030000001</v>
       </c>
       <c r="L111" s="9">
         <v>74.44</v>
       </c>
       <c r="M111" s="8">
-        <v>19943589.469999999</v>
+        <v>19942423.969999999</v>
       </c>
       <c r="N111" s="9">
         <v>25.56</v>
@@ -8336,7 +8336,7 @@
         <v>0</v>
       </c>
       <c r="Q111" s="8">
-        <v>19942046.969999999</v>
+        <v>19940881.469999999</v>
       </c>
       <c r="R111" s="9">
         <v>25.56</v>
@@ -8362,28 +8362,28 @@
         <v>640000</v>
       </c>
       <c r="G112" s="12">
-        <v>231355</v>
+        <v>240455</v>
       </c>
       <c r="H112" s="13">
-        <v>36.15</v>
+        <v>37.57</v>
       </c>
       <c r="I112" s="12">
-        <v>31647.5</v>
+        <v>21147.5</v>
       </c>
       <c r="J112" s="13">
-        <v>4.9400000000000004</v>
+        <v>3.3</v>
       </c>
       <c r="K112" s="12">
-        <v>263002.5</v>
+        <v>261602.5</v>
       </c>
       <c r="L112" s="13">
-        <v>41.09</v>
+        <v>40.880000000000003</v>
       </c>
       <c r="M112" s="12">
-        <v>376997.5</v>
+        <v>378397.5</v>
       </c>
       <c r="N112" s="13">
-        <v>58.91</v>
+        <v>59.12</v>
       </c>
       <c r="O112" s="12">
         <v>1542.5</v>
@@ -8392,10 +8392,10 @@
         <v>0.24</v>
       </c>
       <c r="Q112" s="12">
-        <v>375455</v>
+        <v>376855</v>
       </c>
       <c r="R112" s="13">
-        <v>58.66</v>
+        <v>58.88</v>
       </c>
     </row>
     <row r="113" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -8474,10 +8474,10 @@
         <v>75000000</v>
       </c>
       <c r="G114" s="12">
-        <v>55090653.729999997</v>
+        <v>55093219.229999997</v>
       </c>
       <c r="H114" s="13">
-        <v>73.45</v>
+        <v>73.459999999999994</v>
       </c>
       <c r="I114" s="12">
         <v>0</v>
@@ -8486,16 +8486,16 @@
         <v>0</v>
       </c>
       <c r="K114" s="12">
-        <v>55090653.729999997</v>
+        <v>55093219.229999997</v>
       </c>
       <c r="L114" s="13">
-        <v>73.45</v>
+        <v>73.459999999999994</v>
       </c>
       <c r="M114" s="12">
-        <v>19909346.27</v>
+        <v>19906780.77</v>
       </c>
       <c r="N114" s="13">
-        <v>26.55</v>
+        <v>26.54</v>
       </c>
       <c r="O114" s="12">
         <v>0</v>
@@ -8504,10 +8504,10 @@
         <v>0</v>
       </c>
       <c r="Q114" s="12">
-        <v>19909346.27</v>
+        <v>19906780.77</v>
       </c>
       <c r="R114" s="13">
-        <v>26.55</v>
+        <v>26.54</v>
       </c>
     </row>
     <row r="115" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -8696,40 +8696,40 @@
         <v>230702200</v>
       </c>
       <c r="G118" s="14">
-        <v>143284850.61000001</v>
+        <v>145743574.99000001</v>
       </c>
       <c r="H118" s="15">
-        <v>62.11</v>
+        <v>63.17</v>
       </c>
       <c r="I118" s="14">
-        <v>37050134.240000002</v>
+        <v>37387853.369999997</v>
       </c>
       <c r="J118" s="15">
-        <v>16.059999999999999</v>
+        <v>16.21</v>
       </c>
       <c r="K118" s="14">
-        <v>180334984.84999999</v>
+        <v>183131428.36000001</v>
       </c>
       <c r="L118" s="15">
-        <v>78.17</v>
+        <v>79.38</v>
       </c>
       <c r="M118" s="14">
-        <v>50367215.149999999</v>
+        <v>47570771.640000001</v>
       </c>
       <c r="N118" s="15">
-        <v>21.83</v>
+        <v>20.62</v>
       </c>
       <c r="O118" s="14">
-        <v>7831250.9100000001</v>
+        <v>6495994.0700000003</v>
       </c>
       <c r="P118" s="15">
-        <v>3.39</v>
+        <v>2.82</v>
       </c>
       <c r="Q118" s="14">
-        <v>42535964.240000002</v>
+        <v>41074777.57</v>
       </c>
       <c r="R118" s="15">
-        <v>18.440000000000001</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
@@ -8752,40 +8752,40 @@
         <v>100622228.15000001</v>
       </c>
       <c r="G119" s="4">
-        <v>22946611.77</v>
+        <v>25982540.120000001</v>
       </c>
       <c r="H119" s="5">
-        <v>22.8</v>
+        <v>25.82</v>
       </c>
       <c r="I119" s="4">
-        <v>19851637.949999999</v>
+        <v>20918369.199999999</v>
       </c>
       <c r="J119" s="5">
-        <v>19.73</v>
+        <v>20.79</v>
       </c>
       <c r="K119" s="4">
-        <v>42798249.719999999</v>
+        <v>46900909.32</v>
       </c>
       <c r="L119" s="5">
-        <v>42.53</v>
+        <v>46.61</v>
       </c>
       <c r="M119" s="4">
-        <v>57823978.43</v>
+        <v>53721318.829999998</v>
       </c>
       <c r="N119" s="5">
-        <v>57.47</v>
+        <v>53.39</v>
       </c>
       <c r="O119" s="4">
-        <v>6671343</v>
+        <v>4681593</v>
       </c>
       <c r="P119" s="5">
-        <v>6.63</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="Q119" s="4">
-        <v>51152635.43</v>
+        <v>49039725.829999998</v>
       </c>
       <c r="R119" s="5">
-        <v>50.84</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="120" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -9760,40 +9760,40 @@
         <v>7768581.8099999996</v>
       </c>
       <c r="G137" s="8">
-        <v>4902612.9400000004</v>
+        <v>5163933.29</v>
       </c>
       <c r="H137" s="9">
-        <v>63.11</v>
+        <v>66.47</v>
       </c>
       <c r="I137" s="8">
-        <v>962602.16</v>
+        <v>1230546.4099999999</v>
       </c>
       <c r="J137" s="9">
-        <v>12.39</v>
+        <v>15.84</v>
       </c>
       <c r="K137" s="8">
-        <v>5865215.0999999996</v>
+        <v>6394479.7000000002</v>
       </c>
       <c r="L137" s="9">
-        <v>75.5</v>
+        <v>82.31</v>
       </c>
       <c r="M137" s="8">
-        <v>1903366.71</v>
+        <v>1374102.11</v>
       </c>
       <c r="N137" s="9">
-        <v>24.5</v>
+        <v>17.690000000000001</v>
       </c>
       <c r="O137" s="8">
-        <v>613445</v>
+        <v>114945</v>
       </c>
       <c r="P137" s="9">
-        <v>7.9</v>
+        <v>1.48</v>
       </c>
       <c r="Q137" s="8">
-        <v>1289921.71</v>
+        <v>1259157.1100000001</v>
       </c>
       <c r="R137" s="9">
-        <v>16.600000000000001</v>
+        <v>16.21</v>
       </c>
     </row>
     <row r="138" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -9822,34 +9822,34 @@
         <v>81</v>
       </c>
       <c r="I138" s="12">
-        <v>0</v>
+        <v>521800</v>
       </c>
       <c r="J138" s="13">
-        <v>0</v>
+        <v>19.52</v>
       </c>
       <c r="K138" s="12">
-        <v>2164940.1</v>
+        <v>2686740.1</v>
       </c>
       <c r="L138" s="13">
-        <v>81</v>
+        <v>100.52</v>
       </c>
       <c r="M138" s="12">
-        <v>507813.2</v>
+        <v>-13986.8</v>
       </c>
       <c r="N138" s="13">
-        <v>19</v>
+        <v>-0.52</v>
       </c>
       <c r="O138" s="12">
-        <v>554945</v>
+        <v>56445</v>
       </c>
       <c r="P138" s="13">
-        <v>20.76</v>
+        <v>2.11</v>
       </c>
       <c r="Q138" s="12">
-        <v>-47131.8</v>
+        <v>-70431.8</v>
       </c>
       <c r="R138" s="13">
-        <v>-1.76</v>
+        <v>-2.64</v>
       </c>
     </row>
     <row r="139" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -9984,28 +9984,28 @@
         <v>586550</v>
       </c>
       <c r="G141" s="12">
-        <v>423525</v>
+        <v>684845.35</v>
       </c>
       <c r="H141" s="13">
-        <v>72.209999999999994</v>
+        <v>116.76</v>
       </c>
       <c r="I141" s="12">
-        <v>280700</v>
+        <v>26844.25</v>
       </c>
       <c r="J141" s="13">
-        <v>47.86</v>
+        <v>4.58</v>
       </c>
       <c r="K141" s="12">
-        <v>704225</v>
+        <v>711689.6</v>
       </c>
       <c r="L141" s="13">
-        <v>120.06</v>
+        <v>121.33</v>
       </c>
       <c r="M141" s="12">
-        <v>-117675</v>
+        <v>-125139.6</v>
       </c>
       <c r="N141" s="13">
-        <v>-20.059999999999999</v>
+        <v>-21.33</v>
       </c>
       <c r="O141" s="12">
         <v>50000</v>
@@ -10014,10 +10014,10 @@
         <v>8.52</v>
       </c>
       <c r="Q141" s="12">
-        <v>-167675</v>
+        <v>-175139.6</v>
       </c>
       <c r="R141" s="13">
-        <v>-28.59</v>
+        <v>-29.86</v>
       </c>
     </row>
     <row r="142" spans="1:18" x14ac:dyDescent="0.25">
@@ -11608,40 +11608,40 @@
         <v>8926239.0199999996</v>
       </c>
       <c r="G170" s="8">
-        <v>1080387.78</v>
+        <v>1303585.78</v>
       </c>
       <c r="H170" s="9">
-        <v>12.1</v>
+        <v>14.6</v>
       </c>
       <c r="I170" s="8">
-        <v>5243008</v>
+        <v>7401905</v>
       </c>
       <c r="J170" s="9">
-        <v>58.74</v>
+        <v>82.92</v>
       </c>
       <c r="K170" s="8">
-        <v>6323395.7800000003</v>
+        <v>8705490.7799999993</v>
       </c>
       <c r="L170" s="9">
-        <v>70.84</v>
+        <v>97.53</v>
       </c>
       <c r="M170" s="8">
-        <v>2602843.2400000002</v>
+        <v>220748.24</v>
       </c>
       <c r="N170" s="9">
-        <v>29.16</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="O170" s="8">
-        <v>500000</v>
+        <v>15000</v>
       </c>
       <c r="P170" s="9">
-        <v>5.6</v>
+        <v>0.17</v>
       </c>
       <c r="Q170" s="8">
-        <v>2102843.2400000002</v>
+        <v>205748.24</v>
       </c>
       <c r="R170" s="9">
-        <v>23.56</v>
+        <v>2.2999999999999998</v>
       </c>
     </row>
     <row r="171" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -11670,22 +11670,22 @@
         <v>16.64</v>
       </c>
       <c r="I171" s="12">
-        <v>1902000</v>
+        <v>3804000</v>
       </c>
       <c r="J171" s="13">
-        <v>82.63</v>
+        <v>165.27</v>
       </c>
       <c r="K171" s="12">
-        <v>2285035.81</v>
+        <v>4187035.81</v>
       </c>
       <c r="L171" s="13">
-        <v>99.27</v>
+        <v>181.91</v>
       </c>
       <c r="M171" s="12">
-        <v>16714.189999999999</v>
+        <v>-1885285.81</v>
       </c>
       <c r="N171" s="13">
-        <v>0.73</v>
+        <v>-81.91</v>
       </c>
       <c r="O171" s="12">
         <v>0</v>
@@ -11694,10 +11694,10 @@
         <v>0</v>
       </c>
       <c r="Q171" s="12">
-        <v>16714.189999999999</v>
+        <v>-1885285.81</v>
       </c>
       <c r="R171" s="13">
-        <v>0.73</v>
+        <v>-81.91</v>
       </c>
     </row>
     <row r="172" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -11776,28 +11776,28 @@
         <v>363000</v>
       </c>
       <c r="G173" s="12">
-        <v>0</v>
+        <v>75768</v>
       </c>
       <c r="H173" s="13">
-        <v>0</v>
+        <v>20.87</v>
       </c>
       <c r="I173" s="12">
-        <v>79100</v>
+        <v>0</v>
       </c>
       <c r="J173" s="13">
-        <v>21.79</v>
+        <v>0</v>
       </c>
       <c r="K173" s="12">
-        <v>79100</v>
+        <v>75768</v>
       </c>
       <c r="L173" s="13">
-        <v>21.79</v>
+        <v>20.87</v>
       </c>
       <c r="M173" s="12">
-        <v>283900</v>
+        <v>287232</v>
       </c>
       <c r="N173" s="13">
-        <v>78.209999999999994</v>
+        <v>79.13</v>
       </c>
       <c r="O173" s="12">
         <v>0</v>
@@ -11806,10 +11806,10 @@
         <v>0</v>
       </c>
       <c r="Q173" s="12">
-        <v>283900</v>
+        <v>287232</v>
       </c>
       <c r="R173" s="13">
-        <v>78.209999999999994</v>
+        <v>79.13</v>
       </c>
     </row>
     <row r="174" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
@@ -11944,28 +11944,28 @@
         <v>213000</v>
       </c>
       <c r="G176" s="12">
-        <v>64400</v>
+        <v>204030</v>
       </c>
       <c r="H176" s="13">
-        <v>30.23</v>
+        <v>95.79</v>
       </c>
       <c r="I176" s="12">
-        <v>139600</v>
+        <v>0</v>
       </c>
       <c r="J176" s="13">
-        <v>65.540000000000006</v>
+        <v>0</v>
       </c>
       <c r="K176" s="12">
-        <v>204000</v>
+        <v>204030</v>
       </c>
       <c r="L176" s="13">
-        <v>95.77</v>
+        <v>95.79</v>
       </c>
       <c r="M176" s="12">
-        <v>9000</v>
+        <v>8970</v>
       </c>
       <c r="N176" s="13">
-        <v>4.2300000000000004</v>
+        <v>4.21</v>
       </c>
       <c r="O176" s="12">
         <v>0</v>
@@ -11974,10 +11974,10 @@
         <v>0</v>
       </c>
       <c r="Q176" s="12">
-        <v>9000</v>
+        <v>8970</v>
       </c>
       <c r="R176" s="13">
-        <v>4.2300000000000004</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="177" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -12230,28 +12230,28 @@
         <v>0</v>
       </c>
       <c r="I181" s="12">
-        <v>0</v>
+        <v>485000</v>
       </c>
       <c r="J181" s="13">
-        <v>0</v>
+        <v>47.71</v>
       </c>
       <c r="K181" s="12">
-        <v>0</v>
+        <v>485000</v>
       </c>
       <c r="L181" s="13">
-        <v>0</v>
+        <v>47.71</v>
       </c>
       <c r="M181" s="12">
-        <v>1016489.02</v>
+        <v>531489.02</v>
       </c>
       <c r="N181" s="13">
-        <v>100</v>
+        <v>52.29</v>
       </c>
       <c r="O181" s="12">
-        <v>500000</v>
+        <v>15000</v>
       </c>
       <c r="P181" s="13">
-        <v>49.19</v>
+        <v>1.48</v>
       </c>
       <c r="Q181" s="12">
         <v>516489.02</v>
@@ -12280,28 +12280,28 @@
         <v>1410000</v>
       </c>
       <c r="G182" s="12">
-        <v>72587.7</v>
+        <v>80387.7</v>
       </c>
       <c r="H182" s="13">
-        <v>5.15</v>
+        <v>5.7</v>
       </c>
       <c r="I182" s="12">
-        <v>50228</v>
+        <v>40825</v>
       </c>
       <c r="J182" s="13">
-        <v>3.56</v>
+        <v>2.9</v>
       </c>
       <c r="K182" s="12">
-        <v>122815.7</v>
+        <v>121212.7</v>
       </c>
       <c r="L182" s="13">
-        <v>8.7100000000000009</v>
+        <v>8.6</v>
       </c>
       <c r="M182" s="12">
-        <v>1287184.3</v>
+        <v>1288787.3</v>
       </c>
       <c r="N182" s="13">
-        <v>91.29</v>
+        <v>91.4</v>
       </c>
       <c r="O182" s="12">
         <v>0</v>
@@ -12310,10 +12310,10 @@
         <v>0</v>
       </c>
       <c r="Q182" s="12">
-        <v>1287184.3</v>
+        <v>1288787.3</v>
       </c>
       <c r="R182" s="13">
-        <v>91.29</v>
+        <v>91.4</v>
       </c>
     </row>
     <row r="183" spans="1:18" x14ac:dyDescent="0.25">
@@ -13456,40 +13456,40 @@
         <v>12829676.84</v>
       </c>
       <c r="G203" s="8">
-        <v>2672712.91</v>
+        <v>2673312.91</v>
       </c>
       <c r="H203" s="9">
-        <v>20.83</v>
+        <v>20.84</v>
       </c>
       <c r="I203" s="8">
-        <v>898161.56</v>
+        <v>1295901.56</v>
       </c>
       <c r="J203" s="9">
-        <v>7</v>
+        <v>10.1</v>
       </c>
       <c r="K203" s="8">
-        <v>3570874.47</v>
+        <v>3969214.47</v>
       </c>
       <c r="L203" s="9">
-        <v>27.83</v>
+        <v>30.94</v>
       </c>
       <c r="M203" s="8">
-        <v>9258802.3699999992</v>
+        <v>8860462.3699999992</v>
       </c>
       <c r="N203" s="9">
-        <v>72.17</v>
+        <v>69.06</v>
       </c>
       <c r="O203" s="8">
-        <v>200000</v>
+        <v>54000</v>
       </c>
       <c r="P203" s="9">
-        <v>1.56</v>
+        <v>0.42</v>
       </c>
       <c r="Q203" s="8">
-        <v>9058802.3699999992</v>
+        <v>8806462.3699999992</v>
       </c>
       <c r="R203" s="9">
-        <v>70.61</v>
+        <v>68.64</v>
       </c>
     </row>
     <row r="204" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -13512,40 +13512,40 @@
         <v>1681566.8</v>
       </c>
       <c r="G204" s="12">
-        <v>228160</v>
+        <v>228760</v>
       </c>
       <c r="H204" s="13">
-        <v>13.57</v>
+        <v>13.6</v>
       </c>
       <c r="I204" s="12">
-        <v>58100</v>
+        <v>255840</v>
       </c>
       <c r="J204" s="13">
-        <v>3.46</v>
+        <v>15.21</v>
       </c>
       <c r="K204" s="12">
-        <v>286260</v>
+        <v>484600</v>
       </c>
       <c r="L204" s="13">
-        <v>17.02</v>
+        <v>28.82</v>
       </c>
       <c r="M204" s="12">
-        <v>1395306.8</v>
+        <v>1196966.8</v>
       </c>
       <c r="N204" s="13">
-        <v>82.98</v>
+        <v>71.180000000000007</v>
       </c>
       <c r="O204" s="12">
-        <v>0</v>
+        <v>54000</v>
       </c>
       <c r="P204" s="13">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q204" s="12">
-        <v>1395306.8</v>
+        <v>1142966.8</v>
       </c>
       <c r="R204" s="13">
-        <v>82.98</v>
+        <v>67.97</v>
       </c>
     </row>
     <row r="205" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -13742,28 +13742,28 @@
         <v>22.07</v>
       </c>
       <c r="I208" s="12">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="J208" s="13">
-        <v>0</v>
+        <v>14.87</v>
       </c>
       <c r="K208" s="12">
-        <v>296772</v>
+        <v>496772</v>
       </c>
       <c r="L208" s="13">
-        <v>22.07</v>
+        <v>36.950000000000003</v>
       </c>
       <c r="M208" s="12">
-        <v>1047828</v>
+        <v>847828</v>
       </c>
       <c r="N208" s="13">
-        <v>77.930000000000007</v>
+        <v>63.05</v>
       </c>
       <c r="O208" s="12">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="P208" s="13">
-        <v>14.87</v>
+        <v>0</v>
       </c>
       <c r="Q208" s="12">
         <v>847828</v>
@@ -16088,28 +16088,28 @@
         <v>2528000</v>
       </c>
       <c r="G250" s="8">
-        <v>615729.84</v>
+        <v>666089.84</v>
       </c>
       <c r="H250" s="9">
-        <v>24.36</v>
+        <v>26.35</v>
       </c>
       <c r="I250" s="8">
-        <v>665560</v>
+        <v>768860</v>
       </c>
       <c r="J250" s="9">
-        <v>26.33</v>
+        <v>30.41</v>
       </c>
       <c r="K250" s="8">
-        <v>1281289.8400000001</v>
+        <v>1434949.84</v>
       </c>
       <c r="L250" s="9">
-        <v>50.68</v>
+        <v>56.76</v>
       </c>
       <c r="M250" s="8">
-        <v>1246710.1599999999</v>
+        <v>1093050.1599999999</v>
       </c>
       <c r="N250" s="9">
-        <v>49.32</v>
+        <v>43.24</v>
       </c>
       <c r="O250" s="8">
         <v>20000</v>
@@ -16118,10 +16118,10 @@
         <v>0.79</v>
       </c>
       <c r="Q250" s="8">
-        <v>1226710.1599999999</v>
+        <v>1073050.1599999999</v>
       </c>
       <c r="R250" s="9">
-        <v>48.52</v>
+        <v>42.45</v>
       </c>
     </row>
     <row r="251" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -16150,22 +16150,22 @@
         <v>18.559999999999999</v>
       </c>
       <c r="I251" s="12">
-        <v>335600</v>
+        <v>406900</v>
       </c>
       <c r="J251" s="13">
-        <v>42.37</v>
+        <v>51.38</v>
       </c>
       <c r="K251" s="12">
-        <v>482600</v>
+        <v>553900</v>
       </c>
       <c r="L251" s="13">
-        <v>60.93</v>
+        <v>69.94</v>
       </c>
       <c r="M251" s="12">
-        <v>309400</v>
+        <v>238100</v>
       </c>
       <c r="N251" s="13">
-        <v>39.07</v>
+        <v>30.06</v>
       </c>
       <c r="O251" s="12">
         <v>20000</v>
@@ -16174,10 +16174,10 @@
         <v>2.5299999999999998</v>
       </c>
       <c r="Q251" s="12">
-        <v>289400</v>
+        <v>218100</v>
       </c>
       <c r="R251" s="13">
-        <v>36.54</v>
+        <v>27.54</v>
       </c>
     </row>
     <row r="252" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -16200,10 +16200,10 @@
         <v>944000</v>
       </c>
       <c r="G252" s="12">
-        <v>273027.24</v>
+        <v>276027.24</v>
       </c>
       <c r="H252" s="13">
-        <v>28.92</v>
+        <v>29.24</v>
       </c>
       <c r="I252" s="12">
         <v>220000</v>
@@ -16212,16 +16212,16 @@
         <v>23.31</v>
       </c>
       <c r="K252" s="12">
-        <v>493027.24</v>
+        <v>496027.24</v>
       </c>
       <c r="L252" s="13">
-        <v>52.23</v>
+        <v>52.55</v>
       </c>
       <c r="M252" s="12">
-        <v>450972.76</v>
+        <v>447972.76</v>
       </c>
       <c r="N252" s="13">
-        <v>47.77</v>
+        <v>47.45</v>
       </c>
       <c r="O252" s="12">
         <v>0</v>
@@ -16230,10 +16230,10 @@
         <v>0</v>
       </c>
       <c r="Q252" s="12">
-        <v>450972.76</v>
+        <v>447972.76</v>
       </c>
       <c r="R252" s="13">
-        <v>47.77</v>
+        <v>47.45</v>
       </c>
     </row>
     <row r="253" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
@@ -16256,28 +16256,28 @@
         <v>792000</v>
       </c>
       <c r="G253" s="12">
-        <v>195702.6</v>
+        <v>243062.6</v>
       </c>
       <c r="H253" s="13">
-        <v>24.71</v>
+        <v>30.69</v>
       </c>
       <c r="I253" s="12">
-        <v>109960</v>
+        <v>141960</v>
       </c>
       <c r="J253" s="13">
-        <v>13.88</v>
+        <v>17.920000000000002</v>
       </c>
       <c r="K253" s="12">
-        <v>305662.59999999998</v>
+        <v>385022.6</v>
       </c>
       <c r="L253" s="13">
-        <v>38.590000000000003</v>
+        <v>48.61</v>
       </c>
       <c r="M253" s="12">
-        <v>486337.4</v>
+        <v>406977.4</v>
       </c>
       <c r="N253" s="13">
-        <v>61.41</v>
+        <v>51.39</v>
       </c>
       <c r="O253" s="12">
         <v>0</v>
@@ -16286,10 +16286,10 @@
         <v>0</v>
       </c>
       <c r="Q253" s="12">
-        <v>486337.4</v>
+        <v>406977.4</v>
       </c>
       <c r="R253" s="13">
-        <v>61.41</v>
+        <v>51.39</v>
       </c>
     </row>
     <row r="254" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -16312,40 +16312,40 @@
         <v>12554100</v>
       </c>
       <c r="G254" s="8">
-        <v>2866335.44</v>
+        <v>2966335.44</v>
       </c>
       <c r="H254" s="9">
-        <v>22.83</v>
+        <v>23.63</v>
       </c>
       <c r="I254" s="8">
-        <v>1192358.56</v>
+        <v>1530958.56</v>
       </c>
       <c r="J254" s="9">
-        <v>9.5</v>
+        <v>12.19</v>
       </c>
       <c r="K254" s="8">
-        <v>4058694</v>
+        <v>4497294</v>
       </c>
       <c r="L254" s="9">
-        <v>32.33</v>
+        <v>35.82</v>
       </c>
       <c r="M254" s="8">
-        <v>8495406</v>
+        <v>8056806</v>
       </c>
       <c r="N254" s="9">
-        <v>67.67</v>
+        <v>64.180000000000007</v>
       </c>
       <c r="O254" s="8">
-        <v>864148</v>
+        <v>564148</v>
       </c>
       <c r="P254" s="9">
-        <v>6.88</v>
+        <v>4.49</v>
       </c>
       <c r="Q254" s="8">
-        <v>7631258</v>
+        <v>7492658</v>
       </c>
       <c r="R254" s="9">
-        <v>60.79</v>
+        <v>59.68</v>
       </c>
     </row>
     <row r="255" spans="1:18" ht="132" x14ac:dyDescent="0.25">
@@ -16374,28 +16374,28 @@
         <v>16.350000000000001</v>
       </c>
       <c r="I255" s="12">
-        <v>168000</v>
+        <v>468000</v>
       </c>
       <c r="J255" s="13">
-        <v>3.84</v>
+        <v>10.7</v>
       </c>
       <c r="K255" s="12">
-        <v>883494</v>
+        <v>1183494</v>
       </c>
       <c r="L255" s="13">
-        <v>20.190000000000001</v>
+        <v>27.05</v>
       </c>
       <c r="M255" s="12">
-        <v>3491506</v>
+        <v>3191506</v>
       </c>
       <c r="N255" s="13">
-        <v>79.81</v>
+        <v>72.95</v>
       </c>
       <c r="O255" s="12">
-        <v>804000</v>
+        <v>504000</v>
       </c>
       <c r="P255" s="13">
-        <v>18.38</v>
+        <v>11.52</v>
       </c>
       <c r="Q255" s="12">
         <v>2687506</v>
@@ -16424,28 +16424,28 @@
         <v>4556000</v>
       </c>
       <c r="G256" s="12">
-        <v>1484743</v>
+        <v>1584743</v>
       </c>
       <c r="H256" s="13">
-        <v>32.590000000000003</v>
+        <v>34.78</v>
       </c>
       <c r="I256" s="12">
-        <v>626100</v>
+        <v>664700</v>
       </c>
       <c r="J256" s="13">
-        <v>13.74</v>
+        <v>14.59</v>
       </c>
       <c r="K256" s="12">
-        <v>2110843</v>
+        <v>2249443</v>
       </c>
       <c r="L256" s="13">
-        <v>46.33</v>
+        <v>49.37</v>
       </c>
       <c r="M256" s="12">
-        <v>2445157</v>
+        <v>2306557</v>
       </c>
       <c r="N256" s="13">
-        <v>53.67</v>
+        <v>50.63</v>
       </c>
       <c r="O256" s="12">
         <v>60000</v>
@@ -16454,10 +16454,10 @@
         <v>1.32</v>
       </c>
       <c r="Q256" s="12">
-        <v>2385157</v>
+        <v>2246557</v>
       </c>
       <c r="R256" s="13">
-        <v>52.35</v>
+        <v>49.31</v>
       </c>
     </row>
     <row r="257" spans="1:18" x14ac:dyDescent="0.25">
@@ -17040,37 +17040,37 @@
         <v>19811100</v>
       </c>
       <c r="G267" s="8">
-        <v>12550</v>
+        <v>2413000</v>
       </c>
       <c r="H267" s="9">
-        <v>0.06</v>
+        <v>12.18</v>
       </c>
       <c r="I267" s="8">
-        <v>7348620</v>
+        <v>5148870</v>
       </c>
       <c r="J267" s="9">
-        <v>37.090000000000003</v>
+        <v>25.99</v>
       </c>
       <c r="K267" s="8">
-        <v>7361170</v>
+        <v>7561870</v>
       </c>
       <c r="L267" s="9">
-        <v>37.159999999999997</v>
+        <v>38.17</v>
       </c>
       <c r="M267" s="8">
-        <v>12449930</v>
+        <v>12249230</v>
       </c>
       <c r="N267" s="9">
-        <v>62.84</v>
+        <v>61.83</v>
       </c>
       <c r="O267" s="8">
-        <v>200250</v>
+        <v>0</v>
       </c>
       <c r="P267" s="9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Q267" s="8">
-        <v>12249680</v>
+        <v>12249230</v>
       </c>
       <c r="R267" s="9">
         <v>61.83</v>
@@ -17152,16 +17152,16 @@
         <v>10400000</v>
       </c>
       <c r="G269" s="12">
-        <v>0</v>
+        <v>2400000</v>
       </c>
       <c r="H269" s="13">
-        <v>0</v>
+        <v>23.08</v>
       </c>
       <c r="I269" s="12">
-        <v>7200000</v>
+        <v>4800000</v>
       </c>
       <c r="J269" s="13">
-        <v>69.23</v>
+        <v>46.15</v>
       </c>
       <c r="K269" s="12">
         <v>7200000</v>
@@ -17382,28 +17382,28 @@
         <v>0</v>
       </c>
       <c r="I273" s="12">
-        <v>140250</v>
+        <v>340500</v>
       </c>
       <c r="J273" s="13">
-        <v>3.79</v>
+        <v>9.2100000000000009</v>
       </c>
       <c r="K273" s="12">
-        <v>140250</v>
+        <v>340500</v>
       </c>
       <c r="L273" s="13">
-        <v>3.79</v>
+        <v>9.2100000000000009</v>
       </c>
       <c r="M273" s="12">
-        <v>3556950</v>
+        <v>3356700</v>
       </c>
       <c r="N273" s="13">
-        <v>96.21</v>
+        <v>90.79</v>
       </c>
       <c r="O273" s="12">
-        <v>200250</v>
+        <v>0</v>
       </c>
       <c r="P273" s="13">
-        <v>5.42</v>
+        <v>0</v>
       </c>
       <c r="Q273" s="12">
         <v>3356700</v>
@@ -17432,10 +17432,10 @@
         <v>406250</v>
       </c>
       <c r="G274" s="12">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="H274" s="13">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="I274" s="12">
         <v>0</v>
@@ -17444,16 +17444,16 @@
         <v>0</v>
       </c>
       <c r="K274" s="12">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="L274" s="13">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="M274" s="12">
-        <v>406250</v>
+        <v>405800</v>
       </c>
       <c r="N274" s="13">
-        <v>100</v>
+        <v>99.89</v>
       </c>
       <c r="O274" s="12">
         <v>0</v>
@@ -17462,10 +17462,10 @@
         <v>0</v>
       </c>
       <c r="Q274" s="12">
-        <v>406250</v>
+        <v>405800</v>
       </c>
       <c r="R274" s="13">
-        <v>100</v>
+        <v>99.89</v>
       </c>
     </row>
     <row r="275" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -17568,16 +17568,16 @@
         <v>92.96</v>
       </c>
       <c r="O276" s="8">
-        <v>720000</v>
+        <v>360000</v>
       </c>
       <c r="P276" s="9">
-        <v>32.65</v>
+        <v>16.32</v>
       </c>
       <c r="Q276" s="8">
-        <v>1330250</v>
+        <v>1690250</v>
       </c>
       <c r="R276" s="9">
-        <v>60.32</v>
+        <v>76.64</v>
       </c>
     </row>
     <row r="277" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -17624,16 +17624,16 @@
         <v>100</v>
       </c>
       <c r="O277" s="12">
-        <v>720000</v>
+        <v>360000</v>
       </c>
       <c r="P277" s="13">
-        <v>40.82</v>
+        <v>20.41</v>
       </c>
       <c r="Q277" s="12">
-        <v>1043750</v>
+        <v>1403750</v>
       </c>
       <c r="R277" s="13">
-        <v>59.18</v>
+        <v>79.59</v>
       </c>
     </row>
     <row r="278" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -17766,40 +17766,40 @@
         <v>100622228.15000001</v>
       </c>
       <c r="G280" s="14">
-        <v>22946611.77</v>
+        <v>25982540.120000001</v>
       </c>
       <c r="H280" s="15">
-        <v>22.8</v>
+        <v>25.82</v>
       </c>
       <c r="I280" s="14">
-        <v>19851637.949999999</v>
+        <v>20918369.199999999</v>
       </c>
       <c r="J280" s="15">
-        <v>19.73</v>
+        <v>20.79</v>
       </c>
       <c r="K280" s="14">
-        <v>42798249.719999999</v>
+        <v>46900909.32</v>
       </c>
       <c r="L280" s="15">
-        <v>42.53</v>
+        <v>46.61</v>
       </c>
       <c r="M280" s="14">
-        <v>57823978.43</v>
+        <v>53721318.829999998</v>
       </c>
       <c r="N280" s="15">
-        <v>57.47</v>
+        <v>53.39</v>
       </c>
       <c r="O280" s="14">
-        <v>6671343</v>
+        <v>4681593</v>
       </c>
       <c r="P280" s="15">
-        <v>6.63</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="Q280" s="14">
-        <v>51152635.43</v>
+        <v>49039725.829999998</v>
       </c>
       <c r="R280" s="15">
-        <v>50.84</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="281" spans="1:18" x14ac:dyDescent="0.25">
@@ -17820,40 +17820,40 @@
         <v>331324428.14999998</v>
       </c>
       <c r="G281" s="16">
-        <v>166231462.38</v>
+        <v>171726115.11000001</v>
       </c>
       <c r="H281" s="17">
-        <v>50.17</v>
+        <v>51.83</v>
       </c>
       <c r="I281" s="16">
-        <v>56901772.189999998</v>
+        <v>58306222.57</v>
       </c>
       <c r="J281" s="17">
-        <v>17.170000000000002</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="K281" s="16">
-        <v>223133234.56999999</v>
+        <v>230032337.68000001</v>
       </c>
       <c r="L281" s="17">
-        <v>67.349999999999994</v>
+        <v>69.430000000000007</v>
       </c>
       <c r="M281" s="16">
-        <v>108191193.58</v>
+        <v>101292090.47</v>
       </c>
       <c r="N281" s="17">
-        <v>32.65</v>
+        <v>30.57</v>
       </c>
       <c r="O281" s="16">
-        <v>14502593.91</v>
+        <v>11177587.07</v>
       </c>
       <c r="P281" s="17">
-        <v>4.38</v>
+        <v>3.37</v>
       </c>
       <c r="Q281" s="16">
-        <v>93688599.670000002</v>
+        <v>90114503.400000006</v>
       </c>
       <c r="R281" s="17">
-        <v>28.28</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="282" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -18096,40 +18096,40 @@
         <v>337490008.32999998</v>
       </c>
       <c r="G286" s="16">
-        <v>166231462.38</v>
+        <v>171726115.11000001</v>
       </c>
       <c r="H286" s="17">
-        <v>49.26</v>
+        <v>50.88</v>
       </c>
       <c r="I286" s="16">
-        <v>56901772.189999998</v>
+        <v>58306222.57</v>
       </c>
       <c r="J286" s="17">
-        <v>16.86</v>
+        <v>17.28</v>
       </c>
       <c r="K286" s="16">
-        <v>223133234.56999999</v>
+        <v>230032337.68000001</v>
       </c>
       <c r="L286" s="17">
-        <v>66.12</v>
+        <v>68.16</v>
       </c>
       <c r="M286" s="16">
-        <v>114356773.76000001</v>
+        <v>107457670.65000001</v>
       </c>
       <c r="N286" s="17">
-        <v>33.880000000000003</v>
+        <v>31.84</v>
       </c>
       <c r="O286" s="16">
-        <v>14502593.91</v>
+        <v>11177587.07</v>
       </c>
       <c r="P286" s="17">
-        <v>4.3</v>
+        <v>3.31</v>
       </c>
       <c r="Q286" s="16">
-        <v>99854179.849999994</v>
+        <v>96280083.579999998</v>
       </c>
       <c r="R286" s="17">
-        <v>29.59</v>
+        <v>28.53</v>
       </c>
     </row>
     <row r="287" spans="1:18" x14ac:dyDescent="0.25">
@@ -18152,13 +18152,13 @@
         <v>4037940.24</v>
       </c>
       <c r="G287" s="4">
-        <v>555190.98</v>
+        <v>555191.18000000005</v>
       </c>
       <c r="H287" s="5">
         <v>13.75</v>
       </c>
       <c r="I287" s="4">
-        <v>158448.9</v>
+        <v>158448.70000000001</v>
       </c>
       <c r="J287" s="5">
         <v>3.92</v>
@@ -18208,13 +18208,13 @@
         <v>4037940.24</v>
       </c>
       <c r="G288" s="8">
-        <v>555190.98</v>
+        <v>555191.18000000005</v>
       </c>
       <c r="H288" s="9">
         <v>13.75</v>
       </c>
       <c r="I288" s="8">
-        <v>158448.9</v>
+        <v>158448.70000000001</v>
       </c>
       <c r="J288" s="9">
         <v>3.92</v>
@@ -18264,13 +18264,13 @@
         <v>4037940.24</v>
       </c>
       <c r="G289" s="12">
-        <v>555190.98</v>
+        <v>555191.18000000005</v>
       </c>
       <c r="H289" s="13">
         <v>13.75</v>
       </c>
       <c r="I289" s="12">
-        <v>158448.9</v>
+        <v>158448.70000000001</v>
       </c>
       <c r="J289" s="13">
         <v>3.92</v>
@@ -18318,13 +18318,13 @@
         <v>4037940.24</v>
       </c>
       <c r="G290" s="14">
-        <v>555190.98</v>
+        <v>555191.18000000005</v>
       </c>
       <c r="H290" s="15">
         <v>13.75</v>
       </c>
       <c r="I290" s="14">
-        <v>158448.9</v>
+        <v>158448.70000000001</v>
       </c>
       <c r="J290" s="15">
         <v>3.92</v>
@@ -18372,40 +18372,40 @@
         <v>341527948.56999999</v>
       </c>
       <c r="G291" s="16">
-        <v>166786653.36000001</v>
+        <v>172281306.28999999</v>
       </c>
       <c r="H291" s="17">
-        <v>48.84</v>
+        <v>50.44</v>
       </c>
       <c r="I291" s="16">
-        <v>57060221.090000004</v>
+        <v>58464671.270000003</v>
       </c>
       <c r="J291" s="17">
-        <v>16.71</v>
+        <v>17.12</v>
       </c>
       <c r="K291" s="16">
-        <v>223846874.44999999</v>
+        <v>230745977.56</v>
       </c>
       <c r="L291" s="17">
-        <v>65.540000000000006</v>
+        <v>67.56</v>
       </c>
       <c r="M291" s="16">
-        <v>117681074.12</v>
+        <v>110781971.01000001</v>
       </c>
       <c r="N291" s="17">
-        <v>34.46</v>
+        <v>32.44</v>
       </c>
       <c r="O291" s="16">
-        <v>14508723.029999999</v>
+        <v>11183716.189999999</v>
       </c>
       <c r="P291" s="17">
-        <v>4.25</v>
+        <v>3.27</v>
       </c>
       <c r="Q291" s="16">
-        <v>103172351.09</v>
+        <v>99598254.819999993</v>
       </c>
       <c r="R291" s="17">
-        <v>30.21</v>
+        <v>29.16</v>
       </c>
     </row>
     <row r="292" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -18428,40 +18428,40 @@
         <v>46540814</v>
       </c>
       <c r="G292" s="19">
-        <v>21481675.600000001</v>
+        <v>21925150.120000001</v>
       </c>
       <c r="H292" s="20">
-        <v>46.16</v>
+        <v>47.11</v>
       </c>
       <c r="I292" s="19">
-        <v>16350843.189999999</v>
+        <v>16086468.67</v>
       </c>
       <c r="J292" s="20">
-        <v>35.130000000000003</v>
+        <v>34.56</v>
       </c>
       <c r="K292" s="19">
-        <v>37832518.789999999</v>
+        <v>38011618.789999999</v>
       </c>
       <c r="L292" s="20">
-        <v>81.290000000000006</v>
+        <v>81.67</v>
       </c>
       <c r="M292" s="19">
-        <v>8708295.2100000009</v>
+        <v>8529195.2100000009</v>
       </c>
       <c r="N292" s="20">
-        <v>18.71</v>
+        <v>18.329999999999998</v>
       </c>
       <c r="O292" s="19">
-        <v>1938721.6</v>
+        <v>1493446.6</v>
       </c>
       <c r="P292" s="20">
-        <v>4.17</v>
+        <v>3.21</v>
       </c>
       <c r="Q292" s="19">
-        <v>6769573.6100000003</v>
+        <v>7035748.6100000003</v>
       </c>
       <c r="R292" s="20">
-        <v>14.55</v>
+        <v>15.12</v>
       </c>
     </row>
     <row r="293" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -18484,40 +18484,40 @@
         <v>54940200</v>
       </c>
       <c r="G293" s="19">
-        <v>38494573.619999997</v>
+        <v>39760418.880000003</v>
       </c>
       <c r="H293" s="20">
-        <v>70.069999999999993</v>
+        <v>72.37</v>
       </c>
       <c r="I293" s="19">
-        <v>5999195.7599999998</v>
+        <v>6458190.6699999999</v>
       </c>
       <c r="J293" s="20">
-        <v>10.92</v>
+        <v>11.75</v>
       </c>
       <c r="K293" s="19">
-        <v>44493769.380000003</v>
+        <v>46218609.549999997</v>
       </c>
       <c r="L293" s="20">
-        <v>80.989999999999995</v>
+        <v>84.13</v>
       </c>
       <c r="M293" s="19">
-        <v>10446430.619999999</v>
+        <v>8721590.4499999993</v>
       </c>
       <c r="N293" s="20">
-        <v>19.010000000000002</v>
+        <v>15.87</v>
       </c>
       <c r="O293" s="19">
-        <v>1046422.5</v>
+        <v>1019422.5</v>
       </c>
       <c r="P293" s="20">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="Q293" s="19">
-        <v>9400008.1199999992</v>
+        <v>7702167.9500000002</v>
       </c>
       <c r="R293" s="20">
-        <v>17.11</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="294" spans="1:18" x14ac:dyDescent="0.25">
@@ -18540,40 +18540,40 @@
         <v>9800000</v>
       </c>
       <c r="G294" s="19">
-        <v>4952297.9800000004</v>
+        <v>5245581.9800000004</v>
       </c>
       <c r="H294" s="20">
-        <v>50.53</v>
+        <v>53.53</v>
       </c>
       <c r="I294" s="19">
-        <v>1012522.97</v>
+        <v>1204232.97</v>
       </c>
       <c r="J294" s="20">
-        <v>10.33</v>
+        <v>12.29</v>
       </c>
       <c r="K294" s="19">
-        <v>5964820.9500000002</v>
+        <v>6449814.9500000002</v>
       </c>
       <c r="L294" s="20">
-        <v>60.87</v>
+        <v>65.81</v>
       </c>
       <c r="M294" s="19">
-        <v>3835179.05</v>
+        <v>3350185.05</v>
       </c>
       <c r="N294" s="20">
-        <v>39.130000000000003</v>
+        <v>34.19</v>
       </c>
       <c r="O294" s="19">
-        <v>2233789.54</v>
+        <v>1737551.54</v>
       </c>
       <c r="P294" s="20">
-        <v>22.79</v>
+        <v>17.73</v>
       </c>
       <c r="Q294" s="19">
-        <v>1601389.51</v>
+        <v>1612633.51</v>
       </c>
       <c r="R294" s="20">
-        <v>16.34</v>
+        <v>16.46</v>
       </c>
     </row>
     <row r="295" spans="1:18" x14ac:dyDescent="0.25">
@@ -18596,40 +18596,40 @@
         <v>100622228.15000001</v>
       </c>
       <c r="G295" s="19">
-        <v>22946611.77</v>
+        <v>25982540.120000001</v>
       </c>
       <c r="H295" s="20">
-        <v>22.8</v>
+        <v>25.82</v>
       </c>
       <c r="I295" s="19">
-        <v>19851637.949999999</v>
+        <v>20918369.199999999</v>
       </c>
       <c r="J295" s="20">
-        <v>19.73</v>
+        <v>20.79</v>
       </c>
       <c r="K295" s="19">
-        <v>42798249.719999999</v>
+        <v>46900909.32</v>
       </c>
       <c r="L295" s="20">
-        <v>42.53</v>
+        <v>46.61</v>
       </c>
       <c r="M295" s="19">
-        <v>57823978.43</v>
+        <v>53721318.829999998</v>
       </c>
       <c r="N295" s="20">
-        <v>57.47</v>
+        <v>53.39</v>
       </c>
       <c r="O295" s="19">
-        <v>6671343</v>
+        <v>4681593</v>
       </c>
       <c r="P295" s="20">
-        <v>6.63</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="Q295" s="19">
-        <v>51152635.43</v>
+        <v>49039725.829999998</v>
       </c>
       <c r="R295" s="20">
-        <v>50.84</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="296" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -18708,13 +18708,13 @@
         <v>4037940.24</v>
       </c>
       <c r="G297" s="19">
-        <v>555190.98</v>
+        <v>555191.18000000005</v>
       </c>
       <c r="H297" s="20">
         <v>13.75</v>
       </c>
       <c r="I297" s="19">
-        <v>158448.9</v>
+        <v>158448.70000000001</v>
       </c>
       <c r="J297" s="20">
         <v>3.92</v>
@@ -18764,40 +18764,40 @@
         <v>119421186</v>
       </c>
       <c r="G298" s="19">
-        <v>78356303.409999996</v>
+        <v>78812424.010000005</v>
       </c>
       <c r="H298" s="20">
-        <v>65.61</v>
+        <v>66</v>
       </c>
       <c r="I298" s="19">
-        <v>13687572.32</v>
+        <v>13638961.060000001</v>
       </c>
       <c r="J298" s="20">
-        <v>11.46</v>
+        <v>11.42</v>
       </c>
       <c r="K298" s="19">
-        <v>92043875.730000004</v>
+        <v>92451385.069999993</v>
       </c>
       <c r="L298" s="20">
-        <v>77.069999999999993</v>
+        <v>77.42</v>
       </c>
       <c r="M298" s="19">
-        <v>27377310.27</v>
+        <v>26969800.93</v>
       </c>
       <c r="N298" s="20">
-        <v>22.93</v>
+        <v>22.58</v>
       </c>
       <c r="O298" s="19">
-        <v>2612317.27</v>
+        <v>2245573.4300000002</v>
       </c>
       <c r="P298" s="20">
-        <v>2.19</v>
+        <v>1.88</v>
       </c>
       <c r="Q298" s="19">
-        <v>24764993</v>
+        <v>24724227.5</v>
       </c>
       <c r="R298" s="20">
-        <v>20.74</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="299" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -18874,40 +18874,40 @@
         <v>341527948.56999999</v>
       </c>
       <c r="G300" s="19">
-        <v>166786653.36000001</v>
+        <v>172281306.28999999</v>
       </c>
       <c r="H300" s="20">
-        <v>48.84</v>
+        <v>50.44</v>
       </c>
       <c r="I300" s="19">
-        <v>57060221.090000004</v>
+        <v>58464671.270000003</v>
       </c>
       <c r="J300" s="20">
-        <v>16.71</v>
+        <v>17.12</v>
       </c>
       <c r="K300" s="19">
-        <v>223846874.44999999</v>
+        <v>230745977.56</v>
       </c>
       <c r="L300" s="20">
-        <v>65.540000000000006</v>
+        <v>67.56</v>
       </c>
       <c r="M300" s="19">
-        <v>117681074.12</v>
+        <v>110781971.01000001</v>
       </c>
       <c r="N300" s="20">
-        <v>34.46</v>
+        <v>32.44</v>
       </c>
       <c r="O300" s="19">
-        <v>14508723.029999999</v>
+        <v>11183716.189999999</v>
       </c>
       <c r="P300" s="20">
-        <v>4.25</v>
+        <v>3.27</v>
       </c>
       <c r="Q300" s="19">
-        <v>103172351.09</v>
+        <v>99598254.819999993</v>
       </c>
       <c r="R300" s="20">
-        <v>30.21</v>
+        <v>29.16</v>
       </c>
     </row>
     <row r="301" spans="1:18" x14ac:dyDescent="0.25">
@@ -18948,11 +18948,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AD63382-A003-4D81-892C-760F98FB6BA0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC439B99-3F23-4CA6-BF5F-86D3A4EE47D8}">
   <dimension ref="A1:R83"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21" style="28" customWidth="1"/>
+    <col min="1" max="1" width="17.69921875" style="28" customWidth="1"/>
     <col min="2" max="2" width="12.796875" style="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.8984375" style="28" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.19921875" style="28" bestFit="1" customWidth="1"/>
@@ -18967,7 +18967,7 @@
     <col min="14" max="14" width="7" style="28" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.796875" style="28" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="5.3984375" style="28" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.8984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.796875" style="28" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="7" style="28" bestFit="1" customWidth="1"/>
     <col min="19" max="16384" width="8.796875" style="28"/>
   </cols>
@@ -19089,28 +19089,28 @@
         <v>1000000</v>
       </c>
       <c r="G6" s="4">
-        <v>730475.74</v>
+        <v>747825.74</v>
       </c>
       <c r="H6" s="5">
-        <v>73.05</v>
+        <v>74.78</v>
       </c>
       <c r="I6" s="4">
-        <v>194668</v>
+        <v>173268</v>
       </c>
       <c r="J6" s="5">
-        <v>19.47</v>
+        <v>17.329999999999998</v>
       </c>
       <c r="K6" s="4">
-        <v>925143.74</v>
+        <v>921093.74</v>
       </c>
       <c r="L6" s="5">
-        <v>92.51</v>
+        <v>92.11</v>
       </c>
       <c r="M6" s="4">
-        <v>74856.259999999995</v>
+        <v>78906.259999999995</v>
       </c>
       <c r="N6" s="5">
-        <v>7.49</v>
+        <v>7.89</v>
       </c>
       <c r="O6" s="4">
         <v>0</v>
@@ -19119,13 +19119,13 @@
         <v>0</v>
       </c>
       <c r="Q6" s="4">
-        <v>74856.259999999995</v>
+        <v>78906.259999999995</v>
       </c>
       <c r="R6" s="5">
-        <v>7.49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
+        <v>7.89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>207</v>
       </c>
@@ -19145,28 +19145,28 @@
         <v>1000000</v>
       </c>
       <c r="G7" s="8">
-        <v>730475.74</v>
+        <v>747825.74</v>
       </c>
       <c r="H7" s="9">
-        <v>73.05</v>
+        <v>74.78</v>
       </c>
       <c r="I7" s="8">
-        <v>194668</v>
+        <v>173268</v>
       </c>
       <c r="J7" s="9">
-        <v>19.47</v>
+        <v>17.329999999999998</v>
       </c>
       <c r="K7" s="8">
-        <v>925143.74</v>
+        <v>921093.74</v>
       </c>
       <c r="L7" s="9">
-        <v>92.51</v>
+        <v>92.11</v>
       </c>
       <c r="M7" s="8">
-        <v>74856.259999999995</v>
+        <v>78906.259999999995</v>
       </c>
       <c r="N7" s="9">
-        <v>7.49</v>
+        <v>7.89</v>
       </c>
       <c r="O7" s="8">
         <v>0</v>
@@ -19175,10 +19175,10 @@
         <v>0</v>
       </c>
       <c r="Q7" s="8">
-        <v>74856.259999999995</v>
+        <v>78906.259999999995</v>
       </c>
       <c r="R7" s="9">
-        <v>7.49</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -19205,22 +19205,22 @@
         <v>49.87</v>
       </c>
       <c r="I8" s="4">
-        <v>30120</v>
+        <v>67120</v>
       </c>
       <c r="J8" s="5">
-        <v>3.01</v>
+        <v>6.71</v>
       </c>
       <c r="K8" s="4">
-        <v>528839</v>
+        <v>565839</v>
       </c>
       <c r="L8" s="5">
-        <v>52.88</v>
+        <v>56.58</v>
       </c>
       <c r="M8" s="4">
-        <v>471161</v>
+        <v>434161</v>
       </c>
       <c r="N8" s="5">
-        <v>47.12</v>
+        <v>43.42</v>
       </c>
       <c r="O8" s="4">
         <v>0</v>
@@ -19229,13 +19229,13 @@
         <v>0</v>
       </c>
       <c r="Q8" s="4">
-        <v>471161</v>
+        <v>434161</v>
       </c>
       <c r="R8" s="5">
-        <v>47.12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+        <v>43.42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>201</v>
       </c>
@@ -19261,22 +19261,22 @@
         <v>49.87</v>
       </c>
       <c r="I9" s="8">
-        <v>30120</v>
+        <v>67120</v>
       </c>
       <c r="J9" s="9">
-        <v>3.01</v>
+        <v>6.71</v>
       </c>
       <c r="K9" s="8">
-        <v>528839</v>
+        <v>565839</v>
       </c>
       <c r="L9" s="9">
-        <v>52.88</v>
+        <v>56.58</v>
       </c>
       <c r="M9" s="8">
-        <v>471161</v>
+        <v>434161</v>
       </c>
       <c r="N9" s="9">
-        <v>47.12</v>
+        <v>43.42</v>
       </c>
       <c r="O9" s="8">
         <v>0</v>
@@ -19285,10 +19285,10 @@
         <v>0</v>
       </c>
       <c r="Q9" s="8">
-        <v>471161</v>
+        <v>434161</v>
       </c>
       <c r="R9" s="9">
-        <v>47.12</v>
+        <v>43.42</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -19309,28 +19309,28 @@
         <v>11720000</v>
       </c>
       <c r="G10" s="4">
-        <v>7481436</v>
+        <v>7582346</v>
       </c>
       <c r="H10" s="5">
-        <v>63.83</v>
+        <v>64.7</v>
       </c>
       <c r="I10" s="4">
-        <v>1458873</v>
+        <v>1490828</v>
       </c>
       <c r="J10" s="5">
-        <v>12.45</v>
+        <v>12.72</v>
       </c>
       <c r="K10" s="4">
-        <v>8940309</v>
+        <v>9073174</v>
       </c>
       <c r="L10" s="5">
-        <v>76.28</v>
+        <v>77.42</v>
       </c>
       <c r="M10" s="4">
-        <v>2779691</v>
+        <v>2646826</v>
       </c>
       <c r="N10" s="5">
-        <v>23.72</v>
+        <v>22.58</v>
       </c>
       <c r="O10" s="4">
         <v>600</v>
@@ -19339,13 +19339,13 @@
         <v>0.01</v>
       </c>
       <c r="Q10" s="4">
-        <v>2779091</v>
+        <v>2646226</v>
       </c>
       <c r="R10" s="5">
-        <v>23.71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+        <v>22.58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>133</v>
       </c>
@@ -19365,28 +19365,28 @@
         <v>11720000</v>
       </c>
       <c r="G11" s="8">
-        <v>7481436</v>
+        <v>7582346</v>
       </c>
       <c r="H11" s="9">
-        <v>63.83</v>
+        <v>64.7</v>
       </c>
       <c r="I11" s="8">
-        <v>1458873</v>
+        <v>1490828</v>
       </c>
       <c r="J11" s="9">
-        <v>12.45</v>
+        <v>12.72</v>
       </c>
       <c r="K11" s="8">
-        <v>8940309</v>
+        <v>9073174</v>
       </c>
       <c r="L11" s="9">
-        <v>76.28</v>
+        <v>77.42</v>
       </c>
       <c r="M11" s="8">
-        <v>2779691</v>
+        <v>2646826</v>
       </c>
       <c r="N11" s="9">
-        <v>23.72</v>
+        <v>22.58</v>
       </c>
       <c r="O11" s="8">
         <v>600</v>
@@ -19395,10 +19395,10 @@
         <v>0.01</v>
       </c>
       <c r="Q11" s="8">
-        <v>2779091</v>
+        <v>2646226</v>
       </c>
       <c r="R11" s="9">
-        <v>23.71</v>
+        <v>22.58</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -19419,28 +19419,28 @@
         <v>11820000</v>
       </c>
       <c r="G12" s="4">
-        <v>8448373.2899999991</v>
+        <v>8645193.2899999991</v>
       </c>
       <c r="H12" s="5">
-        <v>71.48</v>
+        <v>73.14</v>
       </c>
       <c r="I12" s="4">
-        <v>1227197</v>
+        <v>1319847</v>
       </c>
       <c r="J12" s="5">
-        <v>10.38</v>
+        <v>11.17</v>
       </c>
       <c r="K12" s="4">
-        <v>9675570.2899999991</v>
+        <v>9965040.2899999991</v>
       </c>
       <c r="L12" s="5">
-        <v>81.86</v>
+        <v>84.31</v>
       </c>
       <c r="M12" s="4">
-        <v>2144429.71</v>
+        <v>1854959.71</v>
       </c>
       <c r="N12" s="5">
-        <v>18.14</v>
+        <v>15.69</v>
       </c>
       <c r="O12" s="4">
         <v>80000</v>
@@ -19449,10 +19449,10 @@
         <v>0.68</v>
       </c>
       <c r="Q12" s="4">
-        <v>2064429.71</v>
+        <v>1774959.71</v>
       </c>
       <c r="R12" s="5">
-        <v>17.47</v>
+        <v>15.02</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -19511,7 +19511,7 @@
         <v>22.43</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>143</v>
       </c>
@@ -19531,28 +19531,28 @@
         <v>10640000</v>
       </c>
       <c r="G14" s="8">
-        <v>7810024.29</v>
+        <v>8006844.29</v>
       </c>
       <c r="H14" s="9">
-        <v>73.400000000000006</v>
+        <v>75.25</v>
       </c>
       <c r="I14" s="8">
-        <v>950197</v>
+        <v>1042847</v>
       </c>
       <c r="J14" s="9">
-        <v>8.93</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="K14" s="8">
-        <v>8760221.2899999991</v>
+        <v>9049691.2899999991</v>
       </c>
       <c r="L14" s="9">
-        <v>82.33</v>
+        <v>85.05</v>
       </c>
       <c r="M14" s="8">
-        <v>1879778.71</v>
+        <v>1590308.71</v>
       </c>
       <c r="N14" s="9">
-        <v>17.670000000000002</v>
+        <v>14.95</v>
       </c>
       <c r="O14" s="8">
         <v>80000</v>
@@ -19561,10 +19561,10 @@
         <v>0.75</v>
       </c>
       <c r="Q14" s="8">
-        <v>1799778.71</v>
+        <v>1510308.71</v>
       </c>
       <c r="R14" s="9">
-        <v>16.920000000000002</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -19585,28 +19585,28 @@
         <v>11840200</v>
       </c>
       <c r="G15" s="4">
-        <v>8763472.8599999994</v>
+        <v>8998397.8599999994</v>
       </c>
       <c r="H15" s="5">
-        <v>74.010000000000005</v>
+        <v>76</v>
       </c>
       <c r="I15" s="4">
-        <v>1455847.35</v>
+        <v>1614322.67</v>
       </c>
       <c r="J15" s="5">
-        <v>12.3</v>
+        <v>13.63</v>
       </c>
       <c r="K15" s="4">
-        <v>10219320.210000001</v>
+        <v>10612720.529999999</v>
       </c>
       <c r="L15" s="5">
-        <v>86.31</v>
+        <v>89.63</v>
       </c>
       <c r="M15" s="4">
-        <v>1620879.79</v>
+        <v>1227479.47</v>
       </c>
       <c r="N15" s="5">
-        <v>13.69</v>
+        <v>10.37</v>
       </c>
       <c r="O15" s="4">
         <v>144801.1</v>
@@ -19615,13 +19615,13 @@
         <v>1.22</v>
       </c>
       <c r="Q15" s="4">
-        <v>1476078.69</v>
+        <v>1082678.3700000001</v>
       </c>
       <c r="R15" s="5">
-        <v>12.47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+        <v>9.14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>75</v>
       </c>
@@ -19641,16 +19641,16 @@
         <v>500000</v>
       </c>
       <c r="G16" s="8">
-        <v>357667.9</v>
+        <v>435867.9</v>
       </c>
       <c r="H16" s="9">
-        <v>71.53</v>
+        <v>87.17</v>
       </c>
       <c r="I16" s="8">
-        <v>118800</v>
+        <v>40600</v>
       </c>
       <c r="J16" s="9">
-        <v>23.76</v>
+        <v>8.1199999999999992</v>
       </c>
       <c r="K16" s="8">
         <v>476467.9</v>
@@ -19677,7 +19677,7 @@
         <v>3.76</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>99</v>
       </c>
@@ -19697,28 +19697,28 @@
         <v>11340200</v>
       </c>
       <c r="G17" s="8">
-        <v>8405804.9600000009</v>
+        <v>8562529.9600000009</v>
       </c>
       <c r="H17" s="9">
-        <v>74.12</v>
+        <v>75.510000000000005</v>
       </c>
       <c r="I17" s="8">
-        <v>1337047.3500000001</v>
+        <v>1573722.67</v>
       </c>
       <c r="J17" s="9">
-        <v>11.79</v>
+        <v>13.88</v>
       </c>
       <c r="K17" s="8">
-        <v>9742852.3100000005</v>
+        <v>10136252.630000001</v>
       </c>
       <c r="L17" s="9">
-        <v>85.91</v>
+        <v>89.38</v>
       </c>
       <c r="M17" s="8">
-        <v>1597347.69</v>
+        <v>1203947.3700000001</v>
       </c>
       <c r="N17" s="9">
-        <v>14.09</v>
+        <v>10.62</v>
       </c>
       <c r="O17" s="8">
         <v>140079.5</v>
@@ -19727,10 +19727,10 @@
         <v>1.24</v>
       </c>
       <c r="Q17" s="8">
-        <v>1457268.19</v>
+        <v>1063867.8700000001</v>
       </c>
       <c r="R17" s="9">
-        <v>12.85</v>
+        <v>9.3800000000000008</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -19751,28 +19751,28 @@
         <v>7820000</v>
       </c>
       <c r="G18" s="4">
-        <v>5358529.5999999996</v>
+        <v>5477358.5999999996</v>
       </c>
       <c r="H18" s="5">
-        <v>68.52</v>
+        <v>70.040000000000006</v>
       </c>
       <c r="I18" s="4">
-        <v>603659</v>
+        <v>548489</v>
       </c>
       <c r="J18" s="5">
-        <v>7.72</v>
+        <v>7.01</v>
       </c>
       <c r="K18" s="4">
-        <v>5962188.5999999996</v>
+        <v>6025847.5999999996</v>
       </c>
       <c r="L18" s="5">
-        <v>76.239999999999995</v>
+        <v>77.06</v>
       </c>
       <c r="M18" s="4">
-        <v>1857811.4</v>
+        <v>1794152.4</v>
       </c>
       <c r="N18" s="5">
-        <v>23.76</v>
+        <v>22.94</v>
       </c>
       <c r="O18" s="4">
         <v>550000</v>
@@ -19781,13 +19781,13 @@
         <v>7.03</v>
       </c>
       <c r="Q18" s="4">
-        <v>1307811.3999999999</v>
+        <v>1244152.3999999999</v>
       </c>
       <c r="R18" s="5">
-        <v>16.72</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+        <v>15.91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>161</v>
       </c>
@@ -19807,28 +19807,28 @@
         <v>7820000</v>
       </c>
       <c r="G19" s="8">
-        <v>5358529.5999999996</v>
+        <v>5477358.5999999996</v>
       </c>
       <c r="H19" s="9">
-        <v>68.52</v>
+        <v>70.040000000000006</v>
       </c>
       <c r="I19" s="8">
-        <v>603659</v>
+        <v>548489</v>
       </c>
       <c r="J19" s="9">
-        <v>7.72</v>
+        <v>7.01</v>
       </c>
       <c r="K19" s="8">
-        <v>5962188.5999999996</v>
+        <v>6025847.5999999996</v>
       </c>
       <c r="L19" s="9">
-        <v>76.239999999999995</v>
+        <v>77.06</v>
       </c>
       <c r="M19" s="8">
-        <v>1857811.4</v>
+        <v>1794152.4</v>
       </c>
       <c r="N19" s="9">
-        <v>23.76</v>
+        <v>22.94</v>
       </c>
       <c r="O19" s="8">
         <v>550000</v>
@@ -19837,10 +19837,10 @@
         <v>7.03</v>
       </c>
       <c r="Q19" s="8">
-        <v>1307811.3999999999</v>
+        <v>1244152.3999999999</v>
       </c>
       <c r="R19" s="9">
-        <v>16.72</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -19861,43 +19861,43 @@
         <v>13420000</v>
       </c>
       <c r="G20" s="4">
-        <v>9438778.7699999996</v>
+        <v>10131340.029999999</v>
       </c>
       <c r="H20" s="5">
-        <v>70.33</v>
+        <v>75.489999999999995</v>
       </c>
       <c r="I20" s="4">
-        <v>1649419.41</v>
+        <v>1802304</v>
       </c>
       <c r="J20" s="5">
-        <v>12.29</v>
+        <v>13.43</v>
       </c>
       <c r="K20" s="4">
-        <v>11088198.18</v>
+        <v>11933644.029999999</v>
       </c>
       <c r="L20" s="5">
-        <v>82.62</v>
+        <v>88.92</v>
       </c>
       <c r="M20" s="4">
-        <v>2331801.8199999998</v>
+        <v>1486355.97</v>
       </c>
       <c r="N20" s="5">
-        <v>17.38</v>
+        <v>11.08</v>
       </c>
       <c r="O20" s="4">
-        <v>275743</v>
+        <v>248743</v>
       </c>
       <c r="P20" s="5">
-        <v>2.0499999999999998</v>
+        <v>1.85</v>
       </c>
       <c r="Q20" s="4">
-        <v>2056058.82</v>
+        <v>1237612.97</v>
       </c>
       <c r="R20" s="5">
-        <v>15.32</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+        <v>9.2200000000000006</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>111</v>
       </c>
@@ -19917,40 +19917,40 @@
         <v>13420000</v>
       </c>
       <c r="G21" s="8">
-        <v>9438778.7699999996</v>
+        <v>10131340.029999999</v>
       </c>
       <c r="H21" s="9">
-        <v>70.33</v>
+        <v>75.489999999999995</v>
       </c>
       <c r="I21" s="8">
-        <v>1649419.41</v>
+        <v>1802304</v>
       </c>
       <c r="J21" s="9">
-        <v>12.29</v>
+        <v>13.43</v>
       </c>
       <c r="K21" s="8">
-        <v>11088198.18</v>
+        <v>11933644.029999999</v>
       </c>
       <c r="L21" s="9">
-        <v>82.62</v>
+        <v>88.92</v>
       </c>
       <c r="M21" s="8">
-        <v>2331801.8199999998</v>
+        <v>1486355.97</v>
       </c>
       <c r="N21" s="9">
-        <v>17.38</v>
+        <v>11.08</v>
       </c>
       <c r="O21" s="8">
-        <v>275743</v>
+        <v>248743</v>
       </c>
       <c r="P21" s="9">
-        <v>2.0499999999999998</v>
+        <v>1.85</v>
       </c>
       <c r="Q21" s="8">
-        <v>2056058.82</v>
+        <v>1237612.97</v>
       </c>
       <c r="R21" s="9">
-        <v>15.32</v>
+        <v>9.2200000000000006</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -19971,43 +19971,43 @@
         <v>107227000</v>
       </c>
       <c r="G22" s="4">
-        <v>74028265.670000002</v>
+        <v>74070680.269999996</v>
       </c>
       <c r="H22" s="5">
-        <v>69.040000000000006</v>
+        <v>69.08</v>
       </c>
       <c r="I22" s="4">
-        <v>7556427.7199999997</v>
+        <v>7886828.6200000001</v>
       </c>
       <c r="J22" s="5">
-        <v>7.05</v>
+        <v>7.36</v>
       </c>
       <c r="K22" s="4">
-        <v>81584693.390000001</v>
+        <v>81957508.890000001</v>
       </c>
       <c r="L22" s="5">
-        <v>76.09</v>
+        <v>76.430000000000007</v>
       </c>
       <c r="M22" s="4">
-        <v>25642306.609999999</v>
+        <v>25269491.109999999</v>
       </c>
       <c r="N22" s="5">
-        <v>23.91</v>
+        <v>23.57</v>
       </c>
       <c r="O22" s="4">
-        <v>1640875.87</v>
+        <v>1275875.8700000001</v>
       </c>
       <c r="P22" s="5">
-        <v>1.53</v>
+        <v>1.19</v>
       </c>
       <c r="Q22" s="4">
-        <v>24001430.739999998</v>
+        <v>23993615.239999998</v>
       </c>
       <c r="R22" s="5">
         <v>22.38</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>190</v>
       </c>
@@ -20027,43 +20027,43 @@
         <v>29200000</v>
       </c>
       <c r="G23" s="8">
-        <v>16148502.869999999</v>
+        <v>16179251.970000001</v>
       </c>
       <c r="H23" s="9">
-        <v>55.3</v>
+        <v>55.41</v>
       </c>
       <c r="I23" s="8">
-        <v>7352779.9900000002</v>
+        <v>7693680.8899999997</v>
       </c>
       <c r="J23" s="9">
-        <v>25.18</v>
+        <v>26.35</v>
       </c>
       <c r="K23" s="8">
-        <v>23501282.859999999</v>
+        <v>23872932.859999999</v>
       </c>
       <c r="L23" s="9">
-        <v>80.48</v>
+        <v>81.760000000000005</v>
       </c>
       <c r="M23" s="8">
-        <v>5698717.1399999997</v>
+        <v>5327067.1399999997</v>
       </c>
       <c r="N23" s="9">
-        <v>19.52</v>
+        <v>18.239999999999998</v>
       </c>
       <c r="O23" s="8">
-        <v>1639333.37</v>
+        <v>1274333.3700000001</v>
       </c>
       <c r="P23" s="9">
-        <v>5.61</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="Q23" s="8">
-        <v>4059383.77</v>
+        <v>4052733.77</v>
       </c>
       <c r="R23" s="9">
-        <v>13.9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+        <v>13.88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>219</v>
       </c>
@@ -20083,25 +20083,25 @@
         <v>78027000</v>
       </c>
       <c r="G24" s="8">
-        <v>57879762.799999997</v>
+        <v>57891428.299999997</v>
       </c>
       <c r="H24" s="9">
-        <v>74.180000000000007</v>
+        <v>74.19</v>
       </c>
       <c r="I24" s="8">
-        <v>203647.73</v>
+        <v>193147.73</v>
       </c>
       <c r="J24" s="9">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="K24" s="8">
-        <v>58083410.530000001</v>
+        <v>58084576.030000001</v>
       </c>
       <c r="L24" s="9">
         <v>74.44</v>
       </c>
       <c r="M24" s="8">
-        <v>19943589.469999999</v>
+        <v>19942423.969999999</v>
       </c>
       <c r="N24" s="9">
         <v>25.56</v>
@@ -20113,7 +20113,7 @@
         <v>0</v>
       </c>
       <c r="Q24" s="8">
-        <v>19942046.969999999</v>
+        <v>19940881.469999999</v>
       </c>
       <c r="R24" s="9">
         <v>25.56</v>
@@ -20199,28 +20199,28 @@
         <v>39.909999999999997</v>
       </c>
       <c r="I26" s="4">
-        <v>580421.67000000004</v>
+        <v>732896.67</v>
       </c>
       <c r="J26" s="5">
-        <v>13.62</v>
+        <v>17.2</v>
       </c>
       <c r="K26" s="4">
-        <v>2280792.1</v>
+        <v>2433267.1</v>
       </c>
       <c r="L26" s="5">
-        <v>53.54</v>
+        <v>57.12</v>
       </c>
       <c r="M26" s="4">
-        <v>1979207.9</v>
+        <v>1826732.9</v>
       </c>
       <c r="N26" s="5">
-        <v>46.46</v>
+        <v>42.88</v>
       </c>
       <c r="O26" s="4">
-        <v>254000</v>
+        <v>101525</v>
       </c>
       <c r="P26" s="5">
-        <v>5.96</v>
+        <v>2.38</v>
       </c>
       <c r="Q26" s="4">
         <v>1725207.9</v>
@@ -20229,7 +20229,7 @@
         <v>40.5</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>59</v>
       </c>
@@ -20255,28 +20255,28 @@
         <v>39.909999999999997</v>
       </c>
       <c r="I27" s="8">
-        <v>580421.67000000004</v>
+        <v>732896.67</v>
       </c>
       <c r="J27" s="9">
-        <v>13.62</v>
+        <v>17.2</v>
       </c>
       <c r="K27" s="8">
-        <v>2280792.1</v>
+        <v>2433267.1</v>
       </c>
       <c r="L27" s="9">
-        <v>53.54</v>
+        <v>57.12</v>
       </c>
       <c r="M27" s="8">
-        <v>1979207.9</v>
+        <v>1826732.9</v>
       </c>
       <c r="N27" s="9">
-        <v>46.46</v>
+        <v>42.88</v>
       </c>
       <c r="O27" s="8">
-        <v>254000</v>
+        <v>101525</v>
       </c>
       <c r="P27" s="9">
-        <v>5.96</v>
+        <v>2.38</v>
       </c>
       <c r="Q27" s="8">
         <v>1725207.9</v>
@@ -20303,43 +20303,43 @@
         <v>60595000</v>
       </c>
       <c r="G28" s="4">
-        <v>26836429.25</v>
+        <v>27891343.77</v>
       </c>
       <c r="H28" s="5">
-        <v>44.29</v>
+        <v>46.03</v>
       </c>
       <c r="I28" s="4">
-        <v>22293501.09</v>
+        <v>21751949.41</v>
       </c>
       <c r="J28" s="5">
-        <v>36.79</v>
+        <v>35.9</v>
       </c>
       <c r="K28" s="4">
-        <v>49129930.340000004</v>
+        <v>49643293.18</v>
       </c>
       <c r="L28" s="5">
-        <v>81.08</v>
+        <v>81.93</v>
       </c>
       <c r="M28" s="4">
-        <v>11465069.66</v>
+        <v>10951706.82</v>
       </c>
       <c r="N28" s="5">
-        <v>18.920000000000002</v>
+        <v>18.07</v>
       </c>
       <c r="O28" s="4">
-        <v>4885230.9400000004</v>
+        <v>4094449.1</v>
       </c>
       <c r="P28" s="5">
-        <v>8.06</v>
+        <v>6.76</v>
       </c>
       <c r="Q28" s="4">
-        <v>6579838.7199999997</v>
+        <v>6857257.7199999997</v>
       </c>
       <c r="R28" s="5">
-        <v>10.86</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+        <v>11.32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>17</v>
       </c>
@@ -20359,40 +20359,40 @@
         <v>37235000</v>
       </c>
       <c r="G29" s="8">
-        <v>16601351.6</v>
+        <v>16966626.120000001</v>
       </c>
       <c r="H29" s="9">
-        <v>44.59</v>
+        <v>45.57</v>
       </c>
       <c r="I29" s="8">
-        <v>14809523.52</v>
+        <v>14425034</v>
       </c>
       <c r="J29" s="9">
-        <v>39.770000000000003</v>
+        <v>38.74</v>
       </c>
       <c r="K29" s="8">
-        <v>31410875.120000001</v>
+        <v>31391660.120000001</v>
       </c>
       <c r="L29" s="9">
-        <v>84.36</v>
+        <v>84.31</v>
       </c>
       <c r="M29" s="8">
-        <v>5824124.8799999999</v>
+        <v>5843339.8799999999</v>
       </c>
       <c r="N29" s="9">
-        <v>15.64</v>
+        <v>15.69</v>
       </c>
       <c r="O29" s="8">
-        <v>1680000</v>
+        <v>1387200</v>
       </c>
       <c r="P29" s="9">
-        <v>4.51</v>
+        <v>3.73</v>
       </c>
       <c r="Q29" s="8">
-        <v>4144124.88</v>
+        <v>4456139.88</v>
       </c>
       <c r="R29" s="9">
-        <v>11.13</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -20421,22 +20421,22 @@
         <v>81.48</v>
       </c>
       <c r="I30" s="8">
-        <v>150000</v>
+        <v>151840</v>
       </c>
       <c r="J30" s="9">
-        <v>19.920000000000002</v>
+        <v>20.170000000000002</v>
       </c>
       <c r="K30" s="8">
-        <v>763450</v>
+        <v>765290</v>
       </c>
       <c r="L30" s="9">
-        <v>101.4</v>
+        <v>101.65</v>
       </c>
       <c r="M30" s="8">
-        <v>-10550</v>
+        <v>-12390</v>
       </c>
       <c r="N30" s="9">
-        <v>-1.4</v>
+        <v>-1.65</v>
       </c>
       <c r="O30" s="8">
         <v>0</v>
@@ -20445,10 +20445,10 @@
         <v>0</v>
       </c>
       <c r="Q30" s="8">
-        <v>-10550</v>
+        <v>-12390</v>
       </c>
       <c r="R30" s="9">
-        <v>-1.4</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -20477,22 +20477,22 @@
         <v>60.1</v>
       </c>
       <c r="I31" s="8">
-        <v>415098</v>
+        <v>459098</v>
       </c>
       <c r="J31" s="9">
-        <v>15.89</v>
+        <v>17.57</v>
       </c>
       <c r="K31" s="8">
-        <v>1985584.67</v>
+        <v>2029584.67</v>
       </c>
       <c r="L31" s="9">
-        <v>75.989999999999995</v>
+        <v>77.680000000000007</v>
       </c>
       <c r="M31" s="8">
-        <v>627329.32999999996</v>
+        <v>583329.32999999996</v>
       </c>
       <c r="N31" s="9">
-        <v>24.01</v>
+        <v>22.32</v>
       </c>
       <c r="O31" s="8">
         <v>0</v>
@@ -20501,10 +20501,10 @@
         <v>0</v>
       </c>
       <c r="Q31" s="8">
-        <v>627329.32999999996</v>
+        <v>583329.32999999996</v>
       </c>
       <c r="R31" s="9">
-        <v>24.01</v>
+        <v>22.32</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -20527,40 +20527,40 @@
         <v>9800000</v>
       </c>
       <c r="G32" s="8">
-        <v>4952297.9800000004</v>
+        <v>5245581.9800000004</v>
       </c>
       <c r="H32" s="9">
-        <v>50.53</v>
+        <v>53.53</v>
       </c>
       <c r="I32" s="8">
-        <v>1012522.97</v>
+        <v>1204232.97</v>
       </c>
       <c r="J32" s="9">
-        <v>10.33</v>
+        <v>12.29</v>
       </c>
       <c r="K32" s="8">
-        <v>5964820.9500000002</v>
+        <v>6449814.9500000002</v>
       </c>
       <c r="L32" s="9">
-        <v>60.87</v>
+        <v>65.81</v>
       </c>
       <c r="M32" s="8">
-        <v>3835179.05</v>
+        <v>3350185.05</v>
       </c>
       <c r="N32" s="9">
-        <v>39.130000000000003</v>
+        <v>34.19</v>
       </c>
       <c r="O32" s="8">
-        <v>2233789.54</v>
+        <v>1737551.54</v>
       </c>
       <c r="P32" s="9">
-        <v>22.79</v>
+        <v>17.73</v>
       </c>
       <c r="Q32" s="8">
-        <v>1601389.51</v>
+        <v>1612633.51</v>
       </c>
       <c r="R32" s="9">
-        <v>16.34</v>
+        <v>16.46</v>
       </c>
     </row>
     <row r="33" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -20583,34 +20583,34 @@
         <v>10194186</v>
       </c>
       <c r="G33" s="8">
-        <v>3098843</v>
+        <v>3495199</v>
       </c>
       <c r="H33" s="9">
-        <v>30.4</v>
+        <v>34.29</v>
       </c>
       <c r="I33" s="8">
-        <v>5906356.5999999996</v>
+        <v>5511744.4400000004</v>
       </c>
       <c r="J33" s="9">
-        <v>57.94</v>
+        <v>54.07</v>
       </c>
       <c r="K33" s="8">
-        <v>9005199.5999999996</v>
+        <v>9006943.4399999995</v>
       </c>
       <c r="L33" s="9">
-        <v>88.34</v>
+        <v>88.35</v>
       </c>
       <c r="M33" s="8">
-        <v>1188986.3999999999</v>
+        <v>1187242.56</v>
       </c>
       <c r="N33" s="9">
-        <v>11.66</v>
+        <v>11.65</v>
       </c>
       <c r="O33" s="8">
-        <v>971441.4</v>
+        <v>969697.56</v>
       </c>
       <c r="P33" s="9">
-        <v>9.5299999999999994</v>
+        <v>9.51</v>
       </c>
       <c r="Q33" s="8">
         <v>217545</v>
@@ -20637,40 +20637,40 @@
         <v>230702200</v>
       </c>
       <c r="G34" s="14">
-        <v>143284850.61000001</v>
+        <v>145743574.99000001</v>
       </c>
       <c r="H34" s="15">
-        <v>62.11</v>
+        <v>63.17</v>
       </c>
       <c r="I34" s="14">
-        <v>37050134.240000002</v>
+        <v>37387853.369999997</v>
       </c>
       <c r="J34" s="15">
-        <v>16.059999999999999</v>
+        <v>16.21</v>
       </c>
       <c r="K34" s="14">
-        <v>180334984.84999999</v>
+        <v>183131428.36000001</v>
       </c>
       <c r="L34" s="15">
-        <v>78.17</v>
+        <v>79.38</v>
       </c>
       <c r="M34" s="14">
-        <v>50367215.149999999</v>
+        <v>47570771.640000001</v>
       </c>
       <c r="N34" s="15">
-        <v>21.83</v>
+        <v>20.62</v>
       </c>
       <c r="O34" s="14">
-        <v>7831250.9100000001</v>
+        <v>6495994.0700000003</v>
       </c>
       <c r="P34" s="15">
-        <v>3.39</v>
+        <v>2.82</v>
       </c>
       <c r="Q34" s="14">
-        <v>42535964.240000002</v>
+        <v>41074777.57</v>
       </c>
       <c r="R34" s="15">
-        <v>18.440000000000001</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
@@ -20727,7 +20727,7 @@
         <v>54.44</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ht="105.6" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>279</v>
       </c>
@@ -20837,7 +20837,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>236</v>
       </c>
@@ -20947,7 +20947,7 @@
         <v>39.450000000000003</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="66" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
         <v>307</v>
       </c>
@@ -21021,43 +21021,43 @@
         <v>22528181.809999999</v>
       </c>
       <c r="G41" s="4">
-        <v>7768948.3799999999</v>
+        <v>8130268.7300000004</v>
       </c>
       <c r="H41" s="5">
-        <v>34.49</v>
+        <v>36.090000000000003</v>
       </c>
       <c r="I41" s="4">
-        <v>2310210.7200000002</v>
+        <v>2916754.97</v>
       </c>
       <c r="J41" s="5">
-        <v>10.25</v>
+        <v>12.95</v>
       </c>
       <c r="K41" s="4">
-        <v>10079159.1</v>
+        <v>11047023.699999999</v>
       </c>
       <c r="L41" s="5">
-        <v>44.74</v>
+        <v>49.04</v>
       </c>
       <c r="M41" s="4">
-        <v>12449022.710000001</v>
+        <v>11481158.109999999</v>
       </c>
       <c r="N41" s="5">
-        <v>55.26</v>
+        <v>50.96</v>
       </c>
       <c r="O41" s="4">
-        <v>2197593</v>
+        <v>1039093</v>
       </c>
       <c r="P41" s="5">
-        <v>9.75</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="Q41" s="4">
-        <v>10251429.710000001</v>
+        <v>10442065.109999999</v>
       </c>
       <c r="R41" s="5">
-        <v>45.5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" ht="66" x14ac:dyDescent="0.25">
+        <v>46.35</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
         <v>267</v>
       </c>
@@ -21077,40 +21077,40 @@
         <v>7768581.8099999996</v>
       </c>
       <c r="G42" s="8">
-        <v>4902612.9400000004</v>
+        <v>5163933.29</v>
       </c>
       <c r="H42" s="9">
-        <v>63.11</v>
+        <v>66.47</v>
       </c>
       <c r="I42" s="8">
-        <v>962602.16</v>
+        <v>1230546.4099999999</v>
       </c>
       <c r="J42" s="9">
-        <v>12.39</v>
+        <v>15.84</v>
       </c>
       <c r="K42" s="8">
-        <v>5865215.0999999996</v>
+        <v>6394479.7000000002</v>
       </c>
       <c r="L42" s="9">
-        <v>75.5</v>
+        <v>82.31</v>
       </c>
       <c r="M42" s="8">
-        <v>1903366.71</v>
+        <v>1374102.11</v>
       </c>
       <c r="N42" s="9">
-        <v>24.5</v>
+        <v>17.690000000000001</v>
       </c>
       <c r="O42" s="8">
-        <v>613445</v>
+        <v>114945</v>
       </c>
       <c r="P42" s="9">
-        <v>7.9</v>
+        <v>1.48</v>
       </c>
       <c r="Q42" s="8">
-        <v>1289921.71</v>
+        <v>1259157.1100000001</v>
       </c>
       <c r="R42" s="9">
-        <v>16.600000000000001</v>
+        <v>16.21</v>
       </c>
     </row>
     <row r="43" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
@@ -21133,43 +21133,43 @@
         <v>12554100</v>
       </c>
       <c r="G43" s="8">
-        <v>2866335.44</v>
+        <v>2966335.44</v>
       </c>
       <c r="H43" s="9">
-        <v>22.83</v>
+        <v>23.63</v>
       </c>
       <c r="I43" s="8">
-        <v>1192358.56</v>
+        <v>1530958.56</v>
       </c>
       <c r="J43" s="9">
-        <v>9.5</v>
+        <v>12.19</v>
       </c>
       <c r="K43" s="8">
-        <v>4058694</v>
+        <v>4497294</v>
       </c>
       <c r="L43" s="9">
-        <v>32.33</v>
+        <v>35.82</v>
       </c>
       <c r="M43" s="8">
-        <v>8495406</v>
+        <v>8056806</v>
       </c>
       <c r="N43" s="9">
-        <v>67.67</v>
+        <v>64.180000000000007</v>
       </c>
       <c r="O43" s="8">
-        <v>864148</v>
+        <v>564148</v>
       </c>
       <c r="P43" s="9">
-        <v>6.88</v>
+        <v>4.49</v>
       </c>
       <c r="Q43" s="8">
-        <v>7631258</v>
+        <v>7492658</v>
       </c>
       <c r="R43" s="9">
-        <v>60.79</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+        <v>59.68</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>541</v>
       </c>
@@ -21213,16 +21213,16 @@
         <v>92.96</v>
       </c>
       <c r="O44" s="8">
-        <v>720000</v>
+        <v>360000</v>
       </c>
       <c r="P44" s="9">
-        <v>32.65</v>
+        <v>16.32</v>
       </c>
       <c r="Q44" s="8">
-        <v>1330250</v>
+        <v>1690250</v>
       </c>
       <c r="R44" s="9">
-        <v>60.32</v>
+        <v>76.64</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
@@ -21279,7 +21279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>488</v>
       </c>
@@ -21353,43 +21353,43 @@
         <v>72788490.920000002</v>
       </c>
       <c r="G47" s="4">
-        <v>13108669.16</v>
+        <v>15783277.16</v>
       </c>
       <c r="H47" s="5">
-        <v>18.010000000000002</v>
+        <v>21.68</v>
       </c>
       <c r="I47" s="4">
-        <v>17460532.23</v>
+        <v>17920719.23</v>
       </c>
       <c r="J47" s="5">
-        <v>23.99</v>
+        <v>24.62</v>
       </c>
       <c r="K47" s="4">
-        <v>30569201.390000001</v>
+        <v>33703996.390000001</v>
       </c>
       <c r="L47" s="5">
-        <v>42</v>
+        <v>46.3</v>
       </c>
       <c r="M47" s="4">
-        <v>42219289.530000001</v>
+        <v>39084494.530000001</v>
       </c>
       <c r="N47" s="5">
-        <v>58</v>
+        <v>53.7</v>
       </c>
       <c r="O47" s="4">
-        <v>4473750</v>
+        <v>3642500</v>
       </c>
       <c r="P47" s="5">
-        <v>6.15</v>
+        <v>5</v>
       </c>
       <c r="Q47" s="4">
-        <v>37745539.530000001</v>
+        <v>35441994.530000001</v>
       </c>
       <c r="R47" s="5">
-        <v>51.86</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" ht="118.8" x14ac:dyDescent="0.25">
+        <v>48.69</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="145.19999999999999" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>248</v>
       </c>
@@ -21445,7 +21445,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" ht="118.8" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>260</v>
       </c>
@@ -21501,7 +21501,7 @@
         <v>99.98</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>299</v>
       </c>
@@ -21557,7 +21557,7 @@
         <v>90.15</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
         <v>317</v>
       </c>
@@ -21613,7 +21613,7 @@
         <v>22.96</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="132" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" ht="145.19999999999999" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>333</v>
       </c>
@@ -21633,43 +21633,43 @@
         <v>8926239.0199999996</v>
       </c>
       <c r="G52" s="8">
-        <v>1080387.78</v>
+        <v>1303585.78</v>
       </c>
       <c r="H52" s="9">
-        <v>12.1</v>
+        <v>14.6</v>
       </c>
       <c r="I52" s="8">
-        <v>5243008</v>
+        <v>7401905</v>
       </c>
       <c r="J52" s="9">
-        <v>58.74</v>
+        <v>82.92</v>
       </c>
       <c r="K52" s="8">
-        <v>6323395.7800000003</v>
+        <v>8705490.7799999993</v>
       </c>
       <c r="L52" s="9">
-        <v>70.84</v>
+        <v>97.53</v>
       </c>
       <c r="M52" s="8">
-        <v>2602843.2400000002</v>
+        <v>220748.24</v>
       </c>
       <c r="N52" s="9">
-        <v>29.16</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="O52" s="8">
-        <v>500000</v>
+        <v>15000</v>
       </c>
       <c r="P52" s="9">
-        <v>5.6</v>
+        <v>0.17</v>
       </c>
       <c r="Q52" s="8">
-        <v>2102843.2400000002</v>
+        <v>205748.24</v>
       </c>
       <c r="R52" s="9">
-        <v>23.56</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18" ht="66" x14ac:dyDescent="0.25">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
         <v>362</v>
       </c>
@@ -21725,7 +21725,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="66" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
         <v>390</v>
       </c>
@@ -21781,7 +21781,7 @@
         <v>-17.489999999999998</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>398</v>
       </c>
@@ -21801,43 +21801,43 @@
         <v>12829676.84</v>
       </c>
       <c r="G55" s="8">
-        <v>2672712.91</v>
+        <v>2673312.91</v>
       </c>
       <c r="H55" s="9">
-        <v>20.83</v>
+        <v>20.84</v>
       </c>
       <c r="I55" s="8">
-        <v>898161.56</v>
+        <v>1295901.56</v>
       </c>
       <c r="J55" s="9">
-        <v>7</v>
+        <v>10.1</v>
       </c>
       <c r="K55" s="8">
-        <v>3570874.47</v>
+        <v>3969214.47</v>
       </c>
       <c r="L55" s="9">
-        <v>27.83</v>
+        <v>30.94</v>
       </c>
       <c r="M55" s="8">
-        <v>9258802.3699999992</v>
+        <v>8860462.3699999992</v>
       </c>
       <c r="N55" s="9">
-        <v>72.17</v>
+        <v>69.06</v>
       </c>
       <c r="O55" s="8">
-        <v>200000</v>
+        <v>54000</v>
       </c>
       <c r="P55" s="9">
-        <v>1.56</v>
+        <v>0.42</v>
       </c>
       <c r="Q55" s="8">
-        <v>9058802.3699999992</v>
+        <v>8806462.3699999992</v>
       </c>
       <c r="R55" s="9">
-        <v>70.61</v>
-      </c>
-    </row>
-    <row r="56" spans="1:18" ht="118.8" x14ac:dyDescent="0.25">
+        <v>68.64</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" ht="145.19999999999999" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
         <v>422</v>
       </c>
@@ -21893,7 +21893,7 @@
         <v>53.06</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
         <v>460</v>
       </c>
@@ -22005,7 +22005,7 @@
         <v>-8.08</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
         <v>492</v>
       </c>
@@ -22025,28 +22025,28 @@
         <v>2528000</v>
       </c>
       <c r="G59" s="8">
-        <v>615729.84</v>
+        <v>666089.84</v>
       </c>
       <c r="H59" s="9">
-        <v>24.36</v>
+        <v>26.35</v>
       </c>
       <c r="I59" s="8">
-        <v>665560</v>
+        <v>768860</v>
       </c>
       <c r="J59" s="9">
-        <v>26.33</v>
+        <v>30.41</v>
       </c>
       <c r="K59" s="8">
-        <v>1281289.8400000001</v>
+        <v>1434949.84</v>
       </c>
       <c r="L59" s="9">
-        <v>50.68</v>
+        <v>56.76</v>
       </c>
       <c r="M59" s="8">
-        <v>1246710.1599999999</v>
+        <v>1093050.1599999999</v>
       </c>
       <c r="N59" s="9">
-        <v>49.32</v>
+        <v>43.24</v>
       </c>
       <c r="O59" s="8">
         <v>20000</v>
@@ -22055,13 +22055,13 @@
         <v>0.79</v>
       </c>
       <c r="Q59" s="8">
-        <v>1226710.1599999999</v>
+        <v>1073050.1599999999</v>
       </c>
       <c r="R59" s="9">
-        <v>48.52</v>
-      </c>
-    </row>
-    <row r="60" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
+        <v>42.45</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
         <v>508</v>
       </c>
@@ -22117,7 +22117,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" ht="105.6" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
         <v>523</v>
       </c>
@@ -22137,37 +22137,37 @@
         <v>19811100</v>
       </c>
       <c r="G61" s="8">
-        <v>12550</v>
+        <v>2413000</v>
       </c>
       <c r="H61" s="9">
-        <v>0.06</v>
+        <v>12.18</v>
       </c>
       <c r="I61" s="8">
-        <v>7348620</v>
+        <v>5148870</v>
       </c>
       <c r="J61" s="9">
-        <v>37.090000000000003</v>
+        <v>25.99</v>
       </c>
       <c r="K61" s="8">
-        <v>7361170</v>
+        <v>7561870</v>
       </c>
       <c r="L61" s="9">
-        <v>37.159999999999997</v>
+        <v>38.17</v>
       </c>
       <c r="M61" s="8">
-        <v>12449930</v>
+        <v>12249230</v>
       </c>
       <c r="N61" s="9">
-        <v>62.84</v>
+        <v>61.83</v>
       </c>
       <c r="O61" s="8">
-        <v>200250</v>
+        <v>0</v>
       </c>
       <c r="P61" s="9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="8">
-        <v>12249680</v>
+        <v>12249230</v>
       </c>
       <c r="R61" s="9">
         <v>61.83</v>
@@ -22191,40 +22191,40 @@
         <v>100622228.15000001</v>
       </c>
       <c r="G62" s="14">
-        <v>22946611.77</v>
+        <v>25982540.120000001</v>
       </c>
       <c r="H62" s="15">
-        <v>22.8</v>
+        <v>25.82</v>
       </c>
       <c r="I62" s="14">
-        <v>19851637.949999999</v>
+        <v>20918369.199999999</v>
       </c>
       <c r="J62" s="15">
-        <v>19.73</v>
+        <v>20.79</v>
       </c>
       <c r="K62" s="14">
-        <v>42798249.719999999</v>
+        <v>46900909.32</v>
       </c>
       <c r="L62" s="15">
-        <v>42.53</v>
+        <v>46.61</v>
       </c>
       <c r="M62" s="14">
-        <v>57823978.43</v>
+        <v>53721318.829999998</v>
       </c>
       <c r="N62" s="15">
-        <v>57.47</v>
+        <v>53.39</v>
       </c>
       <c r="O62" s="14">
-        <v>6671343</v>
+        <v>4681593</v>
       </c>
       <c r="P62" s="15">
-        <v>6.63</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="Q62" s="14">
-        <v>51152635.43</v>
+        <v>49039725.829999998</v>
       </c>
       <c r="R62" s="15">
-        <v>50.84</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
@@ -22245,40 +22245,40 @@
         <v>331324428.14999998</v>
       </c>
       <c r="G63" s="16">
-        <v>166231462.38</v>
+        <v>171726115.11000001</v>
       </c>
       <c r="H63" s="17">
-        <v>50.17</v>
+        <v>51.83</v>
       </c>
       <c r="I63" s="16">
-        <v>56901772.189999998</v>
+        <v>58306222.57</v>
       </c>
       <c r="J63" s="17">
-        <v>17.170000000000002</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="K63" s="16">
-        <v>223133234.56999999</v>
+        <v>230032337.68000001</v>
       </c>
       <c r="L63" s="17">
-        <v>67.349999999999994</v>
+        <v>69.430000000000007</v>
       </c>
       <c r="M63" s="16">
-        <v>108191193.58</v>
+        <v>101292090.47</v>
       </c>
       <c r="N63" s="17">
-        <v>32.65</v>
+        <v>30.57</v>
       </c>
       <c r="O63" s="16">
-        <v>14502593.91</v>
+        <v>11177587.07</v>
       </c>
       <c r="P63" s="17">
-        <v>4.38</v>
+        <v>3.37</v>
       </c>
       <c r="Q63" s="16">
-        <v>93688599.670000002</v>
+        <v>90114503.400000006</v>
       </c>
       <c r="R63" s="17">
-        <v>28.28</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
@@ -22463,40 +22463,40 @@
         <v>337490008.32999998</v>
       </c>
       <c r="G67" s="16">
-        <v>166231462.38</v>
+        <v>171726115.11000001</v>
       </c>
       <c r="H67" s="17">
-        <v>49.26</v>
+        <v>50.88</v>
       </c>
       <c r="I67" s="16">
-        <v>56901772.189999998</v>
+        <v>58306222.57</v>
       </c>
       <c r="J67" s="17">
-        <v>16.86</v>
+        <v>17.28</v>
       </c>
       <c r="K67" s="16">
-        <v>223133234.56999999</v>
+        <v>230032337.68000001</v>
       </c>
       <c r="L67" s="17">
-        <v>66.12</v>
+        <v>68.16</v>
       </c>
       <c r="M67" s="16">
-        <v>114356773.76000001</v>
+        <v>107457670.65000001</v>
       </c>
       <c r="N67" s="17">
-        <v>33.880000000000003</v>
+        <v>31.84</v>
       </c>
       <c r="O67" s="16">
-        <v>14502593.91</v>
+        <v>11177587.07</v>
       </c>
       <c r="P67" s="17">
-        <v>4.3</v>
+        <v>3.31</v>
       </c>
       <c r="Q67" s="16">
-        <v>99854179.849999994</v>
+        <v>96280083.579999998</v>
       </c>
       <c r="R67" s="17">
-        <v>29.59</v>
+        <v>28.53</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
@@ -22517,13 +22517,13 @@
         <v>4037940.24</v>
       </c>
       <c r="G68" s="4">
-        <v>555190.98</v>
+        <v>555191.18000000005</v>
       </c>
       <c r="H68" s="5">
         <v>13.75</v>
       </c>
       <c r="I68" s="4">
-        <v>158448.9</v>
+        <v>158448.70000000001</v>
       </c>
       <c r="J68" s="5">
         <v>3.92</v>
@@ -22573,13 +22573,13 @@
         <v>4037940.24</v>
       </c>
       <c r="G69" s="8">
-        <v>555190.98</v>
+        <v>555191.18000000005</v>
       </c>
       <c r="H69" s="9">
         <v>13.75</v>
       </c>
       <c r="I69" s="8">
-        <v>158448.9</v>
+        <v>158448.70000000001</v>
       </c>
       <c r="J69" s="9">
         <v>3.92</v>
@@ -22627,13 +22627,13 @@
         <v>4037940.24</v>
       </c>
       <c r="G70" s="14">
-        <v>555190.98</v>
+        <v>555191.18000000005</v>
       </c>
       <c r="H70" s="15">
         <v>13.75</v>
       </c>
       <c r="I70" s="14">
-        <v>158448.9</v>
+        <v>158448.70000000001</v>
       </c>
       <c r="J70" s="15">
         <v>3.92</v>
@@ -22681,40 +22681,40 @@
         <v>341527948.56999999</v>
       </c>
       <c r="G71" s="16">
-        <v>166786653.36000001</v>
+        <v>172281306.28999999</v>
       </c>
       <c r="H71" s="17">
-        <v>48.84</v>
+        <v>50.44</v>
       </c>
       <c r="I71" s="16">
-        <v>57060221.090000004</v>
+        <v>58464671.270000003</v>
       </c>
       <c r="J71" s="17">
-        <v>16.71</v>
+        <v>17.12</v>
       </c>
       <c r="K71" s="16">
-        <v>223846874.44999999</v>
+        <v>230745977.56</v>
       </c>
       <c r="L71" s="17">
-        <v>65.540000000000006</v>
+        <v>67.56</v>
       </c>
       <c r="M71" s="16">
-        <v>117681074.12</v>
+        <v>110781971.01000001</v>
       </c>
       <c r="N71" s="17">
-        <v>34.46</v>
+        <v>32.44</v>
       </c>
       <c r="O71" s="16">
-        <v>14508723.029999999</v>
+        <v>11183716.189999999</v>
       </c>
       <c r="P71" s="17">
-        <v>4.25</v>
+        <v>3.27</v>
       </c>
       <c r="Q71" s="16">
-        <v>103172351.09</v>
+        <v>99598254.819999993</v>
       </c>
       <c r="R71" s="17">
-        <v>30.21</v>
+        <v>29.16</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
@@ -22735,28 +22735,28 @@
         <v>1000000</v>
       </c>
       <c r="G72" s="19">
-        <v>730475.74</v>
+        <v>747825.74</v>
       </c>
       <c r="H72" s="20">
-        <v>73.05</v>
+        <v>74.78</v>
       </c>
       <c r="I72" s="19">
-        <v>194668</v>
+        <v>173268</v>
       </c>
       <c r="J72" s="20">
-        <v>19.47</v>
+        <v>17.329999999999998</v>
       </c>
       <c r="K72" s="19">
-        <v>925143.74</v>
+        <v>921093.74</v>
       </c>
       <c r="L72" s="20">
-        <v>92.51</v>
+        <v>92.11</v>
       </c>
       <c r="M72" s="19">
-        <v>74856.259999999995</v>
+        <v>78906.259999999995</v>
       </c>
       <c r="N72" s="20">
-        <v>7.49</v>
+        <v>7.89</v>
       </c>
       <c r="O72" s="19">
         <v>0</v>
@@ -22765,10 +22765,10 @@
         <v>0</v>
       </c>
       <c r="Q72" s="19">
-        <v>74856.259999999995</v>
+        <v>78906.259999999995</v>
       </c>
       <c r="R72" s="20">
-        <v>7.49</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
@@ -22795,22 +22795,22 @@
         <v>49.87</v>
       </c>
       <c r="I73" s="19">
-        <v>30120</v>
+        <v>67120</v>
       </c>
       <c r="J73" s="20">
-        <v>3.01</v>
+        <v>6.71</v>
       </c>
       <c r="K73" s="19">
-        <v>528839</v>
+        <v>565839</v>
       </c>
       <c r="L73" s="20">
-        <v>52.88</v>
+        <v>56.58</v>
       </c>
       <c r="M73" s="19">
-        <v>471161</v>
+        <v>434161</v>
       </c>
       <c r="N73" s="20">
-        <v>47.12</v>
+        <v>43.42</v>
       </c>
       <c r="O73" s="19">
         <v>0</v>
@@ -22819,10 +22819,10 @@
         <v>0</v>
       </c>
       <c r="Q73" s="19">
-        <v>471161</v>
+        <v>434161</v>
       </c>
       <c r="R73" s="20">
-        <v>47.12</v>
+        <v>43.42</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
@@ -22843,28 +22843,28 @@
         <v>12535870.93</v>
       </c>
       <c r="G74" s="19">
-        <v>7853161.0499999998</v>
+        <v>7954071.0499999998</v>
       </c>
       <c r="H74" s="20">
-        <v>62.65</v>
+        <v>63.45</v>
       </c>
       <c r="I74" s="19">
-        <v>1458883</v>
+        <v>1490838</v>
       </c>
       <c r="J74" s="20">
-        <v>11.64</v>
+        <v>11.89</v>
       </c>
       <c r="K74" s="19">
-        <v>9312044.0500000007</v>
+        <v>9444909.0500000007</v>
       </c>
       <c r="L74" s="20">
-        <v>74.28</v>
+        <v>75.34</v>
       </c>
       <c r="M74" s="19">
-        <v>3223826.88</v>
+        <v>3090961.88</v>
       </c>
       <c r="N74" s="20">
-        <v>25.72</v>
+        <v>24.66</v>
       </c>
       <c r="O74" s="19">
         <v>600</v>
@@ -22873,10 +22873,10 @@
         <v>0</v>
       </c>
       <c r="Q74" s="19">
-        <v>3223226.88</v>
+        <v>3090361.88</v>
       </c>
       <c r="R74" s="20">
-        <v>25.71</v>
+        <v>24.65</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
@@ -22897,28 +22897,28 @@
         <v>13373180.710000001</v>
       </c>
       <c r="G75" s="19">
-        <v>8448378.2899999991</v>
+        <v>8645198.2899999991</v>
       </c>
       <c r="H75" s="20">
-        <v>63.17</v>
+        <v>64.650000000000006</v>
       </c>
       <c r="I75" s="19">
-        <v>1227197</v>
+        <v>1319847</v>
       </c>
       <c r="J75" s="20">
-        <v>9.18</v>
+        <v>9.8699999999999992</v>
       </c>
       <c r="K75" s="19">
-        <v>9675575.2899999991</v>
+        <v>9965045.2899999991</v>
       </c>
       <c r="L75" s="20">
-        <v>72.349999999999994</v>
+        <v>74.52</v>
       </c>
       <c r="M75" s="19">
-        <v>3697605.42</v>
+        <v>3408135.42</v>
       </c>
       <c r="N75" s="20">
-        <v>27.65</v>
+        <v>25.48</v>
       </c>
       <c r="O75" s="19">
         <v>80000</v>
@@ -22927,10 +22927,10 @@
         <v>0.6</v>
       </c>
       <c r="Q75" s="19">
-        <v>3617605.42</v>
+        <v>3328135.42</v>
       </c>
       <c r="R75" s="20">
-        <v>27.05</v>
+        <v>24.89</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
@@ -22951,28 +22951,28 @@
         <v>14776703.779999999</v>
       </c>
       <c r="G76" s="19">
-        <v>10460737.039999999</v>
+        <v>10695662.039999999</v>
       </c>
       <c r="H76" s="20">
-        <v>70.790000000000006</v>
+        <v>72.38</v>
       </c>
       <c r="I76" s="19">
-        <v>1536732.35</v>
+        <v>1695207.67</v>
       </c>
       <c r="J76" s="20">
-        <v>10.4</v>
+        <v>11.47</v>
       </c>
       <c r="K76" s="19">
-        <v>11997469.390000001</v>
+        <v>12390869.710000001</v>
       </c>
       <c r="L76" s="20">
-        <v>81.19</v>
+        <v>83.85</v>
       </c>
       <c r="M76" s="19">
-        <v>2779234.39</v>
+        <v>2385834.0699999998</v>
       </c>
       <c r="N76" s="20">
-        <v>18.809999999999999</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="O76" s="19">
         <v>144801.1</v>
@@ -22981,10 +22981,10 @@
         <v>0.98</v>
       </c>
       <c r="Q76" s="19">
-        <v>2634433.29</v>
+        <v>2241032.9700000002</v>
       </c>
       <c r="R76" s="20">
-        <v>17.829999999999998</v>
+        <v>15.17</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
@@ -23005,40 +23005,40 @@
         <v>30348181.809999999</v>
       </c>
       <c r="G77" s="19">
-        <v>13127477.98</v>
+        <v>13607627.33</v>
       </c>
       <c r="H77" s="20">
-        <v>43.26</v>
+        <v>44.84</v>
       </c>
       <c r="I77" s="19">
-        <v>2913869.72</v>
+        <v>3465243.97</v>
       </c>
       <c r="J77" s="20">
-        <v>9.6</v>
+        <v>11.42</v>
       </c>
       <c r="K77" s="19">
-        <v>16041347.699999999</v>
+        <v>17072871.300000001</v>
       </c>
       <c r="L77" s="20">
-        <v>52.86</v>
+        <v>56.26</v>
       </c>
       <c r="M77" s="19">
-        <v>14306834.109999999</v>
+        <v>13275310.51</v>
       </c>
       <c r="N77" s="20">
-        <v>47.14</v>
+        <v>43.74</v>
       </c>
       <c r="O77" s="19">
-        <v>2747593</v>
+        <v>1589093</v>
       </c>
       <c r="P77" s="20">
-        <v>9.0500000000000007</v>
+        <v>5.24</v>
       </c>
       <c r="Q77" s="19">
-        <v>11559241.109999999</v>
+        <v>11686217.51</v>
       </c>
       <c r="R77" s="20">
-        <v>38.090000000000003</v>
+        <v>38.51</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
@@ -23059,40 +23059,40 @@
         <v>13420000</v>
       </c>
       <c r="G78" s="19">
-        <v>9438778.7699999996</v>
+        <v>10131340.029999999</v>
       </c>
       <c r="H78" s="20">
-        <v>70.33</v>
+        <v>75.489999999999995</v>
       </c>
       <c r="I78" s="19">
-        <v>1649419.41</v>
+        <v>1802304</v>
       </c>
       <c r="J78" s="20">
-        <v>12.29</v>
+        <v>13.43</v>
       </c>
       <c r="K78" s="19">
-        <v>11088198.18</v>
+        <v>11933644.029999999</v>
       </c>
       <c r="L78" s="20">
-        <v>82.62</v>
+        <v>88.92</v>
       </c>
       <c r="M78" s="19">
-        <v>2331801.8199999998</v>
+        <v>1486355.97</v>
       </c>
       <c r="N78" s="20">
-        <v>17.38</v>
+        <v>11.08</v>
       </c>
       <c r="O78" s="19">
-        <v>275743</v>
+        <v>248743</v>
       </c>
       <c r="P78" s="20">
-        <v>2.0499999999999998</v>
+        <v>1.85</v>
       </c>
       <c r="Q78" s="19">
-        <v>2056058.82</v>
+        <v>1237612.97</v>
       </c>
       <c r="R78" s="20">
-        <v>15.32</v>
+        <v>9.2200000000000006</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
@@ -23113,37 +23113,37 @@
         <v>111264940.23999999</v>
       </c>
       <c r="G79" s="19">
-        <v>74583456.650000006</v>
+        <v>74625871.450000003</v>
       </c>
       <c r="H79" s="20">
-        <v>67.03</v>
+        <v>67.069999999999993</v>
       </c>
       <c r="I79" s="19">
-        <v>7714876.6200000001</v>
+        <v>8045277.3200000003</v>
       </c>
       <c r="J79" s="20">
-        <v>6.93</v>
+        <v>7.23</v>
       </c>
       <c r="K79" s="19">
-        <v>82298333.269999996</v>
+        <v>82671148.769999996</v>
       </c>
       <c r="L79" s="20">
-        <v>73.97</v>
+        <v>74.3</v>
       </c>
       <c r="M79" s="19">
-        <v>28966606.969999999</v>
+        <v>28593791.469999999</v>
       </c>
       <c r="N79" s="20">
-        <v>26.03</v>
+        <v>25.7</v>
       </c>
       <c r="O79" s="19">
-        <v>1647004.99</v>
+        <v>1282004.99</v>
       </c>
       <c r="P79" s="20">
-        <v>1.48</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="Q79" s="19">
-        <v>27319601.98</v>
+        <v>27311786.48</v>
       </c>
       <c r="R79" s="20">
         <v>24.55</v>
@@ -23173,28 +23173,28 @@
         <v>39.909999999999997</v>
       </c>
       <c r="I80" s="19">
-        <v>580421.67000000004</v>
+        <v>732896.67</v>
       </c>
       <c r="J80" s="20">
-        <v>13.62</v>
+        <v>17.2</v>
       </c>
       <c r="K80" s="19">
-        <v>2280792.1</v>
+        <v>2433267.1</v>
       </c>
       <c r="L80" s="20">
-        <v>53.54</v>
+        <v>57.12</v>
       </c>
       <c r="M80" s="19">
-        <v>1979207.9</v>
+        <v>1826732.9</v>
       </c>
       <c r="N80" s="20">
-        <v>46.46</v>
+        <v>42.88</v>
       </c>
       <c r="O80" s="19">
-        <v>254000</v>
+        <v>101525</v>
       </c>
       <c r="P80" s="20">
-        <v>5.96</v>
+        <v>2.38</v>
       </c>
       <c r="Q80" s="19">
         <v>1725207.9</v>
@@ -23221,40 +23221,40 @@
         <v>139549071.09999999</v>
       </c>
       <c r="G81" s="19">
-        <v>39945098.409999996</v>
+        <v>43674620.93</v>
       </c>
       <c r="H81" s="20">
-        <v>28.62</v>
+        <v>31.3</v>
       </c>
       <c r="I81" s="19">
-        <v>39754033.32</v>
+        <v>39672668.640000001</v>
       </c>
       <c r="J81" s="20">
-        <v>28.49</v>
+        <v>28.43</v>
       </c>
       <c r="K81" s="19">
-        <v>79699131.730000004</v>
+        <v>83347289.569999993</v>
       </c>
       <c r="L81" s="20">
-        <v>57.11</v>
+        <v>59.73</v>
       </c>
       <c r="M81" s="19">
-        <v>59849939.369999997</v>
+        <v>56201781.530000001</v>
       </c>
       <c r="N81" s="20">
-        <v>42.89</v>
+        <v>40.270000000000003</v>
       </c>
       <c r="O81" s="19">
-        <v>9358980.9399999995</v>
+        <v>7736949.0999999996</v>
       </c>
       <c r="P81" s="20">
-        <v>6.71</v>
+        <v>5.54</v>
       </c>
       <c r="Q81" s="19">
-        <v>50490958.43</v>
+        <v>48464832.43</v>
       </c>
       <c r="R81" s="20">
-        <v>36.18</v>
+        <v>34.729999999999997</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
@@ -23275,40 +23275,40 @@
         <v>341527948.56999999</v>
       </c>
       <c r="G82" s="19">
-        <v>166786653.36000001</v>
+        <v>172281306.28999999</v>
       </c>
       <c r="H82" s="20">
-        <v>48.84</v>
+        <v>50.44</v>
       </c>
       <c r="I82" s="19">
-        <v>57060221.090000004</v>
+        <v>58464671.270000003</v>
       </c>
       <c r="J82" s="20">
-        <v>16.71</v>
+        <v>17.12</v>
       </c>
       <c r="K82" s="19">
-        <v>223846874.44999999</v>
+        <v>230745977.56</v>
       </c>
       <c r="L82" s="20">
-        <v>65.540000000000006</v>
+        <v>67.56</v>
       </c>
       <c r="M82" s="19">
-        <v>117681074.12</v>
+        <v>110781971.01000001</v>
       </c>
       <c r="N82" s="20">
-        <v>34.46</v>
+        <v>32.44</v>
       </c>
       <c r="O82" s="19">
-        <v>14508723.029999999</v>
+        <v>11183716.189999999</v>
       </c>
       <c r="P82" s="20">
-        <v>4.25</v>
+        <v>3.27</v>
       </c>
       <c r="Q82" s="19">
-        <v>103172351.09</v>
+        <v>99598254.819999993</v>
       </c>
       <c r="R82" s="20">
-        <v>30.21</v>
+        <v>29.16</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">

--- a/Budget-Report.xlsx
+++ b/Budget-Report.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orathai\Desktop\Claude Cowork\Budget Report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orathai\Desktop\Claude Cowork\Budget Report\00 BK\25690724\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79997101-4733-4573-B2C8-4A4965B404F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78D84BE-B2D7-49D9-BC08-C5802B47FFAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1766,7 +1766,7 @@
     <t>รวมทั้งสิ้น</t>
   </si>
   <si>
-    <t>( ข้อมูลระบบ ณ วันที่ 18 กรกฎาคม 2569 เวลา 23:14:00 น.)</t>
+    <t>( ข้อมูลระบบ ณ วันที่ 24 กรกฎาคม 2569 เวลา 22:07:44 น.)</t>
   </si>
   <si>
     <t>สำนัก/โครงการ</t>
@@ -1805,7 +1805,7 @@
     <t>สย.</t>
   </si>
   <si>
-    <t>( ข้อมูลระบบ ณ วันที่ 18 กรกฎาคม 2569 เวลา 23:15:27 น.)</t>
+    <t>( ข้อมูลระบบ ณ วันที่ 24 กรกฎาคม 2569 เวลา 22:09:22 น.)</t>
   </si>
 </sst>
 </file>
@@ -1930,7 +1930,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -2012,6 +2012,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2320,23 +2323,23 @@
   <dimension ref="A1:R307"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.69921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.8984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.19921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.8984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.8984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.3984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.8984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.09765625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.8984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.796875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.09765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24" style="28" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.69921875" style="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.8984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.796875" style="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.8984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.3984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.796875" style="28" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.3984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.8984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.3984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.8984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.09765625" style="28" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.796875" style="28" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.8984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.796875" style="28" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.09765625" style="28" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.796875" style="28"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -2350,7 +2353,7 @@
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
         <v>1</v>
       </c>
@@ -2458,40 +2461,40 @@
         <v>46540814</v>
       </c>
       <c r="G6" s="4">
-        <v>22132140.120000001</v>
+        <v>23670542.129999999</v>
       </c>
       <c r="H6" s="5">
-        <v>47.55</v>
+        <v>50.86</v>
       </c>
       <c r="I6" s="4">
-        <v>15887933.67</v>
+        <v>14870696.67</v>
       </c>
       <c r="J6" s="5">
-        <v>34.14</v>
+        <v>31.95</v>
       </c>
       <c r="K6" s="4">
-        <v>38020073.789999999</v>
+        <v>38541238.799999997</v>
       </c>
       <c r="L6" s="5">
-        <v>81.69</v>
+        <v>82.81</v>
       </c>
       <c r="M6" s="4">
-        <v>8520740.2100000009</v>
+        <v>7999575.2000000002</v>
       </c>
       <c r="N6" s="5">
-        <v>18.309999999999999</v>
+        <v>17.190000000000001</v>
       </c>
       <c r="O6" s="4">
-        <v>1305921.6000000001</v>
+        <v>1317521.6000000001</v>
       </c>
       <c r="P6" s="5">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="Q6" s="4">
-        <v>7214818.6100000003</v>
+        <v>6682053.5999999996</v>
       </c>
       <c r="R6" s="5">
-        <v>15.5</v>
+        <v>14.36</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -2514,40 +2517,40 @@
         <v>37235000</v>
       </c>
       <c r="G7" s="8">
-        <v>17247376.120000001</v>
+        <v>18197586.129999999</v>
       </c>
       <c r="H7" s="9">
-        <v>46.32</v>
+        <v>48.87</v>
       </c>
       <c r="I7" s="8">
-        <v>14058219</v>
+        <v>13653617</v>
       </c>
       <c r="J7" s="9">
-        <v>37.76</v>
+        <v>36.67</v>
       </c>
       <c r="K7" s="8">
-        <v>31305595.120000001</v>
+        <v>31851203.129999999</v>
       </c>
       <c r="L7" s="9">
-        <v>84.08</v>
+        <v>85.54</v>
       </c>
       <c r="M7" s="8">
-        <v>5929404.8799999999</v>
+        <v>5383796.8700000001</v>
       </c>
       <c r="N7" s="9">
-        <v>15.92</v>
+        <v>14.46</v>
       </c>
       <c r="O7" s="8">
-        <v>1027200</v>
+        <v>1038800</v>
       </c>
       <c r="P7" s="9">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="Q7" s="8">
-        <v>4902204.88</v>
+        <v>4344996.87</v>
       </c>
       <c r="R7" s="9">
-        <v>13.17</v>
+        <v>11.67</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -2576,34 +2579,34 @@
         <v>58.65</v>
       </c>
       <c r="I8" s="12">
-        <v>38300</v>
+        <v>143800</v>
       </c>
       <c r="J8" s="13">
-        <v>1.0900000000000001</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="K8" s="12">
-        <v>2091206.41</v>
+        <v>2196706.41</v>
       </c>
       <c r="L8" s="13">
-        <v>59.75</v>
+        <v>62.76</v>
       </c>
       <c r="M8" s="12">
-        <v>1408793.59</v>
+        <v>1303293.5900000001</v>
       </c>
       <c r="N8" s="13">
-        <v>40.25</v>
+        <v>37.24</v>
       </c>
       <c r="O8" s="12">
-        <v>0</v>
+        <v>21600</v>
       </c>
       <c r="P8" s="13">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="Q8" s="12">
-        <v>1408793.59</v>
+        <v>1281693.5900000001</v>
       </c>
       <c r="R8" s="13">
-        <v>40.25</v>
+        <v>36.619999999999997</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
@@ -2626,28 +2629,28 @@
         <v>698900</v>
       </c>
       <c r="G9" s="12">
-        <v>431671</v>
+        <v>436021</v>
       </c>
       <c r="H9" s="13">
-        <v>61.76</v>
+        <v>62.39</v>
       </c>
       <c r="I9" s="12">
-        <v>12900</v>
+        <v>378100</v>
       </c>
       <c r="J9" s="13">
-        <v>1.85</v>
+        <v>54.1</v>
       </c>
       <c r="K9" s="12">
-        <v>444571</v>
+        <v>814121</v>
       </c>
       <c r="L9" s="13">
-        <v>63.61</v>
+        <v>116.49</v>
       </c>
       <c r="M9" s="12">
-        <v>254329</v>
+        <v>-115221</v>
       </c>
       <c r="N9" s="13">
-        <v>36.39</v>
+        <v>-16.489999999999998</v>
       </c>
       <c r="O9" s="12">
         <v>0</v>
@@ -2656,10 +2659,10 @@
         <v>0</v>
       </c>
       <c r="Q9" s="12">
-        <v>254329</v>
+        <v>-115221</v>
       </c>
       <c r="R9" s="13">
-        <v>36.39</v>
+        <v>-16.489999999999998</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -2682,28 +2685,28 @@
         <v>700000</v>
       </c>
       <c r="G10" s="12">
-        <v>372481</v>
+        <v>861652</v>
       </c>
       <c r="H10" s="13">
-        <v>53.21</v>
+        <v>123.09</v>
       </c>
       <c r="I10" s="12">
-        <v>463606</v>
+        <v>0</v>
       </c>
       <c r="J10" s="13">
-        <v>66.23</v>
+        <v>0</v>
       </c>
       <c r="K10" s="12">
-        <v>836087</v>
+        <v>861652</v>
       </c>
       <c r="L10" s="13">
-        <v>119.44</v>
+        <v>123.09</v>
       </c>
       <c r="M10" s="12">
-        <v>-136087</v>
+        <v>-161652</v>
       </c>
       <c r="N10" s="13">
-        <v>-19.440000000000001</v>
+        <v>-23.09</v>
       </c>
       <c r="O10" s="12">
         <v>2200</v>
@@ -2712,10 +2715,10 @@
         <v>0.31</v>
       </c>
       <c r="Q10" s="12">
-        <v>-138287</v>
+        <v>-163852</v>
       </c>
       <c r="R10" s="13">
-        <v>-19.760000000000002</v>
+        <v>-23.41</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
@@ -2738,40 +2741,40 @@
         <v>3030982</v>
       </c>
       <c r="G11" s="12">
-        <v>885582</v>
+        <v>897882</v>
       </c>
       <c r="H11" s="13">
-        <v>29.22</v>
+        <v>29.62</v>
       </c>
       <c r="I11" s="12">
-        <v>2114550</v>
+        <v>2100000</v>
       </c>
       <c r="J11" s="13">
-        <v>69.760000000000005</v>
+        <v>69.28</v>
       </c>
       <c r="K11" s="12">
-        <v>3000132</v>
+        <v>2997882</v>
       </c>
       <c r="L11" s="13">
-        <v>98.98</v>
+        <v>98.91</v>
       </c>
       <c r="M11" s="12">
-        <v>30850</v>
+        <v>33100</v>
       </c>
       <c r="N11" s="13">
-        <v>1.02</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="O11" s="12">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="P11" s="13">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="12">
-        <v>20850</v>
+        <v>33100</v>
       </c>
       <c r="R11" s="13">
-        <v>0.69</v>
+        <v>1.0900000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -2794,28 +2797,28 @@
         <v>20000000</v>
       </c>
       <c r="G12" s="12">
-        <v>8082555</v>
+        <v>8085155</v>
       </c>
       <c r="H12" s="13">
-        <v>40.409999999999997</v>
+        <v>40.43</v>
       </c>
       <c r="I12" s="12">
-        <v>9963500</v>
+        <v>9981250</v>
       </c>
       <c r="J12" s="13">
-        <v>49.82</v>
+        <v>49.91</v>
       </c>
       <c r="K12" s="12">
-        <v>18046055</v>
+        <v>18066405</v>
       </c>
       <c r="L12" s="13">
-        <v>90.23</v>
+        <v>90.33</v>
       </c>
       <c r="M12" s="12">
-        <v>1953945</v>
+        <v>1933595</v>
       </c>
       <c r="N12" s="13">
-        <v>9.77</v>
+        <v>9.67</v>
       </c>
       <c r="O12" s="12">
         <v>1000000</v>
@@ -2824,10 +2827,10 @@
         <v>5</v>
       </c>
       <c r="Q12" s="12">
-        <v>953945</v>
+        <v>933595</v>
       </c>
       <c r="R12" s="13">
-        <v>4.7699999999999996</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -2850,28 +2853,28 @@
         <v>800000</v>
       </c>
       <c r="G13" s="12">
-        <v>624979.5</v>
+        <v>655055.5</v>
       </c>
       <c r="H13" s="13">
-        <v>78.12</v>
+        <v>81.88</v>
       </c>
       <c r="I13" s="12">
-        <v>119518</v>
+        <v>102562</v>
       </c>
       <c r="J13" s="13">
-        <v>14.94</v>
+        <v>12.82</v>
       </c>
       <c r="K13" s="12">
-        <v>744497.5</v>
+        <v>757617.5</v>
       </c>
       <c r="L13" s="13">
-        <v>93.06</v>
+        <v>94.7</v>
       </c>
       <c r="M13" s="12">
-        <v>55502.5</v>
+        <v>42382.5</v>
       </c>
       <c r="N13" s="13">
-        <v>6.94</v>
+        <v>5.3</v>
       </c>
       <c r="O13" s="12">
         <v>0</v>
@@ -2880,10 +2883,10 @@
         <v>0</v>
       </c>
       <c r="Q13" s="12">
-        <v>55502.5</v>
+        <v>42382.5</v>
       </c>
       <c r="R13" s="13">
-        <v>6.94</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -2962,28 +2965,28 @@
         <v>2706831.37</v>
       </c>
       <c r="G15" s="12">
-        <v>1889126.56</v>
+        <v>2143024.5699999998</v>
       </c>
       <c r="H15" s="13">
-        <v>69.790000000000006</v>
+        <v>79.17</v>
       </c>
       <c r="I15" s="12">
-        <v>238800</v>
+        <v>3500</v>
       </c>
       <c r="J15" s="13">
-        <v>8.82</v>
+        <v>0.13</v>
       </c>
       <c r="K15" s="12">
-        <v>2127926.56</v>
+        <v>2146524.5699999998</v>
       </c>
       <c r="L15" s="13">
-        <v>78.61</v>
+        <v>79.3</v>
       </c>
       <c r="M15" s="12">
-        <v>578904.81000000006</v>
+        <v>560306.80000000005</v>
       </c>
       <c r="N15" s="13">
-        <v>21.39</v>
+        <v>20.7</v>
       </c>
       <c r="O15" s="12">
         <v>5000</v>
@@ -2992,10 +2995,10 @@
         <v>0.18</v>
       </c>
       <c r="Q15" s="12">
-        <v>573904.81000000006</v>
+        <v>555306.80000000005</v>
       </c>
       <c r="R15" s="13">
-        <v>21.2</v>
+        <v>20.52</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -3130,28 +3133,28 @@
         <v>1148575.97</v>
       </c>
       <c r="G18" s="12">
-        <v>237141</v>
+        <v>284136</v>
       </c>
       <c r="H18" s="13">
-        <v>20.65</v>
+        <v>24.74</v>
       </c>
       <c r="I18" s="12">
-        <v>63740</v>
+        <v>32100</v>
       </c>
       <c r="J18" s="13">
-        <v>5.55</v>
+        <v>2.79</v>
       </c>
       <c r="K18" s="12">
-        <v>300881</v>
+        <v>316236</v>
       </c>
       <c r="L18" s="13">
-        <v>26.2</v>
+        <v>27.53</v>
       </c>
       <c r="M18" s="12">
-        <v>847694.97</v>
+        <v>832339.97</v>
       </c>
       <c r="N18" s="13">
-        <v>73.8</v>
+        <v>72.47</v>
       </c>
       <c r="O18" s="12">
         <v>0</v>
@@ -3160,10 +3163,10 @@
         <v>0</v>
       </c>
       <c r="Q18" s="12">
-        <v>847694.97</v>
+        <v>832339.97</v>
       </c>
       <c r="R18" s="13">
-        <v>73.8</v>
+        <v>72.47</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
@@ -3186,28 +3189,28 @@
         <v>591000</v>
       </c>
       <c r="G19" s="12">
-        <v>452095</v>
+        <v>562915</v>
       </c>
       <c r="H19" s="13">
-        <v>76.5</v>
+        <v>95.25</v>
       </c>
       <c r="I19" s="12">
-        <v>198000</v>
+        <v>40000</v>
       </c>
       <c r="J19" s="13">
-        <v>33.5</v>
+        <v>6.77</v>
       </c>
       <c r="K19" s="12">
-        <v>650095</v>
+        <v>602915</v>
       </c>
       <c r="L19" s="13">
-        <v>110</v>
+        <v>102.02</v>
       </c>
       <c r="M19" s="12">
-        <v>-59095</v>
+        <v>-11915</v>
       </c>
       <c r="N19" s="13">
-        <v>-10</v>
+        <v>-2.02</v>
       </c>
       <c r="O19" s="12">
         <v>0</v>
@@ -3216,10 +3219,10 @@
         <v>0</v>
       </c>
       <c r="Q19" s="12">
-        <v>-59095</v>
+        <v>-11915</v>
       </c>
       <c r="R19" s="13">
-        <v>-10</v>
+        <v>-2.02</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -3304,22 +3307,22 @@
         <v>100</v>
       </c>
       <c r="I21" s="12">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="J21" s="13">
-        <v>0</v>
+        <v>15.55</v>
       </c>
       <c r="K21" s="12">
-        <v>173666</v>
+        <v>200666</v>
       </c>
       <c r="L21" s="13">
-        <v>100</v>
+        <v>115.55</v>
       </c>
       <c r="M21" s="12">
-        <v>0</v>
+        <v>-27000</v>
       </c>
       <c r="N21" s="13">
-        <v>0</v>
+        <v>-15.55</v>
       </c>
       <c r="O21" s="12">
         <v>0</v>
@@ -3328,10 +3331,10 @@
         <v>0</v>
       </c>
       <c r="Q21" s="12">
-        <v>0</v>
+        <v>-27000</v>
       </c>
       <c r="R21" s="13">
-        <v>0</v>
+        <v>-15.55</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -3690,28 +3693,28 @@
         <v>4260000</v>
       </c>
       <c r="G28" s="8">
-        <v>1700370.43</v>
+        <v>2025237.43</v>
       </c>
       <c r="H28" s="9">
-        <v>39.909999999999997</v>
+        <v>47.54</v>
       </c>
       <c r="I28" s="8">
-        <v>848371.67</v>
+        <v>502696.67</v>
       </c>
       <c r="J28" s="9">
-        <v>19.91</v>
+        <v>11.8</v>
       </c>
       <c r="K28" s="8">
-        <v>2548742.1</v>
+        <v>2527934.1</v>
       </c>
       <c r="L28" s="9">
-        <v>59.83</v>
+        <v>59.34</v>
       </c>
       <c r="M28" s="8">
-        <v>1711257.9</v>
+        <v>1732065.9</v>
       </c>
       <c r="N28" s="9">
-        <v>40.17</v>
+        <v>40.659999999999997</v>
       </c>
       <c r="O28" s="8">
         <v>274000</v>
@@ -3720,10 +3723,10 @@
         <v>6.43</v>
       </c>
       <c r="Q28" s="8">
-        <v>1437257.9</v>
+        <v>1458065.9</v>
       </c>
       <c r="R28" s="9">
-        <v>33.74</v>
+        <v>34.229999999999997</v>
       </c>
     </row>
     <row r="29" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
@@ -3746,16 +3749,16 @@
         <v>1820000</v>
       </c>
       <c r="G29" s="12">
-        <v>737089.87</v>
+        <v>767964.87</v>
       </c>
       <c r="H29" s="13">
-        <v>40.5</v>
+        <v>42.2</v>
       </c>
       <c r="I29" s="12">
-        <v>397605</v>
+        <v>366730</v>
       </c>
       <c r="J29" s="13">
-        <v>21.85</v>
+        <v>20.149999999999999</v>
       </c>
       <c r="K29" s="12">
         <v>1134694.8700000001</v>
@@ -3802,16 +3805,16 @@
         <v>1000000</v>
       </c>
       <c r="G30" s="12">
-        <v>119365.8</v>
+        <v>149365.79999999999</v>
       </c>
       <c r="H30" s="13">
-        <v>11.94</v>
+        <v>14.94</v>
       </c>
       <c r="I30" s="12">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="J30" s="13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K30" s="12">
         <v>149365.79999999999</v>
@@ -3858,16 +3861,16 @@
         <v>1000000</v>
       </c>
       <c r="G31" s="12">
-        <v>11400</v>
+        <v>13000</v>
       </c>
       <c r="H31" s="13">
-        <v>1.1399999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="I31" s="12">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="J31" s="13">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="K31" s="12">
         <v>13000</v>
@@ -3914,28 +3917,28 @@
         <v>400000</v>
       </c>
       <c r="G32" s="12">
-        <v>777194.76</v>
+        <v>1039586.76</v>
       </c>
       <c r="H32" s="13">
-        <v>194.3</v>
+        <v>259.89999999999998</v>
       </c>
       <c r="I32" s="12">
-        <v>417896.67</v>
+        <v>134696.67000000001</v>
       </c>
       <c r="J32" s="13">
-        <v>104.47</v>
+        <v>33.67</v>
       </c>
       <c r="K32" s="12">
-        <v>1195091.43</v>
+        <v>1174283.43</v>
       </c>
       <c r="L32" s="13">
-        <v>298.77</v>
+        <v>293.57</v>
       </c>
       <c r="M32" s="12">
-        <v>-795091.43</v>
+        <v>-774283.43</v>
       </c>
       <c r="N32" s="13">
-        <v>-198.77</v>
+        <v>-193.57</v>
       </c>
       <c r="O32" s="12">
         <v>2000</v>
@@ -3944,10 +3947,10 @@
         <v>0.5</v>
       </c>
       <c r="Q32" s="12">
-        <v>-797091.43</v>
+        <v>-776283.43</v>
       </c>
       <c r="R32" s="13">
-        <v>-199.27</v>
+        <v>-194.07</v>
       </c>
     </row>
     <row r="33" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -4032,22 +4035,22 @@
         <v>81.48</v>
       </c>
       <c r="I34" s="8">
-        <v>151840</v>
+        <v>150000</v>
       </c>
       <c r="J34" s="9">
-        <v>20.170000000000002</v>
+        <v>19.920000000000002</v>
       </c>
       <c r="K34" s="8">
-        <v>765290</v>
+        <v>763450</v>
       </c>
       <c r="L34" s="9">
-        <v>101.65</v>
+        <v>101.4</v>
       </c>
       <c r="M34" s="8">
-        <v>-12390</v>
+        <v>-10550</v>
       </c>
       <c r="N34" s="9">
-        <v>-1.65</v>
+        <v>-1.4</v>
       </c>
       <c r="O34" s="8">
         <v>0</v>
@@ -4056,10 +4059,10 @@
         <v>0</v>
       </c>
       <c r="Q34" s="8">
-        <v>-12390</v>
+        <v>-10550</v>
       </c>
       <c r="R34" s="9">
-        <v>-1.65</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -4088,22 +4091,22 @@
         <v>81.48</v>
       </c>
       <c r="I35" s="12">
-        <v>151840</v>
+        <v>150000</v>
       </c>
       <c r="J35" s="13">
-        <v>20.170000000000002</v>
+        <v>19.920000000000002</v>
       </c>
       <c r="K35" s="12">
-        <v>765290</v>
+        <v>763450</v>
       </c>
       <c r="L35" s="13">
-        <v>101.65</v>
+        <v>101.4</v>
       </c>
       <c r="M35" s="12">
-        <v>-12390</v>
+        <v>-10550</v>
       </c>
       <c r="N35" s="13">
-        <v>-1.65</v>
+        <v>-1.4</v>
       </c>
       <c r="O35" s="12">
         <v>0</v>
@@ -4112,10 +4115,10 @@
         <v>0</v>
       </c>
       <c r="Q35" s="12">
-        <v>-12390</v>
+        <v>-10550</v>
       </c>
       <c r="R35" s="13">
-        <v>-1.65</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="36" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -4138,28 +4141,28 @@
         <v>500000</v>
       </c>
       <c r="G36" s="8">
-        <v>357667.9</v>
+        <v>471112.9</v>
       </c>
       <c r="H36" s="9">
-        <v>71.53</v>
+        <v>94.22</v>
       </c>
       <c r="I36" s="8">
-        <v>116245</v>
+        <v>2600</v>
       </c>
       <c r="J36" s="9">
-        <v>23.25</v>
+        <v>0.52</v>
       </c>
       <c r="K36" s="8">
-        <v>473912.9</v>
+        <v>473712.9</v>
       </c>
       <c r="L36" s="9">
-        <v>94.78</v>
+        <v>94.74</v>
       </c>
       <c r="M36" s="8">
-        <v>26087.1</v>
+        <v>26287.1</v>
       </c>
       <c r="N36" s="9">
-        <v>5.22</v>
+        <v>5.26</v>
       </c>
       <c r="O36" s="8">
         <v>4721.6000000000004</v>
@@ -4168,10 +4171,10 @@
         <v>0.94</v>
       </c>
       <c r="Q36" s="8">
-        <v>21365.5</v>
+        <v>21565.5</v>
       </c>
       <c r="R36" s="9">
-        <v>4.2699999999999996</v>
+        <v>4.3099999999999996</v>
       </c>
     </row>
     <row r="37" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -4194,28 +4197,28 @@
         <v>400000</v>
       </c>
       <c r="G37" s="12">
-        <v>295879.90000000002</v>
+        <v>373324.9</v>
       </c>
       <c r="H37" s="13">
-        <v>73.97</v>
+        <v>93.33</v>
       </c>
       <c r="I37" s="12">
-        <v>78245</v>
+        <v>2600</v>
       </c>
       <c r="J37" s="13">
-        <v>19.559999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="K37" s="12">
-        <v>374124.9</v>
+        <v>375924.9</v>
       </c>
       <c r="L37" s="13">
-        <v>93.53</v>
+        <v>93.98</v>
       </c>
       <c r="M37" s="12">
-        <v>25875.1</v>
+        <v>24075.1</v>
       </c>
       <c r="N37" s="13">
-        <v>6.47</v>
+        <v>6.02</v>
       </c>
       <c r="O37" s="12">
         <v>4721.6000000000004</v>
@@ -4224,10 +4227,10 @@
         <v>1.18</v>
       </c>
       <c r="Q37" s="12">
-        <v>21153.5</v>
+        <v>19353.5</v>
       </c>
       <c r="R37" s="13">
-        <v>5.29</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="38" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -4250,28 +4253,28 @@
         <v>100000</v>
       </c>
       <c r="G38" s="12">
-        <v>61788</v>
+        <v>97788</v>
       </c>
       <c r="H38" s="13">
-        <v>61.79</v>
+        <v>97.79</v>
       </c>
       <c r="I38" s="12">
-        <v>38000</v>
+        <v>0</v>
       </c>
       <c r="J38" s="13">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K38" s="12">
-        <v>99788</v>
+        <v>97788</v>
       </c>
       <c r="L38" s="13">
-        <v>99.79</v>
+        <v>97.79</v>
       </c>
       <c r="M38" s="12">
-        <v>212</v>
+        <v>2212</v>
       </c>
       <c r="N38" s="13">
-        <v>0.21</v>
+        <v>2.21</v>
       </c>
       <c r="O38" s="12">
         <v>0</v>
@@ -4280,10 +4283,10 @@
         <v>0</v>
       </c>
       <c r="Q38" s="12">
-        <v>212</v>
+        <v>2212</v>
       </c>
       <c r="R38" s="13">
-        <v>0.21</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="39" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -4474,28 +4477,28 @@
         <v>2612914</v>
       </c>
       <c r="G42" s="8">
-        <v>1574926.67</v>
+        <v>1724806.67</v>
       </c>
       <c r="H42" s="9">
-        <v>60.27</v>
+        <v>66.010000000000005</v>
       </c>
       <c r="I42" s="8">
-        <v>436258</v>
+        <v>284783</v>
       </c>
       <c r="J42" s="9">
-        <v>16.7</v>
+        <v>10.9</v>
       </c>
       <c r="K42" s="8">
-        <v>2011184.67</v>
+        <v>2009589.67</v>
       </c>
       <c r="L42" s="9">
-        <v>76.97</v>
+        <v>76.91</v>
       </c>
       <c r="M42" s="8">
-        <v>601729.32999999996</v>
+        <v>603324.32999999996</v>
       </c>
       <c r="N42" s="9">
-        <v>23.03</v>
+        <v>23.09</v>
       </c>
       <c r="O42" s="8">
         <v>0</v>
@@ -4504,10 +4507,10 @@
         <v>0</v>
       </c>
       <c r="Q42" s="8">
-        <v>601729.32999999996</v>
+        <v>603324.32999999996</v>
       </c>
       <c r="R42" s="9">
-        <v>23.03</v>
+        <v>23.09</v>
       </c>
     </row>
     <row r="43" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -4642,16 +4645,16 @@
         <v>1878000</v>
       </c>
       <c r="G45" s="12">
-        <v>1319879.67</v>
+        <v>1445754.67</v>
       </c>
       <c r="H45" s="13">
-        <v>70.28</v>
+        <v>76.98</v>
       </c>
       <c r="I45" s="12">
-        <v>377655</v>
+        <v>251780</v>
       </c>
       <c r="J45" s="13">
-        <v>20.11</v>
+        <v>13.41</v>
       </c>
       <c r="K45" s="12">
         <v>1697534.67</v>
@@ -4698,28 +4701,28 @@
         <v>208400</v>
       </c>
       <c r="G46" s="12">
-        <v>123910</v>
+        <v>147915</v>
       </c>
       <c r="H46" s="13">
-        <v>59.46</v>
+        <v>70.98</v>
       </c>
       <c r="I46" s="12">
-        <v>25600</v>
+        <v>0</v>
       </c>
       <c r="J46" s="13">
-        <v>12.28</v>
+        <v>0</v>
       </c>
       <c r="K46" s="12">
-        <v>149510</v>
+        <v>147915</v>
       </c>
       <c r="L46" s="13">
-        <v>71.739999999999995</v>
+        <v>70.98</v>
       </c>
       <c r="M46" s="12">
-        <v>58890</v>
+        <v>60485</v>
       </c>
       <c r="N46" s="13">
-        <v>28.26</v>
+        <v>29.02</v>
       </c>
       <c r="O46" s="12">
         <v>0</v>
@@ -4728,10 +4731,10 @@
         <v>0</v>
       </c>
       <c r="Q46" s="12">
-        <v>58890</v>
+        <v>60485</v>
       </c>
       <c r="R46" s="13">
-        <v>28.26</v>
+        <v>29.02</v>
       </c>
     </row>
     <row r="47" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -4754,40 +4757,40 @@
         <v>54940200</v>
       </c>
       <c r="G47" s="4">
-        <v>39099135.880000003</v>
+        <v>39899903.969999999</v>
       </c>
       <c r="H47" s="5">
-        <v>71.17</v>
+        <v>72.62</v>
       </c>
       <c r="I47" s="4">
-        <v>6941870.6699999999</v>
+        <v>6393068.6699999999</v>
       </c>
       <c r="J47" s="5">
-        <v>12.64</v>
+        <v>11.64</v>
       </c>
       <c r="K47" s="4">
-        <v>46041006.549999997</v>
+        <v>46292972.640000001</v>
       </c>
       <c r="L47" s="5">
-        <v>83.8</v>
+        <v>84.26</v>
       </c>
       <c r="M47" s="4">
-        <v>8899193.4499999993</v>
+        <v>8647227.3599999994</v>
       </c>
       <c r="N47" s="5">
-        <v>16.2</v>
+        <v>15.74</v>
       </c>
       <c r="O47" s="4">
-        <v>1149422.5</v>
+        <v>1155422.5</v>
       </c>
       <c r="P47" s="5">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="Q47" s="4">
-        <v>7749770.9500000002</v>
+        <v>7491804.8600000003</v>
       </c>
       <c r="R47" s="5">
-        <v>14.11</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -4810,28 +4813,28 @@
         <v>11340200</v>
       </c>
       <c r="G48" s="8">
-        <v>8590524.9600000009</v>
+        <v>8648491.9600000009</v>
       </c>
       <c r="H48" s="9">
-        <v>75.75</v>
+        <v>76.260000000000005</v>
       </c>
       <c r="I48" s="8">
-        <v>1646572.67</v>
+        <v>1643220.67</v>
       </c>
       <c r="J48" s="9">
-        <v>14.52</v>
+        <v>14.49</v>
       </c>
       <c r="K48" s="8">
-        <v>10237097.630000001</v>
+        <v>10291712.630000001</v>
       </c>
       <c r="L48" s="9">
-        <v>90.27</v>
+        <v>90.75</v>
       </c>
       <c r="M48" s="8">
-        <v>1103102.3700000001</v>
+        <v>1048487.37</v>
       </c>
       <c r="N48" s="9">
-        <v>9.73</v>
+        <v>9.25</v>
       </c>
       <c r="O48" s="8">
         <v>140079.5</v>
@@ -4840,10 +4843,10 @@
         <v>1.24</v>
       </c>
       <c r="Q48" s="8">
-        <v>963022.87</v>
+        <v>908407.87</v>
       </c>
       <c r="R48" s="9">
-        <v>8.49</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="49" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -4866,28 +4869,28 @@
         <v>1300000</v>
       </c>
       <c r="G49" s="12">
-        <v>944625.5</v>
+        <v>919630.5</v>
       </c>
       <c r="H49" s="13">
-        <v>72.66</v>
+        <v>70.739999999999995</v>
       </c>
       <c r="I49" s="12">
-        <v>410990</v>
+        <v>457005</v>
       </c>
       <c r="J49" s="13">
-        <v>31.61</v>
+        <v>35.15</v>
       </c>
       <c r="K49" s="12">
-        <v>1355615.5</v>
+        <v>1376635.5</v>
       </c>
       <c r="L49" s="13">
-        <v>104.28</v>
+        <v>105.9</v>
       </c>
       <c r="M49" s="12">
-        <v>-55615.5</v>
+        <v>-76635.5</v>
       </c>
       <c r="N49" s="13">
-        <v>-4.28</v>
+        <v>-5.9</v>
       </c>
       <c r="O49" s="12">
         <v>90000</v>
@@ -4896,10 +4899,10 @@
         <v>6.92</v>
       </c>
       <c r="Q49" s="12">
-        <v>-145615.5</v>
+        <v>-166635.5</v>
       </c>
       <c r="R49" s="13">
-        <v>-11.2</v>
+        <v>-12.82</v>
       </c>
     </row>
     <row r="50" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -4978,28 +4981,28 @@
         <v>4320000</v>
       </c>
       <c r="G51" s="12">
-        <v>2682709.7000000002</v>
+        <v>2771671.7</v>
       </c>
       <c r="H51" s="13">
-        <v>62.1</v>
+        <v>64.16</v>
       </c>
       <c r="I51" s="12">
-        <v>734802.67</v>
+        <v>652925.67000000004</v>
       </c>
       <c r="J51" s="13">
-        <v>17.010000000000002</v>
+        <v>15.11</v>
       </c>
       <c r="K51" s="12">
-        <v>3417512.37</v>
+        <v>3424597.37</v>
       </c>
       <c r="L51" s="13">
-        <v>79.11</v>
+        <v>79.27</v>
       </c>
       <c r="M51" s="12">
-        <v>902487.63</v>
+        <v>895402.63</v>
       </c>
       <c r="N51" s="13">
-        <v>20.89</v>
+        <v>20.73</v>
       </c>
       <c r="O51" s="12">
         <v>0</v>
@@ -5008,10 +5011,10 @@
         <v>0</v>
       </c>
       <c r="Q51" s="12">
-        <v>902487.63</v>
+        <v>895402.63</v>
       </c>
       <c r="R51" s="13">
-        <v>20.89</v>
+        <v>20.73</v>
       </c>
     </row>
     <row r="52" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -5034,28 +5037,28 @@
         <v>2020200</v>
       </c>
       <c r="G52" s="12">
-        <v>1737956</v>
+        <v>1731956</v>
       </c>
       <c r="H52" s="13">
-        <v>86.03</v>
+        <v>85.73</v>
       </c>
       <c r="I52" s="12">
-        <v>183980</v>
+        <v>216490</v>
       </c>
       <c r="J52" s="13">
-        <v>9.11</v>
+        <v>10.72</v>
       </c>
       <c r="K52" s="12">
-        <v>1921936</v>
+        <v>1948446</v>
       </c>
       <c r="L52" s="13">
-        <v>95.14</v>
+        <v>96.45</v>
       </c>
       <c r="M52" s="12">
-        <v>98264</v>
+        <v>71754</v>
       </c>
       <c r="N52" s="13">
-        <v>4.8600000000000003</v>
+        <v>3.55</v>
       </c>
       <c r="O52" s="12">
         <v>20079.5</v>
@@ -5064,10 +5067,10 @@
         <v>0.99</v>
       </c>
       <c r="Q52" s="12">
-        <v>78184.5</v>
+        <v>51674.5</v>
       </c>
       <c r="R52" s="13">
-        <v>3.87</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="53" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -5146,28 +5149,28 @@
         <v>13420000</v>
       </c>
       <c r="G54" s="8">
-        <v>9985540.0299999993</v>
+        <v>10753868.42</v>
       </c>
       <c r="H54" s="9">
-        <v>74.41</v>
+        <v>80.13</v>
       </c>
       <c r="I54" s="8">
-        <v>1778104</v>
+        <v>926886</v>
       </c>
       <c r="J54" s="9">
-        <v>13.25</v>
+        <v>6.91</v>
       </c>
       <c r="K54" s="8">
-        <v>11763644.029999999</v>
+        <v>11680754.42</v>
       </c>
       <c r="L54" s="9">
-        <v>87.66</v>
+        <v>87.04</v>
       </c>
       <c r="M54" s="8">
-        <v>1656355.97</v>
+        <v>1739245.58</v>
       </c>
       <c r="N54" s="9">
-        <v>12.34</v>
+        <v>12.96</v>
       </c>
       <c r="O54" s="8">
         <v>378743</v>
@@ -5176,10 +5179,10 @@
         <v>2.82</v>
       </c>
       <c r="Q54" s="8">
-        <v>1277612.97</v>
+        <v>1360502.58</v>
       </c>
       <c r="R54" s="9">
-        <v>9.52</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="55" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -5258,28 +5261,28 @@
         <v>2700000</v>
       </c>
       <c r="G56" s="12">
-        <v>1916310.35</v>
+        <v>2022285.35</v>
       </c>
       <c r="H56" s="13">
-        <v>70.97</v>
+        <v>74.900000000000006</v>
       </c>
       <c r="I56" s="12">
-        <v>241954</v>
+        <v>157786</v>
       </c>
       <c r="J56" s="13">
-        <v>8.9600000000000009</v>
+        <v>5.84</v>
       </c>
       <c r="K56" s="12">
-        <v>2158264.35</v>
+        <v>2180071.35</v>
       </c>
       <c r="L56" s="13">
-        <v>79.94</v>
+        <v>80.739999999999995</v>
       </c>
       <c r="M56" s="12">
-        <v>541735.65</v>
+        <v>519928.65</v>
       </c>
       <c r="N56" s="13">
-        <v>20.059999999999999</v>
+        <v>19.260000000000002</v>
       </c>
       <c r="O56" s="12">
         <v>263000</v>
@@ -5288,10 +5291,10 @@
         <v>9.74</v>
       </c>
       <c r="Q56" s="12">
-        <v>278735.65000000002</v>
+        <v>256928.65</v>
       </c>
       <c r="R56" s="13">
-        <v>10.32</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="57" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -5314,28 +5317,28 @@
         <v>3400000</v>
       </c>
       <c r="G57" s="12">
-        <v>2336168.41</v>
+        <v>2417705.41</v>
       </c>
       <c r="H57" s="13">
-        <v>68.709999999999994</v>
+        <v>71.11</v>
       </c>
       <c r="I57" s="12">
-        <v>351450</v>
+        <v>268150</v>
       </c>
       <c r="J57" s="13">
-        <v>10.34</v>
+        <v>7.89</v>
       </c>
       <c r="K57" s="12">
-        <v>2687618.41</v>
+        <v>2685855.41</v>
       </c>
       <c r="L57" s="13">
-        <v>79.05</v>
+        <v>79</v>
       </c>
       <c r="M57" s="12">
-        <v>712381.59</v>
+        <v>714144.59</v>
       </c>
       <c r="N57" s="13">
-        <v>20.95</v>
+        <v>21</v>
       </c>
       <c r="O57" s="12">
         <v>0</v>
@@ -5344,10 +5347,10 @@
         <v>0</v>
       </c>
       <c r="Q57" s="12">
-        <v>712381.59</v>
+        <v>714144.59</v>
       </c>
       <c r="R57" s="13">
-        <v>20.95</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -5538,28 +5541,28 @@
         <v>2600000</v>
       </c>
       <c r="G61" s="12">
-        <v>1641234.22</v>
+        <v>2222050.61</v>
       </c>
       <c r="H61" s="13">
-        <v>63.12</v>
+        <v>85.46</v>
       </c>
       <c r="I61" s="12">
-        <v>684700</v>
+        <v>950</v>
       </c>
       <c r="J61" s="13">
-        <v>26.33</v>
+        <v>0.04</v>
       </c>
       <c r="K61" s="12">
-        <v>2325934.2200000002</v>
+        <v>2223000.61</v>
       </c>
       <c r="L61" s="13">
-        <v>89.46</v>
+        <v>85.5</v>
       </c>
       <c r="M61" s="12">
-        <v>274065.78000000003</v>
+        <v>376999.39</v>
       </c>
       <c r="N61" s="13">
-        <v>10.54</v>
+        <v>14.5</v>
       </c>
       <c r="O61" s="12">
         <v>115743</v>
@@ -5568,10 +5571,10 @@
         <v>4.45</v>
       </c>
       <c r="Q61" s="12">
-        <v>158322.78</v>
+        <v>261256.39</v>
       </c>
       <c r="R61" s="13">
-        <v>6.09</v>
+        <v>10.050000000000001</v>
       </c>
     </row>
     <row r="62" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -5762,40 +5765,40 @@
         <v>11720000</v>
       </c>
       <c r="G65" s="8">
-        <v>7582346</v>
+        <v>7901987</v>
       </c>
       <c r="H65" s="9">
-        <v>64.7</v>
+        <v>67.42</v>
       </c>
       <c r="I65" s="8">
-        <v>1861278</v>
+        <v>1671535</v>
       </c>
       <c r="J65" s="9">
-        <v>15.88</v>
+        <v>14.26</v>
       </c>
       <c r="K65" s="8">
-        <v>9443624</v>
+        <v>9573522</v>
       </c>
       <c r="L65" s="9">
-        <v>80.58</v>
+        <v>81.69</v>
       </c>
       <c r="M65" s="8">
-        <v>2276376</v>
+        <v>2146478</v>
       </c>
       <c r="N65" s="9">
-        <v>19.420000000000002</v>
+        <v>18.309999999999999</v>
       </c>
       <c r="O65" s="8">
-        <v>600</v>
+        <v>30600</v>
       </c>
       <c r="P65" s="9">
-        <v>0.01</v>
+        <v>0.26</v>
       </c>
       <c r="Q65" s="8">
-        <v>2275776</v>
+        <v>2115878</v>
       </c>
       <c r="R65" s="9">
-        <v>19.420000000000002</v>
+        <v>18.05</v>
       </c>
     </row>
     <row r="66" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -5874,40 +5877,40 @@
         <v>1775000</v>
       </c>
       <c r="G67" s="12">
-        <v>608047</v>
+        <v>649252</v>
       </c>
       <c r="H67" s="13">
-        <v>34.26</v>
+        <v>36.58</v>
       </c>
       <c r="I67" s="12">
-        <v>41205</v>
+        <v>106000</v>
       </c>
       <c r="J67" s="13">
-        <v>2.3199999999999998</v>
+        <v>5.97</v>
       </c>
       <c r="K67" s="12">
-        <v>649252</v>
+        <v>755252</v>
       </c>
       <c r="L67" s="13">
-        <v>36.58</v>
+        <v>42.55</v>
       </c>
       <c r="M67" s="12">
-        <v>1125748</v>
+        <v>1019748</v>
       </c>
       <c r="N67" s="13">
-        <v>63.42</v>
+        <v>57.45</v>
       </c>
       <c r="O67" s="12">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="P67" s="13">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q67" s="12">
-        <v>1125748</v>
+        <v>989748</v>
       </c>
       <c r="R67" s="13">
-        <v>63.42</v>
+        <v>55.76</v>
       </c>
     </row>
     <row r="68" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -5930,28 +5933,28 @@
         <v>2820000</v>
       </c>
       <c r="G68" s="12">
-        <v>1874599</v>
+        <v>2120447</v>
       </c>
       <c r="H68" s="13">
-        <v>66.48</v>
+        <v>75.19</v>
       </c>
       <c r="I68" s="12">
-        <v>655544</v>
+        <v>433594</v>
       </c>
       <c r="J68" s="13">
-        <v>23.25</v>
+        <v>15.38</v>
       </c>
       <c r="K68" s="12">
-        <v>2530143</v>
+        <v>2554041</v>
       </c>
       <c r="L68" s="13">
-        <v>89.72</v>
+        <v>90.57</v>
       </c>
       <c r="M68" s="12">
-        <v>289857</v>
+        <v>265959</v>
       </c>
       <c r="N68" s="13">
-        <v>10.28</v>
+        <v>9.43</v>
       </c>
       <c r="O68" s="12">
         <v>600</v>
@@ -5960,10 +5963,10 @@
         <v>0.02</v>
       </c>
       <c r="Q68" s="12">
-        <v>289257</v>
+        <v>265359</v>
       </c>
       <c r="R68" s="13">
-        <v>10.26</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="69" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -6042,16 +6045,16 @@
         <v>4061000</v>
       </c>
       <c r="G70" s="12">
-        <v>2293140</v>
+        <v>2325728</v>
       </c>
       <c r="H70" s="13">
-        <v>56.47</v>
+        <v>57.27</v>
       </c>
       <c r="I70" s="12">
-        <v>863754</v>
+        <v>831166</v>
       </c>
       <c r="J70" s="13">
-        <v>21.27</v>
+        <v>20.47</v>
       </c>
       <c r="K70" s="12">
         <v>3156894</v>
@@ -6098,40 +6101,40 @@
         <v>10640000</v>
       </c>
       <c r="G71" s="8">
-        <v>7787344.29</v>
+        <v>7550908.29</v>
       </c>
       <c r="H71" s="9">
-        <v>73.19</v>
+        <v>70.97</v>
       </c>
       <c r="I71" s="8">
-        <v>1033047</v>
+        <v>1108133</v>
       </c>
       <c r="J71" s="9">
-        <v>9.7100000000000009</v>
+        <v>10.41</v>
       </c>
       <c r="K71" s="8">
-        <v>8820391.2899999991</v>
+        <v>8659041.2899999991</v>
       </c>
       <c r="L71" s="9">
-        <v>82.9</v>
+        <v>81.38</v>
       </c>
       <c r="M71" s="8">
-        <v>1819608.71</v>
+        <v>1980958.71</v>
       </c>
       <c r="N71" s="9">
-        <v>17.100000000000001</v>
+        <v>18.62</v>
       </c>
       <c r="O71" s="8">
-        <v>80000</v>
+        <v>56000</v>
       </c>
       <c r="P71" s="9">
-        <v>0.75</v>
+        <v>0.53</v>
       </c>
       <c r="Q71" s="8">
-        <v>1739608.71</v>
+        <v>1924958.71</v>
       </c>
       <c r="R71" s="9">
-        <v>16.350000000000001</v>
+        <v>18.09</v>
       </c>
     </row>
     <row r="72" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -6154,28 +6157,28 @@
         <v>1140000</v>
       </c>
       <c r="G72" s="12">
-        <v>773074.22</v>
+        <v>781824.22</v>
       </c>
       <c r="H72" s="13">
-        <v>67.81</v>
+        <v>68.58</v>
       </c>
       <c r="I72" s="12">
-        <v>37810</v>
+        <v>30910</v>
       </c>
       <c r="J72" s="13">
-        <v>3.32</v>
+        <v>2.71</v>
       </c>
       <c r="K72" s="12">
-        <v>810884.22</v>
+        <v>812734.22</v>
       </c>
       <c r="L72" s="13">
-        <v>71.13</v>
+        <v>71.290000000000006</v>
       </c>
       <c r="M72" s="12">
-        <v>329115.78000000003</v>
+        <v>327265.78000000003</v>
       </c>
       <c r="N72" s="13">
-        <v>28.87</v>
+        <v>28.71</v>
       </c>
       <c r="O72" s="12">
         <v>0</v>
@@ -6184,10 +6187,10 @@
         <v>0</v>
       </c>
       <c r="Q72" s="12">
-        <v>329115.78000000003</v>
+        <v>327265.78000000003</v>
       </c>
       <c r="R72" s="13">
-        <v>28.87</v>
+        <v>28.71</v>
       </c>
     </row>
     <row r="73" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -6272,28 +6275,28 @@
         <v>62.06</v>
       </c>
       <c r="I74" s="12">
-        <v>236300</v>
+        <v>260300</v>
       </c>
       <c r="J74" s="13">
-        <v>33.76</v>
+        <v>37.19</v>
       </c>
       <c r="K74" s="12">
-        <v>670711</v>
+        <v>694711</v>
       </c>
       <c r="L74" s="13">
-        <v>95.82</v>
+        <v>99.24</v>
       </c>
       <c r="M74" s="12">
-        <v>29289</v>
+        <v>5289</v>
       </c>
       <c r="N74" s="13">
-        <v>4.18</v>
+        <v>0.76</v>
       </c>
       <c r="O74" s="12">
-        <v>30000</v>
+        <v>6000</v>
       </c>
       <c r="P74" s="13">
-        <v>4.29</v>
+        <v>0.86</v>
       </c>
       <c r="Q74" s="12">
         <v>-711</v>
@@ -6378,28 +6381,28 @@
         <v>3300000</v>
       </c>
       <c r="G76" s="12">
-        <v>2067973.6</v>
+        <v>1808287.6</v>
       </c>
       <c r="H76" s="13">
-        <v>62.67</v>
+        <v>54.8</v>
       </c>
       <c r="I76" s="12">
-        <v>375897</v>
+        <v>455783</v>
       </c>
       <c r="J76" s="13">
-        <v>11.39</v>
+        <v>13.81</v>
       </c>
       <c r="K76" s="12">
-        <v>2443870.6</v>
+        <v>2264070.6</v>
       </c>
       <c r="L76" s="13">
-        <v>74.06</v>
+        <v>68.61</v>
       </c>
       <c r="M76" s="12">
-        <v>856129.4</v>
+        <v>1035929.4</v>
       </c>
       <c r="N76" s="13">
-        <v>25.94</v>
+        <v>31.39</v>
       </c>
       <c r="O76" s="12">
         <v>0</v>
@@ -6408,10 +6411,10 @@
         <v>0</v>
       </c>
       <c r="Q76" s="12">
-        <v>856129.4</v>
+        <v>1035929.4</v>
       </c>
       <c r="R76" s="13">
-        <v>25.94</v>
+        <v>31.39</v>
       </c>
     </row>
     <row r="77" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -6490,28 +6493,28 @@
         <v>500000</v>
       </c>
       <c r="G78" s="12">
-        <v>274150</v>
+        <v>288650</v>
       </c>
       <c r="H78" s="13">
-        <v>54.83</v>
+        <v>57.73</v>
       </c>
       <c r="I78" s="12">
-        <v>172900</v>
+        <v>151000</v>
       </c>
       <c r="J78" s="13">
-        <v>34.58</v>
+        <v>30.2</v>
       </c>
       <c r="K78" s="12">
-        <v>447050</v>
+        <v>439650</v>
       </c>
       <c r="L78" s="13">
-        <v>89.41</v>
+        <v>87.93</v>
       </c>
       <c r="M78" s="12">
-        <v>52950</v>
+        <v>60350</v>
       </c>
       <c r="N78" s="13">
-        <v>10.59</v>
+        <v>12.07</v>
       </c>
       <c r="O78" s="12">
         <v>50000</v>
@@ -6520,10 +6523,10 @@
         <v>10</v>
       </c>
       <c r="Q78" s="12">
-        <v>2950</v>
+        <v>10350</v>
       </c>
       <c r="R78" s="13">
-        <v>0.59</v>
+        <v>2.0699999999999998</v>
       </c>
     </row>
     <row r="79" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -6602,28 +6605,28 @@
         <v>7820000</v>
       </c>
       <c r="G80" s="8">
-        <v>5153380.5999999996</v>
+        <v>5044648.3</v>
       </c>
       <c r="H80" s="9">
-        <v>65.900000000000006</v>
+        <v>64.510000000000005</v>
       </c>
       <c r="I80" s="8">
-        <v>622869</v>
+        <v>1043294</v>
       </c>
       <c r="J80" s="9">
-        <v>7.97</v>
+        <v>13.34</v>
       </c>
       <c r="K80" s="8">
-        <v>5776249.5999999996</v>
+        <v>6087942.2999999998</v>
       </c>
       <c r="L80" s="9">
-        <v>73.87</v>
+        <v>77.849999999999994</v>
       </c>
       <c r="M80" s="8">
-        <v>2043750.3999999999</v>
+        <v>1732057.7</v>
       </c>
       <c r="N80" s="9">
-        <v>26.13</v>
+        <v>22.15</v>
       </c>
       <c r="O80" s="8">
         <v>550000</v>
@@ -6632,10 +6635,10 @@
         <v>7.03</v>
       </c>
       <c r="Q80" s="8">
-        <v>1493750.4</v>
+        <v>1182057.7</v>
       </c>
       <c r="R80" s="9">
-        <v>19.100000000000001</v>
+        <v>15.12</v>
       </c>
     </row>
     <row r="81" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -6720,22 +6723,22 @@
         <v>115.56</v>
       </c>
       <c r="I82" s="12">
-        <v>281350</v>
+        <v>189750</v>
       </c>
       <c r="J82" s="13">
-        <v>23.45</v>
+        <v>15.81</v>
       </c>
       <c r="K82" s="12">
-        <v>1668064</v>
+        <v>1576464</v>
       </c>
       <c r="L82" s="13">
-        <v>139.01</v>
+        <v>131.37</v>
       </c>
       <c r="M82" s="12">
-        <v>-468064</v>
+        <v>-376464</v>
       </c>
       <c r="N82" s="13">
-        <v>-39.01</v>
+        <v>-31.37</v>
       </c>
       <c r="O82" s="12">
         <v>0</v>
@@ -6744,10 +6747,10 @@
         <v>0</v>
       </c>
       <c r="Q82" s="12">
-        <v>-468064</v>
+        <v>-376464</v>
       </c>
       <c r="R82" s="13">
-        <v>-39.01</v>
+        <v>-31.37</v>
       </c>
     </row>
     <row r="83" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -6826,28 +6829,28 @@
         <v>3000000</v>
       </c>
       <c r="G84" s="12">
-        <v>2329481.2999999998</v>
+        <v>2220749</v>
       </c>
       <c r="H84" s="13">
-        <v>77.650000000000006</v>
+        <v>74.02</v>
       </c>
       <c r="I84" s="12">
-        <v>287319</v>
+        <v>195544</v>
       </c>
       <c r="J84" s="13">
-        <v>9.58</v>
+        <v>6.52</v>
       </c>
       <c r="K84" s="12">
-        <v>2616800.2999999998</v>
+        <v>2416293</v>
       </c>
       <c r="L84" s="13">
-        <v>87.23</v>
+        <v>80.540000000000006</v>
       </c>
       <c r="M84" s="12">
-        <v>383199.7</v>
+        <v>583707</v>
       </c>
       <c r="N84" s="13">
-        <v>12.77</v>
+        <v>19.46</v>
       </c>
       <c r="O84" s="12">
         <v>0</v>
@@ -6856,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="Q84" s="12">
-        <v>383199.7</v>
+        <v>583707</v>
       </c>
       <c r="R84" s="13">
-        <v>12.77</v>
+        <v>19.46</v>
       </c>
     </row>
     <row r="85" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -7056,22 +7059,22 @@
         <v>21.41</v>
       </c>
       <c r="I88" s="12">
-        <v>0</v>
+        <v>116600</v>
       </c>
       <c r="J88" s="13">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="K88" s="12">
-        <v>47105</v>
+        <v>163705</v>
       </c>
       <c r="L88" s="13">
-        <v>21.41</v>
+        <v>74.41</v>
       </c>
       <c r="M88" s="12">
-        <v>172895</v>
+        <v>56295</v>
       </c>
       <c r="N88" s="13">
-        <v>78.59</v>
+        <v>25.59</v>
       </c>
       <c r="O88" s="12">
         <v>0</v>
@@ -7080,10 +7083,10 @@
         <v>0</v>
       </c>
       <c r="Q88" s="12">
-        <v>172895</v>
+        <v>56295</v>
       </c>
       <c r="R88" s="13">
-        <v>78.59</v>
+        <v>25.59</v>
       </c>
     </row>
     <row r="89" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -7112,22 +7115,22 @@
         <v>6.82</v>
       </c>
       <c r="I89" s="12">
-        <v>20700</v>
+        <v>507900</v>
       </c>
       <c r="J89" s="13">
-        <v>2.0699999999999998</v>
+        <v>50.79</v>
       </c>
       <c r="K89" s="12">
-        <v>88910</v>
+        <v>576110</v>
       </c>
       <c r="L89" s="13">
-        <v>8.89</v>
+        <v>57.61</v>
       </c>
       <c r="M89" s="12">
-        <v>911090</v>
+        <v>423890</v>
       </c>
       <c r="N89" s="13">
-        <v>91.11</v>
+        <v>42.39</v>
       </c>
       <c r="O89" s="12">
         <v>550000</v>
@@ -7136,10 +7139,10 @@
         <v>55</v>
       </c>
       <c r="Q89" s="12">
-        <v>361090</v>
+        <v>-126110</v>
       </c>
       <c r="R89" s="13">
-        <v>36.11</v>
+        <v>-12.61</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
@@ -7162,40 +7165,40 @@
         <v>9800000</v>
       </c>
       <c r="G90" s="4">
-        <v>5245581.9800000004</v>
+        <v>5515006.6399999997</v>
       </c>
       <c r="H90" s="5">
-        <v>53.53</v>
+        <v>56.28</v>
       </c>
       <c r="I90" s="4">
-        <v>1204232.97</v>
+        <v>961508.31</v>
       </c>
       <c r="J90" s="5">
-        <v>12.29</v>
+        <v>9.81</v>
       </c>
       <c r="K90" s="4">
-        <v>6449814.9500000002</v>
+        <v>6476514.9500000002</v>
       </c>
       <c r="L90" s="5">
-        <v>65.81</v>
+        <v>66.09</v>
       </c>
       <c r="M90" s="4">
-        <v>3350185.05</v>
+        <v>3323485.05</v>
       </c>
       <c r="N90" s="5">
-        <v>34.19</v>
+        <v>33.909999999999997</v>
       </c>
       <c r="O90" s="4">
-        <v>1837551.54</v>
+        <v>2287551.54</v>
       </c>
       <c r="P90" s="5">
-        <v>18.75</v>
+        <v>23.34</v>
       </c>
       <c r="Q90" s="4">
-        <v>1512633.51</v>
+        <v>1035933.51</v>
       </c>
       <c r="R90" s="5">
-        <v>15.44</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="91" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -7218,40 +7221,40 @@
         <v>9800000</v>
       </c>
       <c r="G91" s="8">
-        <v>5245581.9800000004</v>
+        <v>5515006.6399999997</v>
       </c>
       <c r="H91" s="9">
-        <v>53.53</v>
+        <v>56.28</v>
       </c>
       <c r="I91" s="8">
-        <v>1204232.97</v>
+        <v>961508.31</v>
       </c>
       <c r="J91" s="9">
-        <v>12.29</v>
+        <v>9.81</v>
       </c>
       <c r="K91" s="8">
-        <v>6449814.9500000002</v>
+        <v>6476514.9500000002</v>
       </c>
       <c r="L91" s="9">
-        <v>65.81</v>
+        <v>66.09</v>
       </c>
       <c r="M91" s="8">
-        <v>3350185.05</v>
+        <v>3323485.05</v>
       </c>
       <c r="N91" s="9">
-        <v>34.19</v>
+        <v>33.909999999999997</v>
       </c>
       <c r="O91" s="8">
-        <v>1837551.54</v>
+        <v>2287551.54</v>
       </c>
       <c r="P91" s="9">
-        <v>18.75</v>
+        <v>23.34</v>
       </c>
       <c r="Q91" s="8">
-        <v>1512633.51</v>
+        <v>1035933.51</v>
       </c>
       <c r="R91" s="9">
-        <v>15.44</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="92" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
@@ -7274,16 +7277,16 @@
         <v>4305000</v>
       </c>
       <c r="G92" s="12">
-        <v>2611023.4900000002</v>
+        <v>2709448.15</v>
       </c>
       <c r="H92" s="13">
-        <v>60.65</v>
+        <v>62.94</v>
       </c>
       <c r="I92" s="12">
-        <v>440544.97</v>
+        <v>342120.31</v>
       </c>
       <c r="J92" s="13">
-        <v>10.23</v>
+        <v>7.95</v>
       </c>
       <c r="K92" s="12">
         <v>3051568.46</v>
@@ -7298,16 +7301,16 @@
         <v>29.12</v>
       </c>
       <c r="O92" s="12">
-        <v>801289.54</v>
+        <v>1251289.54</v>
       </c>
       <c r="P92" s="13">
-        <v>18.61</v>
+        <v>29.07</v>
       </c>
       <c r="Q92" s="12">
-        <v>452142</v>
+        <v>2142</v>
       </c>
       <c r="R92" s="13">
-        <v>10.5</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="93" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -7330,16 +7333,16 @@
         <v>3140000</v>
       </c>
       <c r="G93" s="12">
-        <v>1660527.49</v>
+        <v>1831527.49</v>
       </c>
       <c r="H93" s="13">
-        <v>52.88</v>
+        <v>58.33</v>
       </c>
       <c r="I93" s="12">
-        <v>560750</v>
+        <v>389750</v>
       </c>
       <c r="J93" s="13">
-        <v>17.86</v>
+        <v>12.41</v>
       </c>
       <c r="K93" s="12">
         <v>2221277.4900000002</v>
@@ -7392,22 +7395,22 @@
         <v>41.36</v>
       </c>
       <c r="I94" s="12">
-        <v>202938</v>
+        <v>229638</v>
       </c>
       <c r="J94" s="13">
-        <v>8.6199999999999992</v>
+        <v>9.75</v>
       </c>
       <c r="K94" s="12">
-        <v>1176969</v>
+        <v>1203669</v>
       </c>
       <c r="L94" s="13">
-        <v>49.98</v>
+        <v>51.11</v>
       </c>
       <c r="M94" s="12">
-        <v>1178031</v>
+        <v>1151331</v>
       </c>
       <c r="N94" s="13">
-        <v>50.02</v>
+        <v>48.89</v>
       </c>
       <c r="O94" s="12">
         <v>653762</v>
@@ -7416,10 +7419,10 @@
         <v>27.76</v>
       </c>
       <c r="Q94" s="12">
-        <v>524269</v>
+        <v>497569</v>
       </c>
       <c r="R94" s="13">
-        <v>22.26</v>
+        <v>21.13</v>
       </c>
     </row>
     <row r="95" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -7442,40 +7445,40 @@
         <v>119421186</v>
       </c>
       <c r="G95" s="4">
-        <v>80025459.469999999</v>
+        <v>87786367.969999999</v>
       </c>
       <c r="H95" s="5">
-        <v>67.010000000000005</v>
+        <v>73.510000000000005</v>
       </c>
       <c r="I95" s="4">
-        <v>11794424.359999999</v>
+        <v>11218687.52</v>
       </c>
       <c r="J95" s="5">
-        <v>9.8800000000000008</v>
+        <v>9.39</v>
       </c>
       <c r="K95" s="4">
-        <v>91819883.829999998</v>
+        <v>99005055.489999995</v>
       </c>
       <c r="L95" s="5">
-        <v>76.89</v>
+        <v>82.9</v>
       </c>
       <c r="M95" s="4">
-        <v>27601302.170000002</v>
+        <v>20416130.510000002</v>
       </c>
       <c r="N95" s="5">
-        <v>23.11</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="O95" s="4">
-        <v>5916663.4299999997</v>
+        <v>5827810.6299999999</v>
       </c>
       <c r="P95" s="5">
-        <v>4.95</v>
+        <v>4.88</v>
       </c>
       <c r="Q95" s="4">
-        <v>21684638.739999998</v>
+        <v>14588319.880000001</v>
       </c>
       <c r="R95" s="5">
-        <v>18.16</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="96" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -7498,28 +7501,28 @@
         <v>29200000</v>
       </c>
       <c r="G96" s="8">
-        <v>17363324.93</v>
+        <v>17566256.93</v>
       </c>
       <c r="H96" s="9">
-        <v>59.46</v>
+        <v>60.16</v>
       </c>
       <c r="I96" s="8">
-        <v>5858944.1900000004</v>
+        <v>5658302.1900000004</v>
       </c>
       <c r="J96" s="9">
-        <v>20.059999999999999</v>
+        <v>19.38</v>
       </c>
       <c r="K96" s="8">
-        <v>23222269.120000001</v>
+        <v>23224559.120000001</v>
       </c>
       <c r="L96" s="9">
-        <v>79.53</v>
+        <v>79.540000000000006</v>
       </c>
       <c r="M96" s="8">
-        <v>5977730.8799999999</v>
+        <v>5975440.8799999999</v>
       </c>
       <c r="N96" s="9">
-        <v>20.47</v>
+        <v>20.46</v>
       </c>
       <c r="O96" s="8">
         <v>4945423.37</v>
@@ -7528,10 +7531,10 @@
         <v>16.940000000000001</v>
       </c>
       <c r="Q96" s="8">
-        <v>1032307.51</v>
+        <v>1030017.51</v>
       </c>
       <c r="R96" s="9">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="97" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -7554,28 +7557,28 @@
         <v>3261268.89</v>
       </c>
       <c r="G97" s="12">
-        <v>2061042.37</v>
+        <v>2249322.37</v>
       </c>
       <c r="H97" s="13">
-        <v>63.2</v>
+        <v>68.97</v>
       </c>
       <c r="I97" s="12">
-        <v>1128480</v>
+        <v>942100</v>
       </c>
       <c r="J97" s="13">
-        <v>34.6</v>
+        <v>28.89</v>
       </c>
       <c r="K97" s="12">
-        <v>3189522.37</v>
+        <v>3191422.37</v>
       </c>
       <c r="L97" s="13">
-        <v>97.8</v>
+        <v>97.86</v>
       </c>
       <c r="M97" s="12">
-        <v>71746.52</v>
+        <v>69846.52</v>
       </c>
       <c r="N97" s="13">
-        <v>2.2000000000000002</v>
+        <v>2.14</v>
       </c>
       <c r="O97" s="12">
         <v>0</v>
@@ -7584,10 +7587,10 @@
         <v>0</v>
       </c>
       <c r="Q97" s="12">
-        <v>71746.52</v>
+        <v>69846.52</v>
       </c>
       <c r="R97" s="13">
-        <v>2.2000000000000002</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="98" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -7610,16 +7613,16 @@
         <v>4780425.63</v>
       </c>
       <c r="G98" s="12">
-        <v>3433998.35</v>
+        <v>3448260.35</v>
       </c>
       <c r="H98" s="13">
-        <v>71.83</v>
+        <v>72.13</v>
       </c>
       <c r="I98" s="12">
-        <v>682263.54</v>
+        <v>668001.54</v>
       </c>
       <c r="J98" s="13">
-        <v>14.27</v>
+        <v>13.97</v>
       </c>
       <c r="K98" s="12">
         <v>4116261.89</v>
@@ -7666,7 +7669,7 @@
         <v>8310076.75</v>
       </c>
       <c r="G99" s="12">
-        <v>2948087.48</v>
+        <v>2948477.48</v>
       </c>
       <c r="H99" s="13">
         <v>35.479999999999997</v>
@@ -7678,13 +7681,13 @@
         <v>44.32</v>
       </c>
       <c r="K99" s="12">
-        <v>6631288.1299999999</v>
+        <v>6631678.1299999999</v>
       </c>
       <c r="L99" s="13">
         <v>79.8</v>
       </c>
       <c r="M99" s="12">
-        <v>1678788.62</v>
+        <v>1678398.62</v>
       </c>
       <c r="N99" s="13">
         <v>20.2</v>
@@ -7696,7 +7699,7 @@
         <v>14.99</v>
       </c>
       <c r="Q99" s="12">
-        <v>433365.25</v>
+        <v>432975.25</v>
       </c>
       <c r="R99" s="13">
         <v>5.21</v>
@@ -7834,28 +7837,28 @@
         <v>1000000</v>
       </c>
       <c r="G102" s="8">
-        <v>511529</v>
+        <v>533379</v>
       </c>
       <c r="H102" s="9">
-        <v>51.15</v>
+        <v>53.34</v>
       </c>
       <c r="I102" s="8">
-        <v>54820</v>
+        <v>5570</v>
       </c>
       <c r="J102" s="9">
-        <v>5.48</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="K102" s="8">
-        <v>566349</v>
+        <v>538949</v>
       </c>
       <c r="L102" s="9">
-        <v>56.63</v>
+        <v>53.89</v>
       </c>
       <c r="M102" s="8">
-        <v>433651</v>
+        <v>461051</v>
       </c>
       <c r="N102" s="9">
-        <v>43.37</v>
+        <v>46.11</v>
       </c>
       <c r="O102" s="8">
         <v>0</v>
@@ -7864,10 +7867,10 @@
         <v>0</v>
       </c>
       <c r="Q102" s="8">
-        <v>433651</v>
+        <v>461051</v>
       </c>
       <c r="R102" s="9">
-        <v>43.37</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="103" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -7890,28 +7893,28 @@
         <v>886600</v>
       </c>
       <c r="G103" s="12">
-        <v>441139</v>
+        <v>462989</v>
       </c>
       <c r="H103" s="13">
-        <v>49.76</v>
+        <v>52.22</v>
       </c>
       <c r="I103" s="12">
-        <v>42570</v>
+        <v>5570</v>
       </c>
       <c r="J103" s="13">
-        <v>4.8</v>
+        <v>0.63</v>
       </c>
       <c r="K103" s="12">
-        <v>483709</v>
+        <v>468559</v>
       </c>
       <c r="L103" s="13">
-        <v>54.56</v>
+        <v>52.85</v>
       </c>
       <c r="M103" s="12">
-        <v>402891</v>
+        <v>418041</v>
       </c>
       <c r="N103" s="13">
-        <v>45.44</v>
+        <v>47.15</v>
       </c>
       <c r="O103" s="12">
         <v>0</v>
@@ -7920,10 +7923,10 @@
         <v>0</v>
       </c>
       <c r="Q103" s="12">
-        <v>402891</v>
+        <v>418041</v>
       </c>
       <c r="R103" s="13">
-        <v>45.44</v>
+        <v>47.15</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
@@ -7952,22 +7955,22 @@
         <v>62.07</v>
       </c>
       <c r="I104" s="12">
-        <v>12250</v>
+        <v>0</v>
       </c>
       <c r="J104" s="13">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="K104" s="12">
-        <v>82640</v>
+        <v>70390</v>
       </c>
       <c r="L104" s="13">
-        <v>72.87</v>
+        <v>62.07</v>
       </c>
       <c r="M104" s="12">
-        <v>30760</v>
+        <v>43010</v>
       </c>
       <c r="N104" s="13">
-        <v>27.13</v>
+        <v>37.93</v>
       </c>
       <c r="O104" s="12">
         <v>0</v>
@@ -7976,10 +7979,10 @@
         <v>0</v>
       </c>
       <c r="Q104" s="12">
-        <v>30760</v>
+        <v>43010</v>
       </c>
       <c r="R104" s="13">
-        <v>27.13</v>
+        <v>37.93</v>
       </c>
     </row>
     <row r="105" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -8002,16 +8005,16 @@
         <v>1000000</v>
       </c>
       <c r="G105" s="8">
-        <v>747825.74</v>
+        <v>805551.74</v>
       </c>
       <c r="H105" s="9">
-        <v>74.78</v>
+        <v>80.56</v>
       </c>
       <c r="I105" s="8">
-        <v>173268</v>
+        <v>115542</v>
       </c>
       <c r="J105" s="9">
-        <v>17.329999999999998</v>
+        <v>11.55</v>
       </c>
       <c r="K105" s="8">
         <v>921093.74</v>
@@ -8114,16 +8117,16 @@
         <v>787000</v>
       </c>
       <c r="G107" s="12">
-        <v>579487.74</v>
+        <v>637213.74</v>
       </c>
       <c r="H107" s="13">
-        <v>73.63</v>
+        <v>80.97</v>
       </c>
       <c r="I107" s="12">
-        <v>173268</v>
+        <v>115542</v>
       </c>
       <c r="J107" s="13">
-        <v>22.02</v>
+        <v>14.68</v>
       </c>
       <c r="K107" s="12">
         <v>752755.74</v>
@@ -8170,40 +8173,40 @@
         <v>10194186</v>
       </c>
       <c r="G108" s="8">
-        <v>3495199</v>
+        <v>3768775.64</v>
       </c>
       <c r="H108" s="9">
-        <v>34.29</v>
+        <v>36.97</v>
       </c>
       <c r="I108" s="8">
-        <v>5511744.4400000004</v>
+        <v>5328625.5999999996</v>
       </c>
       <c r="J108" s="9">
-        <v>54.07</v>
+        <v>52.27</v>
       </c>
       <c r="K108" s="8">
-        <v>9006943.4399999995</v>
+        <v>9097401.2400000002</v>
       </c>
       <c r="L108" s="9">
-        <v>88.35</v>
+        <v>89.24</v>
       </c>
       <c r="M108" s="8">
-        <v>1187242.56</v>
+        <v>1096784.76</v>
       </c>
       <c r="N108" s="9">
-        <v>11.65</v>
+        <v>10.76</v>
       </c>
       <c r="O108" s="8">
-        <v>969697.56</v>
+        <v>880844.76</v>
       </c>
       <c r="P108" s="9">
-        <v>9.51</v>
+        <v>8.64</v>
       </c>
       <c r="Q108" s="8">
-        <v>217545</v>
+        <v>215940</v>
       </c>
       <c r="R108" s="9">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="109" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -8226,16 +8229,16 @@
         <v>5612100</v>
       </c>
       <c r="G109" s="12">
-        <v>1525479</v>
+        <v>1628700.64</v>
       </c>
       <c r="H109" s="13">
-        <v>27.18</v>
+        <v>29.02</v>
       </c>
       <c r="I109" s="12">
-        <v>3152293.44</v>
+        <v>3049071.8</v>
       </c>
       <c r="J109" s="13">
-        <v>56.17</v>
+        <v>54.33</v>
       </c>
       <c r="K109" s="12">
         <v>4677772.4400000004</v>
@@ -8282,40 +8285,40 @@
         <v>4582086</v>
       </c>
       <c r="G110" s="12">
-        <v>1969720</v>
+        <v>2140075</v>
       </c>
       <c r="H110" s="13">
-        <v>42.99</v>
+        <v>46.71</v>
       </c>
       <c r="I110" s="12">
-        <v>2359451</v>
+        <v>2279553.7999999998</v>
       </c>
       <c r="J110" s="13">
-        <v>51.49</v>
+        <v>49.75</v>
       </c>
       <c r="K110" s="12">
-        <v>4329171</v>
+        <v>4419628.8</v>
       </c>
       <c r="L110" s="13">
-        <v>94.48</v>
+        <v>96.45</v>
       </c>
       <c r="M110" s="12">
-        <v>252915</v>
+        <v>162457.20000000001</v>
       </c>
       <c r="N110" s="13">
-        <v>5.52</v>
+        <v>3.55</v>
       </c>
       <c r="O110" s="12">
-        <v>268753</v>
+        <v>179900.2</v>
       </c>
       <c r="P110" s="13">
-        <v>5.87</v>
+        <v>3.93</v>
       </c>
       <c r="Q110" s="12">
-        <v>-15838</v>
+        <v>-17443</v>
       </c>
       <c r="R110" s="13">
-        <v>-0.35</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="111" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -8338,28 +8341,28 @@
         <v>78027000</v>
       </c>
       <c r="G111" s="8">
-        <v>57907580.799999997</v>
+        <v>65112404.659999996</v>
       </c>
       <c r="H111" s="9">
-        <v>74.209999999999994</v>
+        <v>83.45</v>
       </c>
       <c r="I111" s="8">
-        <v>195647.73</v>
+        <v>110647.73</v>
       </c>
       <c r="J111" s="9">
-        <v>0.25</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="K111" s="8">
-        <v>58103228.530000001</v>
+        <v>65223052.390000001</v>
       </c>
       <c r="L111" s="9">
-        <v>74.47</v>
+        <v>83.59</v>
       </c>
       <c r="M111" s="8">
-        <v>19923771.469999999</v>
+        <v>12803947.609999999</v>
       </c>
       <c r="N111" s="9">
-        <v>25.53</v>
+        <v>16.41</v>
       </c>
       <c r="O111" s="8">
         <v>1542.5</v>
@@ -8368,10 +8371,10 @@
         <v>0</v>
       </c>
       <c r="Q111" s="8">
-        <v>19922228.969999999</v>
+        <v>12802405.109999999</v>
       </c>
       <c r="R111" s="9">
-        <v>25.53</v>
+        <v>16.41</v>
       </c>
     </row>
     <row r="112" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -8450,28 +8453,28 @@
         <v>2387000</v>
       </c>
       <c r="G113" s="12">
-        <v>2557754.0699999998</v>
+        <v>2664354.0699999998</v>
       </c>
       <c r="H113" s="13">
-        <v>107.15</v>
+        <v>111.62</v>
       </c>
       <c r="I113" s="12">
-        <v>172000.23</v>
+        <v>87000.23</v>
       </c>
       <c r="J113" s="13">
-        <v>7.21</v>
+        <v>3.64</v>
       </c>
       <c r="K113" s="12">
-        <v>2729754.3</v>
+        <v>2751354.3</v>
       </c>
       <c r="L113" s="13">
-        <v>114.36</v>
+        <v>115.26</v>
       </c>
       <c r="M113" s="12">
-        <v>-342754.3</v>
+        <v>-364354.3</v>
       </c>
       <c r="N113" s="13">
-        <v>-14.36</v>
+        <v>-15.26</v>
       </c>
       <c r="O113" s="12">
         <v>0</v>
@@ -8480,10 +8483,10 @@
         <v>0</v>
       </c>
       <c r="Q113" s="12">
-        <v>-342754.3</v>
+        <v>-364354.3</v>
       </c>
       <c r="R113" s="13">
-        <v>-14.36</v>
+        <v>-15.26</v>
       </c>
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.25">
@@ -8506,10 +8509,10 @@
         <v>75000000</v>
       </c>
       <c r="G114" s="12">
-        <v>55109371.729999997</v>
+        <v>62207595.590000004</v>
       </c>
       <c r="H114" s="13">
-        <v>73.48</v>
+        <v>82.94</v>
       </c>
       <c r="I114" s="12">
         <v>0</v>
@@ -8518,16 +8521,16 @@
         <v>0</v>
       </c>
       <c r="K114" s="12">
-        <v>55109371.729999997</v>
+        <v>62207595.590000004</v>
       </c>
       <c r="L114" s="13">
-        <v>73.48</v>
+        <v>82.94</v>
       </c>
       <c r="M114" s="12">
-        <v>19890628.27</v>
+        <v>12792404.41</v>
       </c>
       <c r="N114" s="13">
-        <v>26.52</v>
+        <v>17.059999999999999</v>
       </c>
       <c r="O114" s="12">
         <v>0</v>
@@ -8536,10 +8539,10 @@
         <v>0</v>
       </c>
       <c r="Q114" s="12">
-        <v>19890628.27</v>
+        <v>12792404.41</v>
       </c>
       <c r="R114" s="13">
-        <v>26.52</v>
+        <v>17.059999999999999</v>
       </c>
     </row>
     <row r="115" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -8728,40 +8731,40 @@
         <v>230702200</v>
       </c>
       <c r="G118" s="14">
-        <v>146502317.44999999</v>
+        <v>156871820.71000001</v>
       </c>
       <c r="H118" s="15">
-        <v>63.5</v>
+        <v>68</v>
       </c>
       <c r="I118" s="14">
-        <v>35828461.670000002</v>
+        <v>33443961.170000002</v>
       </c>
       <c r="J118" s="15">
-        <v>15.53</v>
+        <v>14.5</v>
       </c>
       <c r="K118" s="14">
-        <v>182330779.12</v>
+        <v>190315781.88</v>
       </c>
       <c r="L118" s="15">
-        <v>79.03</v>
+        <v>82.49</v>
       </c>
       <c r="M118" s="14">
-        <v>48371420.880000003</v>
+        <v>40386418.119999997</v>
       </c>
       <c r="N118" s="15">
-        <v>20.97</v>
+        <v>17.510000000000002</v>
       </c>
       <c r="O118" s="14">
-        <v>10209559.07</v>
+        <v>10588306.27</v>
       </c>
       <c r="P118" s="15">
-        <v>4.43</v>
+        <v>4.59</v>
       </c>
       <c r="Q118" s="14">
-        <v>38161861.810000002</v>
+        <v>29798111.850000001</v>
       </c>
       <c r="R118" s="15">
-        <v>16.54</v>
+        <v>12.92</v>
       </c>
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
@@ -8775,49 +8778,49 @@
         <v>101298156.95</v>
       </c>
       <c r="D119" s="4">
-        <v>0</v>
+        <v>71946</v>
       </c>
       <c r="E119" s="4">
         <v>0</v>
       </c>
       <c r="F119" s="4">
-        <v>101298156.95</v>
+        <v>101370102.95</v>
       </c>
       <c r="G119" s="4">
-        <v>26248895.120000001</v>
+        <v>28497772.09</v>
       </c>
       <c r="H119" s="5">
-        <v>25.91</v>
+        <v>28.11</v>
       </c>
       <c r="I119" s="4">
-        <v>20247819.949999999</v>
+        <v>19891917.98</v>
       </c>
       <c r="J119" s="5">
-        <v>19.989999999999998</v>
+        <v>19.62</v>
       </c>
       <c r="K119" s="4">
-        <v>46496715.07</v>
+        <v>48389690.07</v>
       </c>
       <c r="L119" s="5">
-        <v>45.9</v>
+        <v>47.74</v>
       </c>
       <c r="M119" s="4">
-        <v>54801441.880000003</v>
+        <v>52980412.880000003</v>
       </c>
       <c r="N119" s="5">
-        <v>54.1</v>
+        <v>52.26</v>
       </c>
       <c r="O119" s="4">
-        <v>4944593</v>
+        <v>4899593</v>
       </c>
       <c r="P119" s="5">
-        <v>4.88</v>
+        <v>4.83</v>
       </c>
       <c r="Q119" s="4">
-        <v>49856848.880000003</v>
+        <v>48080819.880000003</v>
       </c>
       <c r="R119" s="5">
-        <v>49.22</v>
+        <v>47.43</v>
       </c>
     </row>
     <row r="120" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -9783,49 +9786,49 @@
         <v>7768581.8099999996</v>
       </c>
       <c r="D137" s="8">
-        <v>0</v>
+        <v>71946</v>
       </c>
       <c r="E137" s="8">
         <v>0</v>
       </c>
       <c r="F137" s="8">
-        <v>7768581.8099999996</v>
+        <v>7840527.8099999996</v>
       </c>
       <c r="G137" s="8">
-        <v>5166723.29</v>
+        <v>5771723.29</v>
       </c>
       <c r="H137" s="9">
-        <v>66.510000000000005</v>
+        <v>73.61</v>
       </c>
       <c r="I137" s="8">
-        <v>1693912.16</v>
+        <v>999782.16</v>
       </c>
       <c r="J137" s="9">
-        <v>21.8</v>
+        <v>12.75</v>
       </c>
       <c r="K137" s="8">
-        <v>6860635.4500000002</v>
+        <v>6771505.4500000002</v>
       </c>
       <c r="L137" s="9">
-        <v>88.31</v>
+        <v>86.37</v>
       </c>
       <c r="M137" s="8">
-        <v>907946.36</v>
+        <v>1069022.3600000001</v>
       </c>
       <c r="N137" s="9">
-        <v>11.69</v>
+        <v>13.63</v>
       </c>
       <c r="O137" s="8">
         <v>106945</v>
       </c>
       <c r="P137" s="9">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Q137" s="8">
-        <v>801001.36</v>
+        <v>962077.36</v>
       </c>
       <c r="R137" s="9">
-        <v>10.31</v>
+        <v>12.27</v>
       </c>
     </row>
     <row r="138" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -9848,28 +9851,28 @@
         <v>2672753.2999999998</v>
       </c>
       <c r="G138" s="12">
-        <v>2167685.1</v>
+        <v>2666185.1</v>
       </c>
       <c r="H138" s="13">
-        <v>81.099999999999994</v>
+        <v>99.75</v>
       </c>
       <c r="I138" s="12">
-        <v>1081055</v>
+        <v>389425</v>
       </c>
       <c r="J138" s="13">
-        <v>40.450000000000003</v>
+        <v>14.57</v>
       </c>
       <c r="K138" s="12">
-        <v>3248740.1</v>
+        <v>3055610.1</v>
       </c>
       <c r="L138" s="13">
-        <v>121.55</v>
+        <v>114.32</v>
       </c>
       <c r="M138" s="12">
-        <v>-575986.80000000005</v>
+        <v>-382856.8</v>
       </c>
       <c r="N138" s="13">
-        <v>-21.55</v>
+        <v>-14.32</v>
       </c>
       <c r="O138" s="12">
         <v>56445</v>
@@ -9878,10 +9881,10 @@
         <v>2.11</v>
       </c>
       <c r="Q138" s="12">
-        <v>-632431.80000000005</v>
+        <v>-439301.8</v>
       </c>
       <c r="R138" s="13">
-        <v>-23.66</v>
+        <v>-16.440000000000001</v>
       </c>
     </row>
     <row r="139" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -10022,22 +10025,22 @@
         <v>116.76</v>
       </c>
       <c r="I141" s="12">
-        <v>0</v>
+        <v>104000</v>
       </c>
       <c r="J141" s="13">
-        <v>0</v>
+        <v>17.73</v>
       </c>
       <c r="K141" s="12">
-        <v>684845.35</v>
+        <v>788845.35</v>
       </c>
       <c r="L141" s="13">
-        <v>116.76</v>
+        <v>134.49</v>
       </c>
       <c r="M141" s="12">
-        <v>-98295.35</v>
+        <v>-202295.35</v>
       </c>
       <c r="N141" s="13">
-        <v>-16.760000000000002</v>
+        <v>-34.49</v>
       </c>
       <c r="O141" s="12">
         <v>50000</v>
@@ -10046,10 +10049,10 @@
         <v>8.52</v>
       </c>
       <c r="Q141" s="12">
-        <v>-148295.35</v>
+        <v>-252295.35</v>
       </c>
       <c r="R141" s="13">
-        <v>-25.28</v>
+        <v>-43.01</v>
       </c>
     </row>
     <row r="142" spans="1:18" x14ac:dyDescent="0.25">
@@ -10063,37 +10066,37 @@
         <v>2071260</v>
       </c>
       <c r="D142" s="12">
-        <v>0</v>
+        <v>71946</v>
       </c>
       <c r="E142" s="12">
         <v>0</v>
       </c>
       <c r="F142" s="12">
-        <v>2071260</v>
+        <v>2143206</v>
       </c>
       <c r="G142" s="12">
-        <v>978312.84</v>
+        <v>1084812.8400000001</v>
       </c>
       <c r="H142" s="13">
-        <v>47.23</v>
+        <v>50.62</v>
       </c>
       <c r="I142" s="12">
-        <v>312857.15999999997</v>
+        <v>206357.16</v>
       </c>
       <c r="J142" s="13">
-        <v>15.1</v>
+        <v>9.6300000000000008</v>
       </c>
       <c r="K142" s="12">
         <v>1291170</v>
       </c>
       <c r="L142" s="13">
-        <v>62.34</v>
+        <v>60.24</v>
       </c>
       <c r="M142" s="12">
-        <v>780090</v>
+        <v>852036</v>
       </c>
       <c r="N142" s="13">
-        <v>37.659999999999997</v>
+        <v>39.76</v>
       </c>
       <c r="O142" s="12">
         <v>500</v>
@@ -10102,10 +10105,10 @@
         <v>0.02</v>
       </c>
       <c r="Q142" s="12">
-        <v>779590</v>
+        <v>851536</v>
       </c>
       <c r="R142" s="13">
-        <v>37.64</v>
+        <v>39.729999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
@@ -10912,7 +10915,7 @@
         <v>2936503.78</v>
       </c>
       <c r="G157" s="8">
-        <v>1697264.18</v>
+        <v>1697269.18</v>
       </c>
       <c r="H157" s="9">
         <v>57.8</v>
@@ -10924,13 +10927,13 @@
         <v>2.75</v>
       </c>
       <c r="K157" s="8">
-        <v>1778149.18</v>
+        <v>1778154.18</v>
       </c>
       <c r="L157" s="9">
         <v>60.55</v>
       </c>
       <c r="M157" s="8">
-        <v>1158354.6000000001</v>
+        <v>1158349.6000000001</v>
       </c>
       <c r="N157" s="9">
         <v>39.450000000000003</v>
@@ -10942,7 +10945,7 @@
         <v>0</v>
       </c>
       <c r="Q157" s="8">
-        <v>1158354.6000000001</v>
+        <v>1158349.6000000001</v>
       </c>
       <c r="R157" s="9">
         <v>39.450000000000003</v>
@@ -11080,7 +11083,7 @@
         <v>353725</v>
       </c>
       <c r="G160" s="12">
-        <v>172218.33</v>
+        <v>172223.33</v>
       </c>
       <c r="H160" s="13">
         <v>48.69</v>
@@ -11092,16 +11095,16 @@
         <v>22.87</v>
       </c>
       <c r="K160" s="12">
-        <v>253103.33</v>
+        <v>253108.33</v>
       </c>
       <c r="L160" s="13">
-        <v>71.55</v>
+        <v>71.56</v>
       </c>
       <c r="M160" s="12">
-        <v>100621.67</v>
+        <v>100616.67</v>
       </c>
       <c r="N160" s="13">
-        <v>28.45</v>
+        <v>28.44</v>
       </c>
       <c r="O160" s="12">
         <v>0</v>
@@ -11110,10 +11113,10 @@
         <v>0</v>
       </c>
       <c r="Q160" s="12">
-        <v>100621.67</v>
+        <v>100616.67</v>
       </c>
       <c r="R160" s="13">
-        <v>28.45</v>
+        <v>28.44</v>
       </c>
     </row>
     <row r="161" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -11192,7 +11195,7 @@
         <v>1900050</v>
       </c>
       <c r="G162" s="8">
-        <v>1287607.6399999999</v>
+        <v>1287592.6399999999</v>
       </c>
       <c r="H162" s="9">
         <v>67.77</v>
@@ -11204,13 +11207,13 @@
         <v>9.2799999999999994</v>
       </c>
       <c r="K162" s="8">
-        <v>1463852.64</v>
+        <v>1463837.64</v>
       </c>
       <c r="L162" s="9">
         <v>77.040000000000006</v>
       </c>
       <c r="M162" s="8">
-        <v>436197.36</v>
+        <v>436212.36</v>
       </c>
       <c r="N162" s="9">
         <v>22.96</v>
@@ -11222,7 +11225,7 @@
         <v>0</v>
       </c>
       <c r="Q162" s="8">
-        <v>436197.36</v>
+        <v>436212.36</v>
       </c>
       <c r="R162" s="9">
         <v>22.96</v>
@@ -11472,10 +11475,10 @@
         <v>299230</v>
       </c>
       <c r="G167" s="12">
-        <v>484385</v>
+        <v>484370</v>
       </c>
       <c r="H167" s="13">
-        <v>161.88</v>
+        <v>161.87</v>
       </c>
       <c r="I167" s="12">
         <v>7245</v>
@@ -11484,16 +11487,16 @@
         <v>2.42</v>
       </c>
       <c r="K167" s="12">
-        <v>491630</v>
+        <v>491615</v>
       </c>
       <c r="L167" s="13">
-        <v>164.3</v>
+        <v>164.29</v>
       </c>
       <c r="M167" s="12">
-        <v>-192400</v>
+        <v>-192385</v>
       </c>
       <c r="N167" s="13">
-        <v>-64.3</v>
+        <v>-64.290000000000006</v>
       </c>
       <c r="O167" s="12">
         <v>0</v>
@@ -11502,10 +11505,10 @@
         <v>0</v>
       </c>
       <c r="Q167" s="12">
-        <v>-192400</v>
+        <v>-192385</v>
       </c>
       <c r="R167" s="13">
-        <v>-64.3</v>
+        <v>-64.290000000000006</v>
       </c>
     </row>
     <row r="168" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -11646,22 +11649,22 @@
         <v>14.6</v>
       </c>
       <c r="I170" s="8">
-        <v>5409905</v>
+        <v>5403925</v>
       </c>
       <c r="J170" s="9">
-        <v>60.61</v>
+        <v>60.54</v>
       </c>
       <c r="K170" s="8">
-        <v>6713550.7800000003</v>
+        <v>6707570.7800000003</v>
       </c>
       <c r="L170" s="9">
-        <v>75.209999999999994</v>
+        <v>75.14</v>
       </c>
       <c r="M170" s="8">
-        <v>2212688.2400000002</v>
+        <v>2218668.2400000002</v>
       </c>
       <c r="N170" s="9">
-        <v>24.79</v>
+        <v>24.86</v>
       </c>
       <c r="O170" s="8">
         <v>15000</v>
@@ -11670,10 +11673,10 @@
         <v>0.17</v>
       </c>
       <c r="Q170" s="8">
-        <v>2197688.2400000002</v>
+        <v>2203668.2400000002</v>
       </c>
       <c r="R170" s="9">
-        <v>24.62</v>
+        <v>24.69</v>
       </c>
     </row>
     <row r="171" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -12318,22 +12321,22 @@
         <v>5.71</v>
       </c>
       <c r="I182" s="12">
-        <v>40825</v>
+        <v>34845</v>
       </c>
       <c r="J182" s="13">
-        <v>2.9</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="K182" s="12">
-        <v>121272.7</v>
+        <v>115292.7</v>
       </c>
       <c r="L182" s="13">
-        <v>8.6</v>
+        <v>8.18</v>
       </c>
       <c r="M182" s="12">
-        <v>1288727.3</v>
+        <v>1294707.3</v>
       </c>
       <c r="N182" s="13">
-        <v>91.4</v>
+        <v>91.82</v>
       </c>
       <c r="O182" s="12">
         <v>0</v>
@@ -12342,10 +12345,10 @@
         <v>0</v>
       </c>
       <c r="Q182" s="12">
-        <v>1288727.3</v>
+        <v>1294707.3</v>
       </c>
       <c r="R182" s="13">
-        <v>91.4</v>
+        <v>91.82</v>
       </c>
     </row>
     <row r="183" spans="1:18" x14ac:dyDescent="0.25">
@@ -13488,40 +13491,40 @@
         <v>12829676.84</v>
       </c>
       <c r="G203" s="8">
-        <v>2729857.91</v>
+        <v>2983932.91</v>
       </c>
       <c r="H203" s="9">
-        <v>21.28</v>
+        <v>23.26</v>
       </c>
       <c r="I203" s="8">
-        <v>1238356.56</v>
+        <v>1021641.56</v>
       </c>
       <c r="J203" s="9">
-        <v>9.65</v>
+        <v>7.96</v>
       </c>
       <c r="K203" s="8">
-        <v>3968214.47</v>
+        <v>4005574.47</v>
       </c>
       <c r="L203" s="9">
-        <v>30.93</v>
+        <v>31.22</v>
       </c>
       <c r="M203" s="8">
-        <v>8861462.3699999992</v>
+        <v>8824102.3699999992</v>
       </c>
       <c r="N203" s="9">
-        <v>69.069999999999993</v>
+        <v>68.78</v>
       </c>
       <c r="O203" s="8">
-        <v>54000</v>
+        <v>9000</v>
       </c>
       <c r="P203" s="9">
-        <v>0.42</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="Q203" s="8">
-        <v>8807462.3699999992</v>
+        <v>8815102.3699999992</v>
       </c>
       <c r="R203" s="9">
-        <v>68.650000000000006</v>
+        <v>68.709999999999994</v>
       </c>
     </row>
     <row r="204" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -13544,40 +13547,40 @@
         <v>1681566.8</v>
       </c>
       <c r="G204" s="12">
-        <v>285260</v>
+        <v>435085</v>
       </c>
       <c r="H204" s="13">
-        <v>16.96</v>
+        <v>25.87</v>
       </c>
       <c r="I204" s="12">
-        <v>198340</v>
+        <v>45000</v>
       </c>
       <c r="J204" s="13">
-        <v>11.79</v>
+        <v>2.68</v>
       </c>
       <c r="K204" s="12">
-        <v>483600</v>
+        <v>480085</v>
       </c>
       <c r="L204" s="13">
-        <v>28.76</v>
+        <v>28.55</v>
       </c>
       <c r="M204" s="12">
-        <v>1197966.8</v>
+        <v>1201481.8</v>
       </c>
       <c r="N204" s="13">
-        <v>71.239999999999995</v>
+        <v>71.45</v>
       </c>
       <c r="O204" s="12">
-        <v>54000</v>
+        <v>9000</v>
       </c>
       <c r="P204" s="13">
-        <v>3.21</v>
+        <v>0.54</v>
       </c>
       <c r="Q204" s="12">
-        <v>1143966.8</v>
+        <v>1192481.8</v>
       </c>
       <c r="R204" s="13">
-        <v>68.03</v>
+        <v>70.91</v>
       </c>
     </row>
     <row r="205" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -13992,28 +13995,28 @@
         <v>3830323</v>
       </c>
       <c r="G212" s="12">
-        <v>1561873.01</v>
+        <v>1666123.01</v>
       </c>
       <c r="H212" s="13">
-        <v>40.78</v>
+        <v>43.5</v>
       </c>
       <c r="I212" s="12">
-        <v>591210.16</v>
+        <v>527835.16</v>
       </c>
       <c r="J212" s="13">
-        <v>15.43</v>
+        <v>13.78</v>
       </c>
       <c r="K212" s="12">
-        <v>2153083.17</v>
+        <v>2193958.17</v>
       </c>
       <c r="L212" s="13">
-        <v>56.21</v>
+        <v>57.28</v>
       </c>
       <c r="M212" s="12">
-        <v>1677239.83</v>
+        <v>1636364.83</v>
       </c>
       <c r="N212" s="13">
-        <v>43.79</v>
+        <v>42.72</v>
       </c>
       <c r="O212" s="12">
         <v>0</v>
@@ -14022,10 +14025,10 @@
         <v>0</v>
       </c>
       <c r="Q212" s="12">
-        <v>1677239.83</v>
+        <v>1636364.83</v>
       </c>
       <c r="R212" s="13">
-        <v>43.79</v>
+        <v>42.72</v>
       </c>
     </row>
     <row r="213" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -14160,28 +14163,28 @@
         <v>18605882.420000002</v>
       </c>
       <c r="G215" s="8">
-        <v>3079527.03</v>
+        <v>3185402.03</v>
       </c>
       <c r="H215" s="9">
-        <v>16.55</v>
+        <v>17.12</v>
       </c>
       <c r="I215" s="8">
-        <v>2359966</v>
+        <v>2737311</v>
       </c>
       <c r="J215" s="9">
-        <v>12.68</v>
+        <v>14.71</v>
       </c>
       <c r="K215" s="8">
-        <v>5439493.0300000003</v>
+        <v>5922713.0300000003</v>
       </c>
       <c r="L215" s="9">
-        <v>29.24</v>
+        <v>31.83</v>
       </c>
       <c r="M215" s="8">
-        <v>13166389.390000001</v>
+        <v>12683169.390000001</v>
       </c>
       <c r="N215" s="9">
-        <v>70.760000000000005</v>
+        <v>68.17</v>
       </c>
       <c r="O215" s="8">
         <v>3295000</v>
@@ -14190,10 +14193,10 @@
         <v>17.71</v>
       </c>
       <c r="Q215" s="8">
-        <v>9871389.3900000006</v>
+        <v>9388169.3900000006</v>
       </c>
       <c r="R215" s="9">
-        <v>53.06</v>
+        <v>50.46</v>
       </c>
     </row>
     <row r="216" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -14670,22 +14673,22 @@
         <v>0</v>
       </c>
       <c r="I224" s="12">
-        <v>0</v>
+        <v>483220</v>
       </c>
       <c r="J224" s="13">
-        <v>0</v>
+        <v>96.22</v>
       </c>
       <c r="K224" s="12">
-        <v>0</v>
+        <v>483220</v>
       </c>
       <c r="L224" s="13">
-        <v>0</v>
+        <v>96.22</v>
       </c>
       <c r="M224" s="12">
-        <v>502200</v>
+        <v>18980</v>
       </c>
       <c r="N224" s="13">
-        <v>100</v>
+        <v>3.78</v>
       </c>
       <c r="O224" s="12">
         <v>0</v>
@@ -14694,10 +14697,10 @@
         <v>0</v>
       </c>
       <c r="Q224" s="12">
-        <v>502200</v>
+        <v>18980</v>
       </c>
       <c r="R224" s="13">
-        <v>100</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="225" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -15112,16 +15115,16 @@
         <v>4577150</v>
       </c>
       <c r="G232" s="12">
-        <v>1426019.63</v>
+        <v>1531894.63</v>
       </c>
       <c r="H232" s="13">
-        <v>31.16</v>
+        <v>33.47</v>
       </c>
       <c r="I232" s="12">
-        <v>540921</v>
+        <v>435046</v>
       </c>
       <c r="J232" s="13">
-        <v>11.82</v>
+        <v>9.5</v>
       </c>
       <c r="K232" s="12">
         <v>1966940.63</v>
@@ -15560,7 +15563,7 @@
         <v>1995235</v>
       </c>
       <c r="G240" s="8">
-        <v>1974647</v>
+        <v>1974622</v>
       </c>
       <c r="H240" s="9">
         <v>98.97</v>
@@ -15572,13 +15575,13 @@
         <v>9.1199999999999992</v>
       </c>
       <c r="K240" s="8">
-        <v>2156517</v>
+        <v>2156492</v>
       </c>
       <c r="L240" s="9">
         <v>108.08</v>
       </c>
       <c r="M240" s="8">
-        <v>-161282</v>
+        <v>-161257</v>
       </c>
       <c r="N240" s="9">
         <v>-8.08</v>
@@ -15590,7 +15593,7 @@
         <v>0</v>
       </c>
       <c r="Q240" s="8">
-        <v>-161282</v>
+        <v>-161257</v>
       </c>
       <c r="R240" s="9">
         <v>-8.08</v>
@@ -15672,10 +15675,10 @@
         <v>14200</v>
       </c>
       <c r="G242" s="12">
-        <v>15010</v>
+        <v>14985</v>
       </c>
       <c r="H242" s="13">
-        <v>105.7</v>
+        <v>105.53</v>
       </c>
       <c r="I242" s="12">
         <v>485</v>
@@ -15684,16 +15687,16 @@
         <v>3.42</v>
       </c>
       <c r="K242" s="12">
-        <v>15495</v>
+        <v>15470</v>
       </c>
       <c r="L242" s="13">
-        <v>109.12</v>
+        <v>108.94</v>
       </c>
       <c r="M242" s="12">
-        <v>-1295</v>
+        <v>-1270</v>
       </c>
       <c r="N242" s="13">
-        <v>-9.1199999999999992</v>
+        <v>-8.94</v>
       </c>
       <c r="O242" s="12">
         <v>0</v>
@@ -15702,10 +15705,10 @@
         <v>0</v>
       </c>
       <c r="Q242" s="12">
-        <v>-1295</v>
+        <v>-1270</v>
       </c>
       <c r="R242" s="13">
-        <v>-9.1199999999999992</v>
+        <v>-8.94</v>
       </c>
     </row>
     <row r="243" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -16120,28 +16123,28 @@
         <v>2528000</v>
       </c>
       <c r="G250" s="8">
-        <v>752429.84</v>
+        <v>900179.84</v>
       </c>
       <c r="H250" s="9">
-        <v>29.76</v>
+        <v>35.61</v>
       </c>
       <c r="I250" s="8">
-        <v>697510</v>
+        <v>674050</v>
       </c>
       <c r="J250" s="9">
-        <v>27.59</v>
+        <v>26.66</v>
       </c>
       <c r="K250" s="8">
-        <v>1449939.84</v>
+        <v>1574229.84</v>
       </c>
       <c r="L250" s="9">
-        <v>57.36</v>
+        <v>62.27</v>
       </c>
       <c r="M250" s="8">
-        <v>1078060.1599999999</v>
+        <v>953770.16</v>
       </c>
       <c r="N250" s="9">
-        <v>42.64</v>
+        <v>37.729999999999997</v>
       </c>
       <c r="O250" s="8">
         <v>20000</v>
@@ -16150,10 +16153,10 @@
         <v>0.79</v>
       </c>
       <c r="Q250" s="8">
-        <v>1058060.1599999999</v>
+        <v>933770.16</v>
       </c>
       <c r="R250" s="9">
-        <v>41.85</v>
+        <v>36.94</v>
       </c>
     </row>
     <row r="251" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -16176,28 +16179,28 @@
         <v>792000</v>
       </c>
       <c r="G251" s="12">
-        <v>186025</v>
+        <v>331625</v>
       </c>
       <c r="H251" s="13">
-        <v>23.49</v>
+        <v>41.87</v>
       </c>
       <c r="I251" s="12">
-        <v>389000</v>
+        <v>275440</v>
       </c>
       <c r="J251" s="13">
-        <v>49.12</v>
+        <v>34.78</v>
       </c>
       <c r="K251" s="12">
-        <v>575025</v>
+        <v>607065</v>
       </c>
       <c r="L251" s="13">
-        <v>72.599999999999994</v>
+        <v>76.650000000000006</v>
       </c>
       <c r="M251" s="12">
-        <v>216975</v>
+        <v>184935</v>
       </c>
       <c r="N251" s="13">
-        <v>27.4</v>
+        <v>23.35</v>
       </c>
       <c r="O251" s="12">
         <v>20000</v>
@@ -16206,10 +16209,10 @@
         <v>2.5299999999999998</v>
       </c>
       <c r="Q251" s="12">
-        <v>196975</v>
+        <v>164935</v>
       </c>
       <c r="R251" s="13">
-        <v>24.87</v>
+        <v>20.83</v>
       </c>
     </row>
     <row r="252" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -16288,28 +16291,28 @@
         <v>792000</v>
       </c>
       <c r="G253" s="12">
-        <v>290377.59999999998</v>
+        <v>292527.59999999998</v>
       </c>
       <c r="H253" s="13">
-        <v>36.659999999999997</v>
+        <v>36.94</v>
       </c>
       <c r="I253" s="12">
-        <v>88510</v>
+        <v>178610</v>
       </c>
       <c r="J253" s="13">
-        <v>11.18</v>
+        <v>22.55</v>
       </c>
       <c r="K253" s="12">
-        <v>378887.6</v>
+        <v>471137.6</v>
       </c>
       <c r="L253" s="13">
-        <v>47.84</v>
+        <v>59.49</v>
       </c>
       <c r="M253" s="12">
-        <v>413112.4</v>
+        <v>320862.40000000002</v>
       </c>
       <c r="N253" s="13">
-        <v>52.16</v>
+        <v>40.51</v>
       </c>
       <c r="O253" s="12">
         <v>0</v>
@@ -16318,10 +16321,10 @@
         <v>0</v>
       </c>
       <c r="Q253" s="12">
-        <v>413112.4</v>
+        <v>320862.40000000002</v>
       </c>
       <c r="R253" s="13">
-        <v>52.16</v>
+        <v>40.51</v>
       </c>
     </row>
     <row r="254" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -16344,28 +16347,28 @@
         <v>12554100</v>
       </c>
       <c r="G254" s="8">
-        <v>3086795.44</v>
+        <v>3499420.44</v>
       </c>
       <c r="H254" s="9">
-        <v>24.59</v>
+        <v>27.87</v>
       </c>
       <c r="I254" s="8">
-        <v>1394828.56</v>
+        <v>1152503.56</v>
       </c>
       <c r="J254" s="9">
-        <v>11.11</v>
+        <v>9.18</v>
       </c>
       <c r="K254" s="8">
-        <v>4481624</v>
+        <v>4651924</v>
       </c>
       <c r="L254" s="9">
-        <v>35.700000000000003</v>
+        <v>37.06</v>
       </c>
       <c r="M254" s="8">
-        <v>8072476</v>
+        <v>7902176</v>
       </c>
       <c r="N254" s="9">
-        <v>64.3</v>
+        <v>62.94</v>
       </c>
       <c r="O254" s="8">
         <v>715148</v>
@@ -16374,10 +16377,10 @@
         <v>5.7</v>
       </c>
       <c r="Q254" s="8">
-        <v>7357328</v>
+        <v>7187028</v>
       </c>
       <c r="R254" s="9">
-        <v>58.6</v>
+        <v>57.25</v>
       </c>
     </row>
     <row r="255" spans="1:18" ht="132" x14ac:dyDescent="0.25">
@@ -16400,16 +16403,16 @@
         <v>4375000</v>
       </c>
       <c r="G255" s="12">
-        <v>715494</v>
+        <v>1015494</v>
       </c>
       <c r="H255" s="13">
-        <v>16.350000000000001</v>
+        <v>23.21</v>
       </c>
       <c r="I255" s="12">
-        <v>468000</v>
+        <v>168000</v>
       </c>
       <c r="J255" s="13">
-        <v>10.7</v>
+        <v>3.84</v>
       </c>
       <c r="K255" s="12">
         <v>1183494</v>
@@ -16462,22 +16465,22 @@
         <v>37.43</v>
       </c>
       <c r="I256" s="12">
-        <v>528600</v>
+        <v>653900</v>
       </c>
       <c r="J256" s="13">
-        <v>11.6</v>
+        <v>14.35</v>
       </c>
       <c r="K256" s="12">
-        <v>2233773</v>
+        <v>2359073</v>
       </c>
       <c r="L256" s="13">
-        <v>49.03</v>
+        <v>51.78</v>
       </c>
       <c r="M256" s="12">
-        <v>2322227</v>
+        <v>2196927</v>
       </c>
       <c r="N256" s="13">
-        <v>50.97</v>
+        <v>48.22</v>
       </c>
       <c r="O256" s="12">
         <v>211000</v>
@@ -16486,10 +16489,10 @@
         <v>4.63</v>
       </c>
       <c r="Q256" s="12">
-        <v>2111227</v>
+        <v>1985927</v>
       </c>
       <c r="R256" s="13">
-        <v>46.34</v>
+        <v>43.59</v>
       </c>
     </row>
     <row r="257" spans="1:18" x14ac:dyDescent="0.25">
@@ -16512,28 +16515,28 @@
         <v>2730000</v>
       </c>
       <c r="G257" s="12">
-        <v>666128.43999999994</v>
+        <v>778753.44</v>
       </c>
       <c r="H257" s="13">
-        <v>24.4</v>
+        <v>28.53</v>
       </c>
       <c r="I257" s="12">
-        <v>398228.56</v>
+        <v>330603.56</v>
       </c>
       <c r="J257" s="13">
-        <v>14.59</v>
+        <v>12.11</v>
       </c>
       <c r="K257" s="12">
-        <v>1064357</v>
+        <v>1109357</v>
       </c>
       <c r="L257" s="13">
-        <v>38.99</v>
+        <v>40.64</v>
       </c>
       <c r="M257" s="12">
-        <v>1665643</v>
+        <v>1620643</v>
       </c>
       <c r="N257" s="13">
-        <v>61.01</v>
+        <v>59.36</v>
       </c>
       <c r="O257" s="12">
         <v>148</v>
@@ -16542,10 +16545,10 @@
         <v>0.01</v>
       </c>
       <c r="Q257" s="12">
-        <v>1665495</v>
+        <v>1620495</v>
       </c>
       <c r="R257" s="13">
-        <v>61.01</v>
+        <v>59.36</v>
       </c>
     </row>
     <row r="258" spans="1:18" x14ac:dyDescent="0.25">
@@ -17072,16 +17075,16 @@
         <v>19811100</v>
       </c>
       <c r="G267" s="8">
-        <v>2413000</v>
+        <v>3110261.97</v>
       </c>
       <c r="H267" s="9">
-        <v>12.18</v>
+        <v>15.7</v>
       </c>
       <c r="I267" s="8">
-        <v>6349170</v>
+        <v>5651908.0300000003</v>
       </c>
       <c r="J267" s="9">
-        <v>32.049999999999997</v>
+        <v>28.53</v>
       </c>
       <c r="K267" s="8">
         <v>8762170</v>
@@ -17184,16 +17187,16 @@
         <v>10400000</v>
       </c>
       <c r="G269" s="12">
-        <v>2400000</v>
+        <v>3000000</v>
       </c>
       <c r="H269" s="13">
-        <v>23.08</v>
+        <v>28.85</v>
       </c>
       <c r="I269" s="12">
-        <v>6000000</v>
+        <v>5400000</v>
       </c>
       <c r="J269" s="13">
-        <v>57.69</v>
+        <v>51.92</v>
       </c>
       <c r="K269" s="12">
         <v>8400000</v>
@@ -17408,16 +17411,16 @@
         <v>3697200</v>
       </c>
       <c r="G273" s="12">
-        <v>0</v>
+        <v>97261.97</v>
       </c>
       <c r="H273" s="13">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="I273" s="12">
-        <v>340500</v>
+        <v>243238.03</v>
       </c>
       <c r="J273" s="13">
-        <v>9.2100000000000009</v>
+        <v>6.58</v>
       </c>
       <c r="K273" s="12">
         <v>340500</v>
@@ -17576,28 +17579,28 @@
         <v>2205500</v>
       </c>
       <c r="G276" s="8">
-        <v>0</v>
+        <v>26325</v>
       </c>
       <c r="H276" s="9">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="I276" s="8">
-        <v>78075</v>
+        <v>1224700</v>
       </c>
       <c r="J276" s="9">
-        <v>3.54</v>
+        <v>55.53</v>
       </c>
       <c r="K276" s="8">
-        <v>78075</v>
+        <v>1251025</v>
       </c>
       <c r="L276" s="9">
-        <v>3.54</v>
+        <v>56.72</v>
       </c>
       <c r="M276" s="8">
-        <v>2127425</v>
+        <v>954475</v>
       </c>
       <c r="N276" s="9">
-        <v>96.46</v>
+        <v>43.28</v>
       </c>
       <c r="O276" s="8">
         <v>360000</v>
@@ -17606,10 +17609,10 @@
         <v>16.32</v>
       </c>
       <c r="Q276" s="8">
-        <v>1767425</v>
+        <v>594475</v>
       </c>
       <c r="R276" s="9">
-        <v>80.14</v>
+        <v>26.95</v>
       </c>
     </row>
     <row r="277" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -17638,22 +17641,22 @@
         <v>0</v>
       </c>
       <c r="I277" s="12">
-        <v>0</v>
+        <v>1172500</v>
       </c>
       <c r="J277" s="13">
-        <v>0</v>
+        <v>66.48</v>
       </c>
       <c r="K277" s="12">
-        <v>0</v>
+        <v>1172500</v>
       </c>
       <c r="L277" s="13">
-        <v>0</v>
+        <v>66.48</v>
       </c>
       <c r="M277" s="12">
-        <v>1763750</v>
+        <v>591250</v>
       </c>
       <c r="N277" s="13">
-        <v>100</v>
+        <v>33.520000000000003</v>
       </c>
       <c r="O277" s="12">
         <v>360000</v>
@@ -17662,10 +17665,10 @@
         <v>20.41</v>
       </c>
       <c r="Q277" s="12">
-        <v>1403750</v>
+        <v>231250</v>
       </c>
       <c r="R277" s="13">
-        <v>79.59</v>
+        <v>13.11</v>
       </c>
     </row>
     <row r="278" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -17744,28 +17747,28 @@
         <v>177750</v>
       </c>
       <c r="G279" s="12">
-        <v>0</v>
+        <v>26325</v>
       </c>
       <c r="H279" s="13">
-        <v>0</v>
+        <v>14.81</v>
       </c>
       <c r="I279" s="12">
-        <v>78075</v>
+        <v>52200</v>
       </c>
       <c r="J279" s="13">
-        <v>43.92</v>
+        <v>29.37</v>
       </c>
       <c r="K279" s="12">
-        <v>78075</v>
+        <v>78525</v>
       </c>
       <c r="L279" s="13">
-        <v>43.92</v>
+        <v>44.18</v>
       </c>
       <c r="M279" s="12">
-        <v>99675</v>
+        <v>99225</v>
       </c>
       <c r="N279" s="13">
-        <v>56.08</v>
+        <v>55.82</v>
       </c>
       <c r="O279" s="12">
         <v>0</v>
@@ -17774,10 +17777,10 @@
         <v>0</v>
       </c>
       <c r="Q279" s="12">
-        <v>99675</v>
+        <v>99225</v>
       </c>
       <c r="R279" s="13">
-        <v>56.08</v>
+        <v>55.82</v>
       </c>
     </row>
     <row r="280" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -18125,49 +18128,49 @@
         <v>101298156.95</v>
       </c>
       <c r="D286" s="14">
-        <v>0</v>
+        <v>71946</v>
       </c>
       <c r="E286" s="14">
         <v>0</v>
       </c>
       <c r="F286" s="14">
-        <v>101298156.95</v>
+        <v>101370102.95</v>
       </c>
       <c r="G286" s="14">
-        <v>26248895.120000001</v>
+        <v>28497772.09</v>
       </c>
       <c r="H286" s="15">
-        <v>25.91</v>
+        <v>28.11</v>
       </c>
       <c r="I286" s="14">
-        <v>20247819.949999999</v>
+        <v>19891917.98</v>
       </c>
       <c r="J286" s="15">
-        <v>19.989999999999998</v>
+        <v>19.62</v>
       </c>
       <c r="K286" s="14">
-        <v>46496715.07</v>
+        <v>48389690.07</v>
       </c>
       <c r="L286" s="15">
-        <v>45.9</v>
+        <v>47.74</v>
       </c>
       <c r="M286" s="14">
-        <v>54801441.880000003</v>
+        <v>52980412.880000003</v>
       </c>
       <c r="N286" s="15">
-        <v>54.1</v>
+        <v>52.26</v>
       </c>
       <c r="O286" s="14">
-        <v>4944593</v>
+        <v>4899593</v>
       </c>
       <c r="P286" s="15">
-        <v>4.88</v>
+        <v>4.83</v>
       </c>
       <c r="Q286" s="14">
-        <v>49856848.880000003</v>
+        <v>48080819.880000003</v>
       </c>
       <c r="R286" s="15">
-        <v>49.22</v>
+        <v>47.43</v>
       </c>
     </row>
     <row r="287" spans="1:18" x14ac:dyDescent="0.25">
@@ -18179,49 +18182,49 @@
         <v>332000356.94999999</v>
       </c>
       <c r="D287" s="16">
-        <v>0</v>
+        <v>71946</v>
       </c>
       <c r="E287" s="16">
         <v>0</v>
       </c>
       <c r="F287" s="16">
-        <v>332000356.94999999</v>
+        <v>332072302.94999999</v>
       </c>
       <c r="G287" s="16">
-        <v>172751212.56999999</v>
+        <v>185369592.80000001</v>
       </c>
       <c r="H287" s="17">
-        <v>52.03</v>
+        <v>55.82</v>
       </c>
       <c r="I287" s="16">
-        <v>56076281.619999997</v>
+        <v>53335879.149999999</v>
       </c>
       <c r="J287" s="17">
-        <v>16.89</v>
+        <v>16.059999999999999</v>
       </c>
       <c r="K287" s="16">
-        <v>228827494.19</v>
+        <v>238705471.94999999</v>
       </c>
       <c r="L287" s="17">
-        <v>68.92</v>
+        <v>71.88</v>
       </c>
       <c r="M287" s="16">
-        <v>103172862.76000001</v>
+        <v>93366831</v>
       </c>
       <c r="N287" s="17">
-        <v>31.08</v>
+        <v>28.12</v>
       </c>
       <c r="O287" s="16">
-        <v>15154152.07</v>
+        <v>15487899.27</v>
       </c>
       <c r="P287" s="17">
-        <v>4.5599999999999996</v>
+        <v>4.66</v>
       </c>
       <c r="Q287" s="16">
-        <v>88018710.689999998</v>
+        <v>77878931.730000004</v>
       </c>
       <c r="R287" s="17">
-        <v>26.51</v>
+        <v>23.45</v>
       </c>
     </row>
     <row r="288" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -18455,49 +18458,49 @@
         <v>338655937.13</v>
       </c>
       <c r="D292" s="16">
-        <v>0</v>
+        <v>71946</v>
       </c>
       <c r="E292" s="16">
         <v>0</v>
       </c>
       <c r="F292" s="16">
-        <v>338655937.13</v>
+        <v>338727883.13</v>
       </c>
       <c r="G292" s="16">
-        <v>172751212.56999999</v>
+        <v>185369592.80000001</v>
       </c>
       <c r="H292" s="17">
-        <v>51.01</v>
+        <v>54.73</v>
       </c>
       <c r="I292" s="16">
-        <v>56076281.619999997</v>
+        <v>53335879.149999999</v>
       </c>
       <c r="J292" s="17">
-        <v>16.559999999999999</v>
+        <v>15.75</v>
       </c>
       <c r="K292" s="16">
-        <v>228827494.19</v>
+        <v>238705471.94999999</v>
       </c>
       <c r="L292" s="17">
-        <v>67.569999999999993</v>
+        <v>70.47</v>
       </c>
       <c r="M292" s="16">
-        <v>109828442.94</v>
+        <v>100022411.18000001</v>
       </c>
       <c r="N292" s="17">
-        <v>32.43</v>
+        <v>29.53</v>
       </c>
       <c r="O292" s="16">
-        <v>15154152.07</v>
+        <v>15487899.27</v>
       </c>
       <c r="P292" s="17">
-        <v>4.47</v>
+        <v>4.57</v>
       </c>
       <c r="Q292" s="16">
-        <v>94674290.870000005</v>
+        <v>84534511.909999996</v>
       </c>
       <c r="R292" s="17">
-        <v>27.96</v>
+        <v>24.96</v>
       </c>
     </row>
     <row r="293" spans="1:18" x14ac:dyDescent="0.25">
@@ -18514,34 +18517,34 @@
         <v>0</v>
       </c>
       <c r="E293" s="4">
-        <v>0</v>
+        <v>71946</v>
       </c>
       <c r="F293" s="4">
-        <v>4037940.24</v>
+        <v>3965994.24</v>
       </c>
       <c r="G293" s="4">
         <v>558139.18000000005</v>
       </c>
       <c r="H293" s="5">
-        <v>13.82</v>
+        <v>14.07</v>
       </c>
       <c r="I293" s="4">
         <v>156393.70000000001</v>
       </c>
       <c r="J293" s="5">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="K293" s="4">
         <v>714532.88</v>
       </c>
       <c r="L293" s="5">
-        <v>17.7</v>
+        <v>18.02</v>
       </c>
       <c r="M293" s="4">
-        <v>3323407.36</v>
+        <v>3251461.36</v>
       </c>
       <c r="N293" s="5">
-        <v>82.3</v>
+        <v>81.98</v>
       </c>
       <c r="O293" s="4">
         <v>6129.12</v>
@@ -18550,10 +18553,10 @@
         <v>0.15</v>
       </c>
       <c r="Q293" s="4">
-        <v>3317278.24</v>
+        <v>3245332.24</v>
       </c>
       <c r="R293" s="5">
-        <v>82.15</v>
+        <v>81.83</v>
       </c>
     </row>
     <row r="294" spans="1:18" x14ac:dyDescent="0.25">
@@ -18570,34 +18573,34 @@
         <v>0</v>
       </c>
       <c r="E294" s="8">
-        <v>0</v>
+        <v>71946</v>
       </c>
       <c r="F294" s="8">
-        <v>4037940.24</v>
+        <v>3965994.24</v>
       </c>
       <c r="G294" s="8">
         <v>558139.18000000005</v>
       </c>
       <c r="H294" s="9">
-        <v>13.82</v>
+        <v>14.07</v>
       </c>
       <c r="I294" s="8">
         <v>156393.70000000001</v>
       </c>
       <c r="J294" s="9">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="K294" s="8">
         <v>714532.88</v>
       </c>
       <c r="L294" s="9">
-        <v>17.7</v>
+        <v>18.02</v>
       </c>
       <c r="M294" s="8">
-        <v>3323407.36</v>
+        <v>3251461.36</v>
       </c>
       <c r="N294" s="9">
-        <v>82.3</v>
+        <v>81.98</v>
       </c>
       <c r="O294" s="8">
         <v>6129.12</v>
@@ -18606,10 +18609,10 @@
         <v>0.15</v>
       </c>
       <c r="Q294" s="8">
-        <v>3317278.24</v>
+        <v>3245332.24</v>
       </c>
       <c r="R294" s="9">
-        <v>82.15</v>
+        <v>81.83</v>
       </c>
     </row>
     <row r="295" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -18626,34 +18629,34 @@
         <v>0</v>
       </c>
       <c r="E295" s="12">
-        <v>0</v>
+        <v>71946</v>
       </c>
       <c r="F295" s="12">
-        <v>4037940.24</v>
+        <v>3965994.24</v>
       </c>
       <c r="G295" s="12">
         <v>558139.18000000005</v>
       </c>
       <c r="H295" s="13">
-        <v>13.82</v>
+        <v>14.07</v>
       </c>
       <c r="I295" s="12">
         <v>156393.70000000001</v>
       </c>
       <c r="J295" s="13">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="K295" s="12">
         <v>714532.88</v>
       </c>
       <c r="L295" s="13">
-        <v>17.7</v>
+        <v>18.02</v>
       </c>
       <c r="M295" s="12">
-        <v>3323407.36</v>
+        <v>3251461.36</v>
       </c>
       <c r="N295" s="13">
-        <v>82.3</v>
+        <v>81.98</v>
       </c>
       <c r="O295" s="12">
         <v>6129.12</v>
@@ -18662,10 +18665,10 @@
         <v>0.15</v>
       </c>
       <c r="Q295" s="12">
-        <v>3317278.24</v>
+        <v>3245332.24</v>
       </c>
       <c r="R295" s="13">
-        <v>82.15</v>
+        <v>81.83</v>
       </c>
     </row>
     <row r="296" spans="1:18" x14ac:dyDescent="0.25">
@@ -18680,34 +18683,34 @@
         <v>0</v>
       </c>
       <c r="E296" s="14">
-        <v>0</v>
+        <v>71946</v>
       </c>
       <c r="F296" s="14">
-        <v>4037940.24</v>
+        <v>3965994.24</v>
       </c>
       <c r="G296" s="14">
         <v>558139.18000000005</v>
       </c>
       <c r="H296" s="15">
-        <v>13.82</v>
+        <v>14.07</v>
       </c>
       <c r="I296" s="14">
         <v>156393.70000000001</v>
       </c>
       <c r="J296" s="15">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="K296" s="14">
         <v>714532.88</v>
       </c>
       <c r="L296" s="15">
-        <v>17.7</v>
+        <v>18.02</v>
       </c>
       <c r="M296" s="14">
-        <v>3323407.36</v>
+        <v>3251461.36</v>
       </c>
       <c r="N296" s="15">
-        <v>82.3</v>
+        <v>81.98</v>
       </c>
       <c r="O296" s="14">
         <v>6129.12</v>
@@ -18716,10 +18719,10 @@
         <v>0.15</v>
       </c>
       <c r="Q296" s="14">
-        <v>3317278.24</v>
+        <v>3245332.24</v>
       </c>
       <c r="R296" s="15">
-        <v>82.15</v>
+        <v>81.83</v>
       </c>
     </row>
     <row r="297" spans="1:18" x14ac:dyDescent="0.25">
@@ -18731,49 +18734,49 @@
         <v>342693877.37</v>
       </c>
       <c r="D297" s="16">
-        <v>0</v>
+        <v>71946</v>
       </c>
       <c r="E297" s="16">
-        <v>0</v>
+        <v>71946</v>
       </c>
       <c r="F297" s="16">
         <v>342693877.37</v>
       </c>
       <c r="G297" s="16">
-        <v>173309351.75</v>
+        <v>185927731.97999999</v>
       </c>
       <c r="H297" s="17">
-        <v>50.57</v>
+        <v>54.25</v>
       </c>
       <c r="I297" s="16">
-        <v>56232675.32</v>
+        <v>53492272.850000001</v>
       </c>
       <c r="J297" s="17">
-        <v>16.41</v>
+        <v>15.61</v>
       </c>
       <c r="K297" s="16">
-        <v>229542027.06999999</v>
+        <v>239420004.83000001</v>
       </c>
       <c r="L297" s="17">
-        <v>66.98</v>
+        <v>69.86</v>
       </c>
       <c r="M297" s="16">
-        <v>113151850.3</v>
+        <v>103273872.54000001</v>
       </c>
       <c r="N297" s="17">
-        <v>33.020000000000003</v>
+        <v>30.14</v>
       </c>
       <c r="O297" s="16">
-        <v>15160281.189999999</v>
+        <v>15494028.390000001</v>
       </c>
       <c r="P297" s="17">
-        <v>4.42</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="Q297" s="16">
-        <v>97991569.109999999</v>
+        <v>87779844.150000006</v>
       </c>
       <c r="R297" s="17">
-        <v>28.59</v>
+        <v>25.61</v>
       </c>
     </row>
     <row r="298" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -18796,40 +18799,40 @@
         <v>46540814</v>
       </c>
       <c r="G298" s="19">
-        <v>22132140.120000001</v>
+        <v>23670542.129999999</v>
       </c>
       <c r="H298" s="20">
-        <v>47.55</v>
+        <v>50.86</v>
       </c>
       <c r="I298" s="19">
-        <v>15887933.67</v>
+        <v>14870696.67</v>
       </c>
       <c r="J298" s="20">
-        <v>34.14</v>
+        <v>31.95</v>
       </c>
       <c r="K298" s="19">
-        <v>38020073.789999999</v>
+        <v>38541238.799999997</v>
       </c>
       <c r="L298" s="20">
-        <v>81.69</v>
+        <v>82.81</v>
       </c>
       <c r="M298" s="19">
-        <v>8520740.2100000009</v>
+        <v>7999575.2000000002</v>
       </c>
       <c r="N298" s="20">
-        <v>18.309999999999999</v>
+        <v>17.190000000000001</v>
       </c>
       <c r="O298" s="19">
-        <v>1305921.6000000001</v>
+        <v>1317521.6000000001</v>
       </c>
       <c r="P298" s="20">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="Q298" s="19">
-        <v>7214818.6100000003</v>
+        <v>6682053.5999999996</v>
       </c>
       <c r="R298" s="20">
-        <v>15.5</v>
+        <v>14.36</v>
       </c>
     </row>
     <row r="299" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -18852,40 +18855,40 @@
         <v>54940200</v>
       </c>
       <c r="G299" s="19">
-        <v>39099135.880000003</v>
+        <v>39899903.969999999</v>
       </c>
       <c r="H299" s="20">
-        <v>71.17</v>
+        <v>72.62</v>
       </c>
       <c r="I299" s="19">
-        <v>6941870.6699999999</v>
+        <v>6393068.6699999999</v>
       </c>
       <c r="J299" s="20">
-        <v>12.64</v>
+        <v>11.64</v>
       </c>
       <c r="K299" s="19">
-        <v>46041006.549999997</v>
+        <v>46292972.640000001</v>
       </c>
       <c r="L299" s="20">
-        <v>83.8</v>
+        <v>84.26</v>
       </c>
       <c r="M299" s="19">
-        <v>8899193.4499999993</v>
+        <v>8647227.3599999994</v>
       </c>
       <c r="N299" s="20">
-        <v>16.2</v>
+        <v>15.74</v>
       </c>
       <c r="O299" s="19">
-        <v>1149422.5</v>
+        <v>1155422.5</v>
       </c>
       <c r="P299" s="20">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="Q299" s="19">
-        <v>7749770.9500000002</v>
+        <v>7491804.8600000003</v>
       </c>
       <c r="R299" s="20">
-        <v>14.11</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="300" spans="1:18" x14ac:dyDescent="0.25">
@@ -18908,40 +18911,40 @@
         <v>9800000</v>
       </c>
       <c r="G300" s="19">
-        <v>5245581.9800000004</v>
+        <v>5515006.6399999997</v>
       </c>
       <c r="H300" s="20">
-        <v>53.53</v>
+        <v>56.28</v>
       </c>
       <c r="I300" s="19">
-        <v>1204232.97</v>
+        <v>961508.31</v>
       </c>
       <c r="J300" s="20">
-        <v>12.29</v>
+        <v>9.81</v>
       </c>
       <c r="K300" s="19">
-        <v>6449814.9500000002</v>
+        <v>6476514.9500000002</v>
       </c>
       <c r="L300" s="20">
-        <v>65.81</v>
+        <v>66.09</v>
       </c>
       <c r="M300" s="19">
-        <v>3350185.05</v>
+        <v>3323485.05</v>
       </c>
       <c r="N300" s="20">
-        <v>34.19</v>
+        <v>33.909999999999997</v>
       </c>
       <c r="O300" s="19">
-        <v>1837551.54</v>
+        <v>2287551.54</v>
       </c>
       <c r="P300" s="20">
-        <v>18.75</v>
+        <v>23.34</v>
       </c>
       <c r="Q300" s="19">
-        <v>1512633.51</v>
+        <v>1035933.51</v>
       </c>
       <c r="R300" s="20">
-        <v>15.44</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="301" spans="1:18" x14ac:dyDescent="0.25">
@@ -18955,49 +18958,49 @@
         <v>101298156.95</v>
       </c>
       <c r="D301" s="19">
-        <v>0</v>
+        <v>71946</v>
       </c>
       <c r="E301" s="19">
         <v>0</v>
       </c>
       <c r="F301" s="19">
-        <v>101298156.95</v>
+        <v>101370102.95</v>
       </c>
       <c r="G301" s="19">
-        <v>26248895.120000001</v>
+        <v>28497772.09</v>
       </c>
       <c r="H301" s="20">
-        <v>25.91</v>
+        <v>28.11</v>
       </c>
       <c r="I301" s="19">
-        <v>20247819.949999999</v>
+        <v>19891917.98</v>
       </c>
       <c r="J301" s="20">
-        <v>19.989999999999998</v>
+        <v>19.62</v>
       </c>
       <c r="K301" s="19">
-        <v>46496715.07</v>
+        <v>48389690.07</v>
       </c>
       <c r="L301" s="20">
-        <v>45.9</v>
+        <v>47.74</v>
       </c>
       <c r="M301" s="19">
-        <v>54801441.880000003</v>
+        <v>52980412.880000003</v>
       </c>
       <c r="N301" s="20">
-        <v>54.1</v>
+        <v>52.26</v>
       </c>
       <c r="O301" s="19">
-        <v>4944593</v>
+        <v>4899593</v>
       </c>
       <c r="P301" s="20">
-        <v>4.88</v>
+        <v>4.83</v>
       </c>
       <c r="Q301" s="19">
-        <v>49856848.880000003</v>
+        <v>48080819.880000003</v>
       </c>
       <c r="R301" s="20">
-        <v>49.22</v>
+        <v>47.43</v>
       </c>
     </row>
     <row r="302" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -19070,34 +19073,34 @@
         <v>0</v>
       </c>
       <c r="E303" s="19">
-        <v>0</v>
+        <v>71946</v>
       </c>
       <c r="F303" s="19">
-        <v>4037940.24</v>
+        <v>3965994.24</v>
       </c>
       <c r="G303" s="19">
         <v>558139.18000000005</v>
       </c>
       <c r="H303" s="20">
-        <v>13.82</v>
+        <v>14.07</v>
       </c>
       <c r="I303" s="19">
         <v>156393.70000000001</v>
       </c>
       <c r="J303" s="20">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="K303" s="19">
         <v>714532.88</v>
       </c>
       <c r="L303" s="20">
-        <v>17.7</v>
+        <v>18.02</v>
       </c>
       <c r="M303" s="19">
-        <v>3323407.36</v>
+        <v>3251461.36</v>
       </c>
       <c r="N303" s="20">
-        <v>82.3</v>
+        <v>81.98</v>
       </c>
       <c r="O303" s="19">
         <v>6129.12</v>
@@ -19106,10 +19109,10 @@
         <v>0.15</v>
       </c>
       <c r="Q303" s="19">
-        <v>3317278.24</v>
+        <v>3245332.24</v>
       </c>
       <c r="R303" s="20">
-        <v>82.15</v>
+        <v>81.83</v>
       </c>
     </row>
     <row r="304" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -19132,40 +19135,40 @@
         <v>119421186</v>
       </c>
       <c r="G304" s="19">
-        <v>80025459.469999999</v>
+        <v>87786367.969999999</v>
       </c>
       <c r="H304" s="20">
-        <v>67.010000000000005</v>
+        <v>73.510000000000005</v>
       </c>
       <c r="I304" s="19">
-        <v>11794424.359999999</v>
+        <v>11218687.52</v>
       </c>
       <c r="J304" s="20">
-        <v>9.8800000000000008</v>
+        <v>9.39</v>
       </c>
       <c r="K304" s="19">
-        <v>91819883.829999998</v>
+        <v>99005055.489999995</v>
       </c>
       <c r="L304" s="20">
-        <v>76.89</v>
+        <v>82.9</v>
       </c>
       <c r="M304" s="19">
-        <v>27601302.170000002</v>
+        <v>20416130.510000002</v>
       </c>
       <c r="N304" s="20">
-        <v>23.11</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="O304" s="19">
-        <v>5916663.4299999997</v>
+        <v>5827810.6299999999</v>
       </c>
       <c r="P304" s="20">
-        <v>4.95</v>
+        <v>4.88</v>
       </c>
       <c r="Q304" s="19">
-        <v>21684638.739999998</v>
+        <v>14588319.880000001</v>
       </c>
       <c r="R304" s="20">
-        <v>18.16</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="305" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -19233,49 +19236,49 @@
         <v>342693877.37</v>
       </c>
       <c r="D306" s="19">
-        <v>0</v>
+        <v>71946</v>
       </c>
       <c r="E306" s="19">
-        <v>0</v>
+        <v>71946</v>
       </c>
       <c r="F306" s="19">
         <v>342693877.37</v>
       </c>
       <c r="G306" s="19">
-        <v>173309351.75</v>
+        <v>185927731.97999999</v>
       </c>
       <c r="H306" s="20">
-        <v>50.57</v>
+        <v>54.25</v>
       </c>
       <c r="I306" s="19">
-        <v>56232675.32</v>
+        <v>53492272.850000001</v>
       </c>
       <c r="J306" s="20">
-        <v>16.41</v>
+        <v>15.61</v>
       </c>
       <c r="K306" s="19">
-        <v>229542027.06999999</v>
+        <v>239420004.83000001</v>
       </c>
       <c r="L306" s="20">
-        <v>66.98</v>
+        <v>69.86</v>
       </c>
       <c r="M306" s="19">
-        <v>113151850.3</v>
+        <v>103273872.54000001</v>
       </c>
       <c r="N306" s="20">
-        <v>33.020000000000003</v>
+        <v>30.14</v>
       </c>
       <c r="O306" s="19">
-        <v>15160281.189999999</v>
+        <v>15494028.390000001</v>
       </c>
       <c r="P306" s="20">
-        <v>4.42</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="Q306" s="19">
-        <v>97991569.109999999</v>
+        <v>87779844.150000006</v>
       </c>
       <c r="R306" s="20">
-        <v>28.59</v>
+        <v>25.61</v>
       </c>
     </row>
     <row r="307" spans="1:18" x14ac:dyDescent="0.25">
@@ -19316,27 +19319,27 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A58F7114-4B5D-4A26-AE65-4A4C52DEC72F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7BA2E36-AFAE-49FE-9111-E1D1F5311A1B}">
   <dimension ref="A1:R84"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.796875" customWidth="1"/>
-    <col min="2" max="2" width="12.796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.8984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.19921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.8984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.8984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.8984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.8984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.3984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.8984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.3984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.796875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.59765625" style="28" customWidth="1"/>
+    <col min="2" max="2" width="12.796875" style="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.8984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.796875" style="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.8984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.8984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.796875" style="28" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.8984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.8984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.3984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.8984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7" style="28" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.796875" style="28" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.3984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.796875" style="28" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7" style="28" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.796875" style="28"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -19350,7 +19353,7 @@
       <c r="F1" s="27"/>
       <c r="G1" s="27"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
         <v>580</v>
       </c>
@@ -19456,16 +19459,16 @@
         <v>1000000</v>
       </c>
       <c r="G6" s="4">
-        <v>747825.74</v>
+        <v>805551.74</v>
       </c>
       <c r="H6" s="5">
-        <v>74.78</v>
+        <v>80.56</v>
       </c>
       <c r="I6" s="4">
-        <v>173268</v>
+        <v>115542</v>
       </c>
       <c r="J6" s="5">
-        <v>17.329999999999998</v>
+        <v>11.55</v>
       </c>
       <c r="K6" s="4">
         <v>921093.74</v>
@@ -19512,16 +19515,16 @@
         <v>1000000</v>
       </c>
       <c r="G7" s="8">
-        <v>747825.74</v>
+        <v>805551.74</v>
       </c>
       <c r="H7" s="9">
-        <v>74.78</v>
+        <v>80.56</v>
       </c>
       <c r="I7" s="8">
-        <v>173268</v>
+        <v>115542</v>
       </c>
       <c r="J7" s="9">
-        <v>17.329999999999998</v>
+        <v>11.55</v>
       </c>
       <c r="K7" s="8">
         <v>921093.74</v>
@@ -19566,28 +19569,28 @@
         <v>1000000</v>
       </c>
       <c r="G8" s="4">
-        <v>511529</v>
+        <v>533379</v>
       </c>
       <c r="H8" s="5">
-        <v>51.15</v>
+        <v>53.34</v>
       </c>
       <c r="I8" s="4">
-        <v>54820</v>
+        <v>5570</v>
       </c>
       <c r="J8" s="5">
-        <v>5.48</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="K8" s="4">
-        <v>566349</v>
+        <v>538949</v>
       </c>
       <c r="L8" s="5">
-        <v>56.63</v>
+        <v>53.89</v>
       </c>
       <c r="M8" s="4">
-        <v>433651</v>
+        <v>461051</v>
       </c>
       <c r="N8" s="5">
-        <v>43.37</v>
+        <v>46.11</v>
       </c>
       <c r="O8" s="4">
         <v>0</v>
@@ -19596,10 +19599,10 @@
         <v>0</v>
       </c>
       <c r="Q8" s="4">
-        <v>433651</v>
+        <v>461051</v>
       </c>
       <c r="R8" s="5">
-        <v>43.37</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -19622,28 +19625,28 @@
         <v>1000000</v>
       </c>
       <c r="G9" s="8">
-        <v>511529</v>
+        <v>533379</v>
       </c>
       <c r="H9" s="9">
-        <v>51.15</v>
+        <v>53.34</v>
       </c>
       <c r="I9" s="8">
-        <v>54820</v>
+        <v>5570</v>
       </c>
       <c r="J9" s="9">
-        <v>5.48</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="K9" s="8">
-        <v>566349</v>
+        <v>538949</v>
       </c>
       <c r="L9" s="9">
-        <v>56.63</v>
+        <v>53.89</v>
       </c>
       <c r="M9" s="8">
-        <v>433651</v>
+        <v>461051</v>
       </c>
       <c r="N9" s="9">
-        <v>43.37</v>
+        <v>46.11</v>
       </c>
       <c r="O9" s="8">
         <v>0</v>
@@ -19652,10 +19655,10 @@
         <v>0</v>
       </c>
       <c r="Q9" s="8">
-        <v>433651</v>
+        <v>461051</v>
       </c>
       <c r="R9" s="9">
-        <v>43.37</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -19676,40 +19679,40 @@
         <v>11720000</v>
       </c>
       <c r="G10" s="4">
-        <v>7582346</v>
+        <v>7901987</v>
       </c>
       <c r="H10" s="5">
-        <v>64.7</v>
+        <v>67.42</v>
       </c>
       <c r="I10" s="4">
-        <v>1861278</v>
+        <v>1671535</v>
       </c>
       <c r="J10" s="5">
-        <v>15.88</v>
+        <v>14.26</v>
       </c>
       <c r="K10" s="4">
-        <v>9443624</v>
+        <v>9573522</v>
       </c>
       <c r="L10" s="5">
-        <v>80.58</v>
+        <v>81.69</v>
       </c>
       <c r="M10" s="4">
-        <v>2276376</v>
+        <v>2146478</v>
       </c>
       <c r="N10" s="5">
-        <v>19.420000000000002</v>
+        <v>18.309999999999999</v>
       </c>
       <c r="O10" s="4">
-        <v>600</v>
+        <v>30600</v>
       </c>
       <c r="P10" s="5">
-        <v>0.01</v>
+        <v>0.26</v>
       </c>
       <c r="Q10" s="4">
-        <v>2275776</v>
+        <v>2115878</v>
       </c>
       <c r="R10" s="5">
-        <v>19.420000000000002</v>
+        <v>18.05</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -19732,40 +19735,40 @@
         <v>11720000</v>
       </c>
       <c r="G11" s="8">
-        <v>7582346</v>
+        <v>7901987</v>
       </c>
       <c r="H11" s="9">
-        <v>64.7</v>
+        <v>67.42</v>
       </c>
       <c r="I11" s="8">
-        <v>1861278</v>
+        <v>1671535</v>
       </c>
       <c r="J11" s="9">
-        <v>15.88</v>
+        <v>14.26</v>
       </c>
       <c r="K11" s="8">
-        <v>9443624</v>
+        <v>9573522</v>
       </c>
       <c r="L11" s="9">
-        <v>80.58</v>
+        <v>81.69</v>
       </c>
       <c r="M11" s="8">
-        <v>2276376</v>
+        <v>2146478</v>
       </c>
       <c r="N11" s="9">
-        <v>19.420000000000002</v>
+        <v>18.309999999999999</v>
       </c>
       <c r="O11" s="8">
-        <v>600</v>
+        <v>30600</v>
       </c>
       <c r="P11" s="9">
-        <v>0.01</v>
+        <v>0.26</v>
       </c>
       <c r="Q11" s="8">
-        <v>2275776</v>
+        <v>2115878</v>
       </c>
       <c r="R11" s="9">
-        <v>19.420000000000002</v>
+        <v>18.05</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -19786,40 +19789,40 @@
         <v>11820000</v>
       </c>
       <c r="G12" s="4">
-        <v>8425693.2899999991</v>
+        <v>8189257.29</v>
       </c>
       <c r="H12" s="5">
-        <v>71.28</v>
+        <v>69.28</v>
       </c>
       <c r="I12" s="4">
-        <v>1310047</v>
+        <v>1385133</v>
       </c>
       <c r="J12" s="5">
-        <v>11.08</v>
+        <v>11.72</v>
       </c>
       <c r="K12" s="4">
-        <v>9735740.2899999991</v>
+        <v>9574390.2899999991</v>
       </c>
       <c r="L12" s="5">
-        <v>82.37</v>
+        <v>81</v>
       </c>
       <c r="M12" s="4">
-        <v>2084259.71</v>
+        <v>2245609.71</v>
       </c>
       <c r="N12" s="5">
-        <v>17.63</v>
+        <v>19</v>
       </c>
       <c r="O12" s="4">
-        <v>80000</v>
+        <v>56000</v>
       </c>
       <c r="P12" s="5">
-        <v>0.68</v>
+        <v>0.47</v>
       </c>
       <c r="Q12" s="4">
-        <v>2004259.71</v>
+        <v>2189609.71</v>
       </c>
       <c r="R12" s="5">
-        <v>16.96</v>
+        <v>18.52</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -19898,40 +19901,40 @@
         <v>10640000</v>
       </c>
       <c r="G14" s="8">
-        <v>7787344.29</v>
+        <v>7550908.29</v>
       </c>
       <c r="H14" s="9">
-        <v>73.19</v>
+        <v>70.97</v>
       </c>
       <c r="I14" s="8">
-        <v>1033047</v>
+        <v>1108133</v>
       </c>
       <c r="J14" s="9">
-        <v>9.7100000000000009</v>
+        <v>10.41</v>
       </c>
       <c r="K14" s="8">
-        <v>8820391.2899999991</v>
+        <v>8659041.2899999991</v>
       </c>
       <c r="L14" s="9">
-        <v>82.9</v>
+        <v>81.38</v>
       </c>
       <c r="M14" s="8">
-        <v>1819608.71</v>
+        <v>1980958.71</v>
       </c>
       <c r="N14" s="9">
-        <v>17.100000000000001</v>
+        <v>18.62</v>
       </c>
       <c r="O14" s="8">
-        <v>80000</v>
+        <v>56000</v>
       </c>
       <c r="P14" s="9">
-        <v>0.75</v>
+        <v>0.53</v>
       </c>
       <c r="Q14" s="8">
-        <v>1739608.71</v>
+        <v>1924958.71</v>
       </c>
       <c r="R14" s="9">
-        <v>16.350000000000001</v>
+        <v>18.09</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -19952,28 +19955,28 @@
         <v>11840200</v>
       </c>
       <c r="G15" s="4">
-        <v>8948192.8599999994</v>
+        <v>9119604.8599999994</v>
       </c>
       <c r="H15" s="5">
-        <v>75.569999999999993</v>
+        <v>77.02</v>
       </c>
       <c r="I15" s="4">
-        <v>1762817.67</v>
+        <v>1645820.67</v>
       </c>
       <c r="J15" s="5">
-        <v>14.89</v>
+        <v>13.9</v>
       </c>
       <c r="K15" s="4">
-        <v>10711010.529999999</v>
+        <v>10765425.529999999</v>
       </c>
       <c r="L15" s="5">
-        <v>90.46</v>
+        <v>90.92</v>
       </c>
       <c r="M15" s="4">
-        <v>1129189.47</v>
+        <v>1074774.47</v>
       </c>
       <c r="N15" s="5">
-        <v>9.5399999999999991</v>
+        <v>9.08</v>
       </c>
       <c r="O15" s="4">
         <v>144801.1</v>
@@ -19982,13 +19985,13 @@
         <v>1.22</v>
       </c>
       <c r="Q15" s="4">
-        <v>984388.37</v>
+        <v>929973.37</v>
       </c>
       <c r="R15" s="5">
-        <v>8.31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
+        <v>7.85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>75</v>
       </c>
@@ -20008,28 +20011,28 @@
         <v>500000</v>
       </c>
       <c r="G16" s="8">
-        <v>357667.9</v>
+        <v>471112.9</v>
       </c>
       <c r="H16" s="9">
-        <v>71.53</v>
+        <v>94.22</v>
       </c>
       <c r="I16" s="8">
-        <v>116245</v>
+        <v>2600</v>
       </c>
       <c r="J16" s="9">
-        <v>23.25</v>
+        <v>0.52</v>
       </c>
       <c r="K16" s="8">
-        <v>473912.9</v>
+        <v>473712.9</v>
       </c>
       <c r="L16" s="9">
-        <v>94.78</v>
+        <v>94.74</v>
       </c>
       <c r="M16" s="8">
-        <v>26087.1</v>
+        <v>26287.1</v>
       </c>
       <c r="N16" s="9">
-        <v>5.22</v>
+        <v>5.26</v>
       </c>
       <c r="O16" s="8">
         <v>4721.6000000000004</v>
@@ -20038,10 +20041,10 @@
         <v>0.94</v>
       </c>
       <c r="Q16" s="8">
-        <v>21365.5</v>
+        <v>21565.5</v>
       </c>
       <c r="R16" s="9">
-        <v>4.2699999999999996</v>
+        <v>4.3099999999999996</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -20064,28 +20067,28 @@
         <v>11340200</v>
       </c>
       <c r="G17" s="8">
-        <v>8590524.9600000009</v>
+        <v>8648491.9600000009</v>
       </c>
       <c r="H17" s="9">
-        <v>75.75</v>
+        <v>76.260000000000005</v>
       </c>
       <c r="I17" s="8">
-        <v>1646572.67</v>
+        <v>1643220.67</v>
       </c>
       <c r="J17" s="9">
-        <v>14.52</v>
+        <v>14.49</v>
       </c>
       <c r="K17" s="8">
-        <v>10237097.630000001</v>
+        <v>10291712.630000001</v>
       </c>
       <c r="L17" s="9">
-        <v>90.27</v>
+        <v>90.75</v>
       </c>
       <c r="M17" s="8">
-        <v>1103102.3700000001</v>
+        <v>1048487.37</v>
       </c>
       <c r="N17" s="9">
-        <v>9.73</v>
+        <v>9.25</v>
       </c>
       <c r="O17" s="8">
         <v>140079.5</v>
@@ -20094,10 +20097,10 @@
         <v>1.24</v>
       </c>
       <c r="Q17" s="8">
-        <v>963022.87</v>
+        <v>908407.87</v>
       </c>
       <c r="R17" s="9">
-        <v>8.49</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -20118,28 +20121,28 @@
         <v>7820000</v>
       </c>
       <c r="G18" s="4">
-        <v>5153380.5999999996</v>
+        <v>5044648.3</v>
       </c>
       <c r="H18" s="5">
-        <v>65.900000000000006</v>
+        <v>64.510000000000005</v>
       </c>
       <c r="I18" s="4">
-        <v>622869</v>
+        <v>1043294</v>
       </c>
       <c r="J18" s="5">
-        <v>7.97</v>
+        <v>13.34</v>
       </c>
       <c r="K18" s="4">
-        <v>5776249.5999999996</v>
+        <v>6087942.2999999998</v>
       </c>
       <c r="L18" s="5">
-        <v>73.87</v>
+        <v>77.849999999999994</v>
       </c>
       <c r="M18" s="4">
-        <v>2043750.3999999999</v>
+        <v>1732057.7</v>
       </c>
       <c r="N18" s="5">
-        <v>26.13</v>
+        <v>22.15</v>
       </c>
       <c r="O18" s="4">
         <v>550000</v>
@@ -20148,13 +20151,13 @@
         <v>7.03</v>
       </c>
       <c r="Q18" s="4">
-        <v>1493750.4</v>
+        <v>1182057.7</v>
       </c>
       <c r="R18" s="5">
-        <v>19.100000000000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+        <v>15.12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>161</v>
       </c>
@@ -20174,28 +20177,28 @@
         <v>7820000</v>
       </c>
       <c r="G19" s="8">
-        <v>5153380.5999999996</v>
+        <v>5044648.3</v>
       </c>
       <c r="H19" s="9">
-        <v>65.900000000000006</v>
+        <v>64.510000000000005</v>
       </c>
       <c r="I19" s="8">
-        <v>622869</v>
+        <v>1043294</v>
       </c>
       <c r="J19" s="9">
-        <v>7.97</v>
+        <v>13.34</v>
       </c>
       <c r="K19" s="8">
-        <v>5776249.5999999996</v>
+        <v>6087942.2999999998</v>
       </c>
       <c r="L19" s="9">
-        <v>73.87</v>
+        <v>77.849999999999994</v>
       </c>
       <c r="M19" s="8">
-        <v>2043750.3999999999</v>
+        <v>1732057.7</v>
       </c>
       <c r="N19" s="9">
-        <v>26.13</v>
+        <v>22.15</v>
       </c>
       <c r="O19" s="8">
         <v>550000</v>
@@ -20204,10 +20207,10 @@
         <v>7.03</v>
       </c>
       <c r="Q19" s="8">
-        <v>1493750.4</v>
+        <v>1182057.7</v>
       </c>
       <c r="R19" s="9">
-        <v>19.100000000000001</v>
+        <v>15.12</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -20228,28 +20231,28 @@
         <v>13420000</v>
       </c>
       <c r="G20" s="4">
-        <v>9985540.0299999993</v>
+        <v>10753868.42</v>
       </c>
       <c r="H20" s="5">
-        <v>74.41</v>
+        <v>80.13</v>
       </c>
       <c r="I20" s="4">
-        <v>1778104</v>
+        <v>926886</v>
       </c>
       <c r="J20" s="5">
-        <v>13.25</v>
+        <v>6.91</v>
       </c>
       <c r="K20" s="4">
-        <v>11763644.029999999</v>
+        <v>11680754.42</v>
       </c>
       <c r="L20" s="5">
-        <v>87.66</v>
+        <v>87.04</v>
       </c>
       <c r="M20" s="4">
-        <v>1656355.97</v>
+        <v>1739245.58</v>
       </c>
       <c r="N20" s="5">
-        <v>12.34</v>
+        <v>12.96</v>
       </c>
       <c r="O20" s="4">
         <v>378743</v>
@@ -20258,10 +20261,10 @@
         <v>2.82</v>
       </c>
       <c r="Q20" s="4">
-        <v>1277612.97</v>
+        <v>1360502.58</v>
       </c>
       <c r="R20" s="5">
-        <v>9.52</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -20284,28 +20287,28 @@
         <v>13420000</v>
       </c>
       <c r="G21" s="8">
-        <v>9985540.0299999993</v>
+        <v>10753868.42</v>
       </c>
       <c r="H21" s="9">
-        <v>74.41</v>
+        <v>80.13</v>
       </c>
       <c r="I21" s="8">
-        <v>1778104</v>
+        <v>926886</v>
       </c>
       <c r="J21" s="9">
-        <v>13.25</v>
+        <v>6.91</v>
       </c>
       <c r="K21" s="8">
-        <v>11763644.029999999</v>
+        <v>11680754.42</v>
       </c>
       <c r="L21" s="9">
-        <v>87.66</v>
+        <v>87.04</v>
       </c>
       <c r="M21" s="8">
-        <v>1656355.97</v>
+        <v>1739245.58</v>
       </c>
       <c r="N21" s="9">
-        <v>12.34</v>
+        <v>12.96</v>
       </c>
       <c r="O21" s="8">
         <v>378743</v>
@@ -20314,10 +20317,10 @@
         <v>2.82</v>
       </c>
       <c r="Q21" s="8">
-        <v>1277612.97</v>
+        <v>1360502.58</v>
       </c>
       <c r="R21" s="9">
-        <v>9.52</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -20338,28 +20341,28 @@
         <v>107227000</v>
       </c>
       <c r="G22" s="4">
-        <v>75270905.730000004</v>
+        <v>82678661.590000004</v>
       </c>
       <c r="H22" s="5">
-        <v>70.2</v>
+        <v>77.11</v>
       </c>
       <c r="I22" s="4">
-        <v>6054591.9199999999</v>
+        <v>5768949.9199999999</v>
       </c>
       <c r="J22" s="5">
-        <v>5.65</v>
+        <v>5.38</v>
       </c>
       <c r="K22" s="4">
-        <v>81325497.650000006</v>
+        <v>88447611.510000005</v>
       </c>
       <c r="L22" s="5">
-        <v>75.84</v>
+        <v>82.49</v>
       </c>
       <c r="M22" s="4">
-        <v>25901502.350000001</v>
+        <v>18779388.489999998</v>
       </c>
       <c r="N22" s="5">
-        <v>24.16</v>
+        <v>17.510000000000002</v>
       </c>
       <c r="O22" s="4">
         <v>4946965.87</v>
@@ -20368,10 +20371,10 @@
         <v>4.6100000000000003</v>
       </c>
       <c r="Q22" s="4">
-        <v>20954536.48</v>
+        <v>13832422.619999999</v>
       </c>
       <c r="R22" s="5">
-        <v>19.54</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -20394,28 +20397,28 @@
         <v>29200000</v>
       </c>
       <c r="G23" s="8">
-        <v>17363324.93</v>
+        <v>17566256.93</v>
       </c>
       <c r="H23" s="9">
-        <v>59.46</v>
+        <v>60.16</v>
       </c>
       <c r="I23" s="8">
-        <v>5858944.1900000004</v>
+        <v>5658302.1900000004</v>
       </c>
       <c r="J23" s="9">
-        <v>20.059999999999999</v>
+        <v>19.38</v>
       </c>
       <c r="K23" s="8">
-        <v>23222269.120000001</v>
+        <v>23224559.120000001</v>
       </c>
       <c r="L23" s="9">
-        <v>79.53</v>
+        <v>79.540000000000006</v>
       </c>
       <c r="M23" s="8">
-        <v>5977730.8799999999</v>
+        <v>5975440.8799999999</v>
       </c>
       <c r="N23" s="9">
-        <v>20.47</v>
+        <v>20.46</v>
       </c>
       <c r="O23" s="8">
         <v>4945423.37</v>
@@ -20424,10 +20427,10 @@
         <v>16.940000000000001</v>
       </c>
       <c r="Q23" s="8">
-        <v>1032307.51</v>
+        <v>1030017.51</v>
       </c>
       <c r="R23" s="9">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="24" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -20450,28 +20453,28 @@
         <v>78027000</v>
       </c>
       <c r="G24" s="8">
-        <v>57907580.799999997</v>
+        <v>65112404.659999996</v>
       </c>
       <c r="H24" s="9">
-        <v>74.209999999999994</v>
+        <v>83.45</v>
       </c>
       <c r="I24" s="8">
-        <v>195647.73</v>
+        <v>110647.73</v>
       </c>
       <c r="J24" s="9">
-        <v>0.25</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="K24" s="8">
-        <v>58103228.530000001</v>
+        <v>65223052.390000001</v>
       </c>
       <c r="L24" s="9">
-        <v>74.47</v>
+        <v>83.59</v>
       </c>
       <c r="M24" s="8">
-        <v>19923771.469999999</v>
+        <v>12803947.609999999</v>
       </c>
       <c r="N24" s="9">
-        <v>25.53</v>
+        <v>16.41</v>
       </c>
       <c r="O24" s="8">
         <v>1542.5</v>
@@ -20480,10 +20483,10 @@
         <v>0</v>
       </c>
       <c r="Q24" s="8">
-        <v>19922228.969999999</v>
+        <v>12802405.109999999</v>
       </c>
       <c r="R24" s="9">
-        <v>25.53</v>
+        <v>16.41</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -20560,28 +20563,28 @@
         <v>4260000</v>
       </c>
       <c r="G26" s="4">
-        <v>1700370.43</v>
+        <v>2025237.43</v>
       </c>
       <c r="H26" s="5">
-        <v>39.909999999999997</v>
+        <v>47.54</v>
       </c>
       <c r="I26" s="4">
-        <v>848371.67</v>
+        <v>502696.67</v>
       </c>
       <c r="J26" s="5">
-        <v>19.91</v>
+        <v>11.8</v>
       </c>
       <c r="K26" s="4">
-        <v>2548742.1</v>
+        <v>2527934.1</v>
       </c>
       <c r="L26" s="5">
-        <v>59.83</v>
+        <v>59.34</v>
       </c>
       <c r="M26" s="4">
-        <v>1711257.9</v>
+        <v>1732065.9</v>
       </c>
       <c r="N26" s="5">
-        <v>40.17</v>
+        <v>40.659999999999997</v>
       </c>
       <c r="O26" s="4">
         <v>274000</v>
@@ -20590,10 +20593,10 @@
         <v>6.43</v>
       </c>
       <c r="Q26" s="4">
-        <v>1437257.9</v>
+        <v>1458065.9</v>
       </c>
       <c r="R26" s="5">
-        <v>33.74</v>
+        <v>34.229999999999997</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -20616,28 +20619,28 @@
         <v>4260000</v>
       </c>
       <c r="G27" s="8">
-        <v>1700370.43</v>
+        <v>2025237.43</v>
       </c>
       <c r="H27" s="9">
-        <v>39.909999999999997</v>
+        <v>47.54</v>
       </c>
       <c r="I27" s="8">
-        <v>848371.67</v>
+        <v>502696.67</v>
       </c>
       <c r="J27" s="9">
-        <v>19.91</v>
+        <v>11.8</v>
       </c>
       <c r="K27" s="8">
-        <v>2548742.1</v>
+        <v>2527934.1</v>
       </c>
       <c r="L27" s="9">
-        <v>59.83</v>
+        <v>59.34</v>
       </c>
       <c r="M27" s="8">
-        <v>1711257.9</v>
+        <v>1732065.9</v>
       </c>
       <c r="N27" s="9">
-        <v>40.17</v>
+        <v>40.659999999999997</v>
       </c>
       <c r="O27" s="8">
         <v>274000</v>
@@ -20646,10 +20649,10 @@
         <v>6.43</v>
       </c>
       <c r="Q27" s="8">
-        <v>1437257.9</v>
+        <v>1458065.9</v>
       </c>
       <c r="R27" s="9">
-        <v>33.74</v>
+        <v>34.229999999999997</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
@@ -20670,40 +20673,40 @@
         <v>60595000</v>
       </c>
       <c r="G28" s="4">
-        <v>28176533.77</v>
+        <v>29819625.079999998</v>
       </c>
       <c r="H28" s="5">
-        <v>46.5</v>
+        <v>49.21</v>
       </c>
       <c r="I28" s="4">
-        <v>21362294.41</v>
+        <v>20378533.91</v>
       </c>
       <c r="J28" s="5">
-        <v>35.25</v>
+        <v>33.630000000000003</v>
       </c>
       <c r="K28" s="4">
-        <v>49538828.18</v>
+        <v>50198158.990000002</v>
       </c>
       <c r="L28" s="5">
-        <v>81.75</v>
+        <v>82.84</v>
       </c>
       <c r="M28" s="4">
-        <v>11056171.82</v>
+        <v>10396841.01</v>
       </c>
       <c r="N28" s="5">
-        <v>18.25</v>
+        <v>17.16</v>
       </c>
       <c r="O28" s="4">
-        <v>3834449.1</v>
+        <v>4207196.3</v>
       </c>
       <c r="P28" s="5">
-        <v>6.33</v>
+        <v>6.94</v>
       </c>
       <c r="Q28" s="4">
-        <v>7221722.7199999997</v>
+        <v>6189644.71</v>
       </c>
       <c r="R28" s="5">
-        <v>11.92</v>
+        <v>10.210000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -20726,40 +20729,40 @@
         <v>37235000</v>
       </c>
       <c r="G29" s="8">
-        <v>17247376.120000001</v>
+        <v>18197586.129999999</v>
       </c>
       <c r="H29" s="9">
-        <v>46.32</v>
+        <v>48.87</v>
       </c>
       <c r="I29" s="8">
-        <v>14058219</v>
+        <v>13653617</v>
       </c>
       <c r="J29" s="9">
-        <v>37.76</v>
+        <v>36.67</v>
       </c>
       <c r="K29" s="8">
-        <v>31305595.120000001</v>
+        <v>31851203.129999999</v>
       </c>
       <c r="L29" s="9">
-        <v>84.08</v>
+        <v>85.54</v>
       </c>
       <c r="M29" s="8">
-        <v>5929404.8799999999</v>
+        <v>5383796.8700000001</v>
       </c>
       <c r="N29" s="9">
-        <v>15.92</v>
+        <v>14.46</v>
       </c>
       <c r="O29" s="8">
-        <v>1027200</v>
+        <v>1038800</v>
       </c>
       <c r="P29" s="9">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="Q29" s="8">
-        <v>4902204.88</v>
+        <v>4344996.87</v>
       </c>
       <c r="R29" s="9">
-        <v>13.17</v>
+        <v>11.67</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -20788,22 +20791,22 @@
         <v>81.48</v>
       </c>
       <c r="I30" s="8">
-        <v>151840</v>
+        <v>150000</v>
       </c>
       <c r="J30" s="9">
-        <v>20.170000000000002</v>
+        <v>19.920000000000002</v>
       </c>
       <c r="K30" s="8">
-        <v>765290</v>
+        <v>763450</v>
       </c>
       <c r="L30" s="9">
-        <v>101.65</v>
+        <v>101.4</v>
       </c>
       <c r="M30" s="8">
-        <v>-12390</v>
+        <v>-10550</v>
       </c>
       <c r="N30" s="9">
-        <v>-1.65</v>
+        <v>-1.4</v>
       </c>
       <c r="O30" s="8">
         <v>0</v>
@@ -20812,10 +20815,10 @@
         <v>0</v>
       </c>
       <c r="Q30" s="8">
-        <v>-12390</v>
+        <v>-10550</v>
       </c>
       <c r="R30" s="9">
-        <v>-1.65</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -20838,28 +20841,28 @@
         <v>2612914</v>
       </c>
       <c r="G31" s="8">
-        <v>1574926.67</v>
+        <v>1724806.67</v>
       </c>
       <c r="H31" s="9">
-        <v>60.27</v>
+        <v>66.010000000000005</v>
       </c>
       <c r="I31" s="8">
-        <v>436258</v>
+        <v>284783</v>
       </c>
       <c r="J31" s="9">
-        <v>16.7</v>
+        <v>10.9</v>
       </c>
       <c r="K31" s="8">
-        <v>2011184.67</v>
+        <v>2009589.67</v>
       </c>
       <c r="L31" s="9">
-        <v>76.97</v>
+        <v>76.91</v>
       </c>
       <c r="M31" s="8">
-        <v>601729.32999999996</v>
+        <v>603324.32999999996</v>
       </c>
       <c r="N31" s="9">
-        <v>23.03</v>
+        <v>23.09</v>
       </c>
       <c r="O31" s="8">
         <v>0</v>
@@ -20868,10 +20871,10 @@
         <v>0</v>
       </c>
       <c r="Q31" s="8">
-        <v>601729.32999999996</v>
+        <v>603324.32999999996</v>
       </c>
       <c r="R31" s="9">
-        <v>23.03</v>
+        <v>23.09</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -20894,40 +20897,40 @@
         <v>9800000</v>
       </c>
       <c r="G32" s="8">
-        <v>5245581.9800000004</v>
+        <v>5515006.6399999997</v>
       </c>
       <c r="H32" s="9">
-        <v>53.53</v>
+        <v>56.28</v>
       </c>
       <c r="I32" s="8">
-        <v>1204232.97</v>
+        <v>961508.31</v>
       </c>
       <c r="J32" s="9">
-        <v>12.29</v>
+        <v>9.81</v>
       </c>
       <c r="K32" s="8">
-        <v>6449814.9500000002</v>
+        <v>6476514.9500000002</v>
       </c>
       <c r="L32" s="9">
-        <v>65.81</v>
+        <v>66.09</v>
       </c>
       <c r="M32" s="8">
-        <v>3350185.05</v>
+        <v>3323485.05</v>
       </c>
       <c r="N32" s="9">
-        <v>34.19</v>
+        <v>33.909999999999997</v>
       </c>
       <c r="O32" s="8">
-        <v>1837551.54</v>
+        <v>2287551.54</v>
       </c>
       <c r="P32" s="9">
-        <v>18.75</v>
+        <v>23.34</v>
       </c>
       <c r="Q32" s="8">
-        <v>1512633.51</v>
+        <v>1035933.51</v>
       </c>
       <c r="R32" s="9">
-        <v>15.44</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="33" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -20950,40 +20953,40 @@
         <v>10194186</v>
       </c>
       <c r="G33" s="8">
-        <v>3495199</v>
+        <v>3768775.64</v>
       </c>
       <c r="H33" s="9">
-        <v>34.29</v>
+        <v>36.97</v>
       </c>
       <c r="I33" s="8">
-        <v>5511744.4400000004</v>
+        <v>5328625.5999999996</v>
       </c>
       <c r="J33" s="9">
-        <v>54.07</v>
+        <v>52.27</v>
       </c>
       <c r="K33" s="8">
-        <v>9006943.4399999995</v>
+        <v>9097401.2400000002</v>
       </c>
       <c r="L33" s="9">
-        <v>88.35</v>
+        <v>89.24</v>
       </c>
       <c r="M33" s="8">
-        <v>1187242.56</v>
+        <v>1096784.76</v>
       </c>
       <c r="N33" s="9">
-        <v>11.65</v>
+        <v>10.76</v>
       </c>
       <c r="O33" s="8">
-        <v>969697.56</v>
+        <v>880844.76</v>
       </c>
       <c r="P33" s="9">
-        <v>9.51</v>
+        <v>8.64</v>
       </c>
       <c r="Q33" s="8">
-        <v>217545</v>
+        <v>215940</v>
       </c>
       <c r="R33" s="9">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
@@ -21004,40 +21007,40 @@
         <v>230702200</v>
       </c>
       <c r="G34" s="14">
-        <v>146502317.44999999</v>
+        <v>156871820.71000001</v>
       </c>
       <c r="H34" s="15">
-        <v>63.5</v>
+        <v>68</v>
       </c>
       <c r="I34" s="14">
-        <v>35828461.670000002</v>
+        <v>33443961.170000002</v>
       </c>
       <c r="J34" s="15">
-        <v>15.53</v>
+        <v>14.5</v>
       </c>
       <c r="K34" s="14">
-        <v>182330779.12</v>
+        <v>190315781.88</v>
       </c>
       <c r="L34" s="15">
-        <v>79.03</v>
+        <v>82.49</v>
       </c>
       <c r="M34" s="14">
-        <v>48371420.880000003</v>
+        <v>40386418.119999997</v>
       </c>
       <c r="N34" s="15">
-        <v>20.97</v>
+        <v>17.510000000000002</v>
       </c>
       <c r="O34" s="14">
-        <v>10209559.07</v>
+        <v>10588306.27</v>
       </c>
       <c r="P34" s="15">
-        <v>4.43</v>
+        <v>4.59</v>
       </c>
       <c r="Q34" s="14">
-        <v>38161861.810000002</v>
+        <v>29798111.850000001</v>
       </c>
       <c r="R34" s="15">
-        <v>16.54</v>
+        <v>12.92</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
@@ -21094,7 +21097,7 @@
         <v>54.44</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="66" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>279</v>
       </c>
@@ -21204,7 +21207,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>236</v>
       </c>
@@ -21278,7 +21281,7 @@
         <v>2936503.78</v>
       </c>
       <c r="G39" s="4">
-        <v>1697264.18</v>
+        <v>1697269.18</v>
       </c>
       <c r="H39" s="5">
         <v>57.8</v>
@@ -21290,13 +21293,13 @@
         <v>2.75</v>
       </c>
       <c r="K39" s="4">
-        <v>1778149.18</v>
+        <v>1778154.18</v>
       </c>
       <c r="L39" s="5">
         <v>60.55</v>
       </c>
       <c r="M39" s="4">
-        <v>1158354.6000000001</v>
+        <v>1158349.6000000001</v>
       </c>
       <c r="N39" s="5">
         <v>39.450000000000003</v>
@@ -21308,13 +21311,13 @@
         <v>0</v>
       </c>
       <c r="Q39" s="4">
-        <v>1158354.6000000001</v>
+        <v>1158349.6000000001</v>
       </c>
       <c r="R39" s="5">
         <v>39.450000000000003</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
         <v>307</v>
       </c>
@@ -21334,7 +21337,7 @@
         <v>2936503.78</v>
       </c>
       <c r="G40" s="8">
-        <v>1697264.18</v>
+        <v>1697269.18</v>
       </c>
       <c r="H40" s="9">
         <v>57.8</v>
@@ -21346,13 +21349,13 @@
         <v>2.75</v>
       </c>
       <c r="K40" s="8">
-        <v>1778149.18</v>
+        <v>1778154.18</v>
       </c>
       <c r="L40" s="9">
         <v>60.55</v>
       </c>
       <c r="M40" s="8">
-        <v>1158354.6000000001</v>
+        <v>1158349.6000000001</v>
       </c>
       <c r="N40" s="9">
         <v>39.450000000000003</v>
@@ -21364,7 +21367,7 @@
         <v>0</v>
       </c>
       <c r="Q40" s="8">
-        <v>1158354.6000000001</v>
+        <v>1158349.6000000001</v>
       </c>
       <c r="R40" s="9">
         <v>39.450000000000003</v>
@@ -21379,49 +21382,49 @@
         <v>22528181.809999999</v>
       </c>
       <c r="D41" s="4">
-        <v>0</v>
+        <v>71946</v>
       </c>
       <c r="E41" s="4">
         <v>0</v>
       </c>
       <c r="F41" s="4">
-        <v>22528181.809999999</v>
+        <v>22600127.809999999</v>
       </c>
       <c r="G41" s="4">
-        <v>8253518.7300000004</v>
+        <v>9297468.7300000004</v>
       </c>
       <c r="H41" s="5">
-        <v>36.64</v>
+        <v>41.14</v>
       </c>
       <c r="I41" s="4">
-        <v>3166815.72</v>
+        <v>3376985.72</v>
       </c>
       <c r="J41" s="5">
-        <v>14.06</v>
+        <v>14.94</v>
       </c>
       <c r="K41" s="4">
-        <v>11420334.449999999</v>
+        <v>12674454.449999999</v>
       </c>
       <c r="L41" s="5">
-        <v>50.69</v>
+        <v>56.08</v>
       </c>
       <c r="M41" s="4">
-        <v>11107847.359999999</v>
+        <v>9925673.3599999994</v>
       </c>
       <c r="N41" s="5">
-        <v>49.31</v>
+        <v>43.92</v>
       </c>
       <c r="O41" s="4">
         <v>1182093</v>
       </c>
       <c r="P41" s="5">
-        <v>5.25</v>
+        <v>5.23</v>
       </c>
       <c r="Q41" s="4">
-        <v>9925754.3599999994</v>
+        <v>8743580.3599999994</v>
       </c>
       <c r="R41" s="5">
-        <v>44.06</v>
+        <v>38.69</v>
       </c>
     </row>
     <row r="42" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -21435,52 +21438,52 @@
         <v>7768581.8099999996</v>
       </c>
       <c r="D42" s="8">
-        <v>0</v>
+        <v>71946</v>
       </c>
       <c r="E42" s="8">
         <v>0</v>
       </c>
       <c r="F42" s="8">
-        <v>7768581.8099999996</v>
+        <v>7840527.8099999996</v>
       </c>
       <c r="G42" s="8">
-        <v>5166723.29</v>
+        <v>5771723.29</v>
       </c>
       <c r="H42" s="9">
-        <v>66.510000000000005</v>
+        <v>73.61</v>
       </c>
       <c r="I42" s="8">
-        <v>1693912.16</v>
+        <v>999782.16</v>
       </c>
       <c r="J42" s="9">
-        <v>21.8</v>
+        <v>12.75</v>
       </c>
       <c r="K42" s="8">
-        <v>6860635.4500000002</v>
+        <v>6771505.4500000002</v>
       </c>
       <c r="L42" s="9">
-        <v>88.31</v>
+        <v>86.37</v>
       </c>
       <c r="M42" s="8">
-        <v>907946.36</v>
+        <v>1069022.3600000001</v>
       </c>
       <c r="N42" s="9">
-        <v>11.69</v>
+        <v>13.63</v>
       </c>
       <c r="O42" s="8">
         <v>106945</v>
       </c>
       <c r="P42" s="9">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Q42" s="8">
-        <v>801001.36</v>
+        <v>962077.36</v>
       </c>
       <c r="R42" s="9">
-        <v>10.31</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" ht="66" x14ac:dyDescent="0.25">
+        <v>12.27</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
         <v>500</v>
       </c>
@@ -21500,28 +21503,28 @@
         <v>12554100</v>
       </c>
       <c r="G43" s="8">
-        <v>3086795.44</v>
+        <v>3499420.44</v>
       </c>
       <c r="H43" s="9">
-        <v>24.59</v>
+        <v>27.87</v>
       </c>
       <c r="I43" s="8">
-        <v>1394828.56</v>
+        <v>1152503.56</v>
       </c>
       <c r="J43" s="9">
-        <v>11.11</v>
+        <v>9.18</v>
       </c>
       <c r="K43" s="8">
-        <v>4481624</v>
+        <v>4651924</v>
       </c>
       <c r="L43" s="9">
-        <v>35.700000000000003</v>
+        <v>37.06</v>
       </c>
       <c r="M43" s="8">
-        <v>8072476</v>
+        <v>7902176</v>
       </c>
       <c r="N43" s="9">
-        <v>64.3</v>
+        <v>62.94</v>
       </c>
       <c r="O43" s="8">
         <v>715148</v>
@@ -21530,13 +21533,13 @@
         <v>5.7</v>
       </c>
       <c r="Q43" s="8">
-        <v>7357328</v>
+        <v>7187028</v>
       </c>
       <c r="R43" s="9">
-        <v>58.6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+        <v>57.25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>541</v>
       </c>
@@ -21556,28 +21559,28 @@
         <v>2205500</v>
       </c>
       <c r="G44" s="8">
-        <v>0</v>
+        <v>26325</v>
       </c>
       <c r="H44" s="9">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="I44" s="8">
-        <v>78075</v>
+        <v>1224700</v>
       </c>
       <c r="J44" s="9">
-        <v>3.54</v>
+        <v>55.53</v>
       </c>
       <c r="K44" s="8">
-        <v>78075</v>
+        <v>1251025</v>
       </c>
       <c r="L44" s="9">
-        <v>3.54</v>
+        <v>56.72</v>
       </c>
       <c r="M44" s="8">
-        <v>2127425</v>
+        <v>954475</v>
       </c>
       <c r="N44" s="9">
-        <v>96.46</v>
+        <v>43.28</v>
       </c>
       <c r="O44" s="8">
         <v>360000</v>
@@ -21586,10 +21589,10 @@
         <v>16.32</v>
       </c>
       <c r="Q44" s="8">
-        <v>1767425</v>
+        <v>594475</v>
       </c>
       <c r="R44" s="9">
-        <v>80.14</v>
+        <v>26.95</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
@@ -21646,7 +21649,7 @@
         <v>82.25</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>488</v>
       </c>
@@ -21776,43 +21779,43 @@
         <v>72788490.920000002</v>
       </c>
       <c r="G48" s="4">
-        <v>15926382.16</v>
+        <v>17131304.129999999</v>
       </c>
       <c r="H48" s="5">
-        <v>21.88</v>
+        <v>23.54</v>
       </c>
       <c r="I48" s="4">
-        <v>17000109.23</v>
+        <v>16434037.26</v>
       </c>
       <c r="J48" s="5">
-        <v>23.36</v>
+        <v>22.58</v>
       </c>
       <c r="K48" s="4">
-        <v>32926491.390000001</v>
+        <v>33565341.390000001</v>
       </c>
       <c r="L48" s="5">
-        <v>45.24</v>
+        <v>46.11</v>
       </c>
       <c r="M48" s="4">
-        <v>39861999.530000001</v>
+        <v>39223149.530000001</v>
       </c>
       <c r="N48" s="5">
-        <v>54.76</v>
+        <v>53.89</v>
       </c>
       <c r="O48" s="4">
-        <v>3642500</v>
+        <v>3597500</v>
       </c>
       <c r="P48" s="5">
-        <v>5</v>
+        <v>4.9400000000000004</v>
       </c>
       <c r="Q48" s="4">
-        <v>36219499.530000001</v>
+        <v>35625649.530000001</v>
       </c>
       <c r="R48" s="5">
-        <v>49.76</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
+        <v>48.94</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="105.6" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>248</v>
       </c>
@@ -21980,7 +21983,7 @@
         <v>90.15</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="66" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>317</v>
       </c>
@@ -22000,7 +22003,7 @@
         <v>1900050</v>
       </c>
       <c r="G52" s="8">
-        <v>1287607.6399999999</v>
+        <v>1287592.6399999999</v>
       </c>
       <c r="H52" s="9">
         <v>67.77</v>
@@ -22012,13 +22015,13 @@
         <v>9.2799999999999994</v>
       </c>
       <c r="K52" s="8">
-        <v>1463852.64</v>
+        <v>1463837.64</v>
       </c>
       <c r="L52" s="9">
         <v>77.040000000000006</v>
       </c>
       <c r="M52" s="8">
-        <v>436197.36</v>
+        <v>436212.36</v>
       </c>
       <c r="N52" s="9">
         <v>22.96</v>
@@ -22030,13 +22033,13 @@
         <v>0</v>
       </c>
       <c r="Q52" s="8">
-        <v>436197.36</v>
+        <v>436212.36</v>
       </c>
       <c r="R52" s="9">
         <v>22.96</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" ht="105.6" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
         <v>333</v>
       </c>
@@ -22062,22 +22065,22 @@
         <v>14.6</v>
       </c>
       <c r="I53" s="8">
-        <v>5409905</v>
+        <v>5403925</v>
       </c>
       <c r="J53" s="9">
-        <v>60.61</v>
+        <v>60.54</v>
       </c>
       <c r="K53" s="8">
-        <v>6713550.7800000003</v>
+        <v>6707570.7800000003</v>
       </c>
       <c r="L53" s="9">
-        <v>75.209999999999994</v>
+        <v>75.14</v>
       </c>
       <c r="M53" s="8">
-        <v>2212688.2400000002</v>
+        <v>2218668.2400000002</v>
       </c>
       <c r="N53" s="9">
-        <v>24.79</v>
+        <v>24.86</v>
       </c>
       <c r="O53" s="8">
         <v>15000</v>
@@ -22086,10 +22089,10 @@
         <v>0.17</v>
       </c>
       <c r="Q53" s="8">
-        <v>2197688.2400000002</v>
+        <v>2203668.2400000002</v>
       </c>
       <c r="R53" s="9">
-        <v>24.62</v>
+        <v>24.69</v>
       </c>
     </row>
     <row r="54" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -22148,7 +22151,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>390</v>
       </c>
@@ -22204,7 +22207,7 @@
         <v>-17.489999999999998</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
         <v>398</v>
       </c>
@@ -22224,43 +22227,43 @@
         <v>12829676.84</v>
       </c>
       <c r="G56" s="8">
-        <v>2729857.91</v>
+        <v>2983932.91</v>
       </c>
       <c r="H56" s="9">
-        <v>21.28</v>
+        <v>23.26</v>
       </c>
       <c r="I56" s="8">
-        <v>1238356.56</v>
+        <v>1021641.56</v>
       </c>
       <c r="J56" s="9">
-        <v>9.65</v>
+        <v>7.96</v>
       </c>
       <c r="K56" s="8">
-        <v>3968214.47</v>
+        <v>4005574.47</v>
       </c>
       <c r="L56" s="9">
-        <v>30.93</v>
+        <v>31.22</v>
       </c>
       <c r="M56" s="8">
-        <v>8861462.3699999992</v>
+        <v>8824102.3699999992</v>
       </c>
       <c r="N56" s="9">
-        <v>69.069999999999993</v>
+        <v>68.78</v>
       </c>
       <c r="O56" s="8">
-        <v>54000</v>
+        <v>9000</v>
       </c>
       <c r="P56" s="9">
-        <v>0.42</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="Q56" s="8">
-        <v>8807462.3699999992</v>
+        <v>8815102.3699999992</v>
       </c>
       <c r="R56" s="9">
-        <v>68.650000000000006</v>
-      </c>
-    </row>
-    <row r="57" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
+        <v>68.709999999999994</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" ht="105.6" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
         <v>422</v>
       </c>
@@ -22280,28 +22283,28 @@
         <v>18605882.420000002</v>
       </c>
       <c r="G57" s="8">
-        <v>3079527.03</v>
+        <v>3185402.03</v>
       </c>
       <c r="H57" s="9">
-        <v>16.55</v>
+        <v>17.12</v>
       </c>
       <c r="I57" s="8">
-        <v>2359966</v>
+        <v>2737311</v>
       </c>
       <c r="J57" s="9">
-        <v>12.68</v>
+        <v>14.71</v>
       </c>
       <c r="K57" s="8">
-        <v>5439493.0300000003</v>
+        <v>5922713.0300000003</v>
       </c>
       <c r="L57" s="9">
-        <v>29.24</v>
+        <v>31.83</v>
       </c>
       <c r="M57" s="8">
-        <v>13166389.390000001</v>
+        <v>12683169.390000001</v>
       </c>
       <c r="N57" s="9">
-        <v>70.760000000000005</v>
+        <v>68.17</v>
       </c>
       <c r="O57" s="8">
         <v>3295000</v>
@@ -22310,10 +22313,10 @@
         <v>17.71</v>
       </c>
       <c r="Q57" s="8">
-        <v>9871389.3900000006</v>
+        <v>9388169.3900000006</v>
       </c>
       <c r="R57" s="9">
-        <v>53.06</v>
+        <v>50.46</v>
       </c>
     </row>
     <row r="58" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -22372,7 +22375,7 @@
         <v>30.38</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
         <v>472</v>
       </c>
@@ -22392,7 +22395,7 @@
         <v>1995235</v>
       </c>
       <c r="G59" s="8">
-        <v>1974647</v>
+        <v>1974622</v>
       </c>
       <c r="H59" s="9">
         <v>98.97</v>
@@ -22404,13 +22407,13 @@
         <v>9.1199999999999992</v>
       </c>
       <c r="K59" s="8">
-        <v>2156517</v>
+        <v>2156492</v>
       </c>
       <c r="L59" s="9">
         <v>108.08</v>
       </c>
       <c r="M59" s="8">
-        <v>-161282</v>
+        <v>-161257</v>
       </c>
       <c r="N59" s="9">
         <v>-8.08</v>
@@ -22422,7 +22425,7 @@
         <v>0</v>
       </c>
       <c r="Q59" s="8">
-        <v>-161282</v>
+        <v>-161257</v>
       </c>
       <c r="R59" s="9">
         <v>-8.08</v>
@@ -22448,28 +22451,28 @@
         <v>2528000</v>
       </c>
       <c r="G60" s="8">
-        <v>752429.84</v>
+        <v>900179.84</v>
       </c>
       <c r="H60" s="9">
-        <v>29.76</v>
+        <v>35.61</v>
       </c>
       <c r="I60" s="8">
-        <v>697510</v>
+        <v>674050</v>
       </c>
       <c r="J60" s="9">
-        <v>27.59</v>
+        <v>26.66</v>
       </c>
       <c r="K60" s="8">
-        <v>1449939.84</v>
+        <v>1574229.84</v>
       </c>
       <c r="L60" s="9">
-        <v>57.36</v>
+        <v>62.27</v>
       </c>
       <c r="M60" s="8">
-        <v>1078060.1599999999</v>
+        <v>953770.16</v>
       </c>
       <c r="N60" s="9">
-        <v>42.64</v>
+        <v>37.729999999999997</v>
       </c>
       <c r="O60" s="8">
         <v>20000</v>
@@ -22478,10 +22481,10 @@
         <v>0.79</v>
       </c>
       <c r="Q60" s="8">
-        <v>1058060.1599999999</v>
+        <v>933770.16</v>
       </c>
       <c r="R60" s="9">
-        <v>41.85</v>
+        <v>36.94</v>
       </c>
     </row>
     <row r="61" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -22560,16 +22563,16 @@
         <v>19811100</v>
       </c>
       <c r="G62" s="8">
-        <v>2413000</v>
+        <v>3110261.97</v>
       </c>
       <c r="H62" s="9">
-        <v>12.18</v>
+        <v>15.7</v>
       </c>
       <c r="I62" s="8">
-        <v>6349170</v>
+        <v>5651908.0300000003</v>
       </c>
       <c r="J62" s="9">
-        <v>32.049999999999997</v>
+        <v>28.53</v>
       </c>
       <c r="K62" s="8">
         <v>8762170</v>
@@ -22605,49 +22608,49 @@
         <v>101298156.95</v>
       </c>
       <c r="D63" s="14">
-        <v>0</v>
+        <v>71946</v>
       </c>
       <c r="E63" s="14">
         <v>0</v>
       </c>
       <c r="F63" s="14">
-        <v>101298156.95</v>
+        <v>101370102.95</v>
       </c>
       <c r="G63" s="14">
-        <v>26248895.120000001</v>
+        <v>28497772.09</v>
       </c>
       <c r="H63" s="15">
-        <v>25.91</v>
+        <v>28.11</v>
       </c>
       <c r="I63" s="14">
-        <v>20247819.949999999</v>
+        <v>19891917.98</v>
       </c>
       <c r="J63" s="15">
-        <v>19.989999999999998</v>
+        <v>19.62</v>
       </c>
       <c r="K63" s="14">
-        <v>46496715.07</v>
+        <v>48389690.07</v>
       </c>
       <c r="L63" s="15">
-        <v>45.9</v>
+        <v>47.74</v>
       </c>
       <c r="M63" s="14">
-        <v>54801441.880000003</v>
+        <v>52980412.880000003</v>
       </c>
       <c r="N63" s="15">
-        <v>54.1</v>
+        <v>52.26</v>
       </c>
       <c r="O63" s="14">
-        <v>4944593</v>
+        <v>4899593</v>
       </c>
       <c r="P63" s="15">
-        <v>4.88</v>
+        <v>4.83</v>
       </c>
       <c r="Q63" s="14">
-        <v>49856848.880000003</v>
+        <v>48080819.880000003</v>
       </c>
       <c r="R63" s="15">
-        <v>49.22</v>
+        <v>47.43</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
@@ -22659,49 +22662,49 @@
         <v>332000356.94999999</v>
       </c>
       <c r="D64" s="16">
-        <v>0</v>
+        <v>71946</v>
       </c>
       <c r="E64" s="16">
         <v>0</v>
       </c>
       <c r="F64" s="16">
-        <v>332000356.94999999</v>
+        <v>332072302.94999999</v>
       </c>
       <c r="G64" s="16">
-        <v>172751212.56999999</v>
+        <v>185369592.80000001</v>
       </c>
       <c r="H64" s="17">
-        <v>52.03</v>
+        <v>55.82</v>
       </c>
       <c r="I64" s="16">
-        <v>56076281.619999997</v>
+        <v>53335879.149999999</v>
       </c>
       <c r="J64" s="17">
-        <v>16.89</v>
+        <v>16.059999999999999</v>
       </c>
       <c r="K64" s="16">
-        <v>228827494.19</v>
+        <v>238705471.94999999</v>
       </c>
       <c r="L64" s="17">
-        <v>68.92</v>
+        <v>71.88</v>
       </c>
       <c r="M64" s="16">
-        <v>103172862.76000001</v>
+        <v>93366831</v>
       </c>
       <c r="N64" s="17">
-        <v>31.08</v>
+        <v>28.12</v>
       </c>
       <c r="O64" s="16">
-        <v>15154152.07</v>
+        <v>15487899.27</v>
       </c>
       <c r="P64" s="17">
-        <v>4.5599999999999996</v>
+        <v>4.66</v>
       </c>
       <c r="Q64" s="16">
-        <v>88018710.689999998</v>
+        <v>77878931.730000004</v>
       </c>
       <c r="R64" s="17">
-        <v>26.51</v>
+        <v>23.45</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
@@ -22877,49 +22880,49 @@
         <v>338655937.13</v>
       </c>
       <c r="D68" s="16">
-        <v>0</v>
+        <v>71946</v>
       </c>
       <c r="E68" s="16">
         <v>0</v>
       </c>
       <c r="F68" s="16">
-        <v>338655937.13</v>
+        <v>338727883.13</v>
       </c>
       <c r="G68" s="16">
-        <v>172751212.56999999</v>
+        <v>185369592.80000001</v>
       </c>
       <c r="H68" s="17">
-        <v>51.01</v>
+        <v>54.73</v>
       </c>
       <c r="I68" s="16">
-        <v>56076281.619999997</v>
+        <v>53335879.149999999</v>
       </c>
       <c r="J68" s="17">
-        <v>16.559999999999999</v>
+        <v>15.75</v>
       </c>
       <c r="K68" s="16">
-        <v>228827494.19</v>
+        <v>238705471.94999999</v>
       </c>
       <c r="L68" s="17">
-        <v>67.569999999999993</v>
+        <v>70.47</v>
       </c>
       <c r="M68" s="16">
-        <v>109828442.94</v>
+        <v>100022411.18000001</v>
       </c>
       <c r="N68" s="17">
-        <v>32.43</v>
+        <v>29.53</v>
       </c>
       <c r="O68" s="16">
-        <v>15154152.07</v>
+        <v>15487899.27</v>
       </c>
       <c r="P68" s="17">
-        <v>4.47</v>
+        <v>4.57</v>
       </c>
       <c r="Q68" s="16">
-        <v>94674290.870000005</v>
+        <v>84534511.909999996</v>
       </c>
       <c r="R68" s="17">
-        <v>27.96</v>
+        <v>24.96</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
@@ -22934,34 +22937,34 @@
         <v>0</v>
       </c>
       <c r="E69" s="4">
-        <v>0</v>
+        <v>71946</v>
       </c>
       <c r="F69" s="4">
-        <v>4037940.24</v>
+        <v>3965994.24</v>
       </c>
       <c r="G69" s="4">
         <v>558139.18000000005</v>
       </c>
       <c r="H69" s="5">
-        <v>13.82</v>
+        <v>14.07</v>
       </c>
       <c r="I69" s="4">
         <v>156393.70000000001</v>
       </c>
       <c r="J69" s="5">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="K69" s="4">
         <v>714532.88</v>
       </c>
       <c r="L69" s="5">
-        <v>17.7</v>
+        <v>18.02</v>
       </c>
       <c r="M69" s="4">
-        <v>3323407.36</v>
+        <v>3251461.36</v>
       </c>
       <c r="N69" s="5">
-        <v>82.3</v>
+        <v>81.98</v>
       </c>
       <c r="O69" s="4">
         <v>6129.12</v>
@@ -22970,10 +22973,10 @@
         <v>0.15</v>
       </c>
       <c r="Q69" s="4">
-        <v>3317278.24</v>
+        <v>3245332.24</v>
       </c>
       <c r="R69" s="5">
-        <v>82.15</v>
+        <v>81.83</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
@@ -22990,34 +22993,34 @@
         <v>0</v>
       </c>
       <c r="E70" s="8">
-        <v>0</v>
+        <v>71946</v>
       </c>
       <c r="F70" s="8">
-        <v>4037940.24</v>
+        <v>3965994.24</v>
       </c>
       <c r="G70" s="8">
         <v>558139.18000000005</v>
       </c>
       <c r="H70" s="9">
-        <v>13.82</v>
+        <v>14.07</v>
       </c>
       <c r="I70" s="8">
         <v>156393.70000000001</v>
       </c>
       <c r="J70" s="9">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="K70" s="8">
         <v>714532.88</v>
       </c>
       <c r="L70" s="9">
-        <v>17.7</v>
+        <v>18.02</v>
       </c>
       <c r="M70" s="8">
-        <v>3323407.36</v>
+        <v>3251461.36</v>
       </c>
       <c r="N70" s="9">
-        <v>82.3</v>
+        <v>81.98</v>
       </c>
       <c r="O70" s="8">
         <v>6129.12</v>
@@ -23026,10 +23029,10 @@
         <v>0.15</v>
       </c>
       <c r="Q70" s="8">
-        <v>3317278.24</v>
+        <v>3245332.24</v>
       </c>
       <c r="R70" s="9">
-        <v>82.15</v>
+        <v>81.83</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
@@ -23044,34 +23047,34 @@
         <v>0</v>
       </c>
       <c r="E71" s="14">
-        <v>0</v>
+        <v>71946</v>
       </c>
       <c r="F71" s="14">
-        <v>4037940.24</v>
+        <v>3965994.24</v>
       </c>
       <c r="G71" s="14">
         <v>558139.18000000005</v>
       </c>
       <c r="H71" s="15">
-        <v>13.82</v>
+        <v>14.07</v>
       </c>
       <c r="I71" s="14">
         <v>156393.70000000001</v>
       </c>
       <c r="J71" s="15">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="K71" s="14">
         <v>714532.88</v>
       </c>
       <c r="L71" s="15">
-        <v>17.7</v>
+        <v>18.02</v>
       </c>
       <c r="M71" s="14">
-        <v>3323407.36</v>
+        <v>3251461.36</v>
       </c>
       <c r="N71" s="15">
-        <v>82.3</v>
+        <v>81.98</v>
       </c>
       <c r="O71" s="14">
         <v>6129.12</v>
@@ -23080,10 +23083,10 @@
         <v>0.15</v>
       </c>
       <c r="Q71" s="14">
-        <v>3317278.24</v>
+        <v>3245332.24</v>
       </c>
       <c r="R71" s="15">
-        <v>82.15</v>
+        <v>81.83</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
@@ -23095,49 +23098,49 @@
         <v>342693877.37</v>
       </c>
       <c r="D72" s="16">
-        <v>0</v>
+        <v>71946</v>
       </c>
       <c r="E72" s="16">
-        <v>0</v>
+        <v>71946</v>
       </c>
       <c r="F72" s="16">
         <v>342693877.37</v>
       </c>
       <c r="G72" s="16">
-        <v>173309351.75</v>
+        <v>185927731.97999999</v>
       </c>
       <c r="H72" s="17">
-        <v>50.57</v>
+        <v>54.25</v>
       </c>
       <c r="I72" s="16">
-        <v>56232675.32</v>
+        <v>53492272.850000001</v>
       </c>
       <c r="J72" s="17">
-        <v>16.41</v>
+        <v>15.61</v>
       </c>
       <c r="K72" s="16">
-        <v>229542027.06999999</v>
+        <v>239420004.83000001</v>
       </c>
       <c r="L72" s="17">
-        <v>66.98</v>
+        <v>69.86</v>
       </c>
       <c r="M72" s="16">
-        <v>113151850.3</v>
+        <v>103273872.54000001</v>
       </c>
       <c r="N72" s="17">
-        <v>33.020000000000003</v>
+        <v>30.14</v>
       </c>
       <c r="O72" s="16">
-        <v>15160281.189999999</v>
+        <v>15494028.390000001</v>
       </c>
       <c r="P72" s="17">
-        <v>4.42</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="Q72" s="16">
-        <v>97991569.109999999</v>
+        <v>87779844.150000006</v>
       </c>
       <c r="R72" s="17">
-        <v>28.59</v>
+        <v>25.61</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
@@ -23158,16 +23161,16 @@
         <v>1000000</v>
       </c>
       <c r="G73" s="19">
-        <v>747825.74</v>
+        <v>805551.74</v>
       </c>
       <c r="H73" s="20">
-        <v>74.78</v>
+        <v>80.56</v>
       </c>
       <c r="I73" s="19">
-        <v>173268</v>
+        <v>115542</v>
       </c>
       <c r="J73" s="20">
-        <v>17.329999999999998</v>
+        <v>11.55</v>
       </c>
       <c r="K73" s="19">
         <v>921093.74</v>
@@ -23212,28 +23215,28 @@
         <v>1000000</v>
       </c>
       <c r="G74" s="19">
-        <v>511529</v>
+        <v>533379</v>
       </c>
       <c r="H74" s="20">
-        <v>51.15</v>
+        <v>53.34</v>
       </c>
       <c r="I74" s="19">
-        <v>54820</v>
+        <v>5570</v>
       </c>
       <c r="J74" s="20">
-        <v>5.48</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="K74" s="19">
-        <v>566349</v>
+        <v>538949</v>
       </c>
       <c r="L74" s="20">
-        <v>56.63</v>
+        <v>53.89</v>
       </c>
       <c r="M74" s="19">
-        <v>433651</v>
+        <v>461051</v>
       </c>
       <c r="N74" s="20">
-        <v>43.37</v>
+        <v>46.11</v>
       </c>
       <c r="O74" s="19">
         <v>0</v>
@@ -23242,10 +23245,10 @@
         <v>0</v>
       </c>
       <c r="Q74" s="19">
-        <v>433651</v>
+        <v>461051</v>
       </c>
       <c r="R74" s="20">
-        <v>43.37</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
@@ -23266,40 +23269,40 @@
         <v>12535870.93</v>
       </c>
       <c r="G75" s="19">
-        <v>7954071.0499999998</v>
+        <v>8273712.0499999998</v>
       </c>
       <c r="H75" s="20">
-        <v>63.45</v>
+        <v>66</v>
       </c>
       <c r="I75" s="19">
-        <v>1861288</v>
+        <v>1671545</v>
       </c>
       <c r="J75" s="20">
-        <v>14.85</v>
+        <v>13.33</v>
       </c>
       <c r="K75" s="19">
-        <v>9815359.0500000007</v>
+        <v>9945257.0500000007</v>
       </c>
       <c r="L75" s="20">
-        <v>78.3</v>
+        <v>79.33</v>
       </c>
       <c r="M75" s="19">
-        <v>2720511.88</v>
+        <v>2590613.88</v>
       </c>
       <c r="N75" s="20">
-        <v>21.7</v>
+        <v>20.67</v>
       </c>
       <c r="O75" s="19">
-        <v>600</v>
+        <v>30600</v>
       </c>
       <c r="P75" s="20">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="Q75" s="19">
-        <v>2719911.88</v>
+        <v>2560013.88</v>
       </c>
       <c r="R75" s="20">
-        <v>21.7</v>
+        <v>20.420000000000002</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
@@ -23320,40 +23323,40 @@
         <v>13373180.710000001</v>
       </c>
       <c r="G76" s="19">
-        <v>8425698.2899999991</v>
+        <v>8189262.29</v>
       </c>
       <c r="H76" s="20">
-        <v>63</v>
+        <v>61.24</v>
       </c>
       <c r="I76" s="19">
-        <v>1310047</v>
+        <v>1385133</v>
       </c>
       <c r="J76" s="20">
-        <v>9.8000000000000007</v>
+        <v>10.36</v>
       </c>
       <c r="K76" s="19">
-        <v>9735745.2899999991</v>
+        <v>9574395.2899999991</v>
       </c>
       <c r="L76" s="20">
-        <v>72.8</v>
+        <v>71.59</v>
       </c>
       <c r="M76" s="19">
-        <v>3637435.42</v>
+        <v>3798785.42</v>
       </c>
       <c r="N76" s="20">
-        <v>27.2</v>
+        <v>28.41</v>
       </c>
       <c r="O76" s="19">
-        <v>80000</v>
+        <v>56000</v>
       </c>
       <c r="P76" s="20">
-        <v>0.6</v>
+        <v>0.42</v>
       </c>
       <c r="Q76" s="19">
-        <v>3557435.42</v>
+        <v>3742785.42</v>
       </c>
       <c r="R76" s="20">
-        <v>26.6</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
@@ -23374,28 +23377,28 @@
         <v>14776703.779999999</v>
       </c>
       <c r="G77" s="19">
-        <v>10645457.039999999</v>
+        <v>10816874.039999999</v>
       </c>
       <c r="H77" s="20">
-        <v>72.040000000000006</v>
+        <v>73.2</v>
       </c>
       <c r="I77" s="19">
-        <v>1843702.67</v>
+        <v>1726705.67</v>
       </c>
       <c r="J77" s="20">
-        <v>12.48</v>
+        <v>11.69</v>
       </c>
       <c r="K77" s="19">
-        <v>12489159.710000001</v>
+        <v>12543579.710000001</v>
       </c>
       <c r="L77" s="20">
-        <v>84.52</v>
+        <v>84.89</v>
       </c>
       <c r="M77" s="19">
-        <v>2287544.0699999998</v>
+        <v>2233124.0699999998</v>
       </c>
       <c r="N77" s="20">
-        <v>15.48</v>
+        <v>15.11</v>
       </c>
       <c r="O77" s="19">
         <v>144801.1</v>
@@ -23404,10 +23407,10 @@
         <v>0.98</v>
       </c>
       <c r="Q77" s="19">
-        <v>2142742.9700000002</v>
+        <v>2088322.97</v>
       </c>
       <c r="R77" s="20">
-        <v>14.5</v>
+        <v>14.13</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
@@ -23419,49 +23422,49 @@
         <v>30348181.809999999</v>
       </c>
       <c r="D78" s="19">
-        <v>0</v>
+        <v>71946</v>
       </c>
       <c r="E78" s="19">
         <v>0</v>
       </c>
       <c r="F78" s="19">
-        <v>30348181.809999999</v>
+        <v>30420127.809999999</v>
       </c>
       <c r="G78" s="19">
-        <v>13406899.33</v>
+        <v>14342117.029999999</v>
       </c>
       <c r="H78" s="20">
-        <v>44.18</v>
+        <v>47.15</v>
       </c>
       <c r="I78" s="19">
-        <v>3789684.72</v>
+        <v>4420279.72</v>
       </c>
       <c r="J78" s="20">
-        <v>12.49</v>
+        <v>14.53</v>
       </c>
       <c r="K78" s="19">
-        <v>17196584.050000001</v>
+        <v>18762396.75</v>
       </c>
       <c r="L78" s="20">
-        <v>56.66</v>
+        <v>61.68</v>
       </c>
       <c r="M78" s="19">
-        <v>13151597.76</v>
+        <v>11657731.060000001</v>
       </c>
       <c r="N78" s="20">
-        <v>43.34</v>
+        <v>38.32</v>
       </c>
       <c r="O78" s="19">
         <v>1732093</v>
       </c>
       <c r="P78" s="20">
-        <v>5.71</v>
+        <v>5.69</v>
       </c>
       <c r="Q78" s="19">
-        <v>11419504.76</v>
+        <v>9925638.0600000005</v>
       </c>
       <c r="R78" s="20">
-        <v>37.630000000000003</v>
+        <v>32.630000000000003</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
@@ -23482,28 +23485,28 @@
         <v>13420000</v>
       </c>
       <c r="G79" s="19">
-        <v>9985540.0299999993</v>
+        <v>10753868.42</v>
       </c>
       <c r="H79" s="20">
-        <v>74.41</v>
+        <v>80.13</v>
       </c>
       <c r="I79" s="19">
-        <v>1778104</v>
+        <v>926886</v>
       </c>
       <c r="J79" s="20">
-        <v>13.25</v>
+        <v>6.91</v>
       </c>
       <c r="K79" s="19">
-        <v>11763644.029999999</v>
+        <v>11680754.42</v>
       </c>
       <c r="L79" s="20">
-        <v>87.66</v>
+        <v>87.04</v>
       </c>
       <c r="M79" s="19">
-        <v>1656355.97</v>
+        <v>1739245.58</v>
       </c>
       <c r="N79" s="20">
-        <v>12.34</v>
+        <v>12.96</v>
       </c>
       <c r="O79" s="19">
         <v>378743</v>
@@ -23512,10 +23515,10 @@
         <v>2.82</v>
       </c>
       <c r="Q79" s="19">
-        <v>1277612.97</v>
+        <v>1360502.58</v>
       </c>
       <c r="R79" s="20">
-        <v>9.52</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
@@ -23530,34 +23533,34 @@
         <v>0</v>
       </c>
       <c r="E80" s="19">
-        <v>0</v>
+        <v>71946</v>
       </c>
       <c r="F80" s="19">
-        <v>111264940.23999999</v>
+        <v>111192994.23999999</v>
       </c>
       <c r="G80" s="19">
-        <v>75829044.909999996</v>
+        <v>83236800.769999996</v>
       </c>
       <c r="H80" s="20">
-        <v>68.150000000000006</v>
+        <v>74.86</v>
       </c>
       <c r="I80" s="19">
-        <v>6210985.6200000001</v>
+        <v>5925343.6200000001</v>
       </c>
       <c r="J80" s="20">
-        <v>5.58</v>
+        <v>5.33</v>
       </c>
       <c r="K80" s="19">
-        <v>82040030.530000001</v>
+        <v>89162144.390000001</v>
       </c>
       <c r="L80" s="20">
-        <v>73.73</v>
+        <v>80.19</v>
       </c>
       <c r="M80" s="19">
-        <v>29224909.710000001</v>
+        <v>22030849.850000001</v>
       </c>
       <c r="N80" s="20">
-        <v>26.27</v>
+        <v>19.809999999999999</v>
       </c>
       <c r="O80" s="19">
         <v>4953094.99</v>
@@ -23566,10 +23569,10 @@
         <v>4.45</v>
       </c>
       <c r="Q80" s="19">
-        <v>24271814.719999999</v>
+        <v>17077754.859999999</v>
       </c>
       <c r="R80" s="20">
-        <v>21.81</v>
+        <v>15.36</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
@@ -23590,28 +23593,28 @@
         <v>4935928.8</v>
       </c>
       <c r="G81" s="19">
-        <v>1700370.43</v>
+        <v>2025237.43</v>
       </c>
       <c r="H81" s="20">
-        <v>34.450000000000003</v>
+        <v>41.03</v>
       </c>
       <c r="I81" s="19">
-        <v>848371.67</v>
+        <v>502696.67</v>
       </c>
       <c r="J81" s="20">
-        <v>17.190000000000001</v>
+        <v>10.18</v>
       </c>
       <c r="K81" s="19">
-        <v>2548742.1</v>
+        <v>2527934.1</v>
       </c>
       <c r="L81" s="20">
-        <v>51.64</v>
+        <v>51.21</v>
       </c>
       <c r="M81" s="19">
-        <v>2387186.7000000002</v>
+        <v>2407994.7000000002</v>
       </c>
       <c r="N81" s="20">
-        <v>48.36</v>
+        <v>48.79</v>
       </c>
       <c r="O81" s="19">
         <v>394000</v>
@@ -23620,10 +23623,10 @@
         <v>7.98</v>
       </c>
       <c r="Q81" s="19">
-        <v>1993186.7</v>
+        <v>2013994.7</v>
       </c>
       <c r="R81" s="20">
-        <v>40.380000000000003</v>
+        <v>40.799999999999997</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
@@ -23644,40 +23647,40 @@
         <v>140039071.09999999</v>
       </c>
       <c r="G82" s="19">
-        <v>44102915.93</v>
+        <v>46950929.210000001</v>
       </c>
       <c r="H82" s="20">
-        <v>31.49</v>
+        <v>33.53</v>
       </c>
       <c r="I82" s="19">
-        <v>38362403.640000001</v>
+        <v>36812571.170000002</v>
       </c>
       <c r="J82" s="20">
-        <v>27.39</v>
+        <v>26.29</v>
       </c>
       <c r="K82" s="19">
-        <v>82465319.569999993</v>
+        <v>83763500.379999995</v>
       </c>
       <c r="L82" s="20">
-        <v>58.89</v>
+        <v>59.81</v>
       </c>
       <c r="M82" s="19">
-        <v>57573751.530000001</v>
+        <v>56275570.719999999</v>
       </c>
       <c r="N82" s="20">
-        <v>41.11</v>
+        <v>40.19</v>
       </c>
       <c r="O82" s="19">
-        <v>7476949.0999999996</v>
+        <v>7804696.2999999998</v>
       </c>
       <c r="P82" s="20">
-        <v>5.34</v>
+        <v>5.57</v>
       </c>
       <c r="Q82" s="19">
-        <v>50096802.43</v>
+        <v>48470874.420000002</v>
       </c>
       <c r="R82" s="20">
-        <v>35.770000000000003</v>
+        <v>34.61</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
@@ -23689,49 +23692,49 @@
         <v>342693877.37</v>
       </c>
       <c r="D83" s="19">
-        <v>0</v>
+        <v>71946</v>
       </c>
       <c r="E83" s="19">
-        <v>0</v>
+        <v>71946</v>
       </c>
       <c r="F83" s="19">
         <v>342693877.37</v>
       </c>
       <c r="G83" s="19">
-        <v>173309351.75</v>
+        <v>185927731.97999999</v>
       </c>
       <c r="H83" s="20">
-        <v>50.57</v>
+        <v>54.25</v>
       </c>
       <c r="I83" s="19">
-        <v>56232675.32</v>
+        <v>53492272.850000001</v>
       </c>
       <c r="J83" s="20">
-        <v>16.41</v>
+        <v>15.61</v>
       </c>
       <c r="K83" s="19">
-        <v>229542027.06999999</v>
+        <v>239420004.83000001</v>
       </c>
       <c r="L83" s="20">
-        <v>66.98</v>
+        <v>69.86</v>
       </c>
       <c r="M83" s="19">
-        <v>113151850.3</v>
+        <v>103273872.54000001</v>
       </c>
       <c r="N83" s="20">
-        <v>33.020000000000003</v>
+        <v>30.14</v>
       </c>
       <c r="O83" s="19">
-        <v>15160281.189999999</v>
+        <v>15494028.390000001</v>
       </c>
       <c r="P83" s="20">
-        <v>4.42</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="Q83" s="19">
-        <v>97991569.109999999</v>
+        <v>87779844.150000006</v>
       </c>
       <c r="R83" s="20">
-        <v>28.59</v>
+        <v>25.61</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">

--- a/Budget-Report.xlsx
+++ b/Budget-Report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orathai\Desktop\Claude Cowork\Budget Report\00 BK\25690724\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orathai\Desktop\Claude Cowork\Budget Report\00 BK\25690731\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78D84BE-B2D7-49D9-BC08-C5802B47FFAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D07E38-78BA-487D-8C0F-12C5A1CEB225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="จำแนกตามแผนงาน" sheetId="1" r:id="rId1"/>
@@ -1766,7 +1766,7 @@
     <t>รวมทั้งสิ้น</t>
   </si>
   <si>
-    <t>( ข้อมูลระบบ ณ วันที่ 24 กรกฎาคม 2569 เวลา 22:07:44 น.)</t>
+    <t>( ข้อมูลระบบ ณ วันที่ 31 กรกฎาคม 2569 เวลา 22:14:05 น.)</t>
   </si>
   <si>
     <t>สำนัก/โครงการ</t>
@@ -1805,7 +1805,7 @@
     <t>สย.</t>
   </si>
   <si>
-    <t>( ข้อมูลระบบ ณ วันที่ 24 กรกฎาคม 2569 เวลา 22:09:22 น.)</t>
+    <t>( ข้อมูลระบบ ณ วันที่ 31 กรกฎาคม 2569 เวลา 22:15:33 น.)</t>
   </si>
 </sst>
 </file>
@@ -1930,7 +1930,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -2012,9 +2012,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2323,23 +2320,22 @@
   <dimension ref="A1:R307"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24" style="28" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.69921875" style="28" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.8984375" style="28" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.796875" style="28" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.8984375" style="28" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.3984375" style="28" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.796875" style="28" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.3984375" style="28" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.8984375" style="28" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.3984375" style="28" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.8984375" style="28" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.09765625" style="28" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.796875" style="28" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.8984375" style="28" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.796875" style="28" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.09765625" style="28" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="8.796875" style="28"/>
+    <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.69921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.8984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.8984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.8984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.3984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.8984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.09765625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.8984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -2353,7 +2349,7 @@
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
     </row>
-    <row r="4" spans="1:18" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
         <v>1</v>
       </c>
@@ -2461,40 +2457,40 @@
         <v>46540814</v>
       </c>
       <c r="G6" s="4">
-        <v>23670542.129999999</v>
+        <v>23910276</v>
       </c>
       <c r="H6" s="5">
-        <v>50.86</v>
+        <v>51.37</v>
       </c>
       <c r="I6" s="4">
-        <v>14870696.67</v>
+        <v>14530196.67</v>
       </c>
       <c r="J6" s="5">
-        <v>31.95</v>
+        <v>31.22</v>
       </c>
       <c r="K6" s="4">
-        <v>38541238.799999997</v>
+        <v>38440472.670000002</v>
       </c>
       <c r="L6" s="5">
-        <v>82.81</v>
+        <v>82.6</v>
       </c>
       <c r="M6" s="4">
-        <v>7999575.2000000002</v>
+        <v>8100341.3300000001</v>
       </c>
       <c r="N6" s="5">
-        <v>17.190000000000001</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="O6" s="4">
-        <v>1317521.6000000001</v>
+        <v>1385521.6</v>
       </c>
       <c r="P6" s="5">
-        <v>2.83</v>
+        <v>2.98</v>
       </c>
       <c r="Q6" s="4">
-        <v>6682053.5999999996</v>
+        <v>6714819.7300000004</v>
       </c>
       <c r="R6" s="5">
-        <v>14.36</v>
+        <v>14.43</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -2517,40 +2513,40 @@
         <v>37235000</v>
       </c>
       <c r="G7" s="8">
-        <v>18197586.129999999</v>
+        <v>18203766.129999999</v>
       </c>
       <c r="H7" s="9">
-        <v>48.87</v>
+        <v>48.89</v>
       </c>
       <c r="I7" s="8">
-        <v>13653617</v>
+        <v>13581617</v>
       </c>
       <c r="J7" s="9">
-        <v>36.67</v>
+        <v>36.479999999999997</v>
       </c>
       <c r="K7" s="8">
-        <v>31851203.129999999</v>
+        <v>31785383.129999999</v>
       </c>
       <c r="L7" s="9">
-        <v>85.54</v>
+        <v>85.36</v>
       </c>
       <c r="M7" s="8">
-        <v>5383796.8700000001</v>
+        <v>5449616.8700000001</v>
       </c>
       <c r="N7" s="9">
-        <v>14.46</v>
+        <v>14.64</v>
       </c>
       <c r="O7" s="8">
-        <v>1038800</v>
+        <v>1106800</v>
       </c>
       <c r="P7" s="9">
-        <v>2.79</v>
+        <v>2.97</v>
       </c>
       <c r="Q7" s="8">
-        <v>4344996.87</v>
+        <v>4342816.87</v>
       </c>
       <c r="R7" s="9">
-        <v>11.67</v>
+        <v>11.66</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -2573,40 +2569,40 @@
         <v>3500000</v>
       </c>
       <c r="G8" s="12">
-        <v>2052906.41</v>
+        <v>2053866.41</v>
       </c>
       <c r="H8" s="13">
-        <v>58.65</v>
+        <v>58.68</v>
       </c>
       <c r="I8" s="12">
-        <v>143800</v>
+        <v>65800</v>
       </c>
       <c r="J8" s="13">
-        <v>4.1100000000000003</v>
+        <v>1.88</v>
       </c>
       <c r="K8" s="12">
-        <v>2196706.41</v>
+        <v>2119666.41</v>
       </c>
       <c r="L8" s="13">
-        <v>62.76</v>
+        <v>60.56</v>
       </c>
       <c r="M8" s="12">
-        <v>1303293.5900000001</v>
+        <v>1380333.59</v>
       </c>
       <c r="N8" s="13">
-        <v>37.24</v>
+        <v>39.44</v>
       </c>
       <c r="O8" s="12">
-        <v>21600</v>
+        <v>99600</v>
       </c>
       <c r="P8" s="13">
-        <v>0.62</v>
+        <v>2.85</v>
       </c>
       <c r="Q8" s="12">
-        <v>1281693.5900000001</v>
+        <v>1280733.5900000001</v>
       </c>
       <c r="R8" s="13">
-        <v>36.619999999999997</v>
+        <v>36.590000000000003</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
@@ -2685,10 +2681,10 @@
         <v>700000</v>
       </c>
       <c r="G10" s="12">
-        <v>861652</v>
+        <v>885172</v>
       </c>
       <c r="H10" s="13">
-        <v>123.09</v>
+        <v>126.45</v>
       </c>
       <c r="I10" s="12">
         <v>0</v>
@@ -2697,16 +2693,16 @@
         <v>0</v>
       </c>
       <c r="K10" s="12">
-        <v>861652</v>
+        <v>885172</v>
       </c>
       <c r="L10" s="13">
-        <v>123.09</v>
+        <v>126.45</v>
       </c>
       <c r="M10" s="12">
-        <v>-161652</v>
+        <v>-185172</v>
       </c>
       <c r="N10" s="13">
-        <v>-23.09</v>
+        <v>-26.45</v>
       </c>
       <c r="O10" s="12">
         <v>2200</v>
@@ -2715,10 +2711,10 @@
         <v>0.31</v>
       </c>
       <c r="Q10" s="12">
-        <v>-163852</v>
+        <v>-187372</v>
       </c>
       <c r="R10" s="13">
-        <v>-23.41</v>
+        <v>-26.77</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
@@ -2965,10 +2961,10 @@
         <v>2706831.37</v>
       </c>
       <c r="G15" s="12">
-        <v>2143024.5699999998</v>
+        <v>2124724.5699999998</v>
       </c>
       <c r="H15" s="13">
-        <v>79.17</v>
+        <v>78.489999999999995</v>
       </c>
       <c r="I15" s="12">
         <v>3500</v>
@@ -2977,16 +2973,16 @@
         <v>0.13</v>
       </c>
       <c r="K15" s="12">
-        <v>2146524.5699999998</v>
+        <v>2128224.5699999998</v>
       </c>
       <c r="L15" s="13">
-        <v>79.3</v>
+        <v>78.62</v>
       </c>
       <c r="M15" s="12">
-        <v>560306.80000000005</v>
+        <v>578606.80000000005</v>
       </c>
       <c r="N15" s="13">
-        <v>20.7</v>
+        <v>21.38</v>
       </c>
       <c r="O15" s="12">
         <v>5000</v>
@@ -2995,10 +2991,10 @@
         <v>0.18</v>
       </c>
       <c r="Q15" s="12">
-        <v>555306.80000000005</v>
+        <v>573606.80000000005</v>
       </c>
       <c r="R15" s="13">
-        <v>20.52</v>
+        <v>21.19</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -3587,34 +3583,34 @@
         <v>73.22</v>
       </c>
       <c r="I26" s="12">
-        <v>200850</v>
+        <v>206850</v>
       </c>
       <c r="J26" s="13">
-        <v>60.86</v>
+        <v>62.68</v>
       </c>
       <c r="K26" s="12">
-        <v>442485.39</v>
+        <v>448485.39</v>
       </c>
       <c r="L26" s="13">
-        <v>134.09</v>
+        <v>135.9</v>
       </c>
       <c r="M26" s="12">
-        <v>-112485.39</v>
+        <v>-118485.39</v>
       </c>
       <c r="N26" s="13">
-        <v>-34.090000000000003</v>
+        <v>-35.9</v>
       </c>
       <c r="O26" s="12">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="P26" s="13">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="12">
-        <v>-122485.39</v>
+        <v>-118485.39</v>
       </c>
       <c r="R26" s="13">
-        <v>-37.119999999999997</v>
+        <v>-35.9</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -4309,28 +4305,28 @@
         <v>1180000</v>
       </c>
       <c r="G39" s="8">
-        <v>638349</v>
+        <v>871902.87</v>
       </c>
       <c r="H39" s="9">
-        <v>54.1</v>
+        <v>73.89</v>
       </c>
       <c r="I39" s="8">
-        <v>277000</v>
+        <v>5000</v>
       </c>
       <c r="J39" s="9">
-        <v>23.47</v>
+        <v>0.42</v>
       </c>
       <c r="K39" s="8">
-        <v>915349</v>
+        <v>876902.87</v>
       </c>
       <c r="L39" s="9">
-        <v>77.569999999999993</v>
+        <v>74.31</v>
       </c>
       <c r="M39" s="8">
-        <v>264651</v>
+        <v>303097.13</v>
       </c>
       <c r="N39" s="9">
-        <v>22.43</v>
+        <v>25.69</v>
       </c>
       <c r="O39" s="8">
         <v>0</v>
@@ -4339,10 +4335,10 @@
         <v>0</v>
       </c>
       <c r="Q39" s="8">
-        <v>264651</v>
+        <v>303097.13</v>
       </c>
       <c r="R39" s="9">
-        <v>22.43</v>
+        <v>25.69</v>
       </c>
     </row>
     <row r="40" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -4365,28 +4361,28 @@
         <v>400000</v>
       </c>
       <c r="G40" s="12">
-        <v>288811</v>
+        <v>522364.87</v>
       </c>
       <c r="H40" s="13">
-        <v>72.2</v>
+        <v>130.59</v>
       </c>
       <c r="I40" s="12">
-        <v>277000</v>
+        <v>0</v>
       </c>
       <c r="J40" s="13">
-        <v>69.25</v>
+        <v>0</v>
       </c>
       <c r="K40" s="12">
-        <v>565811</v>
+        <v>522364.87</v>
       </c>
       <c r="L40" s="13">
-        <v>141.44999999999999</v>
+        <v>130.59</v>
       </c>
       <c r="M40" s="12">
-        <v>-165811</v>
+        <v>-122364.87</v>
       </c>
       <c r="N40" s="13">
-        <v>-41.45</v>
+        <v>-30.59</v>
       </c>
       <c r="O40" s="12">
         <v>0</v>
@@ -4395,10 +4391,10 @@
         <v>0</v>
       </c>
       <c r="Q40" s="12">
-        <v>-165811</v>
+        <v>-122364.87</v>
       </c>
       <c r="R40" s="13">
-        <v>-41.45</v>
+        <v>-30.59</v>
       </c>
     </row>
     <row r="41" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -4427,22 +4423,22 @@
         <v>44.81</v>
       </c>
       <c r="I41" s="12">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="J41" s="13">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="K41" s="12">
-        <v>349538</v>
+        <v>354538</v>
       </c>
       <c r="L41" s="13">
-        <v>44.81</v>
+        <v>45.45</v>
       </c>
       <c r="M41" s="12">
-        <v>430462</v>
+        <v>425462</v>
       </c>
       <c r="N41" s="13">
-        <v>55.19</v>
+        <v>54.55</v>
       </c>
       <c r="O41" s="12">
         <v>0</v>
@@ -4451,10 +4447,10 @@
         <v>0</v>
       </c>
       <c r="Q41" s="12">
-        <v>430462</v>
+        <v>425462</v>
       </c>
       <c r="R41" s="13">
-        <v>55.19</v>
+        <v>54.55</v>
       </c>
     </row>
     <row r="42" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -4483,22 +4479,22 @@
         <v>66.010000000000005</v>
       </c>
       <c r="I42" s="8">
-        <v>284783</v>
+        <v>288283</v>
       </c>
       <c r="J42" s="9">
-        <v>10.9</v>
+        <v>11.03</v>
       </c>
       <c r="K42" s="8">
-        <v>2009589.67</v>
+        <v>2013089.67</v>
       </c>
       <c r="L42" s="9">
-        <v>76.91</v>
+        <v>77.040000000000006</v>
       </c>
       <c r="M42" s="8">
-        <v>603324.32999999996</v>
+        <v>599824.32999999996</v>
       </c>
       <c r="N42" s="9">
-        <v>23.09</v>
+        <v>22.96</v>
       </c>
       <c r="O42" s="8">
         <v>0</v>
@@ -4507,10 +4503,10 @@
         <v>0</v>
       </c>
       <c r="Q42" s="8">
-        <v>603324.32999999996</v>
+        <v>599824.32999999996</v>
       </c>
       <c r="R42" s="9">
-        <v>23.09</v>
+        <v>22.96</v>
       </c>
     </row>
     <row r="43" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -4651,22 +4647,22 @@
         <v>76.98</v>
       </c>
       <c r="I45" s="12">
-        <v>251780</v>
+        <v>255280</v>
       </c>
       <c r="J45" s="13">
-        <v>13.41</v>
+        <v>13.59</v>
       </c>
       <c r="K45" s="12">
-        <v>1697534.67</v>
+        <v>1701034.67</v>
       </c>
       <c r="L45" s="13">
-        <v>90.39</v>
+        <v>90.58</v>
       </c>
       <c r="M45" s="12">
-        <v>180465.33</v>
+        <v>176965.33</v>
       </c>
       <c r="N45" s="13">
-        <v>9.61</v>
+        <v>9.42</v>
       </c>
       <c r="O45" s="12">
         <v>0</v>
@@ -4675,10 +4671,10 @@
         <v>0</v>
       </c>
       <c r="Q45" s="12">
-        <v>180465.33</v>
+        <v>176965.33</v>
       </c>
       <c r="R45" s="13">
-        <v>9.61</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="46" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -4757,28 +4753,28 @@
         <v>54940200</v>
       </c>
       <c r="G47" s="4">
-        <v>39899903.969999999</v>
+        <v>39654207.579999998</v>
       </c>
       <c r="H47" s="5">
-        <v>72.62</v>
+        <v>72.180000000000007</v>
       </c>
       <c r="I47" s="4">
-        <v>6393068.6699999999</v>
+        <v>6647725.0599999996</v>
       </c>
       <c r="J47" s="5">
-        <v>11.64</v>
+        <v>12.1</v>
       </c>
       <c r="K47" s="4">
-        <v>46292972.640000001</v>
+        <v>46301932.640000001</v>
       </c>
       <c r="L47" s="5">
-        <v>84.26</v>
+        <v>84.28</v>
       </c>
       <c r="M47" s="4">
-        <v>8647227.3599999994</v>
+        <v>8638267.3599999994</v>
       </c>
       <c r="N47" s="5">
-        <v>15.74</v>
+        <v>15.72</v>
       </c>
       <c r="O47" s="4">
         <v>1155422.5</v>
@@ -4787,10 +4783,10 @@
         <v>2.1</v>
       </c>
       <c r="Q47" s="4">
-        <v>7491804.8600000003</v>
+        <v>7482844.8600000003</v>
       </c>
       <c r="R47" s="5">
-        <v>13.64</v>
+        <v>13.62</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -4819,22 +4815,22 @@
         <v>76.260000000000005</v>
       </c>
       <c r="I48" s="8">
-        <v>1643220.67</v>
+        <v>1673930.67</v>
       </c>
       <c r="J48" s="9">
-        <v>14.49</v>
+        <v>14.76</v>
       </c>
       <c r="K48" s="8">
-        <v>10291712.630000001</v>
+        <v>10322422.630000001</v>
       </c>
       <c r="L48" s="9">
-        <v>90.75</v>
+        <v>91.03</v>
       </c>
       <c r="M48" s="8">
-        <v>1048487.37</v>
+        <v>1017777.37</v>
       </c>
       <c r="N48" s="9">
-        <v>9.25</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="O48" s="8">
         <v>140079.5</v>
@@ -4843,10 +4839,10 @@
         <v>1.24</v>
       </c>
       <c r="Q48" s="8">
-        <v>908407.87</v>
+        <v>877697.87</v>
       </c>
       <c r="R48" s="9">
-        <v>8.01</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="49" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -4987,22 +4983,22 @@
         <v>64.16</v>
       </c>
       <c r="I51" s="12">
-        <v>652925.67000000004</v>
+        <v>653335.67000000004</v>
       </c>
       <c r="J51" s="13">
-        <v>15.11</v>
+        <v>15.12</v>
       </c>
       <c r="K51" s="12">
-        <v>3424597.37</v>
+        <v>3425007.37</v>
       </c>
       <c r="L51" s="13">
-        <v>79.27</v>
+        <v>79.28</v>
       </c>
       <c r="M51" s="12">
-        <v>895402.63</v>
+        <v>894992.63</v>
       </c>
       <c r="N51" s="13">
-        <v>20.73</v>
+        <v>20.72</v>
       </c>
       <c r="O51" s="12">
         <v>0</v>
@@ -5011,10 +5007,10 @@
         <v>0</v>
       </c>
       <c r="Q51" s="12">
-        <v>895402.63</v>
+        <v>894992.63</v>
       </c>
       <c r="R51" s="13">
-        <v>20.73</v>
+        <v>20.72</v>
       </c>
     </row>
     <row r="52" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -5043,22 +5039,22 @@
         <v>85.73</v>
       </c>
       <c r="I52" s="12">
-        <v>216490</v>
+        <v>246790</v>
       </c>
       <c r="J52" s="13">
-        <v>10.72</v>
+        <v>12.22</v>
       </c>
       <c r="K52" s="12">
-        <v>1948446</v>
+        <v>1978746</v>
       </c>
       <c r="L52" s="13">
-        <v>96.45</v>
+        <v>97.95</v>
       </c>
       <c r="M52" s="12">
-        <v>71754</v>
+        <v>41454</v>
       </c>
       <c r="N52" s="13">
-        <v>3.55</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="O52" s="12">
         <v>20079.5</v>
@@ -5067,10 +5063,10 @@
         <v>0.99</v>
       </c>
       <c r="Q52" s="12">
-        <v>51674.5</v>
+        <v>21374.5</v>
       </c>
       <c r="R52" s="13">
-        <v>2.56</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="53" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -5149,28 +5145,28 @@
         <v>13420000</v>
       </c>
       <c r="G54" s="8">
-        <v>10753868.42</v>
+        <v>10318412.029999999</v>
       </c>
       <c r="H54" s="9">
-        <v>80.13</v>
+        <v>76.89</v>
       </c>
       <c r="I54" s="8">
-        <v>926886</v>
+        <v>1389392.39</v>
       </c>
       <c r="J54" s="9">
-        <v>6.91</v>
+        <v>10.35</v>
       </c>
       <c r="K54" s="8">
-        <v>11680754.42</v>
+        <v>11707804.42</v>
       </c>
       <c r="L54" s="9">
-        <v>87.04</v>
+        <v>87.24</v>
       </c>
       <c r="M54" s="8">
-        <v>1739245.58</v>
+        <v>1712195.58</v>
       </c>
       <c r="N54" s="9">
-        <v>12.96</v>
+        <v>12.76</v>
       </c>
       <c r="O54" s="8">
         <v>378743</v>
@@ -5179,10 +5175,10 @@
         <v>2.82</v>
       </c>
       <c r="Q54" s="8">
-        <v>1360502.58</v>
+        <v>1333452.58</v>
       </c>
       <c r="R54" s="9">
-        <v>10.14</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="55" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -5317,28 +5313,28 @@
         <v>3400000</v>
       </c>
       <c r="G57" s="12">
-        <v>2417705.41</v>
+        <v>2439305.41</v>
       </c>
       <c r="H57" s="13">
-        <v>71.11</v>
+        <v>71.739999999999995</v>
       </c>
       <c r="I57" s="12">
-        <v>268150</v>
+        <v>283650</v>
       </c>
       <c r="J57" s="13">
-        <v>7.89</v>
+        <v>8.34</v>
       </c>
       <c r="K57" s="12">
-        <v>2685855.41</v>
+        <v>2722955.41</v>
       </c>
       <c r="L57" s="13">
-        <v>79</v>
+        <v>80.09</v>
       </c>
       <c r="M57" s="12">
-        <v>714144.59</v>
+        <v>677044.59</v>
       </c>
       <c r="N57" s="13">
-        <v>21</v>
+        <v>19.91</v>
       </c>
       <c r="O57" s="12">
         <v>0</v>
@@ -5347,10 +5343,10 @@
         <v>0</v>
       </c>
       <c r="Q57" s="12">
-        <v>714144.59</v>
+        <v>677044.59</v>
       </c>
       <c r="R57" s="13">
-        <v>21</v>
+        <v>19.91</v>
       </c>
     </row>
     <row r="58" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -5429,28 +5425,28 @@
         <v>200000</v>
       </c>
       <c r="G59" s="12">
-        <v>154338</v>
+        <v>238348</v>
       </c>
       <c r="H59" s="13">
-        <v>77.17</v>
+        <v>119.17</v>
       </c>
       <c r="I59" s="12">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="J59" s="13">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K59" s="12">
-        <v>254338</v>
+        <v>238348</v>
       </c>
       <c r="L59" s="13">
-        <v>127.17</v>
+        <v>119.17</v>
       </c>
       <c r="M59" s="12">
-        <v>-54338</v>
+        <v>-38348</v>
       </c>
       <c r="N59" s="13">
-        <v>-27.17</v>
+        <v>-19.170000000000002</v>
       </c>
       <c r="O59" s="12">
         <v>0</v>
@@ -5459,10 +5455,10 @@
         <v>0</v>
       </c>
       <c r="Q59" s="12">
-        <v>-54338</v>
+        <v>-38348</v>
       </c>
       <c r="R59" s="13">
-        <v>-27.17</v>
+        <v>-19.170000000000002</v>
       </c>
     </row>
     <row r="60" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -5541,28 +5537,28 @@
         <v>2600000</v>
       </c>
       <c r="G61" s="12">
-        <v>2222050.61</v>
+        <v>1680984.22</v>
       </c>
       <c r="H61" s="13">
-        <v>85.46</v>
+        <v>64.650000000000006</v>
       </c>
       <c r="I61" s="12">
-        <v>950</v>
+        <v>547956.39</v>
       </c>
       <c r="J61" s="13">
-        <v>0.04</v>
+        <v>21.08</v>
       </c>
       <c r="K61" s="12">
-        <v>2223000.61</v>
+        <v>2228940.61</v>
       </c>
       <c r="L61" s="13">
-        <v>85.5</v>
+        <v>85.73</v>
       </c>
       <c r="M61" s="12">
-        <v>376999.39</v>
+        <v>371059.39</v>
       </c>
       <c r="N61" s="13">
-        <v>14.5</v>
+        <v>14.27</v>
       </c>
       <c r="O61" s="12">
         <v>115743</v>
@@ -5571,10 +5567,10 @@
         <v>4.45</v>
       </c>
       <c r="Q61" s="12">
-        <v>261256.39</v>
+        <v>255316.39</v>
       </c>
       <c r="R61" s="13">
-        <v>10.050000000000001</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="62" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -5765,28 +5761,28 @@
         <v>11720000</v>
       </c>
       <c r="G65" s="8">
-        <v>7901987</v>
+        <v>7948887</v>
       </c>
       <c r="H65" s="9">
-        <v>67.42</v>
+        <v>67.819999999999993</v>
       </c>
       <c r="I65" s="8">
-        <v>1671535</v>
+        <v>1650895</v>
       </c>
       <c r="J65" s="9">
-        <v>14.26</v>
+        <v>14.09</v>
       </c>
       <c r="K65" s="8">
-        <v>9573522</v>
+        <v>9599782</v>
       </c>
       <c r="L65" s="9">
-        <v>81.69</v>
+        <v>81.91</v>
       </c>
       <c r="M65" s="8">
-        <v>2146478</v>
+        <v>2120218</v>
       </c>
       <c r="N65" s="9">
-        <v>18.309999999999999</v>
+        <v>18.09</v>
       </c>
       <c r="O65" s="8">
         <v>30600</v>
@@ -5795,10 +5791,10 @@
         <v>0.26</v>
       </c>
       <c r="Q65" s="8">
-        <v>2115878</v>
+        <v>2089618</v>
       </c>
       <c r="R65" s="9">
-        <v>18.05</v>
+        <v>17.829999999999998</v>
       </c>
     </row>
     <row r="66" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -5933,28 +5929,28 @@
         <v>2820000</v>
       </c>
       <c r="G68" s="12">
-        <v>2120447</v>
+        <v>2167347</v>
       </c>
       <c r="H68" s="13">
-        <v>75.19</v>
+        <v>76.86</v>
       </c>
       <c r="I68" s="12">
-        <v>433594</v>
+        <v>412954</v>
       </c>
       <c r="J68" s="13">
-        <v>15.38</v>
+        <v>14.64</v>
       </c>
       <c r="K68" s="12">
-        <v>2554041</v>
+        <v>2580301</v>
       </c>
       <c r="L68" s="13">
-        <v>90.57</v>
+        <v>91.5</v>
       </c>
       <c r="M68" s="12">
-        <v>265959</v>
+        <v>239699</v>
       </c>
       <c r="N68" s="13">
-        <v>9.43</v>
+        <v>8.5</v>
       </c>
       <c r="O68" s="12">
         <v>600</v>
@@ -5963,10 +5959,10 @@
         <v>0.02</v>
       </c>
       <c r="Q68" s="12">
-        <v>265359</v>
+        <v>239099</v>
       </c>
       <c r="R68" s="13">
-        <v>9.41</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="69" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -6101,28 +6097,28 @@
         <v>10640000</v>
       </c>
       <c r="G71" s="8">
-        <v>7550908.29</v>
+        <v>7691068.29</v>
       </c>
       <c r="H71" s="9">
-        <v>70.97</v>
+        <v>72.28</v>
       </c>
       <c r="I71" s="8">
-        <v>1108133</v>
+        <v>912513</v>
       </c>
       <c r="J71" s="9">
-        <v>10.41</v>
+        <v>8.58</v>
       </c>
       <c r="K71" s="8">
-        <v>8659041.2899999991</v>
+        <v>8603581.2899999991</v>
       </c>
       <c r="L71" s="9">
-        <v>81.38</v>
+        <v>80.86</v>
       </c>
       <c r="M71" s="8">
-        <v>1980958.71</v>
+        <v>2036418.71</v>
       </c>
       <c r="N71" s="9">
-        <v>18.62</v>
+        <v>19.14</v>
       </c>
       <c r="O71" s="8">
         <v>56000</v>
@@ -6131,10 +6127,10 @@
         <v>0.53</v>
       </c>
       <c r="Q71" s="8">
-        <v>1924958.71</v>
+        <v>1980418.71</v>
       </c>
       <c r="R71" s="9">
-        <v>18.09</v>
+        <v>18.61</v>
       </c>
     </row>
     <row r="72" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -6163,22 +6159,22 @@
         <v>68.58</v>
       </c>
       <c r="I72" s="12">
-        <v>30910</v>
+        <v>42210</v>
       </c>
       <c r="J72" s="13">
-        <v>2.71</v>
+        <v>3.7</v>
       </c>
       <c r="K72" s="12">
-        <v>812734.22</v>
+        <v>824034.22</v>
       </c>
       <c r="L72" s="13">
-        <v>71.290000000000006</v>
+        <v>72.28</v>
       </c>
       <c r="M72" s="12">
-        <v>327265.78000000003</v>
+        <v>315965.78000000003</v>
       </c>
       <c r="N72" s="13">
-        <v>28.71</v>
+        <v>27.72</v>
       </c>
       <c r="O72" s="12">
         <v>0</v>
@@ -6187,10 +6183,10 @@
         <v>0</v>
       </c>
       <c r="Q72" s="12">
-        <v>327265.78000000003</v>
+        <v>315965.78000000003</v>
       </c>
       <c r="R72" s="13">
-        <v>28.71</v>
+        <v>27.72</v>
       </c>
     </row>
     <row r="73" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -6275,22 +6271,22 @@
         <v>62.06</v>
       </c>
       <c r="I74" s="12">
-        <v>260300</v>
+        <v>186300</v>
       </c>
       <c r="J74" s="13">
-        <v>37.19</v>
+        <v>26.61</v>
       </c>
       <c r="K74" s="12">
-        <v>694711</v>
+        <v>620711</v>
       </c>
       <c r="L74" s="13">
-        <v>99.24</v>
+        <v>88.67</v>
       </c>
       <c r="M74" s="12">
-        <v>5289</v>
+        <v>79289</v>
       </c>
       <c r="N74" s="13">
-        <v>0.76</v>
+        <v>11.33</v>
       </c>
       <c r="O74" s="12">
         <v>6000</v>
@@ -6299,10 +6295,10 @@
         <v>0.86</v>
       </c>
       <c r="Q74" s="12">
-        <v>-711</v>
+        <v>73289</v>
       </c>
       <c r="R74" s="13">
-        <v>-0.1</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="75" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -6381,28 +6377,28 @@
         <v>3300000</v>
       </c>
       <c r="G76" s="12">
-        <v>1808287.6</v>
+        <v>1889427.6</v>
       </c>
       <c r="H76" s="13">
-        <v>54.8</v>
+        <v>57.26</v>
       </c>
       <c r="I76" s="12">
-        <v>455783</v>
+        <v>373863</v>
       </c>
       <c r="J76" s="13">
-        <v>13.81</v>
+        <v>11.33</v>
       </c>
       <c r="K76" s="12">
-        <v>2264070.6</v>
+        <v>2263290.6</v>
       </c>
       <c r="L76" s="13">
-        <v>68.61</v>
+        <v>68.58</v>
       </c>
       <c r="M76" s="12">
-        <v>1035929.4</v>
+        <v>1036709.4</v>
       </c>
       <c r="N76" s="13">
-        <v>31.39</v>
+        <v>31.42</v>
       </c>
       <c r="O76" s="12">
         <v>0</v>
@@ -6411,10 +6407,10 @@
         <v>0</v>
       </c>
       <c r="Q76" s="12">
-        <v>1035929.4</v>
+        <v>1036709.4</v>
       </c>
       <c r="R76" s="13">
-        <v>31.39</v>
+        <v>31.42</v>
       </c>
     </row>
     <row r="77" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -6493,28 +6489,28 @@
         <v>500000</v>
       </c>
       <c r="G78" s="12">
-        <v>288650</v>
+        <v>347670</v>
       </c>
       <c r="H78" s="13">
-        <v>57.73</v>
+        <v>69.53</v>
       </c>
       <c r="I78" s="12">
-        <v>151000</v>
+        <v>100000</v>
       </c>
       <c r="J78" s="13">
-        <v>30.2</v>
+        <v>20</v>
       </c>
       <c r="K78" s="12">
-        <v>439650</v>
+        <v>447670</v>
       </c>
       <c r="L78" s="13">
-        <v>87.93</v>
+        <v>89.53</v>
       </c>
       <c r="M78" s="12">
-        <v>60350</v>
+        <v>52330</v>
       </c>
       <c r="N78" s="13">
-        <v>12.07</v>
+        <v>10.47</v>
       </c>
       <c r="O78" s="12">
         <v>50000</v>
@@ -6523,10 +6519,10 @@
         <v>10</v>
       </c>
       <c r="Q78" s="12">
-        <v>10350</v>
+        <v>2330</v>
       </c>
       <c r="R78" s="13">
-        <v>2.0699999999999998</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="79" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -6605,28 +6601,28 @@
         <v>7820000</v>
       </c>
       <c r="G80" s="8">
-        <v>5044648.3</v>
+        <v>5047348.3</v>
       </c>
       <c r="H80" s="9">
-        <v>64.510000000000005</v>
+        <v>64.540000000000006</v>
       </c>
       <c r="I80" s="8">
-        <v>1043294</v>
+        <v>1020994</v>
       </c>
       <c r="J80" s="9">
-        <v>13.34</v>
+        <v>13.06</v>
       </c>
       <c r="K80" s="8">
-        <v>6087942.2999999998</v>
+        <v>6068342.2999999998</v>
       </c>
       <c r="L80" s="9">
-        <v>77.849999999999994</v>
+        <v>77.599999999999994</v>
       </c>
       <c r="M80" s="8">
-        <v>1732057.7</v>
+        <v>1751657.7</v>
       </c>
       <c r="N80" s="9">
-        <v>22.15</v>
+        <v>22.4</v>
       </c>
       <c r="O80" s="8">
         <v>550000</v>
@@ -6635,10 +6631,10 @@
         <v>7.03</v>
       </c>
       <c r="Q80" s="8">
-        <v>1182057.7</v>
+        <v>1201657.7</v>
       </c>
       <c r="R80" s="9">
-        <v>15.12</v>
+        <v>15.37</v>
       </c>
     </row>
     <row r="81" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -6667,22 +6663,22 @@
         <v>55.59</v>
       </c>
       <c r="I81" s="12">
-        <v>33500</v>
+        <v>21500</v>
       </c>
       <c r="J81" s="13">
-        <v>3.35</v>
+        <v>2.15</v>
       </c>
       <c r="K81" s="12">
-        <v>589428</v>
+        <v>577428</v>
       </c>
       <c r="L81" s="13">
-        <v>58.94</v>
+        <v>57.74</v>
       </c>
       <c r="M81" s="12">
-        <v>410572</v>
+        <v>422572</v>
       </c>
       <c r="N81" s="13">
-        <v>41.06</v>
+        <v>42.26</v>
       </c>
       <c r="O81" s="12">
         <v>0</v>
@@ -6691,10 +6687,10 @@
         <v>0</v>
       </c>
       <c r="Q81" s="12">
-        <v>410572</v>
+        <v>422572</v>
       </c>
       <c r="R81" s="13">
-        <v>41.06</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="82" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -6829,28 +6825,28 @@
         <v>3000000</v>
       </c>
       <c r="G84" s="12">
-        <v>2220749</v>
+        <v>2223449</v>
       </c>
       <c r="H84" s="13">
-        <v>74.02</v>
+        <v>74.11</v>
       </c>
       <c r="I84" s="12">
-        <v>195544</v>
+        <v>192344</v>
       </c>
       <c r="J84" s="13">
-        <v>6.52</v>
+        <v>6.41</v>
       </c>
       <c r="K84" s="12">
-        <v>2416293</v>
+        <v>2415793</v>
       </c>
       <c r="L84" s="13">
-        <v>80.540000000000006</v>
+        <v>80.53</v>
       </c>
       <c r="M84" s="12">
-        <v>583707</v>
+        <v>584207</v>
       </c>
       <c r="N84" s="13">
-        <v>19.46</v>
+        <v>19.47</v>
       </c>
       <c r="O84" s="12">
         <v>0</v>
@@ -6859,10 +6855,10 @@
         <v>0</v>
       </c>
       <c r="Q84" s="12">
-        <v>583707</v>
+        <v>584207</v>
       </c>
       <c r="R84" s="13">
-        <v>19.46</v>
+        <v>19.47</v>
       </c>
     </row>
     <row r="85" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -7115,22 +7111,22 @@
         <v>6.82</v>
       </c>
       <c r="I89" s="12">
-        <v>507900</v>
+        <v>500800</v>
       </c>
       <c r="J89" s="13">
-        <v>50.79</v>
+        <v>50.08</v>
       </c>
       <c r="K89" s="12">
-        <v>576110</v>
+        <v>569010</v>
       </c>
       <c r="L89" s="13">
-        <v>57.61</v>
+        <v>56.9</v>
       </c>
       <c r="M89" s="12">
-        <v>423890</v>
+        <v>430990</v>
       </c>
       <c r="N89" s="13">
-        <v>42.39</v>
+        <v>43.1</v>
       </c>
       <c r="O89" s="12">
         <v>550000</v>
@@ -7139,10 +7135,10 @@
         <v>55</v>
       </c>
       <c r="Q89" s="12">
-        <v>-126110</v>
+        <v>-119010</v>
       </c>
       <c r="R89" s="13">
-        <v>-12.61</v>
+        <v>-11.9</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
@@ -7171,22 +7167,22 @@
         <v>56.28</v>
       </c>
       <c r="I90" s="4">
-        <v>961508.31</v>
+        <v>960008.31</v>
       </c>
       <c r="J90" s="5">
-        <v>9.81</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="K90" s="4">
-        <v>6476514.9500000002</v>
+        <v>6475014.9500000002</v>
       </c>
       <c r="L90" s="5">
-        <v>66.09</v>
+        <v>66.069999999999993</v>
       </c>
       <c r="M90" s="4">
-        <v>3323485.05</v>
+        <v>3324985.05</v>
       </c>
       <c r="N90" s="5">
-        <v>33.909999999999997</v>
+        <v>33.93</v>
       </c>
       <c r="O90" s="4">
         <v>2287551.54</v>
@@ -7195,10 +7191,10 @@
         <v>23.34</v>
       </c>
       <c r="Q90" s="4">
-        <v>1035933.51</v>
+        <v>1037433.51</v>
       </c>
       <c r="R90" s="5">
-        <v>10.57</v>
+        <v>10.59</v>
       </c>
     </row>
     <row r="91" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -7227,22 +7223,22 @@
         <v>56.28</v>
       </c>
       <c r="I91" s="8">
-        <v>961508.31</v>
+        <v>960008.31</v>
       </c>
       <c r="J91" s="9">
-        <v>9.81</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="K91" s="8">
-        <v>6476514.9500000002</v>
+        <v>6475014.9500000002</v>
       </c>
       <c r="L91" s="9">
-        <v>66.09</v>
+        <v>66.069999999999993</v>
       </c>
       <c r="M91" s="8">
-        <v>3323485.05</v>
+        <v>3324985.05</v>
       </c>
       <c r="N91" s="9">
-        <v>33.909999999999997</v>
+        <v>33.93</v>
       </c>
       <c r="O91" s="8">
         <v>2287551.54</v>
@@ -7251,10 +7247,10 @@
         <v>23.34</v>
       </c>
       <c r="Q91" s="8">
-        <v>1035933.51</v>
+        <v>1037433.51</v>
       </c>
       <c r="R91" s="9">
-        <v>10.57</v>
+        <v>10.59</v>
       </c>
     </row>
     <row r="92" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
@@ -7395,22 +7391,22 @@
         <v>41.36</v>
       </c>
       <c r="I94" s="12">
-        <v>229638</v>
+        <v>228138</v>
       </c>
       <c r="J94" s="13">
-        <v>9.75</v>
+        <v>9.69</v>
       </c>
       <c r="K94" s="12">
-        <v>1203669</v>
+        <v>1202169</v>
       </c>
       <c r="L94" s="13">
-        <v>51.11</v>
+        <v>51.05</v>
       </c>
       <c r="M94" s="12">
-        <v>1151331</v>
+        <v>1152831</v>
       </c>
       <c r="N94" s="13">
-        <v>48.89</v>
+        <v>48.95</v>
       </c>
       <c r="O94" s="12">
         <v>653762</v>
@@ -7419,10 +7415,10 @@
         <v>27.76</v>
       </c>
       <c r="Q94" s="12">
-        <v>497569</v>
+        <v>499069</v>
       </c>
       <c r="R94" s="13">
-        <v>21.13</v>
+        <v>21.19</v>
       </c>
     </row>
     <row r="95" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -7445,28 +7441,28 @@
         <v>119421186</v>
       </c>
       <c r="G95" s="4">
-        <v>87786367.969999999</v>
+        <v>88118376.469999999</v>
       </c>
       <c r="H95" s="5">
-        <v>73.510000000000005</v>
+        <v>73.790000000000006</v>
       </c>
       <c r="I95" s="4">
-        <v>11218687.52</v>
+        <v>10927195.02</v>
       </c>
       <c r="J95" s="5">
-        <v>9.39</v>
+        <v>9.15</v>
       </c>
       <c r="K95" s="4">
-        <v>99005055.489999995</v>
+        <v>99045571.489999995</v>
       </c>
       <c r="L95" s="5">
-        <v>82.9</v>
+        <v>82.94</v>
       </c>
       <c r="M95" s="4">
-        <v>20416130.510000002</v>
+        <v>20375614.510000002</v>
       </c>
       <c r="N95" s="5">
-        <v>17.100000000000001</v>
+        <v>17.059999999999999</v>
       </c>
       <c r="O95" s="4">
         <v>5827810.6299999999</v>
@@ -7475,10 +7471,10 @@
         <v>4.88</v>
       </c>
       <c r="Q95" s="4">
-        <v>14588319.880000001</v>
+        <v>14547803.880000001</v>
       </c>
       <c r="R95" s="5">
-        <v>12.22</v>
+        <v>12.18</v>
       </c>
     </row>
     <row r="96" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -7501,16 +7497,16 @@
         <v>29200000</v>
       </c>
       <c r="G96" s="8">
-        <v>17566256.93</v>
+        <v>17874149.43</v>
       </c>
       <c r="H96" s="9">
-        <v>60.16</v>
+        <v>61.21</v>
       </c>
       <c r="I96" s="8">
-        <v>5658302.1900000004</v>
+        <v>5350409.6900000004</v>
       </c>
       <c r="J96" s="9">
-        <v>19.38</v>
+        <v>18.32</v>
       </c>
       <c r="K96" s="8">
         <v>23224559.120000001</v>
@@ -7669,16 +7665,16 @@
         <v>8310076.75</v>
       </c>
       <c r="G99" s="12">
-        <v>2948477.48</v>
+        <v>3256369.98</v>
       </c>
       <c r="H99" s="13">
-        <v>35.479999999999997</v>
+        <v>39.19</v>
       </c>
       <c r="I99" s="12">
-        <v>3683200.65</v>
+        <v>3375308.15</v>
       </c>
       <c r="J99" s="13">
-        <v>44.32</v>
+        <v>40.619999999999997</v>
       </c>
       <c r="K99" s="12">
         <v>6631678.1299999999</v>
@@ -7843,22 +7839,22 @@
         <v>53.34</v>
       </c>
       <c r="I102" s="8">
-        <v>5570</v>
+        <v>19570</v>
       </c>
       <c r="J102" s="9">
-        <v>0.56000000000000005</v>
+        <v>1.96</v>
       </c>
       <c r="K102" s="8">
-        <v>538949</v>
+        <v>552949</v>
       </c>
       <c r="L102" s="9">
-        <v>53.89</v>
+        <v>55.29</v>
       </c>
       <c r="M102" s="8">
-        <v>461051</v>
+        <v>447051</v>
       </c>
       <c r="N102" s="9">
-        <v>46.11</v>
+        <v>44.71</v>
       </c>
       <c r="O102" s="8">
         <v>0</v>
@@ -7867,10 +7863,10 @@
         <v>0</v>
       </c>
       <c r="Q102" s="8">
-        <v>461051</v>
+        <v>447051</v>
       </c>
       <c r="R102" s="9">
-        <v>46.11</v>
+        <v>44.71</v>
       </c>
     </row>
     <row r="103" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -7899,22 +7895,22 @@
         <v>52.22</v>
       </c>
       <c r="I103" s="12">
-        <v>5570</v>
+        <v>19570</v>
       </c>
       <c r="J103" s="13">
-        <v>0.63</v>
+        <v>2.21</v>
       </c>
       <c r="K103" s="12">
-        <v>468559</v>
+        <v>482559</v>
       </c>
       <c r="L103" s="13">
-        <v>52.85</v>
+        <v>54.43</v>
       </c>
       <c r="M103" s="12">
-        <v>418041</v>
+        <v>404041</v>
       </c>
       <c r="N103" s="13">
-        <v>47.15</v>
+        <v>45.57</v>
       </c>
       <c r="O103" s="12">
         <v>0</v>
@@ -7923,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="Q103" s="12">
-        <v>418041</v>
+        <v>404041</v>
       </c>
       <c r="R103" s="13">
-        <v>47.15</v>
+        <v>45.57</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
@@ -8011,22 +8007,22 @@
         <v>80.56</v>
       </c>
       <c r="I105" s="8">
-        <v>115542</v>
+        <v>135942</v>
       </c>
       <c r="J105" s="9">
-        <v>11.55</v>
+        <v>13.59</v>
       </c>
       <c r="K105" s="8">
-        <v>921093.74</v>
+        <v>941493.74</v>
       </c>
       <c r="L105" s="9">
-        <v>92.11</v>
+        <v>94.15</v>
       </c>
       <c r="M105" s="8">
-        <v>78906.259999999995</v>
+        <v>58506.26</v>
       </c>
       <c r="N105" s="9">
-        <v>7.89</v>
+        <v>5.85</v>
       </c>
       <c r="O105" s="8">
         <v>0</v>
@@ -8035,10 +8031,10 @@
         <v>0</v>
       </c>
       <c r="Q105" s="8">
-        <v>78906.259999999995</v>
+        <v>58506.26</v>
       </c>
       <c r="R105" s="9">
-        <v>7.89</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="106" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -8067,22 +8063,22 @@
         <v>79.03</v>
       </c>
       <c r="I106" s="12">
-        <v>0</v>
+        <v>20400</v>
       </c>
       <c r="J106" s="13">
-        <v>0</v>
+        <v>9.58</v>
       </c>
       <c r="K106" s="12">
-        <v>168338</v>
+        <v>188738</v>
       </c>
       <c r="L106" s="13">
-        <v>79.03</v>
+        <v>88.61</v>
       </c>
       <c r="M106" s="12">
-        <v>44662</v>
+        <v>24262</v>
       </c>
       <c r="N106" s="13">
-        <v>20.97</v>
+        <v>11.39</v>
       </c>
       <c r="O106" s="12">
         <v>0</v>
@@ -8091,10 +8087,10 @@
         <v>0</v>
       </c>
       <c r="Q106" s="12">
-        <v>44662</v>
+        <v>24262</v>
       </c>
       <c r="R106" s="13">
-        <v>20.97</v>
+        <v>11.39</v>
       </c>
     </row>
     <row r="107" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -8341,28 +8337,28 @@
         <v>78027000</v>
       </c>
       <c r="G111" s="8">
-        <v>65112404.659999996</v>
+        <v>65136520.659999996</v>
       </c>
       <c r="H111" s="9">
-        <v>83.45</v>
+        <v>83.48</v>
       </c>
       <c r="I111" s="8">
-        <v>110647.73</v>
+        <v>92647.73</v>
       </c>
       <c r="J111" s="9">
-        <v>0.14000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="K111" s="8">
-        <v>65223052.390000001</v>
+        <v>65229168.390000001</v>
       </c>
       <c r="L111" s="9">
-        <v>83.59</v>
+        <v>83.6</v>
       </c>
       <c r="M111" s="8">
-        <v>12803947.609999999</v>
+        <v>12797831.609999999</v>
       </c>
       <c r="N111" s="9">
-        <v>16.41</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="O111" s="8">
         <v>1542.5</v>
@@ -8371,10 +8367,10 @@
         <v>0</v>
       </c>
       <c r="Q111" s="8">
-        <v>12802405.109999999</v>
+        <v>12796289.109999999</v>
       </c>
       <c r="R111" s="9">
-        <v>16.41</v>
+        <v>16.399999999999999</v>
       </c>
     </row>
     <row r="112" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -8453,16 +8449,16 @@
         <v>2387000</v>
       </c>
       <c r="G113" s="12">
-        <v>2664354.0699999998</v>
+        <v>2682354.0699999998</v>
       </c>
       <c r="H113" s="13">
-        <v>111.62</v>
+        <v>112.37</v>
       </c>
       <c r="I113" s="12">
-        <v>87000.23</v>
+        <v>69000.23</v>
       </c>
       <c r="J113" s="13">
-        <v>3.64</v>
+        <v>2.89</v>
       </c>
       <c r="K113" s="12">
         <v>2751354.3</v>
@@ -8509,10 +8505,10 @@
         <v>75000000</v>
       </c>
       <c r="G114" s="12">
-        <v>62207595.590000004</v>
+        <v>62213711.590000004</v>
       </c>
       <c r="H114" s="13">
-        <v>82.94</v>
+        <v>82.95</v>
       </c>
       <c r="I114" s="12">
         <v>0</v>
@@ -8521,16 +8517,16 @@
         <v>0</v>
       </c>
       <c r="K114" s="12">
-        <v>62207595.590000004</v>
+        <v>62213711.590000004</v>
       </c>
       <c r="L114" s="13">
-        <v>82.94</v>
+        <v>82.95</v>
       </c>
       <c r="M114" s="12">
-        <v>12792404.41</v>
+        <v>12786288.41</v>
       </c>
       <c r="N114" s="13">
-        <v>17.059999999999999</v>
+        <v>17.05</v>
       </c>
       <c r="O114" s="12">
         <v>0</v>
@@ -8539,10 +8535,10 @@
         <v>0</v>
       </c>
       <c r="Q114" s="12">
-        <v>12792404.41</v>
+        <v>12786288.41</v>
       </c>
       <c r="R114" s="13">
-        <v>17.059999999999999</v>
+        <v>17.05</v>
       </c>
     </row>
     <row r="115" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -8731,40 +8727,40 @@
         <v>230702200</v>
       </c>
       <c r="G118" s="14">
-        <v>156871820.71000001</v>
+        <v>157197866.69</v>
       </c>
       <c r="H118" s="15">
-        <v>68</v>
+        <v>68.14</v>
       </c>
       <c r="I118" s="14">
-        <v>33443961.170000002</v>
+        <v>33065125.059999999</v>
       </c>
       <c r="J118" s="15">
-        <v>14.5</v>
+        <v>14.33</v>
       </c>
       <c r="K118" s="14">
-        <v>190315781.88</v>
+        <v>190262991.75</v>
       </c>
       <c r="L118" s="15">
-        <v>82.49</v>
+        <v>82.47</v>
       </c>
       <c r="M118" s="14">
-        <v>40386418.119999997</v>
+        <v>40439208.25</v>
       </c>
       <c r="N118" s="15">
-        <v>17.510000000000002</v>
+        <v>17.53</v>
       </c>
       <c r="O118" s="14">
-        <v>10588306.27</v>
+        <v>10656306.27</v>
       </c>
       <c r="P118" s="15">
-        <v>4.59</v>
+        <v>4.62</v>
       </c>
       <c r="Q118" s="14">
-        <v>29798111.850000001</v>
+        <v>29782901.98</v>
       </c>
       <c r="R118" s="15">
-        <v>12.92</v>
+        <v>12.91</v>
       </c>
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
@@ -8778,37 +8774,37 @@
         <v>101298156.95</v>
       </c>
       <c r="D119" s="4">
-        <v>71946</v>
+        <v>74571</v>
       </c>
       <c r="E119" s="4">
         <v>0</v>
       </c>
       <c r="F119" s="4">
-        <v>101370102.95</v>
+        <v>101372727.95</v>
       </c>
       <c r="G119" s="4">
-        <v>28497772.09</v>
+        <v>29472433.390000001</v>
       </c>
       <c r="H119" s="5">
-        <v>28.11</v>
+        <v>29.07</v>
       </c>
       <c r="I119" s="4">
-        <v>19891917.98</v>
+        <v>17548472.68</v>
       </c>
       <c r="J119" s="5">
-        <v>19.62</v>
+        <v>17.309999999999999</v>
       </c>
       <c r="K119" s="4">
-        <v>48389690.07</v>
+        <v>47020906.07</v>
       </c>
       <c r="L119" s="5">
-        <v>47.74</v>
+        <v>46.38</v>
       </c>
       <c r="M119" s="4">
-        <v>52980412.880000003</v>
+        <v>54351821.880000003</v>
       </c>
       <c r="N119" s="5">
-        <v>52.26</v>
+        <v>53.62</v>
       </c>
       <c r="O119" s="4">
         <v>4899593</v>
@@ -8817,10 +8813,10 @@
         <v>4.83</v>
       </c>
       <c r="Q119" s="4">
-        <v>48080819.880000003</v>
+        <v>49452228.880000003</v>
       </c>
       <c r="R119" s="5">
-        <v>47.43</v>
+        <v>48.78</v>
       </c>
     </row>
     <row r="120" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -9795,28 +9791,28 @@
         <v>7840527.8099999996</v>
       </c>
       <c r="G137" s="8">
-        <v>5771723.29</v>
+        <v>5817758.5899999999</v>
       </c>
       <c r="H137" s="9">
-        <v>73.61</v>
+        <v>74.2</v>
       </c>
       <c r="I137" s="8">
-        <v>999782.16</v>
+        <v>973946.86</v>
       </c>
       <c r="J137" s="9">
-        <v>12.75</v>
+        <v>12.42</v>
       </c>
       <c r="K137" s="8">
-        <v>6771505.4500000002</v>
+        <v>6791705.4500000002</v>
       </c>
       <c r="L137" s="9">
-        <v>86.37</v>
+        <v>86.62</v>
       </c>
       <c r="M137" s="8">
-        <v>1069022.3600000001</v>
+        <v>1048822.3600000001</v>
       </c>
       <c r="N137" s="9">
-        <v>13.63</v>
+        <v>13.38</v>
       </c>
       <c r="O137" s="8">
         <v>106945</v>
@@ -9825,10 +9821,10 @@
         <v>1.36</v>
       </c>
       <c r="Q137" s="8">
-        <v>962077.36</v>
+        <v>941877.36</v>
       </c>
       <c r="R137" s="9">
-        <v>12.27</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="138" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -9851,16 +9847,16 @@
         <v>2672753.2999999998</v>
       </c>
       <c r="G138" s="12">
-        <v>2666185.1</v>
+        <v>2713180.4</v>
       </c>
       <c r="H138" s="13">
-        <v>99.75</v>
+        <v>101.51</v>
       </c>
       <c r="I138" s="12">
-        <v>389425</v>
+        <v>342429.7</v>
       </c>
       <c r="J138" s="13">
-        <v>14.57</v>
+        <v>12.81</v>
       </c>
       <c r="K138" s="12">
         <v>3055610.1</v>
@@ -10019,28 +10015,28 @@
         <v>586550</v>
       </c>
       <c r="G141" s="12">
-        <v>684845.35</v>
+        <v>683885.35</v>
       </c>
       <c r="H141" s="13">
-        <v>116.76</v>
+        <v>116.59</v>
       </c>
       <c r="I141" s="12">
-        <v>104000</v>
+        <v>125160</v>
       </c>
       <c r="J141" s="13">
-        <v>17.73</v>
+        <v>21.34</v>
       </c>
       <c r="K141" s="12">
-        <v>788845.35</v>
+        <v>809045.35</v>
       </c>
       <c r="L141" s="13">
-        <v>134.49</v>
+        <v>137.93</v>
       </c>
       <c r="M141" s="12">
-        <v>-202295.35</v>
+        <v>-222495.35</v>
       </c>
       <c r="N141" s="13">
-        <v>-34.49</v>
+        <v>-37.93</v>
       </c>
       <c r="O141" s="12">
         <v>50000</v>
@@ -10049,10 +10045,10 @@
         <v>8.52</v>
       </c>
       <c r="Q141" s="12">
-        <v>-252295.35</v>
+        <v>-272495.34999999998</v>
       </c>
       <c r="R141" s="13">
-        <v>-43.01</v>
+        <v>-46.46</v>
       </c>
     </row>
     <row r="142" spans="1:18" x14ac:dyDescent="0.25">
@@ -11643,28 +11639,28 @@
         <v>8926239.0199999996</v>
       </c>
       <c r="G170" s="8">
-        <v>1303645.78</v>
+        <v>2060571.78</v>
       </c>
       <c r="H170" s="9">
-        <v>14.6</v>
+        <v>23.08</v>
       </c>
       <c r="I170" s="8">
-        <v>5403925</v>
+        <v>4551805</v>
       </c>
       <c r="J170" s="9">
-        <v>60.54</v>
+        <v>50.99</v>
       </c>
       <c r="K170" s="8">
-        <v>6707570.7800000003</v>
+        <v>6612376.7800000003</v>
       </c>
       <c r="L170" s="9">
-        <v>75.14</v>
+        <v>74.08</v>
       </c>
       <c r="M170" s="8">
-        <v>2218668.2400000002</v>
+        <v>2313862.2400000002</v>
       </c>
       <c r="N170" s="9">
-        <v>24.86</v>
+        <v>25.92</v>
       </c>
       <c r="O170" s="8">
         <v>15000</v>
@@ -11673,10 +11669,10 @@
         <v>0.17</v>
       </c>
       <c r="Q170" s="8">
-        <v>2203668.2400000002</v>
+        <v>2298862.2400000002</v>
       </c>
       <c r="R170" s="9">
-        <v>24.69</v>
+        <v>25.75</v>
       </c>
     </row>
     <row r="171" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -12203,28 +12199,28 @@
         <v>849000</v>
       </c>
       <c r="G180" s="12">
-        <v>0</v>
+        <v>271926</v>
       </c>
       <c r="H180" s="13">
-        <v>0</v>
+        <v>32.03</v>
       </c>
       <c r="I180" s="12">
-        <v>1272080</v>
+        <v>904960</v>
       </c>
       <c r="J180" s="13">
-        <v>149.83000000000001</v>
+        <v>106.59</v>
       </c>
       <c r="K180" s="12">
-        <v>1272080</v>
+        <v>1176886</v>
       </c>
       <c r="L180" s="13">
-        <v>149.83000000000001</v>
+        <v>138.62</v>
       </c>
       <c r="M180" s="12">
-        <v>-423080</v>
+        <v>-327886</v>
       </c>
       <c r="N180" s="13">
-        <v>-49.83</v>
+        <v>-38.619999999999997</v>
       </c>
       <c r="O180" s="12">
         <v>0</v>
@@ -12233,10 +12229,10 @@
         <v>0</v>
       </c>
       <c r="Q180" s="12">
-        <v>-423080</v>
+        <v>-327886</v>
       </c>
       <c r="R180" s="13">
-        <v>-49.83</v>
+        <v>-38.619999999999997</v>
       </c>
     </row>
     <row r="181" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -12259,16 +12255,16 @@
         <v>1016489.02</v>
       </c>
       <c r="G181" s="12">
-        <v>0</v>
+        <v>485000</v>
       </c>
       <c r="H181" s="13">
-        <v>0</v>
+        <v>47.71</v>
       </c>
       <c r="I181" s="12">
-        <v>485000</v>
+        <v>0</v>
       </c>
       <c r="J181" s="13">
-        <v>47.71</v>
+        <v>0</v>
       </c>
       <c r="K181" s="12">
         <v>485000</v>
@@ -14169,22 +14165,22 @@
         <v>17.12</v>
       </c>
       <c r="I215" s="8">
-        <v>2737311</v>
+        <v>2607311</v>
       </c>
       <c r="J215" s="9">
-        <v>14.71</v>
+        <v>14.01</v>
       </c>
       <c r="K215" s="8">
-        <v>5922713.0300000003</v>
+        <v>5792713.0300000003</v>
       </c>
       <c r="L215" s="9">
-        <v>31.83</v>
+        <v>31.13</v>
       </c>
       <c r="M215" s="8">
-        <v>12683169.390000001</v>
+        <v>12813169.390000001</v>
       </c>
       <c r="N215" s="9">
-        <v>68.17</v>
+        <v>68.87</v>
       </c>
       <c r="O215" s="8">
         <v>3295000</v>
@@ -14193,10 +14189,10 @@
         <v>17.71</v>
       </c>
       <c r="Q215" s="8">
-        <v>9388169.3900000006</v>
+        <v>9518169.3900000006</v>
       </c>
       <c r="R215" s="9">
-        <v>50.46</v>
+        <v>51.16</v>
       </c>
     </row>
     <row r="216" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -14673,22 +14669,22 @@
         <v>0</v>
       </c>
       <c r="I224" s="12">
-        <v>483220</v>
+        <v>353220</v>
       </c>
       <c r="J224" s="13">
-        <v>96.22</v>
+        <v>70.33</v>
       </c>
       <c r="K224" s="12">
-        <v>483220</v>
+        <v>353220</v>
       </c>
       <c r="L224" s="13">
-        <v>96.22</v>
+        <v>70.33</v>
       </c>
       <c r="M224" s="12">
-        <v>18980</v>
+        <v>148980</v>
       </c>
       <c r="N224" s="13">
-        <v>3.78</v>
+        <v>29.67</v>
       </c>
       <c r="O224" s="12">
         <v>0</v>
@@ -14697,10 +14693,10 @@
         <v>0</v>
       </c>
       <c r="Q224" s="12">
-        <v>18980</v>
+        <v>148980</v>
       </c>
       <c r="R224" s="13">
-        <v>3.78</v>
+        <v>29.67</v>
       </c>
     </row>
     <row r="225" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -16123,28 +16119,28 @@
         <v>2528000</v>
       </c>
       <c r="G250" s="8">
-        <v>900179.84</v>
+        <v>952739.83999999997</v>
       </c>
       <c r="H250" s="9">
-        <v>35.61</v>
+        <v>37.69</v>
       </c>
       <c r="I250" s="8">
-        <v>674050</v>
+        <v>625610</v>
       </c>
       <c r="J250" s="9">
-        <v>26.66</v>
+        <v>24.75</v>
       </c>
       <c r="K250" s="8">
-        <v>1574229.84</v>
+        <v>1578349.84</v>
       </c>
       <c r="L250" s="9">
-        <v>62.27</v>
+        <v>62.43</v>
       </c>
       <c r="M250" s="8">
-        <v>953770.16</v>
+        <v>949650.16</v>
       </c>
       <c r="N250" s="9">
-        <v>37.729999999999997</v>
+        <v>37.57</v>
       </c>
       <c r="O250" s="8">
         <v>20000</v>
@@ -16153,10 +16149,10 @@
         <v>0.79</v>
       </c>
       <c r="Q250" s="8">
-        <v>933770.16</v>
+        <v>929650.16</v>
       </c>
       <c r="R250" s="9">
-        <v>36.94</v>
+        <v>36.770000000000003</v>
       </c>
     </row>
     <row r="251" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -16179,28 +16175,28 @@
         <v>792000</v>
       </c>
       <c r="G251" s="12">
-        <v>331625</v>
+        <v>359185</v>
       </c>
       <c r="H251" s="13">
-        <v>41.87</v>
+        <v>45.35</v>
       </c>
       <c r="I251" s="12">
-        <v>275440</v>
+        <v>252000</v>
       </c>
       <c r="J251" s="13">
-        <v>34.78</v>
+        <v>31.82</v>
       </c>
       <c r="K251" s="12">
-        <v>607065</v>
+        <v>611185</v>
       </c>
       <c r="L251" s="13">
-        <v>76.650000000000006</v>
+        <v>77.17</v>
       </c>
       <c r="M251" s="12">
-        <v>184935</v>
+        <v>180815</v>
       </c>
       <c r="N251" s="13">
-        <v>23.35</v>
+        <v>22.83</v>
       </c>
       <c r="O251" s="12">
         <v>20000</v>
@@ -16209,10 +16205,10 @@
         <v>2.5299999999999998</v>
       </c>
       <c r="Q251" s="12">
-        <v>164935</v>
+        <v>160815</v>
       </c>
       <c r="R251" s="13">
-        <v>20.83</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="252" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -16235,16 +16231,16 @@
         <v>944000</v>
       </c>
       <c r="G252" s="12">
-        <v>276027.24</v>
+        <v>301027.24</v>
       </c>
       <c r="H252" s="13">
-        <v>29.24</v>
+        <v>31.89</v>
       </c>
       <c r="I252" s="12">
-        <v>220000</v>
+        <v>195000</v>
       </c>
       <c r="J252" s="13">
-        <v>23.31</v>
+        <v>20.66</v>
       </c>
       <c r="K252" s="12">
         <v>496027.24</v>
@@ -16347,28 +16343,28 @@
         <v>12554100</v>
       </c>
       <c r="G254" s="8">
-        <v>3499420.44</v>
+        <v>3619010.44</v>
       </c>
       <c r="H254" s="9">
-        <v>27.87</v>
+        <v>28.83</v>
       </c>
       <c r="I254" s="8">
-        <v>1152503.56</v>
+        <v>968903.56</v>
       </c>
       <c r="J254" s="9">
-        <v>9.18</v>
+        <v>7.72</v>
       </c>
       <c r="K254" s="8">
-        <v>4651924</v>
+        <v>4587914</v>
       </c>
       <c r="L254" s="9">
-        <v>37.06</v>
+        <v>36.549999999999997</v>
       </c>
       <c r="M254" s="8">
-        <v>7902176</v>
+        <v>7966186</v>
       </c>
       <c r="N254" s="9">
-        <v>62.94</v>
+        <v>63.45</v>
       </c>
       <c r="O254" s="8">
         <v>715148</v>
@@ -16377,10 +16373,10 @@
         <v>5.7</v>
       </c>
       <c r="Q254" s="8">
-        <v>7187028</v>
+        <v>7251038</v>
       </c>
       <c r="R254" s="9">
-        <v>57.25</v>
+        <v>57.76</v>
       </c>
     </row>
     <row r="255" spans="1:18" ht="132" x14ac:dyDescent="0.25">
@@ -16459,28 +16455,28 @@
         <v>4556000</v>
       </c>
       <c r="G256" s="12">
-        <v>1705173</v>
+        <v>1824763</v>
       </c>
       <c r="H256" s="13">
-        <v>37.43</v>
+        <v>40.049999999999997</v>
       </c>
       <c r="I256" s="12">
-        <v>653900</v>
+        <v>515300</v>
       </c>
       <c r="J256" s="13">
-        <v>14.35</v>
+        <v>11.31</v>
       </c>
       <c r="K256" s="12">
-        <v>2359073</v>
+        <v>2340063</v>
       </c>
       <c r="L256" s="13">
-        <v>51.78</v>
+        <v>51.36</v>
       </c>
       <c r="M256" s="12">
-        <v>2196927</v>
+        <v>2215937</v>
       </c>
       <c r="N256" s="13">
-        <v>48.22</v>
+        <v>48.64</v>
       </c>
       <c r="O256" s="12">
         <v>211000</v>
@@ -16489,10 +16485,10 @@
         <v>4.63</v>
       </c>
       <c r="Q256" s="12">
-        <v>1985927</v>
+        <v>2004937</v>
       </c>
       <c r="R256" s="13">
-        <v>43.59</v>
+        <v>44.01</v>
       </c>
     </row>
     <row r="257" spans="1:18" x14ac:dyDescent="0.25">
@@ -16521,22 +16517,22 @@
         <v>28.53</v>
       </c>
       <c r="I257" s="12">
-        <v>330603.56</v>
+        <v>285603.56</v>
       </c>
       <c r="J257" s="13">
-        <v>12.11</v>
+        <v>10.46</v>
       </c>
       <c r="K257" s="12">
-        <v>1109357</v>
+        <v>1064357</v>
       </c>
       <c r="L257" s="13">
-        <v>40.64</v>
+        <v>38.99</v>
       </c>
       <c r="M257" s="12">
-        <v>1620643</v>
+        <v>1665643</v>
       </c>
       <c r="N257" s="13">
-        <v>59.36</v>
+        <v>61.01</v>
       </c>
       <c r="O257" s="12">
         <v>148</v>
@@ -16545,10 +16541,10 @@
         <v>0.01</v>
       </c>
       <c r="Q257" s="12">
-        <v>1620495</v>
+        <v>1665495</v>
       </c>
       <c r="R257" s="13">
-        <v>59.36</v>
+        <v>61.01</v>
       </c>
     </row>
     <row r="258" spans="1:18" x14ac:dyDescent="0.25">
@@ -17075,28 +17071,28 @@
         <v>19811100</v>
       </c>
       <c r="G267" s="8">
-        <v>3110261.97</v>
+        <v>3109811.97</v>
       </c>
       <c r="H267" s="9">
         <v>15.7</v>
       </c>
       <c r="I267" s="8">
-        <v>5651908.0300000003</v>
+        <v>4523658.03</v>
       </c>
       <c r="J267" s="9">
-        <v>28.53</v>
+        <v>22.83</v>
       </c>
       <c r="K267" s="8">
-        <v>8762170</v>
+        <v>7633470</v>
       </c>
       <c r="L267" s="9">
-        <v>44.23</v>
+        <v>38.53</v>
       </c>
       <c r="M267" s="8">
-        <v>11048930</v>
+        <v>12177630</v>
       </c>
       <c r="N267" s="9">
-        <v>55.77</v>
+        <v>61.47</v>
       </c>
       <c r="O267" s="8">
         <v>0</v>
@@ -17105,10 +17101,10 @@
         <v>0</v>
       </c>
       <c r="Q267" s="8">
-        <v>11048930</v>
+        <v>12177630</v>
       </c>
       <c r="R267" s="9">
-        <v>55.77</v>
+        <v>61.47</v>
       </c>
     </row>
     <row r="268" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -17193,22 +17189,22 @@
         <v>28.85</v>
       </c>
       <c r="I269" s="12">
-        <v>5400000</v>
+        <v>4200000</v>
       </c>
       <c r="J269" s="13">
-        <v>51.92</v>
+        <v>40.380000000000003</v>
       </c>
       <c r="K269" s="12">
-        <v>8400000</v>
+        <v>7200000</v>
       </c>
       <c r="L269" s="13">
-        <v>80.77</v>
+        <v>69.23</v>
       </c>
       <c r="M269" s="12">
-        <v>2000000</v>
+        <v>3200000</v>
       </c>
       <c r="N269" s="13">
-        <v>19.23</v>
+        <v>30.77</v>
       </c>
       <c r="O269" s="12">
         <v>0</v>
@@ -17217,10 +17213,10 @@
         <v>0</v>
       </c>
       <c r="Q269" s="12">
-        <v>2000000</v>
+        <v>3200000</v>
       </c>
       <c r="R269" s="13">
-        <v>19.23</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="270" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -17417,22 +17413,22 @@
         <v>2.63</v>
       </c>
       <c r="I273" s="12">
-        <v>243238.03</v>
+        <v>314988.03000000003</v>
       </c>
       <c r="J273" s="13">
-        <v>6.58</v>
+        <v>8.52</v>
       </c>
       <c r="K273" s="12">
-        <v>340500</v>
+        <v>412250</v>
       </c>
       <c r="L273" s="13">
-        <v>9.2100000000000009</v>
+        <v>11.15</v>
       </c>
       <c r="M273" s="12">
-        <v>3356700</v>
+        <v>3284950</v>
       </c>
       <c r="N273" s="13">
-        <v>90.79</v>
+        <v>88.85</v>
       </c>
       <c r="O273" s="12">
         <v>0</v>
@@ -17441,10 +17437,10 @@
         <v>0</v>
       </c>
       <c r="Q273" s="12">
-        <v>3356700</v>
+        <v>3284950</v>
       </c>
       <c r="R273" s="13">
-        <v>90.79</v>
+        <v>88.85</v>
       </c>
     </row>
     <row r="274" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -17467,10 +17463,10 @@
         <v>406250</v>
       </c>
       <c r="G274" s="12">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="H274" s="13">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="I274" s="12">
         <v>300</v>
@@ -17479,16 +17475,16 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="K274" s="12">
-        <v>750</v>
+        <v>300</v>
       </c>
       <c r="L274" s="13">
-        <v>0.18</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="M274" s="12">
-        <v>405500</v>
+        <v>405950</v>
       </c>
       <c r="N274" s="13">
-        <v>99.82</v>
+        <v>99.93</v>
       </c>
       <c r="O274" s="12">
         <v>0</v>
@@ -17497,10 +17493,10 @@
         <v>0</v>
       </c>
       <c r="Q274" s="12">
-        <v>405500</v>
+        <v>405950</v>
       </c>
       <c r="R274" s="13">
-        <v>99.82</v>
+        <v>99.93</v>
       </c>
     </row>
     <row r="275" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -17570,13 +17566,13 @@
         <v>2205500</v>
       </c>
       <c r="D276" s="8">
-        <v>0</v>
+        <v>2625</v>
       </c>
       <c r="E276" s="8">
         <v>0</v>
       </c>
       <c r="F276" s="8">
-        <v>2205500</v>
+        <v>2208125</v>
       </c>
       <c r="G276" s="8">
         <v>26325</v>
@@ -17585,34 +17581,34 @@
         <v>1.19</v>
       </c>
       <c r="I276" s="8">
-        <v>1224700</v>
+        <v>1249500</v>
       </c>
       <c r="J276" s="9">
-        <v>55.53</v>
+        <v>56.59</v>
       </c>
       <c r="K276" s="8">
-        <v>1251025</v>
+        <v>1275825</v>
       </c>
       <c r="L276" s="9">
-        <v>56.72</v>
+        <v>57.78</v>
       </c>
       <c r="M276" s="8">
-        <v>954475</v>
+        <v>932300</v>
       </c>
       <c r="N276" s="9">
-        <v>43.28</v>
+        <v>42.22</v>
       </c>
       <c r="O276" s="8">
         <v>360000</v>
       </c>
       <c r="P276" s="9">
-        <v>16.32</v>
+        <v>16.3</v>
       </c>
       <c r="Q276" s="8">
-        <v>594475</v>
+        <v>572300</v>
       </c>
       <c r="R276" s="9">
-        <v>26.95</v>
+        <v>25.92</v>
       </c>
     </row>
     <row r="277" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -17641,22 +17637,22 @@
         <v>0</v>
       </c>
       <c r="I277" s="12">
-        <v>1172500</v>
+        <v>1197300</v>
       </c>
       <c r="J277" s="13">
-        <v>66.48</v>
+        <v>67.88</v>
       </c>
       <c r="K277" s="12">
-        <v>1172500</v>
+        <v>1197300</v>
       </c>
       <c r="L277" s="13">
-        <v>66.48</v>
+        <v>67.88</v>
       </c>
       <c r="M277" s="12">
-        <v>591250</v>
+        <v>566450</v>
       </c>
       <c r="N277" s="13">
-        <v>33.520000000000003</v>
+        <v>32.119999999999997</v>
       </c>
       <c r="O277" s="12">
         <v>360000</v>
@@ -17665,10 +17661,10 @@
         <v>20.41</v>
       </c>
       <c r="Q277" s="12">
-        <v>231250</v>
+        <v>206450</v>
       </c>
       <c r="R277" s="13">
-        <v>13.11</v>
+        <v>11.71</v>
       </c>
     </row>
     <row r="278" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -17738,37 +17734,37 @@
         <v>177750</v>
       </c>
       <c r="D279" s="12">
-        <v>0</v>
+        <v>2625</v>
       </c>
       <c r="E279" s="12">
         <v>0</v>
       </c>
       <c r="F279" s="12">
-        <v>177750</v>
+        <v>180375</v>
       </c>
       <c r="G279" s="12">
         <v>26325</v>
       </c>
       <c r="H279" s="13">
-        <v>14.81</v>
+        <v>14.59</v>
       </c>
       <c r="I279" s="12">
         <v>52200</v>
       </c>
       <c r="J279" s="13">
-        <v>29.37</v>
+        <v>28.94</v>
       </c>
       <c r="K279" s="12">
         <v>78525</v>
       </c>
       <c r="L279" s="13">
-        <v>44.18</v>
+        <v>43.53</v>
       </c>
       <c r="M279" s="12">
-        <v>99225</v>
+        <v>101850</v>
       </c>
       <c r="N279" s="13">
-        <v>55.82</v>
+        <v>56.47</v>
       </c>
       <c r="O279" s="12">
         <v>0</v>
@@ -17777,10 +17773,10 @@
         <v>0</v>
       </c>
       <c r="Q279" s="12">
-        <v>99225</v>
+        <v>101850</v>
       </c>
       <c r="R279" s="13">
-        <v>55.82</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="280" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -18128,37 +18124,37 @@
         <v>101298156.95</v>
       </c>
       <c r="D286" s="14">
-        <v>71946</v>
+        <v>74571</v>
       </c>
       <c r="E286" s="14">
         <v>0</v>
       </c>
       <c r="F286" s="14">
-        <v>101370102.95</v>
+        <v>101372727.95</v>
       </c>
       <c r="G286" s="14">
-        <v>28497772.09</v>
+        <v>29472433.390000001</v>
       </c>
       <c r="H286" s="15">
-        <v>28.11</v>
+        <v>29.07</v>
       </c>
       <c r="I286" s="14">
-        <v>19891917.98</v>
+        <v>17548472.68</v>
       </c>
       <c r="J286" s="15">
-        <v>19.62</v>
+        <v>17.309999999999999</v>
       </c>
       <c r="K286" s="14">
-        <v>48389690.07</v>
+        <v>47020906.07</v>
       </c>
       <c r="L286" s="15">
-        <v>47.74</v>
+        <v>46.38</v>
       </c>
       <c r="M286" s="14">
-        <v>52980412.880000003</v>
+        <v>54351821.880000003</v>
       </c>
       <c r="N286" s="15">
-        <v>52.26</v>
+        <v>53.62</v>
       </c>
       <c r="O286" s="14">
         <v>4899593</v>
@@ -18167,10 +18163,10 @@
         <v>4.83</v>
       </c>
       <c r="Q286" s="14">
-        <v>48080819.880000003</v>
+        <v>49452228.880000003</v>
       </c>
       <c r="R286" s="15">
-        <v>47.43</v>
+        <v>48.78</v>
       </c>
     </row>
     <row r="287" spans="1:18" x14ac:dyDescent="0.25">
@@ -18182,49 +18178,49 @@
         <v>332000356.94999999</v>
       </c>
       <c r="D287" s="16">
-        <v>71946</v>
+        <v>74571</v>
       </c>
       <c r="E287" s="16">
         <v>0</v>
       </c>
       <c r="F287" s="16">
-        <v>332072302.94999999</v>
+        <v>332074927.94999999</v>
       </c>
       <c r="G287" s="16">
-        <v>185369592.80000001</v>
+        <v>186670300.08000001</v>
       </c>
       <c r="H287" s="17">
-        <v>55.82</v>
+        <v>56.21</v>
       </c>
       <c r="I287" s="16">
-        <v>53335879.149999999</v>
+        <v>50613597.740000002</v>
       </c>
       <c r="J287" s="17">
-        <v>16.059999999999999</v>
+        <v>15.24</v>
       </c>
       <c r="K287" s="16">
-        <v>238705471.94999999</v>
+        <v>237283897.81999999</v>
       </c>
       <c r="L287" s="17">
-        <v>71.88</v>
+        <v>71.45</v>
       </c>
       <c r="M287" s="16">
-        <v>93366831</v>
+        <v>94791030.129999995</v>
       </c>
       <c r="N287" s="17">
-        <v>28.12</v>
+        <v>28.55</v>
       </c>
       <c r="O287" s="16">
-        <v>15487899.27</v>
+        <v>15555899.27</v>
       </c>
       <c r="P287" s="17">
-        <v>4.66</v>
+        <v>4.68</v>
       </c>
       <c r="Q287" s="16">
-        <v>77878931.730000004</v>
+        <v>79235130.859999999</v>
       </c>
       <c r="R287" s="17">
-        <v>23.45</v>
+        <v>23.86</v>
       </c>
     </row>
     <row r="288" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -18458,49 +18454,49 @@
         <v>338655937.13</v>
       </c>
       <c r="D292" s="16">
-        <v>71946</v>
+        <v>74571</v>
       </c>
       <c r="E292" s="16">
         <v>0</v>
       </c>
       <c r="F292" s="16">
-        <v>338727883.13</v>
+        <v>338730508.13</v>
       </c>
       <c r="G292" s="16">
-        <v>185369592.80000001</v>
+        <v>186670300.08000001</v>
       </c>
       <c r="H292" s="17">
-        <v>54.73</v>
+        <v>55.11</v>
       </c>
       <c r="I292" s="16">
-        <v>53335879.149999999</v>
+        <v>50613597.740000002</v>
       </c>
       <c r="J292" s="17">
-        <v>15.75</v>
+        <v>14.94</v>
       </c>
       <c r="K292" s="16">
-        <v>238705471.94999999</v>
+        <v>237283897.81999999</v>
       </c>
       <c r="L292" s="17">
-        <v>70.47</v>
+        <v>70.05</v>
       </c>
       <c r="M292" s="16">
-        <v>100022411.18000001</v>
+        <v>101446610.31</v>
       </c>
       <c r="N292" s="17">
-        <v>29.53</v>
+        <v>29.95</v>
       </c>
       <c r="O292" s="16">
-        <v>15487899.27</v>
+        <v>15555899.27</v>
       </c>
       <c r="P292" s="17">
-        <v>4.57</v>
+        <v>4.59</v>
       </c>
       <c r="Q292" s="16">
-        <v>84534511.909999996</v>
+        <v>85890711.040000007</v>
       </c>
       <c r="R292" s="17">
-        <v>24.96</v>
+        <v>25.36</v>
       </c>
     </row>
     <row r="293" spans="1:18" x14ac:dyDescent="0.25">
@@ -18517,34 +18513,34 @@
         <v>0</v>
       </c>
       <c r="E293" s="4">
-        <v>71946</v>
+        <v>74571</v>
       </c>
       <c r="F293" s="4">
-        <v>3965994.24</v>
+        <v>3963369.24</v>
       </c>
       <c r="G293" s="4">
         <v>558139.18000000005</v>
       </c>
       <c r="H293" s="5">
-        <v>14.07</v>
+        <v>14.08</v>
       </c>
       <c r="I293" s="4">
         <v>156393.70000000001</v>
       </c>
       <c r="J293" s="5">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="K293" s="4">
         <v>714532.88</v>
       </c>
       <c r="L293" s="5">
-        <v>18.02</v>
+        <v>18.03</v>
       </c>
       <c r="M293" s="4">
-        <v>3251461.36</v>
+        <v>3248836.36</v>
       </c>
       <c r="N293" s="5">
-        <v>81.98</v>
+        <v>81.97</v>
       </c>
       <c r="O293" s="4">
         <v>6129.12</v>
@@ -18553,10 +18549,10 @@
         <v>0.15</v>
       </c>
       <c r="Q293" s="4">
-        <v>3245332.24</v>
+        <v>3242707.24</v>
       </c>
       <c r="R293" s="5">
-        <v>81.83</v>
+        <v>81.819999999999993</v>
       </c>
     </row>
     <row r="294" spans="1:18" x14ac:dyDescent="0.25">
@@ -18573,34 +18569,34 @@
         <v>0</v>
       </c>
       <c r="E294" s="8">
-        <v>71946</v>
+        <v>74571</v>
       </c>
       <c r="F294" s="8">
-        <v>3965994.24</v>
+        <v>3963369.24</v>
       </c>
       <c r="G294" s="8">
         <v>558139.18000000005</v>
       </c>
       <c r="H294" s="9">
-        <v>14.07</v>
+        <v>14.08</v>
       </c>
       <c r="I294" s="8">
         <v>156393.70000000001</v>
       </c>
       <c r="J294" s="9">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="K294" s="8">
         <v>714532.88</v>
       </c>
       <c r="L294" s="9">
-        <v>18.02</v>
+        <v>18.03</v>
       </c>
       <c r="M294" s="8">
-        <v>3251461.36</v>
+        <v>3248836.36</v>
       </c>
       <c r="N294" s="9">
-        <v>81.98</v>
+        <v>81.97</v>
       </c>
       <c r="O294" s="8">
         <v>6129.12</v>
@@ -18609,10 +18605,10 @@
         <v>0.15</v>
       </c>
       <c r="Q294" s="8">
-        <v>3245332.24</v>
+        <v>3242707.24</v>
       </c>
       <c r="R294" s="9">
-        <v>81.83</v>
+        <v>81.819999999999993</v>
       </c>
     </row>
     <row r="295" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -18629,34 +18625,34 @@
         <v>0</v>
       </c>
       <c r="E295" s="12">
-        <v>71946</v>
+        <v>74571</v>
       </c>
       <c r="F295" s="12">
-        <v>3965994.24</v>
+        <v>3963369.24</v>
       </c>
       <c r="G295" s="12">
         <v>558139.18000000005</v>
       </c>
       <c r="H295" s="13">
-        <v>14.07</v>
+        <v>14.08</v>
       </c>
       <c r="I295" s="12">
         <v>156393.70000000001</v>
       </c>
       <c r="J295" s="13">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="K295" s="12">
         <v>714532.88</v>
       </c>
       <c r="L295" s="13">
-        <v>18.02</v>
+        <v>18.03</v>
       </c>
       <c r="M295" s="12">
-        <v>3251461.36</v>
+        <v>3248836.36</v>
       </c>
       <c r="N295" s="13">
-        <v>81.98</v>
+        <v>81.97</v>
       </c>
       <c r="O295" s="12">
         <v>6129.12</v>
@@ -18665,10 +18661,10 @@
         <v>0.15</v>
       </c>
       <c r="Q295" s="12">
-        <v>3245332.24</v>
+        <v>3242707.24</v>
       </c>
       <c r="R295" s="13">
-        <v>81.83</v>
+        <v>81.819999999999993</v>
       </c>
     </row>
     <row r="296" spans="1:18" x14ac:dyDescent="0.25">
@@ -18683,34 +18679,34 @@
         <v>0</v>
       </c>
       <c r="E296" s="14">
-        <v>71946</v>
+        <v>74571</v>
       </c>
       <c r="F296" s="14">
-        <v>3965994.24</v>
+        <v>3963369.24</v>
       </c>
       <c r="G296" s="14">
         <v>558139.18000000005</v>
       </c>
       <c r="H296" s="15">
-        <v>14.07</v>
+        <v>14.08</v>
       </c>
       <c r="I296" s="14">
         <v>156393.70000000001</v>
       </c>
       <c r="J296" s="15">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="K296" s="14">
         <v>714532.88</v>
       </c>
       <c r="L296" s="15">
-        <v>18.02</v>
+        <v>18.03</v>
       </c>
       <c r="M296" s="14">
-        <v>3251461.36</v>
+        <v>3248836.36</v>
       </c>
       <c r="N296" s="15">
-        <v>81.98</v>
+        <v>81.97</v>
       </c>
       <c r="O296" s="14">
         <v>6129.12</v>
@@ -18719,10 +18715,10 @@
         <v>0.15</v>
       </c>
       <c r="Q296" s="14">
-        <v>3245332.24</v>
+        <v>3242707.24</v>
       </c>
       <c r="R296" s="15">
-        <v>81.83</v>
+        <v>81.819999999999993</v>
       </c>
     </row>
     <row r="297" spans="1:18" x14ac:dyDescent="0.25">
@@ -18734,49 +18730,49 @@
         <v>342693877.37</v>
       </c>
       <c r="D297" s="16">
-        <v>71946</v>
+        <v>74571</v>
       </c>
       <c r="E297" s="16">
-        <v>71946</v>
+        <v>74571</v>
       </c>
       <c r="F297" s="16">
         <v>342693877.37</v>
       </c>
       <c r="G297" s="16">
-        <v>185927731.97999999</v>
+        <v>187228439.25999999</v>
       </c>
       <c r="H297" s="17">
-        <v>54.25</v>
+        <v>54.63</v>
       </c>
       <c r="I297" s="16">
-        <v>53492272.850000001</v>
+        <v>50769991.439999998</v>
       </c>
       <c r="J297" s="17">
-        <v>15.61</v>
+        <v>14.81</v>
       </c>
       <c r="K297" s="16">
-        <v>239420004.83000001</v>
+        <v>237998430.69999999</v>
       </c>
       <c r="L297" s="17">
-        <v>69.86</v>
+        <v>69.45</v>
       </c>
       <c r="M297" s="16">
-        <v>103273872.54000001</v>
+        <v>104695446.67</v>
       </c>
       <c r="N297" s="17">
-        <v>30.14</v>
+        <v>30.55</v>
       </c>
       <c r="O297" s="16">
-        <v>15494028.390000001</v>
+        <v>15562028.390000001</v>
       </c>
       <c r="P297" s="17">
-        <v>4.5199999999999996</v>
+        <v>4.54</v>
       </c>
       <c r="Q297" s="16">
-        <v>87779844.150000006</v>
+        <v>89133418.280000001</v>
       </c>
       <c r="R297" s="17">
-        <v>25.61</v>
+        <v>26.01</v>
       </c>
     </row>
     <row r="298" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -18799,40 +18795,40 @@
         <v>46540814</v>
       </c>
       <c r="G298" s="19">
-        <v>23670542.129999999</v>
+        <v>23910276</v>
       </c>
       <c r="H298" s="20">
-        <v>50.86</v>
+        <v>51.37</v>
       </c>
       <c r="I298" s="19">
-        <v>14870696.67</v>
+        <v>14530196.67</v>
       </c>
       <c r="J298" s="20">
-        <v>31.95</v>
+        <v>31.22</v>
       </c>
       <c r="K298" s="19">
-        <v>38541238.799999997</v>
+        <v>38440472.670000002</v>
       </c>
       <c r="L298" s="20">
-        <v>82.81</v>
+        <v>82.6</v>
       </c>
       <c r="M298" s="19">
-        <v>7999575.2000000002</v>
+        <v>8100341.3300000001</v>
       </c>
       <c r="N298" s="20">
-        <v>17.190000000000001</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="O298" s="19">
-        <v>1317521.6000000001</v>
+        <v>1385521.6</v>
       </c>
       <c r="P298" s="20">
-        <v>2.83</v>
+        <v>2.98</v>
       </c>
       <c r="Q298" s="19">
-        <v>6682053.5999999996</v>
+        <v>6714819.7300000004</v>
       </c>
       <c r="R298" s="20">
-        <v>14.36</v>
+        <v>14.43</v>
       </c>
     </row>
     <row r="299" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -18855,28 +18851,28 @@
         <v>54940200</v>
       </c>
       <c r="G299" s="19">
-        <v>39899903.969999999</v>
+        <v>39654207.579999998</v>
       </c>
       <c r="H299" s="20">
-        <v>72.62</v>
+        <v>72.180000000000007</v>
       </c>
       <c r="I299" s="19">
-        <v>6393068.6699999999</v>
+        <v>6647725.0599999996</v>
       </c>
       <c r="J299" s="20">
-        <v>11.64</v>
+        <v>12.1</v>
       </c>
       <c r="K299" s="19">
-        <v>46292972.640000001</v>
+        <v>46301932.640000001</v>
       </c>
       <c r="L299" s="20">
-        <v>84.26</v>
+        <v>84.28</v>
       </c>
       <c r="M299" s="19">
-        <v>8647227.3599999994</v>
+        <v>8638267.3599999994</v>
       </c>
       <c r="N299" s="20">
-        <v>15.74</v>
+        <v>15.72</v>
       </c>
       <c r="O299" s="19">
         <v>1155422.5</v>
@@ -18885,10 +18881,10 @@
         <v>2.1</v>
       </c>
       <c r="Q299" s="19">
-        <v>7491804.8600000003</v>
+        <v>7482844.8600000003</v>
       </c>
       <c r="R299" s="20">
-        <v>13.64</v>
+        <v>13.62</v>
       </c>
     </row>
     <row r="300" spans="1:18" x14ac:dyDescent="0.25">
@@ -18917,22 +18913,22 @@
         <v>56.28</v>
       </c>
       <c r="I300" s="19">
-        <v>961508.31</v>
+        <v>960008.31</v>
       </c>
       <c r="J300" s="20">
-        <v>9.81</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="K300" s="19">
-        <v>6476514.9500000002</v>
+        <v>6475014.9500000002</v>
       </c>
       <c r="L300" s="20">
-        <v>66.09</v>
+        <v>66.069999999999993</v>
       </c>
       <c r="M300" s="19">
-        <v>3323485.05</v>
+        <v>3324985.05</v>
       </c>
       <c r="N300" s="20">
-        <v>33.909999999999997</v>
+        <v>33.93</v>
       </c>
       <c r="O300" s="19">
         <v>2287551.54</v>
@@ -18941,10 +18937,10 @@
         <v>23.34</v>
       </c>
       <c r="Q300" s="19">
-        <v>1035933.51</v>
+        <v>1037433.51</v>
       </c>
       <c r="R300" s="20">
-        <v>10.57</v>
+        <v>10.59</v>
       </c>
     </row>
     <row r="301" spans="1:18" x14ac:dyDescent="0.25">
@@ -18958,37 +18954,37 @@
         <v>101298156.95</v>
       </c>
       <c r="D301" s="19">
-        <v>71946</v>
+        <v>74571</v>
       </c>
       <c r="E301" s="19">
         <v>0</v>
       </c>
       <c r="F301" s="19">
-        <v>101370102.95</v>
+        <v>101372727.95</v>
       </c>
       <c r="G301" s="19">
-        <v>28497772.09</v>
+        <v>29472433.390000001</v>
       </c>
       <c r="H301" s="20">
-        <v>28.11</v>
+        <v>29.07</v>
       </c>
       <c r="I301" s="19">
-        <v>19891917.98</v>
+        <v>17548472.68</v>
       </c>
       <c r="J301" s="20">
-        <v>19.62</v>
+        <v>17.309999999999999</v>
       </c>
       <c r="K301" s="19">
-        <v>48389690.07</v>
+        <v>47020906.07</v>
       </c>
       <c r="L301" s="20">
-        <v>47.74</v>
+        <v>46.38</v>
       </c>
       <c r="M301" s="19">
-        <v>52980412.880000003</v>
+        <v>54351821.880000003</v>
       </c>
       <c r="N301" s="20">
-        <v>52.26</v>
+        <v>53.62</v>
       </c>
       <c r="O301" s="19">
         <v>4899593</v>
@@ -18997,10 +18993,10 @@
         <v>4.83</v>
       </c>
       <c r="Q301" s="19">
-        <v>48080819.880000003</v>
+        <v>49452228.880000003</v>
       </c>
       <c r="R301" s="20">
-        <v>47.43</v>
+        <v>48.78</v>
       </c>
     </row>
     <row r="302" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -19073,34 +19069,34 @@
         <v>0</v>
       </c>
       <c r="E303" s="19">
-        <v>71946</v>
+        <v>74571</v>
       </c>
       <c r="F303" s="19">
-        <v>3965994.24</v>
+        <v>3963369.24</v>
       </c>
       <c r="G303" s="19">
         <v>558139.18000000005</v>
       </c>
       <c r="H303" s="20">
-        <v>14.07</v>
+        <v>14.08</v>
       </c>
       <c r="I303" s="19">
         <v>156393.70000000001</v>
       </c>
       <c r="J303" s="20">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="K303" s="19">
         <v>714532.88</v>
       </c>
       <c r="L303" s="20">
-        <v>18.02</v>
+        <v>18.03</v>
       </c>
       <c r="M303" s="19">
-        <v>3251461.36</v>
+        <v>3248836.36</v>
       </c>
       <c r="N303" s="20">
-        <v>81.98</v>
+        <v>81.97</v>
       </c>
       <c r="O303" s="19">
         <v>6129.12</v>
@@ -19109,10 +19105,10 @@
         <v>0.15</v>
       </c>
       <c r="Q303" s="19">
-        <v>3245332.24</v>
+        <v>3242707.24</v>
       </c>
       <c r="R303" s="20">
-        <v>81.83</v>
+        <v>81.819999999999993</v>
       </c>
     </row>
     <row r="304" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -19135,28 +19131,28 @@
         <v>119421186</v>
       </c>
       <c r="G304" s="19">
-        <v>87786367.969999999</v>
+        <v>88118376.469999999</v>
       </c>
       <c r="H304" s="20">
-        <v>73.510000000000005</v>
+        <v>73.790000000000006</v>
       </c>
       <c r="I304" s="19">
-        <v>11218687.52</v>
+        <v>10927195.02</v>
       </c>
       <c r="J304" s="20">
-        <v>9.39</v>
+        <v>9.15</v>
       </c>
       <c r="K304" s="19">
-        <v>99005055.489999995</v>
+        <v>99045571.489999995</v>
       </c>
       <c r="L304" s="20">
-        <v>82.9</v>
+        <v>82.94</v>
       </c>
       <c r="M304" s="19">
-        <v>20416130.510000002</v>
+        <v>20375614.510000002</v>
       </c>
       <c r="N304" s="20">
-        <v>17.100000000000001</v>
+        <v>17.059999999999999</v>
       </c>
       <c r="O304" s="19">
         <v>5827810.6299999999</v>
@@ -19165,10 +19161,10 @@
         <v>4.88</v>
       </c>
       <c r="Q304" s="19">
-        <v>14588319.880000001</v>
+        <v>14547803.880000001</v>
       </c>
       <c r="R304" s="20">
-        <v>12.22</v>
+        <v>12.18</v>
       </c>
     </row>
     <row r="305" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -19236,49 +19232,49 @@
         <v>342693877.37</v>
       </c>
       <c r="D306" s="19">
-        <v>71946</v>
+        <v>74571</v>
       </c>
       <c r="E306" s="19">
-        <v>71946</v>
+        <v>74571</v>
       </c>
       <c r="F306" s="19">
         <v>342693877.37</v>
       </c>
       <c r="G306" s="19">
-        <v>185927731.97999999</v>
+        <v>187228439.25999999</v>
       </c>
       <c r="H306" s="20">
-        <v>54.25</v>
+        <v>54.63</v>
       </c>
       <c r="I306" s="19">
-        <v>53492272.850000001</v>
+        <v>50769991.439999998</v>
       </c>
       <c r="J306" s="20">
-        <v>15.61</v>
+        <v>14.81</v>
       </c>
       <c r="K306" s="19">
-        <v>239420004.83000001</v>
+        <v>237998430.69999999</v>
       </c>
       <c r="L306" s="20">
-        <v>69.86</v>
+        <v>69.45</v>
       </c>
       <c r="M306" s="19">
-        <v>103273872.54000001</v>
+        <v>104695446.67</v>
       </c>
       <c r="N306" s="20">
-        <v>30.14</v>
+        <v>30.55</v>
       </c>
       <c r="O306" s="19">
-        <v>15494028.390000001</v>
+        <v>15562028.390000001</v>
       </c>
       <c r="P306" s="20">
-        <v>4.5199999999999996</v>
+        <v>4.54</v>
       </c>
       <c r="Q306" s="19">
-        <v>87779844.150000006</v>
+        <v>89133418.280000001</v>
       </c>
       <c r="R306" s="20">
-        <v>25.61</v>
+        <v>26.01</v>
       </c>
     </row>
     <row r="307" spans="1:18" x14ac:dyDescent="0.25">
@@ -19319,27 +19315,26 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7BA2E36-AFAE-49FE-9111-E1D1F5311A1B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{282CDDA5-F69B-4E16-884B-87B0D9D5F4AF}">
   <dimension ref="A1:R84"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.59765625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="12.796875" style="28" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.8984375" style="28" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.796875" style="28" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.8984375" style="28" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.8984375" style="28" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.796875" style="28" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.8984375" style="28" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.8984375" style="28" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.3984375" style="28" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.8984375" style="28" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7" style="28" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.796875" style="28" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.3984375" style="28" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.796875" style="28" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7" style="28" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="8.796875" style="28"/>
+    <col min="1" max="1" width="22.09765625" customWidth="1"/>
+    <col min="2" max="2" width="12.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.8984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.8984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.8984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.8984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.8984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.3984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.8984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.3984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -19353,7 +19348,7 @@
       <c r="F1" s="27"/>
       <c r="G1" s="27"/>
     </row>
-    <row r="4" spans="1:18" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
         <v>580</v>
       </c>
@@ -19465,22 +19460,22 @@
         <v>80.56</v>
       </c>
       <c r="I6" s="4">
-        <v>115542</v>
+        <v>135942</v>
       </c>
       <c r="J6" s="5">
-        <v>11.55</v>
+        <v>13.59</v>
       </c>
       <c r="K6" s="4">
-        <v>921093.74</v>
+        <v>941493.74</v>
       </c>
       <c r="L6" s="5">
-        <v>92.11</v>
+        <v>94.15</v>
       </c>
       <c r="M6" s="4">
-        <v>78906.259999999995</v>
+        <v>58506.26</v>
       </c>
       <c r="N6" s="5">
-        <v>7.89</v>
+        <v>5.85</v>
       </c>
       <c r="O6" s="4">
         <v>0</v>
@@ -19489,10 +19484,10 @@
         <v>0</v>
       </c>
       <c r="Q6" s="4">
-        <v>78906.259999999995</v>
+        <v>58506.26</v>
       </c>
       <c r="R6" s="5">
-        <v>7.89</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -19521,22 +19516,22 @@
         <v>80.56</v>
       </c>
       <c r="I7" s="8">
-        <v>115542</v>
+        <v>135942</v>
       </c>
       <c r="J7" s="9">
-        <v>11.55</v>
+        <v>13.59</v>
       </c>
       <c r="K7" s="8">
-        <v>921093.74</v>
+        <v>941493.74</v>
       </c>
       <c r="L7" s="9">
-        <v>92.11</v>
+        <v>94.15</v>
       </c>
       <c r="M7" s="8">
-        <v>78906.259999999995</v>
+        <v>58506.26</v>
       </c>
       <c r="N7" s="9">
-        <v>7.89</v>
+        <v>5.85</v>
       </c>
       <c r="O7" s="8">
         <v>0</v>
@@ -19545,10 +19540,10 @@
         <v>0</v>
       </c>
       <c r="Q7" s="8">
-        <v>78906.259999999995</v>
+        <v>58506.26</v>
       </c>
       <c r="R7" s="9">
-        <v>7.89</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -19575,22 +19570,22 @@
         <v>53.34</v>
       </c>
       <c r="I8" s="4">
-        <v>5570</v>
+        <v>19570</v>
       </c>
       <c r="J8" s="5">
-        <v>0.56000000000000005</v>
+        <v>1.96</v>
       </c>
       <c r="K8" s="4">
-        <v>538949</v>
+        <v>552949</v>
       </c>
       <c r="L8" s="5">
-        <v>53.89</v>
+        <v>55.29</v>
       </c>
       <c r="M8" s="4">
-        <v>461051</v>
+        <v>447051</v>
       </c>
       <c r="N8" s="5">
-        <v>46.11</v>
+        <v>44.71</v>
       </c>
       <c r="O8" s="4">
         <v>0</v>
@@ -19599,10 +19594,10 @@
         <v>0</v>
       </c>
       <c r="Q8" s="4">
-        <v>461051</v>
+        <v>447051</v>
       </c>
       <c r="R8" s="5">
-        <v>46.11</v>
+        <v>44.71</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -19631,22 +19626,22 @@
         <v>53.34</v>
       </c>
       <c r="I9" s="8">
-        <v>5570</v>
+        <v>19570</v>
       </c>
       <c r="J9" s="9">
-        <v>0.56000000000000005</v>
+        <v>1.96</v>
       </c>
       <c r="K9" s="8">
-        <v>538949</v>
+        <v>552949</v>
       </c>
       <c r="L9" s="9">
-        <v>53.89</v>
+        <v>55.29</v>
       </c>
       <c r="M9" s="8">
-        <v>461051</v>
+        <v>447051</v>
       </c>
       <c r="N9" s="9">
-        <v>46.11</v>
+        <v>44.71</v>
       </c>
       <c r="O9" s="8">
         <v>0</v>
@@ -19655,10 +19650,10 @@
         <v>0</v>
       </c>
       <c r="Q9" s="8">
-        <v>461051</v>
+        <v>447051</v>
       </c>
       <c r="R9" s="9">
-        <v>46.11</v>
+        <v>44.71</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -19679,28 +19674,28 @@
         <v>11720000</v>
       </c>
       <c r="G10" s="4">
-        <v>7901987</v>
+        <v>7948887</v>
       </c>
       <c r="H10" s="5">
-        <v>67.42</v>
+        <v>67.819999999999993</v>
       </c>
       <c r="I10" s="4">
-        <v>1671535</v>
+        <v>1650895</v>
       </c>
       <c r="J10" s="5">
-        <v>14.26</v>
+        <v>14.09</v>
       </c>
       <c r="K10" s="4">
-        <v>9573522</v>
+        <v>9599782</v>
       </c>
       <c r="L10" s="5">
-        <v>81.69</v>
+        <v>81.91</v>
       </c>
       <c r="M10" s="4">
-        <v>2146478</v>
+        <v>2120218</v>
       </c>
       <c r="N10" s="5">
-        <v>18.309999999999999</v>
+        <v>18.09</v>
       </c>
       <c r="O10" s="4">
         <v>30600</v>
@@ -19709,10 +19704,10 @@
         <v>0.26</v>
       </c>
       <c r="Q10" s="4">
-        <v>2115878</v>
+        <v>2089618</v>
       </c>
       <c r="R10" s="5">
-        <v>18.05</v>
+        <v>17.829999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -19735,28 +19730,28 @@
         <v>11720000</v>
       </c>
       <c r="G11" s="8">
-        <v>7901987</v>
+        <v>7948887</v>
       </c>
       <c r="H11" s="9">
-        <v>67.42</v>
+        <v>67.819999999999993</v>
       </c>
       <c r="I11" s="8">
-        <v>1671535</v>
+        <v>1650895</v>
       </c>
       <c r="J11" s="9">
-        <v>14.26</v>
+        <v>14.09</v>
       </c>
       <c r="K11" s="8">
-        <v>9573522</v>
+        <v>9599782</v>
       </c>
       <c r="L11" s="9">
-        <v>81.69</v>
+        <v>81.91</v>
       </c>
       <c r="M11" s="8">
-        <v>2146478</v>
+        <v>2120218</v>
       </c>
       <c r="N11" s="9">
-        <v>18.309999999999999</v>
+        <v>18.09</v>
       </c>
       <c r="O11" s="8">
         <v>30600</v>
@@ -19765,10 +19760,10 @@
         <v>0.26</v>
       </c>
       <c r="Q11" s="8">
-        <v>2115878</v>
+        <v>2089618</v>
       </c>
       <c r="R11" s="9">
-        <v>18.05</v>
+        <v>17.829999999999998</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -19789,28 +19784,28 @@
         <v>11820000</v>
       </c>
       <c r="G12" s="4">
-        <v>8189257.29</v>
+        <v>8562971.1600000001</v>
       </c>
       <c r="H12" s="5">
-        <v>69.28</v>
+        <v>72.44</v>
       </c>
       <c r="I12" s="4">
-        <v>1385133</v>
+        <v>917513</v>
       </c>
       <c r="J12" s="5">
-        <v>11.72</v>
+        <v>7.76</v>
       </c>
       <c r="K12" s="4">
-        <v>9574390.2899999991</v>
+        <v>9480484.1600000001</v>
       </c>
       <c r="L12" s="5">
-        <v>81</v>
+        <v>80.209999999999994</v>
       </c>
       <c r="M12" s="4">
-        <v>2245609.71</v>
+        <v>2339515.84</v>
       </c>
       <c r="N12" s="5">
-        <v>19</v>
+        <v>19.79</v>
       </c>
       <c r="O12" s="4">
         <v>56000</v>
@@ -19819,10 +19814,10 @@
         <v>0.47</v>
       </c>
       <c r="Q12" s="4">
-        <v>2189609.71</v>
+        <v>2283515.84</v>
       </c>
       <c r="R12" s="5">
-        <v>18.52</v>
+        <v>19.32</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -19845,28 +19840,28 @@
         <v>1180000</v>
       </c>
       <c r="G13" s="8">
-        <v>638349</v>
+        <v>871902.87</v>
       </c>
       <c r="H13" s="9">
-        <v>54.1</v>
+        <v>73.89</v>
       </c>
       <c r="I13" s="8">
-        <v>277000</v>
+        <v>5000</v>
       </c>
       <c r="J13" s="9">
-        <v>23.47</v>
+        <v>0.42</v>
       </c>
       <c r="K13" s="8">
-        <v>915349</v>
+        <v>876902.87</v>
       </c>
       <c r="L13" s="9">
-        <v>77.569999999999993</v>
+        <v>74.31</v>
       </c>
       <c r="M13" s="8">
-        <v>264651</v>
+        <v>303097.13</v>
       </c>
       <c r="N13" s="9">
-        <v>22.43</v>
+        <v>25.69</v>
       </c>
       <c r="O13" s="8">
         <v>0</v>
@@ -19875,10 +19870,10 @@
         <v>0</v>
       </c>
       <c r="Q13" s="8">
-        <v>264651</v>
+        <v>303097.13</v>
       </c>
       <c r="R13" s="9">
-        <v>22.43</v>
+        <v>25.69</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -19901,28 +19896,28 @@
         <v>10640000</v>
       </c>
       <c r="G14" s="8">
-        <v>7550908.29</v>
+        <v>7691068.29</v>
       </c>
       <c r="H14" s="9">
-        <v>70.97</v>
+        <v>72.28</v>
       </c>
       <c r="I14" s="8">
-        <v>1108133</v>
+        <v>912513</v>
       </c>
       <c r="J14" s="9">
-        <v>10.41</v>
+        <v>8.58</v>
       </c>
       <c r="K14" s="8">
-        <v>8659041.2899999991</v>
+        <v>8603581.2899999991</v>
       </c>
       <c r="L14" s="9">
-        <v>81.38</v>
+        <v>80.86</v>
       </c>
       <c r="M14" s="8">
-        <v>1980958.71</v>
+        <v>2036418.71</v>
       </c>
       <c r="N14" s="9">
-        <v>18.62</v>
+        <v>19.14</v>
       </c>
       <c r="O14" s="8">
         <v>56000</v>
@@ -19931,10 +19926,10 @@
         <v>0.53</v>
       </c>
       <c r="Q14" s="8">
-        <v>1924958.71</v>
+        <v>1980418.71</v>
       </c>
       <c r="R14" s="9">
-        <v>18.09</v>
+        <v>18.61</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -19961,22 +19956,22 @@
         <v>77.02</v>
       </c>
       <c r="I15" s="4">
-        <v>1645820.67</v>
+        <v>1676530.67</v>
       </c>
       <c r="J15" s="5">
-        <v>13.9</v>
+        <v>14.16</v>
       </c>
       <c r="K15" s="4">
-        <v>10765425.529999999</v>
+        <v>10796135.529999999</v>
       </c>
       <c r="L15" s="5">
-        <v>90.92</v>
+        <v>91.18</v>
       </c>
       <c r="M15" s="4">
-        <v>1074774.47</v>
+        <v>1044064.47</v>
       </c>
       <c r="N15" s="5">
-        <v>9.08</v>
+        <v>8.82</v>
       </c>
       <c r="O15" s="4">
         <v>144801.1</v>
@@ -19985,10 +19980,10 @@
         <v>1.22</v>
       </c>
       <c r="Q15" s="4">
-        <v>929973.37</v>
+        <v>899263.37</v>
       </c>
       <c r="R15" s="5">
-        <v>7.85</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -20073,22 +20068,22 @@
         <v>76.260000000000005</v>
       </c>
       <c r="I17" s="8">
-        <v>1643220.67</v>
+        <v>1673930.67</v>
       </c>
       <c r="J17" s="9">
-        <v>14.49</v>
+        <v>14.76</v>
       </c>
       <c r="K17" s="8">
-        <v>10291712.630000001</v>
+        <v>10322422.630000001</v>
       </c>
       <c r="L17" s="9">
-        <v>90.75</v>
+        <v>91.03</v>
       </c>
       <c r="M17" s="8">
-        <v>1048487.37</v>
+        <v>1017777.37</v>
       </c>
       <c r="N17" s="9">
-        <v>9.25</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="O17" s="8">
         <v>140079.5</v>
@@ -20097,10 +20092,10 @@
         <v>1.24</v>
       </c>
       <c r="Q17" s="8">
-        <v>908407.87</v>
+        <v>877697.87</v>
       </c>
       <c r="R17" s="9">
-        <v>8.01</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -20121,28 +20116,28 @@
         <v>7820000</v>
       </c>
       <c r="G18" s="4">
-        <v>5044648.3</v>
+        <v>5047348.3</v>
       </c>
       <c r="H18" s="5">
-        <v>64.510000000000005</v>
+        <v>64.540000000000006</v>
       </c>
       <c r="I18" s="4">
-        <v>1043294</v>
+        <v>1020994</v>
       </c>
       <c r="J18" s="5">
-        <v>13.34</v>
+        <v>13.06</v>
       </c>
       <c r="K18" s="4">
-        <v>6087942.2999999998</v>
+        <v>6068342.2999999998</v>
       </c>
       <c r="L18" s="5">
-        <v>77.849999999999994</v>
+        <v>77.599999999999994</v>
       </c>
       <c r="M18" s="4">
-        <v>1732057.7</v>
+        <v>1751657.7</v>
       </c>
       <c r="N18" s="5">
-        <v>22.15</v>
+        <v>22.4</v>
       </c>
       <c r="O18" s="4">
         <v>550000</v>
@@ -20151,10 +20146,10 @@
         <v>7.03</v>
       </c>
       <c r="Q18" s="4">
-        <v>1182057.7</v>
+        <v>1201657.7</v>
       </c>
       <c r="R18" s="5">
-        <v>15.12</v>
+        <v>15.37</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -20177,28 +20172,28 @@
         <v>7820000</v>
       </c>
       <c r="G19" s="8">
-        <v>5044648.3</v>
+        <v>5047348.3</v>
       </c>
       <c r="H19" s="9">
-        <v>64.510000000000005</v>
+        <v>64.540000000000006</v>
       </c>
       <c r="I19" s="8">
-        <v>1043294</v>
+        <v>1020994</v>
       </c>
       <c r="J19" s="9">
-        <v>13.34</v>
+        <v>13.06</v>
       </c>
       <c r="K19" s="8">
-        <v>6087942.2999999998</v>
+        <v>6068342.2999999998</v>
       </c>
       <c r="L19" s="9">
-        <v>77.849999999999994</v>
+        <v>77.599999999999994</v>
       </c>
       <c r="M19" s="8">
-        <v>1732057.7</v>
+        <v>1751657.7</v>
       </c>
       <c r="N19" s="9">
-        <v>22.15</v>
+        <v>22.4</v>
       </c>
       <c r="O19" s="8">
         <v>550000</v>
@@ -20207,10 +20202,10 @@
         <v>7.03</v>
       </c>
       <c r="Q19" s="8">
-        <v>1182057.7</v>
+        <v>1201657.7</v>
       </c>
       <c r="R19" s="9">
-        <v>15.12</v>
+        <v>15.37</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -20231,28 +20226,28 @@
         <v>13420000</v>
       </c>
       <c r="G20" s="4">
-        <v>10753868.42</v>
+        <v>10318412.029999999</v>
       </c>
       <c r="H20" s="5">
-        <v>80.13</v>
+        <v>76.89</v>
       </c>
       <c r="I20" s="4">
-        <v>926886</v>
+        <v>1389392.39</v>
       </c>
       <c r="J20" s="5">
-        <v>6.91</v>
+        <v>10.35</v>
       </c>
       <c r="K20" s="4">
-        <v>11680754.42</v>
+        <v>11707804.42</v>
       </c>
       <c r="L20" s="5">
-        <v>87.04</v>
+        <v>87.24</v>
       </c>
       <c r="M20" s="4">
-        <v>1739245.58</v>
+        <v>1712195.58</v>
       </c>
       <c r="N20" s="5">
-        <v>12.96</v>
+        <v>12.76</v>
       </c>
       <c r="O20" s="4">
         <v>378743</v>
@@ -20261,13 +20256,13 @@
         <v>2.82</v>
       </c>
       <c r="Q20" s="4">
-        <v>1360502.58</v>
+        <v>1333452.58</v>
       </c>
       <c r="R20" s="5">
-        <v>10.14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+        <v>9.94</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>111</v>
       </c>
@@ -20287,28 +20282,28 @@
         <v>13420000</v>
       </c>
       <c r="G21" s="8">
-        <v>10753868.42</v>
+        <v>10318412.029999999</v>
       </c>
       <c r="H21" s="9">
-        <v>80.13</v>
+        <v>76.89</v>
       </c>
       <c r="I21" s="8">
-        <v>926886</v>
+        <v>1389392.39</v>
       </c>
       <c r="J21" s="9">
-        <v>6.91</v>
+        <v>10.35</v>
       </c>
       <c r="K21" s="8">
-        <v>11680754.42</v>
+        <v>11707804.42</v>
       </c>
       <c r="L21" s="9">
-        <v>87.04</v>
+        <v>87.24</v>
       </c>
       <c r="M21" s="8">
-        <v>1739245.58</v>
+        <v>1712195.58</v>
       </c>
       <c r="N21" s="9">
-        <v>12.96</v>
+        <v>12.76</v>
       </c>
       <c r="O21" s="8">
         <v>378743</v>
@@ -20317,10 +20312,10 @@
         <v>2.82</v>
       </c>
       <c r="Q21" s="8">
-        <v>1360502.58</v>
+        <v>1333452.58</v>
       </c>
       <c r="R21" s="9">
-        <v>10.14</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -20341,25 +20336,25 @@
         <v>107227000</v>
       </c>
       <c r="G22" s="4">
-        <v>82678661.590000004</v>
+        <v>83010670.090000004</v>
       </c>
       <c r="H22" s="5">
-        <v>77.11</v>
+        <v>77.42</v>
       </c>
       <c r="I22" s="4">
-        <v>5768949.9199999999</v>
+        <v>5443057.4199999999</v>
       </c>
       <c r="J22" s="5">
-        <v>5.38</v>
+        <v>5.08</v>
       </c>
       <c r="K22" s="4">
-        <v>88447611.510000005</v>
+        <v>88453727.510000005</v>
       </c>
       <c r="L22" s="5">
         <v>82.49</v>
       </c>
       <c r="M22" s="4">
-        <v>18779388.489999998</v>
+        <v>18773272.489999998</v>
       </c>
       <c r="N22" s="5">
         <v>17.510000000000002</v>
@@ -20371,10 +20366,10 @@
         <v>4.6100000000000003</v>
       </c>
       <c r="Q22" s="4">
-        <v>13832422.619999999</v>
+        <v>13826306.619999999</v>
       </c>
       <c r="R22" s="5">
-        <v>12.9</v>
+        <v>12.89</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -20397,16 +20392,16 @@
         <v>29200000</v>
       </c>
       <c r="G23" s="8">
-        <v>17566256.93</v>
+        <v>17874149.43</v>
       </c>
       <c r="H23" s="9">
-        <v>60.16</v>
+        <v>61.21</v>
       </c>
       <c r="I23" s="8">
-        <v>5658302.1900000004</v>
+        <v>5350409.6900000004</v>
       </c>
       <c r="J23" s="9">
-        <v>19.38</v>
+        <v>18.32</v>
       </c>
       <c r="K23" s="8">
         <v>23224559.120000001</v>
@@ -20453,28 +20448,28 @@
         <v>78027000</v>
       </c>
       <c r="G24" s="8">
-        <v>65112404.659999996</v>
+        <v>65136520.659999996</v>
       </c>
       <c r="H24" s="9">
-        <v>83.45</v>
+        <v>83.48</v>
       </c>
       <c r="I24" s="8">
-        <v>110647.73</v>
+        <v>92647.73</v>
       </c>
       <c r="J24" s="9">
-        <v>0.14000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="K24" s="8">
-        <v>65223052.390000001</v>
+        <v>65229168.390000001</v>
       </c>
       <c r="L24" s="9">
-        <v>83.59</v>
+        <v>83.6</v>
       </c>
       <c r="M24" s="8">
-        <v>12803947.609999999</v>
+        <v>12797831.609999999</v>
       </c>
       <c r="N24" s="9">
-        <v>16.41</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="O24" s="8">
         <v>1542.5</v>
@@ -20483,10 +20478,10 @@
         <v>0</v>
       </c>
       <c r="Q24" s="8">
-        <v>12802405.109999999</v>
+        <v>12796289.109999999</v>
       </c>
       <c r="R24" s="9">
-        <v>16.41</v>
+        <v>16.399999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -20673,43 +20668,43 @@
         <v>60595000</v>
       </c>
       <c r="G28" s="4">
-        <v>29819625.079999998</v>
+        <v>29825805.079999998</v>
       </c>
       <c r="H28" s="5">
-        <v>49.21</v>
+        <v>49.22</v>
       </c>
       <c r="I28" s="4">
-        <v>20378533.91</v>
+        <v>20308533.91</v>
       </c>
       <c r="J28" s="5">
-        <v>33.630000000000003</v>
+        <v>33.520000000000003</v>
       </c>
       <c r="K28" s="4">
-        <v>50198158.990000002</v>
+        <v>50134338.990000002</v>
       </c>
       <c r="L28" s="5">
-        <v>82.84</v>
+        <v>82.74</v>
       </c>
       <c r="M28" s="4">
-        <v>10396841.01</v>
+        <v>10460661.01</v>
       </c>
       <c r="N28" s="5">
-        <v>17.16</v>
+        <v>17.260000000000002</v>
       </c>
       <c r="O28" s="4">
-        <v>4207196.3</v>
+        <v>4275196.3</v>
       </c>
       <c r="P28" s="5">
-        <v>6.94</v>
+        <v>7.06</v>
       </c>
       <c r="Q28" s="4">
-        <v>6189644.71</v>
+        <v>6185464.71</v>
       </c>
       <c r="R28" s="5">
         <v>10.210000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>17</v>
       </c>
@@ -20729,40 +20724,40 @@
         <v>37235000</v>
       </c>
       <c r="G29" s="8">
-        <v>18197586.129999999</v>
+        <v>18203766.129999999</v>
       </c>
       <c r="H29" s="9">
-        <v>48.87</v>
+        <v>48.89</v>
       </c>
       <c r="I29" s="8">
-        <v>13653617</v>
+        <v>13581617</v>
       </c>
       <c r="J29" s="9">
-        <v>36.67</v>
+        <v>36.479999999999997</v>
       </c>
       <c r="K29" s="8">
-        <v>31851203.129999999</v>
+        <v>31785383.129999999</v>
       </c>
       <c r="L29" s="9">
-        <v>85.54</v>
+        <v>85.36</v>
       </c>
       <c r="M29" s="8">
-        <v>5383796.8700000001</v>
+        <v>5449616.8700000001</v>
       </c>
       <c r="N29" s="9">
-        <v>14.46</v>
+        <v>14.64</v>
       </c>
       <c r="O29" s="8">
-        <v>1038800</v>
+        <v>1106800</v>
       </c>
       <c r="P29" s="9">
-        <v>2.79</v>
+        <v>2.97</v>
       </c>
       <c r="Q29" s="8">
-        <v>4344996.87</v>
+        <v>4342816.87</v>
       </c>
       <c r="R29" s="9">
-        <v>11.67</v>
+        <v>11.66</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -20847,22 +20842,22 @@
         <v>66.010000000000005</v>
       </c>
       <c r="I31" s="8">
-        <v>284783</v>
+        <v>288283</v>
       </c>
       <c r="J31" s="9">
-        <v>10.9</v>
+        <v>11.03</v>
       </c>
       <c r="K31" s="8">
-        <v>2009589.67</v>
+        <v>2013089.67</v>
       </c>
       <c r="L31" s="9">
-        <v>76.91</v>
+        <v>77.040000000000006</v>
       </c>
       <c r="M31" s="8">
-        <v>603324.32999999996</v>
+        <v>599824.32999999996</v>
       </c>
       <c r="N31" s="9">
-        <v>23.09</v>
+        <v>22.96</v>
       </c>
       <c r="O31" s="8">
         <v>0</v>
@@ -20871,10 +20866,10 @@
         <v>0</v>
       </c>
       <c r="Q31" s="8">
-        <v>603324.32999999996</v>
+        <v>599824.32999999996</v>
       </c>
       <c r="R31" s="9">
-        <v>23.09</v>
+        <v>22.96</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -20903,22 +20898,22 @@
         <v>56.28</v>
       </c>
       <c r="I32" s="8">
-        <v>961508.31</v>
+        <v>960008.31</v>
       </c>
       <c r="J32" s="9">
-        <v>9.81</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="K32" s="8">
-        <v>6476514.9500000002</v>
+        <v>6475014.9500000002</v>
       </c>
       <c r="L32" s="9">
-        <v>66.09</v>
+        <v>66.069999999999993</v>
       </c>
       <c r="M32" s="8">
-        <v>3323485.05</v>
+        <v>3324985.05</v>
       </c>
       <c r="N32" s="9">
-        <v>33.909999999999997</v>
+        <v>33.93</v>
       </c>
       <c r="O32" s="8">
         <v>2287551.54</v>
@@ -20927,10 +20922,10 @@
         <v>23.34</v>
       </c>
       <c r="Q32" s="8">
-        <v>1035933.51</v>
+        <v>1037433.51</v>
       </c>
       <c r="R32" s="9">
-        <v>10.57</v>
+        <v>10.59</v>
       </c>
     </row>
     <row r="33" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -21007,40 +21002,40 @@
         <v>230702200</v>
       </c>
       <c r="G34" s="14">
-        <v>156871820.71000001</v>
+        <v>157197866.69</v>
       </c>
       <c r="H34" s="15">
-        <v>68</v>
+        <v>68.14</v>
       </c>
       <c r="I34" s="14">
-        <v>33443961.170000002</v>
+        <v>33065125.059999999</v>
       </c>
       <c r="J34" s="15">
-        <v>14.5</v>
+        <v>14.33</v>
       </c>
       <c r="K34" s="14">
-        <v>190315781.88</v>
+        <v>190262991.75</v>
       </c>
       <c r="L34" s="15">
-        <v>82.49</v>
+        <v>82.47</v>
       </c>
       <c r="M34" s="14">
-        <v>40386418.119999997</v>
+        <v>40439208.25</v>
       </c>
       <c r="N34" s="15">
-        <v>17.510000000000002</v>
+        <v>17.53</v>
       </c>
       <c r="O34" s="14">
-        <v>10588306.27</v>
+        <v>10656306.27</v>
       </c>
       <c r="P34" s="15">
-        <v>4.59</v>
+        <v>4.62</v>
       </c>
       <c r="Q34" s="14">
-        <v>29798111.850000001</v>
+        <v>29782901.98</v>
       </c>
       <c r="R34" s="15">
-        <v>12.92</v>
+        <v>12.91</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
@@ -21382,37 +21377,37 @@
         <v>22528181.809999999</v>
       </c>
       <c r="D41" s="4">
-        <v>71946</v>
+        <v>74571</v>
       </c>
       <c r="E41" s="4">
         <v>0</v>
       </c>
       <c r="F41" s="4">
-        <v>22600127.809999999</v>
+        <v>22602752.809999999</v>
       </c>
       <c r="G41" s="4">
-        <v>9297468.7300000004</v>
+        <v>9463094.0299999993</v>
       </c>
       <c r="H41" s="5">
-        <v>41.14</v>
+        <v>41.87</v>
       </c>
       <c r="I41" s="4">
-        <v>3376985.72</v>
+        <v>3192350.42</v>
       </c>
       <c r="J41" s="5">
-        <v>14.94</v>
+        <v>14.12</v>
       </c>
       <c r="K41" s="4">
-        <v>12674454.449999999</v>
+        <v>12655444.449999999</v>
       </c>
       <c r="L41" s="5">
-        <v>56.08</v>
+        <v>55.99</v>
       </c>
       <c r="M41" s="4">
-        <v>9925673.3599999994</v>
+        <v>9947308.3599999994</v>
       </c>
       <c r="N41" s="5">
-        <v>43.92</v>
+        <v>44.01</v>
       </c>
       <c r="O41" s="4">
         <v>1182093</v>
@@ -21421,13 +21416,13 @@
         <v>5.23</v>
       </c>
       <c r="Q41" s="4">
-        <v>8743580.3599999994</v>
+        <v>8765215.3599999994</v>
       </c>
       <c r="R41" s="5">
-        <v>38.69</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+        <v>38.78</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
         <v>267</v>
       </c>
@@ -21447,28 +21442,28 @@
         <v>7840527.8099999996</v>
       </c>
       <c r="G42" s="8">
-        <v>5771723.29</v>
+        <v>5817758.5899999999</v>
       </c>
       <c r="H42" s="9">
-        <v>73.61</v>
+        <v>74.2</v>
       </c>
       <c r="I42" s="8">
-        <v>999782.16</v>
+        <v>973946.86</v>
       </c>
       <c r="J42" s="9">
-        <v>12.75</v>
+        <v>12.42</v>
       </c>
       <c r="K42" s="8">
-        <v>6771505.4500000002</v>
+        <v>6791705.4500000002</v>
       </c>
       <c r="L42" s="9">
-        <v>86.37</v>
+        <v>86.62</v>
       </c>
       <c r="M42" s="8">
-        <v>1069022.3600000001</v>
+        <v>1048822.3600000001</v>
       </c>
       <c r="N42" s="9">
-        <v>13.63</v>
+        <v>13.38</v>
       </c>
       <c r="O42" s="8">
         <v>106945</v>
@@ -21477,10 +21472,10 @@
         <v>1.36</v>
       </c>
       <c r="Q42" s="8">
-        <v>962077.36</v>
+        <v>941877.36</v>
       </c>
       <c r="R42" s="9">
-        <v>12.27</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="43" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
@@ -21503,28 +21498,28 @@
         <v>12554100</v>
       </c>
       <c r="G43" s="8">
-        <v>3499420.44</v>
+        <v>3619010.44</v>
       </c>
       <c r="H43" s="9">
-        <v>27.87</v>
+        <v>28.83</v>
       </c>
       <c r="I43" s="8">
-        <v>1152503.56</v>
+        <v>968903.56</v>
       </c>
       <c r="J43" s="9">
-        <v>9.18</v>
+        <v>7.72</v>
       </c>
       <c r="K43" s="8">
-        <v>4651924</v>
+        <v>4587914</v>
       </c>
       <c r="L43" s="9">
-        <v>37.06</v>
+        <v>36.549999999999997</v>
       </c>
       <c r="M43" s="8">
-        <v>7902176</v>
+        <v>7966186</v>
       </c>
       <c r="N43" s="9">
-        <v>62.94</v>
+        <v>63.45</v>
       </c>
       <c r="O43" s="8">
         <v>715148</v>
@@ -21533,10 +21528,10 @@
         <v>5.7</v>
       </c>
       <c r="Q43" s="8">
-        <v>7187028</v>
+        <v>7251038</v>
       </c>
       <c r="R43" s="9">
-        <v>57.25</v>
+        <v>57.76</v>
       </c>
     </row>
     <row r="44" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -21550,13 +21545,13 @@
         <v>2205500</v>
       </c>
       <c r="D44" s="8">
-        <v>0</v>
+        <v>2625</v>
       </c>
       <c r="E44" s="8">
         <v>0</v>
       </c>
       <c r="F44" s="8">
-        <v>2205500</v>
+        <v>2208125</v>
       </c>
       <c r="G44" s="8">
         <v>26325</v>
@@ -21565,34 +21560,34 @@
         <v>1.19</v>
       </c>
       <c r="I44" s="8">
-        <v>1224700</v>
+        <v>1249500</v>
       </c>
       <c r="J44" s="9">
-        <v>55.53</v>
+        <v>56.59</v>
       </c>
       <c r="K44" s="8">
-        <v>1251025</v>
+        <v>1275825</v>
       </c>
       <c r="L44" s="9">
-        <v>56.72</v>
+        <v>57.78</v>
       </c>
       <c r="M44" s="8">
-        <v>954475</v>
+        <v>932300</v>
       </c>
       <c r="N44" s="9">
-        <v>43.28</v>
+        <v>42.22</v>
       </c>
       <c r="O44" s="8">
         <v>360000</v>
       </c>
       <c r="P44" s="9">
-        <v>16.32</v>
+        <v>16.3</v>
       </c>
       <c r="Q44" s="8">
-        <v>594475</v>
+        <v>572300</v>
       </c>
       <c r="R44" s="9">
-        <v>26.95</v>
+        <v>25.92</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
@@ -21705,7 +21700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
         <v>548</v>
       </c>
@@ -21779,28 +21774,28 @@
         <v>72788490.920000002</v>
       </c>
       <c r="G48" s="4">
-        <v>17131304.129999999</v>
+        <v>17940340.129999999</v>
       </c>
       <c r="H48" s="5">
-        <v>23.54</v>
+        <v>24.65</v>
       </c>
       <c r="I48" s="4">
-        <v>16434037.26</v>
+        <v>14275227.26</v>
       </c>
       <c r="J48" s="5">
-        <v>22.58</v>
+        <v>19.61</v>
       </c>
       <c r="K48" s="4">
-        <v>33565341.390000001</v>
+        <v>32215567.390000001</v>
       </c>
       <c r="L48" s="5">
-        <v>46.11</v>
+        <v>44.26</v>
       </c>
       <c r="M48" s="4">
-        <v>39223149.530000001</v>
+        <v>40572923.530000001</v>
       </c>
       <c r="N48" s="5">
-        <v>53.89</v>
+        <v>55.74</v>
       </c>
       <c r="O48" s="4">
         <v>3597500</v>
@@ -21809,10 +21804,10 @@
         <v>4.9400000000000004</v>
       </c>
       <c r="Q48" s="4">
-        <v>35625649.530000001</v>
+        <v>36975423.530000001</v>
       </c>
       <c r="R48" s="5">
-        <v>48.94</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="49" spans="1:18" ht="105.6" x14ac:dyDescent="0.25">
@@ -21871,7 +21866,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>260</v>
       </c>
@@ -22039,7 +22034,7 @@
         <v>22.96</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" ht="132" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
         <v>333</v>
       </c>
@@ -22059,28 +22054,28 @@
         <v>8926239.0199999996</v>
       </c>
       <c r="G53" s="8">
-        <v>1303645.78</v>
+        <v>2060571.78</v>
       </c>
       <c r="H53" s="9">
-        <v>14.6</v>
+        <v>23.08</v>
       </c>
       <c r="I53" s="8">
-        <v>5403925</v>
+        <v>4551805</v>
       </c>
       <c r="J53" s="9">
-        <v>60.54</v>
+        <v>50.99</v>
       </c>
       <c r="K53" s="8">
-        <v>6707570.7800000003</v>
+        <v>6612376.7800000003</v>
       </c>
       <c r="L53" s="9">
-        <v>75.14</v>
+        <v>74.08</v>
       </c>
       <c r="M53" s="8">
-        <v>2218668.2400000002</v>
+        <v>2313862.2400000002</v>
       </c>
       <c r="N53" s="9">
-        <v>24.86</v>
+        <v>25.92</v>
       </c>
       <c r="O53" s="8">
         <v>15000</v>
@@ -22089,10 +22084,10 @@
         <v>0.17</v>
       </c>
       <c r="Q53" s="8">
-        <v>2203668.2400000002</v>
+        <v>2298862.2400000002</v>
       </c>
       <c r="R53" s="9">
-        <v>24.69</v>
+        <v>25.75</v>
       </c>
     </row>
     <row r="54" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -22263,7 +22258,7 @@
         <v>68.709999999999994</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" ht="118.8" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
         <v>422</v>
       </c>
@@ -22289,22 +22284,22 @@
         <v>17.12</v>
       </c>
       <c r="I57" s="8">
-        <v>2737311</v>
+        <v>2607311</v>
       </c>
       <c r="J57" s="9">
-        <v>14.71</v>
+        <v>14.01</v>
       </c>
       <c r="K57" s="8">
-        <v>5922713.0300000003</v>
+        <v>5792713.0300000003</v>
       </c>
       <c r="L57" s="9">
-        <v>31.83</v>
+        <v>31.13</v>
       </c>
       <c r="M57" s="8">
-        <v>12683169.390000001</v>
+        <v>12813169.390000001</v>
       </c>
       <c r="N57" s="9">
-        <v>68.17</v>
+        <v>68.87</v>
       </c>
       <c r="O57" s="8">
         <v>3295000</v>
@@ -22313,10 +22308,10 @@
         <v>17.71</v>
       </c>
       <c r="Q57" s="8">
-        <v>9388169.3900000006</v>
+        <v>9518169.3900000006</v>
       </c>
       <c r="R57" s="9">
-        <v>50.46</v>
+        <v>51.16</v>
       </c>
     </row>
     <row r="58" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -22451,28 +22446,28 @@
         <v>2528000</v>
       </c>
       <c r="G60" s="8">
-        <v>900179.84</v>
+        <v>952739.83999999997</v>
       </c>
       <c r="H60" s="9">
-        <v>35.61</v>
+        <v>37.69</v>
       </c>
       <c r="I60" s="8">
-        <v>674050</v>
+        <v>625610</v>
       </c>
       <c r="J60" s="9">
-        <v>26.66</v>
+        <v>24.75</v>
       </c>
       <c r="K60" s="8">
-        <v>1574229.84</v>
+        <v>1578349.84</v>
       </c>
       <c r="L60" s="9">
-        <v>62.27</v>
+        <v>62.43</v>
       </c>
       <c r="M60" s="8">
-        <v>953770.16</v>
+        <v>949650.16</v>
       </c>
       <c r="N60" s="9">
-        <v>37.729999999999997</v>
+        <v>37.57</v>
       </c>
       <c r="O60" s="8">
         <v>20000</v>
@@ -22481,13 +22476,13 @@
         <v>0.79</v>
       </c>
       <c r="Q60" s="8">
-        <v>933770.16</v>
+        <v>929650.16</v>
       </c>
       <c r="R60" s="9">
-        <v>36.94</v>
-      </c>
-    </row>
-    <row r="61" spans="1:18" ht="66" x14ac:dyDescent="0.25">
+        <v>36.770000000000003</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
         <v>508</v>
       </c>
@@ -22543,7 +22538,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="66" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
         <v>523</v>
       </c>
@@ -22563,28 +22558,28 @@
         <v>19811100</v>
       </c>
       <c r="G62" s="8">
-        <v>3110261.97</v>
+        <v>3109811.97</v>
       </c>
       <c r="H62" s="9">
         <v>15.7</v>
       </c>
       <c r="I62" s="8">
-        <v>5651908.0300000003</v>
+        <v>4523658.03</v>
       </c>
       <c r="J62" s="9">
-        <v>28.53</v>
+        <v>22.83</v>
       </c>
       <c r="K62" s="8">
-        <v>8762170</v>
+        <v>7633470</v>
       </c>
       <c r="L62" s="9">
-        <v>44.23</v>
+        <v>38.53</v>
       </c>
       <c r="M62" s="8">
-        <v>11048930</v>
+        <v>12177630</v>
       </c>
       <c r="N62" s="9">
-        <v>55.77</v>
+        <v>61.47</v>
       </c>
       <c r="O62" s="8">
         <v>0</v>
@@ -22593,10 +22588,10 @@
         <v>0</v>
       </c>
       <c r="Q62" s="8">
-        <v>11048930</v>
+        <v>12177630</v>
       </c>
       <c r="R62" s="9">
-        <v>55.77</v>
+        <v>61.47</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
@@ -22608,37 +22603,37 @@
         <v>101298156.95</v>
       </c>
       <c r="D63" s="14">
-        <v>71946</v>
+        <v>74571</v>
       </c>
       <c r="E63" s="14">
         <v>0</v>
       </c>
       <c r="F63" s="14">
-        <v>101370102.95</v>
+        <v>101372727.95</v>
       </c>
       <c r="G63" s="14">
-        <v>28497772.09</v>
+        <v>29472433.390000001</v>
       </c>
       <c r="H63" s="15">
-        <v>28.11</v>
+        <v>29.07</v>
       </c>
       <c r="I63" s="14">
-        <v>19891917.98</v>
+        <v>17548472.68</v>
       </c>
       <c r="J63" s="15">
-        <v>19.62</v>
+        <v>17.309999999999999</v>
       </c>
       <c r="K63" s="14">
-        <v>48389690.07</v>
+        <v>47020906.07</v>
       </c>
       <c r="L63" s="15">
-        <v>47.74</v>
+        <v>46.38</v>
       </c>
       <c r="M63" s="14">
-        <v>52980412.880000003</v>
+        <v>54351821.880000003</v>
       </c>
       <c r="N63" s="15">
-        <v>52.26</v>
+        <v>53.62</v>
       </c>
       <c r="O63" s="14">
         <v>4899593</v>
@@ -22647,10 +22642,10 @@
         <v>4.83</v>
       </c>
       <c r="Q63" s="14">
-        <v>48080819.880000003</v>
+        <v>49452228.880000003</v>
       </c>
       <c r="R63" s="15">
-        <v>47.43</v>
+        <v>48.78</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
@@ -22662,49 +22657,49 @@
         <v>332000356.94999999</v>
       </c>
       <c r="D64" s="16">
-        <v>71946</v>
+        <v>74571</v>
       </c>
       <c r="E64" s="16">
         <v>0</v>
       </c>
       <c r="F64" s="16">
-        <v>332072302.94999999</v>
+        <v>332074927.94999999</v>
       </c>
       <c r="G64" s="16">
-        <v>185369592.80000001</v>
+        <v>186670300.08000001</v>
       </c>
       <c r="H64" s="17">
-        <v>55.82</v>
+        <v>56.21</v>
       </c>
       <c r="I64" s="16">
-        <v>53335879.149999999</v>
+        <v>50613597.740000002</v>
       </c>
       <c r="J64" s="17">
-        <v>16.059999999999999</v>
+        <v>15.24</v>
       </c>
       <c r="K64" s="16">
-        <v>238705471.94999999</v>
+        <v>237283897.81999999</v>
       </c>
       <c r="L64" s="17">
-        <v>71.88</v>
+        <v>71.45</v>
       </c>
       <c r="M64" s="16">
-        <v>93366831</v>
+        <v>94791030.129999995</v>
       </c>
       <c r="N64" s="17">
-        <v>28.12</v>
+        <v>28.55</v>
       </c>
       <c r="O64" s="16">
-        <v>15487899.27</v>
+        <v>15555899.27</v>
       </c>
       <c r="P64" s="17">
-        <v>4.66</v>
+        <v>4.68</v>
       </c>
       <c r="Q64" s="16">
-        <v>77878931.730000004</v>
+        <v>79235130.859999999</v>
       </c>
       <c r="R64" s="17">
-        <v>23.45</v>
+        <v>23.86</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
@@ -22761,7 +22756,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="66" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
         <v>564</v>
       </c>
@@ -22880,49 +22875,49 @@
         <v>338655937.13</v>
       </c>
       <c r="D68" s="16">
-        <v>71946</v>
+        <v>74571</v>
       </c>
       <c r="E68" s="16">
         <v>0</v>
       </c>
       <c r="F68" s="16">
-        <v>338727883.13</v>
+        <v>338730508.13</v>
       </c>
       <c r="G68" s="16">
-        <v>185369592.80000001</v>
+        <v>186670300.08000001</v>
       </c>
       <c r="H68" s="17">
-        <v>54.73</v>
+        <v>55.11</v>
       </c>
       <c r="I68" s="16">
-        <v>53335879.149999999</v>
+        <v>50613597.740000002</v>
       </c>
       <c r="J68" s="17">
-        <v>15.75</v>
+        <v>14.94</v>
       </c>
       <c r="K68" s="16">
-        <v>238705471.94999999</v>
+        <v>237283897.81999999</v>
       </c>
       <c r="L68" s="17">
-        <v>70.47</v>
+        <v>70.05</v>
       </c>
       <c r="M68" s="16">
-        <v>100022411.18000001</v>
+        <v>101446610.31</v>
       </c>
       <c r="N68" s="17">
-        <v>29.53</v>
+        <v>29.95</v>
       </c>
       <c r="O68" s="16">
-        <v>15487899.27</v>
+        <v>15555899.27</v>
       </c>
       <c r="P68" s="17">
-        <v>4.57</v>
+        <v>4.59</v>
       </c>
       <c r="Q68" s="16">
-        <v>84534511.909999996</v>
+        <v>85890711.040000007</v>
       </c>
       <c r="R68" s="17">
-        <v>24.96</v>
+        <v>25.36</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
@@ -22937,34 +22932,34 @@
         <v>0</v>
       </c>
       <c r="E69" s="4">
-        <v>71946</v>
+        <v>74571</v>
       </c>
       <c r="F69" s="4">
-        <v>3965994.24</v>
+        <v>3963369.24</v>
       </c>
       <c r="G69" s="4">
         <v>558139.18000000005</v>
       </c>
       <c r="H69" s="5">
-        <v>14.07</v>
+        <v>14.08</v>
       </c>
       <c r="I69" s="4">
         <v>156393.70000000001</v>
       </c>
       <c r="J69" s="5">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="K69" s="4">
         <v>714532.88</v>
       </c>
       <c r="L69" s="5">
-        <v>18.02</v>
+        <v>18.03</v>
       </c>
       <c r="M69" s="4">
-        <v>3251461.36</v>
+        <v>3248836.36</v>
       </c>
       <c r="N69" s="5">
-        <v>81.98</v>
+        <v>81.97</v>
       </c>
       <c r="O69" s="4">
         <v>6129.12</v>
@@ -22973,10 +22968,10 @@
         <v>0.15</v>
       </c>
       <c r="Q69" s="4">
-        <v>3245332.24</v>
+        <v>3242707.24</v>
       </c>
       <c r="R69" s="5">
-        <v>81.83</v>
+        <v>81.819999999999993</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
@@ -22993,34 +22988,34 @@
         <v>0</v>
       </c>
       <c r="E70" s="8">
-        <v>71946</v>
+        <v>74571</v>
       </c>
       <c r="F70" s="8">
-        <v>3965994.24</v>
+        <v>3963369.24</v>
       </c>
       <c r="G70" s="8">
         <v>558139.18000000005</v>
       </c>
       <c r="H70" s="9">
-        <v>14.07</v>
+        <v>14.08</v>
       </c>
       <c r="I70" s="8">
         <v>156393.70000000001</v>
       </c>
       <c r="J70" s="9">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="K70" s="8">
         <v>714532.88</v>
       </c>
       <c r="L70" s="9">
-        <v>18.02</v>
+        <v>18.03</v>
       </c>
       <c r="M70" s="8">
-        <v>3251461.36</v>
+        <v>3248836.36</v>
       </c>
       <c r="N70" s="9">
-        <v>81.98</v>
+        <v>81.97</v>
       </c>
       <c r="O70" s="8">
         <v>6129.12</v>
@@ -23029,10 +23024,10 @@
         <v>0.15</v>
       </c>
       <c r="Q70" s="8">
-        <v>3245332.24</v>
+        <v>3242707.24</v>
       </c>
       <c r="R70" s="9">
-        <v>81.83</v>
+        <v>81.819999999999993</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
@@ -23047,34 +23042,34 @@
         <v>0</v>
       </c>
       <c r="E71" s="14">
-        <v>71946</v>
+        <v>74571</v>
       </c>
       <c r="F71" s="14">
-        <v>3965994.24</v>
+        <v>3963369.24</v>
       </c>
       <c r="G71" s="14">
         <v>558139.18000000005</v>
       </c>
       <c r="H71" s="15">
-        <v>14.07</v>
+        <v>14.08</v>
       </c>
       <c r="I71" s="14">
         <v>156393.70000000001</v>
       </c>
       <c r="J71" s="15">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="K71" s="14">
         <v>714532.88</v>
       </c>
       <c r="L71" s="15">
-        <v>18.02</v>
+        <v>18.03</v>
       </c>
       <c r="M71" s="14">
-        <v>3251461.36</v>
+        <v>3248836.36</v>
       </c>
       <c r="N71" s="15">
-        <v>81.98</v>
+        <v>81.97</v>
       </c>
       <c r="O71" s="14">
         <v>6129.12</v>
@@ -23083,10 +23078,10 @@
         <v>0.15</v>
       </c>
       <c r="Q71" s="14">
-        <v>3245332.24</v>
+        <v>3242707.24</v>
       </c>
       <c r="R71" s="15">
-        <v>81.83</v>
+        <v>81.819999999999993</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
@@ -23098,49 +23093,49 @@
         <v>342693877.37</v>
       </c>
       <c r="D72" s="16">
-        <v>71946</v>
+        <v>74571</v>
       </c>
       <c r="E72" s="16">
-        <v>71946</v>
+        <v>74571</v>
       </c>
       <c r="F72" s="16">
         <v>342693877.37</v>
       </c>
       <c r="G72" s="16">
-        <v>185927731.97999999</v>
+        <v>187228439.25999999</v>
       </c>
       <c r="H72" s="17">
-        <v>54.25</v>
+        <v>54.63</v>
       </c>
       <c r="I72" s="16">
-        <v>53492272.850000001</v>
+        <v>50769991.439999998</v>
       </c>
       <c r="J72" s="17">
-        <v>15.61</v>
+        <v>14.81</v>
       </c>
       <c r="K72" s="16">
-        <v>239420004.83000001</v>
+        <v>237998430.69999999</v>
       </c>
       <c r="L72" s="17">
-        <v>69.86</v>
+        <v>69.45</v>
       </c>
       <c r="M72" s="16">
-        <v>103273872.54000001</v>
+        <v>104695446.67</v>
       </c>
       <c r="N72" s="17">
-        <v>30.14</v>
+        <v>30.55</v>
       </c>
       <c r="O72" s="16">
-        <v>15494028.390000001</v>
+        <v>15562028.390000001</v>
       </c>
       <c r="P72" s="17">
-        <v>4.5199999999999996</v>
+        <v>4.54</v>
       </c>
       <c r="Q72" s="16">
-        <v>87779844.150000006</v>
+        <v>89133418.280000001</v>
       </c>
       <c r="R72" s="17">
-        <v>25.61</v>
+        <v>26.01</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
@@ -23167,22 +23162,22 @@
         <v>80.56</v>
       </c>
       <c r="I73" s="19">
-        <v>115542</v>
+        <v>135942</v>
       </c>
       <c r="J73" s="20">
-        <v>11.55</v>
+        <v>13.59</v>
       </c>
       <c r="K73" s="19">
-        <v>921093.74</v>
+        <v>941493.74</v>
       </c>
       <c r="L73" s="20">
-        <v>92.11</v>
+        <v>94.15</v>
       </c>
       <c r="M73" s="19">
-        <v>78906.259999999995</v>
+        <v>58506.26</v>
       </c>
       <c r="N73" s="20">
-        <v>7.89</v>
+        <v>5.85</v>
       </c>
       <c r="O73" s="19">
         <v>0</v>
@@ -23191,10 +23186,10 @@
         <v>0</v>
       </c>
       <c r="Q73" s="19">
-        <v>78906.259999999995</v>
+        <v>58506.26</v>
       </c>
       <c r="R73" s="20">
-        <v>7.89</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
@@ -23221,22 +23216,22 @@
         <v>53.34</v>
       </c>
       <c r="I74" s="19">
-        <v>5570</v>
+        <v>19570</v>
       </c>
       <c r="J74" s="20">
-        <v>0.56000000000000005</v>
+        <v>1.96</v>
       </c>
       <c r="K74" s="19">
-        <v>538949</v>
+        <v>552949</v>
       </c>
       <c r="L74" s="20">
-        <v>53.89</v>
+        <v>55.29</v>
       </c>
       <c r="M74" s="19">
-        <v>461051</v>
+        <v>447051</v>
       </c>
       <c r="N74" s="20">
-        <v>46.11</v>
+        <v>44.71</v>
       </c>
       <c r="O74" s="19">
         <v>0</v>
@@ -23245,10 +23240,10 @@
         <v>0</v>
       </c>
       <c r="Q74" s="19">
-        <v>461051</v>
+        <v>447051</v>
       </c>
       <c r="R74" s="20">
-        <v>46.11</v>
+        <v>44.71</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
@@ -23269,28 +23264,28 @@
         <v>12535870.93</v>
       </c>
       <c r="G75" s="19">
-        <v>8273712.0499999998</v>
+        <v>8320612.0499999998</v>
       </c>
       <c r="H75" s="20">
-        <v>66</v>
+        <v>66.37</v>
       </c>
       <c r="I75" s="19">
-        <v>1671545</v>
+        <v>1650905</v>
       </c>
       <c r="J75" s="20">
-        <v>13.33</v>
+        <v>13.17</v>
       </c>
       <c r="K75" s="19">
-        <v>9945257.0500000007</v>
+        <v>9971517.0500000007</v>
       </c>
       <c r="L75" s="20">
-        <v>79.33</v>
+        <v>79.540000000000006</v>
       </c>
       <c r="M75" s="19">
-        <v>2590613.88</v>
+        <v>2564353.88</v>
       </c>
       <c r="N75" s="20">
-        <v>20.67</v>
+        <v>20.46</v>
       </c>
       <c r="O75" s="19">
         <v>30600</v>
@@ -23299,10 +23294,10 @@
         <v>0.24</v>
       </c>
       <c r="Q75" s="19">
-        <v>2560013.88</v>
+        <v>2533753.88</v>
       </c>
       <c r="R75" s="20">
-        <v>20.420000000000002</v>
+        <v>20.21</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
@@ -23323,28 +23318,28 @@
         <v>13373180.710000001</v>
       </c>
       <c r="G76" s="19">
-        <v>8189262.29</v>
+        <v>8562976.1600000001</v>
       </c>
       <c r="H76" s="20">
-        <v>61.24</v>
+        <v>64.03</v>
       </c>
       <c r="I76" s="19">
-        <v>1385133</v>
+        <v>917513</v>
       </c>
       <c r="J76" s="20">
-        <v>10.36</v>
+        <v>6.86</v>
       </c>
       <c r="K76" s="19">
-        <v>9574395.2899999991</v>
+        <v>9480489.1600000001</v>
       </c>
       <c r="L76" s="20">
-        <v>71.59</v>
+        <v>70.89</v>
       </c>
       <c r="M76" s="19">
-        <v>3798785.42</v>
+        <v>3892691.55</v>
       </c>
       <c r="N76" s="20">
-        <v>28.41</v>
+        <v>29.11</v>
       </c>
       <c r="O76" s="19">
         <v>56000</v>
@@ -23353,10 +23348,10 @@
         <v>0.42</v>
       </c>
       <c r="Q76" s="19">
-        <v>3742785.42</v>
+        <v>3836691.55</v>
       </c>
       <c r="R76" s="20">
-        <v>27.99</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
@@ -23383,22 +23378,22 @@
         <v>73.2</v>
       </c>
       <c r="I77" s="19">
-        <v>1726705.67</v>
+        <v>1757415.67</v>
       </c>
       <c r="J77" s="20">
-        <v>11.69</v>
+        <v>11.89</v>
       </c>
       <c r="K77" s="19">
-        <v>12543579.710000001</v>
+        <v>12574289.710000001</v>
       </c>
       <c r="L77" s="20">
-        <v>84.89</v>
+        <v>85.1</v>
       </c>
       <c r="M77" s="19">
-        <v>2233124.0699999998</v>
+        <v>2202414.0699999998</v>
       </c>
       <c r="N77" s="20">
-        <v>15.11</v>
+        <v>14.9</v>
       </c>
       <c r="O77" s="19">
         <v>144801.1</v>
@@ -23407,10 +23402,10 @@
         <v>0.98</v>
       </c>
       <c r="Q77" s="19">
-        <v>2088322.97</v>
+        <v>2057612.97</v>
       </c>
       <c r="R77" s="20">
-        <v>14.13</v>
+        <v>13.92</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
@@ -23422,37 +23417,37 @@
         <v>30348181.809999999</v>
       </c>
       <c r="D78" s="19">
-        <v>71946</v>
+        <v>74571</v>
       </c>
       <c r="E78" s="19">
         <v>0</v>
       </c>
       <c r="F78" s="19">
-        <v>30420127.809999999</v>
+        <v>30422752.809999999</v>
       </c>
       <c r="G78" s="19">
-        <v>14342117.029999999</v>
+        <v>14510442.33</v>
       </c>
       <c r="H78" s="20">
-        <v>47.15</v>
+        <v>47.7</v>
       </c>
       <c r="I78" s="19">
-        <v>4420279.72</v>
+        <v>4213344.42</v>
       </c>
       <c r="J78" s="20">
-        <v>14.53</v>
+        <v>13.85</v>
       </c>
       <c r="K78" s="19">
-        <v>18762396.75</v>
+        <v>18723786.75</v>
       </c>
       <c r="L78" s="20">
-        <v>61.68</v>
+        <v>61.55</v>
       </c>
       <c r="M78" s="19">
-        <v>11657731.060000001</v>
+        <v>11698966.060000001</v>
       </c>
       <c r="N78" s="20">
-        <v>38.32</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="O78" s="19">
         <v>1732093</v>
@@ -23461,10 +23456,10 @@
         <v>5.69</v>
       </c>
       <c r="Q78" s="19">
-        <v>9925638.0600000005</v>
+        <v>9966873.0600000005</v>
       </c>
       <c r="R78" s="20">
-        <v>32.630000000000003</v>
+        <v>32.76</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
@@ -23485,28 +23480,28 @@
         <v>13420000</v>
       </c>
       <c r="G79" s="19">
-        <v>10753868.42</v>
+        <v>10318412.029999999</v>
       </c>
       <c r="H79" s="20">
-        <v>80.13</v>
+        <v>76.89</v>
       </c>
       <c r="I79" s="19">
-        <v>926886</v>
+        <v>1389392.39</v>
       </c>
       <c r="J79" s="20">
-        <v>6.91</v>
+        <v>10.35</v>
       </c>
       <c r="K79" s="19">
-        <v>11680754.42</v>
+        <v>11707804.42</v>
       </c>
       <c r="L79" s="20">
-        <v>87.04</v>
+        <v>87.24</v>
       </c>
       <c r="M79" s="19">
-        <v>1739245.58</v>
+        <v>1712195.58</v>
       </c>
       <c r="N79" s="20">
-        <v>12.96</v>
+        <v>12.76</v>
       </c>
       <c r="O79" s="19">
         <v>378743</v>
@@ -23515,10 +23510,10 @@
         <v>2.82</v>
       </c>
       <c r="Q79" s="19">
-        <v>1360502.58</v>
+        <v>1333452.58</v>
       </c>
       <c r="R79" s="20">
-        <v>10.14</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
@@ -23533,31 +23528,31 @@
         <v>0</v>
       </c>
       <c r="E80" s="19">
-        <v>71946</v>
+        <v>74571</v>
       </c>
       <c r="F80" s="19">
-        <v>111192994.23999999</v>
+        <v>111190369.23999999</v>
       </c>
       <c r="G80" s="19">
-        <v>83236800.769999996</v>
+        <v>83568809.269999996</v>
       </c>
       <c r="H80" s="20">
-        <v>74.86</v>
+        <v>75.16</v>
       </c>
       <c r="I80" s="19">
-        <v>5925343.6200000001</v>
+        <v>5599451.1200000001</v>
       </c>
       <c r="J80" s="20">
-        <v>5.33</v>
+        <v>5.04</v>
       </c>
       <c r="K80" s="19">
-        <v>89162144.390000001</v>
+        <v>89168260.390000001</v>
       </c>
       <c r="L80" s="20">
         <v>80.19</v>
       </c>
       <c r="M80" s="19">
-        <v>22030849.850000001</v>
+        <v>22022108.850000001</v>
       </c>
       <c r="N80" s="20">
         <v>19.809999999999999</v>
@@ -23569,10 +23564,10 @@
         <v>4.45</v>
       </c>
       <c r="Q80" s="19">
-        <v>17077754.859999999</v>
+        <v>17069013.859999999</v>
       </c>
       <c r="R80" s="20">
-        <v>15.36</v>
+        <v>15.35</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
@@ -23647,40 +23642,40 @@
         <v>140039071.09999999</v>
       </c>
       <c r="G82" s="19">
-        <v>46950929.210000001</v>
+        <v>47766145.210000001</v>
       </c>
       <c r="H82" s="20">
-        <v>33.53</v>
+        <v>34.11</v>
       </c>
       <c r="I82" s="19">
-        <v>36812571.170000002</v>
+        <v>34583761.170000002</v>
       </c>
       <c r="J82" s="20">
-        <v>26.29</v>
+        <v>24.7</v>
       </c>
       <c r="K82" s="19">
-        <v>83763500.379999995</v>
+        <v>82349906.379999995</v>
       </c>
       <c r="L82" s="20">
-        <v>59.81</v>
+        <v>58.8</v>
       </c>
       <c r="M82" s="19">
-        <v>56275570.719999999</v>
+        <v>57689164.719999999</v>
       </c>
       <c r="N82" s="20">
-        <v>40.19</v>
+        <v>41.2</v>
       </c>
       <c r="O82" s="19">
-        <v>7804696.2999999998</v>
+        <v>7872696.2999999998</v>
       </c>
       <c r="P82" s="20">
-        <v>5.57</v>
+        <v>5.62</v>
       </c>
       <c r="Q82" s="19">
-        <v>48470874.420000002</v>
+        <v>49816468.420000002</v>
       </c>
       <c r="R82" s="20">
-        <v>34.61</v>
+        <v>35.57</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
@@ -23692,49 +23687,49 @@
         <v>342693877.37</v>
       </c>
       <c r="D83" s="19">
-        <v>71946</v>
+        <v>74571</v>
       </c>
       <c r="E83" s="19">
-        <v>71946</v>
+        <v>74571</v>
       </c>
       <c r="F83" s="19">
         <v>342693877.37</v>
       </c>
       <c r="G83" s="19">
-        <v>185927731.97999999</v>
+        <v>187228439.25999999</v>
       </c>
       <c r="H83" s="20">
-        <v>54.25</v>
+        <v>54.63</v>
       </c>
       <c r="I83" s="19">
-        <v>53492272.850000001</v>
+        <v>50769991.439999998</v>
       </c>
       <c r="J83" s="20">
-        <v>15.61</v>
+        <v>14.81</v>
       </c>
       <c r="K83" s="19">
-        <v>239420004.83000001</v>
+        <v>237998430.69999999</v>
       </c>
       <c r="L83" s="20">
-        <v>69.86</v>
+        <v>69.45</v>
       </c>
       <c r="M83" s="19">
-        <v>103273872.54000001</v>
+        <v>104695446.67</v>
       </c>
       <c r="N83" s="20">
-        <v>30.14</v>
+        <v>30.55</v>
       </c>
       <c r="O83" s="19">
-        <v>15494028.390000001</v>
+        <v>15562028.390000001</v>
       </c>
       <c r="P83" s="20">
-        <v>4.5199999999999996</v>
+        <v>4.54</v>
       </c>
       <c r="Q83" s="19">
-        <v>87779844.150000006</v>
+        <v>89133418.280000001</v>
       </c>
       <c r="R83" s="20">
-        <v>25.61</v>
+        <v>26.01</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">

--- a/Budget-Report.xlsx
+++ b/Budget-Report.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orathai\Desktop\Claude Cowork\Budget Report\00 BK\25690731\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orathai\Desktop\Claude Cowork\Budget Report\00 BK\25690807\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D07E38-78BA-487D-8C0F-12C5A1CEB225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E1AFE30-E227-4BCC-A757-0FCDFC2B2C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="จำแนกตามแผนงาน" sheetId="1" r:id="rId1"/>
@@ -1766,7 +1766,7 @@
     <t>รวมทั้งสิ้น</t>
   </si>
   <si>
-    <t>( ข้อมูลระบบ ณ วันที่ 31 กรกฎาคม 2569 เวลา 22:14:05 น.)</t>
+    <t>( ข้อมูลระบบ ณ วันที่ 7 สิงหาคม 2569 เวลา 22:22:45 น.)</t>
   </si>
   <si>
     <t>สำนัก/โครงการ</t>
@@ -1805,7 +1805,7 @@
     <t>สย.</t>
   </si>
   <si>
-    <t>( ข้อมูลระบบ ณ วันที่ 31 กรกฎาคม 2569 เวลา 22:15:33 น.)</t>
+    <t>( ข้อมูลระบบ ณ วันที่ 7 สิงหาคม 2569 เวลา 22:25:19 น.)</t>
   </si>
 </sst>
 </file>
@@ -2349,7 +2349,7 @@
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
         <v>1</v>
       </c>
@@ -2457,40 +2457,40 @@
         <v>46540814</v>
       </c>
       <c r="G6" s="4">
-        <v>23910276</v>
+        <v>24172229.510000002</v>
       </c>
       <c r="H6" s="5">
-        <v>51.37</v>
+        <v>51.94</v>
       </c>
       <c r="I6" s="4">
-        <v>14530196.67</v>
+        <v>14964213.16</v>
       </c>
       <c r="J6" s="5">
-        <v>31.22</v>
+        <v>32.15</v>
       </c>
       <c r="K6" s="4">
-        <v>38440472.670000002</v>
+        <v>39136442.670000002</v>
       </c>
       <c r="L6" s="5">
-        <v>82.6</v>
+        <v>84.09</v>
       </c>
       <c r="M6" s="4">
-        <v>8100341.3300000001</v>
+        <v>7404371.3300000001</v>
       </c>
       <c r="N6" s="5">
-        <v>17.399999999999999</v>
+        <v>15.91</v>
       </c>
       <c r="O6" s="4">
-        <v>1385521.6</v>
+        <v>1380800</v>
       </c>
       <c r="P6" s="5">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="Q6" s="4">
-        <v>6714819.7300000004</v>
+        <v>6023571.3300000001</v>
       </c>
       <c r="R6" s="5">
-        <v>14.43</v>
+        <v>12.94</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -2513,28 +2513,28 @@
         <v>37235000</v>
       </c>
       <c r="G7" s="8">
-        <v>18203766.129999999</v>
+        <v>18382086.129999999</v>
       </c>
       <c r="H7" s="9">
-        <v>48.89</v>
+        <v>49.37</v>
       </c>
       <c r="I7" s="8">
-        <v>13581617</v>
+        <v>14046467</v>
       </c>
       <c r="J7" s="9">
-        <v>36.479999999999997</v>
+        <v>37.72</v>
       </c>
       <c r="K7" s="8">
-        <v>31785383.129999999</v>
+        <v>32428553.129999999</v>
       </c>
       <c r="L7" s="9">
-        <v>85.36</v>
+        <v>87.09</v>
       </c>
       <c r="M7" s="8">
-        <v>5449616.8700000001</v>
+        <v>4806446.87</v>
       </c>
       <c r="N7" s="9">
-        <v>14.64</v>
+        <v>12.91</v>
       </c>
       <c r="O7" s="8">
         <v>1106800</v>
@@ -2543,10 +2543,10 @@
         <v>2.97</v>
       </c>
       <c r="Q7" s="8">
-        <v>4342816.87</v>
+        <v>3699646.87</v>
       </c>
       <c r="R7" s="9">
-        <v>11.66</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -2575,22 +2575,22 @@
         <v>58.68</v>
       </c>
       <c r="I8" s="12">
-        <v>65800</v>
+        <v>76000</v>
       </c>
       <c r="J8" s="13">
-        <v>1.88</v>
+        <v>2.17</v>
       </c>
       <c r="K8" s="12">
-        <v>2119666.41</v>
+        <v>2129866.41</v>
       </c>
       <c r="L8" s="13">
-        <v>60.56</v>
+        <v>60.85</v>
       </c>
       <c r="M8" s="12">
-        <v>1380333.59</v>
+        <v>1370133.59</v>
       </c>
       <c r="N8" s="13">
-        <v>39.44</v>
+        <v>39.15</v>
       </c>
       <c r="O8" s="12">
         <v>99600</v>
@@ -2599,10 +2599,10 @@
         <v>2.85</v>
       </c>
       <c r="Q8" s="12">
-        <v>1280733.5900000001</v>
+        <v>1270533.5900000001</v>
       </c>
       <c r="R8" s="13">
-        <v>36.590000000000003</v>
+        <v>36.299999999999997</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
@@ -2793,25 +2793,25 @@
         <v>20000000</v>
       </c>
       <c r="G12" s="12">
-        <v>8085155</v>
+        <v>8197155</v>
       </c>
       <c r="H12" s="13">
-        <v>40.43</v>
+        <v>40.99</v>
       </c>
       <c r="I12" s="12">
-        <v>9981250</v>
+        <v>9869700</v>
       </c>
       <c r="J12" s="13">
-        <v>49.91</v>
+        <v>49.35</v>
       </c>
       <c r="K12" s="12">
-        <v>18066405</v>
+        <v>18066855</v>
       </c>
       <c r="L12" s="13">
         <v>90.33</v>
       </c>
       <c r="M12" s="12">
-        <v>1933595</v>
+        <v>1933145</v>
       </c>
       <c r="N12" s="13">
         <v>9.67</v>
@@ -2823,7 +2823,7 @@
         <v>5</v>
       </c>
       <c r="Q12" s="12">
-        <v>933595</v>
+        <v>933145</v>
       </c>
       <c r="R12" s="13">
         <v>4.67</v>
@@ -2849,28 +2849,28 @@
         <v>800000</v>
       </c>
       <c r="G13" s="12">
-        <v>655055.5</v>
+        <v>657225.5</v>
       </c>
       <c r="H13" s="13">
-        <v>81.88</v>
+        <v>82.15</v>
       </c>
       <c r="I13" s="12">
-        <v>102562</v>
+        <v>126162</v>
       </c>
       <c r="J13" s="13">
-        <v>12.82</v>
+        <v>15.77</v>
       </c>
       <c r="K13" s="12">
-        <v>757617.5</v>
+        <v>783387.5</v>
       </c>
       <c r="L13" s="13">
-        <v>94.7</v>
+        <v>97.92</v>
       </c>
       <c r="M13" s="12">
-        <v>42382.5</v>
+        <v>16612.5</v>
       </c>
       <c r="N13" s="13">
-        <v>5.3</v>
+        <v>2.08</v>
       </c>
       <c r="O13" s="12">
         <v>0</v>
@@ -2879,10 +2879,10 @@
         <v>0</v>
       </c>
       <c r="Q13" s="12">
-        <v>42382.5</v>
+        <v>16612.5</v>
       </c>
       <c r="R13" s="13">
-        <v>5.3</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -2967,22 +2967,22 @@
         <v>78.489999999999995</v>
       </c>
       <c r="I15" s="12">
-        <v>3500</v>
+        <v>248350</v>
       </c>
       <c r="J15" s="13">
-        <v>0.13</v>
+        <v>9.17</v>
       </c>
       <c r="K15" s="12">
-        <v>2128224.5699999998</v>
+        <v>2373074.5699999998</v>
       </c>
       <c r="L15" s="13">
-        <v>78.62</v>
+        <v>87.67</v>
       </c>
       <c r="M15" s="12">
-        <v>578606.80000000005</v>
+        <v>333756.79999999999</v>
       </c>
       <c r="N15" s="13">
-        <v>21.38</v>
+        <v>12.33</v>
       </c>
       <c r="O15" s="12">
         <v>5000</v>
@@ -2991,10 +2991,10 @@
         <v>0.18</v>
       </c>
       <c r="Q15" s="12">
-        <v>573606.80000000005</v>
+        <v>328756.8</v>
       </c>
       <c r="R15" s="13">
-        <v>21.19</v>
+        <v>12.15</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -3023,22 +3023,22 @@
         <v>8.5500000000000007</v>
       </c>
       <c r="I16" s="12">
-        <v>0</v>
+        <v>352000</v>
       </c>
       <c r="J16" s="13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K16" s="12">
-        <v>30100</v>
+        <v>382100</v>
       </c>
       <c r="L16" s="13">
-        <v>8.5500000000000007</v>
+        <v>108.55</v>
       </c>
       <c r="M16" s="12">
-        <v>321900</v>
+        <v>-30100</v>
       </c>
       <c r="N16" s="13">
-        <v>91.45</v>
+        <v>-8.5500000000000007</v>
       </c>
       <c r="O16" s="12">
         <v>0</v>
@@ -3047,10 +3047,10 @@
         <v>0</v>
       </c>
       <c r="Q16" s="12">
-        <v>321900</v>
+        <v>-30100</v>
       </c>
       <c r="R16" s="13">
-        <v>91.45</v>
+        <v>-8.5500000000000007</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -3129,28 +3129,28 @@
         <v>1148575.97</v>
       </c>
       <c r="G18" s="12">
-        <v>284136</v>
+        <v>321536</v>
       </c>
       <c r="H18" s="13">
-        <v>24.74</v>
+        <v>27.99</v>
       </c>
       <c r="I18" s="12">
-        <v>32100</v>
+        <v>1000</v>
       </c>
       <c r="J18" s="13">
-        <v>2.79</v>
+        <v>0.09</v>
       </c>
       <c r="K18" s="12">
-        <v>316236</v>
+        <v>322536</v>
       </c>
       <c r="L18" s="13">
-        <v>27.53</v>
+        <v>28.08</v>
       </c>
       <c r="M18" s="12">
-        <v>832339.97</v>
+        <v>826039.97</v>
       </c>
       <c r="N18" s="13">
-        <v>72.47</v>
+        <v>71.92</v>
       </c>
       <c r="O18" s="12">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Q18" s="12">
-        <v>832339.97</v>
+        <v>826039.97</v>
       </c>
       <c r="R18" s="13">
-        <v>72.47</v>
+        <v>71.92</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
@@ -3297,28 +3297,28 @@
         <v>173666</v>
       </c>
       <c r="G21" s="12">
-        <v>173666</v>
+        <v>194966</v>
       </c>
       <c r="H21" s="13">
-        <v>100</v>
+        <v>112.26</v>
       </c>
       <c r="I21" s="12">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="J21" s="13">
-        <v>15.55</v>
+        <v>0</v>
       </c>
       <c r="K21" s="12">
-        <v>200666</v>
+        <v>194966</v>
       </c>
       <c r="L21" s="13">
-        <v>115.55</v>
+        <v>112.26</v>
       </c>
       <c r="M21" s="12">
-        <v>-27000</v>
+        <v>-21300</v>
       </c>
       <c r="N21" s="13">
-        <v>-15.55</v>
+        <v>-12.26</v>
       </c>
       <c r="O21" s="12">
         <v>0</v>
@@ -3327,10 +3327,10 @@
         <v>0</v>
       </c>
       <c r="Q21" s="12">
-        <v>-27000</v>
+        <v>-21300</v>
       </c>
       <c r="R21" s="13">
-        <v>-15.55</v>
+        <v>-12.26</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -3577,28 +3577,28 @@
         <v>330000</v>
       </c>
       <c r="G26" s="12">
-        <v>241635.39</v>
+        <v>247085.39</v>
       </c>
       <c r="H26" s="13">
-        <v>73.22</v>
+        <v>74.87</v>
       </c>
       <c r="I26" s="12">
-        <v>206850</v>
+        <v>200850</v>
       </c>
       <c r="J26" s="13">
-        <v>62.68</v>
+        <v>60.86</v>
       </c>
       <c r="K26" s="12">
-        <v>448485.39</v>
+        <v>447935.39</v>
       </c>
       <c r="L26" s="13">
-        <v>135.9</v>
+        <v>135.74</v>
       </c>
       <c r="M26" s="12">
-        <v>-118485.39</v>
+        <v>-117935.39</v>
       </c>
       <c r="N26" s="13">
-        <v>-35.9</v>
+        <v>-35.74</v>
       </c>
       <c r="O26" s="12">
         <v>0</v>
@@ -3607,10 +3607,10 @@
         <v>0</v>
       </c>
       <c r="Q26" s="12">
-        <v>-118485.39</v>
+        <v>-117935.39</v>
       </c>
       <c r="R26" s="13">
-        <v>-35.9</v>
+        <v>-35.74</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -3639,22 +3639,22 @@
         <v>32.29</v>
       </c>
       <c r="I27" s="12">
-        <v>1835</v>
+        <v>11685</v>
       </c>
       <c r="J27" s="13">
-        <v>0.56000000000000005</v>
+        <v>3.54</v>
       </c>
       <c r="K27" s="12">
-        <v>108499.6</v>
+        <v>118349.6</v>
       </c>
       <c r="L27" s="13">
-        <v>32.840000000000003</v>
+        <v>35.82</v>
       </c>
       <c r="M27" s="12">
-        <v>221855.4</v>
+        <v>212005.4</v>
       </c>
       <c r="N27" s="13">
-        <v>67.16</v>
+        <v>64.180000000000007</v>
       </c>
       <c r="O27" s="12">
         <v>0</v>
@@ -3663,10 +3663,10 @@
         <v>0</v>
       </c>
       <c r="Q27" s="12">
-        <v>221855.4</v>
+        <v>212005.4</v>
       </c>
       <c r="R27" s="13">
-        <v>67.16</v>
+        <v>64.180000000000007</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -3689,28 +3689,28 @@
         <v>4260000</v>
       </c>
       <c r="G28" s="8">
-        <v>2025237.43</v>
+        <v>2108870.94</v>
       </c>
       <c r="H28" s="9">
-        <v>47.54</v>
+        <v>49.5</v>
       </c>
       <c r="I28" s="8">
-        <v>502696.67</v>
+        <v>428863.16</v>
       </c>
       <c r="J28" s="9">
-        <v>11.8</v>
+        <v>10.07</v>
       </c>
       <c r="K28" s="8">
-        <v>2527934.1</v>
+        <v>2537734.1</v>
       </c>
       <c r="L28" s="9">
-        <v>59.34</v>
+        <v>59.57</v>
       </c>
       <c r="M28" s="8">
-        <v>1732065.9</v>
+        <v>1722265.9</v>
       </c>
       <c r="N28" s="9">
-        <v>40.659999999999997</v>
+        <v>40.43</v>
       </c>
       <c r="O28" s="8">
         <v>274000</v>
@@ -3719,10 +3719,10 @@
         <v>6.43</v>
       </c>
       <c r="Q28" s="8">
-        <v>1458065.9</v>
+        <v>1448265.9</v>
       </c>
       <c r="R28" s="9">
-        <v>34.229999999999997</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
@@ -3745,16 +3745,16 @@
         <v>1820000</v>
       </c>
       <c r="G29" s="12">
-        <v>767964.87</v>
+        <v>813707.37</v>
       </c>
       <c r="H29" s="13">
-        <v>42.2</v>
+        <v>44.71</v>
       </c>
       <c r="I29" s="12">
-        <v>366730</v>
+        <v>320987.5</v>
       </c>
       <c r="J29" s="13">
-        <v>20.149999999999999</v>
+        <v>17.64</v>
       </c>
       <c r="K29" s="12">
         <v>1134694.8700000001</v>
@@ -3857,28 +3857,28 @@
         <v>1000000</v>
       </c>
       <c r="G31" s="12">
-        <v>13000</v>
+        <v>21455</v>
       </c>
       <c r="H31" s="13">
-        <v>1.3</v>
+        <v>2.15</v>
       </c>
       <c r="I31" s="12">
-        <v>0</v>
+        <v>1345</v>
       </c>
       <c r="J31" s="13">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="K31" s="12">
-        <v>13000</v>
+        <v>22800</v>
       </c>
       <c r="L31" s="13">
-        <v>1.3</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="M31" s="12">
-        <v>987000</v>
+        <v>977200</v>
       </c>
       <c r="N31" s="13">
-        <v>98.7</v>
+        <v>97.72</v>
       </c>
       <c r="O31" s="12">
         <v>0</v>
@@ -3887,10 +3887,10 @@
         <v>0</v>
       </c>
       <c r="Q31" s="12">
-        <v>987000</v>
+        <v>977200</v>
       </c>
       <c r="R31" s="13">
-        <v>98.7</v>
+        <v>97.72</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -3913,16 +3913,16 @@
         <v>400000</v>
       </c>
       <c r="G32" s="12">
-        <v>1039586.76</v>
+        <v>1069022.77</v>
       </c>
       <c r="H32" s="13">
-        <v>259.89999999999998</v>
+        <v>267.26</v>
       </c>
       <c r="I32" s="12">
-        <v>134696.67000000001</v>
+        <v>105260.66</v>
       </c>
       <c r="J32" s="13">
-        <v>33.67</v>
+        <v>26.32</v>
       </c>
       <c r="K32" s="12">
         <v>1174283.43</v>
@@ -4143,34 +4143,34 @@
         <v>94.22</v>
       </c>
       <c r="I36" s="8">
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="J36" s="9">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="K36" s="8">
-        <v>473712.9</v>
+        <v>471112.9</v>
       </c>
       <c r="L36" s="9">
-        <v>94.74</v>
+        <v>94.22</v>
       </c>
       <c r="M36" s="8">
-        <v>26287.1</v>
+        <v>28887.1</v>
       </c>
       <c r="N36" s="9">
-        <v>5.26</v>
+        <v>5.78</v>
       </c>
       <c r="O36" s="8">
-        <v>4721.6000000000004</v>
+        <v>0</v>
       </c>
       <c r="P36" s="9">
-        <v>0.94</v>
+        <v>0</v>
       </c>
       <c r="Q36" s="8">
-        <v>21565.5</v>
+        <v>28887.1</v>
       </c>
       <c r="R36" s="9">
-        <v>4.3099999999999996</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="37" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -4199,34 +4199,34 @@
         <v>93.33</v>
       </c>
       <c r="I37" s="12">
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="J37" s="13">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="K37" s="12">
-        <v>375924.9</v>
+        <v>373324.9</v>
       </c>
       <c r="L37" s="13">
-        <v>93.98</v>
+        <v>93.33</v>
       </c>
       <c r="M37" s="12">
-        <v>24075.1</v>
+        <v>26675.1</v>
       </c>
       <c r="N37" s="13">
-        <v>6.02</v>
+        <v>6.67</v>
       </c>
       <c r="O37" s="12">
-        <v>4721.6000000000004</v>
+        <v>0</v>
       </c>
       <c r="P37" s="13">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q37" s="12">
-        <v>19353.5</v>
+        <v>26675.1</v>
       </c>
       <c r="R37" s="13">
-        <v>4.84</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="38" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -4311,22 +4311,22 @@
         <v>73.89</v>
       </c>
       <c r="I39" s="8">
-        <v>5000</v>
+        <v>4300</v>
       </c>
       <c r="J39" s="9">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="K39" s="8">
-        <v>876902.87</v>
+        <v>876202.87</v>
       </c>
       <c r="L39" s="9">
-        <v>74.31</v>
+        <v>74.25</v>
       </c>
       <c r="M39" s="8">
-        <v>303097.13</v>
+        <v>303797.13</v>
       </c>
       <c r="N39" s="9">
-        <v>25.69</v>
+        <v>25.75</v>
       </c>
       <c r="O39" s="8">
         <v>0</v>
@@ -4335,10 +4335,10 @@
         <v>0</v>
       </c>
       <c r="Q39" s="8">
-        <v>303097.13</v>
+        <v>303797.13</v>
       </c>
       <c r="R39" s="9">
-        <v>25.69</v>
+        <v>25.75</v>
       </c>
     </row>
     <row r="40" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -4423,22 +4423,22 @@
         <v>44.81</v>
       </c>
       <c r="I41" s="12">
-        <v>5000</v>
+        <v>4300</v>
       </c>
       <c r="J41" s="13">
-        <v>0.64</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="K41" s="12">
-        <v>354538</v>
+        <v>353838</v>
       </c>
       <c r="L41" s="13">
-        <v>45.45</v>
+        <v>45.36</v>
       </c>
       <c r="M41" s="12">
-        <v>425462</v>
+        <v>426162</v>
       </c>
       <c r="N41" s="13">
-        <v>54.55</v>
+        <v>54.64</v>
       </c>
       <c r="O41" s="12">
         <v>0</v>
@@ -4447,10 +4447,10 @@
         <v>0</v>
       </c>
       <c r="Q41" s="12">
-        <v>425462</v>
+        <v>426162</v>
       </c>
       <c r="R41" s="13">
-        <v>54.55</v>
+        <v>54.64</v>
       </c>
     </row>
     <row r="42" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -4479,22 +4479,22 @@
         <v>66.010000000000005</v>
       </c>
       <c r="I42" s="8">
-        <v>288283</v>
+        <v>334583</v>
       </c>
       <c r="J42" s="9">
-        <v>11.03</v>
+        <v>12.8</v>
       </c>
       <c r="K42" s="8">
-        <v>2013089.67</v>
+        <v>2059389.67</v>
       </c>
       <c r="L42" s="9">
-        <v>77.040000000000006</v>
+        <v>78.819999999999993</v>
       </c>
       <c r="M42" s="8">
-        <v>599824.32999999996</v>
+        <v>553524.32999999996</v>
       </c>
       <c r="N42" s="9">
-        <v>22.96</v>
+        <v>21.18</v>
       </c>
       <c r="O42" s="8">
         <v>0</v>
@@ -4503,10 +4503,10 @@
         <v>0</v>
       </c>
       <c r="Q42" s="8">
-        <v>599824.32999999996</v>
+        <v>553524.32999999996</v>
       </c>
       <c r="R42" s="9">
-        <v>22.96</v>
+        <v>21.18</v>
       </c>
     </row>
     <row r="43" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -4535,22 +4535,22 @@
         <v>40.159999999999997</v>
       </c>
       <c r="I43" s="12">
-        <v>33003</v>
+        <v>75803</v>
       </c>
       <c r="J43" s="13">
-        <v>10.11</v>
+        <v>23.22</v>
       </c>
       <c r="K43" s="12">
-        <v>164140</v>
+        <v>206940</v>
       </c>
       <c r="L43" s="13">
-        <v>50.27</v>
+        <v>63.38</v>
       </c>
       <c r="M43" s="12">
-        <v>162374</v>
+        <v>119574</v>
       </c>
       <c r="N43" s="13">
-        <v>49.73</v>
+        <v>36.619999999999997</v>
       </c>
       <c r="O43" s="12">
         <v>0</v>
@@ -4559,10 +4559,10 @@
         <v>0</v>
       </c>
       <c r="Q43" s="12">
-        <v>162374</v>
+        <v>119574</v>
       </c>
       <c r="R43" s="13">
-        <v>49.73</v>
+        <v>36.619999999999997</v>
       </c>
     </row>
     <row r="44" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -4647,22 +4647,22 @@
         <v>76.98</v>
       </c>
       <c r="I45" s="12">
-        <v>255280</v>
+        <v>258780</v>
       </c>
       <c r="J45" s="13">
-        <v>13.59</v>
+        <v>13.78</v>
       </c>
       <c r="K45" s="12">
-        <v>1701034.67</v>
+        <v>1704534.67</v>
       </c>
       <c r="L45" s="13">
-        <v>90.58</v>
+        <v>90.76</v>
       </c>
       <c r="M45" s="12">
-        <v>176965.33</v>
+        <v>173465.33</v>
       </c>
       <c r="N45" s="13">
-        <v>9.42</v>
+        <v>9.24</v>
       </c>
       <c r="O45" s="12">
         <v>0</v>
@@ -4671,10 +4671,10 @@
         <v>0</v>
       </c>
       <c r="Q45" s="12">
-        <v>176965.33</v>
+        <v>173465.33</v>
       </c>
       <c r="R45" s="13">
-        <v>9.42</v>
+        <v>9.24</v>
       </c>
     </row>
     <row r="46" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -4753,40 +4753,40 @@
         <v>54940200</v>
       </c>
       <c r="G47" s="4">
-        <v>39654207.579999998</v>
+        <v>41097272.969999999</v>
       </c>
       <c r="H47" s="5">
-        <v>72.180000000000007</v>
+        <v>74.8</v>
       </c>
       <c r="I47" s="4">
-        <v>6647725.0599999996</v>
+        <v>4983091.67</v>
       </c>
       <c r="J47" s="5">
-        <v>12.1</v>
+        <v>9.07</v>
       </c>
       <c r="K47" s="4">
-        <v>46301932.640000001</v>
+        <v>46080364.640000001</v>
       </c>
       <c r="L47" s="5">
-        <v>84.28</v>
+        <v>83.87</v>
       </c>
       <c r="M47" s="4">
-        <v>8638267.3599999994</v>
+        <v>8859835.3599999994</v>
       </c>
       <c r="N47" s="5">
-        <v>15.72</v>
+        <v>16.13</v>
       </c>
       <c r="O47" s="4">
-        <v>1155422.5</v>
+        <v>1200986.5</v>
       </c>
       <c r="P47" s="5">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="Q47" s="4">
-        <v>7482844.8600000003</v>
+        <v>7658848.8600000003</v>
       </c>
       <c r="R47" s="5">
-        <v>13.62</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -4809,40 +4809,40 @@
         <v>11340200</v>
       </c>
       <c r="G48" s="8">
-        <v>8648491.9600000009</v>
+        <v>9109304.9600000009</v>
       </c>
       <c r="H48" s="9">
-        <v>76.260000000000005</v>
+        <v>80.33</v>
       </c>
       <c r="I48" s="8">
-        <v>1673930.67</v>
+        <v>1270099.67</v>
       </c>
       <c r="J48" s="9">
-        <v>14.76</v>
+        <v>11.2</v>
       </c>
       <c r="K48" s="8">
-        <v>10322422.630000001</v>
+        <v>10379404.630000001</v>
       </c>
       <c r="L48" s="9">
-        <v>91.03</v>
+        <v>91.53</v>
       </c>
       <c r="M48" s="8">
-        <v>1017777.37</v>
+        <v>960795.37</v>
       </c>
       <c r="N48" s="9">
-        <v>8.9700000000000006</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="O48" s="8">
-        <v>140079.5</v>
+        <v>110079.5</v>
       </c>
       <c r="P48" s="9">
-        <v>1.24</v>
+        <v>0.97</v>
       </c>
       <c r="Q48" s="8">
-        <v>877697.87</v>
+        <v>850715.87</v>
       </c>
       <c r="R48" s="9">
-        <v>7.74</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="49" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -4865,28 +4865,28 @@
         <v>1300000</v>
       </c>
       <c r="G49" s="12">
-        <v>919630.5</v>
+        <v>1079098.5</v>
       </c>
       <c r="H49" s="13">
-        <v>70.739999999999995</v>
+        <v>83.01</v>
       </c>
       <c r="I49" s="12">
-        <v>457005</v>
+        <v>303240</v>
       </c>
       <c r="J49" s="13">
-        <v>35.15</v>
+        <v>23.33</v>
       </c>
       <c r="K49" s="12">
-        <v>1376635.5</v>
+        <v>1382338.5</v>
       </c>
       <c r="L49" s="13">
-        <v>105.9</v>
+        <v>106.33</v>
       </c>
       <c r="M49" s="12">
-        <v>-76635.5</v>
+        <v>-82338.5</v>
       </c>
       <c r="N49" s="13">
-        <v>-5.9</v>
+        <v>-6.33</v>
       </c>
       <c r="O49" s="12">
         <v>90000</v>
@@ -4895,10 +4895,10 @@
         <v>6.92</v>
       </c>
       <c r="Q49" s="12">
-        <v>-166635.5</v>
+        <v>-172338.5</v>
       </c>
       <c r="R49" s="13">
-        <v>-12.82</v>
+        <v>-13.26</v>
       </c>
     </row>
     <row r="50" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -4977,28 +4977,28 @@
         <v>4320000</v>
       </c>
       <c r="G51" s="12">
-        <v>2771671.7</v>
+        <v>3004251.7</v>
       </c>
       <c r="H51" s="13">
-        <v>64.16</v>
+        <v>69.540000000000006</v>
       </c>
       <c r="I51" s="12">
-        <v>653335.67000000004</v>
+        <v>447729.67</v>
       </c>
       <c r="J51" s="13">
-        <v>15.12</v>
+        <v>10.36</v>
       </c>
       <c r="K51" s="12">
-        <v>3425007.37</v>
+        <v>3451981.37</v>
       </c>
       <c r="L51" s="13">
-        <v>79.28</v>
+        <v>79.91</v>
       </c>
       <c r="M51" s="12">
-        <v>894992.63</v>
+        <v>868018.63</v>
       </c>
       <c r="N51" s="13">
-        <v>20.72</v>
+        <v>20.09</v>
       </c>
       <c r="O51" s="12">
         <v>0</v>
@@ -5007,10 +5007,10 @@
         <v>0</v>
       </c>
       <c r="Q51" s="12">
-        <v>894992.63</v>
+        <v>868018.63</v>
       </c>
       <c r="R51" s="13">
-        <v>20.72</v>
+        <v>20.09</v>
       </c>
     </row>
     <row r="52" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -5033,28 +5033,28 @@
         <v>2020200</v>
       </c>
       <c r="G52" s="12">
-        <v>1731956</v>
+        <v>1770721</v>
       </c>
       <c r="H52" s="13">
-        <v>85.73</v>
+        <v>87.65</v>
       </c>
       <c r="I52" s="12">
-        <v>246790</v>
+        <v>202330</v>
       </c>
       <c r="J52" s="13">
-        <v>12.22</v>
+        <v>10.02</v>
       </c>
       <c r="K52" s="12">
-        <v>1978746</v>
+        <v>1973051</v>
       </c>
       <c r="L52" s="13">
-        <v>97.95</v>
+        <v>97.67</v>
       </c>
       <c r="M52" s="12">
-        <v>41454</v>
+        <v>47149</v>
       </c>
       <c r="N52" s="13">
-        <v>2.0499999999999998</v>
+        <v>2.33</v>
       </c>
       <c r="O52" s="12">
         <v>20079.5</v>
@@ -5063,10 +5063,10 @@
         <v>0.99</v>
       </c>
       <c r="Q52" s="12">
-        <v>21374.5</v>
+        <v>27069.5</v>
       </c>
       <c r="R52" s="13">
-        <v>1.06</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="53" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -5089,10 +5089,10 @@
         <v>500000</v>
       </c>
       <c r="G53" s="12">
-        <v>365443.76</v>
+        <v>395443.76</v>
       </c>
       <c r="H53" s="13">
-        <v>73.09</v>
+        <v>79.09</v>
       </c>
       <c r="I53" s="12">
         <v>0</v>
@@ -5101,22 +5101,22 @@
         <v>0</v>
       </c>
       <c r="K53" s="12">
-        <v>365443.76</v>
+        <v>395443.76</v>
       </c>
       <c r="L53" s="13">
-        <v>73.09</v>
+        <v>79.09</v>
       </c>
       <c r="M53" s="12">
-        <v>134556.24</v>
+        <v>104556.24</v>
       </c>
       <c r="N53" s="13">
-        <v>26.91</v>
+        <v>20.91</v>
       </c>
       <c r="O53" s="12">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="P53" s="13">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q53" s="12">
         <v>104556.24</v>
@@ -5145,40 +5145,40 @@
         <v>13420000</v>
       </c>
       <c r="G54" s="8">
-        <v>10318412.029999999</v>
+        <v>10751421.42</v>
       </c>
       <c r="H54" s="9">
-        <v>76.89</v>
+        <v>80.11</v>
       </c>
       <c r="I54" s="8">
-        <v>1389392.39</v>
+        <v>751226</v>
       </c>
       <c r="J54" s="9">
-        <v>10.35</v>
+        <v>5.6</v>
       </c>
       <c r="K54" s="8">
-        <v>11707804.42</v>
+        <v>11502647.42</v>
       </c>
       <c r="L54" s="9">
-        <v>87.24</v>
+        <v>85.71</v>
       </c>
       <c r="M54" s="8">
-        <v>1712195.58</v>
+        <v>1917352.58</v>
       </c>
       <c r="N54" s="9">
-        <v>12.76</v>
+        <v>14.29</v>
       </c>
       <c r="O54" s="8">
-        <v>378743</v>
+        <v>497000</v>
       </c>
       <c r="P54" s="9">
-        <v>2.82</v>
+        <v>3.7</v>
       </c>
       <c r="Q54" s="8">
-        <v>1333452.58</v>
+        <v>1420352.58</v>
       </c>
       <c r="R54" s="9">
-        <v>9.94</v>
+        <v>10.58</v>
       </c>
     </row>
     <row r="55" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -5257,40 +5257,40 @@
         <v>2700000</v>
       </c>
       <c r="G56" s="12">
-        <v>2022285.35</v>
+        <v>2049285.35</v>
       </c>
       <c r="H56" s="13">
-        <v>74.900000000000006</v>
+        <v>75.900000000000006</v>
       </c>
       <c r="I56" s="12">
-        <v>157786</v>
+        <v>141226</v>
       </c>
       <c r="J56" s="13">
-        <v>5.84</v>
+        <v>5.23</v>
       </c>
       <c r="K56" s="12">
-        <v>2180071.35</v>
+        <v>2190511.35</v>
       </c>
       <c r="L56" s="13">
-        <v>80.739999999999995</v>
+        <v>81.13</v>
       </c>
       <c r="M56" s="12">
-        <v>519928.65</v>
+        <v>509488.65</v>
       </c>
       <c r="N56" s="13">
-        <v>19.260000000000002</v>
+        <v>18.87</v>
       </c>
       <c r="O56" s="12">
-        <v>263000</v>
+        <v>497000</v>
       </c>
       <c r="P56" s="13">
-        <v>9.74</v>
+        <v>18.41</v>
       </c>
       <c r="Q56" s="12">
-        <v>256928.65</v>
+        <v>12488.65</v>
       </c>
       <c r="R56" s="13">
-        <v>9.52</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="57" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -5313,28 +5313,28 @@
         <v>3400000</v>
       </c>
       <c r="G57" s="12">
-        <v>2439305.41</v>
+        <v>2297925.41</v>
       </c>
       <c r="H57" s="13">
-        <v>71.739999999999995</v>
+        <v>67.59</v>
       </c>
       <c r="I57" s="12">
-        <v>283650</v>
+        <v>210000</v>
       </c>
       <c r="J57" s="13">
-        <v>8.34</v>
+        <v>6.18</v>
       </c>
       <c r="K57" s="12">
-        <v>2722955.41</v>
+        <v>2507925.41</v>
       </c>
       <c r="L57" s="13">
-        <v>80.09</v>
+        <v>73.760000000000005</v>
       </c>
       <c r="M57" s="12">
-        <v>677044.59</v>
+        <v>892074.59</v>
       </c>
       <c r="N57" s="13">
-        <v>19.91</v>
+        <v>26.24</v>
       </c>
       <c r="O57" s="12">
         <v>0</v>
@@ -5343,10 +5343,10 @@
         <v>0</v>
       </c>
       <c r="Q57" s="12">
-        <v>677044.59</v>
+        <v>892074.59</v>
       </c>
       <c r="R57" s="13">
-        <v>19.91</v>
+        <v>26.24</v>
       </c>
     </row>
     <row r="58" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -5537,40 +5537,40 @@
         <v>2600000</v>
       </c>
       <c r="G61" s="12">
-        <v>1680984.22</v>
+        <v>2228373.61</v>
       </c>
       <c r="H61" s="13">
-        <v>64.650000000000006</v>
+        <v>85.71</v>
       </c>
       <c r="I61" s="12">
-        <v>547956.39</v>
+        <v>0</v>
       </c>
       <c r="J61" s="13">
-        <v>21.08</v>
+        <v>0</v>
       </c>
       <c r="K61" s="12">
-        <v>2228940.61</v>
+        <v>2228373.61</v>
       </c>
       <c r="L61" s="13">
-        <v>85.73</v>
+        <v>85.71</v>
       </c>
       <c r="M61" s="12">
-        <v>371059.39</v>
+        <v>371626.39</v>
       </c>
       <c r="N61" s="13">
-        <v>14.27</v>
+        <v>14.29</v>
       </c>
       <c r="O61" s="12">
-        <v>115743</v>
+        <v>0</v>
       </c>
       <c r="P61" s="13">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="12">
-        <v>255316.39</v>
+        <v>371626.39</v>
       </c>
       <c r="R61" s="13">
-        <v>9.82</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="62" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -5761,28 +5761,28 @@
         <v>11720000</v>
       </c>
       <c r="G65" s="8">
-        <v>7948887</v>
+        <v>8155521</v>
       </c>
       <c r="H65" s="9">
-        <v>67.819999999999993</v>
+        <v>69.59</v>
       </c>
       <c r="I65" s="8">
-        <v>1650895</v>
+        <v>1281876</v>
       </c>
       <c r="J65" s="9">
-        <v>14.09</v>
+        <v>10.94</v>
       </c>
       <c r="K65" s="8">
-        <v>9599782</v>
+        <v>9437397</v>
       </c>
       <c r="L65" s="9">
-        <v>81.91</v>
+        <v>80.52</v>
       </c>
       <c r="M65" s="8">
-        <v>2120218</v>
+        <v>2282603</v>
       </c>
       <c r="N65" s="9">
-        <v>18.09</v>
+        <v>19.48</v>
       </c>
       <c r="O65" s="8">
         <v>30600</v>
@@ -5791,10 +5791,10 @@
         <v>0.26</v>
       </c>
       <c r="Q65" s="8">
-        <v>2089618</v>
+        <v>2252003</v>
       </c>
       <c r="R65" s="9">
-        <v>17.829999999999998</v>
+        <v>19.22</v>
       </c>
     </row>
     <row r="66" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -5873,28 +5873,28 @@
         <v>1775000</v>
       </c>
       <c r="G67" s="12">
-        <v>649252</v>
+        <v>714086</v>
       </c>
       <c r="H67" s="13">
-        <v>36.58</v>
+        <v>40.229999999999997</v>
       </c>
       <c r="I67" s="12">
-        <v>106000</v>
+        <v>129500</v>
       </c>
       <c r="J67" s="13">
-        <v>5.97</v>
+        <v>7.3</v>
       </c>
       <c r="K67" s="12">
-        <v>755252</v>
+        <v>843586</v>
       </c>
       <c r="L67" s="13">
-        <v>42.55</v>
+        <v>47.53</v>
       </c>
       <c r="M67" s="12">
-        <v>1019748</v>
+        <v>931414</v>
       </c>
       <c r="N67" s="13">
-        <v>57.45</v>
+        <v>52.47</v>
       </c>
       <c r="O67" s="12">
         <v>30000</v>
@@ -5903,10 +5903,10 @@
         <v>1.69</v>
       </c>
       <c r="Q67" s="12">
-        <v>989748</v>
+        <v>901414</v>
       </c>
       <c r="R67" s="13">
-        <v>55.76</v>
+        <v>50.78</v>
       </c>
     </row>
     <row r="68" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -5929,28 +5929,28 @@
         <v>2820000</v>
       </c>
       <c r="G68" s="12">
-        <v>2167347</v>
+        <v>2021147</v>
       </c>
       <c r="H68" s="13">
-        <v>76.86</v>
+        <v>71.67</v>
       </c>
       <c r="I68" s="12">
-        <v>412954</v>
+        <v>331410</v>
       </c>
       <c r="J68" s="13">
-        <v>14.64</v>
+        <v>11.75</v>
       </c>
       <c r="K68" s="12">
-        <v>2580301</v>
+        <v>2352557</v>
       </c>
       <c r="L68" s="13">
-        <v>91.5</v>
+        <v>83.42</v>
       </c>
       <c r="M68" s="12">
-        <v>239699</v>
+        <v>467443</v>
       </c>
       <c r="N68" s="13">
-        <v>8.5</v>
+        <v>16.579999999999998</v>
       </c>
       <c r="O68" s="12">
         <v>600</v>
@@ -5959,10 +5959,10 @@
         <v>0.02</v>
       </c>
       <c r="Q68" s="12">
-        <v>239099</v>
+        <v>466843</v>
       </c>
       <c r="R68" s="13">
-        <v>8.48</v>
+        <v>16.55</v>
       </c>
     </row>
     <row r="69" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -5991,22 +5991,22 @@
         <v>166.5</v>
       </c>
       <c r="I69" s="12">
-        <v>775</v>
+        <v>3700</v>
       </c>
       <c r="J69" s="13">
-        <v>1.21</v>
+        <v>5.78</v>
       </c>
       <c r="K69" s="12">
-        <v>107335</v>
+        <v>110260</v>
       </c>
       <c r="L69" s="13">
-        <v>167.71</v>
+        <v>172.28</v>
       </c>
       <c r="M69" s="12">
-        <v>-43335</v>
+        <v>-46260</v>
       </c>
       <c r="N69" s="13">
-        <v>-67.709999999999994</v>
+        <v>-72.28</v>
       </c>
       <c r="O69" s="12">
         <v>0</v>
@@ -6015,10 +6015,10 @@
         <v>0</v>
       </c>
       <c r="Q69" s="12">
-        <v>-43335</v>
+        <v>-46260</v>
       </c>
       <c r="R69" s="13">
-        <v>-67.709999999999994</v>
+        <v>-72.28</v>
       </c>
     </row>
     <row r="70" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -6041,28 +6041,28 @@
         <v>4061000</v>
       </c>
       <c r="G70" s="12">
-        <v>2325728</v>
+        <v>2613728</v>
       </c>
       <c r="H70" s="13">
-        <v>57.27</v>
+        <v>64.36</v>
       </c>
       <c r="I70" s="12">
-        <v>831166</v>
+        <v>517266</v>
       </c>
       <c r="J70" s="13">
-        <v>20.47</v>
+        <v>12.74</v>
       </c>
       <c r="K70" s="12">
-        <v>3156894</v>
+        <v>3130994</v>
       </c>
       <c r="L70" s="13">
-        <v>77.739999999999995</v>
+        <v>77.099999999999994</v>
       </c>
       <c r="M70" s="12">
-        <v>904106</v>
+        <v>930006</v>
       </c>
       <c r="N70" s="13">
-        <v>22.26</v>
+        <v>22.9</v>
       </c>
       <c r="O70" s="12">
         <v>0</v>
@@ -6071,10 +6071,10 @@
         <v>0</v>
       </c>
       <c r="Q70" s="12">
-        <v>904106</v>
+        <v>930006</v>
       </c>
       <c r="R70" s="13">
-        <v>22.26</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="71" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -6097,40 +6097,40 @@
         <v>10640000</v>
       </c>
       <c r="G71" s="8">
-        <v>7691068.29</v>
+        <v>7984077.29</v>
       </c>
       <c r="H71" s="9">
-        <v>72.28</v>
+        <v>75.040000000000006</v>
       </c>
       <c r="I71" s="8">
-        <v>912513</v>
+        <v>644246</v>
       </c>
       <c r="J71" s="9">
-        <v>8.58</v>
+        <v>6.05</v>
       </c>
       <c r="K71" s="8">
-        <v>8603581.2899999991</v>
+        <v>8628323.2899999991</v>
       </c>
       <c r="L71" s="9">
-        <v>80.86</v>
+        <v>81.09</v>
       </c>
       <c r="M71" s="8">
-        <v>2036418.71</v>
+        <v>2011676.71</v>
       </c>
       <c r="N71" s="9">
-        <v>19.14</v>
+        <v>18.91</v>
       </c>
       <c r="O71" s="8">
-        <v>56000</v>
+        <v>13307</v>
       </c>
       <c r="P71" s="9">
-        <v>0.53</v>
+        <v>0.13</v>
       </c>
       <c r="Q71" s="8">
-        <v>1980418.71</v>
+        <v>1998369.71</v>
       </c>
       <c r="R71" s="9">
-        <v>18.61</v>
+        <v>18.78</v>
       </c>
     </row>
     <row r="72" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -6153,28 +6153,28 @@
         <v>1140000</v>
       </c>
       <c r="G72" s="12">
-        <v>781824.22</v>
+        <v>794453.22</v>
       </c>
       <c r="H72" s="13">
-        <v>68.58</v>
+        <v>69.69</v>
       </c>
       <c r="I72" s="12">
-        <v>42210</v>
+        <v>30010</v>
       </c>
       <c r="J72" s="13">
-        <v>3.7</v>
+        <v>2.63</v>
       </c>
       <c r="K72" s="12">
-        <v>824034.22</v>
+        <v>824463.22</v>
       </c>
       <c r="L72" s="13">
-        <v>72.28</v>
+        <v>72.319999999999993</v>
       </c>
       <c r="M72" s="12">
-        <v>315965.78000000003</v>
+        <v>315536.78000000003</v>
       </c>
       <c r="N72" s="13">
-        <v>27.72</v>
+        <v>27.68</v>
       </c>
       <c r="O72" s="12">
         <v>0</v>
@@ -6183,10 +6183,10 @@
         <v>0</v>
       </c>
       <c r="Q72" s="12">
-        <v>315965.78000000003</v>
+        <v>315536.78000000003</v>
       </c>
       <c r="R72" s="13">
-        <v>27.72</v>
+        <v>27.68</v>
       </c>
     </row>
     <row r="73" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -6215,22 +6215,22 @@
         <v>89.45</v>
       </c>
       <c r="I73" s="12">
-        <v>7630</v>
+        <v>10400</v>
       </c>
       <c r="J73" s="13">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="K73" s="12">
-        <v>1975439.37</v>
+        <v>1978209.37</v>
       </c>
       <c r="L73" s="13">
-        <v>89.79</v>
+        <v>89.92</v>
       </c>
       <c r="M73" s="12">
-        <v>224560.63</v>
+        <v>221790.63</v>
       </c>
       <c r="N73" s="13">
-        <v>10.210000000000001</v>
+        <v>10.08</v>
       </c>
       <c r="O73" s="12">
         <v>0</v>
@@ -6239,10 +6239,10 @@
         <v>0</v>
       </c>
       <c r="Q73" s="12">
-        <v>224560.63</v>
+        <v>221790.63</v>
       </c>
       <c r="R73" s="13">
-        <v>10.210000000000001</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="74" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -6265,28 +6265,28 @@
         <v>700000</v>
       </c>
       <c r="G74" s="12">
-        <v>434411</v>
+        <v>596226</v>
       </c>
       <c r="H74" s="13">
-        <v>62.06</v>
+        <v>85.18</v>
       </c>
       <c r="I74" s="12">
-        <v>186300</v>
+        <v>24000</v>
       </c>
       <c r="J74" s="13">
-        <v>26.61</v>
+        <v>3.43</v>
       </c>
       <c r="K74" s="12">
-        <v>620711</v>
+        <v>620226</v>
       </c>
       <c r="L74" s="13">
-        <v>88.67</v>
+        <v>88.6</v>
       </c>
       <c r="M74" s="12">
-        <v>79289</v>
+        <v>79774</v>
       </c>
       <c r="N74" s="13">
-        <v>11.33</v>
+        <v>11.4</v>
       </c>
       <c r="O74" s="12">
         <v>6000</v>
@@ -6295,10 +6295,10 @@
         <v>0.86</v>
       </c>
       <c r="Q74" s="12">
-        <v>73289</v>
+        <v>73774</v>
       </c>
       <c r="R74" s="13">
-        <v>10.47</v>
+        <v>10.54</v>
       </c>
     </row>
     <row r="75" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -6377,28 +6377,28 @@
         <v>3300000</v>
       </c>
       <c r="G76" s="12">
-        <v>1889427.6</v>
+        <v>2008092.6</v>
       </c>
       <c r="H76" s="13">
-        <v>57.26</v>
+        <v>60.85</v>
       </c>
       <c r="I76" s="12">
-        <v>373863</v>
+        <v>234633</v>
       </c>
       <c r="J76" s="13">
-        <v>11.33</v>
+        <v>7.11</v>
       </c>
       <c r="K76" s="12">
-        <v>2263290.6</v>
+        <v>2242725.6</v>
       </c>
       <c r="L76" s="13">
-        <v>68.58</v>
+        <v>67.959999999999994</v>
       </c>
       <c r="M76" s="12">
-        <v>1036709.4</v>
+        <v>1057274.3999999999</v>
       </c>
       <c r="N76" s="13">
-        <v>31.42</v>
+        <v>32.04</v>
       </c>
       <c r="O76" s="12">
         <v>0</v>
@@ -6407,10 +6407,10 @@
         <v>0</v>
       </c>
       <c r="Q76" s="12">
-        <v>1036709.4</v>
+        <v>1057274.3999999999</v>
       </c>
       <c r="R76" s="13">
-        <v>31.42</v>
+        <v>32.04</v>
       </c>
     </row>
     <row r="77" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -6489,40 +6489,40 @@
         <v>500000</v>
       </c>
       <c r="G78" s="12">
-        <v>347670</v>
+        <v>347570</v>
       </c>
       <c r="H78" s="13">
-        <v>69.53</v>
+        <v>69.510000000000005</v>
       </c>
       <c r="I78" s="12">
-        <v>100000</v>
+        <v>142693</v>
       </c>
       <c r="J78" s="13">
-        <v>20</v>
+        <v>28.54</v>
       </c>
       <c r="K78" s="12">
-        <v>447670</v>
+        <v>490263</v>
       </c>
       <c r="L78" s="13">
-        <v>89.53</v>
+        <v>98.05</v>
       </c>
       <c r="M78" s="12">
-        <v>52330</v>
+        <v>9737</v>
       </c>
       <c r="N78" s="13">
-        <v>10.47</v>
+        <v>1.95</v>
       </c>
       <c r="O78" s="12">
-        <v>50000</v>
+        <v>7307</v>
       </c>
       <c r="P78" s="13">
-        <v>10</v>
+        <v>1.46</v>
       </c>
       <c r="Q78" s="12">
-        <v>2330</v>
+        <v>2430</v>
       </c>
       <c r="R78" s="13">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="79" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -6601,28 +6601,28 @@
         <v>7820000</v>
       </c>
       <c r="G80" s="8">
-        <v>5047348.3</v>
+        <v>5096948.3</v>
       </c>
       <c r="H80" s="9">
-        <v>64.540000000000006</v>
+        <v>65.180000000000007</v>
       </c>
       <c r="I80" s="8">
-        <v>1020994</v>
+        <v>1035644</v>
       </c>
       <c r="J80" s="9">
-        <v>13.06</v>
+        <v>13.24</v>
       </c>
       <c r="K80" s="8">
-        <v>6068342.2999999998</v>
+        <v>6132592.2999999998</v>
       </c>
       <c r="L80" s="9">
-        <v>77.599999999999994</v>
+        <v>78.42</v>
       </c>
       <c r="M80" s="8">
-        <v>1751657.7</v>
+        <v>1687407.7</v>
       </c>
       <c r="N80" s="9">
-        <v>22.4</v>
+        <v>21.58</v>
       </c>
       <c r="O80" s="8">
         <v>550000</v>
@@ -6631,10 +6631,10 @@
         <v>7.03</v>
       </c>
       <c r="Q80" s="8">
-        <v>1201657.7</v>
+        <v>1137407.7</v>
       </c>
       <c r="R80" s="9">
-        <v>15.37</v>
+        <v>14.54</v>
       </c>
     </row>
     <row r="81" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -6719,22 +6719,22 @@
         <v>115.56</v>
       </c>
       <c r="I82" s="12">
-        <v>189750</v>
+        <v>171550</v>
       </c>
       <c r="J82" s="13">
-        <v>15.81</v>
+        <v>14.3</v>
       </c>
       <c r="K82" s="12">
-        <v>1576464</v>
+        <v>1558264</v>
       </c>
       <c r="L82" s="13">
-        <v>131.37</v>
+        <v>129.86000000000001</v>
       </c>
       <c r="M82" s="12">
-        <v>-376464</v>
+        <v>-358264</v>
       </c>
       <c r="N82" s="13">
-        <v>-31.37</v>
+        <v>-29.86</v>
       </c>
       <c r="O82" s="12">
         <v>0</v>
@@ -6743,10 +6743,10 @@
         <v>0</v>
       </c>
       <c r="Q82" s="12">
-        <v>-376464</v>
+        <v>-358264</v>
       </c>
       <c r="R82" s="13">
-        <v>-31.37</v>
+        <v>-29.86</v>
       </c>
     </row>
     <row r="83" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -6825,28 +6825,28 @@
         <v>3000000</v>
       </c>
       <c r="G84" s="12">
-        <v>2223449</v>
+        <v>2265549</v>
       </c>
       <c r="H84" s="13">
-        <v>74.11</v>
+        <v>75.52</v>
       </c>
       <c r="I84" s="12">
-        <v>192344</v>
+        <v>247094</v>
       </c>
       <c r="J84" s="13">
-        <v>6.41</v>
+        <v>8.24</v>
       </c>
       <c r="K84" s="12">
-        <v>2415793</v>
+        <v>2512643</v>
       </c>
       <c r="L84" s="13">
-        <v>80.53</v>
+        <v>83.75</v>
       </c>
       <c r="M84" s="12">
-        <v>584207</v>
+        <v>487357</v>
       </c>
       <c r="N84" s="13">
-        <v>19.47</v>
+        <v>16.25</v>
       </c>
       <c r="O84" s="12">
         <v>0</v>
@@ -6855,10 +6855,10 @@
         <v>0</v>
       </c>
       <c r="Q84" s="12">
-        <v>584207</v>
+        <v>487357</v>
       </c>
       <c r="R84" s="13">
-        <v>19.47</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="85" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -7105,28 +7105,28 @@
         <v>1000000</v>
       </c>
       <c r="G89" s="12">
-        <v>68210</v>
+        <v>75710</v>
       </c>
       <c r="H89" s="13">
-        <v>6.82</v>
+        <v>7.57</v>
       </c>
       <c r="I89" s="12">
-        <v>500800</v>
+        <v>478900</v>
       </c>
       <c r="J89" s="13">
-        <v>50.08</v>
+        <v>47.89</v>
       </c>
       <c r="K89" s="12">
-        <v>569010</v>
+        <v>554610</v>
       </c>
       <c r="L89" s="13">
-        <v>56.9</v>
+        <v>55.46</v>
       </c>
       <c r="M89" s="12">
-        <v>430990</v>
+        <v>445390</v>
       </c>
       <c r="N89" s="13">
-        <v>43.1</v>
+        <v>44.54</v>
       </c>
       <c r="O89" s="12">
         <v>550000</v>
@@ -7135,10 +7135,10 @@
         <v>55</v>
       </c>
       <c r="Q89" s="12">
-        <v>-119010</v>
+        <v>-104610</v>
       </c>
       <c r="R89" s="13">
-        <v>-11.9</v>
+        <v>-10.46</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
@@ -7161,16 +7161,16 @@
         <v>9800000</v>
       </c>
       <c r="G90" s="4">
-        <v>5515006.6399999997</v>
+        <v>5612006.6399999997</v>
       </c>
       <c r="H90" s="5">
-        <v>56.28</v>
+        <v>57.27</v>
       </c>
       <c r="I90" s="4">
-        <v>960008.31</v>
+        <v>863008.31</v>
       </c>
       <c r="J90" s="5">
-        <v>9.8000000000000007</v>
+        <v>8.81</v>
       </c>
       <c r="K90" s="4">
         <v>6475014.9500000002</v>
@@ -7185,16 +7185,16 @@
         <v>33.93</v>
       </c>
       <c r="O90" s="4">
-        <v>2287551.54</v>
+        <v>3152551.54</v>
       </c>
       <c r="P90" s="5">
-        <v>23.34</v>
+        <v>32.17</v>
       </c>
       <c r="Q90" s="4">
-        <v>1037433.51</v>
+        <v>172433.51</v>
       </c>
       <c r="R90" s="5">
-        <v>10.59</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="91" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -7217,16 +7217,16 @@
         <v>9800000</v>
       </c>
       <c r="G91" s="8">
-        <v>5515006.6399999997</v>
+        <v>5612006.6399999997</v>
       </c>
       <c r="H91" s="9">
-        <v>56.28</v>
+        <v>57.27</v>
       </c>
       <c r="I91" s="8">
-        <v>960008.31</v>
+        <v>863008.31</v>
       </c>
       <c r="J91" s="9">
-        <v>9.8000000000000007</v>
+        <v>8.81</v>
       </c>
       <c r="K91" s="8">
         <v>6475014.9500000002</v>
@@ -7241,16 +7241,16 @@
         <v>33.93</v>
       </c>
       <c r="O91" s="8">
-        <v>2287551.54</v>
+        <v>3152551.54</v>
       </c>
       <c r="P91" s="9">
-        <v>23.34</v>
+        <v>32.17</v>
       </c>
       <c r="Q91" s="8">
-        <v>1037433.51</v>
+        <v>172433.51</v>
       </c>
       <c r="R91" s="9">
-        <v>10.59</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="92" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
@@ -7329,16 +7329,16 @@
         <v>3140000</v>
       </c>
       <c r="G93" s="12">
-        <v>1831527.49</v>
+        <v>1928527.49</v>
       </c>
       <c r="H93" s="13">
-        <v>58.33</v>
+        <v>61.42</v>
       </c>
       <c r="I93" s="12">
-        <v>389750</v>
+        <v>292750</v>
       </c>
       <c r="J93" s="13">
-        <v>12.41</v>
+        <v>9.32</v>
       </c>
       <c r="K93" s="12">
         <v>2221277.4900000002</v>
@@ -7353,16 +7353,16 @@
         <v>29.26</v>
       </c>
       <c r="O93" s="12">
-        <v>382500</v>
+        <v>1247500</v>
       </c>
       <c r="P93" s="13">
-        <v>12.18</v>
+        <v>39.729999999999997</v>
       </c>
       <c r="Q93" s="12">
-        <v>536222.51</v>
+        <v>-328777.49</v>
       </c>
       <c r="R93" s="13">
-        <v>17.079999999999998</v>
+        <v>-10.47</v>
       </c>
     </row>
     <row r="94" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -7441,40 +7441,40 @@
         <v>119421186</v>
       </c>
       <c r="G95" s="4">
-        <v>88118376.469999999</v>
+        <v>89759669.310000002</v>
       </c>
       <c r="H95" s="5">
-        <v>73.790000000000006</v>
+        <v>75.16</v>
       </c>
       <c r="I95" s="4">
-        <v>10927195.02</v>
+        <v>9427709.6799999997</v>
       </c>
       <c r="J95" s="5">
-        <v>9.15</v>
+        <v>7.89</v>
       </c>
       <c r="K95" s="4">
-        <v>99045571.489999995</v>
+        <v>99187378.989999995</v>
       </c>
       <c r="L95" s="5">
-        <v>82.94</v>
+        <v>83.06</v>
       </c>
       <c r="M95" s="4">
-        <v>20375614.510000002</v>
+        <v>20233807.010000002</v>
       </c>
       <c r="N95" s="5">
-        <v>17.059999999999999</v>
+        <v>16.940000000000001</v>
       </c>
       <c r="O95" s="4">
-        <v>5827810.6299999999</v>
+        <v>5807810.6299999999</v>
       </c>
       <c r="P95" s="5">
-        <v>4.88</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="Q95" s="4">
-        <v>14547803.880000001</v>
+        <v>14425996.380000001</v>
       </c>
       <c r="R95" s="5">
-        <v>12.18</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="96" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -7497,40 +7497,40 @@
         <v>29200000</v>
       </c>
       <c r="G96" s="8">
-        <v>17874149.43</v>
+        <v>18184522.469999999</v>
       </c>
       <c r="H96" s="9">
-        <v>61.21</v>
+        <v>62.28</v>
       </c>
       <c r="I96" s="8">
-        <v>5350409.6900000004</v>
+        <v>5051979.6500000004</v>
       </c>
       <c r="J96" s="9">
-        <v>18.32</v>
+        <v>17.3</v>
       </c>
       <c r="K96" s="8">
-        <v>23224559.120000001</v>
+        <v>23236502.120000001</v>
       </c>
       <c r="L96" s="9">
-        <v>79.540000000000006</v>
+        <v>79.58</v>
       </c>
       <c r="M96" s="8">
-        <v>5975440.8799999999</v>
+        <v>5963497.8799999999</v>
       </c>
       <c r="N96" s="9">
-        <v>20.46</v>
+        <v>20.420000000000002</v>
       </c>
       <c r="O96" s="8">
-        <v>4945423.37</v>
+        <v>5005423.37</v>
       </c>
       <c r="P96" s="9">
-        <v>16.940000000000001</v>
+        <v>17.14</v>
       </c>
       <c r="Q96" s="8">
-        <v>1030017.51</v>
+        <v>958074.51</v>
       </c>
       <c r="R96" s="9">
-        <v>3.53</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="97" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -7553,28 +7553,28 @@
         <v>3261268.89</v>
       </c>
       <c r="G97" s="12">
-        <v>2249322.37</v>
+        <v>2253215.37</v>
       </c>
       <c r="H97" s="13">
-        <v>68.97</v>
+        <v>69.09</v>
       </c>
       <c r="I97" s="12">
-        <v>942100</v>
+        <v>944200</v>
       </c>
       <c r="J97" s="13">
-        <v>28.89</v>
+        <v>28.95</v>
       </c>
       <c r="K97" s="12">
-        <v>3191422.37</v>
+        <v>3197415.37</v>
       </c>
       <c r="L97" s="13">
-        <v>97.86</v>
+        <v>98.04</v>
       </c>
       <c r="M97" s="12">
-        <v>69846.52</v>
+        <v>63853.52</v>
       </c>
       <c r="N97" s="13">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
       <c r="O97" s="12">
         <v>0</v>
@@ -7583,10 +7583,10 @@
         <v>0</v>
       </c>
       <c r="Q97" s="12">
-        <v>69846.52</v>
+        <v>63853.52</v>
       </c>
       <c r="R97" s="13">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="98" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -7609,16 +7609,16 @@
         <v>4780425.63</v>
       </c>
       <c r="G98" s="12">
-        <v>3448260.35</v>
+        <v>3473506.14</v>
       </c>
       <c r="H98" s="13">
-        <v>72.13</v>
+        <v>72.66</v>
       </c>
       <c r="I98" s="12">
-        <v>668001.54</v>
+        <v>642755.75</v>
       </c>
       <c r="J98" s="13">
-        <v>13.97</v>
+        <v>13.45</v>
       </c>
       <c r="K98" s="12">
         <v>4116261.89</v>
@@ -7665,40 +7665,40 @@
         <v>8310076.75</v>
       </c>
       <c r="G99" s="12">
-        <v>3256369.98</v>
+        <v>3428104.23</v>
       </c>
       <c r="H99" s="13">
-        <v>39.19</v>
+        <v>41.25</v>
       </c>
       <c r="I99" s="12">
-        <v>3375308.15</v>
+        <v>3209523.9</v>
       </c>
       <c r="J99" s="13">
-        <v>40.619999999999997</v>
+        <v>38.619999999999997</v>
       </c>
       <c r="K99" s="12">
-        <v>6631678.1299999999</v>
+        <v>6637628.1299999999</v>
       </c>
       <c r="L99" s="13">
-        <v>79.8</v>
+        <v>79.87</v>
       </c>
       <c r="M99" s="12">
-        <v>1678398.62</v>
+        <v>1672448.62</v>
       </c>
       <c r="N99" s="13">
-        <v>20.2</v>
+        <v>20.13</v>
       </c>
       <c r="O99" s="12">
-        <v>1245423.3700000001</v>
+        <v>1305423.3700000001</v>
       </c>
       <c r="P99" s="13">
-        <v>14.99</v>
+        <v>15.71</v>
       </c>
       <c r="Q99" s="12">
-        <v>432975.25</v>
+        <v>367025.25</v>
       </c>
       <c r="R99" s="13">
-        <v>5.21</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="100" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -7777,16 +7777,16 @@
         <v>12848228.73</v>
       </c>
       <c r="G101" s="12">
-        <v>8920196.7300000004</v>
+        <v>9029696.7300000004</v>
       </c>
       <c r="H101" s="13">
-        <v>69.430000000000007</v>
+        <v>70.28</v>
       </c>
       <c r="I101" s="12">
-        <v>365000</v>
+        <v>255500</v>
       </c>
       <c r="J101" s="13">
-        <v>2.84</v>
+        <v>1.99</v>
       </c>
       <c r="K101" s="12">
         <v>9285196.7300000004</v>
@@ -7839,22 +7839,22 @@
         <v>53.34</v>
       </c>
       <c r="I102" s="8">
-        <v>19570</v>
+        <v>31620</v>
       </c>
       <c r="J102" s="9">
-        <v>1.96</v>
+        <v>3.16</v>
       </c>
       <c r="K102" s="8">
-        <v>552949</v>
+        <v>564999</v>
       </c>
       <c r="L102" s="9">
-        <v>55.29</v>
+        <v>56.5</v>
       </c>
       <c r="M102" s="8">
-        <v>447051</v>
+        <v>435001</v>
       </c>
       <c r="N102" s="9">
-        <v>44.71</v>
+        <v>43.5</v>
       </c>
       <c r="O102" s="8">
         <v>0</v>
@@ -7863,10 +7863,10 @@
         <v>0</v>
       </c>
       <c r="Q102" s="8">
-        <v>447051</v>
+        <v>435001</v>
       </c>
       <c r="R102" s="9">
-        <v>44.71</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="103" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -7895,22 +7895,22 @@
         <v>52.22</v>
       </c>
       <c r="I103" s="12">
-        <v>19570</v>
+        <v>19370</v>
       </c>
       <c r="J103" s="13">
-        <v>2.21</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="K103" s="12">
-        <v>482559</v>
+        <v>482359</v>
       </c>
       <c r="L103" s="13">
-        <v>54.43</v>
+        <v>54.41</v>
       </c>
       <c r="M103" s="12">
-        <v>404041</v>
+        <v>404241</v>
       </c>
       <c r="N103" s="13">
-        <v>45.57</v>
+        <v>45.59</v>
       </c>
       <c r="O103" s="12">
         <v>0</v>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="Q103" s="12">
-        <v>404041</v>
+        <v>404241</v>
       </c>
       <c r="R103" s="13">
-        <v>45.57</v>
+        <v>45.59</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
@@ -7951,22 +7951,22 @@
         <v>62.07</v>
       </c>
       <c r="I104" s="12">
-        <v>0</v>
+        <v>12250</v>
       </c>
       <c r="J104" s="13">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="K104" s="12">
-        <v>70390</v>
+        <v>82640</v>
       </c>
       <c r="L104" s="13">
-        <v>62.07</v>
+        <v>72.87</v>
       </c>
       <c r="M104" s="12">
-        <v>43010</v>
+        <v>30760</v>
       </c>
       <c r="N104" s="13">
-        <v>37.93</v>
+        <v>27.13</v>
       </c>
       <c r="O104" s="12">
         <v>0</v>
@@ -7975,10 +7975,10 @@
         <v>0</v>
       </c>
       <c r="Q104" s="12">
-        <v>43010</v>
+        <v>30760</v>
       </c>
       <c r="R104" s="13">
-        <v>37.93</v>
+        <v>27.13</v>
       </c>
     </row>
     <row r="105" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -8001,28 +8001,28 @@
         <v>1000000</v>
       </c>
       <c r="G105" s="8">
-        <v>805551.74</v>
+        <v>821951.74</v>
       </c>
       <c r="H105" s="9">
-        <v>80.56</v>
+        <v>82.2</v>
       </c>
       <c r="I105" s="8">
-        <v>135942</v>
+        <v>115542</v>
       </c>
       <c r="J105" s="9">
-        <v>13.59</v>
+        <v>11.55</v>
       </c>
       <c r="K105" s="8">
-        <v>941493.74</v>
+        <v>937493.74</v>
       </c>
       <c r="L105" s="9">
-        <v>94.15</v>
+        <v>93.75</v>
       </c>
       <c r="M105" s="8">
-        <v>58506.26</v>
+        <v>62506.26</v>
       </c>
       <c r="N105" s="9">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="O105" s="8">
         <v>0</v>
@@ -8031,10 +8031,10 @@
         <v>0</v>
       </c>
       <c r="Q105" s="8">
-        <v>58506.26</v>
+        <v>62506.26</v>
       </c>
       <c r="R105" s="9">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="106" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -8057,28 +8057,28 @@
         <v>213000</v>
       </c>
       <c r="G106" s="12">
-        <v>168338</v>
+        <v>184738</v>
       </c>
       <c r="H106" s="13">
-        <v>79.03</v>
+        <v>86.73</v>
       </c>
       <c r="I106" s="12">
-        <v>20400</v>
+        <v>0</v>
       </c>
       <c r="J106" s="13">
-        <v>9.58</v>
+        <v>0</v>
       </c>
       <c r="K106" s="12">
-        <v>188738</v>
+        <v>184738</v>
       </c>
       <c r="L106" s="13">
-        <v>88.61</v>
+        <v>86.73</v>
       </c>
       <c r="M106" s="12">
-        <v>24262</v>
+        <v>28262</v>
       </c>
       <c r="N106" s="13">
-        <v>11.39</v>
+        <v>13.27</v>
       </c>
       <c r="O106" s="12">
         <v>0</v>
@@ -8087,10 +8087,10 @@
         <v>0</v>
       </c>
       <c r="Q106" s="12">
-        <v>24262</v>
+        <v>28262</v>
       </c>
       <c r="R106" s="13">
-        <v>11.39</v>
+        <v>13.27</v>
       </c>
     </row>
     <row r="107" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -8169,34 +8169,34 @@
         <v>10194186</v>
       </c>
       <c r="G108" s="8">
-        <v>3768775.64</v>
+        <v>5014823.4400000004</v>
       </c>
       <c r="H108" s="9">
-        <v>36.97</v>
+        <v>49.19</v>
       </c>
       <c r="I108" s="8">
-        <v>5328625.5999999996</v>
+        <v>4162577.8</v>
       </c>
       <c r="J108" s="9">
-        <v>52.27</v>
+        <v>40.83</v>
       </c>
       <c r="K108" s="8">
-        <v>9097401.2400000002</v>
+        <v>9177401.2400000002</v>
       </c>
       <c r="L108" s="9">
-        <v>89.24</v>
+        <v>90.03</v>
       </c>
       <c r="M108" s="8">
-        <v>1096784.76</v>
+        <v>1016784.76</v>
       </c>
       <c r="N108" s="9">
-        <v>10.76</v>
+        <v>9.9700000000000006</v>
       </c>
       <c r="O108" s="8">
-        <v>880844.76</v>
+        <v>800844.76</v>
       </c>
       <c r="P108" s="9">
-        <v>8.64</v>
+        <v>7.86</v>
       </c>
       <c r="Q108" s="8">
         <v>215940</v>
@@ -8225,16 +8225,16 @@
         <v>5612100</v>
       </c>
       <c r="G109" s="12">
-        <v>1628700.64</v>
+        <v>2744700.64</v>
       </c>
       <c r="H109" s="13">
-        <v>29.02</v>
+        <v>48.91</v>
       </c>
       <c r="I109" s="12">
-        <v>3049071.8</v>
+        <v>1933071.8</v>
       </c>
       <c r="J109" s="13">
-        <v>54.33</v>
+        <v>34.44</v>
       </c>
       <c r="K109" s="12">
         <v>4677772.4400000004</v>
@@ -8281,34 +8281,34 @@
         <v>4582086</v>
       </c>
       <c r="G110" s="12">
-        <v>2140075</v>
+        <v>2270122.7999999998</v>
       </c>
       <c r="H110" s="13">
-        <v>46.71</v>
+        <v>49.54</v>
       </c>
       <c r="I110" s="12">
-        <v>2279553.7999999998</v>
+        <v>2229506</v>
       </c>
       <c r="J110" s="13">
-        <v>49.75</v>
+        <v>48.66</v>
       </c>
       <c r="K110" s="12">
-        <v>4419628.8</v>
+        <v>4499628.8</v>
       </c>
       <c r="L110" s="13">
-        <v>96.45</v>
+        <v>98.2</v>
       </c>
       <c r="M110" s="12">
-        <v>162457.20000000001</v>
+        <v>82457.2</v>
       </c>
       <c r="N110" s="13">
-        <v>3.55</v>
+        <v>1.8</v>
       </c>
       <c r="O110" s="12">
-        <v>179900.2</v>
+        <v>99900.2</v>
       </c>
       <c r="P110" s="13">
-        <v>3.93</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="Q110" s="12">
         <v>-17443</v>
@@ -8337,28 +8337,28 @@
         <v>78027000</v>
       </c>
       <c r="G111" s="8">
-        <v>65136520.659999996</v>
+        <v>65204992.659999996</v>
       </c>
       <c r="H111" s="9">
-        <v>83.48</v>
+        <v>83.57</v>
       </c>
       <c r="I111" s="8">
-        <v>92647.73</v>
+        <v>65990.23</v>
       </c>
       <c r="J111" s="9">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="K111" s="8">
-        <v>65229168.390000001</v>
+        <v>65270982.890000001</v>
       </c>
       <c r="L111" s="9">
-        <v>83.6</v>
+        <v>83.65</v>
       </c>
       <c r="M111" s="8">
-        <v>12797831.609999999</v>
+        <v>12756017.109999999</v>
       </c>
       <c r="N111" s="9">
-        <v>16.399999999999999</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="O111" s="8">
         <v>1542.5</v>
@@ -8367,10 +8367,10 @@
         <v>0</v>
       </c>
       <c r="Q111" s="8">
-        <v>12796289.109999999</v>
+        <v>12754474.609999999</v>
       </c>
       <c r="R111" s="9">
-        <v>16.399999999999999</v>
+        <v>16.350000000000001</v>
       </c>
     </row>
     <row r="112" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -8393,16 +8393,16 @@
         <v>640000</v>
       </c>
       <c r="G112" s="12">
-        <v>240455</v>
+        <v>258912.5</v>
       </c>
       <c r="H112" s="13">
-        <v>37.57</v>
+        <v>40.46</v>
       </c>
       <c r="I112" s="12">
-        <v>23647.5</v>
+        <v>5190</v>
       </c>
       <c r="J112" s="13">
-        <v>3.69</v>
+        <v>0.81</v>
       </c>
       <c r="K112" s="12">
         <v>264102.5</v>
@@ -8449,28 +8449,28 @@
         <v>2387000</v>
       </c>
       <c r="G113" s="12">
-        <v>2682354.0699999998</v>
+        <v>2690254.07</v>
       </c>
       <c r="H113" s="13">
-        <v>112.37</v>
+        <v>112.7</v>
       </c>
       <c r="I113" s="12">
-        <v>69000.23</v>
+        <v>60800.23</v>
       </c>
       <c r="J113" s="13">
-        <v>2.89</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="K113" s="12">
-        <v>2751354.3</v>
+        <v>2751054.3</v>
       </c>
       <c r="L113" s="13">
-        <v>115.26</v>
+        <v>115.25</v>
       </c>
       <c r="M113" s="12">
-        <v>-364354.3</v>
+        <v>-364054.3</v>
       </c>
       <c r="N113" s="13">
-        <v>-15.26</v>
+        <v>-15.25</v>
       </c>
       <c r="O113" s="12">
         <v>0</v>
@@ -8479,10 +8479,10 @@
         <v>0</v>
       </c>
       <c r="Q113" s="12">
-        <v>-364354.3</v>
+        <v>-364054.3</v>
       </c>
       <c r="R113" s="13">
-        <v>-15.26</v>
+        <v>-15.25</v>
       </c>
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.25">
@@ -8505,10 +8505,10 @@
         <v>75000000</v>
       </c>
       <c r="G114" s="12">
-        <v>62213711.590000004</v>
+        <v>62255826.090000004</v>
       </c>
       <c r="H114" s="13">
-        <v>82.95</v>
+        <v>83.01</v>
       </c>
       <c r="I114" s="12">
         <v>0</v>
@@ -8517,16 +8517,16 @@
         <v>0</v>
       </c>
       <c r="K114" s="12">
-        <v>62213711.590000004</v>
+        <v>62255826.090000004</v>
       </c>
       <c r="L114" s="13">
-        <v>82.95</v>
+        <v>83.01</v>
       </c>
       <c r="M114" s="12">
-        <v>12786288.41</v>
+        <v>12744173.91</v>
       </c>
       <c r="N114" s="13">
-        <v>17.05</v>
+        <v>16.989999999999998</v>
       </c>
       <c r="O114" s="12">
         <v>0</v>
@@ -8535,10 +8535,10 @@
         <v>0</v>
       </c>
       <c r="Q114" s="12">
-        <v>12786288.41</v>
+        <v>12744173.91</v>
       </c>
       <c r="R114" s="13">
-        <v>17.05</v>
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="115" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -8727,40 +8727,40 @@
         <v>230702200</v>
       </c>
       <c r="G118" s="14">
-        <v>157197866.69</v>
+        <v>160641178.43000001</v>
       </c>
       <c r="H118" s="15">
-        <v>68.14</v>
+        <v>69.63</v>
       </c>
       <c r="I118" s="14">
-        <v>33065125.059999999</v>
+        <v>30238022.82</v>
       </c>
       <c r="J118" s="15">
-        <v>14.33</v>
+        <v>13.11</v>
       </c>
       <c r="K118" s="14">
-        <v>190262991.75</v>
+        <v>190879201.25</v>
       </c>
       <c r="L118" s="15">
-        <v>82.47</v>
+        <v>82.74</v>
       </c>
       <c r="M118" s="14">
-        <v>40439208.25</v>
+        <v>39822998.75</v>
       </c>
       <c r="N118" s="15">
-        <v>17.53</v>
+        <v>17.260000000000002</v>
       </c>
       <c r="O118" s="14">
-        <v>10656306.27</v>
+        <v>11542148.67</v>
       </c>
       <c r="P118" s="15">
-        <v>4.62</v>
+        <v>5</v>
       </c>
       <c r="Q118" s="14">
-        <v>29782901.98</v>
+        <v>28280850.079999998</v>
       </c>
       <c r="R118" s="15">
-        <v>12.91</v>
+        <v>12.26</v>
       </c>
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
@@ -8783,40 +8783,40 @@
         <v>101372727.95</v>
       </c>
       <c r="G119" s="4">
-        <v>29472433.390000001</v>
+        <v>30562243.989999998</v>
       </c>
       <c r="H119" s="5">
-        <v>29.07</v>
+        <v>30.15</v>
       </c>
       <c r="I119" s="4">
-        <v>17548472.68</v>
+        <v>16385336.68</v>
       </c>
       <c r="J119" s="5">
-        <v>17.309999999999999</v>
+        <v>16.16</v>
       </c>
       <c r="K119" s="4">
-        <v>47020906.07</v>
+        <v>46947580.670000002</v>
       </c>
       <c r="L119" s="5">
-        <v>46.38</v>
+        <v>46.31</v>
       </c>
       <c r="M119" s="4">
-        <v>54351821.880000003</v>
+        <v>54425147.280000001</v>
       </c>
       <c r="N119" s="5">
-        <v>53.62</v>
+        <v>53.69</v>
       </c>
       <c r="O119" s="4">
-        <v>4899593</v>
+        <v>4679593</v>
       </c>
       <c r="P119" s="5">
-        <v>4.83</v>
+        <v>4.62</v>
       </c>
       <c r="Q119" s="4">
-        <v>49452228.880000003</v>
+        <v>49745554.280000001</v>
       </c>
       <c r="R119" s="5">
-        <v>48.78</v>
+        <v>49.07</v>
       </c>
     </row>
     <row r="120" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -9791,28 +9791,28 @@
         <v>7840527.8099999996</v>
       </c>
       <c r="G137" s="8">
-        <v>5817758.5899999999</v>
+        <v>6012020.5899999999</v>
       </c>
       <c r="H137" s="9">
-        <v>74.2</v>
+        <v>76.680000000000007</v>
       </c>
       <c r="I137" s="8">
-        <v>973946.86</v>
+        <v>778724.86</v>
       </c>
       <c r="J137" s="9">
-        <v>12.42</v>
+        <v>9.93</v>
       </c>
       <c r="K137" s="8">
-        <v>6791705.4500000002</v>
+        <v>6790745.4500000002</v>
       </c>
       <c r="L137" s="9">
-        <v>86.62</v>
+        <v>86.61</v>
       </c>
       <c r="M137" s="8">
-        <v>1048822.3600000001</v>
+        <v>1049782.3600000001</v>
       </c>
       <c r="N137" s="9">
-        <v>13.38</v>
+        <v>13.39</v>
       </c>
       <c r="O137" s="8">
         <v>106945</v>
@@ -9821,10 +9821,10 @@
         <v>1.36</v>
       </c>
       <c r="Q137" s="8">
-        <v>941877.36</v>
+        <v>942837.36</v>
       </c>
       <c r="R137" s="9">
-        <v>12.01</v>
+        <v>12.03</v>
       </c>
     </row>
     <row r="138" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -9847,16 +9847,16 @@
         <v>2672753.2999999998</v>
       </c>
       <c r="G138" s="12">
-        <v>2713180.4</v>
+        <v>2867567.4</v>
       </c>
       <c r="H138" s="13">
-        <v>101.51</v>
+        <v>107.29</v>
       </c>
       <c r="I138" s="12">
-        <v>342429.7</v>
+        <v>188042.7</v>
       </c>
       <c r="J138" s="13">
-        <v>12.81</v>
+        <v>7.04</v>
       </c>
       <c r="K138" s="12">
         <v>3055610.1</v>
@@ -10021,22 +10021,22 @@
         <v>116.59</v>
       </c>
       <c r="I141" s="12">
-        <v>125160</v>
+        <v>124200</v>
       </c>
       <c r="J141" s="13">
-        <v>21.34</v>
+        <v>21.17</v>
       </c>
       <c r="K141" s="12">
-        <v>809045.35</v>
+        <v>808085.35</v>
       </c>
       <c r="L141" s="13">
-        <v>137.93</v>
+        <v>137.77000000000001</v>
       </c>
       <c r="M141" s="12">
-        <v>-222495.35</v>
+        <v>-221535.35</v>
       </c>
       <c r="N141" s="13">
-        <v>-37.93</v>
+        <v>-37.770000000000003</v>
       </c>
       <c r="O141" s="12">
         <v>50000</v>
@@ -10045,10 +10045,10 @@
         <v>8.52</v>
       </c>
       <c r="Q141" s="12">
-        <v>-272495.34999999998</v>
+        <v>-271535.34999999998</v>
       </c>
       <c r="R141" s="13">
-        <v>-46.46</v>
+        <v>-46.29</v>
       </c>
     </row>
     <row r="142" spans="1:18" x14ac:dyDescent="0.25">
@@ -10071,16 +10071,16 @@
         <v>2143206</v>
       </c>
       <c r="G142" s="12">
-        <v>1084812.8400000001</v>
+        <v>1124687.8400000001</v>
       </c>
       <c r="H142" s="13">
-        <v>50.62</v>
+        <v>52.48</v>
       </c>
       <c r="I142" s="12">
-        <v>206357.16</v>
+        <v>166482.16</v>
       </c>
       <c r="J142" s="13">
-        <v>9.6300000000000008</v>
+        <v>7.77</v>
       </c>
       <c r="K142" s="12">
         <v>1291170</v>
@@ -10133,19 +10133,19 @@
         <v>45.56</v>
       </c>
       <c r="I143" s="8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J143" s="9">
         <v>0</v>
       </c>
       <c r="K143" s="8">
-        <v>371735.05</v>
+        <v>371725.05</v>
       </c>
       <c r="L143" s="9">
         <v>45.56</v>
       </c>
       <c r="M143" s="8">
-        <v>444135.88</v>
+        <v>444145.88</v>
       </c>
       <c r="N143" s="9">
         <v>54.44</v>
@@ -10157,7 +10157,7 @@
         <v>0</v>
       </c>
       <c r="Q143" s="8">
-        <v>444135.88</v>
+        <v>444145.88</v>
       </c>
       <c r="R143" s="9">
         <v>54.44</v>
@@ -10581,22 +10581,22 @@
         <v>96.44</v>
       </c>
       <c r="I151" s="12">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J151" s="13">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="K151" s="12">
-        <v>10265</v>
+        <v>10255</v>
       </c>
       <c r="L151" s="13">
-        <v>96.53</v>
+        <v>96.44</v>
       </c>
       <c r="M151" s="12">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="N151" s="13">
-        <v>3.47</v>
+        <v>3.56</v>
       </c>
       <c r="O151" s="12">
         <v>0</v>
@@ -10605,10 +10605,10 @@
         <v>0</v>
       </c>
       <c r="Q151" s="12">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="R151" s="13">
-        <v>3.47</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="152" spans="1:18" x14ac:dyDescent="0.25">
@@ -10917,22 +10917,22 @@
         <v>57.8</v>
       </c>
       <c r="I157" s="8">
-        <v>80885</v>
+        <v>80500</v>
       </c>
       <c r="J157" s="9">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="K157" s="8">
-        <v>1778154.18</v>
+        <v>1777769.18</v>
       </c>
       <c r="L157" s="9">
-        <v>60.55</v>
+        <v>60.54</v>
       </c>
       <c r="M157" s="8">
-        <v>1158349.6000000001</v>
+        <v>1158734.6000000001</v>
       </c>
       <c r="N157" s="9">
-        <v>39.450000000000003</v>
+        <v>39.46</v>
       </c>
       <c r="O157" s="8">
         <v>0</v>
@@ -10941,10 +10941,10 @@
         <v>0</v>
       </c>
       <c r="Q157" s="8">
-        <v>1158349.6000000001</v>
+        <v>1158734.6000000001</v>
       </c>
       <c r="R157" s="9">
-        <v>39.450000000000003</v>
+        <v>39.46</v>
       </c>
     </row>
     <row r="158" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -11085,22 +11085,22 @@
         <v>48.69</v>
       </c>
       <c r="I160" s="12">
-        <v>80885</v>
+        <v>80500</v>
       </c>
       <c r="J160" s="13">
-        <v>22.87</v>
+        <v>22.76</v>
       </c>
       <c r="K160" s="12">
-        <v>253108.33</v>
+        <v>252723.33</v>
       </c>
       <c r="L160" s="13">
-        <v>71.56</v>
+        <v>71.45</v>
       </c>
       <c r="M160" s="12">
-        <v>100616.67</v>
+        <v>101001.67</v>
       </c>
       <c r="N160" s="13">
-        <v>28.44</v>
+        <v>28.55</v>
       </c>
       <c r="O160" s="12">
         <v>0</v>
@@ -11109,10 +11109,10 @@
         <v>0</v>
       </c>
       <c r="Q160" s="12">
-        <v>100616.67</v>
+        <v>101001.67</v>
       </c>
       <c r="R160" s="13">
-        <v>28.44</v>
+        <v>28.55</v>
       </c>
     </row>
     <row r="161" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -11639,28 +11639,28 @@
         <v>8926239.0199999996</v>
       </c>
       <c r="G170" s="8">
-        <v>2060571.78</v>
+        <v>2165382.08</v>
       </c>
       <c r="H170" s="9">
-        <v>23.08</v>
+        <v>24.26</v>
       </c>
       <c r="I170" s="8">
-        <v>4551805</v>
+        <v>4417881</v>
       </c>
       <c r="J170" s="9">
-        <v>50.99</v>
+        <v>49.49</v>
       </c>
       <c r="K170" s="8">
-        <v>6612376.7800000003</v>
+        <v>6583263.0800000001</v>
       </c>
       <c r="L170" s="9">
-        <v>74.08</v>
+        <v>73.75</v>
       </c>
       <c r="M170" s="8">
-        <v>2313862.2400000002</v>
+        <v>2342975.94</v>
       </c>
       <c r="N170" s="9">
-        <v>25.92</v>
+        <v>26.25</v>
       </c>
       <c r="O170" s="8">
         <v>15000</v>
@@ -11669,10 +11669,10 @@
         <v>0.17</v>
       </c>
       <c r="Q170" s="8">
-        <v>2298862.2400000002</v>
+        <v>2327975.94</v>
       </c>
       <c r="R170" s="9">
-        <v>25.75</v>
+        <v>26.08</v>
       </c>
     </row>
     <row r="171" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -12199,28 +12199,28 @@
         <v>849000</v>
       </c>
       <c r="G180" s="12">
-        <v>271926</v>
+        <v>347136.3</v>
       </c>
       <c r="H180" s="13">
-        <v>32.03</v>
+        <v>40.89</v>
       </c>
       <c r="I180" s="12">
-        <v>904960</v>
+        <v>800636</v>
       </c>
       <c r="J180" s="13">
-        <v>106.59</v>
+        <v>94.3</v>
       </c>
       <c r="K180" s="12">
-        <v>1176886</v>
+        <v>1147772.3</v>
       </c>
       <c r="L180" s="13">
-        <v>138.62</v>
+        <v>135.19</v>
       </c>
       <c r="M180" s="12">
-        <v>-327886</v>
+        <v>-298772.3</v>
       </c>
       <c r="N180" s="13">
-        <v>-38.619999999999997</v>
+        <v>-35.19</v>
       </c>
       <c r="O180" s="12">
         <v>0</v>
@@ -12229,10 +12229,10 @@
         <v>0</v>
       </c>
       <c r="Q180" s="12">
-        <v>-327886</v>
+        <v>-298772.3</v>
       </c>
       <c r="R180" s="13">
-        <v>-38.619999999999997</v>
+        <v>-35.19</v>
       </c>
     </row>
     <row r="181" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -12311,16 +12311,16 @@
         <v>1410000</v>
       </c>
       <c r="G182" s="12">
-        <v>80447.7</v>
+        <v>110047.7</v>
       </c>
       <c r="H182" s="13">
-        <v>5.71</v>
+        <v>7.8</v>
       </c>
       <c r="I182" s="12">
-        <v>34845</v>
+        <v>5245</v>
       </c>
       <c r="J182" s="13">
-        <v>2.4700000000000002</v>
+        <v>0.37</v>
       </c>
       <c r="K182" s="12">
         <v>115292.7</v>
@@ -13287,16 +13287,16 @@
         <v>42.14</v>
       </c>
       <c r="O199" s="8">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="P199" s="9">
-        <v>59.63</v>
+        <v>0</v>
       </c>
       <c r="Q199" s="8">
-        <v>-73323.8</v>
+        <v>176676.2</v>
       </c>
       <c r="R199" s="9">
-        <v>-17.489999999999998</v>
+        <v>42.14</v>
       </c>
     </row>
     <row r="200" spans="1:18" x14ac:dyDescent="0.25">
@@ -13399,16 +13399,16 @@
         <v>24.02</v>
       </c>
       <c r="O201" s="12">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="P201" s="13">
-        <v>78.31</v>
+        <v>0</v>
       </c>
       <c r="Q201" s="12">
-        <v>-173323.8</v>
+        <v>76676.2</v>
       </c>
       <c r="R201" s="13">
-        <v>-54.29</v>
+        <v>24.02</v>
       </c>
     </row>
     <row r="202" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -13487,25 +13487,25 @@
         <v>12829676.84</v>
       </c>
       <c r="G203" s="8">
-        <v>2983932.91</v>
+        <v>3028932.91</v>
       </c>
       <c r="H203" s="9">
-        <v>23.26</v>
+        <v>23.61</v>
       </c>
       <c r="I203" s="8">
-        <v>1021641.56</v>
+        <v>976431.56</v>
       </c>
       <c r="J203" s="9">
-        <v>7.96</v>
+        <v>7.61</v>
       </c>
       <c r="K203" s="8">
-        <v>4005574.47</v>
+        <v>4005364.47</v>
       </c>
       <c r="L203" s="9">
         <v>31.22</v>
       </c>
       <c r="M203" s="8">
-        <v>8824102.3699999992</v>
+        <v>8824312.3699999992</v>
       </c>
       <c r="N203" s="9">
         <v>68.78</v>
@@ -13517,7 +13517,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="Q203" s="8">
-        <v>8815102.3699999992</v>
+        <v>8815312.3699999992</v>
       </c>
       <c r="R203" s="9">
         <v>68.709999999999994</v>
@@ -13543,16 +13543,16 @@
         <v>1681566.8</v>
       </c>
       <c r="G204" s="12">
-        <v>435085</v>
+        <v>480085</v>
       </c>
       <c r="H204" s="13">
-        <v>25.87</v>
+        <v>28.55</v>
       </c>
       <c r="I204" s="12">
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="J204" s="13">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="K204" s="12">
         <v>480085</v>
@@ -13605,22 +13605,22 @@
         <v>16.47</v>
       </c>
       <c r="I205" s="12">
-        <v>840</v>
+        <v>630</v>
       </c>
       <c r="J205" s="13">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="K205" s="12">
-        <v>83195.100000000006</v>
+        <v>82985.100000000006</v>
       </c>
       <c r="L205" s="13">
-        <v>16.64</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="M205" s="12">
-        <v>416804.9</v>
+        <v>417014.9</v>
       </c>
       <c r="N205" s="13">
-        <v>83.36</v>
+        <v>83.4</v>
       </c>
       <c r="O205" s="12">
         <v>0</v>
@@ -13629,10 +13629,10 @@
         <v>0</v>
       </c>
       <c r="Q205" s="12">
-        <v>416804.9</v>
+        <v>417014.9</v>
       </c>
       <c r="R205" s="13">
-        <v>83.36</v>
+        <v>83.4</v>
       </c>
     </row>
     <row r="206" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -14183,16 +14183,16 @@
         <v>68.87</v>
       </c>
       <c r="O215" s="8">
-        <v>3295000</v>
+        <v>3325000</v>
       </c>
       <c r="P215" s="9">
-        <v>17.71</v>
+        <v>17.87</v>
       </c>
       <c r="Q215" s="8">
-        <v>9518169.3900000006</v>
+        <v>9488169.3900000006</v>
       </c>
       <c r="R215" s="9">
-        <v>51.16</v>
+        <v>51</v>
       </c>
     </row>
     <row r="216" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -15191,16 +15191,16 @@
         <v>68.2</v>
       </c>
       <c r="O233" s="12">
-        <v>95000</v>
+        <v>125000</v>
       </c>
       <c r="P233" s="13">
-        <v>24.47</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="Q233" s="12">
-        <v>169763.62</v>
+        <v>139763.62</v>
       </c>
       <c r="R233" s="13">
-        <v>43.73</v>
+        <v>36</v>
       </c>
     </row>
     <row r="234" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -15559,28 +15559,28 @@
         <v>1995235</v>
       </c>
       <c r="G240" s="8">
-        <v>1974622</v>
+        <v>1976130.3</v>
       </c>
       <c r="H240" s="9">
-        <v>98.97</v>
+        <v>99.04</v>
       </c>
       <c r="I240" s="8">
-        <v>181870</v>
+        <v>485</v>
       </c>
       <c r="J240" s="9">
-        <v>9.1199999999999992</v>
+        <v>0.02</v>
       </c>
       <c r="K240" s="8">
-        <v>2156492</v>
+        <v>1976615.3</v>
       </c>
       <c r="L240" s="9">
-        <v>108.08</v>
+        <v>99.07</v>
       </c>
       <c r="M240" s="8">
-        <v>-161257</v>
+        <v>18619.7</v>
       </c>
       <c r="N240" s="9">
-        <v>-8.08</v>
+        <v>0.93</v>
       </c>
       <c r="O240" s="8">
         <v>0</v>
@@ -15589,10 +15589,10 @@
         <v>0</v>
       </c>
       <c r="Q240" s="8">
-        <v>-161257</v>
+        <v>18619.7</v>
       </c>
       <c r="R240" s="9">
-        <v>-8.08</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="241" spans="1:18" x14ac:dyDescent="0.25">
@@ -15727,10 +15727,10 @@
         <v>214550</v>
       </c>
       <c r="G243" s="12">
-        <v>41080</v>
+        <v>42588.3</v>
       </c>
       <c r="H243" s="13">
-        <v>19.149999999999999</v>
+        <v>19.850000000000001</v>
       </c>
       <c r="I243" s="12">
         <v>0</v>
@@ -15739,16 +15739,16 @@
         <v>0</v>
       </c>
       <c r="K243" s="12">
-        <v>41080</v>
+        <v>42588.3</v>
       </c>
       <c r="L243" s="13">
-        <v>19.149999999999999</v>
+        <v>19.850000000000001</v>
       </c>
       <c r="M243" s="12">
-        <v>173470</v>
+        <v>171961.7</v>
       </c>
       <c r="N243" s="13">
-        <v>80.849999999999994</v>
+        <v>80.150000000000006</v>
       </c>
       <c r="O243" s="12">
         <v>0</v>
@@ -15757,10 +15757,10 @@
         <v>0</v>
       </c>
       <c r="Q243" s="12">
-        <v>173470</v>
+        <v>171961.7</v>
       </c>
       <c r="R243" s="13">
-        <v>80.849999999999994</v>
+        <v>80.150000000000006</v>
       </c>
     </row>
     <row r="244" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -15957,22 +15957,22 @@
         <v>100</v>
       </c>
       <c r="I247" s="12">
+        <v>0</v>
+      </c>
+      <c r="J247" s="13">
+        <v>0</v>
+      </c>
+      <c r="K247" s="12">
         <v>181385</v>
       </c>
-      <c r="J247" s="13">
+      <c r="L247" s="13">
         <v>100</v>
       </c>
-      <c r="K247" s="12">
-        <v>362770</v>
-      </c>
-      <c r="L247" s="13">
-        <v>200</v>
-      </c>
       <c r="M247" s="12">
-        <v>-181385</v>
+        <v>0</v>
       </c>
       <c r="N247" s="13">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O247" s="12">
         <v>0</v>
@@ -15981,10 +15981,10 @@
         <v>0</v>
       </c>
       <c r="Q247" s="12">
-        <v>-181385</v>
+        <v>0</v>
       </c>
       <c r="R247" s="13">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -16119,28 +16119,28 @@
         <v>2528000</v>
       </c>
       <c r="G250" s="8">
-        <v>952739.83999999997</v>
+        <v>991389.84</v>
       </c>
       <c r="H250" s="9">
-        <v>37.69</v>
+        <v>39.22</v>
       </c>
       <c r="I250" s="8">
-        <v>625610</v>
+        <v>295610</v>
       </c>
       <c r="J250" s="9">
-        <v>24.75</v>
+        <v>11.69</v>
       </c>
       <c r="K250" s="8">
-        <v>1578349.84</v>
+        <v>1286999.8400000001</v>
       </c>
       <c r="L250" s="9">
-        <v>62.43</v>
+        <v>50.91</v>
       </c>
       <c r="M250" s="8">
-        <v>949650.16</v>
+        <v>1241000.1599999999</v>
       </c>
       <c r="N250" s="9">
-        <v>37.57</v>
+        <v>49.09</v>
       </c>
       <c r="O250" s="8">
         <v>20000</v>
@@ -16149,10 +16149,10 @@
         <v>0.79</v>
       </c>
       <c r="Q250" s="8">
-        <v>929650.16</v>
+        <v>1221000.1599999999</v>
       </c>
       <c r="R250" s="9">
-        <v>36.770000000000003</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="251" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -16175,28 +16175,28 @@
         <v>792000</v>
       </c>
       <c r="G251" s="12">
-        <v>359185</v>
+        <v>397835</v>
       </c>
       <c r="H251" s="13">
-        <v>45.35</v>
+        <v>50.23</v>
       </c>
       <c r="I251" s="12">
-        <v>252000</v>
+        <v>69500</v>
       </c>
       <c r="J251" s="13">
-        <v>31.82</v>
+        <v>8.7799999999999994</v>
       </c>
       <c r="K251" s="12">
-        <v>611185</v>
+        <v>467335</v>
       </c>
       <c r="L251" s="13">
-        <v>77.17</v>
+        <v>59.01</v>
       </c>
       <c r="M251" s="12">
-        <v>180815</v>
+        <v>324665</v>
       </c>
       <c r="N251" s="13">
-        <v>22.83</v>
+        <v>40.99</v>
       </c>
       <c r="O251" s="12">
         <v>20000</v>
@@ -16205,10 +16205,10 @@
         <v>2.5299999999999998</v>
       </c>
       <c r="Q251" s="12">
-        <v>160815</v>
+        <v>304665</v>
       </c>
       <c r="R251" s="13">
-        <v>20.3</v>
+        <v>38.47</v>
       </c>
     </row>
     <row r="252" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -16237,22 +16237,22 @@
         <v>31.89</v>
       </c>
       <c r="I252" s="12">
-        <v>195000</v>
+        <v>45000</v>
       </c>
       <c r="J252" s="13">
-        <v>20.66</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="K252" s="12">
-        <v>496027.24</v>
+        <v>346027.24</v>
       </c>
       <c r="L252" s="13">
-        <v>52.55</v>
+        <v>36.659999999999997</v>
       </c>
       <c r="M252" s="12">
-        <v>447972.76</v>
+        <v>597972.76</v>
       </c>
       <c r="N252" s="13">
-        <v>47.45</v>
+        <v>63.34</v>
       </c>
       <c r="O252" s="12">
         <v>0</v>
@@ -16261,10 +16261,10 @@
         <v>0</v>
       </c>
       <c r="Q252" s="12">
-        <v>447972.76</v>
+        <v>597972.76</v>
       </c>
       <c r="R252" s="13">
-        <v>47.45</v>
+        <v>63.34</v>
       </c>
     </row>
     <row r="253" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
@@ -16293,22 +16293,22 @@
         <v>36.94</v>
       </c>
       <c r="I253" s="12">
-        <v>178610</v>
+        <v>181110</v>
       </c>
       <c r="J253" s="13">
-        <v>22.55</v>
+        <v>22.87</v>
       </c>
       <c r="K253" s="12">
-        <v>471137.6</v>
+        <v>473637.6</v>
       </c>
       <c r="L253" s="13">
-        <v>59.49</v>
+        <v>59.8</v>
       </c>
       <c r="M253" s="12">
-        <v>320862.40000000002</v>
+        <v>318362.40000000002</v>
       </c>
       <c r="N253" s="13">
-        <v>40.51</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="O253" s="12">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Q253" s="12">
-        <v>320862.40000000002</v>
+        <v>318362.40000000002</v>
       </c>
       <c r="R253" s="13">
-        <v>40.51</v>
+        <v>40.200000000000003</v>
       </c>
     </row>
     <row r="254" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -16343,28 +16343,28 @@
         <v>12554100</v>
       </c>
       <c r="G254" s="8">
-        <v>3619010.44</v>
+        <v>3723690.44</v>
       </c>
       <c r="H254" s="9">
-        <v>28.83</v>
+        <v>29.66</v>
       </c>
       <c r="I254" s="8">
-        <v>968903.56</v>
+        <v>1075273.56</v>
       </c>
       <c r="J254" s="9">
-        <v>7.72</v>
+        <v>8.57</v>
       </c>
       <c r="K254" s="8">
-        <v>4587914</v>
+        <v>4798964</v>
       </c>
       <c r="L254" s="9">
-        <v>36.549999999999997</v>
+        <v>38.229999999999997</v>
       </c>
       <c r="M254" s="8">
-        <v>7966186</v>
+        <v>7755136</v>
       </c>
       <c r="N254" s="9">
-        <v>63.45</v>
+        <v>61.77</v>
       </c>
       <c r="O254" s="8">
         <v>715148</v>
@@ -16373,10 +16373,10 @@
         <v>5.7</v>
       </c>
       <c r="Q254" s="8">
-        <v>7251038</v>
+        <v>7039988</v>
       </c>
       <c r="R254" s="9">
-        <v>57.76</v>
+        <v>56.08</v>
       </c>
     </row>
     <row r="255" spans="1:18" ht="132" x14ac:dyDescent="0.25">
@@ -16455,28 +16455,28 @@
         <v>4556000</v>
       </c>
       <c r="G256" s="12">
-        <v>1824763</v>
+        <v>1929443</v>
       </c>
       <c r="H256" s="13">
-        <v>40.049999999999997</v>
+        <v>42.35</v>
       </c>
       <c r="I256" s="12">
-        <v>515300</v>
+        <v>621670</v>
       </c>
       <c r="J256" s="13">
-        <v>11.31</v>
+        <v>13.65</v>
       </c>
       <c r="K256" s="12">
-        <v>2340063</v>
+        <v>2551113</v>
       </c>
       <c r="L256" s="13">
-        <v>51.36</v>
+        <v>55.99</v>
       </c>
       <c r="M256" s="12">
-        <v>2215937</v>
+        <v>2004887</v>
       </c>
       <c r="N256" s="13">
-        <v>48.64</v>
+        <v>44.01</v>
       </c>
       <c r="O256" s="12">
         <v>211000</v>
@@ -16485,10 +16485,10 @@
         <v>4.63</v>
       </c>
       <c r="Q256" s="12">
-        <v>2004937</v>
+        <v>1793887</v>
       </c>
       <c r="R256" s="13">
-        <v>44.01</v>
+        <v>39.369999999999997</v>
       </c>
     </row>
     <row r="257" spans="1:18" x14ac:dyDescent="0.25">
@@ -16629,22 +16629,22 @@
         <v>0</v>
       </c>
       <c r="I259" s="8">
-        <v>0</v>
+        <v>225000</v>
       </c>
       <c r="J259" s="9">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K259" s="8">
-        <v>0</v>
+        <v>225000</v>
       </c>
       <c r="L259" s="9">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M259" s="8">
-        <v>1500000</v>
+        <v>1275000</v>
       </c>
       <c r="N259" s="9">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="O259" s="8">
         <v>0</v>
@@ -16653,10 +16653,10 @@
         <v>0</v>
       </c>
       <c r="Q259" s="8">
-        <v>1500000</v>
+        <v>1275000</v>
       </c>
       <c r="R259" s="9">
-        <v>100</v>
+        <v>85</v>
       </c>
     </row>
     <row r="260" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -16909,22 +16909,22 @@
         <v>0</v>
       </c>
       <c r="I264" s="12">
-        <v>0</v>
+        <v>225000</v>
       </c>
       <c r="J264" s="13">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K264" s="12">
-        <v>0</v>
+        <v>225000</v>
       </c>
       <c r="L264" s="13">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M264" s="12">
-        <v>450000</v>
+        <v>225000</v>
       </c>
       <c r="N264" s="13">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O264" s="12">
         <v>0</v>
@@ -16933,10 +16933,10 @@
         <v>0</v>
       </c>
       <c r="Q264" s="12">
-        <v>450000</v>
+        <v>225000</v>
       </c>
       <c r="R264" s="13">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="265" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -17071,28 +17071,28 @@
         <v>19811100</v>
       </c>
       <c r="G267" s="8">
-        <v>3109811.97</v>
+        <v>3710261.97</v>
       </c>
       <c r="H267" s="9">
-        <v>15.7</v>
+        <v>18.73</v>
       </c>
       <c r="I267" s="8">
-        <v>4523658.03</v>
+        <v>3915288.03</v>
       </c>
       <c r="J267" s="9">
-        <v>22.83</v>
+        <v>19.760000000000002</v>
       </c>
       <c r="K267" s="8">
-        <v>7633470</v>
+        <v>7625550</v>
       </c>
       <c r="L267" s="9">
-        <v>38.53</v>
+        <v>38.49</v>
       </c>
       <c r="M267" s="8">
-        <v>12177630</v>
+        <v>12185550</v>
       </c>
       <c r="N267" s="9">
-        <v>61.47</v>
+        <v>61.51</v>
       </c>
       <c r="O267" s="8">
         <v>0</v>
@@ -17101,10 +17101,10 @@
         <v>0</v>
       </c>
       <c r="Q267" s="8">
-        <v>12177630</v>
+        <v>12185550</v>
       </c>
       <c r="R267" s="9">
-        <v>61.47</v>
+        <v>61.51</v>
       </c>
     </row>
     <row r="268" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -17183,16 +17183,16 @@
         <v>10400000</v>
       </c>
       <c r="G269" s="12">
-        <v>3000000</v>
+        <v>3600000</v>
       </c>
       <c r="H269" s="13">
-        <v>28.85</v>
+        <v>34.619999999999997</v>
       </c>
       <c r="I269" s="12">
-        <v>4200000</v>
+        <v>3600000</v>
       </c>
       <c r="J269" s="13">
-        <v>40.380000000000003</v>
+        <v>34.619999999999997</v>
       </c>
       <c r="K269" s="12">
         <v>7200000</v>
@@ -17357,22 +17357,22 @@
         <v>1.06</v>
       </c>
       <c r="I272" s="12">
-        <v>8370</v>
+        <v>0</v>
       </c>
       <c r="J272" s="13">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="K272" s="12">
-        <v>20920</v>
+        <v>12550</v>
       </c>
       <c r="L272" s="13">
-        <v>1.77</v>
+        <v>1.06</v>
       </c>
       <c r="M272" s="12">
-        <v>1162080</v>
+        <v>1170450</v>
       </c>
       <c r="N272" s="13">
-        <v>98.23</v>
+        <v>98.94</v>
       </c>
       <c r="O272" s="12">
         <v>0</v>
@@ -17381,10 +17381,10 @@
         <v>0</v>
       </c>
       <c r="Q272" s="12">
-        <v>1162080</v>
+        <v>1170450</v>
       </c>
       <c r="R272" s="13">
-        <v>98.23</v>
+        <v>98.94</v>
       </c>
     </row>
     <row r="273" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -17463,10 +17463,10 @@
         <v>406250</v>
       </c>
       <c r="G274" s="12">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="H274" s="13">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="I274" s="12">
         <v>300</v>
@@ -17475,16 +17475,16 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="K274" s="12">
-        <v>300</v>
+        <v>750</v>
       </c>
       <c r="L274" s="13">
-        <v>7.0000000000000007E-2</v>
+        <v>0.18</v>
       </c>
       <c r="M274" s="12">
-        <v>405950</v>
+        <v>405500</v>
       </c>
       <c r="N274" s="13">
-        <v>99.93</v>
+        <v>99.82</v>
       </c>
       <c r="O274" s="12">
         <v>0</v>
@@ -17493,10 +17493,10 @@
         <v>0</v>
       </c>
       <c r="Q274" s="12">
-        <v>405950</v>
+        <v>405500</v>
       </c>
       <c r="R274" s="13">
-        <v>99.93</v>
+        <v>99.82</v>
       </c>
     </row>
     <row r="275" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -17575,10 +17575,10 @@
         <v>2208125</v>
       </c>
       <c r="G276" s="8">
-        <v>26325</v>
+        <v>26775</v>
       </c>
       <c r="H276" s="9">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="I276" s="8">
         <v>1249500</v>
@@ -17587,16 +17587,16 @@
         <v>56.59</v>
       </c>
       <c r="K276" s="8">
-        <v>1275825</v>
+        <v>1276275</v>
       </c>
       <c r="L276" s="9">
-        <v>57.78</v>
+        <v>57.8</v>
       </c>
       <c r="M276" s="8">
-        <v>932300</v>
+        <v>931850</v>
       </c>
       <c r="N276" s="9">
-        <v>42.22</v>
+        <v>42.2</v>
       </c>
       <c r="O276" s="8">
         <v>360000</v>
@@ -17605,10 +17605,10 @@
         <v>16.3</v>
       </c>
       <c r="Q276" s="8">
-        <v>572300</v>
+        <v>571850</v>
       </c>
       <c r="R276" s="9">
-        <v>25.92</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="277" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -17743,10 +17743,10 @@
         <v>180375</v>
       </c>
       <c r="G279" s="12">
-        <v>26325</v>
+        <v>26775</v>
       </c>
       <c r="H279" s="13">
-        <v>14.59</v>
+        <v>14.84</v>
       </c>
       <c r="I279" s="12">
         <v>52200</v>
@@ -17755,16 +17755,16 @@
         <v>28.94</v>
       </c>
       <c r="K279" s="12">
-        <v>78525</v>
+        <v>78975</v>
       </c>
       <c r="L279" s="13">
-        <v>43.53</v>
+        <v>43.78</v>
       </c>
       <c r="M279" s="12">
-        <v>101850</v>
+        <v>101400</v>
       </c>
       <c r="N279" s="13">
-        <v>56.47</v>
+        <v>56.22</v>
       </c>
       <c r="O279" s="12">
         <v>0</v>
@@ -17773,10 +17773,10 @@
         <v>0</v>
       </c>
       <c r="Q279" s="12">
-        <v>101850</v>
+        <v>101400</v>
       </c>
       <c r="R279" s="13">
-        <v>56.47</v>
+        <v>56.22</v>
       </c>
     </row>
     <row r="280" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -18133,40 +18133,40 @@
         <v>101372727.95</v>
       </c>
       <c r="G286" s="14">
-        <v>29472433.390000001</v>
+        <v>30562243.989999998</v>
       </c>
       <c r="H286" s="15">
-        <v>29.07</v>
+        <v>30.15</v>
       </c>
       <c r="I286" s="14">
-        <v>17548472.68</v>
+        <v>16385336.68</v>
       </c>
       <c r="J286" s="15">
-        <v>17.309999999999999</v>
+        <v>16.16</v>
       </c>
       <c r="K286" s="14">
-        <v>47020906.07</v>
+        <v>46947580.670000002</v>
       </c>
       <c r="L286" s="15">
-        <v>46.38</v>
+        <v>46.31</v>
       </c>
       <c r="M286" s="14">
-        <v>54351821.880000003</v>
+        <v>54425147.280000001</v>
       </c>
       <c r="N286" s="15">
-        <v>53.62</v>
+        <v>53.69</v>
       </c>
       <c r="O286" s="14">
-        <v>4899593</v>
+        <v>4679593</v>
       </c>
       <c r="P286" s="15">
-        <v>4.83</v>
+        <v>4.62</v>
       </c>
       <c r="Q286" s="14">
-        <v>49452228.880000003</v>
+        <v>49745554.280000001</v>
       </c>
       <c r="R286" s="15">
-        <v>48.78</v>
+        <v>49.07</v>
       </c>
     </row>
     <row r="287" spans="1:18" x14ac:dyDescent="0.25">
@@ -18187,40 +18187,40 @@
         <v>332074927.94999999</v>
       </c>
       <c r="G287" s="16">
-        <v>186670300.08000001</v>
+        <v>191203422.41999999</v>
       </c>
       <c r="H287" s="17">
-        <v>56.21</v>
+        <v>57.58</v>
       </c>
       <c r="I287" s="16">
-        <v>50613597.740000002</v>
+        <v>46623359.5</v>
       </c>
       <c r="J287" s="17">
-        <v>15.24</v>
+        <v>14.04</v>
       </c>
       <c r="K287" s="16">
-        <v>237283897.81999999</v>
+        <v>237826781.91999999</v>
       </c>
       <c r="L287" s="17">
-        <v>71.45</v>
+        <v>71.62</v>
       </c>
       <c r="M287" s="16">
-        <v>94791030.129999995</v>
+        <v>94248146.030000001</v>
       </c>
       <c r="N287" s="17">
-        <v>28.55</v>
+        <v>28.38</v>
       </c>
       <c r="O287" s="16">
-        <v>15555899.27</v>
+        <v>16221741.67</v>
       </c>
       <c r="P287" s="17">
-        <v>4.68</v>
+        <v>4.88</v>
       </c>
       <c r="Q287" s="16">
-        <v>79235130.859999999</v>
+        <v>78026404.359999999</v>
       </c>
       <c r="R287" s="17">
-        <v>23.86</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="288" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -18463,40 +18463,40 @@
         <v>338730508.13</v>
       </c>
       <c r="G292" s="16">
-        <v>186670300.08000001</v>
+        <v>191203422.41999999</v>
       </c>
       <c r="H292" s="17">
-        <v>55.11</v>
+        <v>56.45</v>
       </c>
       <c r="I292" s="16">
-        <v>50613597.740000002</v>
+        <v>46623359.5</v>
       </c>
       <c r="J292" s="17">
-        <v>14.94</v>
+        <v>13.76</v>
       </c>
       <c r="K292" s="16">
-        <v>237283897.81999999</v>
+        <v>237826781.91999999</v>
       </c>
       <c r="L292" s="17">
-        <v>70.05</v>
+        <v>70.209999999999994</v>
       </c>
       <c r="M292" s="16">
-        <v>101446610.31</v>
+        <v>100903726.20999999</v>
       </c>
       <c r="N292" s="17">
-        <v>29.95</v>
+        <v>29.79</v>
       </c>
       <c r="O292" s="16">
-        <v>15555899.27</v>
+        <v>16221741.67</v>
       </c>
       <c r="P292" s="17">
-        <v>4.59</v>
+        <v>4.79</v>
       </c>
       <c r="Q292" s="16">
-        <v>85890711.040000007</v>
+        <v>84681984.540000007</v>
       </c>
       <c r="R292" s="17">
-        <v>25.36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="293" spans="1:18" x14ac:dyDescent="0.25">
@@ -18519,28 +18519,28 @@
         <v>3963369.24</v>
       </c>
       <c r="G293" s="4">
-        <v>558139.18000000005</v>
+        <v>607139.18000000005</v>
       </c>
       <c r="H293" s="5">
-        <v>14.08</v>
+        <v>15.32</v>
       </c>
       <c r="I293" s="4">
-        <v>156393.70000000001</v>
+        <v>108413.7</v>
       </c>
       <c r="J293" s="5">
-        <v>3.95</v>
+        <v>2.74</v>
       </c>
       <c r="K293" s="4">
-        <v>714532.88</v>
+        <v>715552.88</v>
       </c>
       <c r="L293" s="5">
-        <v>18.03</v>
+        <v>18.05</v>
       </c>
       <c r="M293" s="4">
-        <v>3248836.36</v>
+        <v>3247816.36</v>
       </c>
       <c r="N293" s="5">
-        <v>81.97</v>
+        <v>81.95</v>
       </c>
       <c r="O293" s="4">
         <v>6129.12</v>
@@ -18549,10 +18549,10 @@
         <v>0.15</v>
       </c>
       <c r="Q293" s="4">
-        <v>3242707.24</v>
+        <v>3241687.24</v>
       </c>
       <c r="R293" s="5">
-        <v>81.819999999999993</v>
+        <v>81.790000000000006</v>
       </c>
     </row>
     <row r="294" spans="1:18" x14ac:dyDescent="0.25">
@@ -18575,28 +18575,28 @@
         <v>3963369.24</v>
       </c>
       <c r="G294" s="8">
-        <v>558139.18000000005</v>
+        <v>607139.18000000005</v>
       </c>
       <c r="H294" s="9">
-        <v>14.08</v>
+        <v>15.32</v>
       </c>
       <c r="I294" s="8">
-        <v>156393.70000000001</v>
+        <v>108413.7</v>
       </c>
       <c r="J294" s="9">
-        <v>3.95</v>
+        <v>2.74</v>
       </c>
       <c r="K294" s="8">
-        <v>714532.88</v>
+        <v>715552.88</v>
       </c>
       <c r="L294" s="9">
-        <v>18.03</v>
+        <v>18.05</v>
       </c>
       <c r="M294" s="8">
-        <v>3248836.36</v>
+        <v>3247816.36</v>
       </c>
       <c r="N294" s="9">
-        <v>81.97</v>
+        <v>81.95</v>
       </c>
       <c r="O294" s="8">
         <v>6129.12</v>
@@ -18605,10 +18605,10 @@
         <v>0.15</v>
       </c>
       <c r="Q294" s="8">
-        <v>3242707.24</v>
+        <v>3241687.24</v>
       </c>
       <c r="R294" s="9">
-        <v>81.819999999999993</v>
+        <v>81.790000000000006</v>
       </c>
     </row>
     <row r="295" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -18631,28 +18631,28 @@
         <v>3963369.24</v>
       </c>
       <c r="G295" s="12">
-        <v>558139.18000000005</v>
+        <v>607139.18000000005</v>
       </c>
       <c r="H295" s="13">
-        <v>14.08</v>
+        <v>15.32</v>
       </c>
       <c r="I295" s="12">
-        <v>156393.70000000001</v>
+        <v>108413.7</v>
       </c>
       <c r="J295" s="13">
-        <v>3.95</v>
+        <v>2.74</v>
       </c>
       <c r="K295" s="12">
-        <v>714532.88</v>
+        <v>715552.88</v>
       </c>
       <c r="L295" s="13">
-        <v>18.03</v>
+        <v>18.05</v>
       </c>
       <c r="M295" s="12">
-        <v>3248836.36</v>
+        <v>3247816.36</v>
       </c>
       <c r="N295" s="13">
-        <v>81.97</v>
+        <v>81.95</v>
       </c>
       <c r="O295" s="12">
         <v>6129.12</v>
@@ -18661,10 +18661,10 @@
         <v>0.15</v>
       </c>
       <c r="Q295" s="12">
-        <v>3242707.24</v>
+        <v>3241687.24</v>
       </c>
       <c r="R295" s="13">
-        <v>81.819999999999993</v>
+        <v>81.790000000000006</v>
       </c>
     </row>
     <row r="296" spans="1:18" x14ac:dyDescent="0.25">
@@ -18685,28 +18685,28 @@
         <v>3963369.24</v>
       </c>
       <c r="G296" s="14">
-        <v>558139.18000000005</v>
+        <v>607139.18000000005</v>
       </c>
       <c r="H296" s="15">
-        <v>14.08</v>
+        <v>15.32</v>
       </c>
       <c r="I296" s="14">
-        <v>156393.70000000001</v>
+        <v>108413.7</v>
       </c>
       <c r="J296" s="15">
-        <v>3.95</v>
+        <v>2.74</v>
       </c>
       <c r="K296" s="14">
-        <v>714532.88</v>
+        <v>715552.88</v>
       </c>
       <c r="L296" s="15">
-        <v>18.03</v>
+        <v>18.05</v>
       </c>
       <c r="M296" s="14">
-        <v>3248836.36</v>
+        <v>3247816.36</v>
       </c>
       <c r="N296" s="15">
-        <v>81.97</v>
+        <v>81.95</v>
       </c>
       <c r="O296" s="14">
         <v>6129.12</v>
@@ -18715,10 +18715,10 @@
         <v>0.15</v>
       </c>
       <c r="Q296" s="14">
-        <v>3242707.24</v>
+        <v>3241687.24</v>
       </c>
       <c r="R296" s="15">
-        <v>81.819999999999993</v>
+        <v>81.790000000000006</v>
       </c>
     </row>
     <row r="297" spans="1:18" x14ac:dyDescent="0.25">
@@ -18739,40 +18739,40 @@
         <v>342693877.37</v>
       </c>
       <c r="G297" s="16">
-        <v>187228439.25999999</v>
+        <v>191810561.59999999</v>
       </c>
       <c r="H297" s="17">
-        <v>54.63</v>
+        <v>55.97</v>
       </c>
       <c r="I297" s="16">
-        <v>50769991.439999998</v>
+        <v>46731773.200000003</v>
       </c>
       <c r="J297" s="17">
-        <v>14.81</v>
+        <v>13.64</v>
       </c>
       <c r="K297" s="16">
-        <v>237998430.69999999</v>
+        <v>238542334.80000001</v>
       </c>
       <c r="L297" s="17">
-        <v>69.45</v>
+        <v>69.61</v>
       </c>
       <c r="M297" s="16">
-        <v>104695446.67</v>
+        <v>104151542.56999999</v>
       </c>
       <c r="N297" s="17">
-        <v>30.55</v>
+        <v>30.39</v>
       </c>
       <c r="O297" s="16">
-        <v>15562028.390000001</v>
+        <v>16227870.789999999</v>
       </c>
       <c r="P297" s="17">
-        <v>4.54</v>
+        <v>4.74</v>
       </c>
       <c r="Q297" s="16">
-        <v>89133418.280000001</v>
+        <v>87923671.780000001</v>
       </c>
       <c r="R297" s="17">
-        <v>26.01</v>
+        <v>25.66</v>
       </c>
     </row>
     <row r="298" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -18795,40 +18795,40 @@
         <v>46540814</v>
       </c>
       <c r="G298" s="19">
-        <v>23910276</v>
+        <v>24172229.510000002</v>
       </c>
       <c r="H298" s="20">
-        <v>51.37</v>
+        <v>51.94</v>
       </c>
       <c r="I298" s="19">
-        <v>14530196.67</v>
+        <v>14964213.16</v>
       </c>
       <c r="J298" s="20">
-        <v>31.22</v>
+        <v>32.15</v>
       </c>
       <c r="K298" s="19">
-        <v>38440472.670000002</v>
+        <v>39136442.670000002</v>
       </c>
       <c r="L298" s="20">
-        <v>82.6</v>
+        <v>84.09</v>
       </c>
       <c r="M298" s="19">
-        <v>8100341.3300000001</v>
+        <v>7404371.3300000001</v>
       </c>
       <c r="N298" s="20">
-        <v>17.399999999999999</v>
+        <v>15.91</v>
       </c>
       <c r="O298" s="19">
-        <v>1385521.6</v>
+        <v>1380800</v>
       </c>
       <c r="P298" s="20">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="Q298" s="19">
-        <v>6714819.7300000004</v>
+        <v>6023571.3300000001</v>
       </c>
       <c r="R298" s="20">
-        <v>14.43</v>
+        <v>12.94</v>
       </c>
     </row>
     <row r="299" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -18851,40 +18851,40 @@
         <v>54940200</v>
       </c>
       <c r="G299" s="19">
-        <v>39654207.579999998</v>
+        <v>41097272.969999999</v>
       </c>
       <c r="H299" s="20">
-        <v>72.180000000000007</v>
+        <v>74.8</v>
       </c>
       <c r="I299" s="19">
-        <v>6647725.0599999996</v>
+        <v>4983091.67</v>
       </c>
       <c r="J299" s="20">
-        <v>12.1</v>
+        <v>9.07</v>
       </c>
       <c r="K299" s="19">
-        <v>46301932.640000001</v>
+        <v>46080364.640000001</v>
       </c>
       <c r="L299" s="20">
-        <v>84.28</v>
+        <v>83.87</v>
       </c>
       <c r="M299" s="19">
-        <v>8638267.3599999994</v>
+        <v>8859835.3599999994</v>
       </c>
       <c r="N299" s="20">
-        <v>15.72</v>
+        <v>16.13</v>
       </c>
       <c r="O299" s="19">
-        <v>1155422.5</v>
+        <v>1200986.5</v>
       </c>
       <c r="P299" s="20">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="Q299" s="19">
-        <v>7482844.8600000003</v>
+        <v>7658848.8600000003</v>
       </c>
       <c r="R299" s="20">
-        <v>13.62</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="300" spans="1:18" x14ac:dyDescent="0.25">
@@ -18907,16 +18907,16 @@
         <v>9800000</v>
       </c>
       <c r="G300" s="19">
-        <v>5515006.6399999997</v>
+        <v>5612006.6399999997</v>
       </c>
       <c r="H300" s="20">
-        <v>56.28</v>
+        <v>57.27</v>
       </c>
       <c r="I300" s="19">
-        <v>960008.31</v>
+        <v>863008.31</v>
       </c>
       <c r="J300" s="20">
-        <v>9.8000000000000007</v>
+        <v>8.81</v>
       </c>
       <c r="K300" s="19">
         <v>6475014.9500000002</v>
@@ -18931,16 +18931,16 @@
         <v>33.93</v>
       </c>
       <c r="O300" s="19">
-        <v>2287551.54</v>
+        <v>3152551.54</v>
       </c>
       <c r="P300" s="20">
-        <v>23.34</v>
+        <v>32.17</v>
       </c>
       <c r="Q300" s="19">
-        <v>1037433.51</v>
+        <v>172433.51</v>
       </c>
       <c r="R300" s="20">
-        <v>10.59</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="301" spans="1:18" x14ac:dyDescent="0.25">
@@ -18963,40 +18963,40 @@
         <v>101372727.95</v>
       </c>
       <c r="G301" s="19">
-        <v>29472433.390000001</v>
+        <v>30562243.989999998</v>
       </c>
       <c r="H301" s="20">
-        <v>29.07</v>
+        <v>30.15</v>
       </c>
       <c r="I301" s="19">
-        <v>17548472.68</v>
+        <v>16385336.68</v>
       </c>
       <c r="J301" s="20">
-        <v>17.309999999999999</v>
+        <v>16.16</v>
       </c>
       <c r="K301" s="19">
-        <v>47020906.07</v>
+        <v>46947580.670000002</v>
       </c>
       <c r="L301" s="20">
-        <v>46.38</v>
+        <v>46.31</v>
       </c>
       <c r="M301" s="19">
-        <v>54351821.880000003</v>
+        <v>54425147.280000001</v>
       </c>
       <c r="N301" s="20">
-        <v>53.62</v>
+        <v>53.69</v>
       </c>
       <c r="O301" s="19">
-        <v>4899593</v>
+        <v>4679593</v>
       </c>
       <c r="P301" s="20">
-        <v>4.83</v>
+        <v>4.62</v>
       </c>
       <c r="Q301" s="19">
-        <v>49452228.880000003</v>
+        <v>49745554.280000001</v>
       </c>
       <c r="R301" s="20">
-        <v>48.78</v>
+        <v>49.07</v>
       </c>
     </row>
     <row r="302" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -19075,28 +19075,28 @@
         <v>3963369.24</v>
       </c>
       <c r="G303" s="19">
-        <v>558139.18000000005</v>
+        <v>607139.18000000005</v>
       </c>
       <c r="H303" s="20">
-        <v>14.08</v>
+        <v>15.32</v>
       </c>
       <c r="I303" s="19">
-        <v>156393.70000000001</v>
+        <v>108413.7</v>
       </c>
       <c r="J303" s="20">
-        <v>3.95</v>
+        <v>2.74</v>
       </c>
       <c r="K303" s="19">
-        <v>714532.88</v>
+        <v>715552.88</v>
       </c>
       <c r="L303" s="20">
-        <v>18.03</v>
+        <v>18.05</v>
       </c>
       <c r="M303" s="19">
-        <v>3248836.36</v>
+        <v>3247816.36</v>
       </c>
       <c r="N303" s="20">
-        <v>81.97</v>
+        <v>81.95</v>
       </c>
       <c r="O303" s="19">
         <v>6129.12</v>
@@ -19105,10 +19105,10 @@
         <v>0.15</v>
       </c>
       <c r="Q303" s="19">
-        <v>3242707.24</v>
+        <v>3241687.24</v>
       </c>
       <c r="R303" s="20">
-        <v>81.819999999999993</v>
+        <v>81.790000000000006</v>
       </c>
     </row>
     <row r="304" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -19131,40 +19131,40 @@
         <v>119421186</v>
       </c>
       <c r="G304" s="19">
-        <v>88118376.469999999</v>
+        <v>89759669.310000002</v>
       </c>
       <c r="H304" s="20">
-        <v>73.790000000000006</v>
+        <v>75.16</v>
       </c>
       <c r="I304" s="19">
-        <v>10927195.02</v>
+        <v>9427709.6799999997</v>
       </c>
       <c r="J304" s="20">
-        <v>9.15</v>
+        <v>7.89</v>
       </c>
       <c r="K304" s="19">
-        <v>99045571.489999995</v>
+        <v>99187378.989999995</v>
       </c>
       <c r="L304" s="20">
-        <v>82.94</v>
+        <v>83.06</v>
       </c>
       <c r="M304" s="19">
-        <v>20375614.510000002</v>
+        <v>20233807.010000002</v>
       </c>
       <c r="N304" s="20">
-        <v>17.059999999999999</v>
+        <v>16.940000000000001</v>
       </c>
       <c r="O304" s="19">
-        <v>5827810.6299999999</v>
+        <v>5807810.6299999999</v>
       </c>
       <c r="P304" s="20">
-        <v>4.88</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="Q304" s="19">
-        <v>14547803.880000001</v>
+        <v>14425996.380000001</v>
       </c>
       <c r="R304" s="20">
-        <v>12.18</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="305" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -19241,40 +19241,40 @@
         <v>342693877.37</v>
       </c>
       <c r="G306" s="19">
-        <v>187228439.25999999</v>
+        <v>191810561.59999999</v>
       </c>
       <c r="H306" s="20">
-        <v>54.63</v>
+        <v>55.97</v>
       </c>
       <c r="I306" s="19">
-        <v>50769991.439999998</v>
+        <v>46731773.200000003</v>
       </c>
       <c r="J306" s="20">
-        <v>14.81</v>
+        <v>13.64</v>
       </c>
       <c r="K306" s="19">
-        <v>237998430.69999999</v>
+        <v>238542334.80000001</v>
       </c>
       <c r="L306" s="20">
-        <v>69.45</v>
+        <v>69.61</v>
       </c>
       <c r="M306" s="19">
-        <v>104695446.67</v>
+        <v>104151542.56999999</v>
       </c>
       <c r="N306" s="20">
-        <v>30.55</v>
+        <v>30.39</v>
       </c>
       <c r="O306" s="19">
-        <v>15562028.390000001</v>
+        <v>16227870.789999999</v>
       </c>
       <c r="P306" s="20">
-        <v>4.54</v>
+        <v>4.74</v>
       </c>
       <c r="Q306" s="19">
-        <v>89133418.280000001</v>
+        <v>87923671.780000001</v>
       </c>
       <c r="R306" s="20">
-        <v>26.01</v>
+        <v>25.66</v>
       </c>
     </row>
     <row r="307" spans="1:18" x14ac:dyDescent="0.25">
@@ -19315,11 +19315,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{282CDDA5-F69B-4E16-884B-87B0D9D5F4AF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6CED40E-A45E-4A5B-BC75-E0F470D0E7A4}">
   <dimension ref="A1:R84"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.09765625" customWidth="1"/>
+    <col min="1" max="1" width="18.3984375" customWidth="1"/>
     <col min="2" max="2" width="12.796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.8984375" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="9.796875" bestFit="1" customWidth="1"/>
@@ -19348,7 +19348,7 @@
       <c r="F1" s="27"/>
       <c r="G1" s="27"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
         <v>580</v>
       </c>
@@ -19454,28 +19454,28 @@
         <v>1000000</v>
       </c>
       <c r="G6" s="4">
-        <v>805551.74</v>
+        <v>821951.74</v>
       </c>
       <c r="H6" s="5">
-        <v>80.56</v>
+        <v>82.2</v>
       </c>
       <c r="I6" s="4">
-        <v>135942</v>
+        <v>115542</v>
       </c>
       <c r="J6" s="5">
-        <v>13.59</v>
+        <v>11.55</v>
       </c>
       <c r="K6" s="4">
-        <v>941493.74</v>
+        <v>937493.74</v>
       </c>
       <c r="L6" s="5">
-        <v>94.15</v>
+        <v>93.75</v>
       </c>
       <c r="M6" s="4">
-        <v>58506.26</v>
+        <v>62506.26</v>
       </c>
       <c r="N6" s="5">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="O6" s="4">
         <v>0</v>
@@ -19484,13 +19484,13 @@
         <v>0</v>
       </c>
       <c r="Q6" s="4">
-        <v>58506.26</v>
+        <v>62506.26</v>
       </c>
       <c r="R6" s="5">
-        <v>5.85</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>207</v>
       </c>
@@ -19510,28 +19510,28 @@
         <v>1000000</v>
       </c>
       <c r="G7" s="8">
-        <v>805551.74</v>
+        <v>821951.74</v>
       </c>
       <c r="H7" s="9">
-        <v>80.56</v>
+        <v>82.2</v>
       </c>
       <c r="I7" s="8">
-        <v>135942</v>
+        <v>115542</v>
       </c>
       <c r="J7" s="9">
-        <v>13.59</v>
+        <v>11.55</v>
       </c>
       <c r="K7" s="8">
-        <v>941493.74</v>
+        <v>937493.74</v>
       </c>
       <c r="L7" s="9">
-        <v>94.15</v>
+        <v>93.75</v>
       </c>
       <c r="M7" s="8">
-        <v>58506.26</v>
+        <v>62506.26</v>
       </c>
       <c r="N7" s="9">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="O7" s="8">
         <v>0</v>
@@ -19540,10 +19540,10 @@
         <v>0</v>
       </c>
       <c r="Q7" s="8">
-        <v>58506.26</v>
+        <v>62506.26</v>
       </c>
       <c r="R7" s="9">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -19570,22 +19570,22 @@
         <v>53.34</v>
       </c>
       <c r="I8" s="4">
-        <v>19570</v>
+        <v>31620</v>
       </c>
       <c r="J8" s="5">
-        <v>1.96</v>
+        <v>3.16</v>
       </c>
       <c r="K8" s="4">
-        <v>552949</v>
+        <v>564999</v>
       </c>
       <c r="L8" s="5">
-        <v>55.29</v>
+        <v>56.5</v>
       </c>
       <c r="M8" s="4">
-        <v>447051</v>
+        <v>435001</v>
       </c>
       <c r="N8" s="5">
-        <v>44.71</v>
+        <v>43.5</v>
       </c>
       <c r="O8" s="4">
         <v>0</v>
@@ -19594,13 +19594,13 @@
         <v>0</v>
       </c>
       <c r="Q8" s="4">
-        <v>447051</v>
+        <v>435001</v>
       </c>
       <c r="R8" s="5">
-        <v>44.71</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>201</v>
       </c>
@@ -19626,22 +19626,22 @@
         <v>53.34</v>
       </c>
       <c r="I9" s="8">
-        <v>19570</v>
+        <v>31620</v>
       </c>
       <c r="J9" s="9">
-        <v>1.96</v>
+        <v>3.16</v>
       </c>
       <c r="K9" s="8">
-        <v>552949</v>
+        <v>564999</v>
       </c>
       <c r="L9" s="9">
-        <v>55.29</v>
+        <v>56.5</v>
       </c>
       <c r="M9" s="8">
-        <v>447051</v>
+        <v>435001</v>
       </c>
       <c r="N9" s="9">
-        <v>44.71</v>
+        <v>43.5</v>
       </c>
       <c r="O9" s="8">
         <v>0</v>
@@ -19650,10 +19650,10 @@
         <v>0</v>
       </c>
       <c r="Q9" s="8">
-        <v>447051</v>
+        <v>435001</v>
       </c>
       <c r="R9" s="9">
-        <v>44.71</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -19674,28 +19674,28 @@
         <v>11720000</v>
       </c>
       <c r="G10" s="4">
-        <v>7948887</v>
+        <v>8155521</v>
       </c>
       <c r="H10" s="5">
-        <v>67.819999999999993</v>
+        <v>69.59</v>
       </c>
       <c r="I10" s="4">
-        <v>1650895</v>
+        <v>1281876</v>
       </c>
       <c r="J10" s="5">
-        <v>14.09</v>
+        <v>10.94</v>
       </c>
       <c r="K10" s="4">
-        <v>9599782</v>
+        <v>9437397</v>
       </c>
       <c r="L10" s="5">
-        <v>81.91</v>
+        <v>80.52</v>
       </c>
       <c r="M10" s="4">
-        <v>2120218</v>
+        <v>2282603</v>
       </c>
       <c r="N10" s="5">
-        <v>18.09</v>
+        <v>19.48</v>
       </c>
       <c r="O10" s="4">
         <v>30600</v>
@@ -19704,13 +19704,13 @@
         <v>0.26</v>
       </c>
       <c r="Q10" s="4">
-        <v>2089618</v>
+        <v>2252003</v>
       </c>
       <c r="R10" s="5">
-        <v>17.829999999999998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+        <v>19.22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>133</v>
       </c>
@@ -19730,28 +19730,28 @@
         <v>11720000</v>
       </c>
       <c r="G11" s="8">
-        <v>7948887</v>
+        <v>8155521</v>
       </c>
       <c r="H11" s="9">
-        <v>67.819999999999993</v>
+        <v>69.59</v>
       </c>
       <c r="I11" s="8">
-        <v>1650895</v>
+        <v>1281876</v>
       </c>
       <c r="J11" s="9">
-        <v>14.09</v>
+        <v>10.94</v>
       </c>
       <c r="K11" s="8">
-        <v>9599782</v>
+        <v>9437397</v>
       </c>
       <c r="L11" s="9">
-        <v>81.91</v>
+        <v>80.52</v>
       </c>
       <c r="M11" s="8">
-        <v>2120218</v>
+        <v>2282603</v>
       </c>
       <c r="N11" s="9">
-        <v>18.09</v>
+        <v>19.48</v>
       </c>
       <c r="O11" s="8">
         <v>30600</v>
@@ -19760,10 +19760,10 @@
         <v>0.26</v>
       </c>
       <c r="Q11" s="8">
-        <v>2089618</v>
+        <v>2252003</v>
       </c>
       <c r="R11" s="9">
-        <v>17.829999999999998</v>
+        <v>19.22</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -19784,43 +19784,43 @@
         <v>11820000</v>
       </c>
       <c r="G12" s="4">
-        <v>8562971.1600000001</v>
+        <v>8855980.1600000001</v>
       </c>
       <c r="H12" s="5">
-        <v>72.44</v>
+        <v>74.92</v>
       </c>
       <c r="I12" s="4">
-        <v>917513</v>
+        <v>648546</v>
       </c>
       <c r="J12" s="5">
-        <v>7.76</v>
+        <v>5.49</v>
       </c>
       <c r="K12" s="4">
-        <v>9480484.1600000001</v>
+        <v>9504526.1600000001</v>
       </c>
       <c r="L12" s="5">
-        <v>80.209999999999994</v>
+        <v>80.41</v>
       </c>
       <c r="M12" s="4">
-        <v>2339515.84</v>
+        <v>2315473.84</v>
       </c>
       <c r="N12" s="5">
-        <v>19.79</v>
+        <v>19.59</v>
       </c>
       <c r="O12" s="4">
-        <v>56000</v>
+        <v>13307</v>
       </c>
       <c r="P12" s="5">
-        <v>0.47</v>
+        <v>0.11</v>
       </c>
       <c r="Q12" s="4">
-        <v>2283515.84</v>
+        <v>2302166.84</v>
       </c>
       <c r="R12" s="5">
-        <v>19.32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+        <v>19.48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>81</v>
       </c>
@@ -19846,22 +19846,22 @@
         <v>73.89</v>
       </c>
       <c r="I13" s="8">
-        <v>5000</v>
+        <v>4300</v>
       </c>
       <c r="J13" s="9">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="K13" s="8">
-        <v>876902.87</v>
+        <v>876202.87</v>
       </c>
       <c r="L13" s="9">
-        <v>74.31</v>
+        <v>74.25</v>
       </c>
       <c r="M13" s="8">
-        <v>303097.13</v>
+        <v>303797.13</v>
       </c>
       <c r="N13" s="9">
-        <v>25.69</v>
+        <v>25.75</v>
       </c>
       <c r="O13" s="8">
         <v>0</v>
@@ -19870,13 +19870,13 @@
         <v>0</v>
       </c>
       <c r="Q13" s="8">
-        <v>303097.13</v>
+        <v>303797.13</v>
       </c>
       <c r="R13" s="9">
-        <v>25.69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+        <v>25.75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>143</v>
       </c>
@@ -19896,40 +19896,40 @@
         <v>10640000</v>
       </c>
       <c r="G14" s="8">
-        <v>7691068.29</v>
+        <v>7984077.29</v>
       </c>
       <c r="H14" s="9">
-        <v>72.28</v>
+        <v>75.040000000000006</v>
       </c>
       <c r="I14" s="8">
-        <v>912513</v>
+        <v>644246</v>
       </c>
       <c r="J14" s="9">
-        <v>8.58</v>
+        <v>6.05</v>
       </c>
       <c r="K14" s="8">
-        <v>8603581.2899999991</v>
+        <v>8628323.2899999991</v>
       </c>
       <c r="L14" s="9">
-        <v>80.86</v>
+        <v>81.09</v>
       </c>
       <c r="M14" s="8">
-        <v>2036418.71</v>
+        <v>2011676.71</v>
       </c>
       <c r="N14" s="9">
-        <v>19.14</v>
+        <v>18.91</v>
       </c>
       <c r="O14" s="8">
-        <v>56000</v>
+        <v>13307</v>
       </c>
       <c r="P14" s="9">
-        <v>0.53</v>
+        <v>0.13</v>
       </c>
       <c r="Q14" s="8">
-        <v>1980418.71</v>
+        <v>1998369.71</v>
       </c>
       <c r="R14" s="9">
-        <v>18.61</v>
+        <v>18.78</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -19950,43 +19950,43 @@
         <v>11840200</v>
       </c>
       <c r="G15" s="4">
-        <v>9119604.8599999994</v>
+        <v>9580417.8599999994</v>
       </c>
       <c r="H15" s="5">
-        <v>77.02</v>
+        <v>80.91</v>
       </c>
       <c r="I15" s="4">
-        <v>1676530.67</v>
+        <v>1270099.67</v>
       </c>
       <c r="J15" s="5">
-        <v>14.16</v>
+        <v>10.73</v>
       </c>
       <c r="K15" s="4">
-        <v>10796135.529999999</v>
+        <v>10850517.529999999</v>
       </c>
       <c r="L15" s="5">
-        <v>91.18</v>
+        <v>91.64</v>
       </c>
       <c r="M15" s="4">
-        <v>1044064.47</v>
+        <v>989682.47</v>
       </c>
       <c r="N15" s="5">
-        <v>8.82</v>
+        <v>8.36</v>
       </c>
       <c r="O15" s="4">
-        <v>144801.1</v>
+        <v>110079.5</v>
       </c>
       <c r="P15" s="5">
-        <v>1.22</v>
+        <v>0.93</v>
       </c>
       <c r="Q15" s="4">
-        <v>899263.37</v>
+        <v>879602.97</v>
       </c>
       <c r="R15" s="5">
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+        <v>7.43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>75</v>
       </c>
@@ -20012,37 +20012,37 @@
         <v>94.22</v>
       </c>
       <c r="I16" s="8">
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="J16" s="9">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="K16" s="8">
-        <v>473712.9</v>
+        <v>471112.9</v>
       </c>
       <c r="L16" s="9">
-        <v>94.74</v>
+        <v>94.22</v>
       </c>
       <c r="M16" s="8">
-        <v>26287.1</v>
+        <v>28887.1</v>
       </c>
       <c r="N16" s="9">
-        <v>5.26</v>
+        <v>5.78</v>
       </c>
       <c r="O16" s="8">
-        <v>4721.6000000000004</v>
+        <v>0</v>
       </c>
       <c r="P16" s="9">
-        <v>0.94</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="8">
-        <v>21565.5</v>
+        <v>28887.1</v>
       </c>
       <c r="R16" s="9">
-        <v>4.3099999999999996</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+        <v>5.78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>99</v>
       </c>
@@ -20062,40 +20062,40 @@
         <v>11340200</v>
       </c>
       <c r="G17" s="8">
-        <v>8648491.9600000009</v>
+        <v>9109304.9600000009</v>
       </c>
       <c r="H17" s="9">
-        <v>76.260000000000005</v>
+        <v>80.33</v>
       </c>
       <c r="I17" s="8">
-        <v>1673930.67</v>
+        <v>1270099.67</v>
       </c>
       <c r="J17" s="9">
-        <v>14.76</v>
+        <v>11.2</v>
       </c>
       <c r="K17" s="8">
-        <v>10322422.630000001</v>
+        <v>10379404.630000001</v>
       </c>
       <c r="L17" s="9">
-        <v>91.03</v>
+        <v>91.53</v>
       </c>
       <c r="M17" s="8">
-        <v>1017777.37</v>
+        <v>960795.37</v>
       </c>
       <c r="N17" s="9">
-        <v>8.9700000000000006</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="O17" s="8">
-        <v>140079.5</v>
+        <v>110079.5</v>
       </c>
       <c r="P17" s="9">
-        <v>1.24</v>
+        <v>0.97</v>
       </c>
       <c r="Q17" s="8">
-        <v>877697.87</v>
+        <v>850715.87</v>
       </c>
       <c r="R17" s="9">
-        <v>7.74</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -20116,28 +20116,28 @@
         <v>7820000</v>
       </c>
       <c r="G18" s="4">
-        <v>5047348.3</v>
+        <v>5096948.3</v>
       </c>
       <c r="H18" s="5">
-        <v>64.540000000000006</v>
+        <v>65.180000000000007</v>
       </c>
       <c r="I18" s="4">
-        <v>1020994</v>
+        <v>1035644</v>
       </c>
       <c r="J18" s="5">
-        <v>13.06</v>
+        <v>13.24</v>
       </c>
       <c r="K18" s="4">
-        <v>6068342.2999999998</v>
+        <v>6132592.2999999998</v>
       </c>
       <c r="L18" s="5">
-        <v>77.599999999999994</v>
+        <v>78.42</v>
       </c>
       <c r="M18" s="4">
-        <v>1751657.7</v>
+        <v>1687407.7</v>
       </c>
       <c r="N18" s="5">
-        <v>22.4</v>
+        <v>21.58</v>
       </c>
       <c r="O18" s="4">
         <v>550000</v>
@@ -20146,13 +20146,13 @@
         <v>7.03</v>
       </c>
       <c r="Q18" s="4">
-        <v>1201657.7</v>
+        <v>1137407.7</v>
       </c>
       <c r="R18" s="5">
-        <v>15.37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+        <v>14.54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>161</v>
       </c>
@@ -20172,28 +20172,28 @@
         <v>7820000</v>
       </c>
       <c r="G19" s="8">
-        <v>5047348.3</v>
+        <v>5096948.3</v>
       </c>
       <c r="H19" s="9">
-        <v>64.540000000000006</v>
+        <v>65.180000000000007</v>
       </c>
       <c r="I19" s="8">
-        <v>1020994</v>
+        <v>1035644</v>
       </c>
       <c r="J19" s="9">
-        <v>13.06</v>
+        <v>13.24</v>
       </c>
       <c r="K19" s="8">
-        <v>6068342.2999999998</v>
+        <v>6132592.2999999998</v>
       </c>
       <c r="L19" s="9">
-        <v>77.599999999999994</v>
+        <v>78.42</v>
       </c>
       <c r="M19" s="8">
-        <v>1751657.7</v>
+        <v>1687407.7</v>
       </c>
       <c r="N19" s="9">
-        <v>22.4</v>
+        <v>21.58</v>
       </c>
       <c r="O19" s="8">
         <v>550000</v>
@@ -20202,10 +20202,10 @@
         <v>7.03</v>
       </c>
       <c r="Q19" s="8">
-        <v>1201657.7</v>
+        <v>1137407.7</v>
       </c>
       <c r="R19" s="9">
-        <v>15.37</v>
+        <v>14.54</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -20226,40 +20226,40 @@
         <v>13420000</v>
       </c>
       <c r="G20" s="4">
-        <v>10318412.029999999</v>
+        <v>10751421.42</v>
       </c>
       <c r="H20" s="5">
-        <v>76.89</v>
+        <v>80.11</v>
       </c>
       <c r="I20" s="4">
-        <v>1389392.39</v>
+        <v>751226</v>
       </c>
       <c r="J20" s="5">
-        <v>10.35</v>
+        <v>5.6</v>
       </c>
       <c r="K20" s="4">
-        <v>11707804.42</v>
+        <v>11502647.42</v>
       </c>
       <c r="L20" s="5">
-        <v>87.24</v>
+        <v>85.71</v>
       </c>
       <c r="M20" s="4">
-        <v>1712195.58</v>
+        <v>1917352.58</v>
       </c>
       <c r="N20" s="5">
-        <v>12.76</v>
+        <v>14.29</v>
       </c>
       <c r="O20" s="4">
-        <v>378743</v>
+        <v>497000</v>
       </c>
       <c r="P20" s="5">
-        <v>2.82</v>
+        <v>3.7</v>
       </c>
       <c r="Q20" s="4">
-        <v>1333452.58</v>
+        <v>1420352.58</v>
       </c>
       <c r="R20" s="5">
-        <v>9.94</v>
+        <v>10.58</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -20282,40 +20282,40 @@
         <v>13420000</v>
       </c>
       <c r="G21" s="8">
-        <v>10318412.029999999</v>
+        <v>10751421.42</v>
       </c>
       <c r="H21" s="9">
-        <v>76.89</v>
+        <v>80.11</v>
       </c>
       <c r="I21" s="8">
-        <v>1389392.39</v>
+        <v>751226</v>
       </c>
       <c r="J21" s="9">
-        <v>10.35</v>
+        <v>5.6</v>
       </c>
       <c r="K21" s="8">
-        <v>11707804.42</v>
+        <v>11502647.42</v>
       </c>
       <c r="L21" s="9">
-        <v>87.24</v>
+        <v>85.71</v>
       </c>
       <c r="M21" s="8">
-        <v>1712195.58</v>
+        <v>1917352.58</v>
       </c>
       <c r="N21" s="9">
-        <v>12.76</v>
+        <v>14.29</v>
       </c>
       <c r="O21" s="8">
-        <v>378743</v>
+        <v>497000</v>
       </c>
       <c r="P21" s="9">
-        <v>2.82</v>
+        <v>3.7</v>
       </c>
       <c r="Q21" s="8">
-        <v>1333452.58</v>
+        <v>1420352.58</v>
       </c>
       <c r="R21" s="9">
-        <v>9.94</v>
+        <v>10.58</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -20336,43 +20336,43 @@
         <v>107227000</v>
       </c>
       <c r="G22" s="4">
-        <v>83010670.090000004</v>
+        <v>83389515.129999995</v>
       </c>
       <c r="H22" s="5">
-        <v>77.42</v>
+        <v>77.77</v>
       </c>
       <c r="I22" s="4">
-        <v>5443057.4199999999</v>
+        <v>5117969.88</v>
       </c>
       <c r="J22" s="5">
-        <v>5.08</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="K22" s="4">
-        <v>88453727.510000005</v>
+        <v>88507485.010000005</v>
       </c>
       <c r="L22" s="5">
-        <v>82.49</v>
+        <v>82.54</v>
       </c>
       <c r="M22" s="4">
-        <v>18773272.489999998</v>
+        <v>18719514.989999998</v>
       </c>
       <c r="N22" s="5">
-        <v>17.510000000000002</v>
+        <v>17.46</v>
       </c>
       <c r="O22" s="4">
-        <v>4946965.87</v>
+        <v>5006965.87</v>
       </c>
       <c r="P22" s="5">
-        <v>4.6100000000000003</v>
+        <v>4.67</v>
       </c>
       <c r="Q22" s="4">
-        <v>13826306.619999999</v>
+        <v>13712549.119999999</v>
       </c>
       <c r="R22" s="5">
-        <v>12.89</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+        <v>12.79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>190</v>
       </c>
@@ -20392,43 +20392,43 @@
         <v>29200000</v>
       </c>
       <c r="G23" s="8">
-        <v>17874149.43</v>
+        <v>18184522.469999999</v>
       </c>
       <c r="H23" s="9">
-        <v>61.21</v>
+        <v>62.28</v>
       </c>
       <c r="I23" s="8">
-        <v>5350409.6900000004</v>
+        <v>5051979.6500000004</v>
       </c>
       <c r="J23" s="9">
-        <v>18.32</v>
+        <v>17.3</v>
       </c>
       <c r="K23" s="8">
-        <v>23224559.120000001</v>
+        <v>23236502.120000001</v>
       </c>
       <c r="L23" s="9">
-        <v>79.540000000000006</v>
+        <v>79.58</v>
       </c>
       <c r="M23" s="8">
-        <v>5975440.8799999999</v>
+        <v>5963497.8799999999</v>
       </c>
       <c r="N23" s="9">
-        <v>20.46</v>
+        <v>20.420000000000002</v>
       </c>
       <c r="O23" s="8">
-        <v>4945423.37</v>
+        <v>5005423.37</v>
       </c>
       <c r="P23" s="9">
-        <v>16.940000000000001</v>
+        <v>17.14</v>
       </c>
       <c r="Q23" s="8">
-        <v>1030017.51</v>
+        <v>958074.51</v>
       </c>
       <c r="R23" s="9">
-        <v>3.53</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>219</v>
       </c>
@@ -20448,28 +20448,28 @@
         <v>78027000</v>
       </c>
       <c r="G24" s="8">
-        <v>65136520.659999996</v>
+        <v>65204992.659999996</v>
       </c>
       <c r="H24" s="9">
-        <v>83.48</v>
+        <v>83.57</v>
       </c>
       <c r="I24" s="8">
-        <v>92647.73</v>
+        <v>65990.23</v>
       </c>
       <c r="J24" s="9">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="K24" s="8">
-        <v>65229168.390000001</v>
+        <v>65270982.890000001</v>
       </c>
       <c r="L24" s="9">
-        <v>83.6</v>
+        <v>83.65</v>
       </c>
       <c r="M24" s="8">
-        <v>12797831.609999999</v>
+        <v>12756017.109999999</v>
       </c>
       <c r="N24" s="9">
-        <v>16.399999999999999</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="O24" s="8">
         <v>1542.5</v>
@@ -20478,13 +20478,13 @@
         <v>0</v>
       </c>
       <c r="Q24" s="8">
-        <v>12796289.109999999</v>
+        <v>12754474.609999999</v>
       </c>
       <c r="R24" s="9">
-        <v>16.399999999999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+        <v>16.350000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>229</v>
       </c>
@@ -20558,28 +20558,28 @@
         <v>4260000</v>
       </c>
       <c r="G26" s="4">
-        <v>2025237.43</v>
+        <v>2108870.94</v>
       </c>
       <c r="H26" s="5">
-        <v>47.54</v>
+        <v>49.5</v>
       </c>
       <c r="I26" s="4">
-        <v>502696.67</v>
+        <v>428863.16</v>
       </c>
       <c r="J26" s="5">
-        <v>11.8</v>
+        <v>10.07</v>
       </c>
       <c r="K26" s="4">
-        <v>2527934.1</v>
+        <v>2537734.1</v>
       </c>
       <c r="L26" s="5">
-        <v>59.34</v>
+        <v>59.57</v>
       </c>
       <c r="M26" s="4">
-        <v>1732065.9</v>
+        <v>1722265.9</v>
       </c>
       <c r="N26" s="5">
-        <v>40.659999999999997</v>
+        <v>40.43</v>
       </c>
       <c r="O26" s="4">
         <v>274000</v>
@@ -20588,13 +20588,13 @@
         <v>6.43</v>
       </c>
       <c r="Q26" s="4">
-        <v>1458065.9</v>
+        <v>1448265.9</v>
       </c>
       <c r="R26" s="5">
-        <v>34.229999999999997</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>59</v>
       </c>
@@ -20614,28 +20614,28 @@
         <v>4260000</v>
       </c>
       <c r="G27" s="8">
-        <v>2025237.43</v>
+        <v>2108870.94</v>
       </c>
       <c r="H27" s="9">
-        <v>47.54</v>
+        <v>49.5</v>
       </c>
       <c r="I27" s="8">
-        <v>502696.67</v>
+        <v>428863.16</v>
       </c>
       <c r="J27" s="9">
-        <v>11.8</v>
+        <v>10.07</v>
       </c>
       <c r="K27" s="8">
-        <v>2527934.1</v>
+        <v>2537734.1</v>
       </c>
       <c r="L27" s="9">
-        <v>59.34</v>
+        <v>59.57</v>
       </c>
       <c r="M27" s="8">
-        <v>1732065.9</v>
+        <v>1722265.9</v>
       </c>
       <c r="N27" s="9">
-        <v>40.659999999999997</v>
+        <v>40.43</v>
       </c>
       <c r="O27" s="8">
         <v>274000</v>
@@ -20644,10 +20644,10 @@
         <v>6.43</v>
       </c>
       <c r="Q27" s="8">
-        <v>1458065.9</v>
+        <v>1448265.9</v>
       </c>
       <c r="R27" s="9">
-        <v>34.229999999999997</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
@@ -20668,43 +20668,43 @@
         <v>60595000</v>
       </c>
       <c r="G28" s="4">
-        <v>29825805.079999998</v>
+        <v>31347172.879999999</v>
       </c>
       <c r="H28" s="5">
-        <v>49.22</v>
+        <v>51.73</v>
       </c>
       <c r="I28" s="4">
-        <v>20308533.91</v>
+        <v>19556636.109999999</v>
       </c>
       <c r="J28" s="5">
-        <v>33.520000000000003</v>
+        <v>32.270000000000003</v>
       </c>
       <c r="K28" s="4">
-        <v>50134338.990000002</v>
+        <v>50903808.990000002</v>
       </c>
       <c r="L28" s="5">
-        <v>82.74</v>
+        <v>84.01</v>
       </c>
       <c r="M28" s="4">
-        <v>10460661.01</v>
+        <v>9691191.0099999998</v>
       </c>
       <c r="N28" s="5">
-        <v>17.260000000000002</v>
+        <v>15.99</v>
       </c>
       <c r="O28" s="4">
-        <v>4275196.3</v>
+        <v>5060196.3</v>
       </c>
       <c r="P28" s="5">
-        <v>7.06</v>
+        <v>8.35</v>
       </c>
       <c r="Q28" s="4">
-        <v>6185464.71</v>
+        <v>4630994.71</v>
       </c>
       <c r="R28" s="5">
-        <v>10.210000000000001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+        <v>7.64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>17</v>
       </c>
@@ -20724,28 +20724,28 @@
         <v>37235000</v>
       </c>
       <c r="G29" s="8">
-        <v>18203766.129999999</v>
+        <v>18382086.129999999</v>
       </c>
       <c r="H29" s="9">
-        <v>48.89</v>
+        <v>49.37</v>
       </c>
       <c r="I29" s="8">
-        <v>13581617</v>
+        <v>14046467</v>
       </c>
       <c r="J29" s="9">
-        <v>36.479999999999997</v>
+        <v>37.72</v>
       </c>
       <c r="K29" s="8">
-        <v>31785383.129999999</v>
+        <v>32428553.129999999</v>
       </c>
       <c r="L29" s="9">
-        <v>85.36</v>
+        <v>87.09</v>
       </c>
       <c r="M29" s="8">
-        <v>5449616.8700000001</v>
+        <v>4806446.87</v>
       </c>
       <c r="N29" s="9">
-        <v>14.64</v>
+        <v>12.91</v>
       </c>
       <c r="O29" s="8">
         <v>1106800</v>
@@ -20754,10 +20754,10 @@
         <v>2.97</v>
       </c>
       <c r="Q29" s="8">
-        <v>4342816.87</v>
+        <v>3699646.87</v>
       </c>
       <c r="R29" s="9">
-        <v>11.66</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -20816,7 +20816,7 @@
         <v>-1.4</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>87</v>
       </c>
@@ -20842,22 +20842,22 @@
         <v>66.010000000000005</v>
       </c>
       <c r="I31" s="8">
-        <v>288283</v>
+        <v>334583</v>
       </c>
       <c r="J31" s="9">
-        <v>11.03</v>
+        <v>12.8</v>
       </c>
       <c r="K31" s="8">
-        <v>2013089.67</v>
+        <v>2059389.67</v>
       </c>
       <c r="L31" s="9">
-        <v>77.040000000000006</v>
+        <v>78.819999999999993</v>
       </c>
       <c r="M31" s="8">
-        <v>599824.32999999996</v>
+        <v>553524.32999999996</v>
       </c>
       <c r="N31" s="9">
-        <v>22.96</v>
+        <v>21.18</v>
       </c>
       <c r="O31" s="8">
         <v>0</v>
@@ -20866,13 +20866,13 @@
         <v>0</v>
       </c>
       <c r="Q31" s="8">
-        <v>599824.32999999996</v>
+        <v>553524.32999999996</v>
       </c>
       <c r="R31" s="9">
-        <v>22.96</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
+        <v>21.18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>180</v>
       </c>
@@ -20892,16 +20892,16 @@
         <v>9800000</v>
       </c>
       <c r="G32" s="8">
-        <v>5515006.6399999997</v>
+        <v>5612006.6399999997</v>
       </c>
       <c r="H32" s="9">
-        <v>56.28</v>
+        <v>57.27</v>
       </c>
       <c r="I32" s="8">
-        <v>960008.31</v>
+        <v>863008.31</v>
       </c>
       <c r="J32" s="9">
-        <v>9.8000000000000007</v>
+        <v>8.81</v>
       </c>
       <c r="K32" s="8">
         <v>6475014.9500000002</v>
@@ -20916,19 +20916,19 @@
         <v>33.93</v>
       </c>
       <c r="O32" s="8">
-        <v>2287551.54</v>
+        <v>3152551.54</v>
       </c>
       <c r="P32" s="9">
-        <v>23.34</v>
+        <v>32.17</v>
       </c>
       <c r="Q32" s="8">
-        <v>1037433.51</v>
+        <v>172433.51</v>
       </c>
       <c r="R32" s="9">
-        <v>10.59</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>213</v>
       </c>
@@ -20948,34 +20948,34 @@
         <v>10194186</v>
       </c>
       <c r="G33" s="8">
-        <v>3768775.64</v>
+        <v>5014823.4400000004</v>
       </c>
       <c r="H33" s="9">
-        <v>36.97</v>
+        <v>49.19</v>
       </c>
       <c r="I33" s="8">
-        <v>5328625.5999999996</v>
+        <v>4162577.8</v>
       </c>
       <c r="J33" s="9">
-        <v>52.27</v>
+        <v>40.83</v>
       </c>
       <c r="K33" s="8">
-        <v>9097401.2400000002</v>
+        <v>9177401.2400000002</v>
       </c>
       <c r="L33" s="9">
-        <v>89.24</v>
+        <v>90.03</v>
       </c>
       <c r="M33" s="8">
-        <v>1096784.76</v>
+        <v>1016784.76</v>
       </c>
       <c r="N33" s="9">
-        <v>10.76</v>
+        <v>9.9700000000000006</v>
       </c>
       <c r="O33" s="8">
-        <v>880844.76</v>
+        <v>800844.76</v>
       </c>
       <c r="P33" s="9">
-        <v>8.64</v>
+        <v>7.86</v>
       </c>
       <c r="Q33" s="8">
         <v>215940</v>
@@ -21002,40 +21002,40 @@
         <v>230702200</v>
       </c>
       <c r="G34" s="14">
-        <v>157197866.69</v>
+        <v>160641178.43000001</v>
       </c>
       <c r="H34" s="15">
-        <v>68.14</v>
+        <v>69.63</v>
       </c>
       <c r="I34" s="14">
-        <v>33065125.059999999</v>
+        <v>30238022.82</v>
       </c>
       <c r="J34" s="15">
-        <v>14.33</v>
+        <v>13.11</v>
       </c>
       <c r="K34" s="14">
-        <v>190262991.75</v>
+        <v>190879201.25</v>
       </c>
       <c r="L34" s="15">
-        <v>82.47</v>
+        <v>82.74</v>
       </c>
       <c r="M34" s="14">
-        <v>40439208.25</v>
+        <v>39822998.75</v>
       </c>
       <c r="N34" s="15">
-        <v>17.53</v>
+        <v>17.260000000000002</v>
       </c>
       <c r="O34" s="14">
-        <v>10656306.27</v>
+        <v>11542148.67</v>
       </c>
       <c r="P34" s="15">
-        <v>4.62</v>
+        <v>5</v>
       </c>
       <c r="Q34" s="14">
-        <v>29782901.98</v>
+        <v>28280850.079999998</v>
       </c>
       <c r="R34" s="15">
-        <v>12.91</v>
+        <v>12.26</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
@@ -21062,19 +21062,19 @@
         <v>45.56</v>
       </c>
       <c r="I35" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J35" s="5">
         <v>0</v>
       </c>
       <c r="K35" s="4">
-        <v>371735.05</v>
+        <v>371725.05</v>
       </c>
       <c r="L35" s="5">
         <v>45.56</v>
       </c>
       <c r="M35" s="4">
-        <v>444135.88</v>
+        <v>444145.88</v>
       </c>
       <c r="N35" s="5">
         <v>54.44</v>
@@ -21086,13 +21086,13 @@
         <v>0</v>
       </c>
       <c r="Q35" s="4">
-        <v>444135.88</v>
+        <v>444145.88</v>
       </c>
       <c r="R35" s="5">
         <v>54.44</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ht="105.6" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>279</v>
       </c>
@@ -21118,19 +21118,19 @@
         <v>45.56</v>
       </c>
       <c r="I36" s="8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J36" s="9">
         <v>0</v>
       </c>
       <c r="K36" s="8">
-        <v>371735.05</v>
+        <v>371725.05</v>
       </c>
       <c r="L36" s="9">
         <v>45.56</v>
       </c>
       <c r="M36" s="8">
-        <v>444135.88</v>
+        <v>444145.88</v>
       </c>
       <c r="N36" s="9">
         <v>54.44</v>
@@ -21142,7 +21142,7 @@
         <v>0</v>
       </c>
       <c r="Q36" s="8">
-        <v>444135.88</v>
+        <v>444145.88</v>
       </c>
       <c r="R36" s="9">
         <v>54.44</v>
@@ -21202,7 +21202,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="66" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>236</v>
       </c>
@@ -21282,22 +21282,22 @@
         <v>57.8</v>
       </c>
       <c r="I39" s="4">
-        <v>80885</v>
+        <v>80500</v>
       </c>
       <c r="J39" s="5">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="K39" s="4">
-        <v>1778154.18</v>
+        <v>1777769.18</v>
       </c>
       <c r="L39" s="5">
-        <v>60.55</v>
+        <v>60.54</v>
       </c>
       <c r="M39" s="4">
-        <v>1158349.6000000001</v>
+        <v>1158734.6000000001</v>
       </c>
       <c r="N39" s="5">
-        <v>39.450000000000003</v>
+        <v>39.46</v>
       </c>
       <c r="O39" s="4">
         <v>0</v>
@@ -21306,13 +21306,13 @@
         <v>0</v>
       </c>
       <c r="Q39" s="4">
-        <v>1158349.6000000001</v>
+        <v>1158734.6000000001</v>
       </c>
       <c r="R39" s="5">
-        <v>39.450000000000003</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" ht="66" x14ac:dyDescent="0.25">
+        <v>39.46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
         <v>307</v>
       </c>
@@ -21338,22 +21338,22 @@
         <v>57.8</v>
       </c>
       <c r="I40" s="8">
-        <v>80885</v>
+        <v>80500</v>
       </c>
       <c r="J40" s="9">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="K40" s="8">
-        <v>1778154.18</v>
+        <v>1777769.18</v>
       </c>
       <c r="L40" s="9">
-        <v>60.55</v>
+        <v>60.54</v>
       </c>
       <c r="M40" s="8">
-        <v>1158349.6000000001</v>
+        <v>1158734.6000000001</v>
       </c>
       <c r="N40" s="9">
-        <v>39.450000000000003</v>
+        <v>39.46</v>
       </c>
       <c r="O40" s="8">
         <v>0</v>
@@ -21362,10 +21362,10 @@
         <v>0</v>
       </c>
       <c r="Q40" s="8">
-        <v>1158349.6000000001</v>
+        <v>1158734.6000000001</v>
       </c>
       <c r="R40" s="9">
-        <v>39.450000000000003</v>
+        <v>39.46</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
@@ -21386,28 +21386,28 @@
         <v>22602752.809999999</v>
       </c>
       <c r="G41" s="4">
-        <v>9463094.0299999993</v>
+        <v>9762486.0299999993</v>
       </c>
       <c r="H41" s="5">
-        <v>41.87</v>
+        <v>43.19</v>
       </c>
       <c r="I41" s="4">
-        <v>3192350.42</v>
+        <v>3103498.42</v>
       </c>
       <c r="J41" s="5">
-        <v>14.12</v>
+        <v>13.73</v>
       </c>
       <c r="K41" s="4">
-        <v>12655444.449999999</v>
+        <v>12865984.449999999</v>
       </c>
       <c r="L41" s="5">
-        <v>55.99</v>
+        <v>56.92</v>
       </c>
       <c r="M41" s="4">
-        <v>9947308.3599999994</v>
+        <v>9736768.3599999994</v>
       </c>
       <c r="N41" s="5">
-        <v>44.01</v>
+        <v>43.08</v>
       </c>
       <c r="O41" s="4">
         <v>1182093</v>
@@ -21416,13 +21416,13 @@
         <v>5.23</v>
       </c>
       <c r="Q41" s="4">
-        <v>8765215.3599999994</v>
+        <v>8554675.3599999994</v>
       </c>
       <c r="R41" s="5">
-        <v>38.78</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" ht="66" x14ac:dyDescent="0.25">
+        <v>37.85</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
         <v>267</v>
       </c>
@@ -21442,28 +21442,28 @@
         <v>7840527.8099999996</v>
       </c>
       <c r="G42" s="8">
-        <v>5817758.5899999999</v>
+        <v>6012020.5899999999</v>
       </c>
       <c r="H42" s="9">
-        <v>74.2</v>
+        <v>76.680000000000007</v>
       </c>
       <c r="I42" s="8">
-        <v>973946.86</v>
+        <v>778724.86</v>
       </c>
       <c r="J42" s="9">
-        <v>12.42</v>
+        <v>9.93</v>
       </c>
       <c r="K42" s="8">
-        <v>6791705.4500000002</v>
+        <v>6790745.4500000002</v>
       </c>
       <c r="L42" s="9">
-        <v>86.62</v>
+        <v>86.61</v>
       </c>
       <c r="M42" s="8">
-        <v>1048822.3600000001</v>
+        <v>1049782.3600000001</v>
       </c>
       <c r="N42" s="9">
-        <v>13.38</v>
+        <v>13.39</v>
       </c>
       <c r="O42" s="8">
         <v>106945</v>
@@ -21472,13 +21472,13 @@
         <v>1.36</v>
       </c>
       <c r="Q42" s="8">
-        <v>941877.36</v>
+        <v>942837.36</v>
       </c>
       <c r="R42" s="9">
-        <v>12.01</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
+        <v>12.03</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
         <v>500</v>
       </c>
@@ -21498,28 +21498,28 @@
         <v>12554100</v>
       </c>
       <c r="G43" s="8">
-        <v>3619010.44</v>
+        <v>3723690.44</v>
       </c>
       <c r="H43" s="9">
-        <v>28.83</v>
+        <v>29.66</v>
       </c>
       <c r="I43" s="8">
-        <v>968903.56</v>
+        <v>1075273.56</v>
       </c>
       <c r="J43" s="9">
-        <v>7.72</v>
+        <v>8.57</v>
       </c>
       <c r="K43" s="8">
-        <v>4587914</v>
+        <v>4798964</v>
       </c>
       <c r="L43" s="9">
-        <v>36.549999999999997</v>
+        <v>38.229999999999997</v>
       </c>
       <c r="M43" s="8">
-        <v>7966186</v>
+        <v>7755136</v>
       </c>
       <c r="N43" s="9">
-        <v>63.45</v>
+        <v>61.77</v>
       </c>
       <c r="O43" s="8">
         <v>715148</v>
@@ -21528,13 +21528,13 @@
         <v>5.7</v>
       </c>
       <c r="Q43" s="8">
-        <v>7251038</v>
+        <v>7039988</v>
       </c>
       <c r="R43" s="9">
-        <v>57.76</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+        <v>56.08</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>541</v>
       </c>
@@ -21554,10 +21554,10 @@
         <v>2208125</v>
       </c>
       <c r="G44" s="8">
-        <v>26325</v>
+        <v>26775</v>
       </c>
       <c r="H44" s="9">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="I44" s="8">
         <v>1249500</v>
@@ -21566,16 +21566,16 @@
         <v>56.59</v>
       </c>
       <c r="K44" s="8">
-        <v>1275825</v>
+        <v>1276275</v>
       </c>
       <c r="L44" s="9">
-        <v>57.78</v>
+        <v>57.8</v>
       </c>
       <c r="M44" s="8">
-        <v>932300</v>
+        <v>931850</v>
       </c>
       <c r="N44" s="9">
-        <v>42.22</v>
+        <v>42.2</v>
       </c>
       <c r="O44" s="8">
         <v>360000</v>
@@ -21584,10 +21584,10 @@
         <v>16.3</v>
       </c>
       <c r="Q44" s="8">
-        <v>572300</v>
+        <v>571850</v>
       </c>
       <c r="R44" s="9">
-        <v>25.92</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
@@ -21644,7 +21644,7 @@
         <v>82.25</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>488</v>
       </c>
@@ -21700,7 +21700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="66" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
         <v>548</v>
       </c>
@@ -21774,43 +21774,43 @@
         <v>72788490.920000002</v>
       </c>
       <c r="G48" s="4">
-        <v>17940340.129999999</v>
+        <v>18730758.73</v>
       </c>
       <c r="H48" s="5">
-        <v>24.65</v>
+        <v>25.73</v>
       </c>
       <c r="I48" s="4">
-        <v>14275227.26</v>
+        <v>13201338.26</v>
       </c>
       <c r="J48" s="5">
-        <v>19.61</v>
+        <v>18.14</v>
       </c>
       <c r="K48" s="4">
-        <v>32215567.390000001</v>
+        <v>31932096.989999998</v>
       </c>
       <c r="L48" s="5">
-        <v>44.26</v>
+        <v>43.87</v>
       </c>
       <c r="M48" s="4">
-        <v>40572923.530000001</v>
+        <v>40856393.93</v>
       </c>
       <c r="N48" s="5">
-        <v>55.74</v>
+        <v>56.13</v>
       </c>
       <c r="O48" s="4">
-        <v>3597500</v>
+        <v>3377500</v>
       </c>
       <c r="P48" s="5">
-        <v>4.9400000000000004</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="Q48" s="4">
-        <v>36975423.530000001</v>
+        <v>37478893.93</v>
       </c>
       <c r="R48" s="5">
-        <v>50.8</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" ht="105.6" x14ac:dyDescent="0.25">
+        <v>51.49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="145.19999999999999" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>248</v>
       </c>
@@ -21866,7 +21866,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" ht="105.6" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>260</v>
       </c>
@@ -21922,7 +21922,7 @@
         <v>99.98</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
         <v>299</v>
       </c>
@@ -21978,7 +21978,7 @@
         <v>90.15</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>317</v>
       </c>
@@ -22054,28 +22054,28 @@
         <v>8926239.0199999996</v>
       </c>
       <c r="G53" s="8">
-        <v>2060571.78</v>
+        <v>2165382.08</v>
       </c>
       <c r="H53" s="9">
-        <v>23.08</v>
+        <v>24.26</v>
       </c>
       <c r="I53" s="8">
-        <v>4551805</v>
+        <v>4417881</v>
       </c>
       <c r="J53" s="9">
-        <v>50.99</v>
+        <v>49.49</v>
       </c>
       <c r="K53" s="8">
-        <v>6612376.7800000003</v>
+        <v>6583263.0800000001</v>
       </c>
       <c r="L53" s="9">
-        <v>74.08</v>
+        <v>73.75</v>
       </c>
       <c r="M53" s="8">
-        <v>2313862.2400000002</v>
+        <v>2342975.94</v>
       </c>
       <c r="N53" s="9">
-        <v>25.92</v>
+        <v>26.25</v>
       </c>
       <c r="O53" s="8">
         <v>15000</v>
@@ -22084,13 +22084,13 @@
         <v>0.17</v>
       </c>
       <c r="Q53" s="8">
-        <v>2298862.2400000002</v>
+        <v>2327975.94</v>
       </c>
       <c r="R53" s="9">
-        <v>25.75</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+        <v>26.08</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
         <v>362</v>
       </c>
@@ -22146,7 +22146,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="66" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>390</v>
       </c>
@@ -22190,19 +22190,19 @@
         <v>42.14</v>
       </c>
       <c r="O55" s="8">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="P55" s="9">
-        <v>59.63</v>
+        <v>0</v>
       </c>
       <c r="Q55" s="8">
-        <v>-73323.8</v>
+        <v>176676.2</v>
       </c>
       <c r="R55" s="9">
-        <v>-17.489999999999998</v>
-      </c>
-    </row>
-    <row r="56" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+        <v>42.14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
         <v>398</v>
       </c>
@@ -22222,25 +22222,25 @@
         <v>12829676.84</v>
       </c>
       <c r="G56" s="8">
-        <v>2983932.91</v>
+        <v>3028932.91</v>
       </c>
       <c r="H56" s="9">
-        <v>23.26</v>
+        <v>23.61</v>
       </c>
       <c r="I56" s="8">
-        <v>1021641.56</v>
+        <v>976431.56</v>
       </c>
       <c r="J56" s="9">
-        <v>7.96</v>
+        <v>7.61</v>
       </c>
       <c r="K56" s="8">
-        <v>4005574.47</v>
+        <v>4005364.47</v>
       </c>
       <c r="L56" s="9">
         <v>31.22</v>
       </c>
       <c r="M56" s="8">
-        <v>8824102.3699999992</v>
+        <v>8824312.3699999992</v>
       </c>
       <c r="N56" s="9">
         <v>68.78</v>
@@ -22252,13 +22252,13 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="Q56" s="8">
-        <v>8815102.3699999992</v>
+        <v>8815312.3699999992</v>
       </c>
       <c r="R56" s="9">
         <v>68.709999999999994</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" ht="132" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
         <v>422</v>
       </c>
@@ -22302,19 +22302,19 @@
         <v>68.87</v>
       </c>
       <c r="O57" s="8">
-        <v>3295000</v>
+        <v>3325000</v>
       </c>
       <c r="P57" s="9">
-        <v>17.71</v>
+        <v>17.87</v>
       </c>
       <c r="Q57" s="8">
-        <v>9518169.3900000006</v>
+        <v>9488169.3900000006</v>
       </c>
       <c r="R57" s="9">
-        <v>51.16</v>
-      </c>
-    </row>
-    <row r="58" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
         <v>460</v>
       </c>
@@ -22370,7 +22370,7 @@
         <v>30.38</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
         <v>472</v>
       </c>
@@ -22390,28 +22390,28 @@
         <v>1995235</v>
       </c>
       <c r="G59" s="8">
-        <v>1974622</v>
+        <v>1976130.3</v>
       </c>
       <c r="H59" s="9">
-        <v>98.97</v>
+        <v>99.04</v>
       </c>
       <c r="I59" s="8">
-        <v>181870</v>
+        <v>485</v>
       </c>
       <c r="J59" s="9">
-        <v>9.1199999999999992</v>
+        <v>0.02</v>
       </c>
       <c r="K59" s="8">
-        <v>2156492</v>
+        <v>1976615.3</v>
       </c>
       <c r="L59" s="9">
-        <v>108.08</v>
+        <v>99.07</v>
       </c>
       <c r="M59" s="8">
-        <v>-161257</v>
+        <v>18619.7</v>
       </c>
       <c r="N59" s="9">
-        <v>-8.08</v>
+        <v>0.93</v>
       </c>
       <c r="O59" s="8">
         <v>0</v>
@@ -22420,13 +22420,13 @@
         <v>0</v>
       </c>
       <c r="Q59" s="8">
-        <v>-161257</v>
+        <v>18619.7</v>
       </c>
       <c r="R59" s="9">
-        <v>-8.08</v>
-      </c>
-    </row>
-    <row r="60" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
         <v>492</v>
       </c>
@@ -22446,28 +22446,28 @@
         <v>2528000</v>
       </c>
       <c r="G60" s="8">
-        <v>952739.83999999997</v>
+        <v>991389.84</v>
       </c>
       <c r="H60" s="9">
-        <v>37.69</v>
+        <v>39.22</v>
       </c>
       <c r="I60" s="8">
-        <v>625610</v>
+        <v>295610</v>
       </c>
       <c r="J60" s="9">
-        <v>24.75</v>
+        <v>11.69</v>
       </c>
       <c r="K60" s="8">
-        <v>1578349.84</v>
+        <v>1286999.8400000001</v>
       </c>
       <c r="L60" s="9">
-        <v>62.43</v>
+        <v>50.91</v>
       </c>
       <c r="M60" s="8">
-        <v>949650.16</v>
+        <v>1241000.1599999999</v>
       </c>
       <c r="N60" s="9">
-        <v>37.57</v>
+        <v>49.09</v>
       </c>
       <c r="O60" s="8">
         <v>20000</v>
@@ -22476,13 +22476,13 @@
         <v>0.79</v>
       </c>
       <c r="Q60" s="8">
-        <v>929650.16</v>
+        <v>1221000.1599999999</v>
       </c>
       <c r="R60" s="9">
-        <v>36.770000000000003</v>
-      </c>
-    </row>
-    <row r="61" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
+        <v>48.3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
         <v>508</v>
       </c>
@@ -22508,22 +22508,22 @@
         <v>0</v>
       </c>
       <c r="I61" s="8">
-        <v>0</v>
+        <v>225000</v>
       </c>
       <c r="J61" s="9">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K61" s="8">
-        <v>0</v>
+        <v>225000</v>
       </c>
       <c r="L61" s="9">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M61" s="8">
-        <v>1500000</v>
+        <v>1275000</v>
       </c>
       <c r="N61" s="9">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="O61" s="8">
         <v>0</v>
@@ -22532,13 +22532,13 @@
         <v>0</v>
       </c>
       <c r="Q61" s="8">
-        <v>1500000</v>
+        <v>1275000</v>
       </c>
       <c r="R61" s="9">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="105.6" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
         <v>523</v>
       </c>
@@ -22558,28 +22558,28 @@
         <v>19811100</v>
       </c>
       <c r="G62" s="8">
-        <v>3109811.97</v>
+        <v>3710261.97</v>
       </c>
       <c r="H62" s="9">
-        <v>15.7</v>
+        <v>18.73</v>
       </c>
       <c r="I62" s="8">
-        <v>4523658.03</v>
+        <v>3915288.03</v>
       </c>
       <c r="J62" s="9">
-        <v>22.83</v>
+        <v>19.760000000000002</v>
       </c>
       <c r="K62" s="8">
-        <v>7633470</v>
+        <v>7625550</v>
       </c>
       <c r="L62" s="9">
-        <v>38.53</v>
+        <v>38.49</v>
       </c>
       <c r="M62" s="8">
-        <v>12177630</v>
+        <v>12185550</v>
       </c>
       <c r="N62" s="9">
-        <v>61.47</v>
+        <v>61.51</v>
       </c>
       <c r="O62" s="8">
         <v>0</v>
@@ -22588,10 +22588,10 @@
         <v>0</v>
       </c>
       <c r="Q62" s="8">
-        <v>12177630</v>
+        <v>12185550</v>
       </c>
       <c r="R62" s="9">
-        <v>61.47</v>
+        <v>61.51</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
@@ -22612,40 +22612,40 @@
         <v>101372727.95</v>
       </c>
       <c r="G63" s="14">
-        <v>29472433.390000001</v>
+        <v>30562243.989999998</v>
       </c>
       <c r="H63" s="15">
-        <v>29.07</v>
+        <v>30.15</v>
       </c>
       <c r="I63" s="14">
-        <v>17548472.68</v>
+        <v>16385336.68</v>
       </c>
       <c r="J63" s="15">
-        <v>17.309999999999999</v>
+        <v>16.16</v>
       </c>
       <c r="K63" s="14">
-        <v>47020906.07</v>
+        <v>46947580.670000002</v>
       </c>
       <c r="L63" s="15">
-        <v>46.38</v>
+        <v>46.31</v>
       </c>
       <c r="M63" s="14">
-        <v>54351821.880000003</v>
+        <v>54425147.280000001</v>
       </c>
       <c r="N63" s="15">
-        <v>53.62</v>
+        <v>53.69</v>
       </c>
       <c r="O63" s="14">
-        <v>4899593</v>
+        <v>4679593</v>
       </c>
       <c r="P63" s="15">
-        <v>4.83</v>
+        <v>4.62</v>
       </c>
       <c r="Q63" s="14">
-        <v>49452228.880000003</v>
+        <v>49745554.280000001</v>
       </c>
       <c r="R63" s="15">
-        <v>48.78</v>
+        <v>49.07</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
@@ -22666,40 +22666,40 @@
         <v>332074927.94999999</v>
       </c>
       <c r="G64" s="16">
-        <v>186670300.08000001</v>
+        <v>191203422.41999999</v>
       </c>
       <c r="H64" s="17">
-        <v>56.21</v>
+        <v>57.58</v>
       </c>
       <c r="I64" s="16">
-        <v>50613597.740000002</v>
+        <v>46623359.5</v>
       </c>
       <c r="J64" s="17">
-        <v>15.24</v>
+        <v>14.04</v>
       </c>
       <c r="K64" s="16">
-        <v>237283897.81999999</v>
+        <v>237826781.91999999</v>
       </c>
       <c r="L64" s="17">
-        <v>71.45</v>
+        <v>71.62</v>
       </c>
       <c r="M64" s="16">
-        <v>94791030.129999995</v>
+        <v>94248146.030000001</v>
       </c>
       <c r="N64" s="17">
-        <v>28.55</v>
+        <v>28.38</v>
       </c>
       <c r="O64" s="16">
-        <v>15555899.27</v>
+        <v>16221741.67</v>
       </c>
       <c r="P64" s="17">
-        <v>4.68</v>
+        <v>4.88</v>
       </c>
       <c r="Q64" s="16">
-        <v>79235130.859999999</v>
+        <v>78026404.359999999</v>
       </c>
       <c r="R64" s="17">
-        <v>23.86</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
@@ -22884,40 +22884,40 @@
         <v>338730508.13</v>
       </c>
       <c r="G68" s="16">
-        <v>186670300.08000001</v>
+        <v>191203422.41999999</v>
       </c>
       <c r="H68" s="17">
-        <v>55.11</v>
+        <v>56.45</v>
       </c>
       <c r="I68" s="16">
-        <v>50613597.740000002</v>
+        <v>46623359.5</v>
       </c>
       <c r="J68" s="17">
-        <v>14.94</v>
+        <v>13.76</v>
       </c>
       <c r="K68" s="16">
-        <v>237283897.81999999</v>
+        <v>237826781.91999999</v>
       </c>
       <c r="L68" s="17">
-        <v>70.05</v>
+        <v>70.209999999999994</v>
       </c>
       <c r="M68" s="16">
-        <v>101446610.31</v>
+        <v>100903726.20999999</v>
       </c>
       <c r="N68" s="17">
-        <v>29.95</v>
+        <v>29.79</v>
       </c>
       <c r="O68" s="16">
-        <v>15555899.27</v>
+        <v>16221741.67</v>
       </c>
       <c r="P68" s="17">
-        <v>4.59</v>
+        <v>4.79</v>
       </c>
       <c r="Q68" s="16">
-        <v>85890711.040000007</v>
+        <v>84681984.540000007</v>
       </c>
       <c r="R68" s="17">
-        <v>25.36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
@@ -22938,28 +22938,28 @@
         <v>3963369.24</v>
       </c>
       <c r="G69" s="4">
-        <v>558139.18000000005</v>
+        <v>607139.18000000005</v>
       </c>
       <c r="H69" s="5">
-        <v>14.08</v>
+        <v>15.32</v>
       </c>
       <c r="I69" s="4">
-        <v>156393.70000000001</v>
+        <v>108413.7</v>
       </c>
       <c r="J69" s="5">
-        <v>3.95</v>
+        <v>2.74</v>
       </c>
       <c r="K69" s="4">
-        <v>714532.88</v>
+        <v>715552.88</v>
       </c>
       <c r="L69" s="5">
-        <v>18.03</v>
+        <v>18.05</v>
       </c>
       <c r="M69" s="4">
-        <v>3248836.36</v>
+        <v>3247816.36</v>
       </c>
       <c r="N69" s="5">
-        <v>81.97</v>
+        <v>81.95</v>
       </c>
       <c r="O69" s="4">
         <v>6129.12</v>
@@ -22968,10 +22968,10 @@
         <v>0.15</v>
       </c>
       <c r="Q69" s="4">
-        <v>3242707.24</v>
+        <v>3241687.24</v>
       </c>
       <c r="R69" s="5">
-        <v>81.819999999999993</v>
+        <v>81.790000000000006</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
@@ -22994,28 +22994,28 @@
         <v>3963369.24</v>
       </c>
       <c r="G70" s="8">
-        <v>558139.18000000005</v>
+        <v>607139.18000000005</v>
       </c>
       <c r="H70" s="9">
-        <v>14.08</v>
+        <v>15.32</v>
       </c>
       <c r="I70" s="8">
-        <v>156393.70000000001</v>
+        <v>108413.7</v>
       </c>
       <c r="J70" s="9">
-        <v>3.95</v>
+        <v>2.74</v>
       </c>
       <c r="K70" s="8">
-        <v>714532.88</v>
+        <v>715552.88</v>
       </c>
       <c r="L70" s="9">
-        <v>18.03</v>
+        <v>18.05</v>
       </c>
       <c r="M70" s="8">
-        <v>3248836.36</v>
+        <v>3247816.36</v>
       </c>
       <c r="N70" s="9">
-        <v>81.97</v>
+        <v>81.95</v>
       </c>
       <c r="O70" s="8">
         <v>6129.12</v>
@@ -23024,10 +23024,10 @@
         <v>0.15</v>
       </c>
       <c r="Q70" s="8">
-        <v>3242707.24</v>
+        <v>3241687.24</v>
       </c>
       <c r="R70" s="9">
-        <v>81.819999999999993</v>
+        <v>81.790000000000006</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
@@ -23048,28 +23048,28 @@
         <v>3963369.24</v>
       </c>
       <c r="G71" s="14">
-        <v>558139.18000000005</v>
+        <v>607139.18000000005</v>
       </c>
       <c r="H71" s="15">
-        <v>14.08</v>
+        <v>15.32</v>
       </c>
       <c r="I71" s="14">
-        <v>156393.70000000001</v>
+        <v>108413.7</v>
       </c>
       <c r="J71" s="15">
-        <v>3.95</v>
+        <v>2.74</v>
       </c>
       <c r="K71" s="14">
-        <v>714532.88</v>
+        <v>715552.88</v>
       </c>
       <c r="L71" s="15">
-        <v>18.03</v>
+        <v>18.05</v>
       </c>
       <c r="M71" s="14">
-        <v>3248836.36</v>
+        <v>3247816.36</v>
       </c>
       <c r="N71" s="15">
-        <v>81.97</v>
+        <v>81.95</v>
       </c>
       <c r="O71" s="14">
         <v>6129.12</v>
@@ -23078,10 +23078,10 @@
         <v>0.15</v>
       </c>
       <c r="Q71" s="14">
-        <v>3242707.24</v>
+        <v>3241687.24</v>
       </c>
       <c r="R71" s="15">
-        <v>81.819999999999993</v>
+        <v>81.790000000000006</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
@@ -23102,40 +23102,40 @@
         <v>342693877.37</v>
       </c>
       <c r="G72" s="16">
-        <v>187228439.25999999</v>
+        <v>191810561.59999999</v>
       </c>
       <c r="H72" s="17">
-        <v>54.63</v>
+        <v>55.97</v>
       </c>
       <c r="I72" s="16">
-        <v>50769991.439999998</v>
+        <v>46731773.200000003</v>
       </c>
       <c r="J72" s="17">
-        <v>14.81</v>
+        <v>13.64</v>
       </c>
       <c r="K72" s="16">
-        <v>237998430.69999999</v>
+        <v>238542334.80000001</v>
       </c>
       <c r="L72" s="17">
-        <v>69.45</v>
+        <v>69.61</v>
       </c>
       <c r="M72" s="16">
-        <v>104695446.67</v>
+        <v>104151542.56999999</v>
       </c>
       <c r="N72" s="17">
-        <v>30.55</v>
+        <v>30.39</v>
       </c>
       <c r="O72" s="16">
-        <v>15562028.390000001</v>
+        <v>16227870.789999999</v>
       </c>
       <c r="P72" s="17">
-        <v>4.54</v>
+        <v>4.74</v>
       </c>
       <c r="Q72" s="16">
-        <v>89133418.280000001</v>
+        <v>87923671.780000001</v>
       </c>
       <c r="R72" s="17">
-        <v>26.01</v>
+        <v>25.66</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
@@ -23156,28 +23156,28 @@
         <v>1000000</v>
       </c>
       <c r="G73" s="19">
-        <v>805551.74</v>
+        <v>821951.74</v>
       </c>
       <c r="H73" s="20">
-        <v>80.56</v>
+        <v>82.2</v>
       </c>
       <c r="I73" s="19">
-        <v>135942</v>
+        <v>115542</v>
       </c>
       <c r="J73" s="20">
-        <v>13.59</v>
+        <v>11.55</v>
       </c>
       <c r="K73" s="19">
-        <v>941493.74</v>
+        <v>937493.74</v>
       </c>
       <c r="L73" s="20">
-        <v>94.15</v>
+        <v>93.75</v>
       </c>
       <c r="M73" s="19">
-        <v>58506.26</v>
+        <v>62506.26</v>
       </c>
       <c r="N73" s="20">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="O73" s="19">
         <v>0</v>
@@ -23186,10 +23186,10 @@
         <v>0</v>
       </c>
       <c r="Q73" s="19">
-        <v>58506.26</v>
+        <v>62506.26</v>
       </c>
       <c r="R73" s="20">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
@@ -23216,22 +23216,22 @@
         <v>53.34</v>
       </c>
       <c r="I74" s="19">
-        <v>19570</v>
+        <v>31620</v>
       </c>
       <c r="J74" s="20">
-        <v>1.96</v>
+        <v>3.16</v>
       </c>
       <c r="K74" s="19">
-        <v>552949</v>
+        <v>564999</v>
       </c>
       <c r="L74" s="20">
-        <v>55.29</v>
+        <v>56.5</v>
       </c>
       <c r="M74" s="19">
-        <v>447051</v>
+        <v>435001</v>
       </c>
       <c r="N74" s="20">
-        <v>44.71</v>
+        <v>43.5</v>
       </c>
       <c r="O74" s="19">
         <v>0</v>
@@ -23240,10 +23240,10 @@
         <v>0</v>
       </c>
       <c r="Q74" s="19">
-        <v>447051</v>
+        <v>435001</v>
       </c>
       <c r="R74" s="20">
-        <v>44.71</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
@@ -23264,28 +23264,28 @@
         <v>12535870.93</v>
       </c>
       <c r="G75" s="19">
-        <v>8320612.0499999998</v>
+        <v>8527246.0500000007</v>
       </c>
       <c r="H75" s="20">
-        <v>66.37</v>
+        <v>68.02</v>
       </c>
       <c r="I75" s="19">
-        <v>1650905</v>
+        <v>1281876</v>
       </c>
       <c r="J75" s="20">
-        <v>13.17</v>
+        <v>10.23</v>
       </c>
       <c r="K75" s="19">
-        <v>9971517.0500000007</v>
+        <v>9809122.0500000007</v>
       </c>
       <c r="L75" s="20">
-        <v>79.540000000000006</v>
+        <v>78.25</v>
       </c>
       <c r="M75" s="19">
-        <v>2564353.88</v>
+        <v>2726748.88</v>
       </c>
       <c r="N75" s="20">
-        <v>20.46</v>
+        <v>21.75</v>
       </c>
       <c r="O75" s="19">
         <v>30600</v>
@@ -23294,10 +23294,10 @@
         <v>0.24</v>
       </c>
       <c r="Q75" s="19">
-        <v>2533753.88</v>
+        <v>2696148.88</v>
       </c>
       <c r="R75" s="20">
-        <v>20.21</v>
+        <v>21.51</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
@@ -23318,40 +23318,40 @@
         <v>13373180.710000001</v>
       </c>
       <c r="G76" s="19">
-        <v>8562976.1600000001</v>
+        <v>8855985.1600000001</v>
       </c>
       <c r="H76" s="20">
-        <v>64.03</v>
+        <v>66.22</v>
       </c>
       <c r="I76" s="19">
-        <v>917513</v>
+        <v>648546</v>
       </c>
       <c r="J76" s="20">
-        <v>6.86</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="K76" s="19">
-        <v>9480489.1600000001</v>
+        <v>9504531.1600000001</v>
       </c>
       <c r="L76" s="20">
-        <v>70.89</v>
+        <v>71.069999999999993</v>
       </c>
       <c r="M76" s="19">
-        <v>3892691.55</v>
+        <v>3868649.55</v>
       </c>
       <c r="N76" s="20">
-        <v>29.11</v>
+        <v>28.93</v>
       </c>
       <c r="O76" s="19">
-        <v>56000</v>
+        <v>13307</v>
       </c>
       <c r="P76" s="20">
-        <v>0.42</v>
+        <v>0.1</v>
       </c>
       <c r="Q76" s="19">
-        <v>3836691.55</v>
+        <v>3855342.55</v>
       </c>
       <c r="R76" s="20">
-        <v>28.69</v>
+        <v>28.83</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
@@ -23372,40 +23372,40 @@
         <v>14776703.779999999</v>
       </c>
       <c r="G77" s="19">
-        <v>10816874.039999999</v>
+        <v>11277687.039999999</v>
       </c>
       <c r="H77" s="20">
-        <v>73.2</v>
+        <v>76.319999999999993</v>
       </c>
       <c r="I77" s="19">
-        <v>1757415.67</v>
+        <v>1350599.67</v>
       </c>
       <c r="J77" s="20">
-        <v>11.89</v>
+        <v>9.14</v>
       </c>
       <c r="K77" s="19">
-        <v>12574289.710000001</v>
+        <v>12628286.710000001</v>
       </c>
       <c r="L77" s="20">
-        <v>85.1</v>
+        <v>85.46</v>
       </c>
       <c r="M77" s="19">
-        <v>2202414.0699999998</v>
+        <v>2148417.0699999998</v>
       </c>
       <c r="N77" s="20">
-        <v>14.9</v>
+        <v>14.54</v>
       </c>
       <c r="O77" s="19">
-        <v>144801.1</v>
+        <v>110079.5</v>
       </c>
       <c r="P77" s="20">
-        <v>0.98</v>
+        <v>0.74</v>
       </c>
       <c r="Q77" s="19">
-        <v>2057612.97</v>
+        <v>2038337.57</v>
       </c>
       <c r="R77" s="20">
-        <v>13.92</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
@@ -23426,28 +23426,28 @@
         <v>30422752.809999999</v>
       </c>
       <c r="G78" s="19">
-        <v>14510442.33</v>
+        <v>14859434.33</v>
       </c>
       <c r="H78" s="20">
-        <v>47.7</v>
+        <v>48.84</v>
       </c>
       <c r="I78" s="19">
-        <v>4213344.42</v>
+        <v>4139142.42</v>
       </c>
       <c r="J78" s="20">
-        <v>13.85</v>
+        <v>13.61</v>
       </c>
       <c r="K78" s="19">
-        <v>18723786.75</v>
+        <v>18998576.75</v>
       </c>
       <c r="L78" s="20">
-        <v>61.55</v>
+        <v>62.45</v>
       </c>
       <c r="M78" s="19">
-        <v>11698966.060000001</v>
+        <v>11424176.060000001</v>
       </c>
       <c r="N78" s="20">
-        <v>38.450000000000003</v>
+        <v>37.549999999999997</v>
       </c>
       <c r="O78" s="19">
         <v>1732093</v>
@@ -23456,10 +23456,10 @@
         <v>5.69</v>
       </c>
       <c r="Q78" s="19">
-        <v>9966873.0600000005</v>
+        <v>9692083.0600000005</v>
       </c>
       <c r="R78" s="20">
-        <v>32.76</v>
+        <v>31.86</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
@@ -23480,40 +23480,40 @@
         <v>13420000</v>
       </c>
       <c r="G79" s="19">
-        <v>10318412.029999999</v>
+        <v>10751421.42</v>
       </c>
       <c r="H79" s="20">
-        <v>76.89</v>
+        <v>80.11</v>
       </c>
       <c r="I79" s="19">
-        <v>1389392.39</v>
+        <v>751226</v>
       </c>
       <c r="J79" s="20">
-        <v>10.35</v>
+        <v>5.6</v>
       </c>
       <c r="K79" s="19">
-        <v>11707804.42</v>
+        <v>11502647.42</v>
       </c>
       <c r="L79" s="20">
-        <v>87.24</v>
+        <v>85.71</v>
       </c>
       <c r="M79" s="19">
-        <v>1712195.58</v>
+        <v>1917352.58</v>
       </c>
       <c r="N79" s="20">
-        <v>12.76</v>
+        <v>14.29</v>
       </c>
       <c r="O79" s="19">
-        <v>378743</v>
+        <v>497000</v>
       </c>
       <c r="P79" s="20">
-        <v>2.82</v>
+        <v>3.7</v>
       </c>
       <c r="Q79" s="19">
-        <v>1333452.58</v>
+        <v>1420352.58</v>
       </c>
       <c r="R79" s="20">
-        <v>9.94</v>
+        <v>10.58</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
@@ -23534,40 +23534,40 @@
         <v>111190369.23999999</v>
       </c>
       <c r="G80" s="19">
-        <v>83568809.269999996</v>
+        <v>83996654.310000002</v>
       </c>
       <c r="H80" s="20">
-        <v>75.16</v>
+        <v>75.540000000000006</v>
       </c>
       <c r="I80" s="19">
-        <v>5599451.1200000001</v>
+        <v>5226383.58</v>
       </c>
       <c r="J80" s="20">
-        <v>5.04</v>
+        <v>4.7</v>
       </c>
       <c r="K80" s="19">
-        <v>89168260.390000001</v>
+        <v>89223037.890000001</v>
       </c>
       <c r="L80" s="20">
-        <v>80.19</v>
+        <v>80.239999999999995</v>
       </c>
       <c r="M80" s="19">
-        <v>22022108.850000001</v>
+        <v>21967331.350000001</v>
       </c>
       <c r="N80" s="20">
-        <v>19.809999999999999</v>
+        <v>19.760000000000002</v>
       </c>
       <c r="O80" s="19">
-        <v>4953094.99</v>
+        <v>5013094.99</v>
       </c>
       <c r="P80" s="20">
-        <v>4.45</v>
+        <v>4.51</v>
       </c>
       <c r="Q80" s="19">
-        <v>17069013.859999999</v>
+        <v>16954236.359999999</v>
       </c>
       <c r="R80" s="20">
-        <v>15.35</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
@@ -23588,28 +23588,28 @@
         <v>4935928.8</v>
       </c>
       <c r="G81" s="19">
-        <v>2025237.43</v>
+        <v>2108870.94</v>
       </c>
       <c r="H81" s="20">
-        <v>41.03</v>
+        <v>42.72</v>
       </c>
       <c r="I81" s="19">
-        <v>502696.67</v>
+        <v>428863.16</v>
       </c>
       <c r="J81" s="20">
-        <v>10.18</v>
+        <v>8.69</v>
       </c>
       <c r="K81" s="19">
-        <v>2527934.1</v>
+        <v>2537734.1</v>
       </c>
       <c r="L81" s="20">
-        <v>51.21</v>
+        <v>51.41</v>
       </c>
       <c r="M81" s="19">
-        <v>2407994.7000000002</v>
+        <v>2398194.7000000002</v>
       </c>
       <c r="N81" s="20">
-        <v>48.79</v>
+        <v>48.59</v>
       </c>
       <c r="O81" s="19">
         <v>394000</v>
@@ -23618,10 +23618,10 @@
         <v>7.98</v>
       </c>
       <c r="Q81" s="19">
-        <v>2013994.7</v>
+        <v>2004194.7</v>
       </c>
       <c r="R81" s="20">
-        <v>40.799999999999997</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
@@ -23642,40 +23642,40 @@
         <v>140039071.09999999</v>
       </c>
       <c r="G82" s="19">
-        <v>47766145.210000001</v>
+        <v>50077931.609999999</v>
       </c>
       <c r="H82" s="20">
-        <v>34.11</v>
+        <v>35.76</v>
       </c>
       <c r="I82" s="19">
-        <v>34583761.170000002</v>
+        <v>32757974.370000001</v>
       </c>
       <c r="J82" s="20">
-        <v>24.7</v>
+        <v>23.39</v>
       </c>
       <c r="K82" s="19">
-        <v>82349906.379999995</v>
+        <v>82835905.980000004</v>
       </c>
       <c r="L82" s="20">
-        <v>58.8</v>
+        <v>59.15</v>
       </c>
       <c r="M82" s="19">
-        <v>57689164.719999999</v>
+        <v>57203165.119999997</v>
       </c>
       <c r="N82" s="20">
-        <v>41.2</v>
+        <v>40.85</v>
       </c>
       <c r="O82" s="19">
-        <v>7872696.2999999998</v>
+        <v>8437696.3000000007</v>
       </c>
       <c r="P82" s="20">
-        <v>5.62</v>
+        <v>6.03</v>
       </c>
       <c r="Q82" s="19">
-        <v>49816468.420000002</v>
+        <v>48765468.82</v>
       </c>
       <c r="R82" s="20">
-        <v>35.57</v>
+        <v>34.82</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
@@ -23696,40 +23696,40 @@
         <v>342693877.37</v>
       </c>
       <c r="G83" s="19">
-        <v>187228439.25999999</v>
+        <v>191810561.59999999</v>
       </c>
       <c r="H83" s="20">
-        <v>54.63</v>
+        <v>55.97</v>
       </c>
       <c r="I83" s="19">
-        <v>50769991.439999998</v>
+        <v>46731773.200000003</v>
       </c>
       <c r="J83" s="20">
-        <v>14.81</v>
+        <v>13.64</v>
       </c>
       <c r="K83" s="19">
-        <v>237998430.69999999</v>
+        <v>238542334.80000001</v>
       </c>
       <c r="L83" s="20">
-        <v>69.45</v>
+        <v>69.61</v>
       </c>
       <c r="M83" s="19">
-        <v>104695446.67</v>
+        <v>104151542.56999999</v>
       </c>
       <c r="N83" s="20">
-        <v>30.55</v>
+        <v>30.39</v>
       </c>
       <c r="O83" s="19">
-        <v>15562028.390000001</v>
+        <v>16227870.789999999</v>
       </c>
       <c r="P83" s="20">
-        <v>4.54</v>
+        <v>4.74</v>
       </c>
       <c r="Q83" s="19">
-        <v>89133418.280000001</v>
+        <v>87923671.780000001</v>
       </c>
       <c r="R83" s="20">
-        <v>26.01</v>
+        <v>25.66</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">

--- a/Budget-Report.xlsx
+++ b/Budget-Report.xlsx
@@ -5,17 +5,21 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orathai\Desktop\Claude Cowork\Budget Report\00 BK\25690807\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orathai\Desktop\Claude Cowork\Budget Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E1AFE30-E227-4BCC-A757-0FCDFC2B2C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8021A03-A3ED-4D24-9101-5DF4118771B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="จำแนกตามแผนงาน" sheetId="1" r:id="rId1"/>
     <sheet name="จำแนกตามหน่วยงาน" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">จำแนกตามแผนงาน!$4:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">จำแนกตามหน่วยงาน!$4:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
@@ -1553,7 +1557,7 @@
     <t>69P04R04</t>
   </si>
   <si>
-    <t>โครงการการวิจัยเพื่อพัฒนามาตรฐานกลางสำหรับการพัฒนาหรือประยุกต์ใช้ระบบโทรเวชกรรมทางไกลสำหรับองค์กรปกครองส่วนท้องถิ่น (รวพ.)</t>
+    <t>โครงการการวิจัยเพื่อพัฒนามาตรฐานกลางสำหรับการพัฒนาหรือการประยุกต์ใช้ระบบโทรเวชกรรมทางไกลสำหรับองค์กรปกครองส่วนท้องถิ่น (รวพ.)</t>
   </si>
   <si>
     <t>69P04S</t>
@@ -1766,7 +1770,7 @@
     <t>รวมทั้งสิ้น</t>
   </si>
   <si>
-    <t>( ข้อมูลระบบ ณ วันที่ 7 สิงหาคม 2569 เวลา 22:22:45 น.)</t>
+    <t>( ข้อมูลระบบ ณ วันที่ 14 สิงหาคม 2569 เวลา 23:33:21 น.)</t>
   </si>
   <si>
     <t>สำนัก/โครงการ</t>
@@ -1805,7 +1809,7 @@
     <t>สย.</t>
   </si>
   <si>
-    <t>( ข้อมูลระบบ ณ วันที่ 7 สิงหาคม 2569 เวลา 22:25:19 น.)</t>
+    <t>( ข้อมูลระบบ ณ วันที่ 14 สิงหาคม 2569 เวลา 23:35:05 น.)</t>
   </si>
 </sst>
 </file>
@@ -2317,23 +2321,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:R307"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.69921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.8984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.8984375" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="14.8984375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.3984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.796875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.3984375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.8984375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6.3984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.8984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.796875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="7.09765625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.8984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.3984375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13.796875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="7.09765625" bestFit="1" customWidth="1"/>
   </cols>
@@ -2349,7 +2356,7 @@
       <c r="F1" s="21"/>
       <c r="G1" s="21"/>
     </row>
-    <row r="4" spans="1:18" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
         <v>1</v>
       </c>
@@ -2457,40 +2464,40 @@
         <v>46540814</v>
       </c>
       <c r="G6" s="4">
-        <v>24172229.510000002</v>
+        <v>24324095.649999999</v>
       </c>
       <c r="H6" s="5">
-        <v>51.94</v>
+        <v>52.26</v>
       </c>
       <c r="I6" s="4">
-        <v>14964213.16</v>
+        <v>16096324.17</v>
       </c>
       <c r="J6" s="5">
-        <v>32.15</v>
+        <v>34.590000000000003</v>
       </c>
       <c r="K6" s="4">
-        <v>39136442.670000002</v>
+        <v>40420419.82</v>
       </c>
       <c r="L6" s="5">
-        <v>84.09</v>
+        <v>86.85</v>
       </c>
       <c r="M6" s="4">
-        <v>7404371.3300000001</v>
+        <v>6120394.1799999997</v>
       </c>
       <c r="N6" s="5">
-        <v>15.91</v>
+        <v>13.15</v>
       </c>
       <c r="O6" s="4">
-        <v>1380800</v>
+        <v>1830000</v>
       </c>
       <c r="P6" s="5">
-        <v>2.97</v>
+        <v>3.93</v>
       </c>
       <c r="Q6" s="4">
-        <v>6023571.3300000001</v>
+        <v>4290394.18</v>
       </c>
       <c r="R6" s="5">
-        <v>12.94</v>
+        <v>9.2200000000000006</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -2513,40 +2520,40 @@
         <v>37235000</v>
       </c>
       <c r="G7" s="8">
-        <v>18382086.129999999</v>
+        <v>18510661.129999999</v>
       </c>
       <c r="H7" s="9">
-        <v>49.37</v>
+        <v>49.71</v>
       </c>
       <c r="I7" s="8">
-        <v>14046467</v>
+        <v>14689922</v>
       </c>
       <c r="J7" s="9">
-        <v>37.72</v>
+        <v>39.450000000000003</v>
       </c>
       <c r="K7" s="8">
-        <v>32428553.129999999</v>
+        <v>33200583.129999999</v>
       </c>
       <c r="L7" s="9">
-        <v>87.09</v>
+        <v>89.16</v>
       </c>
       <c r="M7" s="8">
-        <v>4806446.87</v>
+        <v>4034416.87</v>
       </c>
       <c r="N7" s="9">
-        <v>12.91</v>
+        <v>10.84</v>
       </c>
       <c r="O7" s="8">
-        <v>1106800</v>
+        <v>1460000</v>
       </c>
       <c r="P7" s="9">
-        <v>2.97</v>
+        <v>3.92</v>
       </c>
       <c r="Q7" s="8">
-        <v>3699646.87</v>
+        <v>2574416.87</v>
       </c>
       <c r="R7" s="9">
-        <v>9.94</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -2569,40 +2576,40 @@
         <v>3500000</v>
       </c>
       <c r="G8" s="12">
-        <v>2053866.41</v>
+        <v>2081291.41</v>
       </c>
       <c r="H8" s="13">
-        <v>58.68</v>
+        <v>59.47</v>
       </c>
       <c r="I8" s="12">
-        <v>76000</v>
+        <v>565700</v>
       </c>
       <c r="J8" s="13">
-        <v>2.17</v>
+        <v>16.16</v>
       </c>
       <c r="K8" s="12">
-        <v>2129866.41</v>
+        <v>2646991.41</v>
       </c>
       <c r="L8" s="13">
-        <v>60.85</v>
+        <v>75.63</v>
       </c>
       <c r="M8" s="12">
-        <v>1370133.59</v>
+        <v>853008.59</v>
       </c>
       <c r="N8" s="13">
-        <v>39.15</v>
+        <v>24.37</v>
       </c>
       <c r="O8" s="12">
-        <v>99600</v>
+        <v>2800</v>
       </c>
       <c r="P8" s="13">
-        <v>2.85</v>
+        <v>0.08</v>
       </c>
       <c r="Q8" s="12">
-        <v>1270533.5900000001</v>
+        <v>850208.59</v>
       </c>
       <c r="R8" s="13">
-        <v>36.299999999999997</v>
+        <v>24.29</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
@@ -2625,28 +2632,28 @@
         <v>698900</v>
       </c>
       <c r="G9" s="12">
-        <v>436021</v>
+        <v>529031</v>
       </c>
       <c r="H9" s="13">
-        <v>62.39</v>
+        <v>75.69</v>
       </c>
       <c r="I9" s="12">
-        <v>378100</v>
+        <v>281140</v>
       </c>
       <c r="J9" s="13">
-        <v>54.1</v>
+        <v>40.229999999999997</v>
       </c>
       <c r="K9" s="12">
-        <v>814121</v>
+        <v>810171</v>
       </c>
       <c r="L9" s="13">
-        <v>116.49</v>
+        <v>115.92</v>
       </c>
       <c r="M9" s="12">
-        <v>-115221</v>
+        <v>-111271</v>
       </c>
       <c r="N9" s="13">
-        <v>-16.489999999999998</v>
+        <v>-15.92</v>
       </c>
       <c r="O9" s="12">
         <v>0</v>
@@ -2655,10 +2662,10 @@
         <v>0</v>
       </c>
       <c r="Q9" s="12">
-        <v>-115221</v>
+        <v>-111271</v>
       </c>
       <c r="R9" s="13">
-        <v>-16.489999999999998</v>
+        <v>-15.92</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -2687,22 +2694,22 @@
         <v>126.45</v>
       </c>
       <c r="I10" s="12">
-        <v>0</v>
+        <v>21650</v>
       </c>
       <c r="J10" s="13">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="K10" s="12">
-        <v>885172</v>
+        <v>906822</v>
       </c>
       <c r="L10" s="13">
-        <v>126.45</v>
+        <v>129.55000000000001</v>
       </c>
       <c r="M10" s="12">
-        <v>-185172</v>
+        <v>-206822</v>
       </c>
       <c r="N10" s="13">
-        <v>-26.45</v>
+        <v>-29.55</v>
       </c>
       <c r="O10" s="12">
         <v>2200</v>
@@ -2711,10 +2718,10 @@
         <v>0.31</v>
       </c>
       <c r="Q10" s="12">
-        <v>-187372</v>
+        <v>-209022</v>
       </c>
       <c r="R10" s="13">
-        <v>-26.77</v>
+        <v>-29.86</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
@@ -2761,16 +2768,16 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="O11" s="12">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="P11" s="13">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q11" s="12">
-        <v>33100</v>
+        <v>-16900</v>
       </c>
       <c r="R11" s="13">
-        <v>1.0900000000000001</v>
+        <v>-0.56000000000000005</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -2793,25 +2800,25 @@
         <v>20000000</v>
       </c>
       <c r="G12" s="12">
-        <v>8197155</v>
+        <v>8198855</v>
       </c>
       <c r="H12" s="13">
         <v>40.99</v>
       </c>
       <c r="I12" s="12">
-        <v>9869700</v>
+        <v>9866500</v>
       </c>
       <c r="J12" s="13">
-        <v>49.35</v>
+        <v>49.33</v>
       </c>
       <c r="K12" s="12">
-        <v>18066855</v>
+        <v>18065355</v>
       </c>
       <c r="L12" s="13">
         <v>90.33</v>
       </c>
       <c r="M12" s="12">
-        <v>1933145</v>
+        <v>1934645</v>
       </c>
       <c r="N12" s="13">
         <v>9.67</v>
@@ -2823,7 +2830,7 @@
         <v>5</v>
       </c>
       <c r="Q12" s="12">
-        <v>933145</v>
+        <v>934645</v>
       </c>
       <c r="R12" s="13">
         <v>4.67</v>
@@ -2849,28 +2856,28 @@
         <v>800000</v>
       </c>
       <c r="G13" s="12">
-        <v>657225.5</v>
+        <v>664165.5</v>
       </c>
       <c r="H13" s="13">
-        <v>82.15</v>
+        <v>83.02</v>
       </c>
       <c r="I13" s="12">
-        <v>126162</v>
+        <v>116962</v>
       </c>
       <c r="J13" s="13">
-        <v>15.77</v>
+        <v>14.62</v>
       </c>
       <c r="K13" s="12">
-        <v>783387.5</v>
+        <v>781127.5</v>
       </c>
       <c r="L13" s="13">
-        <v>97.92</v>
+        <v>97.64</v>
       </c>
       <c r="M13" s="12">
-        <v>16612.5</v>
+        <v>18872.5</v>
       </c>
       <c r="N13" s="13">
-        <v>2.08</v>
+        <v>2.36</v>
       </c>
       <c r="O13" s="12">
         <v>0</v>
@@ -2879,10 +2886,10 @@
         <v>0</v>
       </c>
       <c r="Q13" s="12">
-        <v>16612.5</v>
+        <v>18872.5</v>
       </c>
       <c r="R13" s="13">
-        <v>2.08</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -3097,16 +3104,16 @@
         <v>100</v>
       </c>
       <c r="O17" s="12">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="P17" s="13">
-        <v>0</v>
+        <v>114.29</v>
       </c>
       <c r="Q17" s="12">
-        <v>350000</v>
+        <v>-50000</v>
       </c>
       <c r="R17" s="13">
-        <v>100</v>
+        <v>-14.29</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
@@ -3129,28 +3136,28 @@
         <v>1148575.97</v>
       </c>
       <c r="G18" s="12">
-        <v>321536</v>
+        <v>321036</v>
       </c>
       <c r="H18" s="13">
-        <v>27.99</v>
+        <v>27.95</v>
       </c>
       <c r="I18" s="12">
-        <v>1000</v>
+        <v>141500</v>
       </c>
       <c r="J18" s="13">
-        <v>0.09</v>
+        <v>12.32</v>
       </c>
       <c r="K18" s="12">
-        <v>322536</v>
+        <v>462536</v>
       </c>
       <c r="L18" s="13">
-        <v>28.08</v>
+        <v>40.270000000000003</v>
       </c>
       <c r="M18" s="12">
-        <v>826039.97</v>
+        <v>686039.97</v>
       </c>
       <c r="N18" s="13">
-        <v>71.92</v>
+        <v>59.73</v>
       </c>
       <c r="O18" s="12">
         <v>0</v>
@@ -3159,10 +3166,10 @@
         <v>0</v>
       </c>
       <c r="Q18" s="12">
-        <v>826039.97</v>
+        <v>686039.97</v>
       </c>
       <c r="R18" s="13">
-        <v>71.92</v>
+        <v>59.73</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
@@ -3247,22 +3254,22 @@
         <v>85.63</v>
       </c>
       <c r="I20" s="12">
-        <v>0</v>
+        <v>25300</v>
       </c>
       <c r="J20" s="13">
-        <v>0</v>
+        <v>14.08</v>
       </c>
       <c r="K20" s="12">
-        <v>153906</v>
+        <v>179206</v>
       </c>
       <c r="L20" s="13">
-        <v>85.63</v>
+        <v>99.71</v>
       </c>
       <c r="M20" s="12">
-        <v>25827</v>
+        <v>527</v>
       </c>
       <c r="N20" s="13">
-        <v>14.37</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="O20" s="12">
         <v>0</v>
@@ -3271,10 +3278,10 @@
         <v>0</v>
       </c>
       <c r="Q20" s="12">
-        <v>25827</v>
+        <v>527</v>
       </c>
       <c r="R20" s="13">
-        <v>14.37</v>
+        <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -3527,22 +3534,22 @@
         <v>69.510000000000005</v>
       </c>
       <c r="I25" s="12">
-        <v>626500</v>
+        <v>700400</v>
       </c>
       <c r="J25" s="13">
-        <v>30.49</v>
+        <v>34.090000000000003</v>
       </c>
       <c r="K25" s="12">
-        <v>2054606.66</v>
+        <v>2128506.66</v>
       </c>
       <c r="L25" s="13">
-        <v>100</v>
+        <v>103.6</v>
       </c>
       <c r="M25" s="12">
-        <v>0</v>
+        <v>-73900</v>
       </c>
       <c r="N25" s="13">
-        <v>0</v>
+        <v>-3.6</v>
       </c>
       <c r="O25" s="12">
         <v>0</v>
@@ -3551,10 +3558,10 @@
         <v>0</v>
       </c>
       <c r="Q25" s="12">
-        <v>0</v>
+        <v>-73900</v>
       </c>
       <c r="R25" s="13">
-        <v>0</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="26" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -3583,22 +3590,22 @@
         <v>74.87</v>
       </c>
       <c r="I26" s="12">
-        <v>200850</v>
+        <v>204450</v>
       </c>
       <c r="J26" s="13">
-        <v>60.86</v>
+        <v>61.95</v>
       </c>
       <c r="K26" s="12">
-        <v>447935.39</v>
+        <v>451535.39</v>
       </c>
       <c r="L26" s="13">
-        <v>135.74</v>
+        <v>136.83000000000001</v>
       </c>
       <c r="M26" s="12">
-        <v>-117935.39</v>
+        <v>-121535.39</v>
       </c>
       <c r="N26" s="13">
-        <v>-35.74</v>
+        <v>-36.83</v>
       </c>
       <c r="O26" s="12">
         <v>0</v>
@@ -3607,10 +3614,10 @@
         <v>0</v>
       </c>
       <c r="Q26" s="12">
-        <v>-117935.39</v>
+        <v>-121535.39</v>
       </c>
       <c r="R26" s="13">
-        <v>-35.74</v>
+        <v>-36.83</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -3639,22 +3646,22 @@
         <v>32.29</v>
       </c>
       <c r="I27" s="12">
-        <v>11685</v>
+        <v>9850</v>
       </c>
       <c r="J27" s="13">
-        <v>3.54</v>
+        <v>2.98</v>
       </c>
       <c r="K27" s="12">
-        <v>118349.6</v>
+        <v>116514.6</v>
       </c>
       <c r="L27" s="13">
-        <v>35.82</v>
+        <v>35.270000000000003</v>
       </c>
       <c r="M27" s="12">
-        <v>212005.4</v>
+        <v>213840.4</v>
       </c>
       <c r="N27" s="13">
-        <v>64.180000000000007</v>
+        <v>64.73</v>
       </c>
       <c r="O27" s="12">
         <v>0</v>
@@ -3663,10 +3670,10 @@
         <v>0</v>
       </c>
       <c r="Q27" s="12">
-        <v>212005.4</v>
+        <v>213840.4</v>
       </c>
       <c r="R27" s="13">
-        <v>64.180000000000007</v>
+        <v>64.73</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -3695,34 +3702,34 @@
         <v>49.5</v>
       </c>
       <c r="I28" s="8">
-        <v>428863.16</v>
+        <v>913209.17</v>
       </c>
       <c r="J28" s="9">
-        <v>10.07</v>
+        <v>21.44</v>
       </c>
       <c r="K28" s="8">
-        <v>2537734.1</v>
+        <v>3022080.11</v>
       </c>
       <c r="L28" s="9">
-        <v>59.57</v>
+        <v>70.94</v>
       </c>
       <c r="M28" s="8">
-        <v>1722265.9</v>
+        <v>1237919.8899999999</v>
       </c>
       <c r="N28" s="9">
-        <v>40.43</v>
+        <v>29.06</v>
       </c>
       <c r="O28" s="8">
-        <v>274000</v>
+        <v>270000</v>
       </c>
       <c r="P28" s="9">
-        <v>6.43</v>
+        <v>6.34</v>
       </c>
       <c r="Q28" s="8">
-        <v>1448265.9</v>
+        <v>967919.89</v>
       </c>
       <c r="R28" s="9">
-        <v>34</v>
+        <v>22.72</v>
       </c>
     </row>
     <row r="29" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
@@ -3751,22 +3758,22 @@
         <v>44.71</v>
       </c>
       <c r="I29" s="12">
-        <v>320987.5</v>
+        <v>711512.5</v>
       </c>
       <c r="J29" s="13">
-        <v>17.64</v>
+        <v>39.090000000000003</v>
       </c>
       <c r="K29" s="12">
-        <v>1134694.8700000001</v>
+        <v>1525219.87</v>
       </c>
       <c r="L29" s="13">
-        <v>62.35</v>
+        <v>83.8</v>
       </c>
       <c r="M29" s="12">
-        <v>685305.13</v>
+        <v>294780.13</v>
       </c>
       <c r="N29" s="13">
-        <v>37.65</v>
+        <v>16.2</v>
       </c>
       <c r="O29" s="12">
         <v>270000</v>
@@ -3775,10 +3782,10 @@
         <v>14.84</v>
       </c>
       <c r="Q29" s="12">
-        <v>415305.13</v>
+        <v>24780.13</v>
       </c>
       <c r="R29" s="13">
-        <v>22.82</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -3807,34 +3814,34 @@
         <v>14.94</v>
       </c>
       <c r="I30" s="12">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="J30" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K30" s="12">
-        <v>149365.79999999999</v>
+        <v>249365.8</v>
       </c>
       <c r="L30" s="13">
-        <v>14.94</v>
+        <v>24.94</v>
       </c>
       <c r="M30" s="12">
-        <v>850634.2</v>
+        <v>750634.2</v>
       </c>
       <c r="N30" s="13">
-        <v>85.06</v>
+        <v>75.06</v>
       </c>
       <c r="O30" s="12">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="P30" s="13">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="12">
-        <v>848634.2</v>
+        <v>750634.2</v>
       </c>
       <c r="R30" s="13">
-        <v>84.86</v>
+        <v>75.06</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
@@ -3863,22 +3870,22 @@
         <v>2.15</v>
       </c>
       <c r="I31" s="12">
-        <v>1345</v>
+        <v>0</v>
       </c>
       <c r="J31" s="13">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="K31" s="12">
-        <v>22800</v>
+        <v>21455</v>
       </c>
       <c r="L31" s="13">
-        <v>2.2799999999999998</v>
+        <v>2.15</v>
       </c>
       <c r="M31" s="12">
-        <v>977200</v>
+        <v>978545</v>
       </c>
       <c r="N31" s="13">
-        <v>97.72</v>
+        <v>97.85</v>
       </c>
       <c r="O31" s="12">
         <v>0</v>
@@ -3887,10 +3894,10 @@
         <v>0</v>
       </c>
       <c r="Q31" s="12">
-        <v>977200</v>
+        <v>978545</v>
       </c>
       <c r="R31" s="13">
-        <v>97.72</v>
+        <v>97.85</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -3919,34 +3926,34 @@
         <v>267.26</v>
       </c>
       <c r="I32" s="12">
-        <v>105260.66</v>
+        <v>101696.67</v>
       </c>
       <c r="J32" s="13">
-        <v>26.32</v>
+        <v>25.42</v>
       </c>
       <c r="K32" s="12">
-        <v>1174283.43</v>
+        <v>1170719.44</v>
       </c>
       <c r="L32" s="13">
-        <v>293.57</v>
+        <v>292.68</v>
       </c>
       <c r="M32" s="12">
-        <v>-774283.43</v>
+        <v>-770719.44</v>
       </c>
       <c r="N32" s="13">
-        <v>-193.57</v>
+        <v>-192.68</v>
       </c>
       <c r="O32" s="12">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="P32" s="13">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="12">
-        <v>-776283.43</v>
+        <v>-770719.44</v>
       </c>
       <c r="R32" s="13">
-        <v>-194.07</v>
+        <v>-192.68</v>
       </c>
     </row>
     <row r="33" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -3975,22 +3982,22 @@
         <v>138.30000000000001</v>
       </c>
       <c r="I33" s="12">
-        <v>1270</v>
+        <v>0</v>
       </c>
       <c r="J33" s="13">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="K33" s="12">
-        <v>56590</v>
+        <v>55320</v>
       </c>
       <c r="L33" s="13">
-        <v>141.47</v>
+        <v>138.30000000000001</v>
       </c>
       <c r="M33" s="12">
-        <v>-16590</v>
+        <v>-15320</v>
       </c>
       <c r="N33" s="13">
-        <v>-41.48</v>
+        <v>-38.299999999999997</v>
       </c>
       <c r="O33" s="12">
         <v>0</v>
@@ -3999,10 +4006,10 @@
         <v>0</v>
       </c>
       <c r="Q33" s="12">
-        <v>-16590</v>
+        <v>-15320</v>
       </c>
       <c r="R33" s="13">
-        <v>-41.48</v>
+        <v>-38.299999999999997</v>
       </c>
     </row>
     <row r="34" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -4143,22 +4150,22 @@
         <v>94.22</v>
       </c>
       <c r="I36" s="8">
-        <v>0</v>
+        <v>16900</v>
       </c>
       <c r="J36" s="9">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="K36" s="8">
-        <v>471112.9</v>
+        <v>488012.9</v>
       </c>
       <c r="L36" s="9">
-        <v>94.22</v>
+        <v>97.6</v>
       </c>
       <c r="M36" s="8">
-        <v>28887.1</v>
+        <v>11987.1</v>
       </c>
       <c r="N36" s="9">
-        <v>5.78</v>
+        <v>2.4</v>
       </c>
       <c r="O36" s="8">
         <v>0</v>
@@ -4167,10 +4174,10 @@
         <v>0</v>
       </c>
       <c r="Q36" s="8">
-        <v>28887.1</v>
+        <v>11987.1</v>
       </c>
       <c r="R36" s="9">
-        <v>5.78</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="37" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -4199,22 +4206,22 @@
         <v>93.33</v>
       </c>
       <c r="I37" s="12">
-        <v>0</v>
+        <v>16900</v>
       </c>
       <c r="J37" s="13">
-        <v>0</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="K37" s="12">
-        <v>373324.9</v>
+        <v>390224.9</v>
       </c>
       <c r="L37" s="13">
-        <v>93.33</v>
+        <v>97.56</v>
       </c>
       <c r="M37" s="12">
-        <v>26675.1</v>
+        <v>9775.1</v>
       </c>
       <c r="N37" s="13">
-        <v>6.67</v>
+        <v>2.44</v>
       </c>
       <c r="O37" s="12">
         <v>0</v>
@@ -4223,10 +4230,10 @@
         <v>0</v>
       </c>
       <c r="Q37" s="12">
-        <v>26675.1</v>
+        <v>9775.1</v>
       </c>
       <c r="R37" s="13">
-        <v>6.67</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="38" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -4305,16 +4312,16 @@
         <v>1180000</v>
       </c>
       <c r="G39" s="8">
-        <v>871902.87</v>
+        <v>876202.87</v>
       </c>
       <c r="H39" s="9">
-        <v>73.89</v>
+        <v>74.25</v>
       </c>
       <c r="I39" s="8">
-        <v>4300</v>
+        <v>0</v>
       </c>
       <c r="J39" s="9">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="K39" s="8">
         <v>876202.87</v>
@@ -4417,16 +4424,16 @@
         <v>780000</v>
       </c>
       <c r="G41" s="12">
-        <v>349538</v>
+        <v>353838</v>
       </c>
       <c r="H41" s="13">
-        <v>44.81</v>
+        <v>45.36</v>
       </c>
       <c r="I41" s="12">
-        <v>4300</v>
+        <v>0</v>
       </c>
       <c r="J41" s="13">
-        <v>0.55000000000000004</v>
+        <v>0</v>
       </c>
       <c r="K41" s="12">
         <v>353838</v>
@@ -4473,40 +4480,40 @@
         <v>2612914</v>
       </c>
       <c r="G42" s="8">
-        <v>1724806.67</v>
+        <v>1743797.81</v>
       </c>
       <c r="H42" s="9">
-        <v>66.010000000000005</v>
+        <v>66.739999999999995</v>
       </c>
       <c r="I42" s="8">
-        <v>334583</v>
+        <v>326293</v>
       </c>
       <c r="J42" s="9">
-        <v>12.8</v>
+        <v>12.49</v>
       </c>
       <c r="K42" s="8">
-        <v>2059389.67</v>
+        <v>2070090.81</v>
       </c>
       <c r="L42" s="9">
-        <v>78.819999999999993</v>
+        <v>79.23</v>
       </c>
       <c r="M42" s="8">
-        <v>553524.32999999996</v>
+        <v>542823.18999999994</v>
       </c>
       <c r="N42" s="9">
-        <v>21.18</v>
+        <v>20.77</v>
       </c>
       <c r="O42" s="8">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="P42" s="9">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Q42" s="8">
-        <v>553524.32999999996</v>
+        <v>442823.19</v>
       </c>
       <c r="R42" s="9">
-        <v>21.18</v>
+        <v>16.95</v>
       </c>
     </row>
     <row r="43" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -4529,28 +4536,28 @@
         <v>326514</v>
       </c>
       <c r="G43" s="12">
-        <v>131137</v>
+        <v>150128.14000000001</v>
       </c>
       <c r="H43" s="13">
-        <v>40.159999999999997</v>
+        <v>45.98</v>
       </c>
       <c r="I43" s="12">
-        <v>75803</v>
+        <v>49213</v>
       </c>
       <c r="J43" s="13">
-        <v>23.22</v>
+        <v>15.07</v>
       </c>
       <c r="K43" s="12">
-        <v>206940</v>
+        <v>199341.14</v>
       </c>
       <c r="L43" s="13">
-        <v>63.38</v>
+        <v>61.05</v>
       </c>
       <c r="M43" s="12">
-        <v>119574</v>
+        <v>127172.86</v>
       </c>
       <c r="N43" s="13">
-        <v>36.619999999999997</v>
+        <v>38.950000000000003</v>
       </c>
       <c r="O43" s="12">
         <v>0</v>
@@ -4559,10 +4566,10 @@
         <v>0</v>
       </c>
       <c r="Q43" s="12">
-        <v>119574</v>
+        <v>127172.86</v>
       </c>
       <c r="R43" s="13">
-        <v>36.619999999999997</v>
+        <v>38.950000000000003</v>
       </c>
     </row>
     <row r="44" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -4609,16 +4616,16 @@
         <v>100</v>
       </c>
       <c r="O44" s="12">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="P44" s="13">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="Q44" s="12">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="R44" s="13">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -4703,22 +4710,22 @@
         <v>70.98</v>
       </c>
       <c r="I46" s="12">
-        <v>0</v>
+        <v>18300</v>
       </c>
       <c r="J46" s="13">
-        <v>0</v>
+        <v>8.7799999999999994</v>
       </c>
       <c r="K46" s="12">
-        <v>147915</v>
+        <v>166215</v>
       </c>
       <c r="L46" s="13">
-        <v>70.98</v>
+        <v>79.760000000000005</v>
       </c>
       <c r="M46" s="12">
-        <v>60485</v>
+        <v>42185</v>
       </c>
       <c r="N46" s="13">
-        <v>29.02</v>
+        <v>20.239999999999998</v>
       </c>
       <c r="O46" s="12">
         <v>0</v>
@@ -4727,10 +4734,10 @@
         <v>0</v>
       </c>
       <c r="Q46" s="12">
-        <v>60485</v>
+        <v>42185</v>
       </c>
       <c r="R46" s="13">
-        <v>29.02</v>
+        <v>20.239999999999998</v>
       </c>
     </row>
     <row r="47" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -4753,40 +4760,40 @@
         <v>54940200</v>
       </c>
       <c r="G47" s="4">
-        <v>41097272.969999999</v>
+        <v>43456973.259999998</v>
       </c>
       <c r="H47" s="5">
-        <v>74.8</v>
+        <v>79.099999999999994</v>
       </c>
       <c r="I47" s="4">
-        <v>4983091.67</v>
+        <v>6585711.0800000001</v>
       </c>
       <c r="J47" s="5">
-        <v>9.07</v>
+        <v>11.99</v>
       </c>
       <c r="K47" s="4">
-        <v>46080364.640000001</v>
+        <v>50042684.340000004</v>
       </c>
       <c r="L47" s="5">
-        <v>83.87</v>
+        <v>91.09</v>
       </c>
       <c r="M47" s="4">
-        <v>8859835.3599999994</v>
+        <v>4897515.66</v>
       </c>
       <c r="N47" s="5">
-        <v>16.13</v>
+        <v>8.91</v>
       </c>
       <c r="O47" s="4">
-        <v>1200986.5</v>
+        <v>576020.80000000005</v>
       </c>
       <c r="P47" s="5">
-        <v>2.19</v>
+        <v>1.05</v>
       </c>
       <c r="Q47" s="4">
-        <v>7658848.8600000003</v>
+        <v>4321494.8600000003</v>
       </c>
       <c r="R47" s="5">
-        <v>13.94</v>
+        <v>7.87</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -4809,40 +4816,40 @@
         <v>11340200</v>
       </c>
       <c r="G48" s="8">
-        <v>9109304.9600000009</v>
+        <v>9457224.25</v>
       </c>
       <c r="H48" s="9">
-        <v>80.33</v>
+        <v>83.4</v>
       </c>
       <c r="I48" s="8">
-        <v>1270099.67</v>
+        <v>1196955.3799999999</v>
       </c>
       <c r="J48" s="9">
-        <v>11.2</v>
+        <v>10.55</v>
       </c>
       <c r="K48" s="8">
-        <v>10379404.630000001</v>
+        <v>10654179.630000001</v>
       </c>
       <c r="L48" s="9">
-        <v>91.53</v>
+        <v>93.95</v>
       </c>
       <c r="M48" s="8">
-        <v>960795.37</v>
+        <v>686020.37</v>
       </c>
       <c r="N48" s="9">
-        <v>8.4700000000000006</v>
+        <v>6.05</v>
       </c>
       <c r="O48" s="8">
-        <v>110079.5</v>
+        <v>30079.5</v>
       </c>
       <c r="P48" s="9">
-        <v>0.97</v>
+        <v>0.27</v>
       </c>
       <c r="Q48" s="8">
-        <v>850715.87</v>
+        <v>655940.87</v>
       </c>
       <c r="R48" s="9">
-        <v>7.5</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="49" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -4865,40 +4872,40 @@
         <v>1300000</v>
       </c>
       <c r="G49" s="12">
-        <v>1079098.5</v>
+        <v>1327407.79</v>
       </c>
       <c r="H49" s="13">
-        <v>83.01</v>
+        <v>102.11</v>
       </c>
       <c r="I49" s="12">
-        <v>303240</v>
+        <v>285605.71000000002</v>
       </c>
       <c r="J49" s="13">
-        <v>23.33</v>
+        <v>21.97</v>
       </c>
       <c r="K49" s="12">
-        <v>1382338.5</v>
+        <v>1613013.5</v>
       </c>
       <c r="L49" s="13">
-        <v>106.33</v>
+        <v>124.08</v>
       </c>
       <c r="M49" s="12">
-        <v>-82338.5</v>
+        <v>-313013.5</v>
       </c>
       <c r="N49" s="13">
-        <v>-6.33</v>
+        <v>-24.08</v>
       </c>
       <c r="O49" s="12">
-        <v>90000</v>
+        <v>10000</v>
       </c>
       <c r="P49" s="13">
-        <v>6.92</v>
+        <v>0.77</v>
       </c>
       <c r="Q49" s="12">
-        <v>-172338.5</v>
+        <v>-323013.5</v>
       </c>
       <c r="R49" s="13">
-        <v>-13.26</v>
+        <v>-24.85</v>
       </c>
     </row>
     <row r="50" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -4977,28 +4984,28 @@
         <v>4320000</v>
       </c>
       <c r="G51" s="12">
-        <v>3004251.7</v>
+        <v>3044681.7</v>
       </c>
       <c r="H51" s="13">
-        <v>69.540000000000006</v>
+        <v>70.48</v>
       </c>
       <c r="I51" s="12">
-        <v>447729.67</v>
+        <v>452529.67</v>
       </c>
       <c r="J51" s="13">
-        <v>10.36</v>
+        <v>10.48</v>
       </c>
       <c r="K51" s="12">
-        <v>3451981.37</v>
+        <v>3497211.37</v>
       </c>
       <c r="L51" s="13">
-        <v>79.91</v>
+        <v>80.95</v>
       </c>
       <c r="M51" s="12">
-        <v>868018.63</v>
+        <v>822788.63</v>
       </c>
       <c r="N51" s="13">
-        <v>20.09</v>
+        <v>19.05</v>
       </c>
       <c r="O51" s="12">
         <v>0</v>
@@ -5007,10 +5014,10 @@
         <v>0</v>
       </c>
       <c r="Q51" s="12">
-        <v>868018.63</v>
+        <v>822788.63</v>
       </c>
       <c r="R51" s="13">
-        <v>20.09</v>
+        <v>19.05</v>
       </c>
     </row>
     <row r="52" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -5033,28 +5040,28 @@
         <v>2020200</v>
       </c>
       <c r="G52" s="12">
-        <v>1770721</v>
+        <v>1829901</v>
       </c>
       <c r="H52" s="13">
-        <v>87.65</v>
+        <v>90.58</v>
       </c>
       <c r="I52" s="12">
-        <v>202330</v>
+        <v>142020</v>
       </c>
       <c r="J52" s="13">
-        <v>10.02</v>
+        <v>7.03</v>
       </c>
       <c r="K52" s="12">
-        <v>1973051</v>
+        <v>1971921</v>
       </c>
       <c r="L52" s="13">
-        <v>97.67</v>
+        <v>97.61</v>
       </c>
       <c r="M52" s="12">
-        <v>47149</v>
+        <v>48279</v>
       </c>
       <c r="N52" s="13">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="O52" s="12">
         <v>20079.5</v>
@@ -5063,10 +5070,10 @@
         <v>0.99</v>
       </c>
       <c r="Q52" s="12">
-        <v>27069.5</v>
+        <v>28199.5</v>
       </c>
       <c r="R52" s="13">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="53" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -5145,40 +5152,40 @@
         <v>13420000</v>
       </c>
       <c r="G54" s="8">
-        <v>10751421.42</v>
+        <v>11285252.42</v>
       </c>
       <c r="H54" s="9">
-        <v>80.11</v>
+        <v>84.09</v>
       </c>
       <c r="I54" s="8">
-        <v>751226</v>
+        <v>1085194.7</v>
       </c>
       <c r="J54" s="9">
-        <v>5.6</v>
+        <v>8.09</v>
       </c>
       <c r="K54" s="8">
-        <v>11502647.42</v>
+        <v>12370447.119999999</v>
       </c>
       <c r="L54" s="9">
-        <v>85.71</v>
+        <v>92.18</v>
       </c>
       <c r="M54" s="8">
-        <v>1917352.58</v>
+        <v>1049552.8799999999</v>
       </c>
       <c r="N54" s="9">
-        <v>14.29</v>
+        <v>7.82</v>
       </c>
       <c r="O54" s="8">
-        <v>497000</v>
+        <v>382034.3</v>
       </c>
       <c r="P54" s="9">
-        <v>3.7</v>
+        <v>2.85</v>
       </c>
       <c r="Q54" s="8">
-        <v>1420352.58</v>
+        <v>667518.57999999996</v>
       </c>
       <c r="R54" s="9">
-        <v>10.58</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="55" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -5257,40 +5264,40 @@
         <v>2700000</v>
       </c>
       <c r="G56" s="12">
-        <v>2049285.35</v>
+        <v>2063116.35</v>
       </c>
       <c r="H56" s="13">
-        <v>75.900000000000006</v>
+        <v>76.41</v>
       </c>
       <c r="I56" s="12">
-        <v>141226</v>
+        <v>259794.7</v>
       </c>
       <c r="J56" s="13">
-        <v>5.23</v>
+        <v>9.6199999999999992</v>
       </c>
       <c r="K56" s="12">
-        <v>2190511.35</v>
+        <v>2322911.0499999998</v>
       </c>
       <c r="L56" s="13">
-        <v>81.13</v>
+        <v>86.03</v>
       </c>
       <c r="M56" s="12">
-        <v>509488.65</v>
+        <v>377088.95</v>
       </c>
       <c r="N56" s="13">
-        <v>18.87</v>
+        <v>13.97</v>
       </c>
       <c r="O56" s="12">
-        <v>497000</v>
+        <v>360034.3</v>
       </c>
       <c r="P56" s="13">
-        <v>18.41</v>
+        <v>13.33</v>
       </c>
       <c r="Q56" s="12">
-        <v>12488.65</v>
+        <v>17054.650000000001</v>
       </c>
       <c r="R56" s="13">
-        <v>0.46</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="57" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -5313,28 +5320,28 @@
         <v>3400000</v>
       </c>
       <c r="G57" s="12">
-        <v>2297925.41</v>
+        <v>2817925.41</v>
       </c>
       <c r="H57" s="13">
-        <v>67.59</v>
+        <v>82.88</v>
       </c>
       <c r="I57" s="12">
-        <v>210000</v>
+        <v>425400</v>
       </c>
       <c r="J57" s="13">
-        <v>6.18</v>
+        <v>12.51</v>
       </c>
       <c r="K57" s="12">
-        <v>2507925.41</v>
+        <v>3243325.41</v>
       </c>
       <c r="L57" s="13">
-        <v>73.760000000000005</v>
+        <v>95.39</v>
       </c>
       <c r="M57" s="12">
-        <v>892074.59</v>
+        <v>156674.59</v>
       </c>
       <c r="N57" s="13">
-        <v>26.24</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="O57" s="12">
         <v>0</v>
@@ -5343,10 +5350,10 @@
         <v>0</v>
       </c>
       <c r="Q57" s="12">
-        <v>892074.59</v>
+        <v>156674.59</v>
       </c>
       <c r="R57" s="13">
-        <v>26.24</v>
+        <v>4.6100000000000003</v>
       </c>
     </row>
     <row r="58" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -5561,16 +5568,16 @@
         <v>14.29</v>
       </c>
       <c r="O61" s="12">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="P61" s="13">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="Q61" s="12">
-        <v>371626.39</v>
+        <v>349626.39</v>
       </c>
       <c r="R61" s="13">
-        <v>14.29</v>
+        <v>13.45</v>
       </c>
     </row>
     <row r="62" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -5761,40 +5768,40 @@
         <v>11720000</v>
       </c>
       <c r="G65" s="8">
-        <v>8155521</v>
+        <v>8537901</v>
       </c>
       <c r="H65" s="9">
-        <v>69.59</v>
+        <v>72.849999999999994</v>
       </c>
       <c r="I65" s="8">
-        <v>1281876</v>
+        <v>1415896</v>
       </c>
       <c r="J65" s="9">
-        <v>10.94</v>
+        <v>12.08</v>
       </c>
       <c r="K65" s="8">
-        <v>9437397</v>
+        <v>9953797</v>
       </c>
       <c r="L65" s="9">
-        <v>80.52</v>
+        <v>84.93</v>
       </c>
       <c r="M65" s="8">
-        <v>2282603</v>
+        <v>1766203</v>
       </c>
       <c r="N65" s="9">
-        <v>19.48</v>
+        <v>15.07</v>
       </c>
       <c r="O65" s="8">
-        <v>30600</v>
+        <v>80600</v>
       </c>
       <c r="P65" s="9">
-        <v>0.26</v>
+        <v>0.69</v>
       </c>
       <c r="Q65" s="8">
-        <v>2252003</v>
+        <v>1685603</v>
       </c>
       <c r="R65" s="9">
-        <v>19.22</v>
+        <v>14.38</v>
       </c>
     </row>
     <row r="66" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -5873,16 +5880,16 @@
         <v>1775000</v>
       </c>
       <c r="G67" s="12">
-        <v>714086</v>
+        <v>717286</v>
       </c>
       <c r="H67" s="13">
-        <v>40.229999999999997</v>
+        <v>40.409999999999997</v>
       </c>
       <c r="I67" s="12">
-        <v>129500</v>
+        <v>126300</v>
       </c>
       <c r="J67" s="13">
-        <v>7.3</v>
+        <v>7.12</v>
       </c>
       <c r="K67" s="12">
         <v>843586</v>
@@ -5929,28 +5936,28 @@
         <v>2820000</v>
       </c>
       <c r="G68" s="12">
-        <v>2021147</v>
+        <v>2400327</v>
       </c>
       <c r="H68" s="13">
-        <v>71.67</v>
+        <v>85.12</v>
       </c>
       <c r="I68" s="12">
-        <v>331410</v>
+        <v>468630</v>
       </c>
       <c r="J68" s="13">
-        <v>11.75</v>
+        <v>16.62</v>
       </c>
       <c r="K68" s="12">
-        <v>2352557</v>
+        <v>2868957</v>
       </c>
       <c r="L68" s="13">
-        <v>83.42</v>
+        <v>101.74</v>
       </c>
       <c r="M68" s="12">
-        <v>467443</v>
+        <v>-48957</v>
       </c>
       <c r="N68" s="13">
-        <v>16.579999999999998</v>
+        <v>-1.74</v>
       </c>
       <c r="O68" s="12">
         <v>600</v>
@@ -5959,10 +5966,10 @@
         <v>0.02</v>
       </c>
       <c r="Q68" s="12">
-        <v>466843</v>
+        <v>-49557</v>
       </c>
       <c r="R68" s="13">
-        <v>16.55</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="69" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -6065,16 +6072,16 @@
         <v>22.9</v>
       </c>
       <c r="O70" s="12">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="P70" s="13">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Q70" s="12">
-        <v>930006</v>
+        <v>880006</v>
       </c>
       <c r="R70" s="13">
-        <v>22.9</v>
+        <v>21.67</v>
       </c>
     </row>
     <row r="71" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -6097,28 +6104,28 @@
         <v>10640000</v>
       </c>
       <c r="G71" s="8">
-        <v>7984077.29</v>
+        <v>8425312.2899999991</v>
       </c>
       <c r="H71" s="9">
-        <v>75.040000000000006</v>
+        <v>79.19</v>
       </c>
       <c r="I71" s="8">
-        <v>644246</v>
+        <v>1198211</v>
       </c>
       <c r="J71" s="9">
-        <v>6.05</v>
+        <v>11.26</v>
       </c>
       <c r="K71" s="8">
-        <v>8628323.2899999991</v>
+        <v>9623523.2899999991</v>
       </c>
       <c r="L71" s="9">
-        <v>81.09</v>
+        <v>90.45</v>
       </c>
       <c r="M71" s="8">
-        <v>2011676.71</v>
+        <v>1016476.71</v>
       </c>
       <c r="N71" s="9">
-        <v>18.91</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="O71" s="8">
         <v>13307</v>
@@ -6127,10 +6134,10 @@
         <v>0.13</v>
       </c>
       <c r="Q71" s="8">
-        <v>1998369.71</v>
+        <v>1003169.71</v>
       </c>
       <c r="R71" s="9">
-        <v>18.78</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="72" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -6153,28 +6160,28 @@
         <v>1140000</v>
       </c>
       <c r="G72" s="12">
-        <v>794453.22</v>
+        <v>825153.22</v>
       </c>
       <c r="H72" s="13">
-        <v>69.69</v>
+        <v>72.38</v>
       </c>
       <c r="I72" s="12">
-        <v>30010</v>
+        <v>28310</v>
       </c>
       <c r="J72" s="13">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="K72" s="12">
-        <v>824463.22</v>
+        <v>853463.22</v>
       </c>
       <c r="L72" s="13">
-        <v>72.319999999999993</v>
+        <v>74.87</v>
       </c>
       <c r="M72" s="12">
-        <v>315536.78000000003</v>
+        <v>286536.78000000003</v>
       </c>
       <c r="N72" s="13">
-        <v>27.68</v>
+        <v>25.13</v>
       </c>
       <c r="O72" s="12">
         <v>0</v>
@@ -6183,10 +6190,10 @@
         <v>0</v>
       </c>
       <c r="Q72" s="12">
-        <v>315536.78000000003</v>
+        <v>286536.78000000003</v>
       </c>
       <c r="R72" s="13">
-        <v>27.68</v>
+        <v>25.13</v>
       </c>
     </row>
     <row r="73" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -6215,22 +6222,22 @@
         <v>89.45</v>
       </c>
       <c r="I73" s="12">
-        <v>10400</v>
+        <v>10000</v>
       </c>
       <c r="J73" s="13">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="K73" s="12">
-        <v>1978209.37</v>
+        <v>1977809.37</v>
       </c>
       <c r="L73" s="13">
-        <v>89.92</v>
+        <v>89.9</v>
       </c>
       <c r="M73" s="12">
-        <v>221790.63</v>
+        <v>222190.63</v>
       </c>
       <c r="N73" s="13">
-        <v>10.08</v>
+        <v>10.1</v>
       </c>
       <c r="O73" s="12">
         <v>0</v>
@@ -6239,10 +6246,10 @@
         <v>0</v>
       </c>
       <c r="Q73" s="12">
-        <v>221790.63</v>
+        <v>222190.63</v>
       </c>
       <c r="R73" s="13">
-        <v>10.08</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="74" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -6265,16 +6272,16 @@
         <v>700000</v>
       </c>
       <c r="G74" s="12">
-        <v>596226</v>
+        <v>434411</v>
       </c>
       <c r="H74" s="13">
-        <v>85.18</v>
+        <v>62.06</v>
       </c>
       <c r="I74" s="12">
-        <v>24000</v>
+        <v>185815</v>
       </c>
       <c r="J74" s="13">
-        <v>3.43</v>
+        <v>26.55</v>
       </c>
       <c r="K74" s="12">
         <v>620226</v>
@@ -6327,22 +6334,22 @@
         <v>80.489999999999995</v>
       </c>
       <c r="I75" s="12">
-        <v>200000</v>
+        <v>230300</v>
       </c>
       <c r="J75" s="13">
-        <v>8.6999999999999993</v>
+        <v>10.01</v>
       </c>
       <c r="K75" s="12">
-        <v>2051170</v>
+        <v>2081470</v>
       </c>
       <c r="L75" s="13">
-        <v>89.18</v>
+        <v>90.5</v>
       </c>
       <c r="M75" s="12">
-        <v>248830</v>
+        <v>218530</v>
       </c>
       <c r="N75" s="13">
-        <v>10.82</v>
+        <v>9.5</v>
       </c>
       <c r="O75" s="12">
         <v>0</v>
@@ -6351,10 +6358,10 @@
         <v>0</v>
       </c>
       <c r="Q75" s="12">
-        <v>248830</v>
+        <v>218530</v>
       </c>
       <c r="R75" s="13">
-        <v>10.82</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="76" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -6377,28 +6384,28 @@
         <v>3300000</v>
       </c>
       <c r="G76" s="12">
-        <v>2008092.6</v>
+        <v>2580442.6</v>
       </c>
       <c r="H76" s="13">
-        <v>60.85</v>
+        <v>78.2</v>
       </c>
       <c r="I76" s="12">
-        <v>234633</v>
+        <v>598583</v>
       </c>
       <c r="J76" s="13">
-        <v>7.11</v>
+        <v>18.14</v>
       </c>
       <c r="K76" s="12">
-        <v>2242725.6</v>
+        <v>3179025.6</v>
       </c>
       <c r="L76" s="13">
-        <v>67.959999999999994</v>
+        <v>96.33</v>
       </c>
       <c r="M76" s="12">
-        <v>1057274.3999999999</v>
+        <v>120974.39999999999</v>
       </c>
       <c r="N76" s="13">
-        <v>32.04</v>
+        <v>3.67</v>
       </c>
       <c r="O76" s="12">
         <v>0</v>
@@ -6407,10 +6414,10 @@
         <v>0</v>
       </c>
       <c r="Q76" s="12">
-        <v>1057274.3999999999</v>
+        <v>120974.39999999999</v>
       </c>
       <c r="R76" s="13">
-        <v>32.04</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="77" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -6601,40 +6608,40 @@
         <v>7820000</v>
       </c>
       <c r="G80" s="8">
-        <v>5096948.3</v>
+        <v>5751283.2999999998</v>
       </c>
       <c r="H80" s="9">
-        <v>65.180000000000007</v>
+        <v>73.55</v>
       </c>
       <c r="I80" s="8">
-        <v>1035644</v>
+        <v>1689454</v>
       </c>
       <c r="J80" s="9">
-        <v>13.24</v>
+        <v>21.6</v>
       </c>
       <c r="K80" s="8">
-        <v>6132592.2999999998</v>
+        <v>7440737.2999999998</v>
       </c>
       <c r="L80" s="9">
-        <v>78.42</v>
+        <v>95.15</v>
       </c>
       <c r="M80" s="8">
-        <v>1687407.7</v>
+        <v>379262.7</v>
       </c>
       <c r="N80" s="9">
-        <v>21.58</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="O80" s="8">
-        <v>550000</v>
+        <v>70000</v>
       </c>
       <c r="P80" s="9">
-        <v>7.03</v>
+        <v>0.9</v>
       </c>
       <c r="Q80" s="8">
-        <v>1137407.7</v>
+        <v>309262.7</v>
       </c>
       <c r="R80" s="9">
-        <v>14.54</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="81" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -6657,28 +6664,28 @@
         <v>1000000</v>
       </c>
       <c r="G81" s="12">
-        <v>555928</v>
+        <v>575428</v>
       </c>
       <c r="H81" s="13">
-        <v>55.59</v>
+        <v>57.54</v>
       </c>
       <c r="I81" s="12">
-        <v>21500</v>
+        <v>0</v>
       </c>
       <c r="J81" s="13">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="K81" s="12">
-        <v>577428</v>
+        <v>575428</v>
       </c>
       <c r="L81" s="13">
-        <v>57.74</v>
+        <v>57.54</v>
       </c>
       <c r="M81" s="12">
-        <v>422572</v>
+        <v>424572</v>
       </c>
       <c r="N81" s="13">
-        <v>42.26</v>
+        <v>42.46</v>
       </c>
       <c r="O81" s="12">
         <v>0</v>
@@ -6687,10 +6694,10 @@
         <v>0</v>
       </c>
       <c r="Q81" s="12">
-        <v>422572</v>
+        <v>424572</v>
       </c>
       <c r="R81" s="13">
-        <v>42.26</v>
+        <v>42.46</v>
       </c>
     </row>
     <row r="82" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -6713,28 +6720,28 @@
         <v>1200000</v>
       </c>
       <c r="G82" s="12">
-        <v>1386714</v>
+        <v>1540449</v>
       </c>
       <c r="H82" s="13">
-        <v>115.56</v>
+        <v>128.37</v>
       </c>
       <c r="I82" s="12">
-        <v>171550</v>
+        <v>15350</v>
       </c>
       <c r="J82" s="13">
-        <v>14.3</v>
+        <v>1.28</v>
       </c>
       <c r="K82" s="12">
-        <v>1558264</v>
+        <v>1555799</v>
       </c>
       <c r="L82" s="13">
-        <v>129.86000000000001</v>
+        <v>129.65</v>
       </c>
       <c r="M82" s="12">
-        <v>-358264</v>
+        <v>-355799</v>
       </c>
       <c r="N82" s="13">
-        <v>-29.86</v>
+        <v>-29.65</v>
       </c>
       <c r="O82" s="12">
         <v>0</v>
@@ -6743,10 +6750,10 @@
         <v>0</v>
       </c>
       <c r="Q82" s="12">
-        <v>-358264</v>
+        <v>-355799</v>
       </c>
       <c r="R82" s="13">
-        <v>-29.86</v>
+        <v>-29.65</v>
       </c>
     </row>
     <row r="83" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -6825,28 +6832,28 @@
         <v>3000000</v>
       </c>
       <c r="G84" s="12">
-        <v>2265549</v>
+        <v>2746649</v>
       </c>
       <c r="H84" s="13">
-        <v>75.52</v>
+        <v>91.55</v>
       </c>
       <c r="I84" s="12">
-        <v>247094</v>
+        <v>441244</v>
       </c>
       <c r="J84" s="13">
-        <v>8.24</v>
+        <v>14.71</v>
       </c>
       <c r="K84" s="12">
-        <v>2512643</v>
+        <v>3187893</v>
       </c>
       <c r="L84" s="13">
-        <v>83.75</v>
+        <v>106.26</v>
       </c>
       <c r="M84" s="12">
-        <v>487357</v>
+        <v>-187893</v>
       </c>
       <c r="N84" s="13">
-        <v>16.25</v>
+        <v>-6.26</v>
       </c>
       <c r="O84" s="12">
         <v>0</v>
@@ -6855,10 +6862,10 @@
         <v>0</v>
       </c>
       <c r="Q84" s="12">
-        <v>487357</v>
+        <v>-187893</v>
       </c>
       <c r="R84" s="13">
-        <v>16.25</v>
+        <v>-6.26</v>
       </c>
     </row>
     <row r="85" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -7055,22 +7062,22 @@
         <v>21.41</v>
       </c>
       <c r="I88" s="12">
-        <v>116600</v>
+        <v>111160</v>
       </c>
       <c r="J88" s="13">
-        <v>53</v>
+        <v>50.53</v>
       </c>
       <c r="K88" s="12">
-        <v>163705</v>
+        <v>158265</v>
       </c>
       <c r="L88" s="13">
-        <v>74.41</v>
+        <v>71.94</v>
       </c>
       <c r="M88" s="12">
-        <v>56295</v>
+        <v>61735</v>
       </c>
       <c r="N88" s="13">
-        <v>25.59</v>
+        <v>28.06</v>
       </c>
       <c r="O88" s="12">
         <v>0</v>
@@ -7079,10 +7086,10 @@
         <v>0</v>
       </c>
       <c r="Q88" s="12">
-        <v>56295</v>
+        <v>61735</v>
       </c>
       <c r="R88" s="13">
-        <v>25.59</v>
+        <v>28.06</v>
       </c>
     </row>
     <row r="89" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -7111,34 +7118,34 @@
         <v>7.57</v>
       </c>
       <c r="I89" s="12">
-        <v>478900</v>
+        <v>1121700</v>
       </c>
       <c r="J89" s="13">
-        <v>47.89</v>
+        <v>112.17</v>
       </c>
       <c r="K89" s="12">
-        <v>554610</v>
+        <v>1197410</v>
       </c>
       <c r="L89" s="13">
-        <v>55.46</v>
+        <v>119.74</v>
       </c>
       <c r="M89" s="12">
-        <v>445390</v>
+        <v>-197410</v>
       </c>
       <c r="N89" s="13">
-        <v>44.54</v>
+        <v>-19.739999999999998</v>
       </c>
       <c r="O89" s="12">
-        <v>550000</v>
+        <v>70000</v>
       </c>
       <c r="P89" s="13">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="Q89" s="12">
-        <v>-104610</v>
+        <v>-267410</v>
       </c>
       <c r="R89" s="13">
-        <v>-10.46</v>
+        <v>-26.74</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
@@ -7161,40 +7168,40 @@
         <v>9800000</v>
       </c>
       <c r="G90" s="4">
-        <v>5612006.6399999997</v>
+        <v>5667604.7999999998</v>
       </c>
       <c r="H90" s="5">
-        <v>57.27</v>
+        <v>57.83</v>
       </c>
       <c r="I90" s="4">
-        <v>863008.31</v>
+        <v>1080307.1499999999</v>
       </c>
       <c r="J90" s="5">
-        <v>8.81</v>
+        <v>11.02</v>
       </c>
       <c r="K90" s="4">
-        <v>6475014.9500000002</v>
+        <v>6747911.9500000002</v>
       </c>
       <c r="L90" s="5">
-        <v>66.069999999999993</v>
+        <v>68.86</v>
       </c>
       <c r="M90" s="4">
-        <v>3324985.05</v>
+        <v>3052088.05</v>
       </c>
       <c r="N90" s="5">
-        <v>33.93</v>
+        <v>31.14</v>
       </c>
       <c r="O90" s="4">
-        <v>3152551.54</v>
+        <v>2977599.54</v>
       </c>
       <c r="P90" s="5">
-        <v>32.17</v>
+        <v>30.38</v>
       </c>
       <c r="Q90" s="4">
-        <v>172433.51</v>
+        <v>74488.509999999995</v>
       </c>
       <c r="R90" s="5">
-        <v>1.76</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="91" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -7217,40 +7224,40 @@
         <v>9800000</v>
       </c>
       <c r="G91" s="8">
-        <v>5612006.6399999997</v>
+        <v>5667604.7999999998</v>
       </c>
       <c r="H91" s="9">
-        <v>57.27</v>
+        <v>57.83</v>
       </c>
       <c r="I91" s="8">
-        <v>863008.31</v>
+        <v>1080307.1499999999</v>
       </c>
       <c r="J91" s="9">
-        <v>8.81</v>
+        <v>11.02</v>
       </c>
       <c r="K91" s="8">
-        <v>6475014.9500000002</v>
+        <v>6747911.9500000002</v>
       </c>
       <c r="L91" s="9">
-        <v>66.069999999999993</v>
+        <v>68.86</v>
       </c>
       <c r="M91" s="8">
-        <v>3324985.05</v>
+        <v>3052088.05</v>
       </c>
       <c r="N91" s="9">
-        <v>33.93</v>
+        <v>31.14</v>
       </c>
       <c r="O91" s="8">
-        <v>3152551.54</v>
+        <v>2977599.54</v>
       </c>
       <c r="P91" s="9">
-        <v>32.17</v>
+        <v>30.38</v>
       </c>
       <c r="Q91" s="8">
-        <v>172433.51</v>
+        <v>74488.509999999995</v>
       </c>
       <c r="R91" s="9">
-        <v>1.76</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="92" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
@@ -7273,40 +7280,40 @@
         <v>4305000</v>
       </c>
       <c r="G92" s="12">
-        <v>2709448.15</v>
+        <v>2759241.31</v>
       </c>
       <c r="H92" s="13">
-        <v>62.94</v>
+        <v>64.09</v>
       </c>
       <c r="I92" s="12">
-        <v>342120.31</v>
+        <v>457819.15</v>
       </c>
       <c r="J92" s="13">
-        <v>7.95</v>
+        <v>10.63</v>
       </c>
       <c r="K92" s="12">
-        <v>3051568.46</v>
+        <v>3217060.46</v>
       </c>
       <c r="L92" s="13">
-        <v>70.88</v>
+        <v>74.73</v>
       </c>
       <c r="M92" s="12">
-        <v>1253431.54</v>
+        <v>1087939.54</v>
       </c>
       <c r="N92" s="13">
-        <v>29.12</v>
+        <v>25.27</v>
       </c>
       <c r="O92" s="12">
-        <v>1251289.54</v>
+        <v>1250099.54</v>
       </c>
       <c r="P92" s="13">
-        <v>29.07</v>
+        <v>29.04</v>
       </c>
       <c r="Q92" s="12">
-        <v>2142</v>
+        <v>-162160</v>
       </c>
       <c r="R92" s="13">
-        <v>0.05</v>
+        <v>-3.77</v>
       </c>
     </row>
     <row r="93" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -7335,34 +7342,34 @@
         <v>61.42</v>
       </c>
       <c r="I93" s="12">
-        <v>292750</v>
+        <v>292500</v>
       </c>
       <c r="J93" s="13">
         <v>9.32</v>
       </c>
       <c r="K93" s="12">
-        <v>2221277.4900000002</v>
+        <v>2221027.4900000002</v>
       </c>
       <c r="L93" s="13">
-        <v>70.739999999999995</v>
+        <v>70.73</v>
       </c>
       <c r="M93" s="12">
-        <v>918722.51</v>
+        <v>918972.51</v>
       </c>
       <c r="N93" s="13">
-        <v>29.26</v>
+        <v>29.27</v>
       </c>
       <c r="O93" s="12">
-        <v>1247500</v>
+        <v>1227500</v>
       </c>
       <c r="P93" s="13">
-        <v>39.729999999999997</v>
+        <v>39.090000000000003</v>
       </c>
       <c r="Q93" s="12">
-        <v>-328777.49</v>
+        <v>-308527.49</v>
       </c>
       <c r="R93" s="13">
-        <v>-10.47</v>
+        <v>-9.83</v>
       </c>
     </row>
     <row r="94" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -7385,40 +7392,40 @@
         <v>2355000</v>
       </c>
       <c r="G94" s="12">
-        <v>974031</v>
+        <v>979836</v>
       </c>
       <c r="H94" s="13">
-        <v>41.36</v>
+        <v>41.61</v>
       </c>
       <c r="I94" s="12">
-        <v>228138</v>
+        <v>329988</v>
       </c>
       <c r="J94" s="13">
-        <v>9.69</v>
+        <v>14.01</v>
       </c>
       <c r="K94" s="12">
-        <v>1202169</v>
+        <v>1309824</v>
       </c>
       <c r="L94" s="13">
-        <v>51.05</v>
+        <v>55.62</v>
       </c>
       <c r="M94" s="12">
-        <v>1152831</v>
+        <v>1045176</v>
       </c>
       <c r="N94" s="13">
-        <v>48.95</v>
+        <v>44.38</v>
       </c>
       <c r="O94" s="12">
-        <v>653762</v>
+        <v>500000</v>
       </c>
       <c r="P94" s="13">
-        <v>27.76</v>
+        <v>21.23</v>
       </c>
       <c r="Q94" s="12">
-        <v>499069</v>
+        <v>545176</v>
       </c>
       <c r="R94" s="13">
-        <v>21.19</v>
+        <v>23.15</v>
       </c>
     </row>
     <row r="95" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -7432,49 +7439,49 @@
         <v>119421186</v>
       </c>
       <c r="D95" s="4">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="E95" s="4">
         <v>0</v>
       </c>
       <c r="F95" s="4">
-        <v>119421186</v>
+        <v>119721186</v>
       </c>
       <c r="G95" s="4">
-        <v>89759669.310000002</v>
+        <v>90342515.459999993</v>
       </c>
       <c r="H95" s="5">
-        <v>75.16</v>
+        <v>75.459999999999994</v>
       </c>
       <c r="I95" s="4">
-        <v>9427709.6799999997</v>
+        <v>9196107.3599999994</v>
       </c>
       <c r="J95" s="5">
-        <v>7.89</v>
+        <v>7.68</v>
       </c>
       <c r="K95" s="4">
-        <v>99187378.989999995</v>
+        <v>99538622.819999993</v>
       </c>
       <c r="L95" s="5">
-        <v>83.06</v>
+        <v>83.14</v>
       </c>
       <c r="M95" s="4">
-        <v>20233807.010000002</v>
+        <v>20182563.18</v>
       </c>
       <c r="N95" s="5">
-        <v>16.940000000000001</v>
+        <v>16.86</v>
       </c>
       <c r="O95" s="4">
-        <v>5807810.6299999999</v>
+        <v>5706965.8700000001</v>
       </c>
       <c r="P95" s="5">
-        <v>4.8600000000000003</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="Q95" s="4">
-        <v>14425996.380000001</v>
+        <v>14475597.310000001</v>
       </c>
       <c r="R95" s="5">
-        <v>12.08</v>
+        <v>12.09</v>
       </c>
     </row>
     <row r="96" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -7497,28 +7504,28 @@
         <v>29200000</v>
       </c>
       <c r="G96" s="8">
-        <v>18184522.469999999</v>
+        <v>18221614.789999999</v>
       </c>
       <c r="H96" s="9">
-        <v>62.28</v>
+        <v>62.4</v>
       </c>
       <c r="I96" s="8">
-        <v>5051979.6500000004</v>
+        <v>5019002.33</v>
       </c>
       <c r="J96" s="9">
-        <v>17.3</v>
+        <v>17.190000000000001</v>
       </c>
       <c r="K96" s="8">
-        <v>23236502.120000001</v>
+        <v>23240617.120000001</v>
       </c>
       <c r="L96" s="9">
-        <v>79.58</v>
+        <v>79.59</v>
       </c>
       <c r="M96" s="8">
-        <v>5963497.8799999999</v>
+        <v>5959382.8799999999</v>
       </c>
       <c r="N96" s="9">
-        <v>20.420000000000002</v>
+        <v>20.41</v>
       </c>
       <c r="O96" s="8">
         <v>5005423.37</v>
@@ -7527,10 +7534,10 @@
         <v>17.14</v>
       </c>
       <c r="Q96" s="8">
-        <v>958074.51</v>
+        <v>953959.51</v>
       </c>
       <c r="R96" s="9">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="97" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -7553,28 +7560,28 @@
         <v>3261268.89</v>
       </c>
       <c r="G97" s="12">
-        <v>2253215.37</v>
+        <v>2259445.37</v>
       </c>
       <c r="H97" s="13">
-        <v>69.09</v>
+        <v>69.28</v>
       </c>
       <c r="I97" s="12">
-        <v>944200</v>
+        <v>942085</v>
       </c>
       <c r="J97" s="13">
-        <v>28.95</v>
+        <v>28.89</v>
       </c>
       <c r="K97" s="12">
-        <v>3197415.37</v>
+        <v>3201530.37</v>
       </c>
       <c r="L97" s="13">
-        <v>98.04</v>
+        <v>98.17</v>
       </c>
       <c r="M97" s="12">
-        <v>63853.52</v>
+        <v>59738.52</v>
       </c>
       <c r="N97" s="13">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="O97" s="12">
         <v>0</v>
@@ -7583,10 +7590,10 @@
         <v>0</v>
       </c>
       <c r="Q97" s="12">
-        <v>63853.52</v>
+        <v>59738.52</v>
       </c>
       <c r="R97" s="13">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="98" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -7609,16 +7616,16 @@
         <v>4780425.63</v>
       </c>
       <c r="G98" s="12">
-        <v>3473506.14</v>
+        <v>3479619.36</v>
       </c>
       <c r="H98" s="13">
-        <v>72.66</v>
+        <v>72.790000000000006</v>
       </c>
       <c r="I98" s="12">
-        <v>642755.75</v>
+        <v>636642.53</v>
       </c>
       <c r="J98" s="13">
-        <v>13.45</v>
+        <v>13.32</v>
       </c>
       <c r="K98" s="12">
         <v>4116261.89</v>
@@ -7665,16 +7672,16 @@
         <v>8310076.75</v>
       </c>
       <c r="G99" s="12">
-        <v>3428104.23</v>
+        <v>3452853.33</v>
       </c>
       <c r="H99" s="13">
-        <v>41.25</v>
+        <v>41.55</v>
       </c>
       <c r="I99" s="12">
-        <v>3209523.9</v>
+        <v>3184774.8</v>
       </c>
       <c r="J99" s="13">
-        <v>38.619999999999997</v>
+        <v>38.32</v>
       </c>
       <c r="K99" s="12">
         <v>6637628.1299999999</v>
@@ -7833,28 +7840,28 @@
         <v>1000000</v>
       </c>
       <c r="G102" s="8">
-        <v>533379</v>
+        <v>543339</v>
       </c>
       <c r="H102" s="9">
-        <v>53.34</v>
+        <v>54.33</v>
       </c>
       <c r="I102" s="8">
-        <v>31620</v>
+        <v>54620</v>
       </c>
       <c r="J102" s="9">
-        <v>3.16</v>
+        <v>5.46</v>
       </c>
       <c r="K102" s="8">
-        <v>564999</v>
+        <v>597959</v>
       </c>
       <c r="L102" s="9">
-        <v>56.5</v>
+        <v>59.8</v>
       </c>
       <c r="M102" s="8">
-        <v>435001</v>
+        <v>402041</v>
       </c>
       <c r="N102" s="9">
-        <v>43.5</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="O102" s="8">
         <v>0</v>
@@ -7863,10 +7870,10 @@
         <v>0</v>
       </c>
       <c r="Q102" s="8">
-        <v>435001</v>
+        <v>402041</v>
       </c>
       <c r="R102" s="9">
-        <v>43.5</v>
+        <v>40.200000000000003</v>
       </c>
     </row>
     <row r="103" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -7889,28 +7896,28 @@
         <v>886600</v>
       </c>
       <c r="G103" s="12">
-        <v>462989</v>
+        <v>472949</v>
       </c>
       <c r="H103" s="13">
-        <v>52.22</v>
+        <v>53.34</v>
       </c>
       <c r="I103" s="12">
-        <v>19370</v>
+        <v>42370</v>
       </c>
       <c r="J103" s="13">
-        <v>2.1800000000000002</v>
+        <v>4.78</v>
       </c>
       <c r="K103" s="12">
-        <v>482359</v>
+        <v>515319</v>
       </c>
       <c r="L103" s="13">
-        <v>54.41</v>
+        <v>58.12</v>
       </c>
       <c r="M103" s="12">
-        <v>404241</v>
+        <v>371281</v>
       </c>
       <c r="N103" s="13">
-        <v>45.59</v>
+        <v>41.88</v>
       </c>
       <c r="O103" s="12">
         <v>0</v>
@@ -7919,10 +7926,10 @@
         <v>0</v>
       </c>
       <c r="Q103" s="12">
-        <v>404241</v>
+        <v>371281</v>
       </c>
       <c r="R103" s="13">
-        <v>45.59</v>
+        <v>41.88</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
@@ -8169,16 +8176,16 @@
         <v>10194186</v>
       </c>
       <c r="G108" s="8">
-        <v>5014823.4400000004</v>
+        <v>5480268.4400000004</v>
       </c>
       <c r="H108" s="9">
-        <v>49.19</v>
+        <v>53.76</v>
       </c>
       <c r="I108" s="8">
-        <v>4162577.8</v>
+        <v>3697132.8</v>
       </c>
       <c r="J108" s="9">
-        <v>40.83</v>
+        <v>36.270000000000003</v>
       </c>
       <c r="K108" s="8">
         <v>9177401.2400000002</v>
@@ -8193,16 +8200,16 @@
         <v>9.9700000000000006</v>
       </c>
       <c r="O108" s="8">
-        <v>800844.76</v>
+        <v>700000</v>
       </c>
       <c r="P108" s="9">
-        <v>7.86</v>
+        <v>6.87</v>
       </c>
       <c r="Q108" s="8">
-        <v>215940</v>
+        <v>316784.76</v>
       </c>
       <c r="R108" s="9">
-        <v>2.12</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="109" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -8225,16 +8232,16 @@
         <v>5612100</v>
       </c>
       <c r="G109" s="12">
-        <v>2744700.64</v>
+        <v>2988950.64</v>
       </c>
       <c r="H109" s="13">
-        <v>48.91</v>
+        <v>53.26</v>
       </c>
       <c r="I109" s="12">
-        <v>1933071.8</v>
+        <v>1688821.8</v>
       </c>
       <c r="J109" s="13">
-        <v>34.44</v>
+        <v>30.09</v>
       </c>
       <c r="K109" s="12">
         <v>4677772.4400000004</v>
@@ -8249,16 +8256,16 @@
         <v>16.649999999999999</v>
       </c>
       <c r="O109" s="12">
-        <v>700944.56</v>
+        <v>700000</v>
       </c>
       <c r="P109" s="13">
-        <v>12.49</v>
+        <v>12.47</v>
       </c>
       <c r="Q109" s="12">
-        <v>233383</v>
+        <v>234327.56</v>
       </c>
       <c r="R109" s="13">
-        <v>4.16</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="110" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -8281,16 +8288,16 @@
         <v>4582086</v>
       </c>
       <c r="G110" s="12">
-        <v>2270122.7999999998</v>
+        <v>2491317.7999999998</v>
       </c>
       <c r="H110" s="13">
-        <v>49.54</v>
+        <v>54.37</v>
       </c>
       <c r="I110" s="12">
-        <v>2229506</v>
+        <v>2008311</v>
       </c>
       <c r="J110" s="13">
-        <v>48.66</v>
+        <v>43.83</v>
       </c>
       <c r="K110" s="12">
         <v>4499628.8</v>
@@ -8305,16 +8312,16 @@
         <v>1.8</v>
       </c>
       <c r="O110" s="12">
-        <v>99900.2</v>
+        <v>0</v>
       </c>
       <c r="P110" s="13">
-        <v>2.1800000000000002</v>
+        <v>0</v>
       </c>
       <c r="Q110" s="12">
-        <v>-17443</v>
+        <v>82457.2</v>
       </c>
       <c r="R110" s="13">
-        <v>-0.38</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="111" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -8328,37 +8335,37 @@
         <v>78027000</v>
       </c>
       <c r="D111" s="8">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="E111" s="8">
         <v>0</v>
       </c>
       <c r="F111" s="8">
-        <v>78027000</v>
+        <v>78327000</v>
       </c>
       <c r="G111" s="8">
-        <v>65204992.659999996</v>
+        <v>65275341.490000002</v>
       </c>
       <c r="H111" s="9">
-        <v>83.57</v>
+        <v>83.34</v>
       </c>
       <c r="I111" s="8">
-        <v>65990.23</v>
+        <v>309810.23</v>
       </c>
       <c r="J111" s="9">
-        <v>0.08</v>
+        <v>0.4</v>
       </c>
       <c r="K111" s="8">
-        <v>65270982.890000001</v>
+        <v>65585151.719999999</v>
       </c>
       <c r="L111" s="9">
-        <v>83.65</v>
+        <v>83.73</v>
       </c>
       <c r="M111" s="8">
-        <v>12756017.109999999</v>
+        <v>12741848.279999999</v>
       </c>
       <c r="N111" s="9">
-        <v>16.350000000000001</v>
+        <v>16.27</v>
       </c>
       <c r="O111" s="8">
         <v>1542.5</v>
@@ -8367,10 +8374,10 @@
         <v>0</v>
       </c>
       <c r="Q111" s="8">
-        <v>12754474.609999999</v>
+        <v>12740305.779999999</v>
       </c>
       <c r="R111" s="9">
-        <v>16.350000000000001</v>
+        <v>16.27</v>
       </c>
     </row>
     <row r="112" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -8393,28 +8400,28 @@
         <v>640000</v>
       </c>
       <c r="G112" s="12">
-        <v>258912.5</v>
+        <v>260752.5</v>
       </c>
       <c r="H112" s="13">
-        <v>40.46</v>
+        <v>40.74</v>
       </c>
       <c r="I112" s="12">
-        <v>5190</v>
+        <v>114350</v>
       </c>
       <c r="J112" s="13">
-        <v>0.81</v>
+        <v>17.87</v>
       </c>
       <c r="K112" s="12">
-        <v>264102.5</v>
+        <v>375102.5</v>
       </c>
       <c r="L112" s="13">
-        <v>41.27</v>
+        <v>58.61</v>
       </c>
       <c r="M112" s="12">
-        <v>375897.5</v>
+        <v>264897.5</v>
       </c>
       <c r="N112" s="13">
-        <v>58.73</v>
+        <v>41.39</v>
       </c>
       <c r="O112" s="12">
         <v>1542.5</v>
@@ -8423,10 +8430,10 @@
         <v>0.24</v>
       </c>
       <c r="Q112" s="12">
-        <v>374355</v>
+        <v>263355</v>
       </c>
       <c r="R112" s="13">
-        <v>58.49</v>
+        <v>41.15</v>
       </c>
     </row>
     <row r="113" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -8440,37 +8447,37 @@
         <v>2387000</v>
       </c>
       <c r="D113" s="12">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="E113" s="12">
         <v>0</v>
       </c>
       <c r="F113" s="12">
-        <v>2387000</v>
+        <v>2687000</v>
       </c>
       <c r="G113" s="12">
-        <v>2690254.07</v>
+        <v>2719254.07</v>
       </c>
       <c r="H113" s="13">
-        <v>112.7</v>
+        <v>101.2</v>
       </c>
       <c r="I113" s="12">
-        <v>60800.23</v>
+        <v>34460.230000000003</v>
       </c>
       <c r="J113" s="13">
-        <v>2.5499999999999998</v>
+        <v>1.28</v>
       </c>
       <c r="K113" s="12">
-        <v>2751054.3</v>
+        <v>2753714.3</v>
       </c>
       <c r="L113" s="13">
-        <v>115.25</v>
+        <v>102.48</v>
       </c>
       <c r="M113" s="12">
-        <v>-364054.3</v>
+        <v>-66714.3</v>
       </c>
       <c r="N113" s="13">
-        <v>-15.25</v>
+        <v>-2.48</v>
       </c>
       <c r="O113" s="12">
         <v>0</v>
@@ -8479,10 +8486,10 @@
         <v>0</v>
       </c>
       <c r="Q113" s="12">
-        <v>-364054.3</v>
+        <v>-66714.3</v>
       </c>
       <c r="R113" s="13">
-        <v>-15.25</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.25">
@@ -8505,28 +8512,28 @@
         <v>75000000</v>
       </c>
       <c r="G114" s="12">
-        <v>62255826.090000004</v>
+        <v>62295334.920000002</v>
       </c>
       <c r="H114" s="13">
-        <v>83.01</v>
+        <v>83.06</v>
       </c>
       <c r="I114" s="12">
-        <v>0</v>
+        <v>161000</v>
       </c>
       <c r="J114" s="13">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="K114" s="12">
-        <v>62255826.090000004</v>
+        <v>62456334.920000002</v>
       </c>
       <c r="L114" s="13">
-        <v>83.01</v>
+        <v>83.28</v>
       </c>
       <c r="M114" s="12">
-        <v>12744173.91</v>
+        <v>12543665.08</v>
       </c>
       <c r="N114" s="13">
-        <v>16.989999999999998</v>
+        <v>16.72</v>
       </c>
       <c r="O114" s="12">
         <v>0</v>
@@ -8535,10 +8542,10 @@
         <v>0</v>
       </c>
       <c r="Q114" s="12">
-        <v>12744173.91</v>
+        <v>12543665.08</v>
       </c>
       <c r="R114" s="13">
-        <v>16.989999999999998</v>
+        <v>16.72</v>
       </c>
     </row>
     <row r="115" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -8718,49 +8725,49 @@
         <v>230702200</v>
       </c>
       <c r="D118" s="14">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="E118" s="14">
         <v>0</v>
       </c>
       <c r="F118" s="14">
-        <v>230702200</v>
+        <v>231002200</v>
       </c>
       <c r="G118" s="14">
-        <v>160641178.43000001</v>
+        <v>163791189.16999999</v>
       </c>
       <c r="H118" s="15">
-        <v>69.63</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="I118" s="14">
-        <v>30238022.82</v>
+        <v>32958449.760000002</v>
       </c>
       <c r="J118" s="15">
-        <v>13.11</v>
+        <v>14.27</v>
       </c>
       <c r="K118" s="14">
-        <v>190879201.25</v>
+        <v>196749638.93000001</v>
       </c>
       <c r="L118" s="15">
-        <v>82.74</v>
+        <v>85.17</v>
       </c>
       <c r="M118" s="14">
-        <v>39822998.75</v>
+        <v>34252561.07</v>
       </c>
       <c r="N118" s="15">
-        <v>17.260000000000002</v>
+        <v>14.83</v>
       </c>
       <c r="O118" s="14">
-        <v>11542148.67</v>
+        <v>11090586.210000001</v>
       </c>
       <c r="P118" s="15">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q118" s="14">
-        <v>28280850.079999998</v>
+        <v>23161974.859999999</v>
       </c>
       <c r="R118" s="15">
-        <v>12.26</v>
+        <v>10.029999999999999</v>
       </c>
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
@@ -8777,46 +8784,46 @@
         <v>74571</v>
       </c>
       <c r="E119" s="4">
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="F119" s="4">
-        <v>101372727.95</v>
+        <v>101370977.95</v>
       </c>
       <c r="G119" s="4">
-        <v>30562243.989999998</v>
+        <v>32165960.289999999</v>
       </c>
       <c r="H119" s="5">
-        <v>30.15</v>
+        <v>31.73</v>
       </c>
       <c r="I119" s="4">
-        <v>16385336.68</v>
+        <v>17954117.379999999</v>
       </c>
       <c r="J119" s="5">
-        <v>16.16</v>
+        <v>17.71</v>
       </c>
       <c r="K119" s="4">
-        <v>46947580.670000002</v>
+        <v>50120077.670000002</v>
       </c>
       <c r="L119" s="5">
-        <v>46.31</v>
+        <v>49.44</v>
       </c>
       <c r="M119" s="4">
-        <v>54425147.280000001</v>
+        <v>51250900.280000001</v>
       </c>
       <c r="N119" s="5">
-        <v>53.69</v>
+        <v>50.56</v>
       </c>
       <c r="O119" s="4">
-        <v>4679593</v>
+        <v>3509593</v>
       </c>
       <c r="P119" s="5">
-        <v>4.62</v>
+        <v>3.46</v>
       </c>
       <c r="Q119" s="4">
-        <v>49745554.280000001</v>
+        <v>47741307.280000001</v>
       </c>
       <c r="R119" s="5">
-        <v>49.07</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="120" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -9791,28 +9798,28 @@
         <v>7840527.8099999996</v>
       </c>
       <c r="G137" s="8">
-        <v>6012020.5899999999</v>
+        <v>6024758.8899999997</v>
       </c>
       <c r="H137" s="9">
-        <v>76.680000000000007</v>
+        <v>76.84</v>
       </c>
       <c r="I137" s="8">
-        <v>778724.86</v>
+        <v>766386.56</v>
       </c>
       <c r="J137" s="9">
-        <v>9.93</v>
+        <v>9.77</v>
       </c>
       <c r="K137" s="8">
-        <v>6790745.4500000002</v>
+        <v>6791145.4500000002</v>
       </c>
       <c r="L137" s="9">
-        <v>86.61</v>
+        <v>86.62</v>
       </c>
       <c r="M137" s="8">
-        <v>1049782.3600000001</v>
+        <v>1049382.3600000001</v>
       </c>
       <c r="N137" s="9">
-        <v>13.39</v>
+        <v>13.38</v>
       </c>
       <c r="O137" s="8">
         <v>106945</v>
@@ -9821,10 +9828,10 @@
         <v>1.36</v>
       </c>
       <c r="Q137" s="8">
-        <v>942837.36</v>
+        <v>942437.36</v>
       </c>
       <c r="R137" s="9">
-        <v>12.03</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="138" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -9847,28 +9854,28 @@
         <v>2672753.2999999998</v>
       </c>
       <c r="G138" s="12">
-        <v>2867567.4</v>
+        <v>2860045.7</v>
       </c>
       <c r="H138" s="13">
-        <v>107.29</v>
+        <v>107.01</v>
       </c>
       <c r="I138" s="12">
-        <v>188042.7</v>
+        <v>195964.4</v>
       </c>
       <c r="J138" s="13">
-        <v>7.04</v>
+        <v>7.33</v>
       </c>
       <c r="K138" s="12">
-        <v>3055610.1</v>
+        <v>3056010.1</v>
       </c>
       <c r="L138" s="13">
-        <v>114.32</v>
+        <v>114.34</v>
       </c>
       <c r="M138" s="12">
-        <v>-382856.8</v>
+        <v>-383256.8</v>
       </c>
       <c r="N138" s="13">
-        <v>-14.32</v>
+        <v>-14.34</v>
       </c>
       <c r="O138" s="12">
         <v>56445</v>
@@ -9877,10 +9884,10 @@
         <v>2.11</v>
       </c>
       <c r="Q138" s="12">
-        <v>-439301.8</v>
+        <v>-439701.8</v>
       </c>
       <c r="R138" s="13">
-        <v>-16.440000000000001</v>
+        <v>-16.45</v>
       </c>
     </row>
     <row r="139" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -10015,16 +10022,16 @@
         <v>586550</v>
       </c>
       <c r="G141" s="12">
-        <v>683885.35</v>
+        <v>704085.35</v>
       </c>
       <c r="H141" s="13">
-        <v>116.59</v>
+        <v>120.04</v>
       </c>
       <c r="I141" s="12">
-        <v>124200</v>
+        <v>104000</v>
       </c>
       <c r="J141" s="13">
-        <v>21.17</v>
+        <v>17.73</v>
       </c>
       <c r="K141" s="12">
         <v>808085.35</v>
@@ -10071,13 +10078,13 @@
         <v>2143206</v>
       </c>
       <c r="G142" s="12">
-        <v>1124687.8400000001</v>
+        <v>1124747.8400000001</v>
       </c>
       <c r="H142" s="13">
         <v>52.48</v>
       </c>
       <c r="I142" s="12">
-        <v>166482.16</v>
+        <v>166422.16</v>
       </c>
       <c r="J142" s="13">
         <v>7.77</v>
@@ -10905,16 +10912,16 @@
         <v>0</v>
       </c>
       <c r="E157" s="8">
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="F157" s="8">
-        <v>2936503.78</v>
+        <v>2934753.78</v>
       </c>
       <c r="G157" s="8">
         <v>1697269.18</v>
       </c>
       <c r="H157" s="9">
-        <v>57.8</v>
+        <v>57.83</v>
       </c>
       <c r="I157" s="8">
         <v>80500</v>
@@ -10926,13 +10933,13 @@
         <v>1777769.18</v>
       </c>
       <c r="L157" s="9">
-        <v>60.54</v>
+        <v>60.58</v>
       </c>
       <c r="M157" s="8">
-        <v>1158734.6000000001</v>
+        <v>1156984.6000000001</v>
       </c>
       <c r="N157" s="9">
-        <v>39.46</v>
+        <v>39.42</v>
       </c>
       <c r="O157" s="8">
         <v>0</v>
@@ -10941,10 +10948,10 @@
         <v>0</v>
       </c>
       <c r="Q157" s="8">
-        <v>1158734.6000000001</v>
+        <v>1156984.6000000001</v>
       </c>
       <c r="R157" s="9">
-        <v>39.46</v>
+        <v>39.42</v>
       </c>
     </row>
     <row r="158" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -11073,34 +11080,34 @@
         <v>0</v>
       </c>
       <c r="E160" s="12">
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="F160" s="12">
-        <v>353725</v>
+        <v>351975</v>
       </c>
       <c r="G160" s="12">
         <v>172223.33</v>
       </c>
       <c r="H160" s="13">
-        <v>48.69</v>
+        <v>48.93</v>
       </c>
       <c r="I160" s="12">
         <v>80500</v>
       </c>
       <c r="J160" s="13">
-        <v>22.76</v>
+        <v>22.87</v>
       </c>
       <c r="K160" s="12">
         <v>252723.33</v>
       </c>
       <c r="L160" s="13">
-        <v>71.45</v>
+        <v>71.8</v>
       </c>
       <c r="M160" s="12">
-        <v>101001.67</v>
+        <v>99251.67</v>
       </c>
       <c r="N160" s="13">
-        <v>28.55</v>
+        <v>28.2</v>
       </c>
       <c r="O160" s="12">
         <v>0</v>
@@ -11109,10 +11116,10 @@
         <v>0</v>
       </c>
       <c r="Q160" s="12">
-        <v>101001.67</v>
+        <v>99251.67</v>
       </c>
       <c r="R160" s="13">
-        <v>28.55</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="161" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -11639,28 +11646,28 @@
         <v>8926239.0199999996</v>
       </c>
       <c r="G170" s="8">
-        <v>2165382.08</v>
+        <v>2952795.08</v>
       </c>
       <c r="H170" s="9">
-        <v>24.26</v>
+        <v>33.08</v>
       </c>
       <c r="I170" s="8">
-        <v>4417881</v>
+        <v>3617245</v>
       </c>
       <c r="J170" s="9">
-        <v>49.49</v>
+        <v>40.520000000000003</v>
       </c>
       <c r="K170" s="8">
-        <v>6583263.0800000001</v>
+        <v>6570040.0800000001</v>
       </c>
       <c r="L170" s="9">
-        <v>73.75</v>
+        <v>73.599999999999994</v>
       </c>
       <c r="M170" s="8">
-        <v>2342975.94</v>
+        <v>2356198.94</v>
       </c>
       <c r="N170" s="9">
-        <v>26.25</v>
+        <v>26.4</v>
       </c>
       <c r="O170" s="8">
         <v>15000</v>
@@ -11669,10 +11676,10 @@
         <v>0.17</v>
       </c>
       <c r="Q170" s="8">
-        <v>2327975.94</v>
+        <v>2341198.94</v>
       </c>
       <c r="R170" s="9">
-        <v>26.08</v>
+        <v>26.23</v>
       </c>
     </row>
     <row r="171" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -12199,28 +12206,28 @@
         <v>849000</v>
       </c>
       <c r="G180" s="12">
-        <v>347136.3</v>
+        <v>1134539.3</v>
       </c>
       <c r="H180" s="13">
-        <v>40.89</v>
+        <v>133.63</v>
       </c>
       <c r="I180" s="12">
-        <v>800636</v>
+        <v>0</v>
       </c>
       <c r="J180" s="13">
-        <v>94.3</v>
+        <v>0</v>
       </c>
       <c r="K180" s="12">
-        <v>1147772.3</v>
+        <v>1134539.3</v>
       </c>
       <c r="L180" s="13">
-        <v>135.19</v>
+        <v>133.63</v>
       </c>
       <c r="M180" s="12">
-        <v>-298772.3</v>
+        <v>-285539.3</v>
       </c>
       <c r="N180" s="13">
-        <v>-35.19</v>
+        <v>-33.630000000000003</v>
       </c>
       <c r="O180" s="12">
         <v>0</v>
@@ -12229,10 +12236,10 @@
         <v>0</v>
       </c>
       <c r="Q180" s="12">
-        <v>-298772.3</v>
+        <v>-285539.3</v>
       </c>
       <c r="R180" s="13">
-        <v>-35.19</v>
+        <v>-33.630000000000003</v>
       </c>
     </row>
     <row r="181" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -12311,10 +12318,10 @@
         <v>1410000</v>
       </c>
       <c r="G182" s="12">
-        <v>110047.7</v>
+        <v>110057.7</v>
       </c>
       <c r="H182" s="13">
-        <v>7.8</v>
+        <v>7.81</v>
       </c>
       <c r="I182" s="12">
         <v>5245</v>
@@ -12323,13 +12330,13 @@
         <v>0.37</v>
       </c>
       <c r="K182" s="12">
-        <v>115292.7</v>
+        <v>115302.7</v>
       </c>
       <c r="L182" s="13">
         <v>8.18</v>
       </c>
       <c r="M182" s="12">
-        <v>1294707.3</v>
+        <v>1294697.3</v>
       </c>
       <c r="N182" s="13">
         <v>91.82</v>
@@ -12341,7 +12348,7 @@
         <v>0</v>
       </c>
       <c r="Q182" s="12">
-        <v>1294707.3</v>
+        <v>1294697.3</v>
       </c>
       <c r="R182" s="13">
         <v>91.82</v>
@@ -12479,7 +12486,7 @@
         <v>1564125</v>
       </c>
       <c r="G185" s="8">
-        <v>950429.96</v>
+        <v>950434.96</v>
       </c>
       <c r="H185" s="9">
         <v>60.76</v>
@@ -12491,13 +12498,13 @@
         <v>37.53</v>
       </c>
       <c r="K185" s="8">
-        <v>1537426.63</v>
+        <v>1537431.63</v>
       </c>
       <c r="L185" s="9">
         <v>98.29</v>
       </c>
       <c r="M185" s="8">
-        <v>26698.37</v>
+        <v>26693.37</v>
       </c>
       <c r="N185" s="9">
         <v>1.71</v>
@@ -12509,7 +12516,7 @@
         <v>0.54</v>
       </c>
       <c r="Q185" s="8">
-        <v>18198.37</v>
+        <v>18193.37</v>
       </c>
       <c r="R185" s="9">
         <v>1.1599999999999999</v>
@@ -12591,10 +12598,10 @@
         <v>13100</v>
       </c>
       <c r="G187" s="12">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="H187" s="13">
-        <v>4.05</v>
+        <v>4.08</v>
       </c>
       <c r="I187" s="12">
         <v>260</v>
@@ -12603,16 +12610,16 @@
         <v>1.98</v>
       </c>
       <c r="K187" s="12">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="L187" s="13">
-        <v>6.03</v>
+        <v>6.07</v>
       </c>
       <c r="M187" s="12">
-        <v>12310</v>
+        <v>12305</v>
       </c>
       <c r="N187" s="13">
-        <v>93.97</v>
+        <v>93.93</v>
       </c>
       <c r="O187" s="12">
         <v>8500</v>
@@ -12621,10 +12628,10 @@
         <v>64.89</v>
       </c>
       <c r="Q187" s="12">
-        <v>3810</v>
+        <v>3805</v>
       </c>
       <c r="R187" s="13">
-        <v>29.08</v>
+        <v>29.05</v>
       </c>
     </row>
     <row r="188" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -13487,13 +13494,13 @@
         <v>12829676.84</v>
       </c>
       <c r="G203" s="8">
-        <v>3028932.91</v>
+        <v>3028982.91</v>
       </c>
       <c r="H203" s="9">
         <v>23.61</v>
       </c>
       <c r="I203" s="8">
-        <v>976431.56</v>
+        <v>976381.56</v>
       </c>
       <c r="J203" s="9">
         <v>7.61</v>
@@ -14047,16 +14054,16 @@
         <v>243280.04</v>
       </c>
       <c r="G213" s="12">
-        <v>15275</v>
+        <v>15325</v>
       </c>
       <c r="H213" s="13">
-        <v>6.28</v>
+        <v>6.3</v>
       </c>
       <c r="I213" s="12">
-        <v>3805</v>
+        <v>3755</v>
       </c>
       <c r="J213" s="13">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="K213" s="12">
         <v>19080</v>
@@ -14159,37 +14166,37 @@
         <v>18605882.420000002</v>
       </c>
       <c r="G215" s="8">
-        <v>3185402.03</v>
+        <v>3185427.03</v>
       </c>
       <c r="H215" s="9">
         <v>17.12</v>
       </c>
       <c r="I215" s="8">
-        <v>2607311</v>
+        <v>3407311</v>
       </c>
       <c r="J215" s="9">
-        <v>14.01</v>
+        <v>18.309999999999999</v>
       </c>
       <c r="K215" s="8">
-        <v>5792713.0300000003</v>
+        <v>6592738.0300000003</v>
       </c>
       <c r="L215" s="9">
-        <v>31.13</v>
+        <v>35.43</v>
       </c>
       <c r="M215" s="8">
-        <v>12813169.390000001</v>
+        <v>12013144.390000001</v>
       </c>
       <c r="N215" s="9">
-        <v>68.87</v>
+        <v>64.569999999999993</v>
       </c>
       <c r="O215" s="8">
-        <v>3325000</v>
+        <v>2525000</v>
       </c>
       <c r="P215" s="9">
-        <v>17.87</v>
+        <v>13.57</v>
       </c>
       <c r="Q215" s="8">
-        <v>9488169.3900000006</v>
+        <v>9488144.3900000006</v>
       </c>
       <c r="R215" s="9">
         <v>51</v>
@@ -14389,28 +14396,28 @@
         <v>0</v>
       </c>
       <c r="I219" s="12">
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="J219" s="13">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="K219" s="12">
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="L219" s="13">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="M219" s="12">
-        <v>1200000</v>
+        <v>400000</v>
       </c>
       <c r="N219" s="13">
-        <v>100</v>
+        <v>33.33</v>
       </c>
       <c r="O219" s="12">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="P219" s="13">
-        <v>66.67</v>
+        <v>0</v>
       </c>
       <c r="Q219" s="12">
         <v>400000</v>
@@ -15167,10 +15174,10 @@
         <v>388200.02</v>
       </c>
       <c r="G233" s="12">
-        <v>122756.4</v>
+        <v>122781.4</v>
       </c>
       <c r="H233" s="13">
-        <v>31.62</v>
+        <v>31.63</v>
       </c>
       <c r="I233" s="12">
         <v>680</v>
@@ -15179,13 +15186,13 @@
         <v>0.18</v>
       </c>
       <c r="K233" s="12">
-        <v>123436.4</v>
+        <v>123461.4</v>
       </c>
       <c r="L233" s="13">
         <v>31.8</v>
       </c>
       <c r="M233" s="12">
-        <v>264763.62</v>
+        <v>264738.62</v>
       </c>
       <c r="N233" s="13">
         <v>68.2</v>
@@ -15197,7 +15204,7 @@
         <v>32.200000000000003</v>
       </c>
       <c r="Q233" s="12">
-        <v>139763.62</v>
+        <v>139738.62</v>
       </c>
       <c r="R233" s="13">
         <v>36</v>
@@ -15223,7 +15230,7 @@
         <v>1603085.31</v>
       </c>
       <c r="G234" s="8">
-        <v>1115930</v>
+        <v>1115935</v>
       </c>
       <c r="H234" s="9">
         <v>69.61</v>
@@ -15235,13 +15242,13 @@
         <v>0.01</v>
       </c>
       <c r="K234" s="8">
-        <v>1116020</v>
+        <v>1116025</v>
       </c>
       <c r="L234" s="9">
         <v>69.62</v>
       </c>
       <c r="M234" s="8">
-        <v>487065.31</v>
+        <v>487060.31</v>
       </c>
       <c r="N234" s="9">
         <v>30.38</v>
@@ -15253,7 +15260,7 @@
         <v>0</v>
       </c>
       <c r="Q234" s="8">
-        <v>487065.31</v>
+        <v>487060.31</v>
       </c>
       <c r="R234" s="9">
         <v>30.38</v>
@@ -15503,7 +15510,7 @@
         <v>160000</v>
       </c>
       <c r="G239" s="12">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="H239" s="13">
         <v>0.1</v>
@@ -15515,16 +15522,16 @@
         <v>0.06</v>
       </c>
       <c r="K239" s="12">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="L239" s="13">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="M239" s="12">
-        <v>159755</v>
+        <v>159750</v>
       </c>
       <c r="N239" s="13">
-        <v>99.85</v>
+        <v>99.84</v>
       </c>
       <c r="O239" s="12">
         <v>0</v>
@@ -15533,10 +15540,10 @@
         <v>0</v>
       </c>
       <c r="Q239" s="12">
-        <v>159755</v>
+        <v>159750</v>
       </c>
       <c r="R239" s="13">
-        <v>99.85</v>
+        <v>99.84</v>
       </c>
     </row>
     <row r="240" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -15559,10 +15566,10 @@
         <v>1995235</v>
       </c>
       <c r="G240" s="8">
-        <v>1976130.3</v>
+        <v>2152090.2999999998</v>
       </c>
       <c r="H240" s="9">
-        <v>99.04</v>
+        <v>107.86</v>
       </c>
       <c r="I240" s="8">
         <v>485</v>
@@ -15571,16 +15578,16 @@
         <v>0.02</v>
       </c>
       <c r="K240" s="8">
-        <v>1976615.3</v>
+        <v>2152575.2999999998</v>
       </c>
       <c r="L240" s="9">
-        <v>99.07</v>
+        <v>107.89</v>
       </c>
       <c r="M240" s="8">
-        <v>18619.7</v>
+        <v>-157340.29999999999</v>
       </c>
       <c r="N240" s="9">
-        <v>0.93</v>
+        <v>-7.89</v>
       </c>
       <c r="O240" s="8">
         <v>0</v>
@@ -15589,10 +15596,10 @@
         <v>0</v>
       </c>
       <c r="Q240" s="8">
-        <v>18619.7</v>
+        <v>-157340.29999999999</v>
       </c>
       <c r="R240" s="9">
-        <v>0.93</v>
+        <v>-7.89</v>
       </c>
     </row>
     <row r="241" spans="1:18" x14ac:dyDescent="0.25">
@@ -15671,10 +15678,10 @@
         <v>14200</v>
       </c>
       <c r="G242" s="12">
-        <v>14985</v>
+        <v>14995</v>
       </c>
       <c r="H242" s="13">
-        <v>105.53</v>
+        <v>105.6</v>
       </c>
       <c r="I242" s="12">
         <v>485</v>
@@ -15683,16 +15690,16 @@
         <v>3.42</v>
       </c>
       <c r="K242" s="12">
-        <v>15470</v>
+        <v>15480</v>
       </c>
       <c r="L242" s="13">
-        <v>108.94</v>
+        <v>109.01</v>
       </c>
       <c r="M242" s="12">
-        <v>-1270</v>
+        <v>-1280</v>
       </c>
       <c r="N242" s="13">
-        <v>-8.94</v>
+        <v>-9.01</v>
       </c>
       <c r="O242" s="12">
         <v>0</v>
@@ -15701,10 +15708,10 @@
         <v>0</v>
       </c>
       <c r="Q242" s="12">
-        <v>-1270</v>
+        <v>-1280</v>
       </c>
       <c r="R242" s="13">
-        <v>-8.94</v>
+        <v>-9.01</v>
       </c>
     </row>
     <row r="243" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -15951,10 +15958,10 @@
         <v>181385</v>
       </c>
       <c r="G247" s="12">
-        <v>181385</v>
+        <v>357335</v>
       </c>
       <c r="H247" s="13">
-        <v>100</v>
+        <v>197</v>
       </c>
       <c r="I247" s="12">
         <v>0</v>
@@ -15963,16 +15970,16 @@
         <v>0</v>
       </c>
       <c r="K247" s="12">
-        <v>181385</v>
+        <v>357335</v>
       </c>
       <c r="L247" s="13">
-        <v>100</v>
+        <v>197</v>
       </c>
       <c r="M247" s="12">
-        <v>0</v>
+        <v>-175950</v>
       </c>
       <c r="N247" s="13">
-        <v>0</v>
+        <v>-97</v>
       </c>
       <c r="O247" s="12">
         <v>0</v>
@@ -15981,10 +15988,10 @@
         <v>0</v>
       </c>
       <c r="Q247" s="12">
-        <v>0</v>
+        <v>-175950</v>
       </c>
       <c r="R247" s="13">
-        <v>0</v>
+        <v>-97</v>
       </c>
     </row>
     <row r="248" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -16119,28 +16126,28 @@
         <v>2528000</v>
       </c>
       <c r="G250" s="8">
-        <v>991389.84</v>
+        <v>1002889.84</v>
       </c>
       <c r="H250" s="9">
-        <v>39.22</v>
+        <v>39.67</v>
       </c>
       <c r="I250" s="8">
-        <v>295610</v>
+        <v>584920</v>
       </c>
       <c r="J250" s="9">
-        <v>11.69</v>
+        <v>23.14</v>
       </c>
       <c r="K250" s="8">
-        <v>1286999.8400000001</v>
+        <v>1587809.84</v>
       </c>
       <c r="L250" s="9">
-        <v>50.91</v>
+        <v>62.81</v>
       </c>
       <c r="M250" s="8">
-        <v>1241000.1599999999</v>
+        <v>940190.16</v>
       </c>
       <c r="N250" s="9">
-        <v>49.09</v>
+        <v>37.19</v>
       </c>
       <c r="O250" s="8">
         <v>20000</v>
@@ -16149,10 +16156,10 @@
         <v>0.79</v>
       </c>
       <c r="Q250" s="8">
-        <v>1221000.1599999999</v>
+        <v>920190.16</v>
       </c>
       <c r="R250" s="9">
-        <v>48.3</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="251" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -16175,28 +16182,28 @@
         <v>792000</v>
       </c>
       <c r="G251" s="12">
-        <v>397835</v>
+        <v>409335</v>
       </c>
       <c r="H251" s="13">
-        <v>50.23</v>
+        <v>51.68</v>
       </c>
       <c r="I251" s="12">
-        <v>69500</v>
+        <v>206000</v>
       </c>
       <c r="J251" s="13">
-        <v>8.7799999999999994</v>
+        <v>26.01</v>
       </c>
       <c r="K251" s="12">
-        <v>467335</v>
+        <v>615335</v>
       </c>
       <c r="L251" s="13">
-        <v>59.01</v>
+        <v>77.69</v>
       </c>
       <c r="M251" s="12">
-        <v>324665</v>
+        <v>176665</v>
       </c>
       <c r="N251" s="13">
-        <v>40.99</v>
+        <v>22.31</v>
       </c>
       <c r="O251" s="12">
         <v>20000</v>
@@ -16205,10 +16212,10 @@
         <v>2.5299999999999998</v>
       </c>
       <c r="Q251" s="12">
-        <v>304665</v>
+        <v>156665</v>
       </c>
       <c r="R251" s="13">
-        <v>38.47</v>
+        <v>19.78</v>
       </c>
     </row>
     <row r="252" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -16237,22 +16244,22 @@
         <v>31.89</v>
       </c>
       <c r="I252" s="12">
-        <v>45000</v>
+        <v>195000</v>
       </c>
       <c r="J252" s="13">
-        <v>4.7699999999999996</v>
+        <v>20.66</v>
       </c>
       <c r="K252" s="12">
-        <v>346027.24</v>
+        <v>496027.24</v>
       </c>
       <c r="L252" s="13">
-        <v>36.659999999999997</v>
+        <v>52.55</v>
       </c>
       <c r="M252" s="12">
-        <v>597972.76</v>
+        <v>447972.76</v>
       </c>
       <c r="N252" s="13">
-        <v>63.34</v>
+        <v>47.45</v>
       </c>
       <c r="O252" s="12">
         <v>0</v>
@@ -16261,10 +16268,10 @@
         <v>0</v>
       </c>
       <c r="Q252" s="12">
-        <v>597972.76</v>
+        <v>447972.76</v>
       </c>
       <c r="R252" s="13">
-        <v>63.34</v>
+        <v>47.45</v>
       </c>
     </row>
     <row r="253" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
@@ -16293,22 +16300,22 @@
         <v>36.94</v>
       </c>
       <c r="I253" s="12">
-        <v>181110</v>
+        <v>183920</v>
       </c>
       <c r="J253" s="13">
-        <v>22.87</v>
+        <v>23.22</v>
       </c>
       <c r="K253" s="12">
-        <v>473637.6</v>
+        <v>476447.6</v>
       </c>
       <c r="L253" s="13">
-        <v>59.8</v>
+        <v>60.16</v>
       </c>
       <c r="M253" s="12">
-        <v>318362.40000000002</v>
+        <v>315552.40000000002</v>
       </c>
       <c r="N253" s="13">
-        <v>40.200000000000003</v>
+        <v>39.840000000000003</v>
       </c>
       <c r="O253" s="12">
         <v>0</v>
@@ -16317,10 +16324,10 @@
         <v>0</v>
       </c>
       <c r="Q253" s="12">
-        <v>318362.40000000002</v>
+        <v>315552.40000000002</v>
       </c>
       <c r="R253" s="13">
-        <v>40.200000000000003</v>
+        <v>39.840000000000003</v>
       </c>
     </row>
     <row r="254" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -16343,34 +16350,34 @@
         <v>12554100</v>
       </c>
       <c r="G254" s="8">
-        <v>3723690.44</v>
+        <v>3738785.44</v>
       </c>
       <c r="H254" s="9">
-        <v>29.66</v>
+        <v>29.78</v>
       </c>
       <c r="I254" s="8">
-        <v>1075273.56</v>
+        <v>1210178.5600000001</v>
       </c>
       <c r="J254" s="9">
-        <v>8.57</v>
+        <v>9.64</v>
       </c>
       <c r="K254" s="8">
-        <v>4798964</v>
+        <v>4948964</v>
       </c>
       <c r="L254" s="9">
-        <v>38.229999999999997</v>
+        <v>39.42</v>
       </c>
       <c r="M254" s="8">
-        <v>7755136</v>
+        <v>7605136</v>
       </c>
       <c r="N254" s="9">
-        <v>61.77</v>
+        <v>60.58</v>
       </c>
       <c r="O254" s="8">
-        <v>715148</v>
+        <v>565148</v>
       </c>
       <c r="P254" s="9">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="Q254" s="8">
         <v>7039988</v>
@@ -16461,28 +16468,28 @@
         <v>42.35</v>
       </c>
       <c r="I256" s="12">
-        <v>621670</v>
+        <v>771670</v>
       </c>
       <c r="J256" s="13">
-        <v>13.65</v>
+        <v>16.940000000000001</v>
       </c>
       <c r="K256" s="12">
-        <v>2551113</v>
+        <v>2701113</v>
       </c>
       <c r="L256" s="13">
-        <v>55.99</v>
+        <v>59.29</v>
       </c>
       <c r="M256" s="12">
-        <v>2004887</v>
+        <v>1854887</v>
       </c>
       <c r="N256" s="13">
-        <v>44.01</v>
+        <v>40.71</v>
       </c>
       <c r="O256" s="12">
-        <v>211000</v>
+        <v>61000</v>
       </c>
       <c r="P256" s="13">
-        <v>4.63</v>
+        <v>1.34</v>
       </c>
       <c r="Q256" s="12">
         <v>1793887</v>
@@ -16511,16 +16518,16 @@
         <v>2730000</v>
       </c>
       <c r="G257" s="12">
-        <v>778753.44</v>
+        <v>793848.44</v>
       </c>
       <c r="H257" s="13">
-        <v>28.53</v>
+        <v>29.08</v>
       </c>
       <c r="I257" s="12">
-        <v>285603.56</v>
+        <v>270508.56</v>
       </c>
       <c r="J257" s="13">
-        <v>10.46</v>
+        <v>9.91</v>
       </c>
       <c r="K257" s="12">
         <v>1064357</v>
@@ -16623,40 +16630,40 @@
         <v>1500000</v>
       </c>
       <c r="G259" s="8">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="H259" s="9">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="I259" s="8">
-        <v>225000</v>
+        <v>225300</v>
       </c>
       <c r="J259" s="9">
-        <v>15</v>
+        <v>15.02</v>
       </c>
       <c r="K259" s="8">
-        <v>225000</v>
+        <v>226200</v>
       </c>
       <c r="L259" s="9">
-        <v>15</v>
+        <v>15.08</v>
       </c>
       <c r="M259" s="8">
-        <v>1275000</v>
+        <v>1273800</v>
       </c>
       <c r="N259" s="9">
-        <v>85</v>
+        <v>84.92</v>
       </c>
       <c r="O259" s="8">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="P259" s="9">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="Q259" s="8">
-        <v>1275000</v>
+        <v>1173800</v>
       </c>
       <c r="R259" s="9">
-        <v>85</v>
+        <v>78.25</v>
       </c>
     </row>
     <row r="260" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -16703,16 +16710,16 @@
         <v>100</v>
       </c>
       <c r="O260" s="12">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="P260" s="13">
-        <v>0</v>
+        <v>67.48</v>
       </c>
       <c r="Q260" s="12">
-        <v>148200</v>
+        <v>48200</v>
       </c>
       <c r="R260" s="13">
-        <v>100</v>
+        <v>32.520000000000003</v>
       </c>
     </row>
     <row r="261" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -16959,28 +16966,28 @@
         <v>8800</v>
       </c>
       <c r="G265" s="12">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="H265" s="13">
-        <v>0</v>
+        <v>10.23</v>
       </c>
       <c r="I265" s="12">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J265" s="13">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="K265" s="12">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="L265" s="13">
-        <v>0</v>
+        <v>13.64</v>
       </c>
       <c r="M265" s="12">
-        <v>8800</v>
+        <v>7600</v>
       </c>
       <c r="N265" s="13">
-        <v>100</v>
+        <v>86.36</v>
       </c>
       <c r="O265" s="12">
         <v>0</v>
@@ -16989,10 +16996,10 @@
         <v>0</v>
       </c>
       <c r="Q265" s="12">
-        <v>8800</v>
+        <v>7600</v>
       </c>
       <c r="R265" s="13">
-        <v>100</v>
+        <v>86.36</v>
       </c>
     </row>
     <row r="266" spans="1:18" x14ac:dyDescent="0.25">
@@ -17071,28 +17078,28 @@
         <v>19811100</v>
       </c>
       <c r="G267" s="8">
-        <v>3710261.97</v>
+        <v>4310276.97</v>
       </c>
       <c r="H267" s="9">
-        <v>18.73</v>
+        <v>21.76</v>
       </c>
       <c r="I267" s="8">
-        <v>3915288.03</v>
+        <v>4515288.03</v>
       </c>
       <c r="J267" s="9">
-        <v>19.760000000000002</v>
+        <v>22.79</v>
       </c>
       <c r="K267" s="8">
-        <v>7625550</v>
+        <v>8825565</v>
       </c>
       <c r="L267" s="9">
-        <v>38.49</v>
+        <v>44.55</v>
       </c>
       <c r="M267" s="8">
-        <v>12185550</v>
+        <v>10985535</v>
       </c>
       <c r="N267" s="9">
-        <v>61.51</v>
+        <v>55.45</v>
       </c>
       <c r="O267" s="8">
         <v>0</v>
@@ -17101,10 +17108,10 @@
         <v>0</v>
       </c>
       <c r="Q267" s="8">
-        <v>12185550</v>
+        <v>10985535</v>
       </c>
       <c r="R267" s="9">
-        <v>61.51</v>
+        <v>55.45</v>
       </c>
     </row>
     <row r="268" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -17183,28 +17190,28 @@
         <v>10400000</v>
       </c>
       <c r="G269" s="12">
-        <v>3600000</v>
+        <v>4200000</v>
       </c>
       <c r="H269" s="13">
-        <v>34.619999999999997</v>
+        <v>40.380000000000003</v>
       </c>
       <c r="I269" s="12">
-        <v>3600000</v>
+        <v>4200000</v>
       </c>
       <c r="J269" s="13">
-        <v>34.619999999999997</v>
+        <v>40.380000000000003</v>
       </c>
       <c r="K269" s="12">
-        <v>7200000</v>
+        <v>8400000</v>
       </c>
       <c r="L269" s="13">
-        <v>69.23</v>
+        <v>80.77</v>
       </c>
       <c r="M269" s="12">
-        <v>3200000</v>
+        <v>2000000</v>
       </c>
       <c r="N269" s="13">
-        <v>30.77</v>
+        <v>19.23</v>
       </c>
       <c r="O269" s="12">
         <v>0</v>
@@ -17213,10 +17220,10 @@
         <v>0</v>
       </c>
       <c r="Q269" s="12">
-        <v>3200000</v>
+        <v>2000000</v>
       </c>
       <c r="R269" s="13">
-        <v>30.77</v>
+        <v>19.23</v>
       </c>
     </row>
     <row r="270" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -17463,7 +17470,7 @@
         <v>406250</v>
       </c>
       <c r="G274" s="12">
-        <v>450</v>
+        <v>465</v>
       </c>
       <c r="H274" s="13">
         <v>0.11</v>
@@ -17475,16 +17482,16 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="K274" s="12">
-        <v>750</v>
+        <v>765</v>
       </c>
       <c r="L274" s="13">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="M274" s="12">
-        <v>405500</v>
+        <v>405485</v>
       </c>
       <c r="N274" s="13">
-        <v>99.82</v>
+        <v>99.81</v>
       </c>
       <c r="O274" s="12">
         <v>0</v>
@@ -17493,10 +17500,10 @@
         <v>0</v>
       </c>
       <c r="Q274" s="12">
-        <v>405500</v>
+        <v>405485</v>
       </c>
       <c r="R274" s="13">
-        <v>99.82</v>
+        <v>99.81</v>
       </c>
     </row>
     <row r="275" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -17575,40 +17582,40 @@
         <v>2208125</v>
       </c>
       <c r="G276" s="8">
-        <v>26775</v>
+        <v>26785</v>
       </c>
       <c r="H276" s="9">
         <v>1.21</v>
       </c>
       <c r="I276" s="8">
-        <v>1249500</v>
+        <v>1806790</v>
       </c>
       <c r="J276" s="9">
-        <v>56.59</v>
+        <v>81.819999999999993</v>
       </c>
       <c r="K276" s="8">
-        <v>1276275</v>
+        <v>1833575</v>
       </c>
       <c r="L276" s="9">
-        <v>57.8</v>
+        <v>83.04</v>
       </c>
       <c r="M276" s="8">
-        <v>931850</v>
+        <v>374550</v>
       </c>
       <c r="N276" s="9">
-        <v>42.2</v>
+        <v>16.96</v>
       </c>
       <c r="O276" s="8">
-        <v>360000</v>
+        <v>40000</v>
       </c>
       <c r="P276" s="9">
-        <v>16.3</v>
+        <v>1.81</v>
       </c>
       <c r="Q276" s="8">
-        <v>571850</v>
+        <v>334550</v>
       </c>
       <c r="R276" s="9">
-        <v>25.9</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="277" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -17637,34 +17644,34 @@
         <v>0</v>
       </c>
       <c r="I277" s="12">
-        <v>1197300</v>
+        <v>1754600</v>
       </c>
       <c r="J277" s="13">
-        <v>67.88</v>
+        <v>99.48</v>
       </c>
       <c r="K277" s="12">
-        <v>1197300</v>
+        <v>1754600</v>
       </c>
       <c r="L277" s="13">
-        <v>67.88</v>
+        <v>99.48</v>
       </c>
       <c r="M277" s="12">
-        <v>566450</v>
+        <v>9150</v>
       </c>
       <c r="N277" s="13">
-        <v>32.119999999999997</v>
+        <v>0.52</v>
       </c>
       <c r="O277" s="12">
-        <v>360000</v>
+        <v>40000</v>
       </c>
       <c r="P277" s="13">
-        <v>20.41</v>
+        <v>2.27</v>
       </c>
       <c r="Q277" s="12">
-        <v>206450</v>
+        <v>-30850</v>
       </c>
       <c r="R277" s="13">
-        <v>11.71</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="278" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -17743,16 +17750,16 @@
         <v>180375</v>
       </c>
       <c r="G279" s="12">
-        <v>26775</v>
+        <v>26785</v>
       </c>
       <c r="H279" s="13">
-        <v>14.84</v>
+        <v>14.85</v>
       </c>
       <c r="I279" s="12">
-        <v>52200</v>
+        <v>52190</v>
       </c>
       <c r="J279" s="13">
-        <v>28.94</v>
+        <v>28.93</v>
       </c>
       <c r="K279" s="12">
         <v>78975</v>
@@ -18127,46 +18134,46 @@
         <v>74571</v>
       </c>
       <c r="E286" s="14">
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="F286" s="14">
-        <v>101372727.95</v>
+        <v>101370977.95</v>
       </c>
       <c r="G286" s="14">
-        <v>30562243.989999998</v>
+        <v>32165960.289999999</v>
       </c>
       <c r="H286" s="15">
-        <v>30.15</v>
+        <v>31.73</v>
       </c>
       <c r="I286" s="14">
-        <v>16385336.68</v>
+        <v>17954117.379999999</v>
       </c>
       <c r="J286" s="15">
-        <v>16.16</v>
+        <v>17.71</v>
       </c>
       <c r="K286" s="14">
-        <v>46947580.670000002</v>
+        <v>50120077.670000002</v>
       </c>
       <c r="L286" s="15">
-        <v>46.31</v>
+        <v>49.44</v>
       </c>
       <c r="M286" s="14">
-        <v>54425147.280000001</v>
+        <v>51250900.280000001</v>
       </c>
       <c r="N286" s="15">
-        <v>53.69</v>
+        <v>50.56</v>
       </c>
       <c r="O286" s="14">
-        <v>4679593</v>
+        <v>3509593</v>
       </c>
       <c r="P286" s="15">
-        <v>4.62</v>
+        <v>3.46</v>
       </c>
       <c r="Q286" s="14">
-        <v>49745554.280000001</v>
+        <v>47741307.280000001</v>
       </c>
       <c r="R286" s="15">
-        <v>49.07</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="287" spans="1:18" x14ac:dyDescent="0.25">
@@ -18178,49 +18185,49 @@
         <v>332000356.94999999</v>
       </c>
       <c r="D287" s="16">
-        <v>74571</v>
+        <v>374571</v>
       </c>
       <c r="E287" s="16">
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="F287" s="16">
-        <v>332074927.94999999</v>
+        <v>332373177.94999999</v>
       </c>
       <c r="G287" s="16">
-        <v>191203422.41999999</v>
+        <v>195957149.46000001</v>
       </c>
       <c r="H287" s="17">
-        <v>57.58</v>
+        <v>58.96</v>
       </c>
       <c r="I287" s="16">
-        <v>46623359.5</v>
+        <v>50912567.140000001</v>
       </c>
       <c r="J287" s="17">
-        <v>14.04</v>
+        <v>15.32</v>
       </c>
       <c r="K287" s="16">
-        <v>237826781.91999999</v>
+        <v>246869716.59999999</v>
       </c>
       <c r="L287" s="17">
-        <v>71.62</v>
+        <v>74.27</v>
       </c>
       <c r="M287" s="16">
-        <v>94248146.030000001</v>
+        <v>85503461.349999994</v>
       </c>
       <c r="N287" s="17">
-        <v>28.38</v>
+        <v>25.73</v>
       </c>
       <c r="O287" s="16">
-        <v>16221741.67</v>
+        <v>14600179.210000001</v>
       </c>
       <c r="P287" s="17">
-        <v>4.88</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="Q287" s="16">
-        <v>78026404.359999999</v>
+        <v>70903282.140000001</v>
       </c>
       <c r="R287" s="17">
-        <v>23.5</v>
+        <v>21.33</v>
       </c>
     </row>
     <row r="288" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -18237,10 +18244,10 @@
         <v>0</v>
       </c>
       <c r="E288" s="4">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="F288" s="4">
-        <v>6655580.1799999997</v>
+        <v>6355580.1799999997</v>
       </c>
       <c r="G288" s="4">
         <v>0</v>
@@ -18261,7 +18268,7 @@
         <v>0</v>
       </c>
       <c r="M288" s="4">
-        <v>6655580.1799999997</v>
+        <v>6355580.1799999997</v>
       </c>
       <c r="N288" s="5">
         <v>100</v>
@@ -18273,7 +18280,7 @@
         <v>0</v>
       </c>
       <c r="Q288" s="4">
-        <v>6655580.1799999997</v>
+        <v>6355580.1799999997</v>
       </c>
       <c r="R288" s="5">
         <v>100</v>
@@ -18293,10 +18300,10 @@
         <v>0</v>
       </c>
       <c r="E289" s="8">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="F289" s="8">
-        <v>6655580.1799999997</v>
+        <v>6355580.1799999997</v>
       </c>
       <c r="G289" s="8">
         <v>0</v>
@@ -18317,7 +18324,7 @@
         <v>0</v>
       </c>
       <c r="M289" s="8">
-        <v>6655580.1799999997</v>
+        <v>6355580.1799999997</v>
       </c>
       <c r="N289" s="9">
         <v>100</v>
@@ -18329,7 +18336,7 @@
         <v>0</v>
       </c>
       <c r="Q289" s="8">
-        <v>6655580.1799999997</v>
+        <v>6355580.1799999997</v>
       </c>
       <c r="R289" s="9">
         <v>100</v>
@@ -18349,10 +18356,10 @@
         <v>0</v>
       </c>
       <c r="E290" s="12">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="F290" s="12">
-        <v>6655580.1799999997</v>
+        <v>6355580.1799999997</v>
       </c>
       <c r="G290" s="12">
         <v>0</v>
@@ -18373,7 +18380,7 @@
         <v>0</v>
       </c>
       <c r="M290" s="12">
-        <v>6655580.1799999997</v>
+        <v>6355580.1799999997</v>
       </c>
       <c r="N290" s="13">
         <v>100</v>
@@ -18385,7 +18392,7 @@
         <v>0</v>
       </c>
       <c r="Q290" s="12">
-        <v>6655580.1799999997</v>
+        <v>6355580.1799999997</v>
       </c>
       <c r="R290" s="13">
         <v>100</v>
@@ -18403,10 +18410,10 @@
         <v>0</v>
       </c>
       <c r="E291" s="14">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="F291" s="14">
-        <v>6655580.1799999997</v>
+        <v>6355580.1799999997</v>
       </c>
       <c r="G291" s="14">
         <v>0</v>
@@ -18427,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="M291" s="14">
-        <v>6655580.1799999997</v>
+        <v>6355580.1799999997</v>
       </c>
       <c r="N291" s="15">
         <v>100</v>
@@ -18439,7 +18446,7 @@
         <v>0</v>
       </c>
       <c r="Q291" s="14">
-        <v>6655580.1799999997</v>
+        <v>6355580.1799999997</v>
       </c>
       <c r="R291" s="15">
         <v>100</v>
@@ -18454,49 +18461,49 @@
         <v>338655937.13</v>
       </c>
       <c r="D292" s="16">
-        <v>74571</v>
+        <v>374571</v>
       </c>
       <c r="E292" s="16">
-        <v>0</v>
+        <v>301750</v>
       </c>
       <c r="F292" s="16">
-        <v>338730508.13</v>
+        <v>338728758.13</v>
       </c>
       <c r="G292" s="16">
-        <v>191203422.41999999</v>
+        <v>195957149.46000001</v>
       </c>
       <c r="H292" s="17">
-        <v>56.45</v>
+        <v>57.85</v>
       </c>
       <c r="I292" s="16">
-        <v>46623359.5</v>
+        <v>50912567.140000001</v>
       </c>
       <c r="J292" s="17">
-        <v>13.76</v>
+        <v>15.03</v>
       </c>
       <c r="K292" s="16">
-        <v>237826781.91999999</v>
+        <v>246869716.59999999</v>
       </c>
       <c r="L292" s="17">
-        <v>70.209999999999994</v>
+        <v>72.88</v>
       </c>
       <c r="M292" s="16">
-        <v>100903726.20999999</v>
+        <v>91859041.530000001</v>
       </c>
       <c r="N292" s="17">
-        <v>29.79</v>
+        <v>27.12</v>
       </c>
       <c r="O292" s="16">
-        <v>16221741.67</v>
+        <v>14600179.210000001</v>
       </c>
       <c r="P292" s="17">
-        <v>4.79</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="Q292" s="16">
-        <v>84681984.540000007</v>
+        <v>77258862.319999993</v>
       </c>
       <c r="R292" s="17">
-        <v>25</v>
+        <v>22.81</v>
       </c>
     </row>
     <row r="293" spans="1:18" x14ac:dyDescent="0.25">
@@ -18510,25 +18517,25 @@
         <v>4037940.24</v>
       </c>
       <c r="D293" s="4">
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="E293" s="4">
         <v>74571</v>
       </c>
       <c r="F293" s="4">
-        <v>3963369.24</v>
+        <v>3965119.24</v>
       </c>
       <c r="G293" s="4">
-        <v>607139.18000000005</v>
+        <v>607169.18000000005</v>
       </c>
       <c r="H293" s="5">
-        <v>15.32</v>
+        <v>15.31</v>
       </c>
       <c r="I293" s="4">
-        <v>108413.7</v>
+        <v>108383.7</v>
       </c>
       <c r="J293" s="5">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="K293" s="4">
         <v>715552.88</v>
@@ -18537,7 +18544,7 @@
         <v>18.05</v>
       </c>
       <c r="M293" s="4">
-        <v>3247816.36</v>
+        <v>3249566.36</v>
       </c>
       <c r="N293" s="5">
         <v>81.95</v>
@@ -18549,10 +18556,10 @@
         <v>0.15</v>
       </c>
       <c r="Q293" s="4">
-        <v>3241687.24</v>
+        <v>3243437.24</v>
       </c>
       <c r="R293" s="5">
-        <v>81.790000000000006</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="294" spans="1:18" x14ac:dyDescent="0.25">
@@ -18566,25 +18573,25 @@
         <v>4037940.24</v>
       </c>
       <c r="D294" s="8">
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="E294" s="8">
         <v>74571</v>
       </c>
       <c r="F294" s="8">
-        <v>3963369.24</v>
+        <v>3965119.24</v>
       </c>
       <c r="G294" s="8">
-        <v>607139.18000000005</v>
+        <v>607169.18000000005</v>
       </c>
       <c r="H294" s="9">
-        <v>15.32</v>
+        <v>15.31</v>
       </c>
       <c r="I294" s="8">
-        <v>108413.7</v>
+        <v>108383.7</v>
       </c>
       <c r="J294" s="9">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="K294" s="8">
         <v>715552.88</v>
@@ -18593,7 +18600,7 @@
         <v>18.05</v>
       </c>
       <c r="M294" s="8">
-        <v>3247816.36</v>
+        <v>3249566.36</v>
       </c>
       <c r="N294" s="9">
         <v>81.95</v>
@@ -18605,10 +18612,10 @@
         <v>0.15</v>
       </c>
       <c r="Q294" s="8">
-        <v>3241687.24</v>
+        <v>3243437.24</v>
       </c>
       <c r="R294" s="9">
-        <v>81.790000000000006</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="295" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -18622,25 +18629,25 @@
         <v>4037940.24</v>
       </c>
       <c r="D295" s="12">
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="E295" s="12">
         <v>74571</v>
       </c>
       <c r="F295" s="12">
-        <v>3963369.24</v>
+        <v>3965119.24</v>
       </c>
       <c r="G295" s="12">
-        <v>607139.18000000005</v>
+        <v>607169.18000000005</v>
       </c>
       <c r="H295" s="13">
-        <v>15.32</v>
+        <v>15.31</v>
       </c>
       <c r="I295" s="12">
-        <v>108413.7</v>
+        <v>108383.7</v>
       </c>
       <c r="J295" s="13">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="K295" s="12">
         <v>715552.88</v>
@@ -18649,7 +18656,7 @@
         <v>18.05</v>
       </c>
       <c r="M295" s="12">
-        <v>3247816.36</v>
+        <v>3249566.36</v>
       </c>
       <c r="N295" s="13">
         <v>81.95</v>
@@ -18661,10 +18668,10 @@
         <v>0.15</v>
       </c>
       <c r="Q295" s="12">
-        <v>3241687.24</v>
+        <v>3243437.24</v>
       </c>
       <c r="R295" s="13">
-        <v>81.790000000000006</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="296" spans="1:18" x14ac:dyDescent="0.25">
@@ -18676,25 +18683,25 @@
         <v>4037940.24</v>
       </c>
       <c r="D296" s="14">
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="E296" s="14">
         <v>74571</v>
       </c>
       <c r="F296" s="14">
-        <v>3963369.24</v>
+        <v>3965119.24</v>
       </c>
       <c r="G296" s="14">
-        <v>607139.18000000005</v>
+        <v>607169.18000000005</v>
       </c>
       <c r="H296" s="15">
-        <v>15.32</v>
+        <v>15.31</v>
       </c>
       <c r="I296" s="14">
-        <v>108413.7</v>
+        <v>108383.7</v>
       </c>
       <c r="J296" s="15">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="K296" s="14">
         <v>715552.88</v>
@@ -18703,7 +18710,7 @@
         <v>18.05</v>
       </c>
       <c r="M296" s="14">
-        <v>3247816.36</v>
+        <v>3249566.36</v>
       </c>
       <c r="N296" s="15">
         <v>81.95</v>
@@ -18715,10 +18722,10 @@
         <v>0.15</v>
       </c>
       <c r="Q296" s="14">
-        <v>3241687.24</v>
+        <v>3243437.24</v>
       </c>
       <c r="R296" s="15">
-        <v>81.790000000000006</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="297" spans="1:18" x14ac:dyDescent="0.25">
@@ -18730,49 +18737,49 @@
         <v>342693877.37</v>
       </c>
       <c r="D297" s="16">
-        <v>74571</v>
+        <v>376321</v>
       </c>
       <c r="E297" s="16">
-        <v>74571</v>
+        <v>376321</v>
       </c>
       <c r="F297" s="16">
         <v>342693877.37</v>
       </c>
       <c r="G297" s="16">
-        <v>191810561.59999999</v>
+        <v>196564318.63999999</v>
       </c>
       <c r="H297" s="17">
-        <v>55.97</v>
+        <v>57.36</v>
       </c>
       <c r="I297" s="16">
-        <v>46731773.200000003</v>
+        <v>51020950.840000004</v>
       </c>
       <c r="J297" s="17">
-        <v>13.64</v>
+        <v>14.89</v>
       </c>
       <c r="K297" s="16">
-        <v>238542334.80000001</v>
+        <v>247585269.47999999</v>
       </c>
       <c r="L297" s="17">
-        <v>69.61</v>
+        <v>72.25</v>
       </c>
       <c r="M297" s="16">
-        <v>104151542.56999999</v>
+        <v>95108607.890000001</v>
       </c>
       <c r="N297" s="17">
-        <v>30.39</v>
+        <v>27.75</v>
       </c>
       <c r="O297" s="16">
-        <v>16227870.789999999</v>
+        <v>14606308.33</v>
       </c>
       <c r="P297" s="17">
-        <v>4.74</v>
+        <v>4.26</v>
       </c>
       <c r="Q297" s="16">
-        <v>87923671.780000001</v>
+        <v>80502299.560000002</v>
       </c>
       <c r="R297" s="17">
-        <v>25.66</v>
+        <v>23.49</v>
       </c>
     </row>
     <row r="298" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -18795,40 +18802,40 @@
         <v>46540814</v>
       </c>
       <c r="G298" s="19">
-        <v>24172229.510000002</v>
+        <v>24324095.649999999</v>
       </c>
       <c r="H298" s="20">
-        <v>51.94</v>
+        <v>52.26</v>
       </c>
       <c r="I298" s="19">
-        <v>14964213.16</v>
+        <v>16096324.17</v>
       </c>
       <c r="J298" s="20">
-        <v>32.15</v>
+        <v>34.590000000000003</v>
       </c>
       <c r="K298" s="19">
-        <v>39136442.670000002</v>
+        <v>40420419.82</v>
       </c>
       <c r="L298" s="20">
-        <v>84.09</v>
+        <v>86.85</v>
       </c>
       <c r="M298" s="19">
-        <v>7404371.3300000001</v>
+        <v>6120394.1799999997</v>
       </c>
       <c r="N298" s="20">
-        <v>15.91</v>
+        <v>13.15</v>
       </c>
       <c r="O298" s="19">
-        <v>1380800</v>
+        <v>1830000</v>
       </c>
       <c r="P298" s="20">
-        <v>2.97</v>
+        <v>3.93</v>
       </c>
       <c r="Q298" s="19">
-        <v>6023571.3300000001</v>
+        <v>4290394.18</v>
       </c>
       <c r="R298" s="20">
-        <v>12.94</v>
+        <v>9.2200000000000006</v>
       </c>
     </row>
     <row r="299" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -18851,40 +18858,40 @@
         <v>54940200</v>
       </c>
       <c r="G299" s="19">
-        <v>41097272.969999999</v>
+        <v>43456973.259999998</v>
       </c>
       <c r="H299" s="20">
-        <v>74.8</v>
+        <v>79.099999999999994</v>
       </c>
       <c r="I299" s="19">
-        <v>4983091.67</v>
+        <v>6585711.0800000001</v>
       </c>
       <c r="J299" s="20">
-        <v>9.07</v>
+        <v>11.99</v>
       </c>
       <c r="K299" s="19">
-        <v>46080364.640000001</v>
+        <v>50042684.340000004</v>
       </c>
       <c r="L299" s="20">
-        <v>83.87</v>
+        <v>91.09</v>
       </c>
       <c r="M299" s="19">
-        <v>8859835.3599999994</v>
+        <v>4897515.66</v>
       </c>
       <c r="N299" s="20">
-        <v>16.13</v>
+        <v>8.91</v>
       </c>
       <c r="O299" s="19">
-        <v>1200986.5</v>
+        <v>576020.80000000005</v>
       </c>
       <c r="P299" s="20">
-        <v>2.19</v>
+        <v>1.05</v>
       </c>
       <c r="Q299" s="19">
-        <v>7658848.8600000003</v>
+        <v>4321494.8600000003</v>
       </c>
       <c r="R299" s="20">
-        <v>13.94</v>
+        <v>7.87</v>
       </c>
     </row>
     <row r="300" spans="1:18" x14ac:dyDescent="0.25">
@@ -18907,40 +18914,40 @@
         <v>9800000</v>
       </c>
       <c r="G300" s="19">
-        <v>5612006.6399999997</v>
+        <v>5667604.7999999998</v>
       </c>
       <c r="H300" s="20">
-        <v>57.27</v>
+        <v>57.83</v>
       </c>
       <c r="I300" s="19">
-        <v>863008.31</v>
+        <v>1080307.1499999999</v>
       </c>
       <c r="J300" s="20">
-        <v>8.81</v>
+        <v>11.02</v>
       </c>
       <c r="K300" s="19">
-        <v>6475014.9500000002</v>
+        <v>6747911.9500000002</v>
       </c>
       <c r="L300" s="20">
-        <v>66.069999999999993</v>
+        <v>68.86</v>
       </c>
       <c r="M300" s="19">
-        <v>3324985.05</v>
+        <v>3052088.05</v>
       </c>
       <c r="N300" s="20">
-        <v>33.93</v>
+        <v>31.14</v>
       </c>
       <c r="O300" s="19">
-        <v>3152551.54</v>
+        <v>2977599.54</v>
       </c>
       <c r="P300" s="20">
-        <v>32.17</v>
+        <v>30.38</v>
       </c>
       <c r="Q300" s="19">
-        <v>172433.51</v>
+        <v>74488.509999999995</v>
       </c>
       <c r="R300" s="20">
-        <v>1.76</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="301" spans="1:18" x14ac:dyDescent="0.25">
@@ -18957,46 +18964,46 @@
         <v>74571</v>
       </c>
       <c r="E301" s="19">
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="F301" s="19">
-        <v>101372727.95</v>
+        <v>101370977.95</v>
       </c>
       <c r="G301" s="19">
-        <v>30562243.989999998</v>
+        <v>32165960.289999999</v>
       </c>
       <c r="H301" s="20">
-        <v>30.15</v>
+        <v>31.73</v>
       </c>
       <c r="I301" s="19">
-        <v>16385336.68</v>
+        <v>17954117.379999999</v>
       </c>
       <c r="J301" s="20">
-        <v>16.16</v>
+        <v>17.71</v>
       </c>
       <c r="K301" s="19">
-        <v>46947580.670000002</v>
+        <v>50120077.670000002</v>
       </c>
       <c r="L301" s="20">
-        <v>46.31</v>
+        <v>49.44</v>
       </c>
       <c r="M301" s="19">
-        <v>54425147.280000001</v>
+        <v>51250900.280000001</v>
       </c>
       <c r="N301" s="20">
-        <v>53.69</v>
+        <v>50.56</v>
       </c>
       <c r="O301" s="19">
-        <v>4679593</v>
+        <v>3509593</v>
       </c>
       <c r="P301" s="20">
-        <v>4.62</v>
+        <v>3.46</v>
       </c>
       <c r="Q301" s="19">
-        <v>49745554.280000001</v>
+        <v>47741307.280000001</v>
       </c>
       <c r="R301" s="20">
-        <v>49.07</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="302" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -19013,10 +19020,10 @@
         <v>0</v>
       </c>
       <c r="E302" s="19">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="F302" s="19">
-        <v>6655580.1799999997</v>
+        <v>6355580.1799999997</v>
       </c>
       <c r="G302" s="19">
         <v>0</v>
@@ -19037,7 +19044,7 @@
         <v>0</v>
       </c>
       <c r="M302" s="19">
-        <v>6655580.1799999997</v>
+        <v>6355580.1799999997</v>
       </c>
       <c r="N302" s="20">
         <v>100</v>
@@ -19049,7 +19056,7 @@
         <v>0</v>
       </c>
       <c r="Q302" s="19">
-        <v>6655580.1799999997</v>
+        <v>6355580.1799999997</v>
       </c>
       <c r="R302" s="20">
         <v>100</v>
@@ -19066,25 +19073,25 @@
         <v>4037940.24</v>
       </c>
       <c r="D303" s="19">
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="E303" s="19">
         <v>74571</v>
       </c>
       <c r="F303" s="19">
-        <v>3963369.24</v>
+        <v>3965119.24</v>
       </c>
       <c r="G303" s="19">
-        <v>607139.18000000005</v>
+        <v>607169.18000000005</v>
       </c>
       <c r="H303" s="20">
-        <v>15.32</v>
+        <v>15.31</v>
       </c>
       <c r="I303" s="19">
-        <v>108413.7</v>
+        <v>108383.7</v>
       </c>
       <c r="J303" s="20">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="K303" s="19">
         <v>715552.88</v>
@@ -19093,7 +19100,7 @@
         <v>18.05</v>
       </c>
       <c r="M303" s="19">
-        <v>3247816.36</v>
+        <v>3249566.36</v>
       </c>
       <c r="N303" s="20">
         <v>81.95</v>
@@ -19105,10 +19112,10 @@
         <v>0.15</v>
       </c>
       <c r="Q303" s="19">
-        <v>3241687.24</v>
+        <v>3243437.24</v>
       </c>
       <c r="R303" s="20">
-        <v>81.790000000000006</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="304" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -19122,49 +19129,49 @@
         <v>119421186</v>
       </c>
       <c r="D304" s="19">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="E304" s="19">
         <v>0</v>
       </c>
       <c r="F304" s="19">
-        <v>119421186</v>
+        <v>119721186</v>
       </c>
       <c r="G304" s="19">
-        <v>89759669.310000002</v>
+        <v>90342515.459999993</v>
       </c>
       <c r="H304" s="20">
-        <v>75.16</v>
+        <v>75.459999999999994</v>
       </c>
       <c r="I304" s="19">
-        <v>9427709.6799999997</v>
+        <v>9196107.3599999994</v>
       </c>
       <c r="J304" s="20">
-        <v>7.89</v>
+        <v>7.68</v>
       </c>
       <c r="K304" s="19">
-        <v>99187378.989999995</v>
+        <v>99538622.819999993</v>
       </c>
       <c r="L304" s="20">
-        <v>83.06</v>
+        <v>83.14</v>
       </c>
       <c r="M304" s="19">
-        <v>20233807.010000002</v>
+        <v>20182563.18</v>
       </c>
       <c r="N304" s="20">
-        <v>16.940000000000001</v>
+        <v>16.86</v>
       </c>
       <c r="O304" s="19">
-        <v>5807810.6299999999</v>
+        <v>5706965.8700000001</v>
       </c>
       <c r="P304" s="20">
-        <v>4.8600000000000003</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="Q304" s="19">
-        <v>14425996.380000001</v>
+        <v>14475597.310000001</v>
       </c>
       <c r="R304" s="20">
-        <v>12.08</v>
+        <v>12.09</v>
       </c>
     </row>
     <row r="305" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -19232,49 +19239,49 @@
         <v>342693877.37</v>
       </c>
       <c r="D306" s="19">
-        <v>74571</v>
+        <v>376321</v>
       </c>
       <c r="E306" s="19">
-        <v>74571</v>
+        <v>376321</v>
       </c>
       <c r="F306" s="19">
         <v>342693877.37</v>
       </c>
       <c r="G306" s="19">
-        <v>191810561.59999999</v>
+        <v>196564318.63999999</v>
       </c>
       <c r="H306" s="20">
-        <v>55.97</v>
+        <v>57.36</v>
       </c>
       <c r="I306" s="19">
-        <v>46731773.200000003</v>
+        <v>51020950.840000004</v>
       </c>
       <c r="J306" s="20">
-        <v>13.64</v>
+        <v>14.89</v>
       </c>
       <c r="K306" s="19">
-        <v>238542334.80000001</v>
+        <v>247585269.47999999</v>
       </c>
       <c r="L306" s="20">
-        <v>69.61</v>
+        <v>72.25</v>
       </c>
       <c r="M306" s="19">
-        <v>104151542.56999999</v>
+        <v>95108607.890000001</v>
       </c>
       <c r="N306" s="20">
-        <v>30.39</v>
+        <v>27.75</v>
       </c>
       <c r="O306" s="19">
-        <v>16227870.789999999</v>
+        <v>14606308.33</v>
       </c>
       <c r="P306" s="20">
-        <v>4.74</v>
+        <v>4.26</v>
       </c>
       <c r="Q306" s="19">
-        <v>87923671.780000001</v>
+        <v>80502299.560000002</v>
       </c>
       <c r="R306" s="20">
-        <v>25.66</v>
+        <v>23.49</v>
       </c>
     </row>
     <row r="307" spans="1:18" x14ac:dyDescent="0.25">
@@ -19310,26 +19317,28 @@
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="G4:H4"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="8" scale="92" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6CED40E-A45E-4A5B-BC75-E0F470D0E7A4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{432D7430-763A-4CE8-BB42-6289CE853E1C}">
   <dimension ref="A1:R84"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.3984375" customWidth="1"/>
+    <col min="1" max="1" width="20.5" customWidth="1"/>
     <col min="2" max="2" width="12.796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.8984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.8984375" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="14.8984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.8984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.3984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.796875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.8984375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.8984375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6.3984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.8984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.796875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="7" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.796875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="5.3984375" bestFit="1" customWidth="1"/>
@@ -19348,7 +19357,7 @@
       <c r="F1" s="27"/>
       <c r="G1" s="27"/>
     </row>
-    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
         <v>580</v>
       </c>
@@ -19490,7 +19499,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>207</v>
       </c>
@@ -19564,28 +19573,28 @@
         <v>1000000</v>
       </c>
       <c r="G8" s="4">
-        <v>533379</v>
+        <v>543339</v>
       </c>
       <c r="H8" s="5">
-        <v>53.34</v>
+        <v>54.33</v>
       </c>
       <c r="I8" s="4">
-        <v>31620</v>
+        <v>54620</v>
       </c>
       <c r="J8" s="5">
-        <v>3.16</v>
+        <v>5.46</v>
       </c>
       <c r="K8" s="4">
-        <v>564999</v>
+        <v>597959</v>
       </c>
       <c r="L8" s="5">
-        <v>56.5</v>
+        <v>59.8</v>
       </c>
       <c r="M8" s="4">
-        <v>435001</v>
+        <v>402041</v>
       </c>
       <c r="N8" s="5">
-        <v>43.5</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="O8" s="4">
         <v>0</v>
@@ -19594,10 +19603,10 @@
         <v>0</v>
       </c>
       <c r="Q8" s="4">
-        <v>435001</v>
+        <v>402041</v>
       </c>
       <c r="R8" s="5">
-        <v>43.5</v>
+        <v>40.200000000000003</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -19620,28 +19629,28 @@
         <v>1000000</v>
       </c>
       <c r="G9" s="8">
-        <v>533379</v>
+        <v>543339</v>
       </c>
       <c r="H9" s="9">
-        <v>53.34</v>
+        <v>54.33</v>
       </c>
       <c r="I9" s="8">
-        <v>31620</v>
+        <v>54620</v>
       </c>
       <c r="J9" s="9">
-        <v>3.16</v>
+        <v>5.46</v>
       </c>
       <c r="K9" s="8">
-        <v>564999</v>
+        <v>597959</v>
       </c>
       <c r="L9" s="9">
-        <v>56.5</v>
+        <v>59.8</v>
       </c>
       <c r="M9" s="8">
-        <v>435001</v>
+        <v>402041</v>
       </c>
       <c r="N9" s="9">
-        <v>43.5</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="O9" s="8">
         <v>0</v>
@@ -19650,10 +19659,10 @@
         <v>0</v>
       </c>
       <c r="Q9" s="8">
-        <v>435001</v>
+        <v>402041</v>
       </c>
       <c r="R9" s="9">
-        <v>43.5</v>
+        <v>40.200000000000003</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -19674,40 +19683,40 @@
         <v>11720000</v>
       </c>
       <c r="G10" s="4">
-        <v>8155521</v>
+        <v>8537901</v>
       </c>
       <c r="H10" s="5">
-        <v>69.59</v>
+        <v>72.849999999999994</v>
       </c>
       <c r="I10" s="4">
-        <v>1281876</v>
+        <v>1415896</v>
       </c>
       <c r="J10" s="5">
-        <v>10.94</v>
+        <v>12.08</v>
       </c>
       <c r="K10" s="4">
-        <v>9437397</v>
+        <v>9953797</v>
       </c>
       <c r="L10" s="5">
-        <v>80.52</v>
+        <v>84.93</v>
       </c>
       <c r="M10" s="4">
-        <v>2282603</v>
+        <v>1766203</v>
       </c>
       <c r="N10" s="5">
-        <v>19.48</v>
+        <v>15.07</v>
       </c>
       <c r="O10" s="4">
-        <v>30600</v>
+        <v>80600</v>
       </c>
       <c r="P10" s="5">
-        <v>0.26</v>
+        <v>0.69</v>
       </c>
       <c r="Q10" s="4">
-        <v>2252003</v>
+        <v>1685603</v>
       </c>
       <c r="R10" s="5">
-        <v>19.22</v>
+        <v>14.38</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -19730,40 +19739,40 @@
         <v>11720000</v>
       </c>
       <c r="G11" s="8">
-        <v>8155521</v>
+        <v>8537901</v>
       </c>
       <c r="H11" s="9">
-        <v>69.59</v>
+        <v>72.849999999999994</v>
       </c>
       <c r="I11" s="8">
-        <v>1281876</v>
+        <v>1415896</v>
       </c>
       <c r="J11" s="9">
-        <v>10.94</v>
+        <v>12.08</v>
       </c>
       <c r="K11" s="8">
-        <v>9437397</v>
+        <v>9953797</v>
       </c>
       <c r="L11" s="9">
-        <v>80.52</v>
+        <v>84.93</v>
       </c>
       <c r="M11" s="8">
-        <v>2282603</v>
+        <v>1766203</v>
       </c>
       <c r="N11" s="9">
-        <v>19.48</v>
+        <v>15.07</v>
       </c>
       <c r="O11" s="8">
-        <v>30600</v>
+        <v>80600</v>
       </c>
       <c r="P11" s="9">
-        <v>0.26</v>
+        <v>0.69</v>
       </c>
       <c r="Q11" s="8">
-        <v>2252003</v>
+        <v>1685603</v>
       </c>
       <c r="R11" s="9">
-        <v>19.22</v>
+        <v>14.38</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -19784,28 +19793,28 @@
         <v>11820000</v>
       </c>
       <c r="G12" s="4">
-        <v>8855980.1600000001</v>
+        <v>9301515.1600000001</v>
       </c>
       <c r="H12" s="5">
-        <v>74.92</v>
+        <v>78.69</v>
       </c>
       <c r="I12" s="4">
-        <v>648546</v>
+        <v>1198211</v>
       </c>
       <c r="J12" s="5">
-        <v>5.49</v>
+        <v>10.14</v>
       </c>
       <c r="K12" s="4">
-        <v>9504526.1600000001</v>
+        <v>10499726.16</v>
       </c>
       <c r="L12" s="5">
-        <v>80.41</v>
+        <v>88.83</v>
       </c>
       <c r="M12" s="4">
-        <v>2315473.84</v>
+        <v>1320273.8400000001</v>
       </c>
       <c r="N12" s="5">
-        <v>19.59</v>
+        <v>11.17</v>
       </c>
       <c r="O12" s="4">
         <v>13307</v>
@@ -19814,10 +19823,10 @@
         <v>0.11</v>
       </c>
       <c r="Q12" s="4">
-        <v>2302166.84</v>
+        <v>1306966.8400000001</v>
       </c>
       <c r="R12" s="5">
-        <v>19.48</v>
+        <v>11.06</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -19840,16 +19849,16 @@
         <v>1180000</v>
       </c>
       <c r="G13" s="8">
-        <v>871902.87</v>
+        <v>876202.87</v>
       </c>
       <c r="H13" s="9">
-        <v>73.89</v>
+        <v>74.25</v>
       </c>
       <c r="I13" s="8">
-        <v>4300</v>
+        <v>0</v>
       </c>
       <c r="J13" s="9">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="K13" s="8">
         <v>876202.87</v>
@@ -19896,28 +19905,28 @@
         <v>10640000</v>
       </c>
       <c r="G14" s="8">
-        <v>7984077.29</v>
+        <v>8425312.2899999991</v>
       </c>
       <c r="H14" s="9">
-        <v>75.040000000000006</v>
+        <v>79.19</v>
       </c>
       <c r="I14" s="8">
-        <v>644246</v>
+        <v>1198211</v>
       </c>
       <c r="J14" s="9">
-        <v>6.05</v>
+        <v>11.26</v>
       </c>
       <c r="K14" s="8">
-        <v>8628323.2899999991</v>
+        <v>9623523.2899999991</v>
       </c>
       <c r="L14" s="9">
-        <v>81.09</v>
+        <v>90.45</v>
       </c>
       <c r="M14" s="8">
-        <v>2011676.71</v>
+        <v>1016476.71</v>
       </c>
       <c r="N14" s="9">
-        <v>18.91</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="O14" s="8">
         <v>13307</v>
@@ -19926,10 +19935,10 @@
         <v>0.13</v>
       </c>
       <c r="Q14" s="8">
-        <v>1998369.71</v>
+        <v>1003169.71</v>
       </c>
       <c r="R14" s="9">
-        <v>18.78</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -19950,43 +19959,43 @@
         <v>11840200</v>
       </c>
       <c r="G15" s="4">
-        <v>9580417.8599999994</v>
+        <v>9928337.1500000004</v>
       </c>
       <c r="H15" s="5">
-        <v>80.91</v>
+        <v>83.85</v>
       </c>
       <c r="I15" s="4">
-        <v>1270099.67</v>
+        <v>1213855.3799999999</v>
       </c>
       <c r="J15" s="5">
-        <v>10.73</v>
+        <v>10.25</v>
       </c>
       <c r="K15" s="4">
-        <v>10850517.529999999</v>
+        <v>11142192.529999999</v>
       </c>
       <c r="L15" s="5">
-        <v>91.64</v>
+        <v>94.1</v>
       </c>
       <c r="M15" s="4">
-        <v>989682.47</v>
+        <v>698007.47</v>
       </c>
       <c r="N15" s="5">
-        <v>8.36</v>
+        <v>5.9</v>
       </c>
       <c r="O15" s="4">
-        <v>110079.5</v>
+        <v>30079.5</v>
       </c>
       <c r="P15" s="5">
-        <v>0.93</v>
+        <v>0.25</v>
       </c>
       <c r="Q15" s="4">
-        <v>879602.97</v>
+        <v>667927.97</v>
       </c>
       <c r="R15" s="5">
-        <v>7.43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+        <v>5.64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>75</v>
       </c>
@@ -20012,22 +20021,22 @@
         <v>94.22</v>
       </c>
       <c r="I16" s="8">
-        <v>0</v>
+        <v>16900</v>
       </c>
       <c r="J16" s="9">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="K16" s="8">
-        <v>471112.9</v>
+        <v>488012.9</v>
       </c>
       <c r="L16" s="9">
-        <v>94.22</v>
+        <v>97.6</v>
       </c>
       <c r="M16" s="8">
-        <v>28887.1</v>
+        <v>11987.1</v>
       </c>
       <c r="N16" s="9">
-        <v>5.78</v>
+        <v>2.4</v>
       </c>
       <c r="O16" s="8">
         <v>0</v>
@@ -20036,10 +20045,10 @@
         <v>0</v>
       </c>
       <c r="Q16" s="8">
-        <v>28887.1</v>
+        <v>11987.1</v>
       </c>
       <c r="R16" s="9">
-        <v>5.78</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -20062,40 +20071,40 @@
         <v>11340200</v>
       </c>
       <c r="G17" s="8">
-        <v>9109304.9600000009</v>
+        <v>9457224.25</v>
       </c>
       <c r="H17" s="9">
-        <v>80.33</v>
+        <v>83.4</v>
       </c>
       <c r="I17" s="8">
-        <v>1270099.67</v>
+        <v>1196955.3799999999</v>
       </c>
       <c r="J17" s="9">
-        <v>11.2</v>
+        <v>10.55</v>
       </c>
       <c r="K17" s="8">
-        <v>10379404.630000001</v>
+        <v>10654179.630000001</v>
       </c>
       <c r="L17" s="9">
-        <v>91.53</v>
+        <v>93.95</v>
       </c>
       <c r="M17" s="8">
-        <v>960795.37</v>
+        <v>686020.37</v>
       </c>
       <c r="N17" s="9">
-        <v>8.4700000000000006</v>
+        <v>6.05</v>
       </c>
       <c r="O17" s="8">
-        <v>110079.5</v>
+        <v>30079.5</v>
       </c>
       <c r="P17" s="9">
-        <v>0.97</v>
+        <v>0.27</v>
       </c>
       <c r="Q17" s="8">
-        <v>850715.87</v>
+        <v>655940.87</v>
       </c>
       <c r="R17" s="9">
-        <v>7.5</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -20116,40 +20125,40 @@
         <v>7820000</v>
       </c>
       <c r="G18" s="4">
-        <v>5096948.3</v>
+        <v>5751283.2999999998</v>
       </c>
       <c r="H18" s="5">
-        <v>65.180000000000007</v>
+        <v>73.55</v>
       </c>
       <c r="I18" s="4">
-        <v>1035644</v>
+        <v>1689454</v>
       </c>
       <c r="J18" s="5">
-        <v>13.24</v>
+        <v>21.6</v>
       </c>
       <c r="K18" s="4">
-        <v>6132592.2999999998</v>
+        <v>7440737.2999999998</v>
       </c>
       <c r="L18" s="5">
-        <v>78.42</v>
+        <v>95.15</v>
       </c>
       <c r="M18" s="4">
-        <v>1687407.7</v>
+        <v>379262.7</v>
       </c>
       <c r="N18" s="5">
-        <v>21.58</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="O18" s="4">
-        <v>550000</v>
+        <v>70000</v>
       </c>
       <c r="P18" s="5">
-        <v>7.03</v>
+        <v>0.9</v>
       </c>
       <c r="Q18" s="4">
-        <v>1137407.7</v>
+        <v>309262.7</v>
       </c>
       <c r="R18" s="5">
-        <v>14.54</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="66" x14ac:dyDescent="0.25">
@@ -20172,40 +20181,40 @@
         <v>7820000</v>
       </c>
       <c r="G19" s="8">
-        <v>5096948.3</v>
+        <v>5751283.2999999998</v>
       </c>
       <c r="H19" s="9">
-        <v>65.180000000000007</v>
+        <v>73.55</v>
       </c>
       <c r="I19" s="8">
-        <v>1035644</v>
+        <v>1689454</v>
       </c>
       <c r="J19" s="9">
-        <v>13.24</v>
+        <v>21.6</v>
       </c>
       <c r="K19" s="8">
-        <v>6132592.2999999998</v>
+        <v>7440737.2999999998</v>
       </c>
       <c r="L19" s="9">
-        <v>78.42</v>
+        <v>95.15</v>
       </c>
       <c r="M19" s="8">
-        <v>1687407.7</v>
+        <v>379262.7</v>
       </c>
       <c r="N19" s="9">
-        <v>21.58</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="O19" s="8">
-        <v>550000</v>
+        <v>70000</v>
       </c>
       <c r="P19" s="9">
-        <v>7.03</v>
+        <v>0.9</v>
       </c>
       <c r="Q19" s="8">
-        <v>1137407.7</v>
+        <v>309262.7</v>
       </c>
       <c r="R19" s="9">
-        <v>14.54</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -20226,40 +20235,40 @@
         <v>13420000</v>
       </c>
       <c r="G20" s="4">
-        <v>10751421.42</v>
+        <v>11285252.42</v>
       </c>
       <c r="H20" s="5">
-        <v>80.11</v>
+        <v>84.09</v>
       </c>
       <c r="I20" s="4">
-        <v>751226</v>
+        <v>1085194.7</v>
       </c>
       <c r="J20" s="5">
-        <v>5.6</v>
+        <v>8.09</v>
       </c>
       <c r="K20" s="4">
-        <v>11502647.42</v>
+        <v>12370447.119999999</v>
       </c>
       <c r="L20" s="5">
-        <v>85.71</v>
+        <v>92.18</v>
       </c>
       <c r="M20" s="4">
-        <v>1917352.58</v>
+        <v>1049552.8799999999</v>
       </c>
       <c r="N20" s="5">
-        <v>14.29</v>
+        <v>7.82</v>
       </c>
       <c r="O20" s="4">
-        <v>497000</v>
+        <v>382034.3</v>
       </c>
       <c r="P20" s="5">
-        <v>3.7</v>
+        <v>2.85</v>
       </c>
       <c r="Q20" s="4">
-        <v>1420352.58</v>
+        <v>667518.57999999996</v>
       </c>
       <c r="R20" s="5">
-        <v>10.58</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -20282,40 +20291,40 @@
         <v>13420000</v>
       </c>
       <c r="G21" s="8">
-        <v>10751421.42</v>
+        <v>11285252.42</v>
       </c>
       <c r="H21" s="9">
-        <v>80.11</v>
+        <v>84.09</v>
       </c>
       <c r="I21" s="8">
-        <v>751226</v>
+        <v>1085194.7</v>
       </c>
       <c r="J21" s="9">
-        <v>5.6</v>
+        <v>8.09</v>
       </c>
       <c r="K21" s="8">
-        <v>11502647.42</v>
+        <v>12370447.119999999</v>
       </c>
       <c r="L21" s="9">
-        <v>85.71</v>
+        <v>92.18</v>
       </c>
       <c r="M21" s="8">
-        <v>1917352.58</v>
+        <v>1049552.8799999999</v>
       </c>
       <c r="N21" s="9">
-        <v>14.29</v>
+        <v>7.82</v>
       </c>
       <c r="O21" s="8">
-        <v>497000</v>
+        <v>382034.3</v>
       </c>
       <c r="P21" s="9">
-        <v>3.7</v>
+        <v>2.85</v>
       </c>
       <c r="Q21" s="8">
-        <v>1420352.58</v>
+        <v>667518.57999999996</v>
       </c>
       <c r="R21" s="9">
-        <v>10.58</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -20327,52 +20336,52 @@
         <v>107227000</v>
       </c>
       <c r="D22" s="4">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="E22" s="4">
         <v>0</v>
       </c>
       <c r="F22" s="4">
-        <v>107227000</v>
+        <v>107527000</v>
       </c>
       <c r="G22" s="4">
-        <v>83389515.129999995</v>
+        <v>83496956.280000001</v>
       </c>
       <c r="H22" s="5">
-        <v>77.77</v>
+        <v>77.650000000000006</v>
       </c>
       <c r="I22" s="4">
-        <v>5117969.88</v>
+        <v>5328812.5599999996</v>
       </c>
       <c r="J22" s="5">
-        <v>4.7699999999999996</v>
+        <v>4.96</v>
       </c>
       <c r="K22" s="4">
-        <v>88507485.010000005</v>
+        <v>88825768.840000004</v>
       </c>
       <c r="L22" s="5">
-        <v>82.54</v>
+        <v>82.61</v>
       </c>
       <c r="M22" s="4">
-        <v>18719514.989999998</v>
+        <v>18701231.16</v>
       </c>
       <c r="N22" s="5">
-        <v>17.46</v>
+        <v>17.39</v>
       </c>
       <c r="O22" s="4">
         <v>5006965.87</v>
       </c>
       <c r="P22" s="5">
-        <v>4.67</v>
+        <v>4.66</v>
       </c>
       <c r="Q22" s="4">
-        <v>13712549.119999999</v>
+        <v>13694265.289999999</v>
       </c>
       <c r="R22" s="5">
-        <v>12.79</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
+        <v>12.74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>190</v>
       </c>
@@ -20392,28 +20401,28 @@
         <v>29200000</v>
       </c>
       <c r="G23" s="8">
-        <v>18184522.469999999</v>
+        <v>18221614.789999999</v>
       </c>
       <c r="H23" s="9">
-        <v>62.28</v>
+        <v>62.4</v>
       </c>
       <c r="I23" s="8">
-        <v>5051979.6500000004</v>
+        <v>5019002.33</v>
       </c>
       <c r="J23" s="9">
-        <v>17.3</v>
+        <v>17.190000000000001</v>
       </c>
       <c r="K23" s="8">
-        <v>23236502.120000001</v>
+        <v>23240617.120000001</v>
       </c>
       <c r="L23" s="9">
-        <v>79.58</v>
+        <v>79.59</v>
       </c>
       <c r="M23" s="8">
-        <v>5963497.8799999999</v>
+        <v>5959382.8799999999</v>
       </c>
       <c r="N23" s="9">
-        <v>20.420000000000002</v>
+        <v>20.41</v>
       </c>
       <c r="O23" s="8">
         <v>5005423.37</v>
@@ -20422,10 +20431,10 @@
         <v>17.14</v>
       </c>
       <c r="Q23" s="8">
-        <v>958074.51</v>
+        <v>953959.51</v>
       </c>
       <c r="R23" s="9">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="24" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -20439,37 +20448,37 @@
         <v>78027000</v>
       </c>
       <c r="D24" s="8">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="E24" s="8">
         <v>0</v>
       </c>
       <c r="F24" s="8">
-        <v>78027000</v>
+        <v>78327000</v>
       </c>
       <c r="G24" s="8">
-        <v>65204992.659999996</v>
+        <v>65275341.490000002</v>
       </c>
       <c r="H24" s="9">
-        <v>83.57</v>
+        <v>83.34</v>
       </c>
       <c r="I24" s="8">
-        <v>65990.23</v>
+        <v>309810.23</v>
       </c>
       <c r="J24" s="9">
-        <v>0.08</v>
+        <v>0.4</v>
       </c>
       <c r="K24" s="8">
-        <v>65270982.890000001</v>
+        <v>65585151.719999999</v>
       </c>
       <c r="L24" s="9">
-        <v>83.65</v>
+        <v>83.73</v>
       </c>
       <c r="M24" s="8">
-        <v>12756017.109999999</v>
+        <v>12741848.279999999</v>
       </c>
       <c r="N24" s="9">
-        <v>16.350000000000001</v>
+        <v>16.27</v>
       </c>
       <c r="O24" s="8">
         <v>1542.5</v>
@@ -20478,10 +20487,10 @@
         <v>0</v>
       </c>
       <c r="Q24" s="8">
-        <v>12754474.609999999</v>
+        <v>12740305.779999999</v>
       </c>
       <c r="R24" s="9">
-        <v>16.350000000000001</v>
+        <v>16.27</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -20564,37 +20573,37 @@
         <v>49.5</v>
       </c>
       <c r="I26" s="4">
-        <v>428863.16</v>
+        <v>913209.17</v>
       </c>
       <c r="J26" s="5">
-        <v>10.07</v>
+        <v>21.44</v>
       </c>
       <c r="K26" s="4">
-        <v>2537734.1</v>
+        <v>3022080.11</v>
       </c>
       <c r="L26" s="5">
-        <v>59.57</v>
+        <v>70.94</v>
       </c>
       <c r="M26" s="4">
-        <v>1722265.9</v>
+        <v>1237919.8899999999</v>
       </c>
       <c r="N26" s="5">
-        <v>40.43</v>
+        <v>29.06</v>
       </c>
       <c r="O26" s="4">
-        <v>274000</v>
+        <v>270000</v>
       </c>
       <c r="P26" s="5">
-        <v>6.43</v>
+        <v>6.34</v>
       </c>
       <c r="Q26" s="4">
-        <v>1448265.9</v>
+        <v>967919.89</v>
       </c>
       <c r="R26" s="5">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" ht="66" x14ac:dyDescent="0.25">
+        <v>22.72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>59</v>
       </c>
@@ -20620,34 +20629,34 @@
         <v>49.5</v>
       </c>
       <c r="I27" s="8">
-        <v>428863.16</v>
+        <v>913209.17</v>
       </c>
       <c r="J27" s="9">
-        <v>10.07</v>
+        <v>21.44</v>
       </c>
       <c r="K27" s="8">
-        <v>2537734.1</v>
+        <v>3022080.11</v>
       </c>
       <c r="L27" s="9">
-        <v>59.57</v>
+        <v>70.94</v>
       </c>
       <c r="M27" s="8">
-        <v>1722265.9</v>
+        <v>1237919.8899999999</v>
       </c>
       <c r="N27" s="9">
-        <v>40.43</v>
+        <v>29.06</v>
       </c>
       <c r="O27" s="8">
-        <v>274000</v>
+        <v>270000</v>
       </c>
       <c r="P27" s="9">
-        <v>6.43</v>
+        <v>6.34</v>
       </c>
       <c r="Q27" s="8">
-        <v>1448265.9</v>
+        <v>967919.89</v>
       </c>
       <c r="R27" s="9">
-        <v>34</v>
+        <v>22.72</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
@@ -20668,43 +20677,43 @@
         <v>60595000</v>
       </c>
       <c r="G28" s="4">
-        <v>31347172.879999999</v>
+        <v>32015782.18</v>
       </c>
       <c r="H28" s="5">
-        <v>51.73</v>
+        <v>52.84</v>
       </c>
       <c r="I28" s="4">
-        <v>19556636.109999999</v>
+        <v>19943654.949999999</v>
       </c>
       <c r="J28" s="5">
-        <v>32.270000000000003</v>
+        <v>32.909999999999997</v>
       </c>
       <c r="K28" s="4">
-        <v>50903808.990000002</v>
+        <v>51959437.130000003</v>
       </c>
       <c r="L28" s="5">
-        <v>84.01</v>
+        <v>85.75</v>
       </c>
       <c r="M28" s="4">
-        <v>9691191.0099999998</v>
+        <v>8635562.8699999992</v>
       </c>
       <c r="N28" s="5">
-        <v>15.99</v>
+        <v>14.25</v>
       </c>
       <c r="O28" s="4">
-        <v>5060196.3</v>
+        <v>5237599.54</v>
       </c>
       <c r="P28" s="5">
-        <v>8.35</v>
+        <v>8.64</v>
       </c>
       <c r="Q28" s="4">
-        <v>4630994.71</v>
+        <v>3397963.33</v>
       </c>
       <c r="R28" s="5">
-        <v>7.64</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" ht="66" x14ac:dyDescent="0.25">
+        <v>5.61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>17</v>
       </c>
@@ -20724,40 +20733,40 @@
         <v>37235000</v>
       </c>
       <c r="G29" s="8">
-        <v>18382086.129999999</v>
+        <v>18510661.129999999</v>
       </c>
       <c r="H29" s="9">
-        <v>49.37</v>
+        <v>49.71</v>
       </c>
       <c r="I29" s="8">
-        <v>14046467</v>
+        <v>14689922</v>
       </c>
       <c r="J29" s="9">
-        <v>37.72</v>
+        <v>39.450000000000003</v>
       </c>
       <c r="K29" s="8">
-        <v>32428553.129999999</v>
+        <v>33200583.129999999</v>
       </c>
       <c r="L29" s="9">
-        <v>87.09</v>
+        <v>89.16</v>
       </c>
       <c r="M29" s="8">
-        <v>4806446.87</v>
+        <v>4034416.87</v>
       </c>
       <c r="N29" s="9">
-        <v>12.91</v>
+        <v>10.84</v>
       </c>
       <c r="O29" s="8">
-        <v>1106800</v>
+        <v>1460000</v>
       </c>
       <c r="P29" s="9">
-        <v>2.97</v>
+        <v>3.92</v>
       </c>
       <c r="Q29" s="8">
-        <v>3699646.87</v>
+        <v>2574416.87</v>
       </c>
       <c r="R29" s="9">
-        <v>9.94</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="26.4" x14ac:dyDescent="0.25">
@@ -20836,40 +20845,40 @@
         <v>2612914</v>
       </c>
       <c r="G31" s="8">
-        <v>1724806.67</v>
+        <v>1743797.81</v>
       </c>
       <c r="H31" s="9">
-        <v>66.010000000000005</v>
+        <v>66.739999999999995</v>
       </c>
       <c r="I31" s="8">
-        <v>334583</v>
+        <v>326293</v>
       </c>
       <c r="J31" s="9">
-        <v>12.8</v>
+        <v>12.49</v>
       </c>
       <c r="K31" s="8">
-        <v>2059389.67</v>
+        <v>2070090.81</v>
       </c>
       <c r="L31" s="9">
-        <v>78.819999999999993</v>
+        <v>79.23</v>
       </c>
       <c r="M31" s="8">
-        <v>553524.32999999996</v>
+        <v>542823.18999999994</v>
       </c>
       <c r="N31" s="9">
-        <v>21.18</v>
+        <v>20.77</v>
       </c>
       <c r="O31" s="8">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="P31" s="9">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Q31" s="8">
-        <v>553524.32999999996</v>
+        <v>442823.19</v>
       </c>
       <c r="R31" s="9">
-        <v>21.18</v>
+        <v>16.95</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="39.6" x14ac:dyDescent="0.25">
@@ -20892,40 +20901,40 @@
         <v>9800000</v>
       </c>
       <c r="G32" s="8">
-        <v>5612006.6399999997</v>
+        <v>5667604.7999999998</v>
       </c>
       <c r="H32" s="9">
-        <v>57.27</v>
+        <v>57.83</v>
       </c>
       <c r="I32" s="8">
-        <v>863008.31</v>
+        <v>1080307.1499999999</v>
       </c>
       <c r="J32" s="9">
-        <v>8.81</v>
+        <v>11.02</v>
       </c>
       <c r="K32" s="8">
-        <v>6475014.9500000002</v>
+        <v>6747911.9500000002</v>
       </c>
       <c r="L32" s="9">
-        <v>66.069999999999993</v>
+        <v>68.86</v>
       </c>
       <c r="M32" s="8">
-        <v>3324985.05</v>
+        <v>3052088.05</v>
       </c>
       <c r="N32" s="9">
-        <v>33.93</v>
+        <v>31.14</v>
       </c>
       <c r="O32" s="8">
-        <v>3152551.54</v>
+        <v>2977599.54</v>
       </c>
       <c r="P32" s="9">
-        <v>32.17</v>
+        <v>30.38</v>
       </c>
       <c r="Q32" s="8">
-        <v>172433.51</v>
+        <v>74488.509999999995</v>
       </c>
       <c r="R32" s="9">
-        <v>1.76</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="33" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
@@ -20948,16 +20957,16 @@
         <v>10194186</v>
       </c>
       <c r="G33" s="8">
-        <v>5014823.4400000004</v>
+        <v>5480268.4400000004</v>
       </c>
       <c r="H33" s="9">
-        <v>49.19</v>
+        <v>53.76</v>
       </c>
       <c r="I33" s="8">
-        <v>4162577.8</v>
+        <v>3697132.8</v>
       </c>
       <c r="J33" s="9">
-        <v>40.83</v>
+        <v>36.270000000000003</v>
       </c>
       <c r="K33" s="8">
         <v>9177401.2400000002</v>
@@ -20972,16 +20981,16 @@
         <v>9.9700000000000006</v>
       </c>
       <c r="O33" s="8">
-        <v>800844.76</v>
+        <v>700000</v>
       </c>
       <c r="P33" s="9">
-        <v>7.86</v>
+        <v>6.87</v>
       </c>
       <c r="Q33" s="8">
-        <v>215940</v>
+        <v>316784.76</v>
       </c>
       <c r="R33" s="9">
-        <v>2.12</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
@@ -20993,49 +21002,49 @@
         <v>230702200</v>
       </c>
       <c r="D34" s="14">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="E34" s="14">
         <v>0</v>
       </c>
       <c r="F34" s="14">
-        <v>230702200</v>
+        <v>231002200</v>
       </c>
       <c r="G34" s="14">
-        <v>160641178.43000001</v>
+        <v>163791189.16999999</v>
       </c>
       <c r="H34" s="15">
-        <v>69.63</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="I34" s="14">
-        <v>30238022.82</v>
+        <v>32958449.760000002</v>
       </c>
       <c r="J34" s="15">
-        <v>13.11</v>
+        <v>14.27</v>
       </c>
       <c r="K34" s="14">
-        <v>190879201.25</v>
+        <v>196749638.93000001</v>
       </c>
       <c r="L34" s="15">
-        <v>82.74</v>
+        <v>85.17</v>
       </c>
       <c r="M34" s="14">
-        <v>39822998.75</v>
+        <v>34252561.07</v>
       </c>
       <c r="N34" s="15">
-        <v>17.260000000000002</v>
+        <v>14.83</v>
       </c>
       <c r="O34" s="14">
-        <v>11542148.67</v>
+        <v>11090586.210000001</v>
       </c>
       <c r="P34" s="15">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q34" s="14">
-        <v>28280850.079999998</v>
+        <v>23161974.859999999</v>
       </c>
       <c r="R34" s="15">
-        <v>12.26</v>
+        <v>10.029999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
@@ -21092,7 +21101,7 @@
         <v>54.44</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>279</v>
       </c>
@@ -21270,16 +21279,16 @@
         <v>0</v>
       </c>
       <c r="E39" s="4">
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="F39" s="4">
-        <v>2936503.78</v>
+        <v>2934753.78</v>
       </c>
       <c r="G39" s="4">
         <v>1697269.18</v>
       </c>
       <c r="H39" s="5">
-        <v>57.8</v>
+        <v>57.83</v>
       </c>
       <c r="I39" s="4">
         <v>80500</v>
@@ -21291,13 +21300,13 @@
         <v>1777769.18</v>
       </c>
       <c r="L39" s="5">
-        <v>60.54</v>
+        <v>60.58</v>
       </c>
       <c r="M39" s="4">
-        <v>1158734.6000000001</v>
+        <v>1156984.6000000001</v>
       </c>
       <c r="N39" s="5">
-        <v>39.46</v>
+        <v>39.42</v>
       </c>
       <c r="O39" s="4">
         <v>0</v>
@@ -21306,13 +21315,13 @@
         <v>0</v>
       </c>
       <c r="Q39" s="4">
-        <v>1158734.6000000001</v>
+        <v>1156984.6000000001</v>
       </c>
       <c r="R39" s="5">
-        <v>39.46</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
+        <v>39.42</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
         <v>307</v>
       </c>
@@ -21326,16 +21335,16 @@
         <v>0</v>
       </c>
       <c r="E40" s="8">
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="F40" s="8">
-        <v>2936503.78</v>
+        <v>2934753.78</v>
       </c>
       <c r="G40" s="8">
         <v>1697269.18</v>
       </c>
       <c r="H40" s="9">
-        <v>57.8</v>
+        <v>57.83</v>
       </c>
       <c r="I40" s="8">
         <v>80500</v>
@@ -21347,13 +21356,13 @@
         <v>1777769.18</v>
       </c>
       <c r="L40" s="9">
-        <v>60.54</v>
+        <v>60.58</v>
       </c>
       <c r="M40" s="8">
-        <v>1158734.6000000001</v>
+        <v>1156984.6000000001</v>
       </c>
       <c r="N40" s="9">
-        <v>39.46</v>
+        <v>39.42</v>
       </c>
       <c r="O40" s="8">
         <v>0</v>
@@ -21362,10 +21371,10 @@
         <v>0</v>
       </c>
       <c r="Q40" s="8">
-        <v>1158734.6000000001</v>
+        <v>1156984.6000000001</v>
       </c>
       <c r="R40" s="9">
-        <v>39.46</v>
+        <v>39.42</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
@@ -21386,43 +21395,43 @@
         <v>22602752.809999999</v>
       </c>
       <c r="G41" s="4">
-        <v>9762486.0299999993</v>
+        <v>9790329.3300000001</v>
       </c>
       <c r="H41" s="5">
-        <v>43.19</v>
+        <v>43.31</v>
       </c>
       <c r="I41" s="4">
-        <v>3103498.42</v>
+        <v>3783355.12</v>
       </c>
       <c r="J41" s="5">
-        <v>13.73</v>
+        <v>16.739999999999998</v>
       </c>
       <c r="K41" s="4">
-        <v>12865984.449999999</v>
+        <v>13573684.449999999</v>
       </c>
       <c r="L41" s="5">
-        <v>56.92</v>
+        <v>60.05</v>
       </c>
       <c r="M41" s="4">
-        <v>9736768.3599999994</v>
+        <v>9029068.3599999994</v>
       </c>
       <c r="N41" s="5">
-        <v>43.08</v>
+        <v>39.950000000000003</v>
       </c>
       <c r="O41" s="4">
-        <v>1182093</v>
+        <v>712093</v>
       </c>
       <c r="P41" s="5">
-        <v>5.23</v>
+        <v>3.15</v>
       </c>
       <c r="Q41" s="4">
-        <v>8554675.3599999994</v>
+        <v>8316975.3600000003</v>
       </c>
       <c r="R41" s="5">
-        <v>37.85</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
+        <v>36.799999999999997</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
         <v>267</v>
       </c>
@@ -21442,28 +21451,28 @@
         <v>7840527.8099999996</v>
       </c>
       <c r="G42" s="8">
-        <v>6012020.5899999999</v>
+        <v>6024758.8899999997</v>
       </c>
       <c r="H42" s="9">
-        <v>76.680000000000007</v>
+        <v>76.84</v>
       </c>
       <c r="I42" s="8">
-        <v>778724.86</v>
+        <v>766386.56</v>
       </c>
       <c r="J42" s="9">
-        <v>9.93</v>
+        <v>9.77</v>
       </c>
       <c r="K42" s="8">
-        <v>6790745.4500000002</v>
+        <v>6791145.4500000002</v>
       </c>
       <c r="L42" s="9">
-        <v>86.61</v>
+        <v>86.62</v>
       </c>
       <c r="M42" s="8">
-        <v>1049782.3600000001</v>
+        <v>1049382.3600000001</v>
       </c>
       <c r="N42" s="9">
-        <v>13.39</v>
+        <v>13.38</v>
       </c>
       <c r="O42" s="8">
         <v>106945</v>
@@ -21472,10 +21481,10 @@
         <v>1.36</v>
       </c>
       <c r="Q42" s="8">
-        <v>942837.36</v>
+        <v>942437.36</v>
       </c>
       <c r="R42" s="9">
-        <v>12.03</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="43" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
@@ -21498,34 +21507,34 @@
         <v>12554100</v>
       </c>
       <c r="G43" s="8">
-        <v>3723690.44</v>
+        <v>3738785.44</v>
       </c>
       <c r="H43" s="9">
-        <v>29.66</v>
+        <v>29.78</v>
       </c>
       <c r="I43" s="8">
-        <v>1075273.56</v>
+        <v>1210178.5600000001</v>
       </c>
       <c r="J43" s="9">
-        <v>8.57</v>
+        <v>9.64</v>
       </c>
       <c r="K43" s="8">
-        <v>4798964</v>
+        <v>4948964</v>
       </c>
       <c r="L43" s="9">
-        <v>38.229999999999997</v>
+        <v>39.42</v>
       </c>
       <c r="M43" s="8">
-        <v>7755136</v>
+        <v>7605136</v>
       </c>
       <c r="N43" s="9">
-        <v>61.77</v>
+        <v>60.58</v>
       </c>
       <c r="O43" s="8">
-        <v>715148</v>
+        <v>565148</v>
       </c>
       <c r="P43" s="9">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="Q43" s="8">
         <v>7039988</v>
@@ -21534,7 +21543,7 @@
         <v>56.08</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="66" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>541</v>
       </c>
@@ -21554,40 +21563,40 @@
         <v>2208125</v>
       </c>
       <c r="G44" s="8">
-        <v>26775</v>
+        <v>26785</v>
       </c>
       <c r="H44" s="9">
         <v>1.21</v>
       </c>
       <c r="I44" s="8">
-        <v>1249500</v>
+        <v>1806790</v>
       </c>
       <c r="J44" s="9">
-        <v>56.59</v>
+        <v>81.819999999999993</v>
       </c>
       <c r="K44" s="8">
-        <v>1276275</v>
+        <v>1833575</v>
       </c>
       <c r="L44" s="9">
-        <v>57.8</v>
+        <v>83.04</v>
       </c>
       <c r="M44" s="8">
-        <v>931850</v>
+        <v>374550</v>
       </c>
       <c r="N44" s="9">
-        <v>42.2</v>
+        <v>16.96</v>
       </c>
       <c r="O44" s="8">
-        <v>360000</v>
+        <v>40000</v>
       </c>
       <c r="P44" s="9">
-        <v>16.3</v>
+        <v>1.81</v>
       </c>
       <c r="Q44" s="8">
-        <v>571850</v>
+        <v>334550</v>
       </c>
       <c r="R44" s="9">
-        <v>25.9</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
@@ -21644,7 +21653,7 @@
         <v>82.25</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="66" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>488</v>
       </c>
@@ -21700,7 +21709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
         <v>548</v>
       </c>
@@ -21774,43 +21783,43 @@
         <v>72788490.920000002</v>
       </c>
       <c r="G48" s="4">
-        <v>18730758.73</v>
+        <v>20306631.73</v>
       </c>
       <c r="H48" s="5">
-        <v>25.73</v>
+        <v>27.9</v>
       </c>
       <c r="I48" s="4">
-        <v>13201338.26</v>
+        <v>14090262.26</v>
       </c>
       <c r="J48" s="5">
-        <v>18.14</v>
+        <v>19.36</v>
       </c>
       <c r="K48" s="4">
-        <v>31932096.989999998</v>
+        <v>34396893.990000002</v>
       </c>
       <c r="L48" s="5">
-        <v>43.87</v>
+        <v>47.26</v>
       </c>
       <c r="M48" s="4">
-        <v>40856393.93</v>
+        <v>38391596.93</v>
       </c>
       <c r="N48" s="5">
-        <v>56.13</v>
+        <v>52.74</v>
       </c>
       <c r="O48" s="4">
-        <v>3377500</v>
+        <v>2677500</v>
       </c>
       <c r="P48" s="5">
-        <v>4.6399999999999997</v>
+        <v>3.68</v>
       </c>
       <c r="Q48" s="4">
-        <v>37478893.93</v>
+        <v>35714096.93</v>
       </c>
       <c r="R48" s="5">
-        <v>51.49</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" ht="145.19999999999999" x14ac:dyDescent="0.25">
+        <v>49.07</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="118.8" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>248</v>
       </c>
@@ -21866,7 +21875,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="105.6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>260</v>
       </c>
@@ -21922,7 +21931,7 @@
         <v>99.98</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="66" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
         <v>299</v>
       </c>
@@ -22054,28 +22063,28 @@
         <v>8926239.0199999996</v>
       </c>
       <c r="G53" s="8">
-        <v>2165382.08</v>
+        <v>2952795.08</v>
       </c>
       <c r="H53" s="9">
-        <v>24.26</v>
+        <v>33.08</v>
       </c>
       <c r="I53" s="8">
-        <v>4417881</v>
+        <v>3617245</v>
       </c>
       <c r="J53" s="9">
-        <v>49.49</v>
+        <v>40.520000000000003</v>
       </c>
       <c r="K53" s="8">
-        <v>6583263.0800000001</v>
+        <v>6570040.0800000001</v>
       </c>
       <c r="L53" s="9">
-        <v>73.75</v>
+        <v>73.599999999999994</v>
       </c>
       <c r="M53" s="8">
-        <v>2342975.94</v>
+        <v>2356198.94</v>
       </c>
       <c r="N53" s="9">
-        <v>26.25</v>
+        <v>26.4</v>
       </c>
       <c r="O53" s="8">
         <v>15000</v>
@@ -22084,13 +22093,13 @@
         <v>0.17</v>
       </c>
       <c r="Q53" s="8">
-        <v>2327975.94</v>
+        <v>2341198.94</v>
       </c>
       <c r="R53" s="9">
-        <v>26.08</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
+        <v>26.23</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
         <v>362</v>
       </c>
@@ -22110,7 +22119,7 @@
         <v>1564125</v>
       </c>
       <c r="G54" s="8">
-        <v>950429.96</v>
+        <v>950434.96</v>
       </c>
       <c r="H54" s="9">
         <v>60.76</v>
@@ -22122,13 +22131,13 @@
         <v>37.53</v>
       </c>
       <c r="K54" s="8">
-        <v>1537426.63</v>
+        <v>1537431.63</v>
       </c>
       <c r="L54" s="9">
         <v>98.29</v>
       </c>
       <c r="M54" s="8">
-        <v>26698.37</v>
+        <v>26693.37</v>
       </c>
       <c r="N54" s="9">
         <v>1.71</v>
@@ -22140,7 +22149,7 @@
         <v>0.54</v>
       </c>
       <c r="Q54" s="8">
-        <v>18198.37</v>
+        <v>18193.37</v>
       </c>
       <c r="R54" s="9">
         <v>1.1599999999999999</v>
@@ -22202,7 +22211,7 @@
         <v>42.14</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="66" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
         <v>398</v>
       </c>
@@ -22222,13 +22231,13 @@
         <v>12829676.84</v>
       </c>
       <c r="G56" s="8">
-        <v>3028932.91</v>
+        <v>3028982.91</v>
       </c>
       <c r="H56" s="9">
         <v>23.61</v>
       </c>
       <c r="I56" s="8">
-        <v>976431.56</v>
+        <v>976381.56</v>
       </c>
       <c r="J56" s="9">
         <v>7.61</v>
@@ -22258,7 +22267,7 @@
         <v>68.709999999999994</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="132" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" ht="118.8" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
         <v>422</v>
       </c>
@@ -22278,43 +22287,43 @@
         <v>18605882.420000002</v>
       </c>
       <c r="G57" s="8">
-        <v>3185402.03</v>
+        <v>3185427.03</v>
       </c>
       <c r="H57" s="9">
         <v>17.12</v>
       </c>
       <c r="I57" s="8">
-        <v>2607311</v>
+        <v>3407311</v>
       </c>
       <c r="J57" s="9">
-        <v>14.01</v>
+        <v>18.309999999999999</v>
       </c>
       <c r="K57" s="8">
-        <v>5792713.0300000003</v>
+        <v>6592738.0300000003</v>
       </c>
       <c r="L57" s="9">
-        <v>31.13</v>
+        <v>35.43</v>
       </c>
       <c r="M57" s="8">
-        <v>12813169.390000001</v>
+        <v>12013144.390000001</v>
       </c>
       <c r="N57" s="9">
-        <v>68.87</v>
+        <v>64.569999999999993</v>
       </c>
       <c r="O57" s="8">
-        <v>3325000</v>
+        <v>2525000</v>
       </c>
       <c r="P57" s="9">
-        <v>17.87</v>
+        <v>13.57</v>
       </c>
       <c r="Q57" s="8">
-        <v>9488169.3900000006</v>
+        <v>9488144.3900000006</v>
       </c>
       <c r="R57" s="9">
         <v>51</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" ht="66" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
         <v>460</v>
       </c>
@@ -22334,7 +22343,7 @@
         <v>1603085.31</v>
       </c>
       <c r="G58" s="8">
-        <v>1115930</v>
+        <v>1115935</v>
       </c>
       <c r="H58" s="9">
         <v>69.61</v>
@@ -22346,13 +22355,13 @@
         <v>0.01</v>
       </c>
       <c r="K58" s="8">
-        <v>1116020</v>
+        <v>1116025</v>
       </c>
       <c r="L58" s="9">
         <v>69.62</v>
       </c>
       <c r="M58" s="8">
-        <v>487065.31</v>
+        <v>487060.31</v>
       </c>
       <c r="N58" s="9">
         <v>30.38</v>
@@ -22364,7 +22373,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="8">
-        <v>487065.31</v>
+        <v>487060.31</v>
       </c>
       <c r="R58" s="9">
         <v>30.38</v>
@@ -22390,10 +22399,10 @@
         <v>1995235</v>
       </c>
       <c r="G59" s="8">
-        <v>1976130.3</v>
+        <v>2152090.2999999998</v>
       </c>
       <c r="H59" s="9">
-        <v>99.04</v>
+        <v>107.86</v>
       </c>
       <c r="I59" s="8">
         <v>485</v>
@@ -22402,16 +22411,16 @@
         <v>0.02</v>
       </c>
       <c r="K59" s="8">
-        <v>1976615.3</v>
+        <v>2152575.2999999998</v>
       </c>
       <c r="L59" s="9">
-        <v>99.07</v>
+        <v>107.89</v>
       </c>
       <c r="M59" s="8">
-        <v>18619.7</v>
+        <v>-157340.29999999999</v>
       </c>
       <c r="N59" s="9">
-        <v>0.93</v>
+        <v>-7.89</v>
       </c>
       <c r="O59" s="8">
         <v>0</v>
@@ -22420,13 +22429,13 @@
         <v>0</v>
       </c>
       <c r="Q59" s="8">
-        <v>18619.7</v>
+        <v>-157340.29999999999</v>
       </c>
       <c r="R59" s="9">
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="60" spans="1:18" ht="66" x14ac:dyDescent="0.25">
+        <v>-7.89</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
         <v>492</v>
       </c>
@@ -22446,28 +22455,28 @@
         <v>2528000</v>
       </c>
       <c r="G60" s="8">
-        <v>991389.84</v>
+        <v>1002889.84</v>
       </c>
       <c r="H60" s="9">
-        <v>39.22</v>
+        <v>39.67</v>
       </c>
       <c r="I60" s="8">
-        <v>295610</v>
+        <v>584920</v>
       </c>
       <c r="J60" s="9">
-        <v>11.69</v>
+        <v>23.14</v>
       </c>
       <c r="K60" s="8">
-        <v>1286999.8400000001</v>
+        <v>1587809.84</v>
       </c>
       <c r="L60" s="9">
-        <v>50.91</v>
+        <v>62.81</v>
       </c>
       <c r="M60" s="8">
-        <v>1241000.1599999999</v>
+        <v>940190.16</v>
       </c>
       <c r="N60" s="9">
-        <v>49.09</v>
+        <v>37.19</v>
       </c>
       <c r="O60" s="8">
         <v>20000</v>
@@ -22476,13 +22485,13 @@
         <v>0.79</v>
       </c>
       <c r="Q60" s="8">
-        <v>1221000.1599999999</v>
+        <v>920190.16</v>
       </c>
       <c r="R60" s="9">
-        <v>48.3</v>
-      </c>
-    </row>
-    <row r="61" spans="1:18" ht="92.4" x14ac:dyDescent="0.25">
+        <v>36.4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
         <v>508</v>
       </c>
@@ -22502,43 +22511,43 @@
         <v>1500000</v>
       </c>
       <c r="G61" s="8">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="H61" s="9">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="I61" s="8">
-        <v>225000</v>
+        <v>225300</v>
       </c>
       <c r="J61" s="9">
-        <v>15</v>
+        <v>15.02</v>
       </c>
       <c r="K61" s="8">
-        <v>225000</v>
+        <v>226200</v>
       </c>
       <c r="L61" s="9">
-        <v>15</v>
+        <v>15.08</v>
       </c>
       <c r="M61" s="8">
-        <v>1275000</v>
+        <v>1273800</v>
       </c>
       <c r="N61" s="9">
-        <v>85</v>
+        <v>84.92</v>
       </c>
       <c r="O61" s="8">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="P61" s="9">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="Q61" s="8">
-        <v>1275000</v>
+        <v>1173800</v>
       </c>
       <c r="R61" s="9">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" ht="105.6" x14ac:dyDescent="0.25">
+        <v>78.25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
         <v>523</v>
       </c>
@@ -22558,28 +22567,28 @@
         <v>19811100</v>
       </c>
       <c r="G62" s="8">
-        <v>3710261.97</v>
+        <v>4310276.97</v>
       </c>
       <c r="H62" s="9">
-        <v>18.73</v>
+        <v>21.76</v>
       </c>
       <c r="I62" s="8">
-        <v>3915288.03</v>
+        <v>4515288.03</v>
       </c>
       <c r="J62" s="9">
-        <v>19.760000000000002</v>
+        <v>22.79</v>
       </c>
       <c r="K62" s="8">
-        <v>7625550</v>
+        <v>8825565</v>
       </c>
       <c r="L62" s="9">
-        <v>38.49</v>
+        <v>44.55</v>
       </c>
       <c r="M62" s="8">
-        <v>12185550</v>
+        <v>10985535</v>
       </c>
       <c r="N62" s="9">
-        <v>61.51</v>
+        <v>55.45</v>
       </c>
       <c r="O62" s="8">
         <v>0</v>
@@ -22588,10 +22597,10 @@
         <v>0</v>
       </c>
       <c r="Q62" s="8">
-        <v>12185550</v>
+        <v>10985535</v>
       </c>
       <c r="R62" s="9">
-        <v>61.51</v>
+        <v>55.45</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
@@ -22606,46 +22615,46 @@
         <v>74571</v>
       </c>
       <c r="E63" s="14">
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="F63" s="14">
-        <v>101372727.95</v>
+        <v>101370977.95</v>
       </c>
       <c r="G63" s="14">
-        <v>30562243.989999998</v>
+        <v>32165960.289999999</v>
       </c>
       <c r="H63" s="15">
-        <v>30.15</v>
+        <v>31.73</v>
       </c>
       <c r="I63" s="14">
-        <v>16385336.68</v>
+        <v>17954117.379999999</v>
       </c>
       <c r="J63" s="15">
-        <v>16.16</v>
+        <v>17.71</v>
       </c>
       <c r="K63" s="14">
-        <v>46947580.670000002</v>
+        <v>50120077.670000002</v>
       </c>
       <c r="L63" s="15">
-        <v>46.31</v>
+        <v>49.44</v>
       </c>
       <c r="M63" s="14">
-        <v>54425147.280000001</v>
+        <v>51250900.280000001</v>
       </c>
       <c r="N63" s="15">
-        <v>53.69</v>
+        <v>50.56</v>
       </c>
       <c r="O63" s="14">
-        <v>4679593</v>
+        <v>3509593</v>
       </c>
       <c r="P63" s="15">
-        <v>4.62</v>
+        <v>3.46</v>
       </c>
       <c r="Q63" s="14">
-        <v>49745554.280000001</v>
+        <v>47741307.280000001</v>
       </c>
       <c r="R63" s="15">
-        <v>49.07</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
@@ -22657,49 +22666,49 @@
         <v>332000356.94999999</v>
       </c>
       <c r="D64" s="16">
-        <v>74571</v>
+        <v>374571</v>
       </c>
       <c r="E64" s="16">
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="F64" s="16">
-        <v>332074927.94999999</v>
+        <v>332373177.94999999</v>
       </c>
       <c r="G64" s="16">
-        <v>191203422.41999999</v>
+        <v>195957149.46000001</v>
       </c>
       <c r="H64" s="17">
-        <v>57.58</v>
+        <v>58.96</v>
       </c>
       <c r="I64" s="16">
-        <v>46623359.5</v>
+        <v>50912567.140000001</v>
       </c>
       <c r="J64" s="17">
-        <v>14.04</v>
+        <v>15.32</v>
       </c>
       <c r="K64" s="16">
-        <v>237826781.91999999</v>
+        <v>246869716.59999999</v>
       </c>
       <c r="L64" s="17">
-        <v>71.62</v>
+        <v>74.27</v>
       </c>
       <c r="M64" s="16">
-        <v>94248146.030000001</v>
+        <v>85503461.349999994</v>
       </c>
       <c r="N64" s="17">
-        <v>28.38</v>
+        <v>25.73</v>
       </c>
       <c r="O64" s="16">
-        <v>16221741.67</v>
+        <v>14600179.210000001</v>
       </c>
       <c r="P64" s="17">
-        <v>4.88</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="Q64" s="16">
-        <v>78026404.359999999</v>
+        <v>70903282.140000001</v>
       </c>
       <c r="R64" s="17">
-        <v>23.5</v>
+        <v>21.33</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
@@ -22714,10 +22723,10 @@
         <v>0</v>
       </c>
       <c r="E65" s="4">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="F65" s="4">
-        <v>6655580.1799999997</v>
+        <v>6355580.1799999997</v>
       </c>
       <c r="G65" s="4">
         <v>0</v>
@@ -22738,7 +22747,7 @@
         <v>0</v>
       </c>
       <c r="M65" s="4">
-        <v>6655580.1799999997</v>
+        <v>6355580.1799999997</v>
       </c>
       <c r="N65" s="5">
         <v>100</v>
@@ -22750,7 +22759,7 @@
         <v>0</v>
       </c>
       <c r="Q65" s="4">
-        <v>6655580.1799999997</v>
+        <v>6355580.1799999997</v>
       </c>
       <c r="R65" s="5">
         <v>100</v>
@@ -22770,10 +22779,10 @@
         <v>0</v>
       </c>
       <c r="E66" s="8">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="F66" s="8">
-        <v>6655580.1799999997</v>
+        <v>6355580.1799999997</v>
       </c>
       <c r="G66" s="8">
         <v>0</v>
@@ -22794,7 +22803,7 @@
         <v>0</v>
       </c>
       <c r="M66" s="8">
-        <v>6655580.1799999997</v>
+        <v>6355580.1799999997</v>
       </c>
       <c r="N66" s="9">
         <v>100</v>
@@ -22806,7 +22815,7 @@
         <v>0</v>
       </c>
       <c r="Q66" s="8">
-        <v>6655580.1799999997</v>
+        <v>6355580.1799999997</v>
       </c>
       <c r="R66" s="9">
         <v>100</v>
@@ -22824,10 +22833,10 @@
         <v>0</v>
       </c>
       <c r="E67" s="14">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="F67" s="14">
-        <v>6655580.1799999997</v>
+        <v>6355580.1799999997</v>
       </c>
       <c r="G67" s="14">
         <v>0</v>
@@ -22848,7 +22857,7 @@
         <v>0</v>
       </c>
       <c r="M67" s="14">
-        <v>6655580.1799999997</v>
+        <v>6355580.1799999997</v>
       </c>
       <c r="N67" s="15">
         <v>100</v>
@@ -22860,7 +22869,7 @@
         <v>0</v>
       </c>
       <c r="Q67" s="14">
-        <v>6655580.1799999997</v>
+        <v>6355580.1799999997</v>
       </c>
       <c r="R67" s="15">
         <v>100</v>
@@ -22875,49 +22884,49 @@
         <v>338655937.13</v>
       </c>
       <c r="D68" s="16">
-        <v>74571</v>
+        <v>374571</v>
       </c>
       <c r="E68" s="16">
-        <v>0</v>
+        <v>301750</v>
       </c>
       <c r="F68" s="16">
-        <v>338730508.13</v>
+        <v>338728758.13</v>
       </c>
       <c r="G68" s="16">
-        <v>191203422.41999999</v>
+        <v>195957149.46000001</v>
       </c>
       <c r="H68" s="17">
-        <v>56.45</v>
+        <v>57.85</v>
       </c>
       <c r="I68" s="16">
-        <v>46623359.5</v>
+        <v>50912567.140000001</v>
       </c>
       <c r="J68" s="17">
-        <v>13.76</v>
+        <v>15.03</v>
       </c>
       <c r="K68" s="16">
-        <v>237826781.91999999</v>
+        <v>246869716.59999999</v>
       </c>
       <c r="L68" s="17">
-        <v>70.209999999999994</v>
+        <v>72.88</v>
       </c>
       <c r="M68" s="16">
-        <v>100903726.20999999</v>
+        <v>91859041.530000001</v>
       </c>
       <c r="N68" s="17">
-        <v>29.79</v>
+        <v>27.12</v>
       </c>
       <c r="O68" s="16">
-        <v>16221741.67</v>
+        <v>14600179.210000001</v>
       </c>
       <c r="P68" s="17">
-        <v>4.79</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="Q68" s="16">
-        <v>84681984.540000007</v>
+        <v>77258862.319999993</v>
       </c>
       <c r="R68" s="17">
-        <v>25</v>
+        <v>22.81</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
@@ -22929,25 +22938,25 @@
         <v>4037940.24</v>
       </c>
       <c r="D69" s="4">
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="E69" s="4">
         <v>74571</v>
       </c>
       <c r="F69" s="4">
-        <v>3963369.24</v>
+        <v>3965119.24</v>
       </c>
       <c r="G69" s="4">
-        <v>607139.18000000005</v>
+        <v>607169.18000000005</v>
       </c>
       <c r="H69" s="5">
-        <v>15.32</v>
+        <v>15.31</v>
       </c>
       <c r="I69" s="4">
-        <v>108413.7</v>
+        <v>108383.7</v>
       </c>
       <c r="J69" s="5">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="K69" s="4">
         <v>715552.88</v>
@@ -22956,7 +22965,7 @@
         <v>18.05</v>
       </c>
       <c r="M69" s="4">
-        <v>3247816.36</v>
+        <v>3249566.36</v>
       </c>
       <c r="N69" s="5">
         <v>81.95</v>
@@ -22968,10 +22977,10 @@
         <v>0.15</v>
       </c>
       <c r="Q69" s="4">
-        <v>3241687.24</v>
+        <v>3243437.24</v>
       </c>
       <c r="R69" s="5">
-        <v>81.790000000000006</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
@@ -22985,25 +22994,25 @@
         <v>4037940.24</v>
       </c>
       <c r="D70" s="8">
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="E70" s="8">
         <v>74571</v>
       </c>
       <c r="F70" s="8">
-        <v>3963369.24</v>
+        <v>3965119.24</v>
       </c>
       <c r="G70" s="8">
-        <v>607139.18000000005</v>
+        <v>607169.18000000005</v>
       </c>
       <c r="H70" s="9">
-        <v>15.32</v>
+        <v>15.31</v>
       </c>
       <c r="I70" s="8">
-        <v>108413.7</v>
+        <v>108383.7</v>
       </c>
       <c r="J70" s="9">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="K70" s="8">
         <v>715552.88</v>
@@ -23012,7 +23021,7 @@
         <v>18.05</v>
       </c>
       <c r="M70" s="8">
-        <v>3247816.36</v>
+        <v>3249566.36</v>
       </c>
       <c r="N70" s="9">
         <v>81.95</v>
@@ -23024,10 +23033,10 @@
         <v>0.15</v>
       </c>
       <c r="Q70" s="8">
-        <v>3241687.24</v>
+        <v>3243437.24</v>
       </c>
       <c r="R70" s="9">
-        <v>81.790000000000006</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
@@ -23039,25 +23048,25 @@
         <v>4037940.24</v>
       </c>
       <c r="D71" s="14">
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="E71" s="14">
         <v>74571</v>
       </c>
       <c r="F71" s="14">
-        <v>3963369.24</v>
+        <v>3965119.24</v>
       </c>
       <c r="G71" s="14">
-        <v>607139.18000000005</v>
+        <v>607169.18000000005</v>
       </c>
       <c r="H71" s="15">
-        <v>15.32</v>
+        <v>15.31</v>
       </c>
       <c r="I71" s="14">
-        <v>108413.7</v>
+        <v>108383.7</v>
       </c>
       <c r="J71" s="15">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="K71" s="14">
         <v>715552.88</v>
@@ -23066,7 +23075,7 @@
         <v>18.05</v>
       </c>
       <c r="M71" s="14">
-        <v>3247816.36</v>
+        <v>3249566.36</v>
       </c>
       <c r="N71" s="15">
         <v>81.95</v>
@@ -23078,10 +23087,10 @@
         <v>0.15</v>
       </c>
       <c r="Q71" s="14">
-        <v>3241687.24</v>
+        <v>3243437.24</v>
       </c>
       <c r="R71" s="15">
-        <v>81.790000000000006</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
@@ -23093,49 +23102,49 @@
         <v>342693877.37</v>
       </c>
       <c r="D72" s="16">
-        <v>74571</v>
+        <v>376321</v>
       </c>
       <c r="E72" s="16">
-        <v>74571</v>
+        <v>376321</v>
       </c>
       <c r="F72" s="16">
         <v>342693877.37</v>
       </c>
       <c r="G72" s="16">
-        <v>191810561.59999999</v>
+        <v>196564318.63999999</v>
       </c>
       <c r="H72" s="17">
-        <v>55.97</v>
+        <v>57.36</v>
       </c>
       <c r="I72" s="16">
-        <v>46731773.200000003</v>
+        <v>51020950.840000004</v>
       </c>
       <c r="J72" s="17">
-        <v>13.64</v>
+        <v>14.89</v>
       </c>
       <c r="K72" s="16">
-        <v>238542334.80000001</v>
+        <v>247585269.47999999</v>
       </c>
       <c r="L72" s="17">
-        <v>69.61</v>
+        <v>72.25</v>
       </c>
       <c r="M72" s="16">
-        <v>104151542.56999999</v>
+        <v>95108607.890000001</v>
       </c>
       <c r="N72" s="17">
-        <v>30.39</v>
+        <v>27.75</v>
       </c>
       <c r="O72" s="16">
-        <v>16227870.789999999</v>
+        <v>14606308.33</v>
       </c>
       <c r="P72" s="17">
-        <v>4.74</v>
+        <v>4.26</v>
       </c>
       <c r="Q72" s="16">
-        <v>87923671.780000001</v>
+        <v>80502299.560000002</v>
       </c>
       <c r="R72" s="17">
-        <v>25.66</v>
+        <v>23.49</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
@@ -23210,28 +23219,28 @@
         <v>1000000</v>
       </c>
       <c r="G74" s="19">
-        <v>533379</v>
+        <v>543339</v>
       </c>
       <c r="H74" s="20">
-        <v>53.34</v>
+        <v>54.33</v>
       </c>
       <c r="I74" s="19">
-        <v>31620</v>
+        <v>54620</v>
       </c>
       <c r="J74" s="20">
-        <v>3.16</v>
+        <v>5.46</v>
       </c>
       <c r="K74" s="19">
-        <v>564999</v>
+        <v>597959</v>
       </c>
       <c r="L74" s="20">
-        <v>56.5</v>
+        <v>59.8</v>
       </c>
       <c r="M74" s="19">
-        <v>435001</v>
+        <v>402041</v>
       </c>
       <c r="N74" s="20">
-        <v>43.5</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="O74" s="19">
         <v>0</v>
@@ -23240,10 +23249,10 @@
         <v>0</v>
       </c>
       <c r="Q74" s="19">
-        <v>435001</v>
+        <v>402041</v>
       </c>
       <c r="R74" s="20">
-        <v>43.5</v>
+        <v>40.200000000000003</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
@@ -23264,40 +23273,40 @@
         <v>12535870.93</v>
       </c>
       <c r="G75" s="19">
-        <v>8527246.0500000007</v>
+        <v>8909626.0500000007</v>
       </c>
       <c r="H75" s="20">
-        <v>68.02</v>
+        <v>71.069999999999993</v>
       </c>
       <c r="I75" s="19">
-        <v>1281876</v>
+        <v>1415896</v>
       </c>
       <c r="J75" s="20">
-        <v>10.23</v>
+        <v>11.29</v>
       </c>
       <c r="K75" s="19">
-        <v>9809122.0500000007</v>
+        <v>10325522.050000001</v>
       </c>
       <c r="L75" s="20">
-        <v>78.25</v>
+        <v>82.37</v>
       </c>
       <c r="M75" s="19">
-        <v>2726748.88</v>
+        <v>2210348.88</v>
       </c>
       <c r="N75" s="20">
-        <v>21.75</v>
+        <v>17.63</v>
       </c>
       <c r="O75" s="19">
-        <v>30600</v>
+        <v>80600</v>
       </c>
       <c r="P75" s="20">
-        <v>0.24</v>
+        <v>0.64</v>
       </c>
       <c r="Q75" s="19">
-        <v>2696148.88</v>
+        <v>2129748.88</v>
       </c>
       <c r="R75" s="20">
-        <v>21.51</v>
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
@@ -23318,28 +23327,28 @@
         <v>13373180.710000001</v>
       </c>
       <c r="G76" s="19">
-        <v>8855985.1600000001</v>
+        <v>9301520.1600000001</v>
       </c>
       <c r="H76" s="20">
-        <v>66.22</v>
+        <v>69.55</v>
       </c>
       <c r="I76" s="19">
-        <v>648546</v>
+        <v>1198211</v>
       </c>
       <c r="J76" s="20">
-        <v>4.8499999999999996</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="K76" s="19">
-        <v>9504531.1600000001</v>
+        <v>10499731.16</v>
       </c>
       <c r="L76" s="20">
-        <v>71.069999999999993</v>
+        <v>78.510000000000005</v>
       </c>
       <c r="M76" s="19">
-        <v>3868649.55</v>
+        <v>2873449.55</v>
       </c>
       <c r="N76" s="20">
-        <v>28.93</v>
+        <v>21.49</v>
       </c>
       <c r="O76" s="19">
         <v>13307</v>
@@ -23348,10 +23357,10 @@
         <v>0.1</v>
       </c>
       <c r="Q76" s="19">
-        <v>3855342.55</v>
+        <v>2860142.55</v>
       </c>
       <c r="R76" s="20">
-        <v>28.83</v>
+        <v>21.39</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
@@ -23366,46 +23375,46 @@
         <v>0</v>
       </c>
       <c r="E77" s="19">
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="F77" s="19">
-        <v>14776703.779999999</v>
+        <v>14774953.779999999</v>
       </c>
       <c r="G77" s="19">
-        <v>11277687.039999999</v>
+        <v>11625606.33</v>
       </c>
       <c r="H77" s="20">
-        <v>76.319999999999993</v>
+        <v>78.680000000000007</v>
       </c>
       <c r="I77" s="19">
-        <v>1350599.67</v>
+        <v>1294355.3799999999</v>
       </c>
       <c r="J77" s="20">
-        <v>9.14</v>
+        <v>8.76</v>
       </c>
       <c r="K77" s="19">
-        <v>12628286.710000001</v>
+        <v>12919961.710000001</v>
       </c>
       <c r="L77" s="20">
-        <v>85.46</v>
+        <v>87.45</v>
       </c>
       <c r="M77" s="19">
-        <v>2148417.0699999998</v>
+        <v>1854992.07</v>
       </c>
       <c r="N77" s="20">
-        <v>14.54</v>
+        <v>12.55</v>
       </c>
       <c r="O77" s="19">
-        <v>110079.5</v>
+        <v>30079.5</v>
       </c>
       <c r="P77" s="20">
-        <v>0.74</v>
+        <v>0.2</v>
       </c>
       <c r="Q77" s="19">
-        <v>2038337.57</v>
+        <v>1824912.57</v>
       </c>
       <c r="R77" s="20">
-        <v>13.79</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
@@ -23426,40 +23435,40 @@
         <v>30422752.809999999</v>
       </c>
       <c r="G78" s="19">
-        <v>14859434.33</v>
+        <v>15541612.630000001</v>
       </c>
       <c r="H78" s="20">
-        <v>48.84</v>
+        <v>51.09</v>
       </c>
       <c r="I78" s="19">
-        <v>4139142.42</v>
+        <v>5472809.1200000001</v>
       </c>
       <c r="J78" s="20">
-        <v>13.61</v>
+        <v>17.989999999999998</v>
       </c>
       <c r="K78" s="19">
-        <v>18998576.75</v>
+        <v>21014421.75</v>
       </c>
       <c r="L78" s="20">
-        <v>62.45</v>
+        <v>69.069999999999993</v>
       </c>
       <c r="M78" s="19">
-        <v>11424176.060000001</v>
+        <v>9408331.0600000005</v>
       </c>
       <c r="N78" s="20">
-        <v>37.549999999999997</v>
+        <v>30.93</v>
       </c>
       <c r="O78" s="19">
-        <v>1732093</v>
+        <v>782093</v>
       </c>
       <c r="P78" s="20">
-        <v>5.69</v>
+        <v>2.57</v>
       </c>
       <c r="Q78" s="19">
-        <v>9692083.0600000005</v>
+        <v>8626238.0600000005</v>
       </c>
       <c r="R78" s="20">
-        <v>31.86</v>
+        <v>28.35</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
@@ -23480,40 +23489,40 @@
         <v>13420000</v>
       </c>
       <c r="G79" s="19">
-        <v>10751421.42</v>
+        <v>11285252.42</v>
       </c>
       <c r="H79" s="20">
-        <v>80.11</v>
+        <v>84.09</v>
       </c>
       <c r="I79" s="19">
-        <v>751226</v>
+        <v>1085194.7</v>
       </c>
       <c r="J79" s="20">
-        <v>5.6</v>
+        <v>8.09</v>
       </c>
       <c r="K79" s="19">
-        <v>11502647.42</v>
+        <v>12370447.119999999</v>
       </c>
       <c r="L79" s="20">
-        <v>85.71</v>
+        <v>92.18</v>
       </c>
       <c r="M79" s="19">
-        <v>1917352.58</v>
+        <v>1049552.8799999999</v>
       </c>
       <c r="N79" s="20">
-        <v>14.29</v>
+        <v>7.82</v>
       </c>
       <c r="O79" s="19">
-        <v>497000</v>
+        <v>382034.3</v>
       </c>
       <c r="P79" s="20">
-        <v>3.7</v>
+        <v>2.85</v>
       </c>
       <c r="Q79" s="19">
-        <v>1420352.58</v>
+        <v>667518.57999999996</v>
       </c>
       <c r="R79" s="20">
-        <v>10.58</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
@@ -23525,49 +23534,49 @@
         <v>111264940.23999999</v>
       </c>
       <c r="D80" s="19">
-        <v>0</v>
+        <v>301750</v>
       </c>
       <c r="E80" s="19">
         <v>74571</v>
       </c>
       <c r="F80" s="19">
-        <v>111190369.23999999</v>
+        <v>111492119.23999999</v>
       </c>
       <c r="G80" s="19">
-        <v>83996654.310000002</v>
+        <v>84104125.459999993</v>
       </c>
       <c r="H80" s="20">
-        <v>75.540000000000006</v>
+        <v>75.44</v>
       </c>
       <c r="I80" s="19">
-        <v>5226383.58</v>
+        <v>5437196.2599999998</v>
       </c>
       <c r="J80" s="20">
-        <v>4.7</v>
+        <v>4.88</v>
       </c>
       <c r="K80" s="19">
-        <v>89223037.890000001</v>
+        <v>89541321.719999999</v>
       </c>
       <c r="L80" s="20">
-        <v>80.239999999999995</v>
+        <v>80.31</v>
       </c>
       <c r="M80" s="19">
-        <v>21967331.350000001</v>
+        <v>21950797.52</v>
       </c>
       <c r="N80" s="20">
-        <v>19.760000000000002</v>
+        <v>19.690000000000001</v>
       </c>
       <c r="O80" s="19">
         <v>5013094.99</v>
       </c>
       <c r="P80" s="20">
-        <v>4.51</v>
+        <v>4.5</v>
       </c>
       <c r="Q80" s="19">
-        <v>16954236.359999999</v>
+        <v>16937702.530000001</v>
       </c>
       <c r="R80" s="20">
-        <v>15.25</v>
+        <v>15.19</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
@@ -23594,34 +23603,34 @@
         <v>42.72</v>
       </c>
       <c r="I81" s="19">
-        <v>428863.16</v>
+        <v>913209.17</v>
       </c>
       <c r="J81" s="20">
-        <v>8.69</v>
+        <v>18.5</v>
       </c>
       <c r="K81" s="19">
-        <v>2537734.1</v>
+        <v>3022080.11</v>
       </c>
       <c r="L81" s="20">
-        <v>51.41</v>
+        <v>61.23</v>
       </c>
       <c r="M81" s="19">
-        <v>2398194.7000000002</v>
+        <v>1913848.69</v>
       </c>
       <c r="N81" s="20">
-        <v>48.59</v>
+        <v>38.770000000000003</v>
       </c>
       <c r="O81" s="19">
-        <v>394000</v>
+        <v>390000</v>
       </c>
       <c r="P81" s="20">
-        <v>7.98</v>
+        <v>7.9</v>
       </c>
       <c r="Q81" s="19">
-        <v>2004194.7</v>
+        <v>1523848.69</v>
       </c>
       <c r="R81" s="20">
-        <v>40.6</v>
+        <v>30.87</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
@@ -23636,46 +23645,46 @@
         <v>0</v>
       </c>
       <c r="E82" s="19">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="F82" s="19">
-        <v>140039071.09999999</v>
+        <v>139739071.09999999</v>
       </c>
       <c r="G82" s="19">
-        <v>50077931.609999999</v>
+        <v>52322413.909999996</v>
       </c>
       <c r="H82" s="20">
-        <v>35.76</v>
+        <v>37.44</v>
       </c>
       <c r="I82" s="19">
-        <v>32757974.370000001</v>
+        <v>34033917.210000001</v>
       </c>
       <c r="J82" s="20">
-        <v>23.39</v>
+        <v>24.36</v>
       </c>
       <c r="K82" s="19">
-        <v>82835905.980000004</v>
+        <v>86356331.120000005</v>
       </c>
       <c r="L82" s="20">
-        <v>59.15</v>
+        <v>61.8</v>
       </c>
       <c r="M82" s="19">
-        <v>57203165.119999997</v>
+        <v>53382739.979999997</v>
       </c>
       <c r="N82" s="20">
-        <v>40.85</v>
+        <v>38.200000000000003</v>
       </c>
       <c r="O82" s="19">
-        <v>8437696.3000000007</v>
+        <v>7915099.54</v>
       </c>
       <c r="P82" s="20">
-        <v>6.03</v>
+        <v>5.66</v>
       </c>
       <c r="Q82" s="19">
-        <v>48765468.82</v>
+        <v>45467640.439999998</v>
       </c>
       <c r="R82" s="20">
-        <v>34.82</v>
+        <v>32.54</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
@@ -23687,49 +23696,49 @@
         <v>342693877.37</v>
       </c>
       <c r="D83" s="19">
-        <v>74571</v>
+        <v>376321</v>
       </c>
       <c r="E83" s="19">
-        <v>74571</v>
+        <v>376321</v>
       </c>
       <c r="F83" s="19">
         <v>342693877.37</v>
       </c>
       <c r="G83" s="19">
-        <v>191810561.59999999</v>
+        <v>196564318.63999999</v>
       </c>
       <c r="H83" s="20">
-        <v>55.97</v>
+        <v>57.36</v>
       </c>
       <c r="I83" s="19">
-        <v>46731773.200000003</v>
+        <v>51020950.840000004</v>
       </c>
       <c r="J83" s="20">
-        <v>13.64</v>
+        <v>14.89</v>
       </c>
       <c r="K83" s="19">
-        <v>238542334.80000001</v>
+        <v>247585269.47999999</v>
       </c>
       <c r="L83" s="20">
-        <v>69.61</v>
+        <v>72.25</v>
       </c>
       <c r="M83" s="19">
-        <v>104151542.56999999</v>
+        <v>95108607.890000001</v>
       </c>
       <c r="N83" s="20">
-        <v>30.39</v>
+        <v>27.75</v>
       </c>
       <c r="O83" s="19">
-        <v>16227870.789999999</v>
+        <v>14606308.33</v>
       </c>
       <c r="P83" s="20">
-        <v>4.74</v>
+        <v>4.26</v>
       </c>
       <c r="Q83" s="19">
-        <v>87923671.780000001</v>
+        <v>80502299.560000002</v>
       </c>
       <c r="R83" s="20">
-        <v>25.66</v>
+        <v>23.49</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
@@ -23765,6 +23774,7 @@
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="G4:H4"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>